--- a/data/france/p6_deployment/data_preparation/df_tagged.xlsx
+++ b/data/france/p6_deployment/data_preparation/df_tagged.xlsx
@@ -520,57 +520,57 @@
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_val_player_start</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_start</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_sub</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_sub</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_sub</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_start</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_sub</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_start</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_start</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_sub</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_hei_player_start</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_start</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_start</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_start</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_sub</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_start</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_sub</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_start</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_sub</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_sub</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_sub</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
@@ -771,37 +771,37 @@
         <v>-2</v>
       </c>
       <c r="S2" t="n">
-        <v>2.719642857142816</v>
+        <v>-11534228.8961039</v>
       </c>
       <c r="T2" t="n">
         <v>0.05162337662337535</v>
       </c>
       <c r="U2" t="n">
+        <v>-0.3747165532879819</v>
+      </c>
+      <c r="V2" t="n">
+        <v>-9.022119745334038</v>
+      </c>
+      <c r="W2" t="n">
+        <v>-5720895.473574045</v>
+      </c>
+      <c r="X2" t="n">
+        <v>-0.4025974025974028</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>-6.515774899703459</v>
+      </c>
+      <c r="Z2" t="n">
         <v>-8.279220779220779</v>
       </c>
-      <c r="V2" t="n">
-        <v>-11534228.8961039</v>
-      </c>
-      <c r="W2" t="n">
-        <v>-0.3747165532879819</v>
-      </c>
-      <c r="X2" t="n">
+      <c r="AA2" t="n">
         <v>-7.081980519480524</v>
       </c>
-      <c r="Y2" t="n">
+      <c r="AB2" t="n">
         <v>4.636490493633374</v>
       </c>
-      <c r="Z2" t="n">
-        <v>-0.4025974025974028</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>-6.515774899703459</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>-5720895.473574045</v>
-      </c>
       <c r="AC2" t="n">
-        <v>-9.022119745334038</v>
+        <v>2.719642857142816</v>
       </c>
       <c r="AD2" t="n">
         <v>-1.740602651316937</v>
@@ -897,37 +897,37 @@
         <v>2</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.9500721500720886</v>
+        <v>839134.1991341989</v>
       </c>
       <c r="T3" t="n">
         <v>2.505772005772009</v>
       </c>
       <c r="U3" t="n">
+        <v>-0.08543577966303584</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.6642355939031006</v>
+      </c>
+      <c r="W3" t="n">
+        <v>138185.9678096436</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0.1305916305916306</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>-1.128653512687123</v>
+      </c>
+      <c r="Z3" t="n">
         <v>1.542279942279947</v>
       </c>
-      <c r="V3" t="n">
-        <v>839134.1991341989</v>
-      </c>
-      <c r="W3" t="n">
-        <v>-0.08543577966303584</v>
-      </c>
-      <c r="X3" t="n">
+      <c r="AA3" t="n">
         <v>-1.494660894660896</v>
       </c>
-      <c r="Y3" t="n">
+      <c r="AB3" t="n">
         <v>-1.105491115063614</v>
       </c>
-      <c r="Z3" t="n">
-        <v>0.1305916305916306</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>-1.128653512687123</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>138185.9678096436</v>
-      </c>
       <c r="AC3" t="n">
-        <v>0.6642355939031006</v>
+        <v>-0.9500721500720886</v>
       </c>
       <c r="AD3" t="n">
         <v>0.9826989881794361</v>
@@ -1023,37 +1023,37 @@
         <v>1</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.7889971139970839</v>
+        <v>644700.5772005767</v>
       </c>
       <c r="T4" t="n">
         <v>-3.045093795093798</v>
       </c>
       <c r="U4" t="n">
+        <v>-0.1347893663047353</v>
+      </c>
+      <c r="V4" t="n">
+        <v>-0.2671600418476743</v>
+      </c>
+      <c r="W4" t="n">
+        <v>2562093.373633344</v>
+      </c>
+      <c r="X4" t="n">
+        <v>-0.4248196248196254</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.000295768227545</v>
+      </c>
+      <c r="Z4" t="n">
         <v>-0.8676587301587375</v>
       </c>
-      <c r="V4" t="n">
-        <v>644700.5772005767</v>
-      </c>
-      <c r="W4" t="n">
-        <v>-0.1347893663047353</v>
-      </c>
-      <c r="X4" t="n">
+      <c r="AA4" t="n">
         <v>1.359686147186153</v>
       </c>
-      <c r="Y4" t="n">
+      <c r="AB4" t="n">
         <v>2.603949179352782</v>
       </c>
-      <c r="Z4" t="n">
-        <v>-0.4248196248196254</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>1.000295768227545</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>2562093.373633344</v>
-      </c>
       <c r="AC4" t="n">
-        <v>-0.2671600418476743</v>
+        <v>-0.7889971139970839</v>
       </c>
       <c r="AD4" t="n">
         <v>-2.092775184236373</v>
@@ -1149,37 +1149,37 @@
         <v>-1</v>
       </c>
       <c r="S5" t="n">
-        <v>0.7142857142857224</v>
+        <v>1274675.324675323</v>
       </c>
       <c r="T5" t="n">
         <v>-3.415584415584419</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>-0.1479177309922652</v>
       </c>
       <c r="V5" t="n">
-        <v>1274675.324675323</v>
+        <v>0.7277365491651153</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.1479177309922652</v>
+        <v>1147735.641687505</v>
       </c>
       <c r="X5" t="n">
+        <v>-0.441558441558441</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>3.55510629811873</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="n">
         <v>3.519480519480524</v>
       </c>
-      <c r="Y5" t="n">
+      <c r="AB5" t="n">
         <v>0.7974801251198471</v>
       </c>
-      <c r="Z5" t="n">
-        <v>-0.441558441558441</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>3.55510629811873</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1147735.641687505</v>
-      </c>
       <c r="AC5" t="n">
-        <v>0.7277365491651153</v>
+        <v>0.7142857142857224</v>
       </c>
       <c r="AD5" t="n">
         <v>-2.582229795739121</v>
@@ -1275,37 +1275,37 @@
         <v>1</v>
       </c>
       <c r="S6" t="n">
-        <v>2.402020202020196</v>
+        <v>-5439402.777777778</v>
       </c>
       <c r="T6" t="n">
         <v>1.211875901875903</v>
       </c>
       <c r="U6" t="n">
+        <v>-0.1275615779375177</v>
+      </c>
+      <c r="V6" t="n">
+        <v>-4.285941961129936</v>
+      </c>
+      <c r="W6" t="n">
+        <v>-3235598.634865553</v>
+      </c>
+      <c r="X6" t="n">
+        <v>-0.2188383838383838</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>-0.5056606718260781</v>
+      </c>
+      <c r="Z6" t="n">
         <v>-2.221493506493502</v>
       </c>
-      <c r="V6" t="n">
-        <v>-5439402.777777778</v>
-      </c>
-      <c r="W6" t="n">
-        <v>-0.1275615779375177</v>
-      </c>
-      <c r="X6" t="n">
+      <c r="AA6" t="n">
         <v>-2.415418470418459</v>
       </c>
-      <c r="Y6" t="n">
+      <c r="AB6" t="n">
         <v>2.97326925372036</v>
       </c>
-      <c r="Z6" t="n">
-        <v>-0.2188383838383838</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>-0.5056606718260781</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>-3235598.634865553</v>
-      </c>
       <c r="AC6" t="n">
-        <v>-4.285941961129936</v>
+        <v>2.402020202020196</v>
       </c>
       <c r="AD6" t="n">
         <v>-2.928895498820307</v>
@@ -1401,37 +1401,37 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>-2.500000000000028</v>
+        <v>-11066030.84415585</v>
       </c>
       <c r="T7" t="n">
         <v>2.336038961038962</v>
       </c>
       <c r="U7" t="n">
+        <v>-0.3257250268528467</v>
+      </c>
+      <c r="V7" t="n">
+        <v>-8.396693166899937</v>
+      </c>
+      <c r="W7" t="n">
+        <v>-6279749.970163506</v>
+      </c>
+      <c r="X7" t="n">
+        <v>-0.3246753246753251</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>-6.911510377675796</v>
+      </c>
+      <c r="Z7" t="n">
         <v>-6.561688311688314</v>
       </c>
-      <c r="V7" t="n">
-        <v>-11066030.84415585</v>
-      </c>
-      <c r="W7" t="n">
-        <v>-0.3257250268528467</v>
-      </c>
-      <c r="X7" t="n">
+      <c r="AA7" t="n">
         <v>-8.461038961038952</v>
       </c>
-      <c r="Y7" t="n">
+      <c r="AB7" t="n">
         <v>-0.686596767893775</v>
       </c>
-      <c r="Z7" t="n">
-        <v>-0.3246753246753251</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>-6.911510377675796</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>-6279749.970163506</v>
-      </c>
       <c r="AC7" t="n">
-        <v>-8.396693166899937</v>
+        <v>-2.500000000000028</v>
       </c>
       <c r="AD7" t="n">
         <v>-0.4180160900085674</v>
@@ -1527,37 +1527,37 @@
         <v>1</v>
       </c>
       <c r="S8" t="n">
-        <v>0.7164764528401122</v>
+        <v>12735890.06952643</v>
       </c>
       <c r="T8" t="n">
         <v>-1.126065853338581</v>
       </c>
       <c r="U8" t="n">
+        <v>0.3430561698363555</v>
+      </c>
+      <c r="V8" t="n">
+        <v>5.901118966954172</v>
+      </c>
+      <c r="W8" t="n">
+        <v>9751131.907230277</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0.5518037518037517</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>7.899077074143904</v>
+      </c>
+      <c r="Z8" t="n">
         <v>6.570431588613403</v>
       </c>
-      <c r="V8" t="n">
-        <v>12735890.06952643</v>
-      </c>
-      <c r="W8" t="n">
-        <v>0.3430561698363555</v>
-      </c>
-      <c r="X8" t="n">
+      <c r="AA8" t="n">
         <v>7.616030434212263</v>
       </c>
-      <c r="Y8" t="n">
+      <c r="AB8" t="n">
         <v>1.077492856925772</v>
       </c>
-      <c r="Z8" t="n">
-        <v>0.5518037518037517</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>7.899077074143904</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>9751131.907230277</v>
-      </c>
       <c r="AC8" t="n">
-        <v>5.901118966954172</v>
+        <v>0.7164764528401122</v>
       </c>
       <c r="AD8" t="n">
         <v>-2.497809011906256</v>
@@ -1653,37 +1653,37 @@
         <v>-1</v>
       </c>
       <c r="S9" t="n">
-        <v>2.367766955266944</v>
+        <v>-33454933.86243385</v>
       </c>
       <c r="T9" t="n">
         <v>0.9788900913900918</v>
       </c>
       <c r="U9" t="n">
+        <v>-1.233638093395253</v>
+      </c>
+      <c r="V9" t="n">
+        <v>-9.125626519677283</v>
+      </c>
+      <c r="W9" t="n">
+        <v>-33999853.09632053</v>
+      </c>
+      <c r="X9" t="n">
+        <v>-1.216666666666666</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>-10.64779148835355</v>
+      </c>
+      <c r="Z9" t="n">
         <v>-8.770244107744119</v>
       </c>
-      <c r="V9" t="n">
-        <v>-33454933.86243385</v>
-      </c>
-      <c r="W9" t="n">
-        <v>-1.233638093395253</v>
-      </c>
-      <c r="X9" t="n">
+      <c r="AA9" t="n">
         <v>-9.6691317941318</v>
       </c>
-      <c r="Y9" t="n">
+      <c r="AB9" t="n">
         <v>-1.987334763710976</v>
       </c>
-      <c r="Z9" t="n">
-        <v>-1.216666666666666</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>-10.64779148835355</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>-33999853.09632053</v>
-      </c>
       <c r="AC9" t="n">
-        <v>-9.125626519677283</v>
+        <v>2.367766955266944</v>
       </c>
       <c r="AD9" t="n">
         <v>1.343246985579132</v>
@@ -1779,37 +1779,37 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.901298701298686</v>
+        <v>-5366883.116883117</v>
       </c>
       <c r="T10" t="n">
         <v>-0.505194805194801</v>
       </c>
       <c r="U10" t="n">
+        <v>-0.127140680833737</v>
+      </c>
+      <c r="V10" t="n">
+        <v>-4.246363808681352</v>
+      </c>
+      <c r="W10" t="n">
+        <v>-5373766.769865839</v>
+      </c>
+      <c r="X10" t="n">
+        <v>-0.3558441558441554</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>-3.874626692782371</v>
+      </c>
+      <c r="Z10" t="n">
         <v>-2.236363636363649</v>
       </c>
-      <c r="V10" t="n">
-        <v>-5366883.116883117</v>
-      </c>
-      <c r="W10" t="n">
-        <v>-0.127140680833737</v>
-      </c>
-      <c r="X10" t="n">
+      <c r="AA10" t="n">
         <v>-1.907792207792184</v>
       </c>
-      <c r="Y10" t="n">
+      <c r="AB10" t="n">
         <v>-4.080095195973115</v>
       </c>
-      <c r="Z10" t="n">
-        <v>-0.3558441558441554</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>-3.874626692782371</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>-5373766.769865839</v>
-      </c>
       <c r="AC10" t="n">
-        <v>-4.246363808681352</v>
+        <v>-1.901298701298686</v>
       </c>
       <c r="AD10" t="n">
         <v>-0.5005170489248307</v>

--- a/data/france/p6_deployment/data_preparation/df_tagged.xlsx
+++ b/data/france/p6_deployment/data_preparation/df_tagged.xlsx
@@ -520,62 +520,62 @@
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_rat_player_start</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_start</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_val_player_start</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_sub</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_age_player_start</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_sub</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_start</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_start</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_sub</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_sub</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_int_rep_player_sub</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_sub</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_val_player_sub</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_start</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_sub</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_start</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_start</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_sub</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_start</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_sub</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
@@ -712,26 +712,26 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>2NocJFqd</t>
+          <t>zkPwWhT1</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45522.5</v>
+        <v>45522.65625</v>
       </c>
       <c r="C2" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D2" t="n">
         <v>134</v>
       </c>
       <c r="E2" t="n">
-        <v>18752</v>
+        <v>29778</v>
       </c>
       <c r="F2" t="n">
-        <v>431</v>
+        <v>573</v>
       </c>
       <c r="G2" t="n">
-        <v>176</v>
+        <v>39</v>
       </c>
       <c r="H2" t="n">
         <v>55</v>
@@ -753,58 +753,58 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>35</v>
+        <v>312</v>
       </c>
       <c r="N2" t="n">
-        <v>234</v>
+        <v>37</v>
       </c>
       <c r="O2" t="n">
-        <v>-3</v>
+        <v>-8</v>
       </c>
       <c r="P2" t="n">
-        <v>-3</v>
+        <v>2</v>
       </c>
       <c r="Q2" t="n">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="R2" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="S2" t="n">
-        <v>-11534228.8961039</v>
+        <v>-0.9551226551226364</v>
       </c>
       <c r="T2" t="n">
-        <v>0.05162337662337535</v>
+        <v>-0.4085137085137087</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.3747165532879819</v>
+        <v>518340.548340546</v>
       </c>
       <c r="V2" t="n">
-        <v>-9.022119745334038</v>
+        <v>-0.2816242180019231</v>
       </c>
       <c r="W2" t="n">
-        <v>-5720895.473574045</v>
+        <v>-3.092352092352094</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.4025974025974028</v>
+        <v>0.9351344790973286</v>
       </c>
       <c r="Y2" t="n">
-        <v>-6.515774899703459</v>
+        <v>1.383549783549782</v>
       </c>
       <c r="Z2" t="n">
-        <v>-8.279220779220779</v>
+        <v>-0.6877344877344456</v>
       </c>
       <c r="AA2" t="n">
-        <v>-7.081980519480524</v>
+        <v>2.54999169790193</v>
       </c>
       <c r="AB2" t="n">
-        <v>4.636490493633374</v>
+        <v>-2.209551619690934</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.719642857142816</v>
+        <v>-0.2061128013140394</v>
       </c>
       <c r="AD2" t="n">
-        <v>-1.740602651316937</v>
+        <v>2659292.869726306</v>
       </c>
       <c r="AE2" t="n">
         <v>0</v>
@@ -838,7 +838,7 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>M5VGwpVA</t>
+          <t>2NocJFqd</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
@@ -851,13 +851,13 @@
         <v>134</v>
       </c>
       <c r="E3" t="n">
-        <v>20484</v>
+        <v>18752</v>
       </c>
       <c r="F3" t="n">
-        <v>242</v>
+        <v>431</v>
       </c>
       <c r="G3" t="n">
-        <v>516</v>
+        <v>176</v>
       </c>
       <c r="H3" t="n">
         <v>55</v>
@@ -879,58 +879,58 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>193</v>
+        <v>35</v>
       </c>
       <c r="N3" t="n">
-        <v>55</v>
+        <v>234</v>
       </c>
       <c r="O3" t="n">
+        <v>-3</v>
+      </c>
+      <c r="P3" t="n">
+        <v>-3</v>
+      </c>
+      <c r="Q3" t="n">
         <v>-4</v>
       </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>5</v>
-      </c>
       <c r="R3" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="S3" t="n">
-        <v>839134.1991341989</v>
+        <v>-8.214285714285708</v>
       </c>
       <c r="T3" t="n">
-        <v>2.505772005772009</v>
+        <v>-0.3939393939393945</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.08543577966303584</v>
+        <v>-11204826.83982684</v>
       </c>
       <c r="V3" t="n">
-        <v>0.6642355939031006</v>
+        <v>-8.970034595034591</v>
       </c>
       <c r="W3" t="n">
-        <v>138185.9678096436</v>
+        <v>-0.1722943722943775</v>
       </c>
       <c r="X3" t="n">
-        <v>0.1305916305916306</v>
+        <v>-6.707141403569977</v>
       </c>
       <c r="Y3" t="n">
-        <v>-1.128653512687123</v>
+        <v>-6.84632034632034</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.542279942279947</v>
+        <v>2.754112554112538</v>
       </c>
       <c r="AA3" t="n">
-        <v>-1.494660894660896</v>
+        <v>4.851979039479033</v>
       </c>
       <c r="AB3" t="n">
-        <v>-1.105491115063614</v>
+        <v>-1.461131461131458</v>
       </c>
       <c r="AC3" t="n">
-        <v>-0.9500721500720886</v>
+        <v>-0.381613756613757</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.9826989881794361</v>
+        <v>-5934025.234025234</v>
       </c>
       <c r="AE3" t="n">
         <v>0</v>
@@ -964,26 +964,26 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>zkPwWhT1</t>
+          <t>M5VGwpVA</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
         <v>45522.5</v>
       </c>
       <c r="C4" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D4" t="n">
         <v>134</v>
       </c>
       <c r="E4" t="n">
-        <v>29778</v>
+        <v>20484</v>
       </c>
       <c r="F4" t="n">
-        <v>573</v>
+        <v>242</v>
       </c>
       <c r="G4" t="n">
-        <v>39</v>
+        <v>516</v>
       </c>
       <c r="H4" t="n">
         <v>55</v>
@@ -1005,58 +1005,58 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>312</v>
+        <v>193</v>
       </c>
       <c r="N4" t="n">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="O4" t="n">
-        <v>-8</v>
+        <v>-4</v>
       </c>
       <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>5</v>
+      </c>
+      <c r="R4" t="n">
         <v>2</v>
       </c>
-      <c r="Q4" t="n">
-        <v>-5</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1</v>
-      </c>
       <c r="S4" t="n">
-        <v>644700.5772005767</v>
+        <v>1.532659932659925</v>
       </c>
       <c r="T4" t="n">
-        <v>-3.045093795093798</v>
+        <v>0.119023569023569</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1347893663047353</v>
+        <v>770656.5656565651</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.2671600418476743</v>
+        <v>0.5527193039980745</v>
       </c>
       <c r="W4" t="n">
-        <v>2562093.373633344</v>
+        <v>2.556734006734004</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.4248196248196254</v>
+        <v>-1.066762431468305</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.000295768227545</v>
+        <v>-1.627104377104388</v>
       </c>
       <c r="Z4" t="n">
-        <v>-0.8676587301587375</v>
+        <v>-0.6917508417508316</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.359686147186153</v>
+        <v>-1.289739634240874</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.603949179352782</v>
+        <v>0.7483340047278659</v>
       </c>
       <c r="AC4" t="n">
-        <v>-0.7889971139970839</v>
+        <v>-0.09041581701428236</v>
       </c>
       <c r="AD4" t="n">
-        <v>-2.092775184236373</v>
+        <v>116772.5180001399</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
@@ -1149,40 +1149,40 @@
         <v>-1</v>
       </c>
       <c r="S5" t="n">
-        <v>1274675.324675323</v>
+        <v>0.2121212121212039</v>
       </c>
       <c r="T5" t="n">
-        <v>-3.415584415584419</v>
+        <v>-0.439393939393939</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1479177309922652</v>
+        <v>1494696.969696969</v>
       </c>
       <c r="V5" t="n">
-        <v>0.7277365491651153</v>
+        <v>0.4045815295815487</v>
       </c>
       <c r="W5" t="n">
-        <v>1147735.641687505</v>
+        <v>-3.454545454545453</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.441558441558441</v>
+        <v>3.35132771817554</v>
       </c>
       <c r="Y5" t="n">
-        <v>3.55510629811873</v>
+        <v>3.666666666666671</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>0.7121212121211613</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.519480519480524</v>
+        <v>0.8007638496768834</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.7974801251198471</v>
+        <v>-2.494082909843787</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.7142857142857224</v>
+        <v>-0.1540521676391242</v>
       </c>
       <c r="AD5" t="n">
-        <v>-2.582229795739121</v>
+        <v>899858.2486354224</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
@@ -1216,26 +1216,26 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>jqSiuc6F</t>
+          <t>ripawyyS</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45522.5</v>
+        <v>45522.41666666666</v>
       </c>
       <c r="C6" t="n">
         <v>101</v>
       </c>
       <c r="D6" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E6" t="n">
-        <v>21029</v>
+        <v>17924</v>
       </c>
       <c r="F6" t="n">
-        <v>826</v>
+        <v>342</v>
       </c>
       <c r="G6" t="n">
-        <v>545</v>
+        <v>370</v>
       </c>
       <c r="H6" t="n">
         <v>55</v>
@@ -1257,58 +1257,58 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>312</v>
+        <v>128</v>
       </c>
       <c r="N6" t="n">
         <v>257</v>
       </c>
       <c r="O6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="P6" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="Q6" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="R6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>-5439402.777777778</v>
+        <v>-6.517316017316034</v>
       </c>
       <c r="T6" t="n">
-        <v>1.211875901875903</v>
+        <v>-0.3333333333333337</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1275615779375177</v>
+        <v>-10976948.05194805</v>
       </c>
       <c r="V6" t="n">
-        <v>-4.285941961129936</v>
+        <v>-8.529176024476783</v>
       </c>
       <c r="W6" t="n">
-        <v>-3235598.634865553</v>
+        <v>2.29004329004329</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.2188383838383838</v>
+        <v>-6.999683326281072</v>
       </c>
       <c r="Y6" t="n">
-        <v>-0.5056606718260781</v>
+        <v>-8.417748917748924</v>
       </c>
       <c r="Z6" t="n">
-        <v>-2.221493506493502</v>
+        <v>-2.549783549783541</v>
       </c>
       <c r="AA6" t="n">
-        <v>-2.415418470418459</v>
+        <v>-0.7203438791785004</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.97326925372036</v>
+        <v>-0.255804554676736</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.402020202020196</v>
+        <v>-0.3244569757727656</v>
       </c>
       <c r="AD6" t="n">
-        <v>-2.928895498820307</v>
+        <v>-6666662.191192267</v>
       </c>
       <c r="AE6" t="n">
         <v>0</v>
@@ -1342,26 +1342,26 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>ripawyyS</t>
+          <t>fHYrsJy3</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45522.5</v>
+        <v>45521.66666666666</v>
       </c>
       <c r="C7" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D7" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E7" t="n">
-        <v>17924</v>
+        <v>18523</v>
       </c>
       <c r="F7" t="n">
-        <v>342</v>
+        <v>47</v>
       </c>
       <c r="G7" t="n">
-        <v>370</v>
+        <v>362</v>
       </c>
       <c r="H7" t="n">
         <v>55</v>
@@ -1383,58 +1383,58 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>128</v>
+        <v>67</v>
       </c>
       <c r="N7" t="n">
-        <v>257</v>
+        <v>226</v>
       </c>
       <c r="O7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P7" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="Q7" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S7" t="n">
-        <v>-11066030.84415585</v>
+        <v>6.508754208754212</v>
       </c>
       <c r="T7" t="n">
-        <v>2.336038961038962</v>
+        <v>0.5225589225589224</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3257250268528467</v>
+        <v>12410824.91582492</v>
       </c>
       <c r="V7" t="n">
-        <v>-8.396693166899937</v>
+        <v>5.849153488840017</v>
       </c>
       <c r="W7" t="n">
-        <v>-6279749.970163506</v>
+        <v>-1.102558922558924</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.3246753246753251</v>
+        <v>8.125588423014889</v>
       </c>
       <c r="Y7" t="n">
-        <v>-6.911510377675796</v>
+        <v>7.527104377104379</v>
       </c>
       <c r="Z7" t="n">
-        <v>-6.561688311688314</v>
+        <v>0.8566329966329818</v>
       </c>
       <c r="AA7" t="n">
-        <v>-8.461038961038952</v>
+        <v>0.5488925677006762</v>
       </c>
       <c r="AB7" t="n">
-        <v>-0.686596767893775</v>
+        <v>-2.673857542955837</v>
       </c>
       <c r="AC7" t="n">
-        <v>-2.500000000000028</v>
+        <v>0.3793988648090814</v>
       </c>
       <c r="AD7" t="n">
-        <v>-0.4180160900085674</v>
+        <v>10210373.44578366</v>
       </c>
       <c r="AE7" t="n">
         <v>0</v>
@@ -1468,26 +1468,26 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>fHYrsJy3</t>
+          <t>jqSiuc6F</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45522.5</v>
+        <v>45521.58333333334</v>
       </c>
       <c r="C8" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D8" t="n">
         <v>133</v>
       </c>
       <c r="E8" t="n">
-        <v>18523</v>
+        <v>21029</v>
       </c>
       <c r="F8" t="n">
-        <v>47</v>
+        <v>826</v>
       </c>
       <c r="G8" t="n">
-        <v>362</v>
+        <v>545</v>
       </c>
       <c r="H8" t="n">
         <v>55</v>
@@ -1509,58 +1509,58 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>67</v>
+        <v>312</v>
       </c>
       <c r="N8" t="n">
-        <v>226</v>
+        <v>257</v>
       </c>
       <c r="O8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="R8" t="n">
         <v>1</v>
       </c>
       <c r="S8" t="n">
-        <v>12735890.06952643</v>
+        <v>-2.145517676767682</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.126065853338581</v>
+        <v>-0.1988005050505053</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3430561698363555</v>
+        <v>-5311223.169191919</v>
       </c>
       <c r="V8" t="n">
-        <v>5.901118966954172</v>
+        <v>-4.313757684810327</v>
       </c>
       <c r="W8" t="n">
-        <v>9751131.907230277</v>
+        <v>1.476388888888891</v>
       </c>
       <c r="X8" t="n">
-        <v>0.5518037518037517</v>
+        <v>-0.6812072917335996</v>
       </c>
       <c r="Y8" t="n">
-        <v>7.899077074143904</v>
+        <v>-2.560290404040401</v>
       </c>
       <c r="Z8" t="n">
-        <v>6.570431588613403</v>
+        <v>2.201515151515167</v>
       </c>
       <c r="AA8" t="n">
-        <v>7.616030434212263</v>
+        <v>3.056115716642012</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.077492856925772</v>
+        <v>-2.853552685131628</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.7164764528401122</v>
+        <v>-0.1210440631493261</v>
       </c>
       <c r="AD8" t="n">
-        <v>-2.497809011906256</v>
+        <v>-3498376.978771716</v>
       </c>
       <c r="AE8" t="n">
         <v>0</v>
@@ -1594,26 +1594,26 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>SOLVXEbk</t>
+          <t>0js8u60b</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45522.5</v>
+        <v>45521.5</v>
       </c>
       <c r="C9" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D9" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E9" t="n">
-        <v>25178</v>
+        <v>15220</v>
       </c>
       <c r="F9" t="n">
-        <v>194</v>
+        <v>211</v>
       </c>
       <c r="G9" t="n">
-        <v>129</v>
+        <v>303</v>
       </c>
       <c r="H9" t="n">
         <v>55</v>
@@ -1635,58 +1635,58 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>12</v>
+        <v>152</v>
       </c>
       <c r="N9" t="n">
-        <v>37</v>
+        <v>67</v>
       </c>
       <c r="O9" t="n">
-        <v>-9</v>
+        <v>-5</v>
       </c>
       <c r="P9" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-33454933.86243385</v>
+        <v>-2.351515151515159</v>
       </c>
       <c r="T9" t="n">
-        <v>0.9788900913900918</v>
+        <v>-0.3848484848484846</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.233638093395253</v>
+        <v>-5597727.272727274</v>
       </c>
       <c r="V9" t="n">
-        <v>-9.125626519677283</v>
+        <v>-4.389276295313451</v>
       </c>
       <c r="W9" t="n">
-        <v>-33999853.09632053</v>
+        <v>-0.7106060606060538</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.216666666666666</v>
+        <v>-3.770397808246102</v>
       </c>
       <c r="Y9" t="n">
-        <v>-10.64779148835355</v>
+        <v>-1.922727272727272</v>
       </c>
       <c r="Z9" t="n">
-        <v>-8.770244107744119</v>
+        <v>-2.096969696969694</v>
       </c>
       <c r="AA9" t="n">
-        <v>-9.6691317941318</v>
+        <v>-3.824925876783453</v>
       </c>
       <c r="AB9" t="n">
-        <v>-1.987334763710976</v>
+        <v>-0.5654180385604519</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.367766955266944</v>
+        <v>-0.1205530165282489</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.343246985579132</v>
+        <v>-5482357.527806443</v>
       </c>
       <c r="AE9" t="n">
         <v>0</v>
@@ -1720,26 +1720,26 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>0js8u60b</t>
+          <t>SOLVXEbk</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45522.5</v>
+        <v>45520.65625</v>
       </c>
       <c r="C10" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D10" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E10" t="n">
-        <v>15220</v>
+        <v>25178</v>
       </c>
       <c r="F10" t="n">
-        <v>211</v>
+        <v>194</v>
       </c>
       <c r="G10" t="n">
-        <v>303</v>
+        <v>129</v>
       </c>
       <c r="H10" t="n">
         <v>55</v>
@@ -1761,58 +1761,58 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>152</v>
+        <v>12</v>
       </c>
       <c r="N10" t="n">
-        <v>67</v>
+        <v>37</v>
       </c>
       <c r="O10" t="n">
-        <v>-5</v>
+        <v>-9</v>
       </c>
       <c r="P10" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="S10" t="n">
-        <v>-5366883.116883117</v>
+        <v>-9.26934343434344</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.505194805194801</v>
+        <v>-1.237777777777777</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.127140680833737</v>
+        <v>-36142222.22222222</v>
       </c>
       <c r="V10" t="n">
-        <v>-4.246363808681352</v>
+        <v>-8.587952293808456</v>
       </c>
       <c r="W10" t="n">
-        <v>-5373766.769865839</v>
+        <v>1.049646464646461</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.3558441558441554</v>
+        <v>-10.19279365827184</v>
       </c>
       <c r="Y10" t="n">
-        <v>-3.874626692782371</v>
+        <v>-10.15191919191919</v>
       </c>
       <c r="Z10" t="n">
-        <v>-2.236363636363649</v>
+        <v>2.663181818181783</v>
       </c>
       <c r="AA10" t="n">
-        <v>-1.907792207792184</v>
+        <v>-2.451684899741764</v>
       </c>
       <c r="AB10" t="n">
-        <v>-4.080095195973115</v>
+        <v>1.202641102207476</v>
       </c>
       <c r="AC10" t="n">
-        <v>-1.901298701298686</v>
+        <v>-1.164974147553758</v>
       </c>
       <c r="AD10" t="n">
-        <v>-0.5005170489248307</v>
+        <v>-29631870.98981469</v>
       </c>
       <c r="AE10" t="n">
         <v>0</v>

--- a/data/france/p6_deployment/data_preparation/df_tagged.xlsx
+++ b/data/france/p6_deployment/data_preparation/df_tagged.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BD10"/>
+  <dimension ref="A1:BD19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -520,62 +520,62 @@
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_int_rep_player_start</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_sub</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_start</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_sub</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_start</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_sub</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_sub</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_start</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_sub</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_sub</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_val_player_start</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_start</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_sub</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_sub</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_sub</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_start</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_sub</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_rat_player_start</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_start</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_sub</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_start</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_sub</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
@@ -712,26 +712,26 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>2NocJFqd</t>
+          <t>OCd990al</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45522.5</v>
+        <v>45529.5</v>
       </c>
       <c r="C2" t="n">
         <v>101</v>
       </c>
       <c r="D2" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E2" t="n">
-        <v>18752</v>
+        <v>38223</v>
       </c>
       <c r="F2" t="n">
-        <v>431</v>
+        <v>273</v>
       </c>
       <c r="G2" t="n">
-        <v>176</v>
+        <v>133</v>
       </c>
       <c r="H2" t="n">
         <v>55</v>
@@ -753,58 +753,58 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>35</v>
+        <v>193</v>
       </c>
       <c r="N2" t="n">
-        <v>234</v>
+        <v>7</v>
       </c>
       <c r="O2" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>-4</v>
+        <v>3</v>
       </c>
       <c r="R2" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="S2" t="n">
-        <v>-11534228.8961039</v>
+        <v>0.07575757575757591</v>
       </c>
       <c r="T2" t="n">
-        <v>0.05162337662337535</v>
+        <v>2.578439153439149</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.3747165532879819</v>
+        <v>0.4393939393939377</v>
       </c>
       <c r="V2" t="n">
-        <v>-9.022119745334038</v>
+        <v>-2.361838624338617</v>
       </c>
       <c r="W2" t="n">
-        <v>-5720895.473574045</v>
+        <v>-1.484848484848499</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.4025974025974028</v>
+        <v>1.457804232804229</v>
       </c>
       <c r="Y2" t="n">
-        <v>-6.515774899703459</v>
+        <v>2498597.883597883</v>
       </c>
       <c r="Z2" t="n">
-        <v>-8.279220779220779</v>
+        <v>1.984848484848484</v>
       </c>
       <c r="AA2" t="n">
-        <v>-7.081980519480524</v>
+        <v>0.2264550264550267</v>
       </c>
       <c r="AB2" t="n">
-        <v>4.636490493633374</v>
+        <v>3.19259259259259</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.719642857142816</v>
+        <v>5923484.848484852</v>
       </c>
       <c r="AD2" t="n">
-        <v>-1.740602651316937</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="AE2" t="n">
         <v>0</v>
@@ -838,26 +838,26 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>M5VGwpVA</t>
+          <t>ObHze1pe</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45522.5</v>
+        <v>45529.5</v>
       </c>
       <c r="C3" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D3" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E3" t="n">
-        <v>20484</v>
+        <v>35322</v>
       </c>
       <c r="F3" t="n">
-        <v>242</v>
+        <v>858</v>
       </c>
       <c r="G3" t="n">
-        <v>516</v>
+        <v>228</v>
       </c>
       <c r="H3" t="n">
         <v>55</v>
@@ -879,58 +879,58 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>193</v>
+        <v>67</v>
       </c>
       <c r="N3" t="n">
-        <v>55</v>
+        <v>181</v>
       </c>
       <c r="O3" t="n">
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S3" t="n">
-        <v>839134.1991341989</v>
+        <v>0.5151515151515149</v>
       </c>
       <c r="T3" t="n">
-        <v>2.505772005772009</v>
+        <v>2.247618711516225</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.08543577966303584</v>
+        <v>0.8311688311688279</v>
       </c>
       <c r="V3" t="n">
-        <v>0.6642355939031006</v>
+        <v>-0.4423869350111715</v>
       </c>
       <c r="W3" t="n">
-        <v>138185.9678096436</v>
+        <v>1.83766233766238</v>
       </c>
       <c r="X3" t="n">
-        <v>0.1305916305916306</v>
+        <v>1.942084442472645</v>
       </c>
       <c r="Y3" t="n">
-        <v>-1.128653512687123</v>
+        <v>1325279.161401056</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.542279942279947</v>
+        <v>3.675324675324674</v>
       </c>
       <c r="AA3" t="n">
-        <v>-1.494660894660896</v>
+        <v>0.1540521676391242</v>
       </c>
       <c r="AB3" t="n">
-        <v>-1.105491115063614</v>
+        <v>4.71931045145331</v>
       </c>
       <c r="AC3" t="n">
-        <v>-0.9500721500720886</v>
+        <v>2609523.80952381</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.9826989881794361</v>
+        <v>4.017316017316034</v>
       </c>
       <c r="AE3" t="n">
         <v>0</v>
@@ -964,26 +964,26 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>zkPwWhT1</t>
+          <t>pSpI7vU0</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45522.5</v>
+        <v>45529.5</v>
       </c>
       <c r="C4" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D4" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E4" t="n">
-        <v>29778</v>
+        <v>59186</v>
       </c>
       <c r="F4" t="n">
-        <v>573</v>
+        <v>56</v>
       </c>
       <c r="G4" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="H4" t="n">
         <v>55</v>
@@ -1005,58 +1005,58 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>312</v>
+        <v>165</v>
       </c>
       <c r="N4" t="n">
-        <v>37</v>
+        <v>141</v>
       </c>
       <c r="O4" t="n">
-        <v>-8</v>
+        <v>6</v>
       </c>
       <c r="P4" t="n">
         <v>2</v>
       </c>
       <c r="Q4" t="n">
-        <v>-5</v>
+        <v>12</v>
       </c>
       <c r="R4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S4" t="n">
-        <v>644700.5772005767</v>
+        <v>0.5677729677729679</v>
       </c>
       <c r="T4" t="n">
-        <v>-3.045093795093798</v>
+        <v>-2.70817174956106</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1347893663047353</v>
+        <v>3.033092833092834</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.2671600418476743</v>
+        <v>-2.441684983403263</v>
       </c>
       <c r="W4" t="n">
-        <v>2562093.373633344</v>
+        <v>-0.1331409331409361</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.4248196248196254</v>
+        <v>2.440366094603711</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.000295768227545</v>
+        <v>-4756542.263635918</v>
       </c>
       <c r="Z4" t="n">
-        <v>-0.8676587301587375</v>
+        <v>-2.536411736411722</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.359686147186153</v>
+        <v>0.2753911851822068</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.603949179352782</v>
+        <v>-0.5081460614548945</v>
       </c>
       <c r="AC4" t="n">
-        <v>-0.7889971139970839</v>
+        <v>-4784165.464165462</v>
       </c>
       <c r="AD4" t="n">
-        <v>-2.092775184236373</v>
+        <v>-0.02938912938914484</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
@@ -1090,26 +1090,26 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>6ehlLyFq</t>
+          <t>xrJSdNFr</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45522.5</v>
+        <v>45529.5</v>
       </c>
       <c r="C5" t="n">
         <v>101</v>
       </c>
       <c r="D5" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E5" t="n">
-        <v>33150</v>
+        <v>26109</v>
       </c>
       <c r="F5" t="n">
-        <v>341</v>
+        <v>736</v>
       </c>
       <c r="G5" t="n">
-        <v>599</v>
+        <v>399</v>
       </c>
       <c r="H5" t="n">
         <v>55</v>
@@ -1131,58 +1131,58 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>152</v>
+        <v>165</v>
       </c>
       <c r="N5" t="n">
-        <v>141</v>
+        <v>211</v>
       </c>
       <c r="O5" t="n">
+        <v>-6</v>
+      </c>
+      <c r="P5" t="n">
         <v>-1</v>
       </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
       <c r="Q5" t="n">
+        <v>4</v>
+      </c>
+      <c r="R5" t="n">
         <v>1</v>
       </c>
-      <c r="R5" t="n">
-        <v>-1</v>
-      </c>
       <c r="S5" t="n">
-        <v>1274675.324675323</v>
+        <v>-0.5114478114478114</v>
       </c>
       <c r="T5" t="n">
-        <v>-3.415584415584419</v>
+        <v>-2.696465081759214</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1479177309922652</v>
+        <v>-2.293097643097639</v>
       </c>
       <c r="V5" t="n">
-        <v>0.7277365491651153</v>
+        <v>1.318052263640453</v>
       </c>
       <c r="W5" t="n">
-        <v>1147735.641687505</v>
+        <v>1.993265993265965</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.441558441558441</v>
+        <v>0.8438100026335285</v>
       </c>
       <c r="Y5" t="n">
-        <v>3.55510629811873</v>
+        <v>-6466870.286576169</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>-0.763804713804717</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.519480519480524</v>
+        <v>-0.1598027245086071</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.7974801251198471</v>
+        <v>-3.619316957552243</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.7142857142857224</v>
+        <v>-5898838.383838383</v>
       </c>
       <c r="AD5" t="n">
-        <v>-2.582229795739121</v>
+        <v>-4.500841750841758</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
@@ -1216,26 +1216,26 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>jqSiuc6F</t>
+          <t>hhlQ5IbD</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45522.5</v>
+        <v>45529.5</v>
       </c>
       <c r="C6" t="n">
         <v>101</v>
       </c>
       <c r="D6" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E6" t="n">
-        <v>21029</v>
+        <v>67394</v>
       </c>
       <c r="F6" t="n">
-        <v>826</v>
+        <v>448</v>
       </c>
       <c r="G6" t="n">
-        <v>545</v>
+        <v>579</v>
       </c>
       <c r="H6" t="n">
         <v>55</v>
@@ -1257,58 +1257,58 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>312</v>
+        <v>12</v>
       </c>
       <c r="N6" t="n">
-        <v>257</v>
+        <v>211</v>
       </c>
       <c r="O6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="P6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S6" t="n">
-        <v>-5439402.777777778</v>
+        <v>0.4412247474747475</v>
       </c>
       <c r="T6" t="n">
-        <v>1.211875901875903</v>
+        <v>1.18043679460088</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1275615779375177</v>
+        <v>1.28270202020202</v>
       </c>
       <c r="V6" t="n">
-        <v>-4.285941961129936</v>
+        <v>0.4084750274379019</v>
       </c>
       <c r="W6" t="n">
-        <v>-3235598.634865553</v>
+        <v>1.437878787878788</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.2188383838383838</v>
+        <v>2.17369567710125</v>
       </c>
       <c r="Y6" t="n">
-        <v>-0.5056606718260781</v>
+        <v>5917058.168296559</v>
       </c>
       <c r="Z6" t="n">
-        <v>-2.221493506493502</v>
+        <v>0.3754419191919141</v>
       </c>
       <c r="AA6" t="n">
-        <v>-2.415418470418459</v>
+        <v>0.190220240142841</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.97326925372036</v>
+        <v>5.883644159418168</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.402020202020196</v>
+        <v>4697738.320707072</v>
       </c>
       <c r="AD6" t="n">
-        <v>-2.928895498820307</v>
+        <v>2.850063131313135</v>
       </c>
       <c r="AE6" t="n">
         <v>0</v>
@@ -1342,26 +1342,26 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>ripawyyS</t>
+          <t>CKcVGr7E</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45522.5</v>
+        <v>45529.5</v>
       </c>
       <c r="C7" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D7" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E7" t="n">
-        <v>17924</v>
+        <v>50186</v>
       </c>
       <c r="F7" t="n">
-        <v>342</v>
+        <v>777</v>
       </c>
       <c r="G7" t="n">
-        <v>370</v>
+        <v>292</v>
       </c>
       <c r="H7" t="n">
         <v>55</v>
@@ -1383,58 +1383,58 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>128</v>
+        <v>98</v>
       </c>
       <c r="N7" t="n">
-        <v>257</v>
+        <v>199</v>
       </c>
       <c r="O7" t="n">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="P7" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S7" t="n">
-        <v>-11066030.84415585</v>
+        <v>0.4606060606060609</v>
       </c>
       <c r="T7" t="n">
-        <v>2.336038961038962</v>
+        <v>7.399870555509651</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3257250268528467</v>
+        <v>-2.315584415584418</v>
       </c>
       <c r="V7" t="n">
-        <v>-8.396693166899937</v>
+        <v>-2.129805282436877</v>
       </c>
       <c r="W7" t="n">
-        <v>-6279749.970163506</v>
+        <v>-2.8116883116883</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.3246753246753251</v>
+        <v>1.24860227491806</v>
       </c>
       <c r="Y7" t="n">
-        <v>-6.911510377675796</v>
+        <v>6499103.688708952</v>
       </c>
       <c r="Z7" t="n">
-        <v>-6.561688311688314</v>
+        <v>8.969047619047615</v>
       </c>
       <c r="AA7" t="n">
-        <v>-8.461038961038952</v>
+        <v>0.2065355696934643</v>
       </c>
       <c r="AB7" t="n">
-        <v>-0.686596767893775</v>
+        <v>8.59683182314761</v>
       </c>
       <c r="AC7" t="n">
-        <v>-2.500000000000028</v>
+        <v>11492554.11255411</v>
       </c>
       <c r="AD7" t="n">
-        <v>-0.4180160900085674</v>
+        <v>7.830952380952382</v>
       </c>
       <c r="AE7" t="n">
         <v>0</v>
@@ -1468,26 +1468,26 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>fHYrsJy3</t>
+          <t>8nivFMyR</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45522.5</v>
+        <v>45529.5</v>
       </c>
       <c r="C8" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D8" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E8" t="n">
-        <v>18523</v>
+        <v>36178</v>
       </c>
       <c r="F8" t="n">
-        <v>47</v>
+        <v>535</v>
       </c>
       <c r="G8" t="n">
-        <v>362</v>
+        <v>226</v>
       </c>
       <c r="H8" t="n">
         <v>55</v>
@@ -1509,16 +1509,16 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>67</v>
+        <v>98</v>
       </c>
       <c r="N8" t="n">
-        <v>226</v>
+        <v>7</v>
       </c>
       <c r="O8" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="P8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>6</v>
@@ -1527,40 +1527,40 @@
         <v>1</v>
       </c>
       <c r="S8" t="n">
-        <v>12735890.06952643</v>
+        <v>0.2575757575757578</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.126065853338581</v>
+        <v>1.400736896589308</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3430561698363555</v>
+        <v>0.3333333333333357</v>
       </c>
       <c r="V8" t="n">
-        <v>5.901118966954172</v>
+        <v>0.3619669645127885</v>
       </c>
       <c r="W8" t="n">
-        <v>9751131.907230277</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0.5518037518037517</v>
+        <v>0.807803022047878</v>
       </c>
       <c r="Y8" t="n">
-        <v>7.899077074143904</v>
+        <v>4441524.781155787</v>
       </c>
       <c r="Z8" t="n">
-        <v>6.570431588613403</v>
+        <v>1.075757575757578</v>
       </c>
       <c r="AA8" t="n">
-        <v>7.616030434212263</v>
+        <v>0.3244569757727656</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.077492856925772</v>
+        <v>3.405284043441924</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.7164764528401122</v>
+        <v>6872727.272727273</v>
       </c>
       <c r="AD8" t="n">
-        <v>-2.497809011906256</v>
+        <v>2.287878787878796</v>
       </c>
       <c r="AE8" t="n">
         <v>0</v>
@@ -1594,26 +1594,26 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>SOLVXEbk</t>
+          <t>ppvl45N8</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45522.5</v>
+        <v>45529.5</v>
       </c>
       <c r="C9" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D9" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E9" t="n">
-        <v>25178</v>
+        <v>48229</v>
       </c>
       <c r="F9" t="n">
-        <v>194</v>
+        <v>206</v>
       </c>
       <c r="G9" t="n">
-        <v>129</v>
+        <v>157</v>
       </c>
       <c r="H9" t="n">
         <v>55</v>
@@ -1635,58 +1635,58 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>12</v>
+        <v>165</v>
       </c>
       <c r="N9" t="n">
-        <v>37</v>
+        <v>234</v>
       </c>
       <c r="O9" t="n">
-        <v>-9</v>
+        <v>14</v>
       </c>
       <c r="P9" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3</v>
+        <v>11</v>
       </c>
       <c r="R9" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="S9" t="n">
-        <v>-33454933.86243385</v>
+        <v>0.9483838383838379</v>
       </c>
       <c r="T9" t="n">
-        <v>0.9788900913900918</v>
+        <v>7.424873253394921</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.233638093395253</v>
+        <v>-0.3435858585858576</v>
       </c>
       <c r="V9" t="n">
-        <v>-9.125626519677283</v>
+        <v>2.453119797372267</v>
       </c>
       <c r="W9" t="n">
-        <v>-33999853.09632053</v>
+        <v>0.6337878787878992</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.216666666666666</v>
+        <v>-0.6812499128815048</v>
       </c>
       <c r="Y9" t="n">
-        <v>-10.64779148835355</v>
+        <v>28295053.06940981</v>
       </c>
       <c r="Z9" t="n">
-        <v>-8.770244107744119</v>
+        <v>7.13525252525254</v>
       </c>
       <c r="AA9" t="n">
-        <v>-9.6691317941318</v>
+        <v>0.9665154403993992</v>
       </c>
       <c r="AB9" t="n">
-        <v>-1.987334763710976</v>
+        <v>6.829708102412084</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.367766955266944</v>
+        <v>33796010.1010101</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.343246985579132</v>
+        <v>7.904191919191931</v>
       </c>
       <c r="AE9" t="n">
         <v>0</v>
@@ -1720,26 +1720,26 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>0js8u60b</t>
+          <t>KQAqguF7</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45522.5</v>
+        <v>45529.5</v>
       </c>
       <c r="C10" t="n">
         <v>101</v>
       </c>
       <c r="D10" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E10" t="n">
-        <v>15220</v>
+        <v>42000</v>
       </c>
       <c r="F10" t="n">
-        <v>211</v>
+        <v>528</v>
       </c>
       <c r="G10" t="n">
-        <v>303</v>
+        <v>122</v>
       </c>
       <c r="H10" t="n">
         <v>55</v>
@@ -1761,58 +1761,58 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>152</v>
+        <v>103</v>
       </c>
       <c r="N10" t="n">
         <v>67</v>
       </c>
       <c r="O10" t="n">
-        <v>-5</v>
+        <v>2</v>
       </c>
       <c r="P10" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="S10" t="n">
-        <v>-5366883.116883117</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.505194805194801</v>
+        <v>0.1785967655532801</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.127140680833737</v>
+        <v>0.192121212121215</v>
       </c>
       <c r="V10" t="n">
-        <v>-4.246363808681352</v>
+        <v>-0.6869468092294255</v>
       </c>
       <c r="W10" t="n">
-        <v>-5373766.769865839</v>
+        <v>-4.634242424242416</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.3558441558441554</v>
+        <v>0.3295078713556947</v>
       </c>
       <c r="Y10" t="n">
-        <v>-3.874626692782371</v>
+        <v>-426208.3628931455</v>
       </c>
       <c r="Z10" t="n">
-        <v>-2.236363636363649</v>
+        <v>-0.9666666666666828</v>
       </c>
       <c r="AA10" t="n">
-        <v>-1.907792207792184</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>-4.080095195973115</v>
+        <v>-0.2345413644326584</v>
       </c>
       <c r="AC10" t="n">
-        <v>-1.901298701298686</v>
+        <v>-670606.060606061</v>
       </c>
       <c r="AD10" t="n">
-        <v>-0.5005170489248307</v>
+        <v>-1.190909090909088</v>
       </c>
       <c r="AE10" t="n">
         <v>0</v>
@@ -1843,6 +1843,1140 @@
       <c r="BC10" t="inlineStr"/>
       <c r="BD10" t="inlineStr"/>
     </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>zkPwWhT1</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45522.65625</v>
+      </c>
+      <c r="C11" t="n">
+        <v>102</v>
+      </c>
+      <c r="D11" t="n">
+        <v>134</v>
+      </c>
+      <c r="E11" t="n">
+        <v>29778</v>
+      </c>
+      <c r="F11" t="n">
+        <v>573</v>
+      </c>
+      <c r="G11" t="n">
+        <v>39</v>
+      </c>
+      <c r="H11" t="n">
+        <v>55</v>
+      </c>
+      <c r="I11" t="n">
+        <v>551</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="M11" t="n">
+        <v>312</v>
+      </c>
+      <c r="N11" t="n">
+        <v>37</v>
+      </c>
+      <c r="O11" t="n">
+        <v>-8</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>-5</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1</v>
+      </c>
+      <c r="S11" t="n">
+        <v>-0.4085137085137087</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0.9351344790973286</v>
+      </c>
+      <c r="U11" t="n">
+        <v>-3.092352092352094</v>
+      </c>
+      <c r="V11" t="n">
+        <v>2.54999169790193</v>
+      </c>
+      <c r="W11" t="n">
+        <v>-0.6877344877344456</v>
+      </c>
+      <c r="X11" t="n">
+        <v>-2.209551619690934</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>2659292.869726306</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1.383549783549782</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>-0.2061128013140394</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>-0.2816242180019231</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>518340.548340546</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>-0.9551226551226364</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="inlineStr"/>
+      <c r="AH11" t="inlineStr"/>
+      <c r="AI11" t="inlineStr"/>
+      <c r="AJ11" t="inlineStr"/>
+      <c r="AK11" t="inlineStr"/>
+      <c r="AL11" t="inlineStr"/>
+      <c r="AM11" t="inlineStr"/>
+      <c r="AN11" t="inlineStr"/>
+      <c r="AO11" t="inlineStr"/>
+      <c r="AP11" t="inlineStr"/>
+      <c r="AQ11" t="inlineStr"/>
+      <c r="AR11" t="inlineStr"/>
+      <c r="AS11" t="inlineStr"/>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AU11" t="inlineStr"/>
+      <c r="AV11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr"/>
+      <c r="AX11" t="inlineStr"/>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr"/>
+      <c r="BA11" t="inlineStr"/>
+      <c r="BB11" t="inlineStr"/>
+      <c r="BC11" t="inlineStr"/>
+      <c r="BD11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>6ehlLyFq</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45522.5</v>
+      </c>
+      <c r="C12" t="n">
+        <v>101</v>
+      </c>
+      <c r="D12" t="n">
+        <v>133</v>
+      </c>
+      <c r="E12" t="n">
+        <v>33150</v>
+      </c>
+      <c r="F12" t="n">
+        <v>341</v>
+      </c>
+      <c r="G12" t="n">
+        <v>599</v>
+      </c>
+      <c r="H12" t="n">
+        <v>55</v>
+      </c>
+      <c r="I12" t="n">
+        <v>551</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="M12" t="n">
+        <v>152</v>
+      </c>
+      <c r="N12" t="n">
+        <v>141</v>
+      </c>
+      <c r="O12" t="n">
+        <v>-1</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1</v>
+      </c>
+      <c r="R12" t="n">
+        <v>-1</v>
+      </c>
+      <c r="S12" t="n">
+        <v>-0.439393939393939</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3.35132771817554</v>
+      </c>
+      <c r="U12" t="n">
+        <v>-3.454545454545453</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0.8007638496768834</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0.7121212121211613</v>
+      </c>
+      <c r="X12" t="n">
+        <v>-2.494082909843787</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>899858.2486354224</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>3.666666666666671</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>-0.1540521676391242</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.4045815295815487</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1494696.969696969</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.2121212121212039</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="inlineStr"/>
+      <c r="AH12" t="inlineStr"/>
+      <c r="AI12" t="inlineStr"/>
+      <c r="AJ12" t="inlineStr"/>
+      <c r="AK12" t="inlineStr"/>
+      <c r="AL12" t="inlineStr"/>
+      <c r="AM12" t="inlineStr"/>
+      <c r="AN12" t="inlineStr"/>
+      <c r="AO12" t="inlineStr"/>
+      <c r="AP12" t="inlineStr"/>
+      <c r="AQ12" t="inlineStr"/>
+      <c r="AR12" t="inlineStr"/>
+      <c r="AS12" t="inlineStr"/>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AU12" t="inlineStr"/>
+      <c r="AV12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr"/>
+      <c r="AX12" t="inlineStr"/>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr"/>
+      <c r="BA12" t="inlineStr"/>
+      <c r="BB12" t="inlineStr"/>
+      <c r="BC12" t="inlineStr"/>
+      <c r="BD12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>M5VGwpVA</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45522.5</v>
+      </c>
+      <c r="C13" t="n">
+        <v>101</v>
+      </c>
+      <c r="D13" t="n">
+        <v>134</v>
+      </c>
+      <c r="E13" t="n">
+        <v>20484</v>
+      </c>
+      <c r="F13" t="n">
+        <v>242</v>
+      </c>
+      <c r="G13" t="n">
+        <v>516</v>
+      </c>
+      <c r="H13" t="n">
+        <v>55</v>
+      </c>
+      <c r="I13" t="n">
+        <v>551</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="M13" t="n">
+        <v>193</v>
+      </c>
+      <c r="N13" t="n">
+        <v>55</v>
+      </c>
+      <c r="O13" t="n">
+        <v>-4</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>5</v>
+      </c>
+      <c r="R13" t="n">
+        <v>2</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.119023569023569</v>
+      </c>
+      <c r="T13" t="n">
+        <v>-1.066762431468305</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2.556734006734004</v>
+      </c>
+      <c r="V13" t="n">
+        <v>-1.289739634240874</v>
+      </c>
+      <c r="W13" t="n">
+        <v>-0.6917508417508316</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0.7483340047278659</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>116772.5180001399</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-1.627104377104388</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>-0.09041581701428236</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.5527193039980745</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>770656.5656565651</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.532659932659925</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="inlineStr"/>
+      <c r="AH13" t="inlineStr"/>
+      <c r="AI13" t="inlineStr"/>
+      <c r="AJ13" t="inlineStr"/>
+      <c r="AK13" t="inlineStr"/>
+      <c r="AL13" t="inlineStr"/>
+      <c r="AM13" t="inlineStr"/>
+      <c r="AN13" t="inlineStr"/>
+      <c r="AO13" t="inlineStr"/>
+      <c r="AP13" t="inlineStr"/>
+      <c r="AQ13" t="inlineStr"/>
+      <c r="AR13" t="inlineStr"/>
+      <c r="AS13" t="inlineStr"/>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AU13" t="inlineStr"/>
+      <c r="AV13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr"/>
+      <c r="AX13" t="inlineStr"/>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr"/>
+      <c r="BA13" t="inlineStr"/>
+      <c r="BB13" t="inlineStr"/>
+      <c r="BC13" t="inlineStr"/>
+      <c r="BD13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>2NocJFqd</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45522.5</v>
+      </c>
+      <c r="C14" t="n">
+        <v>101</v>
+      </c>
+      <c r="D14" t="n">
+        <v>134</v>
+      </c>
+      <c r="E14" t="n">
+        <v>18752</v>
+      </c>
+      <c r="F14" t="n">
+        <v>431</v>
+      </c>
+      <c r="G14" t="n">
+        <v>176</v>
+      </c>
+      <c r="H14" t="n">
+        <v>55</v>
+      </c>
+      <c r="I14" t="n">
+        <v>551</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="M14" t="n">
+        <v>35</v>
+      </c>
+      <c r="N14" t="n">
+        <v>234</v>
+      </c>
+      <c r="O14" t="n">
+        <v>-3</v>
+      </c>
+      <c r="P14" t="n">
+        <v>-3</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>-4</v>
+      </c>
+      <c r="R14" t="n">
+        <v>-2</v>
+      </c>
+      <c r="S14" t="n">
+        <v>-0.3939393939393945</v>
+      </c>
+      <c r="T14" t="n">
+        <v>-6.707141403569977</v>
+      </c>
+      <c r="U14" t="n">
+        <v>-0.1722943722943775</v>
+      </c>
+      <c r="V14" t="n">
+        <v>4.851979039479033</v>
+      </c>
+      <c r="W14" t="n">
+        <v>2.754112554112538</v>
+      </c>
+      <c r="X14" t="n">
+        <v>-1.461131461131458</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>-5934025.234025234</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-6.84632034632034</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>-0.381613756613757</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>-8.970034595034591</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>-11204826.83982684</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>-8.214285714285708</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="inlineStr"/>
+      <c r="AH14" t="inlineStr"/>
+      <c r="AI14" t="inlineStr"/>
+      <c r="AJ14" t="inlineStr"/>
+      <c r="AK14" t="inlineStr"/>
+      <c r="AL14" t="inlineStr"/>
+      <c r="AM14" t="inlineStr"/>
+      <c r="AN14" t="inlineStr"/>
+      <c r="AO14" t="inlineStr"/>
+      <c r="AP14" t="inlineStr"/>
+      <c r="AQ14" t="inlineStr"/>
+      <c r="AR14" t="inlineStr"/>
+      <c r="AS14" t="inlineStr"/>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AU14" t="inlineStr"/>
+      <c r="AV14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr"/>
+      <c r="AX14" t="inlineStr"/>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr"/>
+      <c r="BA14" t="inlineStr"/>
+      <c r="BB14" t="inlineStr"/>
+      <c r="BC14" t="inlineStr"/>
+      <c r="BD14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>ripawyyS</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45522.41666666666</v>
+      </c>
+      <c r="C15" t="n">
+        <v>101</v>
+      </c>
+      <c r="D15" t="n">
+        <v>134</v>
+      </c>
+      <c r="E15" t="n">
+        <v>17924</v>
+      </c>
+      <c r="F15" t="n">
+        <v>342</v>
+      </c>
+      <c r="G15" t="n">
+        <v>370</v>
+      </c>
+      <c r="H15" t="n">
+        <v>55</v>
+      </c>
+      <c r="I15" t="n">
+        <v>551</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="M15" t="n">
+        <v>128</v>
+      </c>
+      <c r="N15" t="n">
+        <v>257</v>
+      </c>
+      <c r="O15" t="n">
+        <v>5</v>
+      </c>
+      <c r="P15" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>8</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>-0.3333333333333337</v>
+      </c>
+      <c r="T15" t="n">
+        <v>-6.999683326281072</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2.29004329004329</v>
+      </c>
+      <c r="V15" t="n">
+        <v>-0.7203438791785004</v>
+      </c>
+      <c r="W15" t="n">
+        <v>-2.549783549783541</v>
+      </c>
+      <c r="X15" t="n">
+        <v>-0.255804554676736</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>-6666662.191192267</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>-8.417748917748924</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>-0.3244569757727656</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>-8.529176024476783</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>-10976948.05194805</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>-6.517316017316034</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="inlineStr"/>
+      <c r="AH15" t="inlineStr"/>
+      <c r="AI15" t="inlineStr"/>
+      <c r="AJ15" t="inlineStr"/>
+      <c r="AK15" t="inlineStr"/>
+      <c r="AL15" t="inlineStr"/>
+      <c r="AM15" t="inlineStr"/>
+      <c r="AN15" t="inlineStr"/>
+      <c r="AO15" t="inlineStr"/>
+      <c r="AP15" t="inlineStr"/>
+      <c r="AQ15" t="inlineStr"/>
+      <c r="AR15" t="inlineStr"/>
+      <c r="AS15" t="inlineStr"/>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AU15" t="inlineStr"/>
+      <c r="AV15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr"/>
+      <c r="AX15" t="inlineStr"/>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr"/>
+      <c r="BA15" t="inlineStr"/>
+      <c r="BB15" t="inlineStr"/>
+      <c r="BC15" t="inlineStr"/>
+      <c r="BD15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>fHYrsJy3</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45521.66666666666</v>
+      </c>
+      <c r="C16" t="n">
+        <v>102</v>
+      </c>
+      <c r="D16" t="n">
+        <v>133</v>
+      </c>
+      <c r="E16" t="n">
+        <v>18523</v>
+      </c>
+      <c r="F16" t="n">
+        <v>47</v>
+      </c>
+      <c r="G16" t="n">
+        <v>362</v>
+      </c>
+      <c r="H16" t="n">
+        <v>55</v>
+      </c>
+      <c r="I16" t="n">
+        <v>551</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="M16" t="n">
+        <v>67</v>
+      </c>
+      <c r="N16" t="n">
+        <v>226</v>
+      </c>
+      <c r="O16" t="n">
+        <v>3</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>6</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0.5225589225589224</v>
+      </c>
+      <c r="T16" t="n">
+        <v>8.125588423014889</v>
+      </c>
+      <c r="U16" t="n">
+        <v>-1.102558922558924</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0.5488925677006762</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0.8566329966329818</v>
+      </c>
+      <c r="X16" t="n">
+        <v>-2.673857542955837</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>10210373.44578366</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>7.527104377104379</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0.3793988648090814</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>5.849153488840017</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>12410824.91582492</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>6.508754208754212</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="inlineStr"/>
+      <c r="AH16" t="inlineStr"/>
+      <c r="AI16" t="inlineStr"/>
+      <c r="AJ16" t="inlineStr"/>
+      <c r="AK16" t="inlineStr"/>
+      <c r="AL16" t="inlineStr"/>
+      <c r="AM16" t="inlineStr"/>
+      <c r="AN16" t="inlineStr"/>
+      <c r="AO16" t="inlineStr"/>
+      <c r="AP16" t="inlineStr"/>
+      <c r="AQ16" t="inlineStr"/>
+      <c r="AR16" t="inlineStr"/>
+      <c r="AS16" t="inlineStr"/>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AU16" t="inlineStr"/>
+      <c r="AV16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr"/>
+      <c r="AX16" t="inlineStr"/>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr"/>
+      <c r="BA16" t="inlineStr"/>
+      <c r="BB16" t="inlineStr"/>
+      <c r="BC16" t="inlineStr"/>
+      <c r="BD16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>jqSiuc6F</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45521.58333333334</v>
+      </c>
+      <c r="C17" t="n">
+        <v>101</v>
+      </c>
+      <c r="D17" t="n">
+        <v>133</v>
+      </c>
+      <c r="E17" t="n">
+        <v>21029</v>
+      </c>
+      <c r="F17" t="n">
+        <v>826</v>
+      </c>
+      <c r="G17" t="n">
+        <v>545</v>
+      </c>
+      <c r="H17" t="n">
+        <v>55</v>
+      </c>
+      <c r="I17" t="n">
+        <v>551</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="M17" t="n">
+        <v>312</v>
+      </c>
+      <c r="N17" t="n">
+        <v>257</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>4</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1</v>
+      </c>
+      <c r="S17" t="n">
+        <v>-0.1988005050505053</v>
+      </c>
+      <c r="T17" t="n">
+        <v>-0.6812072917335996</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.476388888888891</v>
+      </c>
+      <c r="V17" t="n">
+        <v>3.056115716642012</v>
+      </c>
+      <c r="W17" t="n">
+        <v>2.201515151515167</v>
+      </c>
+      <c r="X17" t="n">
+        <v>-2.853552685131628</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>-3498376.978771716</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>-2.560290404040401</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>-0.1210440631493261</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>-4.313757684810327</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>-5311223.169191919</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>-2.145517676767682</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="inlineStr"/>
+      <c r="AH17" t="inlineStr"/>
+      <c r="AI17" t="inlineStr"/>
+      <c r="AJ17" t="inlineStr"/>
+      <c r="AK17" t="inlineStr"/>
+      <c r="AL17" t="inlineStr"/>
+      <c r="AM17" t="inlineStr"/>
+      <c r="AN17" t="inlineStr"/>
+      <c r="AO17" t="inlineStr"/>
+      <c r="AP17" t="inlineStr"/>
+      <c r="AQ17" t="inlineStr"/>
+      <c r="AR17" t="inlineStr"/>
+      <c r="AS17" t="inlineStr"/>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AU17" t="inlineStr"/>
+      <c r="AV17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr"/>
+      <c r="AX17" t="inlineStr"/>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr"/>
+      <c r="BA17" t="inlineStr"/>
+      <c r="BB17" t="inlineStr"/>
+      <c r="BC17" t="inlineStr"/>
+      <c r="BD17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>0js8u60b</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45521.5</v>
+      </c>
+      <c r="C18" t="n">
+        <v>101</v>
+      </c>
+      <c r="D18" t="n">
+        <v>134</v>
+      </c>
+      <c r="E18" t="n">
+        <v>15220</v>
+      </c>
+      <c r="F18" t="n">
+        <v>211</v>
+      </c>
+      <c r="G18" t="n">
+        <v>303</v>
+      </c>
+      <c r="H18" t="n">
+        <v>55</v>
+      </c>
+      <c r="I18" t="n">
+        <v>551</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="M18" t="n">
+        <v>152</v>
+      </c>
+      <c r="N18" t="n">
+        <v>67</v>
+      </c>
+      <c r="O18" t="n">
+        <v>-5</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>-0.3848484848484846</v>
+      </c>
+      <c r="T18" t="n">
+        <v>-3.770397808246102</v>
+      </c>
+      <c r="U18" t="n">
+        <v>-0.7106060606060538</v>
+      </c>
+      <c r="V18" t="n">
+        <v>-3.824925876783453</v>
+      </c>
+      <c r="W18" t="n">
+        <v>-2.096969696969694</v>
+      </c>
+      <c r="X18" t="n">
+        <v>-0.5654180385604519</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>-5482357.527806443</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>-1.922727272727272</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>-0.1205530165282489</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>-4.389276295313451</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>-5597727.272727274</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>-2.351515151515159</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="inlineStr"/>
+      <c r="AH18" t="inlineStr"/>
+      <c r="AI18" t="inlineStr"/>
+      <c r="AJ18" t="inlineStr"/>
+      <c r="AK18" t="inlineStr"/>
+      <c r="AL18" t="inlineStr"/>
+      <c r="AM18" t="inlineStr"/>
+      <c r="AN18" t="inlineStr"/>
+      <c r="AO18" t="inlineStr"/>
+      <c r="AP18" t="inlineStr"/>
+      <c r="AQ18" t="inlineStr"/>
+      <c r="AR18" t="inlineStr"/>
+      <c r="AS18" t="inlineStr"/>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AU18" t="inlineStr"/>
+      <c r="AV18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr"/>
+      <c r="AX18" t="inlineStr"/>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr"/>
+      <c r="BA18" t="inlineStr"/>
+      <c r="BB18" t="inlineStr"/>
+      <c r="BC18" t="inlineStr"/>
+      <c r="BD18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>SOLVXEbk</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45520.65625</v>
+      </c>
+      <c r="C19" t="n">
+        <v>102</v>
+      </c>
+      <c r="D19" t="n">
+        <v>133</v>
+      </c>
+      <c r="E19" t="n">
+        <v>25178</v>
+      </c>
+      <c r="F19" t="n">
+        <v>194</v>
+      </c>
+      <c r="G19" t="n">
+        <v>129</v>
+      </c>
+      <c r="H19" t="n">
+        <v>55</v>
+      </c>
+      <c r="I19" t="n">
+        <v>551</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="M19" t="n">
+        <v>12</v>
+      </c>
+      <c r="N19" t="n">
+        <v>37</v>
+      </c>
+      <c r="O19" t="n">
+        <v>-9</v>
+      </c>
+      <c r="P19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>-3</v>
+      </c>
+      <c r="R19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="S19" t="n">
+        <v>-1.237777777777777</v>
+      </c>
+      <c r="T19" t="n">
+        <v>-10.19279365827184</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.049646464646461</v>
+      </c>
+      <c r="V19" t="n">
+        <v>-2.451684899741764</v>
+      </c>
+      <c r="W19" t="n">
+        <v>2.663181818181783</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.202641102207476</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>-29631870.98981469</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>-10.15191919191919</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>-1.164974147553758</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>-8.587952293808456</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>-36142222.22222222</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>-9.26934343434344</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="inlineStr"/>
+      <c r="AH19" t="inlineStr"/>
+      <c r="AI19" t="inlineStr"/>
+      <c r="AJ19" t="inlineStr"/>
+      <c r="AK19" t="inlineStr"/>
+      <c r="AL19" t="inlineStr"/>
+      <c r="AM19" t="inlineStr"/>
+      <c r="AN19" t="inlineStr"/>
+      <c r="AO19" t="inlineStr"/>
+      <c r="AP19" t="inlineStr"/>
+      <c r="AQ19" t="inlineStr"/>
+      <c r="AR19" t="inlineStr"/>
+      <c r="AS19" t="inlineStr"/>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AU19" t="inlineStr"/>
+      <c r="AV19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr"/>
+      <c r="AX19" t="inlineStr"/>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr"/>
+      <c r="BA19" t="inlineStr"/>
+      <c r="BB19" t="inlineStr"/>
+      <c r="BC19" t="inlineStr"/>
+      <c r="BD19" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/france/p6_deployment/data_preparation/df_tagged.xlsx
+++ b/data/france/p6_deployment/data_preparation/df_tagged.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BD19"/>
+  <dimension ref="A1:BD10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -520,62 +520,62 @@
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_age_player_start</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_int_rep_player_start</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_start</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_pot_player_sub</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_start</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_hei_player_sub</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_start</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_hei_player_start</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_start</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_sub</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_sub</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_sub</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_age_player_sub</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_sub</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_start</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_sub</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_sub</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_start</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_start</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
@@ -712,26 +712,26 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>OCd990al</t>
+          <t>zkPwWhT1</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45529.5</v>
+        <v>45522.65625</v>
       </c>
       <c r="C2" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D2" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E2" t="n">
-        <v>38223</v>
+        <v>29778</v>
       </c>
       <c r="F2" t="n">
-        <v>273</v>
+        <v>573</v>
       </c>
       <c r="G2" t="n">
-        <v>133</v>
+        <v>39</v>
       </c>
       <c r="H2" t="n">
         <v>55</v>
@@ -753,58 +753,58 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>193</v>
+        <v>312</v>
       </c>
       <c r="N2" t="n">
-        <v>7</v>
+        <v>37</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q2" t="n">
-        <v>3</v>
+        <v>-5</v>
       </c>
       <c r="R2" t="n">
         <v>1</v>
       </c>
       <c r="S2" t="n">
-        <v>0.07575757575757591</v>
+        <v>-3.092352092352094</v>
       </c>
       <c r="T2" t="n">
-        <v>2.578439153439149</v>
+        <v>-0.4085137085137087</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4393939393939377</v>
+        <v>518340.548340546</v>
       </c>
       <c r="V2" t="n">
-        <v>-2.361838624338617</v>
+        <v>0.9351344790973286</v>
       </c>
       <c r="W2" t="n">
-        <v>-1.484848484848499</v>
+        <v>2.54999169790193</v>
       </c>
       <c r="X2" t="n">
-        <v>1.457804232804229</v>
+        <v>-0.9551226551226364</v>
       </c>
       <c r="Y2" t="n">
-        <v>2498597.883597883</v>
+        <v>-0.6877344877344456</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.984848484848484</v>
+        <v>1.383549783549782</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.2264550264550267</v>
+        <v>-0.2061128013140394</v>
       </c>
       <c r="AB2" t="n">
-        <v>3.19259259259259</v>
+        <v>-0.2816242180019231</v>
       </c>
       <c r="AC2" t="n">
-        <v>5923484.848484852</v>
+        <v>2659292.869726306</v>
       </c>
       <c r="AD2" t="n">
-        <v>2.030303030303031</v>
+        <v>-2.209551619690934</v>
       </c>
       <c r="AE2" t="n">
         <v>0</v>
@@ -838,26 +838,26 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>ObHze1pe</t>
+          <t>2NocJFqd</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45529.5</v>
+        <v>45522.5</v>
       </c>
       <c r="C3" t="n">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D3" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E3" t="n">
-        <v>35322</v>
+        <v>18752</v>
       </c>
       <c r="F3" t="n">
-        <v>858</v>
+        <v>431</v>
       </c>
       <c r="G3" t="n">
-        <v>228</v>
+        <v>176</v>
       </c>
       <c r="H3" t="n">
         <v>55</v>
@@ -879,58 +879,58 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>67</v>
+        <v>35</v>
       </c>
       <c r="N3" t="n">
-        <v>181</v>
+        <v>234</v>
       </c>
       <c r="O3" t="n">
-        <v>-1</v>
+        <v>-3</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="Q3" t="n">
-        <v>6</v>
+        <v>-4</v>
       </c>
       <c r="R3" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="S3" t="n">
-        <v>0.5151515151515149</v>
+        <v>-0.1722943722943775</v>
       </c>
       <c r="T3" t="n">
-        <v>2.247618711516225</v>
+        <v>-0.3939393939393945</v>
       </c>
       <c r="U3" t="n">
-        <v>0.8311688311688279</v>
+        <v>-11204826.83982684</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.4423869350111715</v>
+        <v>-6.707141403569977</v>
       </c>
       <c r="W3" t="n">
-        <v>1.83766233766238</v>
+        <v>4.851979039479033</v>
       </c>
       <c r="X3" t="n">
-        <v>1.942084442472645</v>
+        <v>-8.214285714285708</v>
       </c>
       <c r="Y3" t="n">
-        <v>1325279.161401056</v>
+        <v>2.754112554112538</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.675324675324674</v>
+        <v>-6.84632034632034</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.1540521676391242</v>
+        <v>-0.381613756613757</v>
       </c>
       <c r="AB3" t="n">
-        <v>4.71931045145331</v>
+        <v>-8.970034595034591</v>
       </c>
       <c r="AC3" t="n">
-        <v>2609523.80952381</v>
+        <v>-5934025.234025234</v>
       </c>
       <c r="AD3" t="n">
-        <v>4.017316017316034</v>
+        <v>-1.461131461131458</v>
       </c>
       <c r="AE3" t="n">
         <v>0</v>
@@ -964,26 +964,26 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>pSpI7vU0</t>
+          <t>M5VGwpVA</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45529.5</v>
+        <v>45522.5</v>
       </c>
       <c r="C4" t="n">
         <v>101</v>
       </c>
       <c r="D4" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E4" t="n">
-        <v>59186</v>
+        <v>20484</v>
       </c>
       <c r="F4" t="n">
-        <v>56</v>
+        <v>242</v>
       </c>
       <c r="G4" t="n">
-        <v>33</v>
+        <v>516</v>
       </c>
       <c r="H4" t="n">
         <v>55</v>
@@ -1005,58 +1005,58 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>165</v>
+        <v>193</v>
       </c>
       <c r="N4" t="n">
-        <v>141</v>
+        <v>55</v>
       </c>
       <c r="O4" t="n">
-        <v>6</v>
+        <v>-4</v>
       </c>
       <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>5</v>
+      </c>
+      <c r="R4" t="n">
         <v>2</v>
       </c>
-      <c r="Q4" t="n">
-        <v>12</v>
-      </c>
-      <c r="R4" t="n">
-        <v>3</v>
-      </c>
       <c r="S4" t="n">
-        <v>0.5677729677729679</v>
+        <v>2.556734006734004</v>
       </c>
       <c r="T4" t="n">
-        <v>-2.70817174956106</v>
+        <v>0.119023569023569</v>
       </c>
       <c r="U4" t="n">
-        <v>3.033092833092834</v>
+        <v>770656.5656565651</v>
       </c>
       <c r="V4" t="n">
-        <v>-2.441684983403263</v>
+        <v>-1.066762431468305</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.1331409331409361</v>
+        <v>-1.289739634240874</v>
       </c>
       <c r="X4" t="n">
-        <v>2.440366094603711</v>
+        <v>1.532659932659925</v>
       </c>
       <c r="Y4" t="n">
-        <v>-4756542.263635918</v>
+        <v>-0.6917508417508316</v>
       </c>
       <c r="Z4" t="n">
-        <v>-2.536411736411722</v>
+        <v>-1.627104377104388</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.2753911851822068</v>
+        <v>-0.09041581701428236</v>
       </c>
       <c r="AB4" t="n">
-        <v>-0.5081460614548945</v>
+        <v>0.5527193039980745</v>
       </c>
       <c r="AC4" t="n">
-        <v>-4784165.464165462</v>
+        <v>116772.5180001399</v>
       </c>
       <c r="AD4" t="n">
-        <v>-0.02938912938914484</v>
+        <v>0.7483340047278659</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
@@ -1090,26 +1090,26 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>xrJSdNFr</t>
+          <t>6ehlLyFq</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45529.5</v>
+        <v>45522.5</v>
       </c>
       <c r="C5" t="n">
         <v>101</v>
       </c>
       <c r="D5" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E5" t="n">
-        <v>26109</v>
+        <v>33150</v>
       </c>
       <c r="F5" t="n">
-        <v>736</v>
+        <v>341</v>
       </c>
       <c r="G5" t="n">
-        <v>399</v>
+        <v>599</v>
       </c>
       <c r="H5" t="n">
         <v>55</v>
@@ -1131,58 +1131,58 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="N5" t="n">
-        <v>211</v>
+        <v>141</v>
       </c>
       <c r="O5" t="n">
-        <v>-6</v>
+        <v>-1</v>
       </c>
       <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1</v>
+      </c>
+      <c r="R5" t="n">
         <v>-1</v>
       </c>
-      <c r="Q5" t="n">
-        <v>4</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1</v>
-      </c>
       <c r="S5" t="n">
-        <v>-0.5114478114478114</v>
+        <v>-3.454545454545453</v>
       </c>
       <c r="T5" t="n">
-        <v>-2.696465081759214</v>
+        <v>-0.439393939393939</v>
       </c>
       <c r="U5" t="n">
-        <v>-2.293097643097639</v>
+        <v>1494696.969696969</v>
       </c>
       <c r="V5" t="n">
-        <v>1.318052263640453</v>
+        <v>3.35132771817554</v>
       </c>
       <c r="W5" t="n">
-        <v>1.993265993265965</v>
+        <v>0.8007638496768834</v>
       </c>
       <c r="X5" t="n">
-        <v>0.8438100026335285</v>
+        <v>0.2121212121212039</v>
       </c>
       <c r="Y5" t="n">
-        <v>-6466870.286576169</v>
+        <v>0.7121212121211613</v>
       </c>
       <c r="Z5" t="n">
-        <v>-0.763804713804717</v>
+        <v>3.666666666666671</v>
       </c>
       <c r="AA5" t="n">
-        <v>-0.1598027245086071</v>
+        <v>-0.1540521676391242</v>
       </c>
       <c r="AB5" t="n">
-        <v>-3.619316957552243</v>
+        <v>0.4045815295815487</v>
       </c>
       <c r="AC5" t="n">
-        <v>-5898838.383838383</v>
+        <v>899858.2486354224</v>
       </c>
       <c r="AD5" t="n">
-        <v>-4.500841750841758</v>
+        <v>-2.494082909843787</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
@@ -1216,26 +1216,26 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hhlQ5IbD</t>
+          <t>ripawyyS</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45529.5</v>
+        <v>45522.41666666666</v>
       </c>
       <c r="C6" t="n">
         <v>101</v>
       </c>
       <c r="D6" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E6" t="n">
-        <v>67394</v>
+        <v>17924</v>
       </c>
       <c r="F6" t="n">
-        <v>448</v>
+        <v>342</v>
       </c>
       <c r="G6" t="n">
-        <v>579</v>
+        <v>370</v>
       </c>
       <c r="H6" t="n">
         <v>55</v>
@@ -1257,58 +1257,58 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>12</v>
+        <v>128</v>
       </c>
       <c r="N6" t="n">
-        <v>211</v>
+        <v>257</v>
       </c>
       <c r="O6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P6" t="n">
-        <v>3</v>
+        <v>-1</v>
       </c>
       <c r="Q6" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="R6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0.4412247474747475</v>
+        <v>2.29004329004329</v>
       </c>
       <c r="T6" t="n">
-        <v>1.18043679460088</v>
+        <v>-0.3333333333333337</v>
       </c>
       <c r="U6" t="n">
-        <v>1.28270202020202</v>
+        <v>-10976948.05194805</v>
       </c>
       <c r="V6" t="n">
-        <v>0.4084750274379019</v>
+        <v>-6.999683326281072</v>
       </c>
       <c r="W6" t="n">
-        <v>1.437878787878788</v>
+        <v>-0.7203438791785004</v>
       </c>
       <c r="X6" t="n">
-        <v>2.17369567710125</v>
+        <v>-6.517316017316034</v>
       </c>
       <c r="Y6" t="n">
-        <v>5917058.168296559</v>
+        <v>-2.549783549783541</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.3754419191919141</v>
+        <v>-8.417748917748924</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.190220240142841</v>
+        <v>-0.3244569757727656</v>
       </c>
       <c r="AB6" t="n">
-        <v>5.883644159418168</v>
+        <v>-8.529176024476783</v>
       </c>
       <c r="AC6" t="n">
-        <v>4697738.320707072</v>
+        <v>-6666662.191192267</v>
       </c>
       <c r="AD6" t="n">
-        <v>2.850063131313135</v>
+        <v>-0.255804554676736</v>
       </c>
       <c r="AE6" t="n">
         <v>0</v>
@@ -1342,26 +1342,26 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>CKcVGr7E</t>
+          <t>fHYrsJy3</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45529.5</v>
+        <v>45521.66666666666</v>
       </c>
       <c r="C7" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D7" t="n">
         <v>133</v>
       </c>
       <c r="E7" t="n">
-        <v>50186</v>
+        <v>18523</v>
       </c>
       <c r="F7" t="n">
-        <v>777</v>
+        <v>47</v>
       </c>
       <c r="G7" t="n">
-        <v>292</v>
+        <v>362</v>
       </c>
       <c r="H7" t="n">
         <v>55</v>
@@ -1383,58 +1383,58 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>98</v>
+        <v>67</v>
       </c>
       <c r="N7" t="n">
-        <v>199</v>
+        <v>226</v>
       </c>
       <c r="O7" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R7" t="n">
         <v>1</v>
       </c>
       <c r="S7" t="n">
-        <v>0.4606060606060609</v>
+        <v>-1.102558922558924</v>
       </c>
       <c r="T7" t="n">
-        <v>7.399870555509651</v>
+        <v>0.5225589225589224</v>
       </c>
       <c r="U7" t="n">
-        <v>-2.315584415584418</v>
+        <v>12410824.91582492</v>
       </c>
       <c r="V7" t="n">
-        <v>-2.129805282436877</v>
+        <v>8.125588423014889</v>
       </c>
       <c r="W7" t="n">
-        <v>-2.8116883116883</v>
+        <v>0.5488925677006762</v>
       </c>
       <c r="X7" t="n">
-        <v>1.24860227491806</v>
+        <v>6.508754208754212</v>
       </c>
       <c r="Y7" t="n">
-        <v>6499103.688708952</v>
+        <v>0.8566329966329818</v>
       </c>
       <c r="Z7" t="n">
-        <v>8.969047619047615</v>
+        <v>7.527104377104379</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.2065355696934643</v>
+        <v>0.3793988648090814</v>
       </c>
       <c r="AB7" t="n">
-        <v>8.59683182314761</v>
+        <v>5.849153488840017</v>
       </c>
       <c r="AC7" t="n">
-        <v>11492554.11255411</v>
+        <v>10210373.44578366</v>
       </c>
       <c r="AD7" t="n">
-        <v>7.830952380952382</v>
+        <v>-2.673857542955837</v>
       </c>
       <c r="AE7" t="n">
         <v>0</v>
@@ -1468,26 +1468,26 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>8nivFMyR</t>
+          <t>jqSiuc6F</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45529.5</v>
+        <v>45521.58333333334</v>
       </c>
       <c r="C8" t="n">
         <v>101</v>
       </c>
       <c r="D8" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E8" t="n">
-        <v>36178</v>
+        <v>21029</v>
       </c>
       <c r="F8" t="n">
-        <v>535</v>
+        <v>826</v>
       </c>
       <c r="G8" t="n">
-        <v>226</v>
+        <v>545</v>
       </c>
       <c r="H8" t="n">
         <v>55</v>
@@ -1509,58 +1509,58 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>98</v>
+        <v>312</v>
       </c>
       <c r="N8" t="n">
-        <v>7</v>
+        <v>257</v>
       </c>
       <c r="O8" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="R8" t="n">
         <v>1</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2575757575757578</v>
+        <v>1.476388888888891</v>
       </c>
       <c r="T8" t="n">
-        <v>1.400736896589308</v>
+        <v>-0.1988005050505053</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3333333333333357</v>
+        <v>-5311223.169191919</v>
       </c>
       <c r="V8" t="n">
-        <v>0.3619669645127885</v>
+        <v>-0.6812072917335996</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>3.056115716642012</v>
       </c>
       <c r="X8" t="n">
-        <v>0.807803022047878</v>
+        <v>-2.145517676767682</v>
       </c>
       <c r="Y8" t="n">
-        <v>4441524.781155787</v>
+        <v>2.201515151515167</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.075757575757578</v>
+        <v>-2.560290404040401</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.3244569757727656</v>
+        <v>-0.1210440631493261</v>
       </c>
       <c r="AB8" t="n">
-        <v>3.405284043441924</v>
+        <v>-4.313757684810327</v>
       </c>
       <c r="AC8" t="n">
-        <v>6872727.272727273</v>
+        <v>-3498376.978771716</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.287878787878796</v>
+        <v>-2.853552685131628</v>
       </c>
       <c r="AE8" t="n">
         <v>0</v>
@@ -1594,26 +1594,26 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>ppvl45N8</t>
+          <t>0js8u60b</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45529.5</v>
+        <v>45521.5</v>
       </c>
       <c r="C9" t="n">
         <v>101</v>
       </c>
       <c r="D9" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E9" t="n">
-        <v>48229</v>
+        <v>15220</v>
       </c>
       <c r="F9" t="n">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="G9" t="n">
-        <v>157</v>
+        <v>303</v>
       </c>
       <c r="H9" t="n">
         <v>55</v>
@@ -1635,58 +1635,58 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="N9" t="n">
-        <v>234</v>
+        <v>67</v>
       </c>
       <c r="O9" t="n">
-        <v>14</v>
+        <v>-5</v>
       </c>
       <c r="P9" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0.9483838383838379</v>
+        <v>-0.7106060606060538</v>
       </c>
       <c r="T9" t="n">
-        <v>7.424873253394921</v>
+        <v>-0.3848484848484846</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3435858585858576</v>
+        <v>-5597727.272727274</v>
       </c>
       <c r="V9" t="n">
-        <v>2.453119797372267</v>
+        <v>-3.770397808246102</v>
       </c>
       <c r="W9" t="n">
-        <v>0.6337878787878992</v>
+        <v>-3.824925876783453</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.6812499128815048</v>
+        <v>-2.351515151515159</v>
       </c>
       <c r="Y9" t="n">
-        <v>28295053.06940981</v>
+        <v>-2.096969696969694</v>
       </c>
       <c r="Z9" t="n">
-        <v>7.13525252525254</v>
+        <v>-1.922727272727272</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.9665154403993992</v>
+        <v>-0.1205530165282489</v>
       </c>
       <c r="AB9" t="n">
-        <v>6.829708102412084</v>
+        <v>-4.389276295313451</v>
       </c>
       <c r="AC9" t="n">
-        <v>33796010.1010101</v>
+        <v>-5482357.527806443</v>
       </c>
       <c r="AD9" t="n">
-        <v>7.904191919191931</v>
+        <v>-0.5654180385604519</v>
       </c>
       <c r="AE9" t="n">
         <v>0</v>
@@ -1720,26 +1720,26 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>KQAqguF7</t>
+          <t>SOLVXEbk</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45529.5</v>
+        <v>45520.65625</v>
       </c>
       <c r="C10" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D10" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E10" t="n">
-        <v>42000</v>
+        <v>25178</v>
       </c>
       <c r="F10" t="n">
-        <v>528</v>
+        <v>194</v>
       </c>
       <c r="G10" t="n">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="H10" t="n">
         <v>55</v>
@@ -1761,58 +1761,58 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>103</v>
+        <v>12</v>
       </c>
       <c r="N10" t="n">
-        <v>67</v>
+        <v>37</v>
       </c>
       <c r="O10" t="n">
-        <v>2</v>
+        <v>-9</v>
       </c>
       <c r="P10" t="n">
         <v>-1</v>
       </c>
       <c r="Q10" t="n">
-        <v>3</v>
+        <v>-3</v>
       </c>
       <c r="R10" t="n">
         <v>-1</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1.049646464646461</v>
       </c>
       <c r="T10" t="n">
-        <v>0.1785967655532801</v>
+        <v>-1.237777777777777</v>
       </c>
       <c r="U10" t="n">
-        <v>0.192121212121215</v>
+        <v>-36142222.22222222</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.6869468092294255</v>
+        <v>-10.19279365827184</v>
       </c>
       <c r="W10" t="n">
-        <v>-4.634242424242416</v>
+        <v>-2.451684899741764</v>
       </c>
       <c r="X10" t="n">
-        <v>0.3295078713556947</v>
+        <v>-9.26934343434344</v>
       </c>
       <c r="Y10" t="n">
-        <v>-426208.3628931455</v>
+        <v>2.663181818181783</v>
       </c>
       <c r="Z10" t="n">
-        <v>-0.9666666666666828</v>
+        <v>-10.15191919191919</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>-1.164974147553758</v>
       </c>
       <c r="AB10" t="n">
-        <v>-0.2345413644326584</v>
+        <v>-8.587952293808456</v>
       </c>
       <c r="AC10" t="n">
-        <v>-670606.060606061</v>
+        <v>-29631870.98981469</v>
       </c>
       <c r="AD10" t="n">
-        <v>-1.190909090909088</v>
+        <v>1.202641102207476</v>
       </c>
       <c r="AE10" t="n">
         <v>0</v>
@@ -1843,1140 +1843,6 @@
       <c r="BC10" t="inlineStr"/>
       <c r="BD10" t="inlineStr"/>
     </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>zkPwWhT1</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="n">
-        <v>45522.65625</v>
-      </c>
-      <c r="C11" t="n">
-        <v>102</v>
-      </c>
-      <c r="D11" t="n">
-        <v>134</v>
-      </c>
-      <c r="E11" t="n">
-        <v>29778</v>
-      </c>
-      <c r="F11" t="n">
-        <v>573</v>
-      </c>
-      <c r="G11" t="n">
-        <v>39</v>
-      </c>
-      <c r="H11" t="n">
-        <v>55</v>
-      </c>
-      <c r="I11" t="n">
-        <v>551</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-      <c r="M11" t="n">
-        <v>312</v>
-      </c>
-      <c r="N11" t="n">
-        <v>37</v>
-      </c>
-      <c r="O11" t="n">
-        <v>-8</v>
-      </c>
-      <c r="P11" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>-5</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1</v>
-      </c>
-      <c r="S11" t="n">
-        <v>-0.4085137085137087</v>
-      </c>
-      <c r="T11" t="n">
-        <v>0.9351344790973286</v>
-      </c>
-      <c r="U11" t="n">
-        <v>-3.092352092352094</v>
-      </c>
-      <c r="V11" t="n">
-        <v>2.54999169790193</v>
-      </c>
-      <c r="W11" t="n">
-        <v>-0.6877344877344456</v>
-      </c>
-      <c r="X11" t="n">
-        <v>-2.209551619690934</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>2659292.869726306</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>1.383549783549782</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>-0.2061128013140394</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>-0.2816242180019231</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>518340.548340546</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>-0.9551226551226364</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF11" t="inlineStr"/>
-      <c r="AG11" t="inlineStr"/>
-      <c r="AH11" t="inlineStr"/>
-      <c r="AI11" t="inlineStr"/>
-      <c r="AJ11" t="inlineStr"/>
-      <c r="AK11" t="inlineStr"/>
-      <c r="AL11" t="inlineStr"/>
-      <c r="AM11" t="inlineStr"/>
-      <c r="AN11" t="inlineStr"/>
-      <c r="AO11" t="inlineStr"/>
-      <c r="AP11" t="inlineStr"/>
-      <c r="AQ11" t="inlineStr"/>
-      <c r="AR11" t="inlineStr"/>
-      <c r="AS11" t="inlineStr"/>
-      <c r="AT11" t="inlineStr"/>
-      <c r="AU11" t="inlineStr"/>
-      <c r="AV11" t="inlineStr"/>
-      <c r="AW11" t="inlineStr"/>
-      <c r="AX11" t="inlineStr"/>
-      <c r="AY11" t="inlineStr"/>
-      <c r="AZ11" t="inlineStr"/>
-      <c r="BA11" t="inlineStr"/>
-      <c r="BB11" t="inlineStr"/>
-      <c r="BC11" t="inlineStr"/>
-      <c r="BD11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>6ehlLyFq</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>45522.5</v>
-      </c>
-      <c r="C12" t="n">
-        <v>101</v>
-      </c>
-      <c r="D12" t="n">
-        <v>133</v>
-      </c>
-      <c r="E12" t="n">
-        <v>33150</v>
-      </c>
-      <c r="F12" t="n">
-        <v>341</v>
-      </c>
-      <c r="G12" t="n">
-        <v>599</v>
-      </c>
-      <c r="H12" t="n">
-        <v>55</v>
-      </c>
-      <c r="I12" t="n">
-        <v>551</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-      <c r="M12" t="n">
-        <v>152</v>
-      </c>
-      <c r="N12" t="n">
-        <v>141</v>
-      </c>
-      <c r="O12" t="n">
-        <v>-1</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1</v>
-      </c>
-      <c r="R12" t="n">
-        <v>-1</v>
-      </c>
-      <c r="S12" t="n">
-        <v>-0.439393939393939</v>
-      </c>
-      <c r="T12" t="n">
-        <v>3.35132771817554</v>
-      </c>
-      <c r="U12" t="n">
-        <v>-3.454545454545453</v>
-      </c>
-      <c r="V12" t="n">
-        <v>0.8007638496768834</v>
-      </c>
-      <c r="W12" t="n">
-        <v>0.7121212121211613</v>
-      </c>
-      <c r="X12" t="n">
-        <v>-2.494082909843787</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>899858.2486354224</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>3.666666666666671</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>-0.1540521676391242</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>0.4045815295815487</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>1494696.969696969</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>0.2121212121212039</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF12" t="inlineStr"/>
-      <c r="AG12" t="inlineStr"/>
-      <c r="AH12" t="inlineStr"/>
-      <c r="AI12" t="inlineStr"/>
-      <c r="AJ12" t="inlineStr"/>
-      <c r="AK12" t="inlineStr"/>
-      <c r="AL12" t="inlineStr"/>
-      <c r="AM12" t="inlineStr"/>
-      <c r="AN12" t="inlineStr"/>
-      <c r="AO12" t="inlineStr"/>
-      <c r="AP12" t="inlineStr"/>
-      <c r="AQ12" t="inlineStr"/>
-      <c r="AR12" t="inlineStr"/>
-      <c r="AS12" t="inlineStr"/>
-      <c r="AT12" t="inlineStr"/>
-      <c r="AU12" t="inlineStr"/>
-      <c r="AV12" t="inlineStr"/>
-      <c r="AW12" t="inlineStr"/>
-      <c r="AX12" t="inlineStr"/>
-      <c r="AY12" t="inlineStr"/>
-      <c r="AZ12" t="inlineStr"/>
-      <c r="BA12" t="inlineStr"/>
-      <c r="BB12" t="inlineStr"/>
-      <c r="BC12" t="inlineStr"/>
-      <c r="BD12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>M5VGwpVA</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n">
-        <v>45522.5</v>
-      </c>
-      <c r="C13" t="n">
-        <v>101</v>
-      </c>
-      <c r="D13" t="n">
-        <v>134</v>
-      </c>
-      <c r="E13" t="n">
-        <v>20484</v>
-      </c>
-      <c r="F13" t="n">
-        <v>242</v>
-      </c>
-      <c r="G13" t="n">
-        <v>516</v>
-      </c>
-      <c r="H13" t="n">
-        <v>55</v>
-      </c>
-      <c r="I13" t="n">
-        <v>551</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-      <c r="M13" t="n">
-        <v>193</v>
-      </c>
-      <c r="N13" t="n">
-        <v>55</v>
-      </c>
-      <c r="O13" t="n">
-        <v>-4</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>5</v>
-      </c>
-      <c r="R13" t="n">
-        <v>2</v>
-      </c>
-      <c r="S13" t="n">
-        <v>0.119023569023569</v>
-      </c>
-      <c r="T13" t="n">
-        <v>-1.066762431468305</v>
-      </c>
-      <c r="U13" t="n">
-        <v>2.556734006734004</v>
-      </c>
-      <c r="V13" t="n">
-        <v>-1.289739634240874</v>
-      </c>
-      <c r="W13" t="n">
-        <v>-0.6917508417508316</v>
-      </c>
-      <c r="X13" t="n">
-        <v>0.7483340047278659</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>116772.5180001399</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>-1.627104377104388</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>-0.09041581701428236</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>0.5527193039980745</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>770656.5656565651</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.532659932659925</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF13" t="inlineStr"/>
-      <c r="AG13" t="inlineStr"/>
-      <c r="AH13" t="inlineStr"/>
-      <c r="AI13" t="inlineStr"/>
-      <c r="AJ13" t="inlineStr"/>
-      <c r="AK13" t="inlineStr"/>
-      <c r="AL13" t="inlineStr"/>
-      <c r="AM13" t="inlineStr"/>
-      <c r="AN13" t="inlineStr"/>
-      <c r="AO13" t="inlineStr"/>
-      <c r="AP13" t="inlineStr"/>
-      <c r="AQ13" t="inlineStr"/>
-      <c r="AR13" t="inlineStr"/>
-      <c r="AS13" t="inlineStr"/>
-      <c r="AT13" t="inlineStr"/>
-      <c r="AU13" t="inlineStr"/>
-      <c r="AV13" t="inlineStr"/>
-      <c r="AW13" t="inlineStr"/>
-      <c r="AX13" t="inlineStr"/>
-      <c r="AY13" t="inlineStr"/>
-      <c r="AZ13" t="inlineStr"/>
-      <c r="BA13" t="inlineStr"/>
-      <c r="BB13" t="inlineStr"/>
-      <c r="BC13" t="inlineStr"/>
-      <c r="BD13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>2NocJFqd</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>45522.5</v>
-      </c>
-      <c r="C14" t="n">
-        <v>101</v>
-      </c>
-      <c r="D14" t="n">
-        <v>134</v>
-      </c>
-      <c r="E14" t="n">
-        <v>18752</v>
-      </c>
-      <c r="F14" t="n">
-        <v>431</v>
-      </c>
-      <c r="G14" t="n">
-        <v>176</v>
-      </c>
-      <c r="H14" t="n">
-        <v>55</v>
-      </c>
-      <c r="I14" t="n">
-        <v>551</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-      <c r="M14" t="n">
-        <v>35</v>
-      </c>
-      <c r="N14" t="n">
-        <v>234</v>
-      </c>
-      <c r="O14" t="n">
-        <v>-3</v>
-      </c>
-      <c r="P14" t="n">
-        <v>-3</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>-4</v>
-      </c>
-      <c r="R14" t="n">
-        <v>-2</v>
-      </c>
-      <c r="S14" t="n">
-        <v>-0.3939393939393945</v>
-      </c>
-      <c r="T14" t="n">
-        <v>-6.707141403569977</v>
-      </c>
-      <c r="U14" t="n">
-        <v>-0.1722943722943775</v>
-      </c>
-      <c r="V14" t="n">
-        <v>4.851979039479033</v>
-      </c>
-      <c r="W14" t="n">
-        <v>2.754112554112538</v>
-      </c>
-      <c r="X14" t="n">
-        <v>-1.461131461131458</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>-5934025.234025234</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>-6.84632034632034</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>-0.381613756613757</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>-8.970034595034591</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>-11204826.83982684</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>-8.214285714285708</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF14" t="inlineStr"/>
-      <c r="AG14" t="inlineStr"/>
-      <c r="AH14" t="inlineStr"/>
-      <c r="AI14" t="inlineStr"/>
-      <c r="AJ14" t="inlineStr"/>
-      <c r="AK14" t="inlineStr"/>
-      <c r="AL14" t="inlineStr"/>
-      <c r="AM14" t="inlineStr"/>
-      <c r="AN14" t="inlineStr"/>
-      <c r="AO14" t="inlineStr"/>
-      <c r="AP14" t="inlineStr"/>
-      <c r="AQ14" t="inlineStr"/>
-      <c r="AR14" t="inlineStr"/>
-      <c r="AS14" t="inlineStr"/>
-      <c r="AT14" t="inlineStr"/>
-      <c r="AU14" t="inlineStr"/>
-      <c r="AV14" t="inlineStr"/>
-      <c r="AW14" t="inlineStr"/>
-      <c r="AX14" t="inlineStr"/>
-      <c r="AY14" t="inlineStr"/>
-      <c r="AZ14" t="inlineStr"/>
-      <c r="BA14" t="inlineStr"/>
-      <c r="BB14" t="inlineStr"/>
-      <c r="BC14" t="inlineStr"/>
-      <c r="BD14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>ripawyyS</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>45522.41666666666</v>
-      </c>
-      <c r="C15" t="n">
-        <v>101</v>
-      </c>
-      <c r="D15" t="n">
-        <v>134</v>
-      </c>
-      <c r="E15" t="n">
-        <v>17924</v>
-      </c>
-      <c r="F15" t="n">
-        <v>342</v>
-      </c>
-      <c r="G15" t="n">
-        <v>370</v>
-      </c>
-      <c r="H15" t="n">
-        <v>55</v>
-      </c>
-      <c r="I15" t="n">
-        <v>551</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-      <c r="M15" t="n">
-        <v>128</v>
-      </c>
-      <c r="N15" t="n">
-        <v>257</v>
-      </c>
-      <c r="O15" t="n">
-        <v>5</v>
-      </c>
-      <c r="P15" t="n">
-        <v>-1</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>8</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>-0.3333333333333337</v>
-      </c>
-      <c r="T15" t="n">
-        <v>-6.999683326281072</v>
-      </c>
-      <c r="U15" t="n">
-        <v>2.29004329004329</v>
-      </c>
-      <c r="V15" t="n">
-        <v>-0.7203438791785004</v>
-      </c>
-      <c r="W15" t="n">
-        <v>-2.549783549783541</v>
-      </c>
-      <c r="X15" t="n">
-        <v>-0.255804554676736</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>-6666662.191192267</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>-8.417748917748924</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>-0.3244569757727656</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>-8.529176024476783</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>-10976948.05194805</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>-6.517316017316034</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF15" t="inlineStr"/>
-      <c r="AG15" t="inlineStr"/>
-      <c r="AH15" t="inlineStr"/>
-      <c r="AI15" t="inlineStr"/>
-      <c r="AJ15" t="inlineStr"/>
-      <c r="AK15" t="inlineStr"/>
-      <c r="AL15" t="inlineStr"/>
-      <c r="AM15" t="inlineStr"/>
-      <c r="AN15" t="inlineStr"/>
-      <c r="AO15" t="inlineStr"/>
-      <c r="AP15" t="inlineStr"/>
-      <c r="AQ15" t="inlineStr"/>
-      <c r="AR15" t="inlineStr"/>
-      <c r="AS15" t="inlineStr"/>
-      <c r="AT15" t="inlineStr"/>
-      <c r="AU15" t="inlineStr"/>
-      <c r="AV15" t="inlineStr"/>
-      <c r="AW15" t="inlineStr"/>
-      <c r="AX15" t="inlineStr"/>
-      <c r="AY15" t="inlineStr"/>
-      <c r="AZ15" t="inlineStr"/>
-      <c r="BA15" t="inlineStr"/>
-      <c r="BB15" t="inlineStr"/>
-      <c r="BC15" t="inlineStr"/>
-      <c r="BD15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>fHYrsJy3</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="n">
-        <v>45521.66666666666</v>
-      </c>
-      <c r="C16" t="n">
-        <v>102</v>
-      </c>
-      <c r="D16" t="n">
-        <v>133</v>
-      </c>
-      <c r="E16" t="n">
-        <v>18523</v>
-      </c>
-      <c r="F16" t="n">
-        <v>47</v>
-      </c>
-      <c r="G16" t="n">
-        <v>362</v>
-      </c>
-      <c r="H16" t="n">
-        <v>55</v>
-      </c>
-      <c r="I16" t="n">
-        <v>551</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-      <c r="M16" t="n">
-        <v>67</v>
-      </c>
-      <c r="N16" t="n">
-        <v>226</v>
-      </c>
-      <c r="O16" t="n">
-        <v>3</v>
-      </c>
-      <c r="P16" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>6</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1</v>
-      </c>
-      <c r="S16" t="n">
-        <v>0.5225589225589224</v>
-      </c>
-      <c r="T16" t="n">
-        <v>8.125588423014889</v>
-      </c>
-      <c r="U16" t="n">
-        <v>-1.102558922558924</v>
-      </c>
-      <c r="V16" t="n">
-        <v>0.5488925677006762</v>
-      </c>
-      <c r="W16" t="n">
-        <v>0.8566329966329818</v>
-      </c>
-      <c r="X16" t="n">
-        <v>-2.673857542955837</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>10210373.44578366</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>7.527104377104379</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>0.3793988648090814</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>5.849153488840017</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>12410824.91582492</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>6.508754208754212</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF16" t="inlineStr"/>
-      <c r="AG16" t="inlineStr"/>
-      <c r="AH16" t="inlineStr"/>
-      <c r="AI16" t="inlineStr"/>
-      <c r="AJ16" t="inlineStr"/>
-      <c r="AK16" t="inlineStr"/>
-      <c r="AL16" t="inlineStr"/>
-      <c r="AM16" t="inlineStr"/>
-      <c r="AN16" t="inlineStr"/>
-      <c r="AO16" t="inlineStr"/>
-      <c r="AP16" t="inlineStr"/>
-      <c r="AQ16" t="inlineStr"/>
-      <c r="AR16" t="inlineStr"/>
-      <c r="AS16" t="inlineStr"/>
-      <c r="AT16" t="inlineStr"/>
-      <c r="AU16" t="inlineStr"/>
-      <c r="AV16" t="inlineStr"/>
-      <c r="AW16" t="inlineStr"/>
-      <c r="AX16" t="inlineStr"/>
-      <c r="AY16" t="inlineStr"/>
-      <c r="AZ16" t="inlineStr"/>
-      <c r="BA16" t="inlineStr"/>
-      <c r="BB16" t="inlineStr"/>
-      <c r="BC16" t="inlineStr"/>
-      <c r="BD16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>jqSiuc6F</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="n">
-        <v>45521.58333333334</v>
-      </c>
-      <c r="C17" t="n">
-        <v>101</v>
-      </c>
-      <c r="D17" t="n">
-        <v>133</v>
-      </c>
-      <c r="E17" t="n">
-        <v>21029</v>
-      </c>
-      <c r="F17" t="n">
-        <v>826</v>
-      </c>
-      <c r="G17" t="n">
-        <v>545</v>
-      </c>
-      <c r="H17" t="n">
-        <v>55</v>
-      </c>
-      <c r="I17" t="n">
-        <v>551</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-      <c r="M17" t="n">
-        <v>312</v>
-      </c>
-      <c r="N17" t="n">
-        <v>257</v>
-      </c>
-      <c r="O17" t="n">
-        <v>1</v>
-      </c>
-      <c r="P17" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>4</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1</v>
-      </c>
-      <c r="S17" t="n">
-        <v>-0.1988005050505053</v>
-      </c>
-      <c r="T17" t="n">
-        <v>-0.6812072917335996</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.476388888888891</v>
-      </c>
-      <c r="V17" t="n">
-        <v>3.056115716642012</v>
-      </c>
-      <c r="W17" t="n">
-        <v>2.201515151515167</v>
-      </c>
-      <c r="X17" t="n">
-        <v>-2.853552685131628</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>-3498376.978771716</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>-2.560290404040401</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>-0.1210440631493261</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>-4.313757684810327</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>-5311223.169191919</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>-2.145517676767682</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF17" t="inlineStr"/>
-      <c r="AG17" t="inlineStr"/>
-      <c r="AH17" t="inlineStr"/>
-      <c r="AI17" t="inlineStr"/>
-      <c r="AJ17" t="inlineStr"/>
-      <c r="AK17" t="inlineStr"/>
-      <c r="AL17" t="inlineStr"/>
-      <c r="AM17" t="inlineStr"/>
-      <c r="AN17" t="inlineStr"/>
-      <c r="AO17" t="inlineStr"/>
-      <c r="AP17" t="inlineStr"/>
-      <c r="AQ17" t="inlineStr"/>
-      <c r="AR17" t="inlineStr"/>
-      <c r="AS17" t="inlineStr"/>
-      <c r="AT17" t="inlineStr"/>
-      <c r="AU17" t="inlineStr"/>
-      <c r="AV17" t="inlineStr"/>
-      <c r="AW17" t="inlineStr"/>
-      <c r="AX17" t="inlineStr"/>
-      <c r="AY17" t="inlineStr"/>
-      <c r="AZ17" t="inlineStr"/>
-      <c r="BA17" t="inlineStr"/>
-      <c r="BB17" t="inlineStr"/>
-      <c r="BC17" t="inlineStr"/>
-      <c r="BD17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>0js8u60b</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="n">
-        <v>45521.5</v>
-      </c>
-      <c r="C18" t="n">
-        <v>101</v>
-      </c>
-      <c r="D18" t="n">
-        <v>134</v>
-      </c>
-      <c r="E18" t="n">
-        <v>15220</v>
-      </c>
-      <c r="F18" t="n">
-        <v>211</v>
-      </c>
-      <c r="G18" t="n">
-        <v>303</v>
-      </c>
-      <c r="H18" t="n">
-        <v>55</v>
-      </c>
-      <c r="I18" t="n">
-        <v>551</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-      <c r="M18" t="n">
-        <v>152</v>
-      </c>
-      <c r="N18" t="n">
-        <v>67</v>
-      </c>
-      <c r="O18" t="n">
-        <v>-5</v>
-      </c>
-      <c r="P18" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>-0.3848484848484846</v>
-      </c>
-      <c r="T18" t="n">
-        <v>-3.770397808246102</v>
-      </c>
-      <c r="U18" t="n">
-        <v>-0.7106060606060538</v>
-      </c>
-      <c r="V18" t="n">
-        <v>-3.824925876783453</v>
-      </c>
-      <c r="W18" t="n">
-        <v>-2.096969696969694</v>
-      </c>
-      <c r="X18" t="n">
-        <v>-0.5654180385604519</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>-5482357.527806443</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>-1.922727272727272</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>-0.1205530165282489</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>-4.389276295313451</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>-5597727.272727274</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>-2.351515151515159</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF18" t="inlineStr"/>
-      <c r="AG18" t="inlineStr"/>
-      <c r="AH18" t="inlineStr"/>
-      <c r="AI18" t="inlineStr"/>
-      <c r="AJ18" t="inlineStr"/>
-      <c r="AK18" t="inlineStr"/>
-      <c r="AL18" t="inlineStr"/>
-      <c r="AM18" t="inlineStr"/>
-      <c r="AN18" t="inlineStr"/>
-      <c r="AO18" t="inlineStr"/>
-      <c r="AP18" t="inlineStr"/>
-      <c r="AQ18" t="inlineStr"/>
-      <c r="AR18" t="inlineStr"/>
-      <c r="AS18" t="inlineStr"/>
-      <c r="AT18" t="inlineStr"/>
-      <c r="AU18" t="inlineStr"/>
-      <c r="AV18" t="inlineStr"/>
-      <c r="AW18" t="inlineStr"/>
-      <c r="AX18" t="inlineStr"/>
-      <c r="AY18" t="inlineStr"/>
-      <c r="AZ18" t="inlineStr"/>
-      <c r="BA18" t="inlineStr"/>
-      <c r="BB18" t="inlineStr"/>
-      <c r="BC18" t="inlineStr"/>
-      <c r="BD18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>SOLVXEbk</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="n">
-        <v>45520.65625</v>
-      </c>
-      <c r="C19" t="n">
-        <v>102</v>
-      </c>
-      <c r="D19" t="n">
-        <v>133</v>
-      </c>
-      <c r="E19" t="n">
-        <v>25178</v>
-      </c>
-      <c r="F19" t="n">
-        <v>194</v>
-      </c>
-      <c r="G19" t="n">
-        <v>129</v>
-      </c>
-      <c r="H19" t="n">
-        <v>55</v>
-      </c>
-      <c r="I19" t="n">
-        <v>551</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-      <c r="M19" t="n">
-        <v>12</v>
-      </c>
-      <c r="N19" t="n">
-        <v>37</v>
-      </c>
-      <c r="O19" t="n">
-        <v>-9</v>
-      </c>
-      <c r="P19" t="n">
-        <v>-1</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>-3</v>
-      </c>
-      <c r="R19" t="n">
-        <v>-1</v>
-      </c>
-      <c r="S19" t="n">
-        <v>-1.237777777777777</v>
-      </c>
-      <c r="T19" t="n">
-        <v>-10.19279365827184</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.049646464646461</v>
-      </c>
-      <c r="V19" t="n">
-        <v>-2.451684899741764</v>
-      </c>
-      <c r="W19" t="n">
-        <v>2.663181818181783</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.202641102207476</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>-29631870.98981469</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>-10.15191919191919</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>-1.164974147553758</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>-8.587952293808456</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>-36142222.22222222</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>-9.26934343434344</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF19" t="inlineStr"/>
-      <c r="AG19" t="inlineStr"/>
-      <c r="AH19" t="inlineStr"/>
-      <c r="AI19" t="inlineStr"/>
-      <c r="AJ19" t="inlineStr"/>
-      <c r="AK19" t="inlineStr"/>
-      <c r="AL19" t="inlineStr"/>
-      <c r="AM19" t="inlineStr"/>
-      <c r="AN19" t="inlineStr"/>
-      <c r="AO19" t="inlineStr"/>
-      <c r="AP19" t="inlineStr"/>
-      <c r="AQ19" t="inlineStr"/>
-      <c r="AR19" t="inlineStr"/>
-      <c r="AS19" t="inlineStr"/>
-      <c r="AT19" t="inlineStr"/>
-      <c r="AU19" t="inlineStr"/>
-      <c r="AV19" t="inlineStr"/>
-      <c r="AW19" t="inlineStr"/>
-      <c r="AX19" t="inlineStr"/>
-      <c r="AY19" t="inlineStr"/>
-      <c r="AZ19" t="inlineStr"/>
-      <c r="BA19" t="inlineStr"/>
-      <c r="BB19" t="inlineStr"/>
-      <c r="BC19" t="inlineStr"/>
-      <c r="BD19" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/france/p6_deployment/data_preparation/df_tagged.xlsx
+++ b/data/france/p6_deployment/data_preparation/df_tagged.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BD10"/>
+  <dimension ref="A1:BD18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -520,57 +520,57 @@
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_pot_player_start</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_sub</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_start</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_sub</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_sub</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_start</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_start</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_age_player_start</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_start</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_sub</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_val_player_start</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_sub</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_sub</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_start</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_start</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_start</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_int_rep_player_sub</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_sub</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_sub</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
@@ -712,26 +712,26 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>zkPwWhT1</t>
+          <t>xrJSdNFr</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45522.65625</v>
+        <v>45529.5</v>
       </c>
       <c r="C2" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D2" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E2" t="n">
-        <v>29778</v>
+        <v>26109</v>
       </c>
       <c r="F2" t="n">
-        <v>573</v>
+        <v>736</v>
       </c>
       <c r="G2" t="n">
-        <v>39</v>
+        <v>399</v>
       </c>
       <c r="H2" t="n">
         <v>55</v>
@@ -753,58 +753,58 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>312</v>
+        <v>165</v>
       </c>
       <c r="N2" t="n">
-        <v>37</v>
+        <v>211</v>
       </c>
       <c r="O2" t="n">
-        <v>-8</v>
+        <v>-6</v>
       </c>
       <c r="P2" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="Q2" t="n">
-        <v>-5</v>
+        <v>4</v>
       </c>
       <c r="R2" t="n">
         <v>1</v>
       </c>
       <c r="S2" t="n">
-        <v>-3.092352092352094</v>
+        <v>-0.8455667789001211</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.4085137085137087</v>
+        <v>-3.038220989250391</v>
       </c>
       <c r="U2" t="n">
-        <v>518340.548340546</v>
+        <v>1.181369248035907</v>
       </c>
       <c r="V2" t="n">
-        <v>0.9351344790973286</v>
+        <v>-3.773151340308203</v>
       </c>
       <c r="W2" t="n">
-        <v>2.54999169790193</v>
+        <v>1.943944013502858</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.9551226551226364</v>
+        <v>-4.53187429854097</v>
       </c>
       <c r="Y2" t="n">
-        <v>-0.6877344877344456</v>
+        <v>-0.4864197530864196</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.383549783549782</v>
+        <v>-2.094388327721656</v>
       </c>
       <c r="AA2" t="n">
-        <v>-0.2061128013140394</v>
+        <v>-5561110.834789757</v>
       </c>
       <c r="AB2" t="n">
-        <v>-0.2816242180019231</v>
+        <v>-6226094.276094274</v>
       </c>
       <c r="AC2" t="n">
-        <v>2659292.869726306</v>
+        <v>-0.1319143383849266</v>
       </c>
       <c r="AD2" t="n">
-        <v>-2.209551619690934</v>
+        <v>0.7093521710678559</v>
       </c>
       <c r="AE2" t="n">
         <v>0</v>
@@ -838,26 +838,26 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>2NocJFqd</t>
+          <t>ObHze1pe</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45522.5</v>
+        <v>45529.5</v>
       </c>
       <c r="C3" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D3" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E3" t="n">
-        <v>18752</v>
+        <v>35322</v>
       </c>
       <c r="F3" t="n">
-        <v>431</v>
+        <v>858</v>
       </c>
       <c r="G3" t="n">
-        <v>176</v>
+        <v>228</v>
       </c>
       <c r="H3" t="n">
         <v>55</v>
@@ -879,58 +879,58 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>35</v>
+        <v>67</v>
       </c>
       <c r="N3" t="n">
-        <v>234</v>
+        <v>181</v>
       </c>
       <c r="O3" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="P3" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>-4</v>
+        <v>6</v>
       </c>
       <c r="R3" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.1722943722943775</v>
+        <v>4.109090909090909</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.3939393939393945</v>
+        <v>2.142556866107583</v>
       </c>
       <c r="U3" t="n">
-        <v>-11204826.83982684</v>
+        <v>1.468686868686888</v>
       </c>
       <c r="V3" t="n">
-        <v>-6.707141403569977</v>
+        <v>4.987461920795255</v>
       </c>
       <c r="W3" t="n">
-        <v>4.851979039479033</v>
+        <v>0.1338197363559743</v>
       </c>
       <c r="X3" t="n">
-        <v>-8.214285714285708</v>
+        <v>4.472727272727269</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.754112554112538</v>
+        <v>0.535353535353535</v>
       </c>
       <c r="Z3" t="n">
-        <v>-6.84632034632034</v>
+        <v>0.6414141414141383</v>
       </c>
       <c r="AA3" t="n">
-        <v>-0.381613756613757</v>
+        <v>1088654.235592642</v>
       </c>
       <c r="AB3" t="n">
-        <v>-8.970034595034591</v>
+        <v>2978712.121212122</v>
       </c>
       <c r="AC3" t="n">
-        <v>-5934025.234025234</v>
+        <v>0.1397384821297865</v>
       </c>
       <c r="AD3" t="n">
-        <v>-1.461131461131458</v>
+        <v>2.502416678865956</v>
       </c>
       <c r="AE3" t="n">
         <v>0</v>
@@ -964,26 +964,26 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>M5VGwpVA</t>
+          <t>8nivFMyR</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45522.5</v>
+        <v>45529.5</v>
       </c>
       <c r="C4" t="n">
         <v>101</v>
       </c>
       <c r="D4" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E4" t="n">
-        <v>20484</v>
+        <v>36178</v>
       </c>
       <c r="F4" t="n">
-        <v>242</v>
+        <v>535</v>
       </c>
       <c r="G4" t="n">
-        <v>516</v>
+        <v>226</v>
       </c>
       <c r="H4" t="n">
         <v>55</v>
@@ -1005,58 +1005,58 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>193</v>
+        <v>98</v>
       </c>
       <c r="N4" t="n">
-        <v>55</v>
+        <v>7</v>
       </c>
       <c r="O4" t="n">
-        <v>-4</v>
+        <v>7</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S4" t="n">
-        <v>2.556734006734004</v>
+        <v>0.9575757575757535</v>
       </c>
       <c r="T4" t="n">
-        <v>0.119023569023569</v>
+        <v>0.8416671207003077</v>
       </c>
       <c r="U4" t="n">
-        <v>770656.5656565651</v>
+        <v>-0.2616161616161605</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.066762431468305</v>
+        <v>2.698946440174524</v>
       </c>
       <c r="W4" t="n">
-        <v>-1.289739634240874</v>
+        <v>-0.2668595805132838</v>
       </c>
       <c r="X4" t="n">
-        <v>1.532659932659925</v>
+        <v>2.385858585858585</v>
       </c>
       <c r="Y4" t="n">
-        <v>-0.6917508417508316</v>
+        <v>0.2464646464646469</v>
       </c>
       <c r="Z4" t="n">
-        <v>-1.627104377104388</v>
+        <v>0.4838383838383855</v>
       </c>
       <c r="AA4" t="n">
-        <v>-0.09041581701428236</v>
+        <v>3429432.352015304</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.5527193039980745</v>
+        <v>6819797.97979798</v>
       </c>
       <c r="AC4" t="n">
-        <v>116772.5180001399</v>
+        <v>0.2958646616541354</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.7483340047278659</v>
+        <v>0.8191001860528964</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
@@ -1090,11 +1090,11 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>6ehlLyFq</t>
+          <t>OCd990al</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45522.5</v>
+        <v>45529.41666666666</v>
       </c>
       <c r="C5" t="n">
         <v>101</v>
@@ -1103,13 +1103,13 @@
         <v>133</v>
       </c>
       <c r="E5" t="n">
-        <v>33150</v>
+        <v>38223</v>
       </c>
       <c r="F5" t="n">
-        <v>341</v>
+        <v>273</v>
       </c>
       <c r="G5" t="n">
-        <v>599</v>
+        <v>133</v>
       </c>
       <c r="H5" t="n">
         <v>55</v>
@@ -1131,58 +1131,58 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>152</v>
+        <v>193</v>
       </c>
       <c r="N5" t="n">
-        <v>141</v>
+        <v>7</v>
       </c>
       <c r="O5" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
+        <v>3</v>
+      </c>
+      <c r="R5" t="n">
         <v>1</v>
       </c>
-      <c r="R5" t="n">
-        <v>-1</v>
-      </c>
       <c r="S5" t="n">
-        <v>-3.454545454545453</v>
+        <v>2.222222222222229</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.439393939393939</v>
+        <v>2.671119929453255</v>
       </c>
       <c r="U5" t="n">
-        <v>1494696.969696969</v>
+        <v>-1.606060606060623</v>
       </c>
       <c r="V5" t="n">
-        <v>3.35132771817554</v>
+        <v>3.816666666666677</v>
       </c>
       <c r="W5" t="n">
-        <v>0.8007638496768834</v>
+        <v>-1.696472663139275</v>
       </c>
       <c r="X5" t="n">
-        <v>0.2121212121212039</v>
+        <v>2.060606060606062</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.7121212121211613</v>
+        <v>0.09090909090909105</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.666666666666671</v>
+        <v>0.08080808080807955</v>
       </c>
       <c r="AA5" t="n">
-        <v>-0.1540521676391242</v>
+        <v>2665654.761904762</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.4045815295815487</v>
+        <v>6296464.646464647</v>
       </c>
       <c r="AC5" t="n">
-        <v>899858.2486354224</v>
+        <v>0.2312169312169312</v>
       </c>
       <c r="AD5" t="n">
-        <v>-2.494082909843787</v>
+        <v>2.011992945326277</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
@@ -1216,26 +1216,26 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>ripawyyS</t>
+          <t>KQAqguF7</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45522.41666666666</v>
+        <v>45528.66666666666</v>
       </c>
       <c r="C6" t="n">
         <v>101</v>
       </c>
       <c r="D6" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E6" t="n">
-        <v>17924</v>
+        <v>42000</v>
       </c>
       <c r="F6" t="n">
-        <v>342</v>
+        <v>528</v>
       </c>
       <c r="G6" t="n">
-        <v>370</v>
+        <v>122</v>
       </c>
       <c r="H6" t="n">
         <v>55</v>
@@ -1257,58 +1257,58 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>128</v>
+        <v>103</v>
       </c>
       <c r="N6" t="n">
-        <v>257</v>
+        <v>67</v>
       </c>
       <c r="O6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="P6" t="n">
         <v>-1</v>
       </c>
       <c r="Q6" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="S6" t="n">
-        <v>2.29004329004329</v>
+        <v>-1.092618492618499</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3333333333333337</v>
+        <v>0.6062536744811098</v>
       </c>
       <c r="U6" t="n">
-        <v>-10976948.05194805</v>
+        <v>-4.518492618492616</v>
       </c>
       <c r="V6" t="n">
-        <v>-6.999683326281072</v>
+        <v>-0.1488848149661948</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.7203438791785004</v>
+        <v>-1.289160124528053</v>
       </c>
       <c r="X6" t="n">
-        <v>-6.517316017316034</v>
+        <v>-1.291686091686088</v>
       </c>
       <c r="Y6" t="n">
-        <v>-2.549783549783541</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>-8.417748917748924</v>
+        <v>0.09829059829059261</v>
       </c>
       <c r="AA6" t="n">
-        <v>-0.3244569757727656</v>
+        <v>-219746.2594591912</v>
       </c>
       <c r="AB6" t="n">
-        <v>-8.529176024476783</v>
+        <v>-783543.1235431237</v>
       </c>
       <c r="AC6" t="n">
-        <v>-6666662.191192267</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>-0.255804554676736</v>
+        <v>-0.0884218912925725</v>
       </c>
       <c r="AE6" t="n">
         <v>0</v>
@@ -1342,26 +1342,26 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>fHYrsJy3</t>
+          <t>CKcVGr7E</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45521.66666666666</v>
+        <v>45528.58333333334</v>
       </c>
       <c r="C7" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D7" t="n">
         <v>133</v>
       </c>
       <c r="E7" t="n">
-        <v>18523</v>
+        <v>50186</v>
       </c>
       <c r="F7" t="n">
-        <v>47</v>
+        <v>777</v>
       </c>
       <c r="G7" t="n">
-        <v>362</v>
+        <v>292</v>
       </c>
       <c r="H7" t="n">
         <v>55</v>
@@ -1383,58 +1383,58 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>67</v>
+        <v>98</v>
       </c>
       <c r="N7" t="n">
-        <v>226</v>
+        <v>199</v>
       </c>
       <c r="O7" t="n">
-        <v>3</v>
+        <v>-1</v>
       </c>
       <c r="P7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
         <v>1</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.102558922558924</v>
+        <v>9.02242424242425</v>
       </c>
       <c r="T7" t="n">
-        <v>0.5225589225589224</v>
+        <v>6.517642932116615</v>
       </c>
       <c r="U7" t="n">
-        <v>12410824.91582492</v>
+        <v>-2.97777777777776</v>
       </c>
       <c r="V7" t="n">
-        <v>8.125588423014889</v>
+        <v>8.274424308634835</v>
       </c>
       <c r="W7" t="n">
-        <v>0.5488925677006762</v>
+        <v>-1.870612964034024</v>
       </c>
       <c r="X7" t="n">
-        <v>6.508754208754212</v>
+        <v>7.596161616161609</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.8566329966329818</v>
+        <v>0.468686868686869</v>
       </c>
       <c r="Z7" t="n">
-        <v>7.527104377104379</v>
+        <v>-2.62191919191919</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.3793988648090814</v>
+        <v>5277594.614206457</v>
       </c>
       <c r="AB7" t="n">
-        <v>5.849153488840017</v>
+        <v>11593406.56565657</v>
       </c>
       <c r="AC7" t="n">
-        <v>10210373.44578366</v>
+        <v>0.2157327078379709</v>
       </c>
       <c r="AD7" t="n">
-        <v>-2.673857542955837</v>
+        <v>1.706414540625065</v>
       </c>
       <c r="AE7" t="n">
         <v>0</v>
@@ -1468,11 +1468,11 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>jqSiuc6F</t>
+          <t>pSpI7vU0</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45521.58333333334</v>
+        <v>45528.5</v>
       </c>
       <c r="C8" t="n">
         <v>101</v>
@@ -1481,13 +1481,13 @@
         <v>133</v>
       </c>
       <c r="E8" t="n">
-        <v>21029</v>
+        <v>59186</v>
       </c>
       <c r="F8" t="n">
-        <v>826</v>
+        <v>56</v>
       </c>
       <c r="G8" t="n">
-        <v>545</v>
+        <v>33</v>
       </c>
       <c r="H8" t="n">
         <v>55</v>
@@ -1509,58 +1509,58 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>312</v>
+        <v>165</v>
       </c>
       <c r="N8" t="n">
-        <v>257</v>
+        <v>141</v>
       </c>
       <c r="O8" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="P8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q8" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="R8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S8" t="n">
-        <v>1.476388888888891</v>
+        <v>-2.564993368023664</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1988005050505053</v>
+        <v>-2.857421471560926</v>
       </c>
       <c r="U8" t="n">
-        <v>-5311223.169191919</v>
+        <v>0.07680848892968584</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.6812072917335996</v>
+        <v>-0.4284869810376506</v>
       </c>
       <c r="W8" t="n">
-        <v>3.056115716642012</v>
+        <v>-2.358161412552107</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.145517676767682</v>
+        <v>-0.1642383430262271</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.201515151515167</v>
+        <v>0.5300479542903789</v>
       </c>
       <c r="Z8" t="n">
-        <v>-2.560290404040401</v>
+        <v>2.857647178859303</v>
       </c>
       <c r="AA8" t="n">
-        <v>-0.1210440631493261</v>
+        <v>-4354841.891906346</v>
       </c>
       <c r="AB8" t="n">
-        <v>-4.313757684810327</v>
+        <v>-5193433.323130291</v>
       </c>
       <c r="AC8" t="n">
-        <v>-3498376.978771716</v>
+        <v>0.2533984653742607</v>
       </c>
       <c r="AD8" t="n">
-        <v>-2.853552685131628</v>
+        <v>2.641520276613861</v>
       </c>
       <c r="AE8" t="n">
         <v>0</v>
@@ -1594,26 +1594,26 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>0js8u60b</t>
+          <t>ppvl45N8</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45521.5</v>
+        <v>45527.65625</v>
       </c>
       <c r="C9" t="n">
         <v>101</v>
       </c>
       <c r="D9" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E9" t="n">
-        <v>15220</v>
+        <v>48229</v>
       </c>
       <c r="F9" t="n">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="G9" t="n">
-        <v>303</v>
+        <v>157</v>
       </c>
       <c r="H9" t="n">
         <v>55</v>
@@ -1635,58 +1635,58 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>152</v>
+        <v>165</v>
       </c>
       <c r="N9" t="n">
-        <v>67</v>
+        <v>234</v>
       </c>
       <c r="O9" t="n">
-        <v>-5</v>
+        <v>14</v>
       </c>
       <c r="P9" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.7106060606060538</v>
+        <v>7.603333333333339</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3848484848484846</v>
+        <v>7.292474565362198</v>
       </c>
       <c r="U9" t="n">
-        <v>-5597727.272727274</v>
+        <v>1.496313131313173</v>
       </c>
       <c r="V9" t="n">
-        <v>-3.770397808246102</v>
+        <v>7.528236673727037</v>
       </c>
       <c r="W9" t="n">
-        <v>-3.824925876783453</v>
+        <v>2.082551324941363</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.351515151515159</v>
+        <v>8.540606060606066</v>
       </c>
       <c r="Y9" t="n">
-        <v>-2.096969696969694</v>
+        <v>1.056515151515151</v>
       </c>
       <c r="Z9" t="n">
-        <v>-1.922727272727272</v>
+        <v>-0.6810606060606048</v>
       </c>
       <c r="AA9" t="n">
-        <v>-0.1205530165282489</v>
+        <v>27826839.14862877</v>
       </c>
       <c r="AB9" t="n">
-        <v>-4.389276295313451</v>
+        <v>40486439.39393938</v>
       </c>
       <c r="AC9" t="n">
-        <v>-5482357.527806443</v>
+        <v>0.9981001904745286</v>
       </c>
       <c r="AD9" t="n">
-        <v>-0.5654180385604519</v>
+        <v>0.0142818112286065</v>
       </c>
       <c r="AE9" t="n">
         <v>0</v>
@@ -1720,26 +1720,26 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>SOLVXEbk</t>
+          <t>zkPwWhT1</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45520.65625</v>
+        <v>45522.65625</v>
       </c>
       <c r="C10" t="n">
         <v>102</v>
       </c>
       <c r="D10" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E10" t="n">
-        <v>25178</v>
+        <v>29778</v>
       </c>
       <c r="F10" t="n">
-        <v>194</v>
+        <v>573</v>
       </c>
       <c r="G10" t="n">
-        <v>129</v>
+        <v>39</v>
       </c>
       <c r="H10" t="n">
         <v>55</v>
@@ -1761,58 +1761,58 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>12</v>
+        <v>312</v>
       </c>
       <c r="N10" t="n">
         <v>37</v>
       </c>
       <c r="O10" t="n">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="P10" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3</v>
+        <v>-5</v>
       </c>
       <c r="R10" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="S10" t="n">
-        <v>1.049646464646461</v>
+        <v>1.251974288337919</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.237777777777777</v>
+        <v>1.021529781551592</v>
       </c>
       <c r="U10" t="n">
-        <v>-36142222.22222222</v>
+        <v>-0.5624426078971396</v>
       </c>
       <c r="V10" t="n">
-        <v>-10.19279365827184</v>
+        <v>-0.6365626938030431</v>
       </c>
       <c r="W10" t="n">
-        <v>-2.451684899741764</v>
+        <v>2.129144548496498</v>
       </c>
       <c r="X10" t="n">
-        <v>-9.26934343434344</v>
+        <v>-0.799173553719001</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.663181818181783</v>
+        <v>-0.410743801652893</v>
       </c>
       <c r="Z10" t="n">
-        <v>-10.15191919191919</v>
+        <v>-2.8850321395776</v>
       </c>
       <c r="AA10" t="n">
-        <v>-1.164974147553758</v>
+        <v>2031854.421187063</v>
       </c>
       <c r="AB10" t="n">
-        <v>-8.587952293808456</v>
+        <v>772681.3590449914</v>
       </c>
       <c r="AC10" t="n">
-        <v>-29631870.98981469</v>
+        <v>-0.1668865974692038</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.202641102207476</v>
+        <v>-2.196889991751377</v>
       </c>
       <c r="AE10" t="n">
         <v>0</v>
@@ -1843,6 +1843,1014 @@
       <c r="BC10" t="inlineStr"/>
       <c r="BD10" t="inlineStr"/>
     </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>6ehlLyFq</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45522.5</v>
+      </c>
+      <c r="C11" t="n">
+        <v>101</v>
+      </c>
+      <c r="D11" t="n">
+        <v>133</v>
+      </c>
+      <c r="E11" t="n">
+        <v>33150</v>
+      </c>
+      <c r="F11" t="n">
+        <v>341</v>
+      </c>
+      <c r="G11" t="n">
+        <v>599</v>
+      </c>
+      <c r="H11" t="n">
+        <v>55</v>
+      </c>
+      <c r="I11" t="n">
+        <v>551</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="M11" t="n">
+        <v>152</v>
+      </c>
+      <c r="N11" t="n">
+        <v>141</v>
+      </c>
+      <c r="O11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3.333333333333329</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3.691008602240501</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0.8383838383838338</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0.5907086740420056</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0.3239660232413826</v>
+      </c>
+      <c r="X11" t="n">
+        <v>-0.2222222222222285</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>-0.4545454545454544</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>-3.343434343434343</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1242559.820077936</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1021717.171717171</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>-0.1397384821297865</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>-2.835561446068695</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="inlineStr"/>
+      <c r="AH11" t="inlineStr"/>
+      <c r="AI11" t="inlineStr"/>
+      <c r="AJ11" t="inlineStr"/>
+      <c r="AK11" t="inlineStr"/>
+      <c r="AL11" t="inlineStr"/>
+      <c r="AM11" t="inlineStr"/>
+      <c r="AN11" t="inlineStr"/>
+      <c r="AO11" t="inlineStr"/>
+      <c r="AP11" t="inlineStr"/>
+      <c r="AQ11" t="inlineStr"/>
+      <c r="AR11" t="inlineStr"/>
+      <c r="AS11" t="inlineStr"/>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AU11" t="inlineStr"/>
+      <c r="AV11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr"/>
+      <c r="AX11" t="inlineStr"/>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr"/>
+      <c r="BA11" t="inlineStr"/>
+      <c r="BB11" t="inlineStr"/>
+      <c r="BC11" t="inlineStr"/>
+      <c r="BD11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>M5VGwpVA</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45522.5</v>
+      </c>
+      <c r="C12" t="n">
+        <v>101</v>
+      </c>
+      <c r="D12" t="n">
+        <v>134</v>
+      </c>
+      <c r="E12" t="n">
+        <v>20484</v>
+      </c>
+      <c r="F12" t="n">
+        <v>242</v>
+      </c>
+      <c r="G12" t="n">
+        <v>516</v>
+      </c>
+      <c r="H12" t="n">
+        <v>55</v>
+      </c>
+      <c r="I12" t="n">
+        <v>551</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="M12" t="n">
+        <v>193</v>
+      </c>
+      <c r="N12" t="n">
+        <v>55</v>
+      </c>
+      <c r="O12" t="n">
+        <v>-4</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>5</v>
+      </c>
+      <c r="R12" t="n">
+        <v>2</v>
+      </c>
+      <c r="S12" t="n">
+        <v>-1.455443322109971</v>
+      </c>
+      <c r="T12" t="n">
+        <v>-0.5826035257407796</v>
+      </c>
+      <c r="U12" t="n">
+        <v>-0.9702581369248264</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.084528918714753</v>
+      </c>
+      <c r="W12" t="n">
+        <v>-1.255240884908403</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.463187429854088</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0.09854096520763189</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2.437822671155999</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>310800.7262858073</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>860134.6801346801</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>-0.07632659405890441</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.8320463029755452</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="inlineStr"/>
+      <c r="AH12" t="inlineStr"/>
+      <c r="AI12" t="inlineStr"/>
+      <c r="AJ12" t="inlineStr"/>
+      <c r="AK12" t="inlineStr"/>
+      <c r="AL12" t="inlineStr"/>
+      <c r="AM12" t="inlineStr"/>
+      <c r="AN12" t="inlineStr"/>
+      <c r="AO12" t="inlineStr"/>
+      <c r="AP12" t="inlineStr"/>
+      <c r="AQ12" t="inlineStr"/>
+      <c r="AR12" t="inlineStr"/>
+      <c r="AS12" t="inlineStr"/>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AU12" t="inlineStr"/>
+      <c r="AV12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr"/>
+      <c r="AX12" t="inlineStr"/>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr"/>
+      <c r="BA12" t="inlineStr"/>
+      <c r="BB12" t="inlineStr"/>
+      <c r="BC12" t="inlineStr"/>
+      <c r="BD12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>2NocJFqd</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45522.5</v>
+      </c>
+      <c r="C13" t="n">
+        <v>101</v>
+      </c>
+      <c r="D13" t="n">
+        <v>134</v>
+      </c>
+      <c r="E13" t="n">
+        <v>18752</v>
+      </c>
+      <c r="F13" t="n">
+        <v>431</v>
+      </c>
+      <c r="G13" t="n">
+        <v>176</v>
+      </c>
+      <c r="H13" t="n">
+        <v>55</v>
+      </c>
+      <c r="I13" t="n">
+        <v>551</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="M13" t="n">
+        <v>35</v>
+      </c>
+      <c r="N13" t="n">
+        <v>234</v>
+      </c>
+      <c r="O13" t="n">
+        <v>-3</v>
+      </c>
+      <c r="P13" t="n">
+        <v>-3</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>-4</v>
+      </c>
+      <c r="R13" t="n">
+        <v>-2</v>
+      </c>
+      <c r="S13" t="n">
+        <v>-7.172929292929297</v>
+      </c>
+      <c r="T13" t="n">
+        <v>-6.355206213539546</v>
+      </c>
+      <c r="U13" t="n">
+        <v>3.27272727272728</v>
+      </c>
+      <c r="V13" t="n">
+        <v>-9.360086826753502</v>
+      </c>
+      <c r="W13" t="n">
+        <v>3.885130918464228</v>
+      </c>
+      <c r="X13" t="n">
+        <v>-8.033535353535356</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>-0.4040404040404044</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0.407777777777774</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>-5700837.064170398</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>-11659164.14141414</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>-0.3840388007054676</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>-2.14351512684846</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="inlineStr"/>
+      <c r="AH13" t="inlineStr"/>
+      <c r="AI13" t="inlineStr"/>
+      <c r="AJ13" t="inlineStr"/>
+      <c r="AK13" t="inlineStr"/>
+      <c r="AL13" t="inlineStr"/>
+      <c r="AM13" t="inlineStr"/>
+      <c r="AN13" t="inlineStr"/>
+      <c r="AO13" t="inlineStr"/>
+      <c r="AP13" t="inlineStr"/>
+      <c r="AQ13" t="inlineStr"/>
+      <c r="AR13" t="inlineStr"/>
+      <c r="AS13" t="inlineStr"/>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AU13" t="inlineStr"/>
+      <c r="AV13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr"/>
+      <c r="AX13" t="inlineStr"/>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr"/>
+      <c r="BA13" t="inlineStr"/>
+      <c r="BB13" t="inlineStr"/>
+      <c r="BC13" t="inlineStr"/>
+      <c r="BD13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>ripawyyS</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45522.41666666666</v>
+      </c>
+      <c r="C14" t="n">
+        <v>101</v>
+      </c>
+      <c r="D14" t="n">
+        <v>134</v>
+      </c>
+      <c r="E14" t="n">
+        <v>17924</v>
+      </c>
+      <c r="F14" t="n">
+        <v>342</v>
+      </c>
+      <c r="G14" t="n">
+        <v>370</v>
+      </c>
+      <c r="H14" t="n">
+        <v>55</v>
+      </c>
+      <c r="I14" t="n">
+        <v>551</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="M14" t="n">
+        <v>128</v>
+      </c>
+      <c r="N14" t="n">
+        <v>257</v>
+      </c>
+      <c r="O14" t="n">
+        <v>5</v>
+      </c>
+      <c r="P14" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>8</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>-8.399999999999991</v>
+      </c>
+      <c r="T14" t="n">
+        <v>-6.675232589048392</v>
+      </c>
+      <c r="U14" t="n">
+        <v>-2.045454545454561</v>
+      </c>
+      <c r="V14" t="n">
+        <v>-8.277117035011784</v>
+      </c>
+      <c r="W14" t="n">
+        <v>-0.1909261790840731</v>
+      </c>
+      <c r="X14" t="n">
+        <v>-6.636363636363626</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>-0.3272727272727276</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2.218181818181819</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>-5760646.407685881</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>-10820227.27272727</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>-0.2958646616541354</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>-0.4859554188501569</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="inlineStr"/>
+      <c r="AH14" t="inlineStr"/>
+      <c r="AI14" t="inlineStr"/>
+      <c r="AJ14" t="inlineStr"/>
+      <c r="AK14" t="inlineStr"/>
+      <c r="AL14" t="inlineStr"/>
+      <c r="AM14" t="inlineStr"/>
+      <c r="AN14" t="inlineStr"/>
+      <c r="AO14" t="inlineStr"/>
+      <c r="AP14" t="inlineStr"/>
+      <c r="AQ14" t="inlineStr"/>
+      <c r="AR14" t="inlineStr"/>
+      <c r="AS14" t="inlineStr"/>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AU14" t="inlineStr"/>
+      <c r="AV14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr"/>
+      <c r="AX14" t="inlineStr"/>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr"/>
+      <c r="BA14" t="inlineStr"/>
+      <c r="BB14" t="inlineStr"/>
+      <c r="BC14" t="inlineStr"/>
+      <c r="BD14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>fHYrsJy3</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45521.66666666666</v>
+      </c>
+      <c r="C15" t="n">
+        <v>102</v>
+      </c>
+      <c r="D15" t="n">
+        <v>133</v>
+      </c>
+      <c r="E15" t="n">
+        <v>18523</v>
+      </c>
+      <c r="F15" t="n">
+        <v>47</v>
+      </c>
+      <c r="G15" t="n">
+        <v>362</v>
+      </c>
+      <c r="H15" t="n">
+        <v>55</v>
+      </c>
+      <c r="I15" t="n">
+        <v>551</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="M15" t="n">
+        <v>67</v>
+      </c>
+      <c r="N15" t="n">
+        <v>226</v>
+      </c>
+      <c r="O15" t="n">
+        <v>3</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>6</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1</v>
+      </c>
+      <c r="S15" t="n">
+        <v>7.613718380385038</v>
+      </c>
+      <c r="T15" t="n">
+        <v>7.790980895675446</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0.6303893637227134</v>
+      </c>
+      <c r="V15" t="n">
+        <v>5.662021292966159</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.048975815360734</v>
+      </c>
+      <c r="X15" t="n">
+        <v>6.575300008633349</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0.5806958473625139</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>-1.062824829491493</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>9160887.178917067</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>12851870.84520418</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>0.2945992432060542</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>-2.634971716934686</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="inlineStr"/>
+      <c r="AH15" t="inlineStr"/>
+      <c r="AI15" t="inlineStr"/>
+      <c r="AJ15" t="inlineStr"/>
+      <c r="AK15" t="inlineStr"/>
+      <c r="AL15" t="inlineStr"/>
+      <c r="AM15" t="inlineStr"/>
+      <c r="AN15" t="inlineStr"/>
+      <c r="AO15" t="inlineStr"/>
+      <c r="AP15" t="inlineStr"/>
+      <c r="AQ15" t="inlineStr"/>
+      <c r="AR15" t="inlineStr"/>
+      <c r="AS15" t="inlineStr"/>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AU15" t="inlineStr"/>
+      <c r="AV15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr"/>
+      <c r="AX15" t="inlineStr"/>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr"/>
+      <c r="BA15" t="inlineStr"/>
+      <c r="BB15" t="inlineStr"/>
+      <c r="BC15" t="inlineStr"/>
+      <c r="BD15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>jqSiuc6F</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45521.58333333334</v>
+      </c>
+      <c r="C16" t="n">
+        <v>101</v>
+      </c>
+      <c r="D16" t="n">
+        <v>133</v>
+      </c>
+      <c r="E16" t="n">
+        <v>21029</v>
+      </c>
+      <c r="F16" t="n">
+        <v>826</v>
+      </c>
+      <c r="G16" t="n">
+        <v>545</v>
+      </c>
+      <c r="H16" t="n">
+        <v>55</v>
+      </c>
+      <c r="I16" t="n">
+        <v>551</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="M16" t="n">
+        <v>312</v>
+      </c>
+      <c r="N16" t="n">
+        <v>257</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>4</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1</v>
+      </c>
+      <c r="S16" t="n">
+        <v>-2.494913419913416</v>
+      </c>
+      <c r="T16" t="n">
+        <v>-0.01167787702875955</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2.023953823953804</v>
+      </c>
+      <c r="V16" t="n">
+        <v>-3.953880784582523</v>
+      </c>
+      <c r="W16" t="n">
+        <v>3.249712065062937</v>
+      </c>
+      <c r="X16" t="n">
+        <v>-2.336688311688306</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>-0.2238455988455992</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1.162842712842714</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>-2541229.493784319</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>-5792473.845598846</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>-0.158738370141879</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>-3.213215017600984</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="inlineStr"/>
+      <c r="AH16" t="inlineStr"/>
+      <c r="AI16" t="inlineStr"/>
+      <c r="AJ16" t="inlineStr"/>
+      <c r="AK16" t="inlineStr"/>
+      <c r="AL16" t="inlineStr"/>
+      <c r="AM16" t="inlineStr"/>
+      <c r="AN16" t="inlineStr"/>
+      <c r="AO16" t="inlineStr"/>
+      <c r="AP16" t="inlineStr"/>
+      <c r="AQ16" t="inlineStr"/>
+      <c r="AR16" t="inlineStr"/>
+      <c r="AS16" t="inlineStr"/>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AU16" t="inlineStr"/>
+      <c r="AV16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr"/>
+      <c r="AX16" t="inlineStr"/>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr"/>
+      <c r="BA16" t="inlineStr"/>
+      <c r="BB16" t="inlineStr"/>
+      <c r="BC16" t="inlineStr"/>
+      <c r="BD16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>0js8u60b</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45521.5</v>
+      </c>
+      <c r="C17" t="n">
+        <v>101</v>
+      </c>
+      <c r="D17" t="n">
+        <v>134</v>
+      </c>
+      <c r="E17" t="n">
+        <v>15220</v>
+      </c>
+      <c r="F17" t="n">
+        <v>211</v>
+      </c>
+      <c r="G17" t="n">
+        <v>303</v>
+      </c>
+      <c r="H17" t="n">
+        <v>55</v>
+      </c>
+      <c r="I17" t="n">
+        <v>551</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="M17" t="n">
+        <v>152</v>
+      </c>
+      <c r="N17" t="n">
+        <v>67</v>
+      </c>
+      <c r="O17" t="n">
+        <v>-5</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>-1.978787878787884</v>
+      </c>
+      <c r="T17" t="n">
+        <v>-3.823122348354545</v>
+      </c>
+      <c r="U17" t="n">
+        <v>-1.692929292929307</v>
+      </c>
+      <c r="V17" t="n">
+        <v>-4.466748570773333</v>
+      </c>
+      <c r="W17" t="n">
+        <v>-3.940603141841592</v>
+      </c>
+      <c r="X17" t="n">
+        <v>-2.264646464646475</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>-0.3848484848484846</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>-0.4626262626262587</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>-5118308.898608176</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>-5563131.313131313</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>-0.08125051190066679</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>-0.6732416553365965</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="inlineStr"/>
+      <c r="AH17" t="inlineStr"/>
+      <c r="AI17" t="inlineStr"/>
+      <c r="AJ17" t="inlineStr"/>
+      <c r="AK17" t="inlineStr"/>
+      <c r="AL17" t="inlineStr"/>
+      <c r="AM17" t="inlineStr"/>
+      <c r="AN17" t="inlineStr"/>
+      <c r="AO17" t="inlineStr"/>
+      <c r="AP17" t="inlineStr"/>
+      <c r="AQ17" t="inlineStr"/>
+      <c r="AR17" t="inlineStr"/>
+      <c r="AS17" t="inlineStr"/>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AU17" t="inlineStr"/>
+      <c r="AV17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr"/>
+      <c r="AX17" t="inlineStr"/>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr"/>
+      <c r="BA17" t="inlineStr"/>
+      <c r="BB17" t="inlineStr"/>
+      <c r="BC17" t="inlineStr"/>
+      <c r="BD17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>SOLVXEbk</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45520.65625</v>
+      </c>
+      <c r="C18" t="n">
+        <v>102</v>
+      </c>
+      <c r="D18" t="n">
+        <v>133</v>
+      </c>
+      <c r="E18" t="n">
+        <v>25178</v>
+      </c>
+      <c r="F18" t="n">
+        <v>194</v>
+      </c>
+      <c r="G18" t="n">
+        <v>129</v>
+      </c>
+      <c r="H18" t="n">
+        <v>55</v>
+      </c>
+      <c r="I18" t="n">
+        <v>551</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="M18" t="n">
+        <v>12</v>
+      </c>
+      <c r="N18" t="n">
+        <v>37</v>
+      </c>
+      <c r="O18" t="n">
+        <v>-9</v>
+      </c>
+      <c r="P18" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>-3</v>
+      </c>
+      <c r="R18" t="n">
+        <v>-1</v>
+      </c>
+      <c r="S18" t="n">
+        <v>-10.51040404040404</v>
+      </c>
+      <c r="T18" t="n">
+        <v>-10.23299293051825</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2.666313131313103</v>
+      </c>
+      <c r="V18" t="n">
+        <v>-9.287701055292857</v>
+      </c>
+      <c r="W18" t="n">
+        <v>-2.30205328031289</v>
+      </c>
+      <c r="X18" t="n">
+        <v>-9.792121212121216</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>-1.368636363636363</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>1.32954545454546</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>-29194682.48886342</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>-42768055.55555554</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>-1.170970369141809</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0.7230830380927671</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="inlineStr"/>
+      <c r="AH18" t="inlineStr"/>
+      <c r="AI18" t="inlineStr"/>
+      <c r="AJ18" t="inlineStr"/>
+      <c r="AK18" t="inlineStr"/>
+      <c r="AL18" t="inlineStr"/>
+      <c r="AM18" t="inlineStr"/>
+      <c r="AN18" t="inlineStr"/>
+      <c r="AO18" t="inlineStr"/>
+      <c r="AP18" t="inlineStr"/>
+      <c r="AQ18" t="inlineStr"/>
+      <c r="AR18" t="inlineStr"/>
+      <c r="AS18" t="inlineStr"/>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AU18" t="inlineStr"/>
+      <c r="AV18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr"/>
+      <c r="AX18" t="inlineStr"/>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr"/>
+      <c r="BA18" t="inlineStr"/>
+      <c r="BB18" t="inlineStr"/>
+      <c r="BC18" t="inlineStr"/>
+      <c r="BD18" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/france/p6_deployment/data_preparation/df_tagged.xlsx
+++ b/data/france/p6_deployment/data_preparation/df_tagged.xlsx
@@ -520,94 +520,94 @@
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_last_match_expected_goals_(xg)</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_expected_goals_(xg)_against</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goals</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goals_against</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_points</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_points_against</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_n_matches_last_days</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_n_matches_last_days_against</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_ball_possession</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_ball_possession_against</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_shots_on_goal</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_shots_on_goal_against</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_last_match_fouls</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_fouls_against</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_n_matches_last_days</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_n_matches_last_days_against</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goal_attempts</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goal_attempts_against</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_interceptions</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_interceptions_against</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goal_attempts</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goal_attempts_against</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_ball_possession</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_ball_possession_against</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_points</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_points_against</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_expected_goals_(xg)</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_expected_goals_(xg)_against</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goals</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goals_against</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_shots_on_goal</t>
-        </is>
-      </c>
-      <c r="AJ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_shots_on_goal_against</t>
-        </is>
-      </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>mean_last_match_mean_rat_player_start_home_against</t>
@@ -620,97 +620,97 @@
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_int_rep_player_sub</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_start</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_sub</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_sub</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_val_player_miss</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_sub</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_sub</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_start</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_sub</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_age_player_miss</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_sub</t>
-        </is>
-      </c>
-      <c r="AO1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_sub</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_sub</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_pot_player_miss</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_start</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_start</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_rat_player_miss</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_miss</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_age_player_start</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_start</t>
-        </is>
-      </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_n_player_miss</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_start</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_hei_player_miss</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_pot_player_miss</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_start</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_sub</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_val_player_miss</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_sub</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_start</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_rat_player_miss</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_miss</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_start</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_sub</t>
-        </is>
-      </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_n_player_miss</t>
-        </is>
-      </c>
-      <c r="BE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_start</t>
         </is>
       </c>
       <c r="BF1" s="1" t="inlineStr">
@@ -784,18 +784,18 @@
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr"/>
+      <c r="W2" t="n">
+        <v>-2</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1</v>
+      </c>
       <c r="Y2" t="inlineStr"/>
       <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="inlineStr"/>
       <c r="AB2" t="inlineStr"/>
-      <c r="AC2" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>1</v>
-      </c>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="inlineStr"/>
       <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="inlineStr"/>
@@ -806,49 +806,49 @@
         <v>68.82727272727273</v>
       </c>
       <c r="AL2" t="inlineStr"/>
-      <c r="AM2" t="inlineStr"/>
+      <c r="AM2" t="n">
+        <v>-1.018994553682376</v>
+      </c>
       <c r="AN2" t="n">
+        <v>-0.8898358585858581</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>1.27096785653287</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>-5.60215478917749</v>
+      </c>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="n">
+        <v>-27567033.61906794</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>-5.815557635900774</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>-29877547.34848484</v>
+      </c>
+      <c r="AU2" t="n">
         <v>-3.368140053292279</v>
       </c>
-      <c r="AO2" t="n">
-        <v>-1.018994553682376</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>-27567033.61906794</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>0.1716856060606062</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>-0.8898358585858581</v>
-      </c>
-      <c r="AS2" t="inlineStr"/>
-      <c r="AT2" t="inlineStr"/>
-      <c r="AU2" t="n">
-        <v>-3.894602272727269</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>-5.815557635900774</v>
-      </c>
+      <c r="AV2" t="inlineStr"/>
       <c r="AW2" t="inlineStr"/>
       <c r="AX2" t="n">
-        <v>-5.60215478917749</v>
+        <v>-4.555681818181824</v>
       </c>
       <c r="AY2" t="n">
-        <v>-29877547.34848484</v>
+        <v>-2.724589646464693</v>
       </c>
       <c r="AZ2" t="inlineStr"/>
       <c r="BA2" t="inlineStr"/>
       <c r="BB2" t="n">
-        <v>-4.555681818181824</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>1.27096785653287</v>
-      </c>
-      <c r="BD2" t="inlineStr"/>
-      <c r="BE2" t="n">
-        <v>-2.724589646464693</v>
-      </c>
+        <v>0.1716856060606062</v>
+      </c>
+      <c r="BC2" t="inlineStr"/>
+      <c r="BD2" t="n">
+        <v>-3.894602272727269</v>
+      </c>
+      <c r="BE2" t="inlineStr"/>
       <c r="BF2" t="n">
         <v>0</v>
       </c>
@@ -918,18 +918,18 @@
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="inlineStr"/>
-      <c r="W3" t="inlineStr"/>
-      <c r="X3" t="inlineStr"/>
+      <c r="W3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X3" t="n">
+        <v>2</v>
+      </c>
       <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="inlineStr"/>
-      <c r="AC3" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>2</v>
-      </c>
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="inlineStr"/>
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="inlineStr"/>
@@ -940,49 +940,49 @@
       <c r="AL3" t="n">
         <v>72.91717171717171</v>
       </c>
-      <c r="AM3" t="inlineStr"/>
+      <c r="AM3" t="n">
+        <v>0</v>
+      </c>
       <c r="AN3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>1.209149727084512</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>3.462799841060686</v>
+      </c>
+      <c r="AQ3" t="inlineStr"/>
+      <c r="AR3" t="n">
+        <v>768801.6879457098</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>1.710279293974935</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>1289191.91919192</v>
+      </c>
+      <c r="AU3" t="n">
         <v>0.9681501871719433</v>
       </c>
-      <c r="AO3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>768801.6879457098</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>-0.3444444444444485</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS3" t="inlineStr"/>
-      <c r="AT3" t="inlineStr"/>
-      <c r="AU3" t="n">
-        <v>3.310101010101036</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>1.710279293974935</v>
-      </c>
+      <c r="AV3" t="inlineStr"/>
       <c r="AW3" t="inlineStr"/>
       <c r="AX3" t="n">
-        <v>3.462799841060686</v>
+        <v>2.984848484848484</v>
       </c>
       <c r="AY3" t="n">
-        <v>1289191.91919192</v>
+        <v>4.172727272727258</v>
       </c>
       <c r="AZ3" t="inlineStr"/>
       <c r="BA3" t="inlineStr"/>
       <c r="BB3" t="n">
-        <v>2.984848484848484</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>1.209149727084512</v>
-      </c>
-      <c r="BD3" t="inlineStr"/>
-      <c r="BE3" t="n">
-        <v>4.172727272727258</v>
-      </c>
+        <v>-0.3444444444444485</v>
+      </c>
+      <c r="BC3" t="inlineStr"/>
+      <c r="BD3" t="n">
+        <v>3.310101010101036</v>
+      </c>
+      <c r="BE3" t="inlineStr"/>
       <c r="BF3" t="n">
         <v>0</v>
       </c>
@@ -1049,25 +1049,25 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>-11</v>
+        <v>-0.41</v>
       </c>
       <c r="T4" t="n">
+        <v>-1.19</v>
+      </c>
+      <c r="U4" t="n">
         <v>-1</v>
       </c>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
+      <c r="V4" t="n">
+        <v>-1</v>
+      </c>
       <c r="W4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>-5</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>-6</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="n">
         <v>-10</v>
       </c>
@@ -1075,28 +1075,28 @@
         <v>10</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AE4" t="n">
-        <v>-0.41</v>
+        <v>-11</v>
       </c>
       <c r="AF4" t="n">
-        <v>-1.19</v>
+        <v>-1</v>
       </c>
       <c r="AG4" t="n">
-        <v>-1</v>
+        <v>-5</v>
       </c>
       <c r="AH4" t="n">
-        <v>-1</v>
+        <v>-6</v>
       </c>
       <c r="AI4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-2</v>
+        <v>4</v>
       </c>
       <c r="AK4" t="n">
         <v>77</v>
@@ -1104,49 +1104,49 @@
       <c r="AL4" t="n">
         <v>68.22222222222223</v>
       </c>
-      <c r="AM4" t="inlineStr"/>
+      <c r="AM4" t="n">
+        <v>-0.280325814536341</v>
+      </c>
       <c r="AN4" t="n">
+        <v>-0.2950505050505052</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0.7055018600632579</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>-8.649826453598394</v>
+      </c>
+      <c r="AQ4" t="inlineStr"/>
+      <c r="AR4" t="n">
+        <v>-6310186.026854886</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>-7.558315375332924</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>-10490007.57575758</v>
+      </c>
+      <c r="AU4" t="n">
         <v>1.91167598483392</v>
       </c>
-      <c r="AO4" t="n">
-        <v>-0.280325814536341</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>-6310186.026854886</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>3.250404040404039</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>-0.2950505050505052</v>
-      </c>
-      <c r="AS4" t="inlineStr"/>
-      <c r="AT4" t="inlineStr"/>
-      <c r="AU4" t="n">
-        <v>-7.495252525252525</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>-7.558315375332924</v>
-      </c>
+      <c r="AV4" t="inlineStr"/>
       <c r="AW4" t="inlineStr"/>
       <c r="AX4" t="n">
-        <v>-8.649826453598394</v>
+        <v>-6.098989898989885</v>
       </c>
       <c r="AY4" t="n">
-        <v>-10490007.57575758</v>
+        <v>-0.08929292929295229</v>
       </c>
       <c r="AZ4" t="inlineStr"/>
       <c r="BA4" t="inlineStr"/>
       <c r="BB4" t="n">
-        <v>-6.098989898989885</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>0.7055018600632579</v>
-      </c>
-      <c r="BD4" t="inlineStr"/>
-      <c r="BE4" t="n">
-        <v>-0.08929292929295229</v>
-      </c>
+        <v>3.250404040404039</v>
+      </c>
+      <c r="BC4" t="inlineStr"/>
+      <c r="BD4" t="n">
+        <v>-7.495252525252525</v>
+      </c>
+      <c r="BE4" t="inlineStr"/>
       <c r="BF4" t="n">
         <v>0</v>
       </c>
@@ -1216,18 +1216,18 @@
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr"/>
-      <c r="W5" t="inlineStr"/>
-      <c r="X5" t="inlineStr"/>
+      <c r="W5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X5" t="n">
+        <v>2</v>
+      </c>
       <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="inlineStr"/>
-      <c r="AC5" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>2</v>
-      </c>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="inlineStr"/>
       <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="inlineStr"/>
@@ -1238,49 +1238,49 @@
       <c r="AL5" t="n">
         <v>71.32222222222224</v>
       </c>
-      <c r="AM5" t="inlineStr"/>
+      <c r="AM5" t="n">
+        <v>-0.3654629272611731</v>
+      </c>
       <c r="AN5" t="n">
+        <v>-0.4445707070707068</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>-0.5794683646438052</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>-4.824374058365279</v>
+      </c>
+      <c r="AQ5" t="inlineStr"/>
+      <c r="AR5" t="n">
+        <v>-5537891.391584374</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>-2.039520292897478</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>-2899527.567340066</v>
+      </c>
+      <c r="AU5" t="n">
         <v>2.286701868631695</v>
       </c>
-      <c r="AO5" t="n">
-        <v>-0.3654629272611731</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>-5537891.391584374</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>0.9752104377104374</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>-0.4445707070707068</v>
-      </c>
-      <c r="AS5" t="inlineStr"/>
-      <c r="AT5" t="inlineStr"/>
-      <c r="AU5" t="n">
-        <v>-1.189772727272739</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>-2.039520292897478</v>
-      </c>
+      <c r="AV5" t="inlineStr"/>
       <c r="AW5" t="inlineStr"/>
       <c r="AX5" t="n">
-        <v>-4.824374058365279</v>
+        <v>-1.504292929292944</v>
       </c>
       <c r="AY5" t="n">
-        <v>-2899527.567340066</v>
+        <v>1.447306397306335</v>
       </c>
       <c r="AZ5" t="inlineStr"/>
       <c r="BA5" t="inlineStr"/>
       <c r="BB5" t="n">
-        <v>-1.504292929292944</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>-0.5794683646438052</v>
-      </c>
-      <c r="BD5" t="inlineStr"/>
-      <c r="BE5" t="n">
-        <v>1.447306397306335</v>
-      </c>
+        <v>0.9752104377104374</v>
+      </c>
+      <c r="BC5" t="inlineStr"/>
+      <c r="BD5" t="n">
+        <v>-1.189772727272739</v>
+      </c>
+      <c r="BE5" t="inlineStr"/>
       <c r="BF5" t="n">
         <v>0</v>
       </c>
@@ -1347,25 +1347,25 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>3</v>
+        <v>0.63</v>
       </c>
       <c r="T6" t="n">
-        <v>8</v>
-      </c>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr"/>
+        <v>0.4299999999999999</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
       <c r="W6" t="n">
-        <v>-7</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>7</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>3</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="n">
         <v>5</v>
       </c>
@@ -1373,76 +1373,76 @@
         <v>-5</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.63</v>
+        <v>3</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.4299999999999999</v>
+        <v>8</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AI6" t="n">
-        <v>1</v>
+        <v>-7</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AK6" t="inlineStr"/>
       <c r="AL6" t="n">
         <v>68</v>
       </c>
-      <c r="AM6" t="inlineStr"/>
+      <c r="AM6" t="n">
+        <v>-0.05417019723005279</v>
+      </c>
       <c r="AN6" t="n">
+        <v>0.1402918069584733</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>-3.80047724654278</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>0.3204769636013225</v>
+      </c>
+      <c r="AQ6" t="inlineStr"/>
+      <c r="AR6" t="n">
+        <v>4245488.492845303</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>4.155497670448653</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>1707519.640852975</v>
+      </c>
+      <c r="AU6" t="n">
         <v>3.297352201557544</v>
       </c>
-      <c r="AO6" t="n">
-        <v>-0.05417019723005279</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>4245488.492845303</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>-2.294837261503933</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>0.1402918069584733</v>
-      </c>
-      <c r="AS6" t="inlineStr"/>
-      <c r="AT6" t="inlineStr"/>
-      <c r="AU6" t="n">
-        <v>2.019079685746348</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>4.155497670448653</v>
-      </c>
+      <c r="AV6" t="inlineStr"/>
       <c r="AW6" t="inlineStr"/>
       <c r="AX6" t="n">
-        <v>0.3204769636013225</v>
+        <v>-0.210325476992125</v>
       </c>
       <c r="AY6" t="n">
-        <v>1707519.640852975</v>
+        <v>1.728058361391675</v>
       </c>
       <c r="AZ6" t="inlineStr"/>
       <c r="BA6" t="inlineStr"/>
       <c r="BB6" t="n">
-        <v>-0.210325476992125</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>-3.80047724654278</v>
-      </c>
-      <c r="BD6" t="inlineStr"/>
-      <c r="BE6" t="n">
-        <v>1.728058361391675</v>
-      </c>
+        <v>-2.294837261503933</v>
+      </c>
+      <c r="BC6" t="inlineStr"/>
+      <c r="BD6" t="n">
+        <v>2.019079685746348</v>
+      </c>
+      <c r="BE6" t="inlineStr"/>
       <c r="BF6" t="n">
         <v>0</v>
       </c>
@@ -1509,25 +1509,25 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>2</v>
+        <v>-1.57</v>
       </c>
       <c r="T7" t="n">
+        <v>-0.8499999999999999</v>
+      </c>
+      <c r="U7" t="n">
+        <v>-5</v>
+      </c>
+      <c r="V7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="W7" t="n">
         <v>-2</v>
       </c>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr"/>
-      <c r="W7" t="n">
-        <v>-4</v>
-      </c>
       <c r="X7" t="n">
-        <v>-7</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>-1</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="n">
         <v>4</v>
       </c>
@@ -1538,73 +1538,73 @@
         <v>-2</v>
       </c>
       <c r="AD7" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="AE7" t="n">
-        <v>-1.57</v>
+        <v>2</v>
       </c>
       <c r="AF7" t="n">
-        <v>-0.8499999999999999</v>
+        <v>-2</v>
       </c>
       <c r="AG7" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
         <v>-1</v>
       </c>
       <c r="AI7" t="n">
-        <v>-2</v>
+        <v>-4</v>
       </c>
       <c r="AJ7" t="n">
-        <v>-3</v>
+        <v>-7</v>
       </c>
       <c r="AK7" t="n">
         <v>72.8</v>
       </c>
       <c r="AL7" t="inlineStr"/>
-      <c r="AM7" t="inlineStr"/>
+      <c r="AM7" t="n">
+        <v>-0.2687044160212377</v>
+      </c>
       <c r="AN7" t="n">
+        <v>-0.615909090909091</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>-1.806859406345662</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>-4.255491155349247</v>
+      </c>
+      <c r="AQ7" t="inlineStr"/>
+      <c r="AR7" t="n">
+        <v>-5950125.747218501</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>-1.31904421366049</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>-6772159.09090909</v>
+      </c>
+      <c r="AU7" t="n">
         <v>-3.0592042669644</v>
       </c>
-      <c r="AO7" t="n">
-        <v>-0.2687044160212377</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>-5950125.747218501</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>-3.824368686868688</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>-0.615909090909091</v>
-      </c>
-      <c r="AS7" t="inlineStr"/>
-      <c r="AT7" t="inlineStr"/>
-      <c r="AU7" t="n">
-        <v>-0.280934343434339</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>-1.31904421366049</v>
-      </c>
+      <c r="AV7" t="inlineStr"/>
       <c r="AW7" t="inlineStr"/>
       <c r="AX7" t="n">
-        <v>-4.255491155349247</v>
+        <v>-4.433838383838406</v>
       </c>
       <c r="AY7" t="n">
-        <v>-6772159.09090909</v>
+        <v>-0.2345959595959641</v>
       </c>
       <c r="AZ7" t="inlineStr"/>
       <c r="BA7" t="inlineStr"/>
       <c r="BB7" t="n">
-        <v>-4.433838383838406</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>-1.806859406345662</v>
-      </c>
-      <c r="BD7" t="inlineStr"/>
-      <c r="BE7" t="n">
-        <v>-0.2345959595959641</v>
-      </c>
+        <v>-3.824368686868688</v>
+      </c>
+      <c r="BC7" t="inlineStr"/>
+      <c r="BD7" t="n">
+        <v>-0.280934343434339</v>
+      </c>
+      <c r="BE7" t="inlineStr"/>
       <c r="BF7" t="n">
         <v>0</v>
       </c>
@@ -1671,25 +1671,25 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>12</v>
+        <v>1.17</v>
       </c>
       <c r="T8" t="n">
-        <v>8</v>
-      </c>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr"/>
+        <v>0.22</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1</v>
+      </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>4</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
       <c r="AA8" t="n">
         <v>-4</v>
       </c>
@@ -1697,25 +1697,25 @@
         <v>4</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.17</v>
+        <v>12</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.22</v>
+        <v>8</v>
       </c>
       <c r="AG8" t="n">
         <v>1</v>
       </c>
       <c r="AH8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AI8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AJ8" t="n">
         <v>1</v>
@@ -1726,49 +1726,49 @@
       <c r="AL8" t="n">
         <v>72.40000000000001</v>
       </c>
-      <c r="AM8" t="inlineStr"/>
+      <c r="AM8" t="n">
+        <v>-0.01614727431010476</v>
+      </c>
       <c r="AN8" t="n">
+        <v>-0.1828282828282823</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>-1.497411290676421</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>0.6434416835098631</v>
+      </c>
+      <c r="AQ8" t="inlineStr"/>
+      <c r="AR8" t="n">
+        <v>988163.3014060548</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>2.203022409373645</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>825555.555555555</v>
+      </c>
+      <c r="AU8" t="n">
         <v>0.8651730535575268</v>
       </c>
-      <c r="AO8" t="n">
-        <v>-0.01614727431010476</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>988163.3014060548</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>-1.404040404040405</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>-0.1828282828282823</v>
-      </c>
-      <c r="AS8" t="inlineStr"/>
-      <c r="AT8" t="inlineStr"/>
-      <c r="AU8" t="n">
-        <v>2.346464646464668</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>2.203022409373645</v>
-      </c>
+      <c r="AV8" t="inlineStr"/>
       <c r="AW8" t="inlineStr"/>
       <c r="AX8" t="n">
-        <v>0.6434416835098631</v>
+        <v>0.1626262626262758</v>
       </c>
       <c r="AY8" t="n">
-        <v>825555.555555555</v>
+        <v>-0.964646464646421</v>
       </c>
       <c r="AZ8" t="inlineStr"/>
       <c r="BA8" t="inlineStr"/>
       <c r="BB8" t="n">
-        <v>0.1626262626262758</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>-1.497411290676421</v>
-      </c>
-      <c r="BD8" t="inlineStr"/>
-      <c r="BE8" t="n">
-        <v>-0.964646464646421</v>
-      </c>
+        <v>-1.404040404040405</v>
+      </c>
+      <c r="BC8" t="inlineStr"/>
+      <c r="BD8" t="n">
+        <v>2.346464646464668</v>
+      </c>
+      <c r="BE8" t="inlineStr"/>
       <c r="BF8" t="n">
         <v>0</v>
       </c>
@@ -1835,25 +1835,25 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-4</v>
+        <v>0.49</v>
       </c>
       <c r="T9" t="n">
-        <v>-5</v>
-      </c>
-      <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr"/>
+        <v>1.03</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
+      </c>
+      <c r="V9" t="n">
+        <v>4</v>
+      </c>
       <c r="W9" t="n">
-        <v>-7</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>8</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>-6</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="n">
         <v>12</v>
       </c>
@@ -1861,74 +1861,74 @@
         <v>-12</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.49</v>
+        <v>-4</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.03</v>
+        <v>-5</v>
       </c>
       <c r="AG9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>4</v>
+        <v>-6</v>
       </c>
       <c r="AI9" t="n">
-        <v>1</v>
+        <v>-7</v>
       </c>
       <c r="AJ9" t="n">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AK9" t="inlineStr"/>
       <c r="AL9" t="inlineStr"/>
-      <c r="AM9" t="inlineStr"/>
+      <c r="AM9" t="n">
+        <v>0.1598765432098768</v>
+      </c>
       <c r="AN9" t="n">
+        <v>0.3161616161616163</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>-0.7171100030074342</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>1.545942708763206</v>
+      </c>
+      <c r="AQ9" t="inlineStr"/>
+      <c r="AR9" t="n">
+        <v>2373768.356524767</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>0.9270287167723126</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>4489595.959595959</v>
+      </c>
+      <c r="AU9" t="n">
         <v>-0.8003759298631223</v>
       </c>
-      <c r="AO9" t="n">
-        <v>0.1598765432098768</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>2373768.356524767</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>1.0949494949495</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>0.3161616161616163</v>
-      </c>
-      <c r="AS9" t="inlineStr"/>
-      <c r="AT9" t="inlineStr"/>
-      <c r="AU9" t="n">
-        <v>3.143939393939391</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>0.9270287167723126</v>
-      </c>
+      <c r="AV9" t="inlineStr"/>
       <c r="AW9" t="inlineStr"/>
       <c r="AX9" t="n">
-        <v>1.545942708763206</v>
+        <v>4.529797979797991</v>
       </c>
       <c r="AY9" t="n">
-        <v>4489595.959595959</v>
+        <v>0.5989898989898848</v>
       </c>
       <c r="AZ9" t="inlineStr"/>
       <c r="BA9" t="inlineStr"/>
       <c r="BB9" t="n">
-        <v>4.529797979797991</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>-0.7171100030074342</v>
-      </c>
-      <c r="BD9" t="inlineStr"/>
-      <c r="BE9" t="n">
-        <v>0.5989898989898848</v>
-      </c>
+        <v>1.0949494949495</v>
+      </c>
+      <c r="BC9" t="inlineStr"/>
+      <c r="BD9" t="n">
+        <v>3.143939393939391</v>
+      </c>
+      <c r="BE9" t="inlineStr"/>
       <c r="BF9" t="n">
         <v>0</v>
       </c>
@@ -1998,18 +1998,18 @@
       <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr"/>
-      <c r="W10" t="inlineStr"/>
-      <c r="X10" t="inlineStr"/>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
       <c r="Y10" t="inlineStr"/>
       <c r="Z10" t="inlineStr"/>
       <c r="AA10" t="inlineStr"/>
       <c r="AB10" t="inlineStr"/>
-      <c r="AC10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>0</v>
-      </c>
+      <c r="AC10" t="inlineStr"/>
+      <c r="AD10" t="inlineStr"/>
       <c r="AE10" t="inlineStr"/>
       <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="inlineStr"/>
@@ -2022,49 +2022,49 @@
       <c r="AL10" t="n">
         <v>74.09999999999999</v>
       </c>
-      <c r="AM10" t="inlineStr"/>
+      <c r="AM10" t="n">
+        <v>0.383006629150733</v>
+      </c>
       <c r="AN10" t="n">
+        <v>0.8836649321497805</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>1.918375417430205</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>4.346246567234701</v>
+      </c>
+      <c r="AQ10" t="inlineStr"/>
+      <c r="AR10" t="n">
+        <v>3444492.081974726</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>1.616901098817792</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>5495950.923375166</v>
+      </c>
+      <c r="AU10" t="n">
         <v>-3.529726368637142</v>
       </c>
-      <c r="AO10" t="n">
-        <v>0.383006629150733</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>3444492.081974726</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>5.011570247933886</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>0.8836649321497805</v>
-      </c>
-      <c r="AS10" t="inlineStr"/>
-      <c r="AT10" t="inlineStr"/>
-      <c r="AU10" t="n">
-        <v>-0.4031527395163721</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>1.616901098817792</v>
-      </c>
+      <c r="AV10" t="inlineStr"/>
       <c r="AW10" t="inlineStr"/>
       <c r="AX10" t="n">
-        <v>4.346246567234701</v>
+        <v>5.386593204775011</v>
       </c>
       <c r="AY10" t="n">
-        <v>5495950.923375166</v>
+        <v>-1.023773084379172</v>
       </c>
       <c r="AZ10" t="inlineStr"/>
       <c r="BA10" t="inlineStr"/>
       <c r="BB10" t="n">
-        <v>5.386593204775011</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>1.918375417430205</v>
-      </c>
-      <c r="BD10" t="inlineStr"/>
-      <c r="BE10" t="n">
-        <v>-1.023773084379172</v>
-      </c>
+        <v>5.011570247933886</v>
+      </c>
+      <c r="BC10" t="inlineStr"/>
+      <c r="BD10" t="n">
+        <v>-0.4031527395163721</v>
+      </c>
+      <c r="BE10" t="inlineStr"/>
       <c r="BF10" t="n">
         <v>0</v>
       </c>
@@ -2150,49 +2150,49 @@
       <c r="AJ11" t="inlineStr"/>
       <c r="AK11" t="inlineStr"/>
       <c r="AL11" t="inlineStr"/>
-      <c r="AM11" t="inlineStr"/>
+      <c r="AM11" t="n">
+        <v>0.2117100783251458</v>
+      </c>
       <c r="AN11" t="n">
+        <v>0.4491161616161616</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>2.40355565582604</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>5.963795480978135</v>
+      </c>
+      <c r="AQ11" t="inlineStr"/>
+      <c r="AR11" t="n">
+        <v>5857518.095843688</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>1.144461470570874</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>4815095.749158249</v>
+      </c>
+      <c r="AU11" t="n">
         <v>0.3723647850067096</v>
       </c>
-      <c r="AO11" t="n">
-        <v>0.2117100783251458</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>5857518.095843688</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>1.374789562289564</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>0.4491161616161616</v>
-      </c>
-      <c r="AS11" t="inlineStr"/>
-      <c r="AT11" t="inlineStr"/>
-      <c r="AU11" t="n">
-        <v>0.2750000000000057</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>1.144461470570874</v>
-      </c>
+      <c r="AV11" t="inlineStr"/>
       <c r="AW11" t="inlineStr"/>
       <c r="AX11" t="n">
-        <v>5.963795480978135</v>
+        <v>2.81906565656567</v>
       </c>
       <c r="AY11" t="n">
-        <v>4815095.749158249</v>
+        <v>0.8686026936027247</v>
       </c>
       <c r="AZ11" t="inlineStr"/>
       <c r="BA11" t="inlineStr"/>
       <c r="BB11" t="n">
-        <v>2.81906565656567</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>2.40355565582604</v>
-      </c>
-      <c r="BD11" t="inlineStr"/>
-      <c r="BE11" t="n">
-        <v>0.8686026936027247</v>
-      </c>
+        <v>1.374789562289564</v>
+      </c>
+      <c r="BC11" t="inlineStr"/>
+      <c r="BD11" t="n">
+        <v>0.2750000000000057</v>
+      </c>
+      <c r="BE11" t="inlineStr"/>
       <c r="BF11" t="n">
         <v>0</v>
       </c>
@@ -2278,49 +2278,49 @@
       <c r="AJ12" t="inlineStr"/>
       <c r="AK12" t="inlineStr"/>
       <c r="AL12" t="inlineStr"/>
-      <c r="AM12" t="inlineStr"/>
+      <c r="AM12" t="n">
+        <v>-0.1954827144533029</v>
+      </c>
       <c r="AN12" t="n">
+        <v>-0.512934904601571</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0.05433080354648823</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>-3.986399203556061</v>
+      </c>
+      <c r="AQ12" t="inlineStr"/>
+      <c r="AR12" t="n">
+        <v>-5889981.561285483</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>-2.444844920874331</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>-6031568.462401793</v>
+      </c>
+      <c r="AU12" t="n">
         <v>1.236358543417367</v>
       </c>
-      <c r="AO12" t="n">
-        <v>-0.1954827144533029</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>-5889981.561285483</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>-2.368308080808081</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>-0.512934904601571</v>
-      </c>
-      <c r="AS12" t="inlineStr"/>
-      <c r="AT12" t="inlineStr"/>
-      <c r="AU12" t="n">
-        <v>-0.7374579124579128</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>-2.444844920874331</v>
-      </c>
+      <c r="AV12" t="inlineStr"/>
       <c r="AW12" t="inlineStr"/>
       <c r="AX12" t="n">
-        <v>-3.986399203556061</v>
+        <v>-4.55845959595959</v>
       </c>
       <c r="AY12" t="n">
-        <v>-6031568.462401793</v>
+        <v>1.797923681257004</v>
       </c>
       <c r="AZ12" t="inlineStr"/>
       <c r="BA12" t="inlineStr"/>
       <c r="BB12" t="n">
-        <v>-4.55845959595959</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>0.05433080354648823</v>
-      </c>
-      <c r="BD12" t="inlineStr"/>
-      <c r="BE12" t="n">
-        <v>1.797923681257004</v>
-      </c>
+        <v>-2.368308080808081</v>
+      </c>
+      <c r="BC12" t="inlineStr"/>
+      <c r="BD12" t="n">
+        <v>-0.7374579124579128</v>
+      </c>
+      <c r="BE12" t="inlineStr"/>
       <c r="BF12" t="n">
         <v>0</v>
       </c>
@@ -2406,49 +2406,49 @@
       <c r="AJ13" t="inlineStr"/>
       <c r="AK13" t="inlineStr"/>
       <c r="AL13" t="inlineStr"/>
-      <c r="AM13" t="inlineStr"/>
+      <c r="AM13" t="n">
+        <v>0.280325814536341</v>
+      </c>
       <c r="AN13" t="n">
+        <v>0.2232323232323234</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0.7150785579084697</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>3.086613524552121</v>
+      </c>
+      <c r="AQ13" t="inlineStr"/>
+      <c r="AR13" t="n">
+        <v>3810824.721828726</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>1.187329888731497</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>6495757.575757576</v>
+      </c>
+      <c r="AU13" t="n">
         <v>-0.1451525351220369</v>
       </c>
-      <c r="AO13" t="n">
-        <v>0.280325814536341</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>3810824.721828726</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>0.3828282828282816</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>0.2232323232323234</v>
-      </c>
-      <c r="AS13" t="inlineStr"/>
-      <c r="AT13" t="inlineStr"/>
-      <c r="AU13" t="n">
-        <v>0.9414141414141426</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>1.187329888731497</v>
-      </c>
+      <c r="AV13" t="inlineStr"/>
       <c r="AW13" t="inlineStr"/>
       <c r="AX13" t="n">
-        <v>3.086613524552121</v>
+        <v>2.164646464646466</v>
       </c>
       <c r="AY13" t="n">
-        <v>6495757.575757576</v>
+        <v>0.07979797979797354</v>
       </c>
       <c r="AZ13" t="inlineStr"/>
       <c r="BA13" t="inlineStr"/>
       <c r="BB13" t="n">
-        <v>2.164646464646466</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>0.7150785579084697</v>
-      </c>
-      <c r="BD13" t="inlineStr"/>
-      <c r="BE13" t="n">
-        <v>0.07979797979797354</v>
-      </c>
+        <v>0.3828282828282816</v>
+      </c>
+      <c r="BC13" t="inlineStr"/>
+      <c r="BD13" t="n">
+        <v>0.9414141414141426</v>
+      </c>
+      <c r="BE13" t="inlineStr"/>
       <c r="BF13" t="n">
         <v>0</v>
       </c>
@@ -2534,49 +2534,49 @@
       <c r="AJ14" t="inlineStr"/>
       <c r="AK14" t="inlineStr"/>
       <c r="AL14" t="inlineStr"/>
-      <c r="AM14" t="inlineStr"/>
+      <c r="AM14" t="n">
+        <v>0.1731444371043689</v>
+      </c>
       <c r="AN14" t="n">
+        <v>0.5090909090909088</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>2.251713805123867</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>5.031644408605189</v>
+      </c>
+      <c r="AQ14" t="inlineStr"/>
+      <c r="AR14" t="n">
+        <v>1245750.796439203</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>2.523833450815545</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>2959393.93939394</v>
+      </c>
+      <c r="AU14" t="n">
         <v>0.3419896709964689</v>
       </c>
-      <c r="AO14" t="n">
-        <v>0.1731444371043689</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>1245750.796439203</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>0.5020202020202014</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>0.5090909090909088</v>
-      </c>
-      <c r="AS14" t="inlineStr"/>
-      <c r="AT14" t="inlineStr"/>
-      <c r="AU14" t="n">
-        <v>3.9969696969697</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>2.523833450815545</v>
-      </c>
+      <c r="AV14" t="inlineStr"/>
       <c r="AW14" t="inlineStr"/>
       <c r="AX14" t="n">
-        <v>5.031644408605189</v>
+        <v>4.358585858585855</v>
       </c>
       <c r="AY14" t="n">
-        <v>2959393.93939394</v>
+        <v>1.309090909090912</v>
       </c>
       <c r="AZ14" t="inlineStr"/>
       <c r="BA14" t="inlineStr"/>
       <c r="BB14" t="n">
-        <v>4.358585858585855</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>2.251713805123867</v>
-      </c>
-      <c r="BD14" t="inlineStr"/>
-      <c r="BE14" t="n">
-        <v>1.309090909090912</v>
-      </c>
+        <v>0.5020202020202014</v>
+      </c>
+      <c r="BC14" t="inlineStr"/>
+      <c r="BD14" t="n">
+        <v>3.9969696969697</v>
+      </c>
+      <c r="BE14" t="inlineStr"/>
       <c r="BF14" t="n">
         <v>0</v>
       </c>
@@ -2662,49 +2662,49 @@
       <c r="AJ15" t="inlineStr"/>
       <c r="AK15" t="inlineStr"/>
       <c r="AL15" t="inlineStr"/>
-      <c r="AM15" t="inlineStr"/>
+      <c r="AM15" t="n">
+        <v>0.1972262305595638</v>
+      </c>
       <c r="AN15" t="n">
+        <v>0.08787878787878811</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>1.926936026936023</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>3.875348725348744</v>
+      </c>
+      <c r="AQ15" t="inlineStr"/>
+      <c r="AR15" t="n">
+        <v>2540530.503447169</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>2.762109187109175</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>6326161.616161616</v>
+      </c>
+      <c r="AU15" t="n">
         <v>-1.359371492704781</v>
       </c>
-      <c r="AO15" t="n">
-        <v>0.1972262305595638</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>2540530.503447169</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>0.01919191919191832</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>0.08787878787878811</v>
-      </c>
-      <c r="AS15" t="inlineStr"/>
-      <c r="AT15" t="inlineStr"/>
-      <c r="AU15" t="n">
-        <v>2.373737373737384</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>2.762109187109175</v>
-      </c>
+      <c r="AV15" t="inlineStr"/>
       <c r="AW15" t="inlineStr"/>
       <c r="AX15" t="n">
-        <v>3.875348725348744</v>
+        <v>2.170707070707067</v>
       </c>
       <c r="AY15" t="n">
-        <v>6326161.616161616</v>
+        <v>-1.631313131313107</v>
       </c>
       <c r="AZ15" t="inlineStr"/>
       <c r="BA15" t="inlineStr"/>
       <c r="BB15" t="n">
-        <v>2.170707070707067</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>1.926936026936023</v>
-      </c>
-      <c r="BD15" t="inlineStr"/>
-      <c r="BE15" t="n">
-        <v>-1.631313131313107</v>
-      </c>
+        <v>0.01919191919191832</v>
+      </c>
+      <c r="BC15" t="inlineStr"/>
+      <c r="BD15" t="n">
+        <v>2.373737373737384</v>
+      </c>
+      <c r="BE15" t="inlineStr"/>
       <c r="BF15" t="n">
         <v>0</v>
       </c>
@@ -2790,49 +2790,49 @@
       <c r="AJ16" t="inlineStr"/>
       <c r="AK16" t="inlineStr"/>
       <c r="AL16" t="inlineStr"/>
-      <c r="AM16" t="inlineStr"/>
+      <c r="AM16" t="n">
+        <v>0</v>
+      </c>
       <c r="AN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0.144881071177057</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>-0.03758253699723468</v>
+      </c>
+      <c r="AQ16" t="inlineStr"/>
+      <c r="AR16" t="n">
+        <v>-226999.0568161553</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>0.5850064032338338</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>-735555.555555556</v>
+      </c>
+      <c r="AU16" t="n">
         <v>-0.7782520511199778</v>
       </c>
-      <c r="AO16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>-226999.0568161553</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>0.1080808080808104</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS16" t="inlineStr"/>
-      <c r="AT16" t="inlineStr"/>
-      <c r="AU16" t="n">
-        <v>-1.044949494949506</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>0.5850064032338338</v>
-      </c>
+      <c r="AV16" t="inlineStr"/>
       <c r="AW16" t="inlineStr"/>
       <c r="AX16" t="n">
-        <v>-0.03758253699723468</v>
+        <v>-1.223737373737379</v>
       </c>
       <c r="AY16" t="n">
-        <v>-735555.555555556</v>
+        <v>-4.336363636363615</v>
       </c>
       <c r="AZ16" t="inlineStr"/>
       <c r="BA16" t="inlineStr"/>
       <c r="BB16" t="n">
-        <v>-1.223737373737379</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>0.144881071177057</v>
-      </c>
-      <c r="BD16" t="inlineStr"/>
-      <c r="BE16" t="n">
-        <v>-4.336363636363615</v>
-      </c>
+        <v>0.1080808080808104</v>
+      </c>
+      <c r="BC16" t="inlineStr"/>
+      <c r="BD16" t="n">
+        <v>-1.044949494949506</v>
+      </c>
+      <c r="BE16" t="inlineStr"/>
       <c r="BF16" t="n">
         <v>0</v>
       </c>
@@ -2918,49 +2918,49 @@
       <c r="AJ17" t="inlineStr"/>
       <c r="AK17" t="inlineStr"/>
       <c r="AL17" t="inlineStr"/>
-      <c r="AM17" t="inlineStr"/>
+      <c r="AM17" t="n">
+        <v>0.2373376461095758</v>
+      </c>
       <c r="AN17" t="n">
+        <v>0.4359595959595961</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>1.042499196709723</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>8.086126248670112</v>
+      </c>
+      <c r="AQ17" t="inlineStr"/>
+      <c r="AR17" t="n">
+        <v>5804070.36376554</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>6.991328999136016</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>11174830.80808081</v>
+      </c>
+      <c r="AU17" t="n">
         <v>-2.226441888196319</v>
       </c>
-      <c r="AO17" t="n">
-        <v>0.2373376461095758</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>5804070.36376554</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>-2.284494949494949</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>0.4359595959595961</v>
-      </c>
-      <c r="AS17" t="inlineStr"/>
-      <c r="AT17" t="inlineStr"/>
-      <c r="AU17" t="n">
-        <v>8.855858585858584</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>6.991328999136016</v>
-      </c>
+      <c r="AV17" t="inlineStr"/>
       <c r="AW17" t="inlineStr"/>
       <c r="AX17" t="n">
-        <v>8.086126248670112</v>
+        <v>7.701262626262618</v>
       </c>
       <c r="AY17" t="n">
-        <v>11174830.80808081</v>
+        <v>-2.860707070707036</v>
       </c>
       <c r="AZ17" t="inlineStr"/>
       <c r="BA17" t="inlineStr"/>
       <c r="BB17" t="n">
-        <v>7.701262626262618</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>1.042499196709723</v>
-      </c>
-      <c r="BD17" t="inlineStr"/>
-      <c r="BE17" t="n">
-        <v>-2.860707070707036</v>
-      </c>
+        <v>-2.284494949494949</v>
+      </c>
+      <c r="BC17" t="inlineStr"/>
+      <c r="BD17" t="n">
+        <v>8.855858585858584</v>
+      </c>
+      <c r="BE17" t="inlineStr"/>
       <c r="BF17" t="n">
         <v>0</v>
       </c>
@@ -3046,49 +3046,49 @@
       <c r="AJ18" t="inlineStr"/>
       <c r="AK18" t="inlineStr"/>
       <c r="AL18" t="inlineStr"/>
-      <c r="AM18" t="inlineStr"/>
+      <c r="AM18" t="n">
+        <v>0.3070486031153075</v>
+      </c>
       <c r="AN18" t="n">
+        <v>0.5195796347311497</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>2.745506021508696</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>-0.2609359293956857</v>
+      </c>
+      <c r="AQ18" t="inlineStr"/>
+      <c r="AR18" t="n">
+        <v>-4273254.37168246</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>-2.876656024886387</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>-4818364.452606875</v>
+      </c>
+      <c r="AU18" t="n">
         <v>-2.863873293263964</v>
       </c>
-      <c r="AO18" t="n">
-        <v>0.3070486031153075</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>-4273254.37168246</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>2.835700438730743</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>0.5195796347311497</v>
-      </c>
-      <c r="AS18" t="inlineStr"/>
-      <c r="AT18" t="inlineStr"/>
-      <c r="AU18" t="n">
-        <v>-2.411458014488318</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>-2.876656024886387</v>
-      </c>
+      <c r="AV18" t="inlineStr"/>
       <c r="AW18" t="inlineStr"/>
       <c r="AX18" t="n">
-        <v>-0.2609359293956857</v>
+        <v>-0.101061116212648</v>
       </c>
       <c r="AY18" t="n">
-        <v>-4818364.452606875</v>
+        <v>0.07690031629425675</v>
       </c>
       <c r="AZ18" t="inlineStr"/>
       <c r="BA18" t="inlineStr"/>
       <c r="BB18" t="n">
-        <v>-0.101061116212648</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>2.745506021508696</v>
-      </c>
-      <c r="BD18" t="inlineStr"/>
-      <c r="BE18" t="n">
-        <v>0.07690031629425675</v>
-      </c>
+        <v>2.835700438730743</v>
+      </c>
+      <c r="BC18" t="inlineStr"/>
+      <c r="BD18" t="n">
+        <v>-2.411458014488318</v>
+      </c>
+      <c r="BE18" t="inlineStr"/>
       <c r="BF18" t="n">
         <v>0</v>
       </c>
@@ -3174,48 +3174,62 @@
       <c r="AJ19" t="inlineStr"/>
       <c r="AK19" t="inlineStr"/>
       <c r="AL19" t="inlineStr"/>
-      <c r="AM19" t="inlineStr"/>
+      <c r="AM19" t="n">
+        <v>1.099335036997688</v>
+      </c>
       <c r="AN19" t="n">
+        <v>1.009532828282828</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>-0.008783495282912668</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>7.880114692652285</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>64500000</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>30881154.62857796</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>7.586151320968142</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>37210754.41919191</v>
+      </c>
+      <c r="AU19" t="n">
         <v>2.057918723925269</v>
       </c>
-      <c r="AO19" t="n">
-        <v>1.099335036997688</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>30881154.62857796</v>
-      </c>
-      <c r="AQ19" t="n">
+      <c r="AV19" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>93</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>8.004419191919183</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>1.426104797979804</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>91</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB19" t="n">
         <v>-0.6199179292929315</v>
       </c>
-      <c r="AR19" t="n">
-        <v>1.009532828282828</v>
-      </c>
-      <c r="AS19" t="inlineStr"/>
-      <c r="AT19" t="inlineStr"/>
-      <c r="AU19" t="n">
+      <c r="BC19" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD19" t="n">
         <v>7.188541666666652</v>
       </c>
-      <c r="AV19" t="n">
-        <v>7.586151320968142</v>
-      </c>
-      <c r="AW19" t="inlineStr"/>
-      <c r="AX19" t="n">
-        <v>7.880114692652285</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>37210754.41919191</v>
-      </c>
-      <c r="AZ19" t="inlineStr"/>
-      <c r="BA19" t="inlineStr"/>
-      <c r="BB19" t="n">
-        <v>8.004419191919183</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>-0.008783495282912668</v>
-      </c>
-      <c r="BD19" t="inlineStr"/>
       <c r="BE19" t="n">
-        <v>1.426104797979804</v>
+        <v>-9.5</v>
       </c>
       <c r="BF19" t="n">
         <v>0</v>

--- a/data/france/p6_deployment/data_preparation/df_tagged.xlsx
+++ b/data/france/p6_deployment/data_preparation/df_tagged.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BF4"/>
+  <dimension ref="A1:BF15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -520,94 +520,94 @@
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_last_match_goals</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goals_against</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_shots_on_goal</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_shots_on_goal_against</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_last_match_n_matches_last_days</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_n_matches_last_days_against</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_interceptions</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_interceptions_against</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_expected_goals_(xg)</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_expected_goals_(xg)_against</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_interceptions</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_interceptions_against</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_shots_on_goal</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_shots_on_goal_against</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_ball_possession</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_ball_possession_against</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_points</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_points_against</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_fouls</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_fouls_against</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_goal_attempts</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_goal_attempts_against</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goals</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goals_against</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_fouls</t>
-        </is>
-      </c>
-      <c r="AJ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_fouls_against</t>
-        </is>
-      </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>mean_last_match_mean_rat_player_start_home_against</t>
@@ -625,92 +625,92 @@
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_int_rep_player_sub</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_start</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_val_player_miss</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_start</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_miss</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_start</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_pot_player_miss</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>dif_n_player_miss</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_miss</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_start</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_sub</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_start</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_miss</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_sub</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_start</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_rat_player_sub</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_start</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_miss</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_start</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_start</t>
-        </is>
-      </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_start</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>dif_n_player_miss</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_sub</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_miss</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_pot_player_sub</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>dif_sum_rat_player_miss</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_miss</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_pot_player_miss</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_sub</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_start</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_sub</t>
-        </is>
-      </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_val_player_miss</t>
-        </is>
-      </c>
-      <c r="BE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_start</t>
         </is>
       </c>
       <c r="BF1" s="1" t="inlineStr">
@@ -722,23 +722,23 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>KQAqguF7</t>
+          <t>6ZfxDZ5t</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45528.66666666666</v>
+        <v>45536.65625</v>
       </c>
       <c r="C2" t="n">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="D2" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E2" t="n">
-        <v>528</v>
+        <v>777</v>
       </c>
       <c r="F2" t="n">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="G2" t="n">
         <v>55</v>
@@ -760,97 +760,127 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>67</v>
+        <v>243</v>
       </c>
       <c r="M2" t="n">
-        <v>37</v>
+        <v>234</v>
       </c>
       <c r="N2" t="n">
+        <v>-21</v>
+      </c>
+      <c r="O2" t="n">
+        <v>-5</v>
+      </c>
+      <c r="P2" t="n">
         <v>2</v>
       </c>
-      <c r="O2" t="n">
+      <c r="Q2" t="n">
+        <v>-2</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="n">
+        <v>-3</v>
+      </c>
+      <c r="T2" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="U2" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="V2" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>-0.9650000000000001</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.08499999999999996</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH2" t="n">
         <v>-1</v>
       </c>
-      <c r="P2" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="inlineStr"/>
-      <c r="AB2" t="inlineStr"/>
-      <c r="AC2" t="inlineStr"/>
-      <c r="AD2" t="inlineStr"/>
-      <c r="AE2" t="inlineStr"/>
-      <c r="AF2" t="inlineStr"/>
-      <c r="AG2" t="inlineStr"/>
-      <c r="AH2" t="inlineStr"/>
-      <c r="AI2" t="inlineStr"/>
-      <c r="AJ2" t="inlineStr"/>
-      <c r="AK2" t="inlineStr"/>
+      <c r="AI2" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>67.3</v>
+      </c>
       <c r="AL2" t="inlineStr"/>
       <c r="AM2" t="n">
-        <v>0.144881071177057</v>
+        <v>1.396133704831463</v>
       </c>
       <c r="AN2" t="n">
-        <v>-0.03758253699723468</v>
+        <v>-0.9745419048186075</v>
       </c>
       <c r="AO2" t="n">
-        <v>0</v>
+        <v>-0.8969318181818178</v>
       </c>
       <c r="AP2" t="inlineStr"/>
       <c r="AQ2" t="n">
-        <v>-4.336363636363615</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>0.1080808080808104</v>
-      </c>
+        <v>-29998559.97474747</v>
+      </c>
+      <c r="AR2" t="inlineStr"/>
       <c r="AS2" t="n">
-        <v>-735555.555555556</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>-226999.0568161553</v>
-      </c>
+        <v>-0.005637626262625872</v>
+      </c>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
       <c r="AV2" t="inlineStr"/>
       <c r="AW2" t="n">
-        <v>0.5850064032338338</v>
+        <v>-3.870460858585858</v>
       </c>
       <c r="AX2" t="n">
-        <v>-64</v>
-      </c>
-      <c r="AY2" t="inlineStr"/>
-      <c r="AZ2" t="n">
-        <v>-74</v>
-      </c>
+        <v>-27025643.90260153</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>-4.758535353535351</v>
+      </c>
+      <c r="AZ2" t="inlineStr"/>
       <c r="BA2" t="n">
-        <v>0</v>
+        <v>-3.488853740214068</v>
       </c>
       <c r="BB2" t="n">
-        <v>-1.044949494949506</v>
+        <v>-2.611155303030358</v>
       </c>
       <c r="BC2" t="n">
-        <v>-0.7782520511199778</v>
+        <v>-5.550613652343515</v>
       </c>
       <c r="BD2" t="n">
-        <v>-1300000</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>-1.223737373737379</v>
-      </c>
+        <v>-5.792218297912967</v>
+      </c>
+      <c r="BE2" t="inlineStr"/>
       <c r="BF2" t="n">
         <v>0</v>
       </c>
@@ -858,23 +888,23 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>CKcVGr7E</t>
+          <t>ChZKNjKb</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45528.58333333334</v>
+        <v>45536.5</v>
       </c>
       <c r="C3" t="n">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="D3" t="n">
         <v>133</v>
       </c>
       <c r="E3" t="n">
-        <v>777</v>
+        <v>194</v>
       </c>
       <c r="F3" t="n">
-        <v>292</v>
+        <v>228</v>
       </c>
       <c r="G3" t="n">
         <v>55</v>
@@ -896,103 +926,123 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>12</v>
+        <v>198</v>
       </c>
       <c r="M3" t="n">
-        <v>83</v>
+        <v>163</v>
       </c>
       <c r="N3" t="n">
+        <v>-4</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q3" t="n">
         <v>-1</v>
       </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>1</v>
-      </c>
       <c r="R3" t="n">
         <v>0</v>
       </c>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
+      <c r="S3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3</v>
+      </c>
+      <c r="U3" t="n">
+        <v>-5</v>
+      </c>
+      <c r="V3" t="n">
+        <v>7</v>
+      </c>
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="inlineStr"/>
-      <c r="AA3" t="inlineStr"/>
-      <c r="AB3" t="inlineStr"/>
-      <c r="AC3" t="inlineStr"/>
-      <c r="AD3" t="inlineStr"/>
-      <c r="AE3" t="inlineStr"/>
-      <c r="AF3" t="inlineStr"/>
-      <c r="AG3" t="inlineStr"/>
-      <c r="AH3" t="inlineStr"/>
-      <c r="AI3" t="inlineStr"/>
-      <c r="AJ3" t="inlineStr"/>
+      <c r="Y3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>-4</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>-2.02</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>-20</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>20</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>-8</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>-11</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>5</v>
+      </c>
       <c r="AK3" t="inlineStr"/>
-      <c r="AL3" t="inlineStr"/>
+      <c r="AL3" t="n">
+        <v>73.30858585858586</v>
+      </c>
       <c r="AM3" t="n">
-        <v>1.042499196709723</v>
+        <v>1.209149727084512</v>
       </c>
       <c r="AN3" t="n">
-        <v>8.086126248670112</v>
+        <v>0</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.4359595959595961</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>2</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AP3" t="inlineStr"/>
       <c r="AQ3" t="n">
-        <v>-2.860707070707036</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>-2.284494949494949</v>
-      </c>
+        <v>1289191.91919192</v>
+      </c>
+      <c r="AR3" t="inlineStr"/>
       <c r="AS3" t="n">
-        <v>11174830.80808081</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>4</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>5804070.36376554</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>4.333333333333332</v>
-      </c>
+        <v>-0.3444444444444485</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AU3" t="inlineStr"/>
+      <c r="AV3" t="inlineStr"/>
       <c r="AW3" t="n">
-        <v>6.991328999136016</v>
+        <v>3.310101010101036</v>
       </c>
       <c r="AX3" t="n">
-        <v>330</v>
+        <v>768801.6879457098</v>
       </c>
       <c r="AY3" t="n">
-        <v>0.6666666666666667</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>327</v>
-      </c>
+        <v>2.984848484848484</v>
+      </c>
+      <c r="AZ3" t="inlineStr"/>
       <c r="BA3" t="n">
-        <v>0.2373376461095758</v>
+        <v>0.9681501871719433</v>
       </c>
       <c r="BB3" t="n">
-        <v>8.855858585858584</v>
+        <v>4.172727272727258</v>
       </c>
       <c r="BC3" t="n">
-        <v>-2.226441888196319</v>
+        <v>3.462799841060686</v>
       </c>
       <c r="BD3" t="n">
-        <v>64475000</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>7.701262626262618</v>
-      </c>
+        <v>1.710279293974935</v>
+      </c>
+      <c r="BE3" t="inlineStr"/>
       <c r="BF3" t="n">
         <v>0</v>
       </c>
@@ -1000,23 +1050,23 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>pSpI7vU0</t>
+          <t>p6XSLUlB</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45528.5</v>
+        <v>45536.5</v>
       </c>
       <c r="C4" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D4" t="n">
         <v>133</v>
       </c>
       <c r="E4" t="n">
-        <v>56</v>
+        <v>826</v>
       </c>
       <c r="F4" t="n">
-        <v>33</v>
+        <v>399</v>
       </c>
       <c r="G4" t="n">
         <v>55</v>
@@ -1038,98 +1088,2004 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>249</v>
+        <v>12</v>
       </c>
       <c r="M4" t="n">
-        <v>226</v>
+        <v>138</v>
       </c>
       <c r="N4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>1</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>-3</v>
+      </c>
+      <c r="T4" t="n">
         <v>2</v>
       </c>
-      <c r="P4" t="n">
-        <v>12</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>3</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="inlineStr"/>
-      <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
-      <c r="AA4" t="inlineStr"/>
-      <c r="AB4" t="inlineStr"/>
-      <c r="AC4" t="inlineStr"/>
-      <c r="AD4" t="inlineStr"/>
-      <c r="AE4" t="inlineStr"/>
-      <c r="AF4" t="inlineStr"/>
-      <c r="AG4" t="inlineStr"/>
-      <c r="AH4" t="inlineStr"/>
-      <c r="AI4" t="inlineStr"/>
-      <c r="AJ4" t="inlineStr"/>
-      <c r="AK4" t="inlineStr"/>
-      <c r="AL4" t="inlineStr"/>
+      <c r="U4" t="n">
+        <v>-8</v>
+      </c>
+      <c r="V4" t="n">
+        <v>4</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>-2.1</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.02000000000000002</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>-19</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>19</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>-7</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>-20</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>76.53522727272727</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>73.82777777777778</v>
+      </c>
       <c r="AM4" t="n">
-        <v>2.745506021508696</v>
+        <v>-0.5794683646438052</v>
       </c>
       <c r="AN4" t="n">
-        <v>-0.2609359293956857</v>
+        <v>-0.3654629272611731</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.5195796347311497</v>
+        <v>-0.4445707070707068</v>
       </c>
       <c r="AP4" t="inlineStr"/>
       <c r="AQ4" t="n">
-        <v>0.07690031629425675</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>2.835700438730743</v>
-      </c>
+        <v>-2899527.567340066</v>
+      </c>
+      <c r="AR4" t="inlineStr"/>
       <c r="AS4" t="n">
-        <v>-4818364.452606875</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>-4273254.37168246</v>
-      </c>
+        <v>0.9752104377104374</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AU4" t="inlineStr"/>
       <c r="AV4" t="inlineStr"/>
       <c r="AW4" t="n">
-        <v>-2.876656024886387</v>
+        <v>-1.189772727272739</v>
       </c>
       <c r="AX4" t="n">
-        <v>-66</v>
-      </c>
-      <c r="AY4" t="inlineStr"/>
-      <c r="AZ4" t="n">
-        <v>-82</v>
-      </c>
+        <v>-5537891.391584374</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>-1.504292929292944</v>
+      </c>
+      <c r="AZ4" t="inlineStr"/>
       <c r="BA4" t="n">
-        <v>0.3070486031153075</v>
+        <v>2.286701868631695</v>
       </c>
       <c r="BB4" t="n">
-        <v>-2.411458014488318</v>
+        <v>1.447306397306335</v>
       </c>
       <c r="BC4" t="n">
-        <v>-2.863873293263964</v>
+        <v>-4.824374058365279</v>
       </c>
       <c r="BD4" t="n">
-        <v>-2200000</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>-0.101061116212648</v>
-      </c>
+        <v>-2.039520292897478</v>
+      </c>
+      <c r="BE4" t="inlineStr"/>
       <c r="BF4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>SU02594U</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>45536.5</v>
+      </c>
+      <c r="C5" t="n">
+        <v>101</v>
+      </c>
+      <c r="D5" t="n">
+        <v>134</v>
+      </c>
+      <c r="E5" t="n">
+        <v>431</v>
+      </c>
+      <c r="F5" t="n">
+        <v>370</v>
+      </c>
+      <c r="G5" t="n">
+        <v>55</v>
+      </c>
+      <c r="H5" t="n">
+        <v>551</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>243</v>
+      </c>
+      <c r="M5" t="n">
+        <v>163</v>
+      </c>
+      <c r="N5" t="n">
+        <v>-4</v>
+      </c>
+      <c r="O5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="P5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="V5" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>-0.24</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>-1.03</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>-15.5</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>75.75</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>70.49191919191918</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>0.7490216735830693</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>-0.280325814536341</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>-0.2959595959595962</v>
+      </c>
+      <c r="AP5" t="inlineStr"/>
+      <c r="AQ5" t="n">
+        <v>-10503898.07162534</v>
+      </c>
+      <c r="AR5" t="inlineStr"/>
+      <c r="AS5" t="n">
+        <v>3.106519742883382</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AU5" t="inlineStr"/>
+      <c r="AV5" t="inlineStr"/>
+      <c r="AW5" t="n">
+        <v>-7.440955004591373</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>-6292488.157695061</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>-6.237832874196499</v>
+      </c>
+      <c r="AZ5" t="inlineStr"/>
+      <c r="BA5" t="n">
+        <v>1.795411669439147</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>0.08558310376491818</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>-8.542343429376231</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>-7.460138407373336</v>
+      </c>
+      <c r="BE5" t="inlineStr"/>
+      <c r="BF5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>IgtCPCkn</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>45536.41666666666</v>
+      </c>
+      <c r="C6" t="n">
+        <v>101</v>
+      </c>
+      <c r="D6" t="n">
+        <v>133</v>
+      </c>
+      <c r="E6" t="n">
+        <v>47</v>
+      </c>
+      <c r="F6" t="n">
+        <v>176</v>
+      </c>
+      <c r="G6" t="n">
+        <v>55</v>
+      </c>
+      <c r="H6" t="n">
+        <v>551</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>165</v>
+      </c>
+      <c r="M6" t="n">
+        <v>83</v>
+      </c>
+      <c r="N6" t="n">
+        <v>10</v>
+      </c>
+      <c r="O6" t="n">
+        <v>2</v>
+      </c>
+      <c r="P6" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>-7</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.265</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.3049999999999999</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>-8.5</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>6</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>75.66666666666667</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>71.42474747474748</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>-3.914877974670286</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>-0.0622412326617694</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0.1258585858585854</v>
+      </c>
+      <c r="AP6" t="inlineStr"/>
+      <c r="AQ6" t="n">
+        <v>1388131.313131314</v>
+      </c>
+      <c r="AR6" t="inlineStr"/>
+      <c r="AS6" t="n">
+        <v>-2.337979797979802</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AU6" t="inlineStr"/>
+      <c r="AV6" t="inlineStr"/>
+      <c r="AW6" t="n">
+        <v>1.956767676767669</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>4263565.605561734</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>-0.3013131313131368</v>
+      </c>
+      <c r="AZ6" t="inlineStr"/>
+      <c r="BA6" t="n">
+        <v>3.448324853776313</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>1.857878787878775</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>0.2461413082865533</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>4.204460088749315</v>
+      </c>
+      <c r="BE6" t="inlineStr"/>
+      <c r="BF6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>tYQyK8JN</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45535.66666666666</v>
+      </c>
+      <c r="C7" t="n">
+        <v>104</v>
+      </c>
+      <c r="D7" t="n">
+        <v>133</v>
+      </c>
+      <c r="E7" t="n">
+        <v>341</v>
+      </c>
+      <c r="F7" t="n">
+        <v>303</v>
+      </c>
+      <c r="G7" t="n">
+        <v>55</v>
+      </c>
+      <c r="H7" t="n">
+        <v>551</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>152</v>
+      </c>
+      <c r="M7" t="n">
+        <v>260</v>
+      </c>
+      <c r="N7" t="n">
+        <v>-23</v>
+      </c>
+      <c r="O7" t="n">
+        <v>-2</v>
+      </c>
+      <c r="P7" t="n">
+        <v>-7</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>-5</v>
+      </c>
+      <c r="T7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U7" t="n">
+        <v>-2</v>
+      </c>
+      <c r="V7" t="n">
+        <v>-3</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>-4</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>-7</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>-1.57</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>-0.8499999999999999</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>-4</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>73.8631313131313</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>74.23819444444445</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>-1.806859406345662</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>-0.2687044160212377</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>-0.615909090909091</v>
+      </c>
+      <c r="AP7" t="inlineStr"/>
+      <c r="AQ7" t="n">
+        <v>-6772159.09090909</v>
+      </c>
+      <c r="AR7" t="inlineStr"/>
+      <c r="AS7" t="n">
+        <v>-3.824368686868688</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AU7" t="inlineStr"/>
+      <c r="AV7" t="inlineStr"/>
+      <c r="AW7" t="n">
+        <v>-0.280934343434339</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>-5950125.747218501</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>-4.433838383838406</v>
+      </c>
+      <c r="AZ7" t="inlineStr"/>
+      <c r="BA7" t="n">
+        <v>-3.0592042669644</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>-0.2345959595959641</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>-4.255491155349247</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>-1.31904421366049</v>
+      </c>
+      <c r="BE7" t="inlineStr"/>
+      <c r="BF7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>6FCg7VZH</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45535.58333333334</v>
+      </c>
+      <c r="C8" t="n">
+        <v>101</v>
+      </c>
+      <c r="D8" t="n">
+        <v>134</v>
+      </c>
+      <c r="E8" t="n">
+        <v>242</v>
+      </c>
+      <c r="F8" t="n">
+        <v>599</v>
+      </c>
+      <c r="G8" t="n">
+        <v>55</v>
+      </c>
+      <c r="H8" t="n">
+        <v>551</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>40</v>
+      </c>
+      <c r="M8" t="n">
+        <v>141</v>
+      </c>
+      <c r="N8" t="n">
+        <v>-2</v>
+      </c>
+      <c r="O8" t="n">
+        <v>-1</v>
+      </c>
+      <c r="P8" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2</v>
+      </c>
+      <c r="V8" t="n">
+        <v>4</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0.6199999999999999</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.075</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>-11</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>9</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>70.77777777777777</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>70.47929292929294</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>-1.419237646017272</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>-0.006846990589531199</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>-0.1699999999999995</v>
+      </c>
+      <c r="AP8" t="inlineStr"/>
+      <c r="AQ8" t="n">
+        <v>828090.9090909082</v>
+      </c>
+      <c r="AR8" t="inlineStr"/>
+      <c r="AS8" t="n">
+        <v>-1.243232323232323</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AU8" t="inlineStr"/>
+      <c r="AV8" t="inlineStr"/>
+      <c r="AW8" t="n">
+        <v>2.277272727272745</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>1167730.224954863</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>0.2455555555555691</v>
+      </c>
+      <c r="AZ8" t="inlineStr"/>
+      <c r="BA8" t="n">
+        <v>0.886513058158414</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>-1.128787878787847</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>0.6794071002723996</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>2.226624702142601</v>
+      </c>
+      <c r="BE8" t="inlineStr"/>
+      <c r="BF8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>bk9o9i55</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45535.5</v>
+      </c>
+      <c r="C9" t="n">
+        <v>101</v>
+      </c>
+      <c r="D9" t="n">
+        <v>134</v>
+      </c>
+      <c r="E9" t="n">
+        <v>211</v>
+      </c>
+      <c r="F9" t="n">
+        <v>362</v>
+      </c>
+      <c r="G9" t="n">
+        <v>55</v>
+      </c>
+      <c r="H9" t="n">
+        <v>551</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>9</v>
+      </c>
+      <c r="M9" t="n">
+        <v>226</v>
+      </c>
+      <c r="N9" t="n">
+        <v>-2</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>4</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
+      </c>
+      <c r="V9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="n">
+        <v>-7</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>-12</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>-4</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>-6</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>77.02020202020202</v>
+      </c>
+      <c r="AL9" t="inlineStr"/>
+      <c r="AM9" t="n">
+        <v>-0.7171100030074342</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>0.1598765432098768</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0.3161616161616163</v>
+      </c>
+      <c r="AP9" t="inlineStr"/>
+      <c r="AQ9" t="n">
+        <v>4489595.959595959</v>
+      </c>
+      <c r="AR9" t="inlineStr"/>
+      <c r="AS9" t="n">
+        <v>1.0949494949495</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AU9" t="inlineStr"/>
+      <c r="AV9" t="inlineStr"/>
+      <c r="AW9" t="n">
+        <v>3.143939393939391</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>2373768.356524767</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>4.529797979797991</v>
+      </c>
+      <c r="AZ9" t="inlineStr"/>
+      <c r="BA9" t="n">
+        <v>-0.8003759298631223</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>0.5989898989898848</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>1.545942708763206</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>0.9270287167723126</v>
+      </c>
+      <c r="BE9" t="inlineStr"/>
+      <c r="BF9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>vmgpBDzg</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45534.65625</v>
+      </c>
+      <c r="C10" t="n">
+        <v>101</v>
+      </c>
+      <c r="D10" t="n">
+        <v>133</v>
+      </c>
+      <c r="E10" t="n">
+        <v>56</v>
+      </c>
+      <c r="F10" t="n">
+        <v>516</v>
+      </c>
+      <c r="G10" t="n">
+        <v>55</v>
+      </c>
+      <c r="H10" t="n">
+        <v>551</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>165</v>
+      </c>
+      <c r="M10" t="n">
+        <v>260</v>
+      </c>
+      <c r="N10" t="n">
+        <v>20</v>
+      </c>
+      <c r="O10" t="n">
+        <v>2</v>
+      </c>
+      <c r="P10" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U10" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>-0.1899999999999999</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.9900000000000002</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>-15</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>-7</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>-10</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>75.7625</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>74.99034090909092</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>1.910070564903538</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>0.3937690670780589</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0.8505611672278337</v>
+      </c>
+      <c r="AP10" t="inlineStr"/>
+      <c r="AQ10" t="n">
+        <v>5522991.021324354</v>
+      </c>
+      <c r="AR10" t="inlineStr"/>
+      <c r="AS10" t="n">
+        <v>4.830976430976431</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AU10" t="inlineStr"/>
+      <c r="AV10" t="inlineStr"/>
+      <c r="AW10" t="n">
+        <v>-0.3393097643097605</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>3463013.933126611</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>5.299747474747463</v>
+      </c>
+      <c r="AZ10" t="inlineStr"/>
+      <c r="BA10" t="n">
+        <v>-3.367554403339824</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>-1.223849607182956</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>4.361801692389022</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>1.687279521939317</v>
+      </c>
+      <c r="BE10" t="inlineStr"/>
+      <c r="BF10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>hhlQ5IbD</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45529.65625</v>
+      </c>
+      <c r="C11" t="n">
+        <v>106</v>
+      </c>
+      <c r="D11" t="n">
+        <v>135</v>
+      </c>
+      <c r="E11" t="n">
+        <v>448</v>
+      </c>
+      <c r="F11" t="n">
+        <v>579</v>
+      </c>
+      <c r="G11" t="n">
+        <v>55</v>
+      </c>
+      <c r="H11" t="n">
+        <v>551</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>9</v>
+      </c>
+      <c r="M11" t="n">
+        <v>204</v>
+      </c>
+      <c r="N11" t="n">
+        <v>4</v>
+      </c>
+      <c r="O11" t="n">
+        <v>3</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U11" t="n">
+        <v>5</v>
+      </c>
+      <c r="V11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>-0.48</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>20</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>-20</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>-14</v>
+      </c>
+      <c r="AK11" t="inlineStr"/>
+      <c r="AL11" t="inlineStr"/>
+      <c r="AM11" t="n">
+        <v>2.40355565582604</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>0.2117100783251458</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>0.4491161616161616</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>-8500000</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>4815095.749158249</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>1.374789562289564</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>-8</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>0.2750000000000057</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>5857518.095843688</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>2.81906565656567</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>-2</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>0.3723647850067096</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>0.8686026936027247</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>5.963795480978135</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>1.144461470570874</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>-11</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>xrJSdNFr</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45529.5</v>
+      </c>
+      <c r="C12" t="n">
+        <v>101</v>
+      </c>
+      <c r="D12" t="n">
+        <v>135</v>
+      </c>
+      <c r="E12" t="n">
+        <v>736</v>
+      </c>
+      <c r="F12" t="n">
+        <v>399</v>
+      </c>
+      <c r="G12" t="n">
+        <v>55</v>
+      </c>
+      <c r="H12" t="n">
+        <v>551</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>286</v>
+      </c>
+      <c r="M12" t="n">
+        <v>138</v>
+      </c>
+      <c r="N12" t="n">
+        <v>-6</v>
+      </c>
+      <c r="O12" t="n">
+        <v>-1</v>
+      </c>
+      <c r="P12" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>-2</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>-4</v>
+      </c>
+      <c r="V12" t="n">
+        <v>3</v>
+      </c>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-8</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>-0.9300000000000002</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>-0.1399999999999999</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>-9</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>8</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>-11</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>-9</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>76.33333333333333</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>0.05433080354648823</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>-0.1954827144533029</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>-0.512934904601571</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>-2900000</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>-6031568.462401793</v>
+      </c>
+      <c r="AR12" t="inlineStr"/>
+      <c r="AS12" t="n">
+        <v>-2.368308080808081</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>-78</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AV12" t="inlineStr"/>
+      <c r="AW12" t="n">
+        <v>-0.7374579124579128</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>-5889981.561285483</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>-4.55845959595959</v>
+      </c>
+      <c r="AZ12" t="inlineStr"/>
+      <c r="BA12" t="n">
+        <v>1.236358543417367</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>1.797923681257004</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>-3.986399203556061</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>-2.444844920874331</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>-72</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>ObHze1pe</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45529.5</v>
+      </c>
+      <c r="C13" t="n">
+        <v>101</v>
+      </c>
+      <c r="D13" t="n">
+        <v>135</v>
+      </c>
+      <c r="E13" t="n">
+        <v>858</v>
+      </c>
+      <c r="F13" t="n">
+        <v>228</v>
+      </c>
+      <c r="G13" t="n">
+        <v>55</v>
+      </c>
+      <c r="H13" t="n">
+        <v>551</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>152</v>
+      </c>
+      <c r="M13" t="n">
+        <v>163</v>
+      </c>
+      <c r="N13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>-2</v>
+      </c>
+      <c r="T13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>-5</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1</v>
+      </c>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="n">
+        <v>-4</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>-1.78</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>-7</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>-10</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>72.40000000000001</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>73.7</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>2.251713805123867</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>0.1731444371043689</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0.5090909090909088</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>4375000</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>2959393.93939394</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>0.5020202020202014</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>-70</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>-4.099999999999994</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>3.9969696969697</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>1245750.796439203</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>4.358585858585855</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>0.3419896709964689</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>1.309090909090912</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>5.031644408605189</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>2.523833450815545</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>-42</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>8nivFMyR</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45529.5</v>
+      </c>
+      <c r="C14" t="n">
+        <v>106</v>
+      </c>
+      <c r="D14" t="n">
+        <v>135</v>
+      </c>
+      <c r="E14" t="n">
+        <v>535</v>
+      </c>
+      <c r="F14" t="n">
+        <v>226</v>
+      </c>
+      <c r="G14" t="n">
+        <v>55</v>
+      </c>
+      <c r="H14" t="n">
+        <v>551</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>128</v>
+      </c>
+      <c r="M14" t="n">
+        <v>141</v>
+      </c>
+      <c r="N14" t="n">
+        <v>7</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>-1</v>
+      </c>
+      <c r="V14" t="n">
+        <v>5</v>
+      </c>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>-0.34</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>7</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>10</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>68.22222222222223</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>72.8</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>0.7150785579084697</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>0.280325814536341</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0.2232323232323234</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>52500000</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>6495757.575757576</v>
+      </c>
+      <c r="AR14" t="inlineStr"/>
+      <c r="AS14" t="n">
+        <v>0.3828282828282816</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>317</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV14" t="inlineStr"/>
+      <c r="AW14" t="n">
+        <v>0.9414141414141426</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>3810824.721828726</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>2.164646464646466</v>
+      </c>
+      <c r="AZ14" t="inlineStr"/>
+      <c r="BA14" t="n">
+        <v>-0.1451525351220369</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>0.07979797979797354</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>3.086613524552121</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>1.187329888731497</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>308</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>OCd990al</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45529.41666666666</v>
+      </c>
+      <c r="C15" t="n">
+        <v>101</v>
+      </c>
+      <c r="D15" t="n">
+        <v>133</v>
+      </c>
+      <c r="E15" t="n">
+        <v>273</v>
+      </c>
+      <c r="F15" t="n">
+        <v>133</v>
+      </c>
+      <c r="G15" t="n">
+        <v>55</v>
+      </c>
+      <c r="H15" t="n">
+        <v>551</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>35</v>
+      </c>
+      <c r="M15" t="n">
+        <v>260</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>-5</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>-2</v>
+      </c>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>-0.2599999999999999</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>-2.32</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>68</v>
+      </c>
+      <c r="AL15" t="inlineStr"/>
+      <c r="AM15" t="n">
+        <v>1.926936026936023</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>0.1972262305595638</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0.08787878787878811</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>17100000</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>6326161.616161616</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>0.01919191919191832</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>228</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>2.373737373737384</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>2540530.503447169</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>2.170707070707067</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>-1.359371492704781</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>-1.631313131313107</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>3.875348725348744</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>2.762109187109175</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>222</v>
+      </c>
+      <c r="BF15" t="n">
         <v>0</v>
       </c>
     </row>

--- a/data/france/p6_deployment/data_preparation/df_tagged.xlsx
+++ b/data/france/p6_deployment/data_preparation/df_tagged.xlsx
@@ -520,94 +520,94 @@
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_last_match_ball_possession</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_ball_possession_against</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_last_match_points</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_points_against</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_expected_goals_(xg)</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_expected_goals_(xg)_against</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goal_attempts</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goal_attempts_against</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goals</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goals_against</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_n_matches_last_days</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_n_matches_last_days_against</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_interceptions</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_interceptions_against</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_n_matches_last_days</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_n_matches_last_days_against</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_shots_on_goal</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_shots_on_goal_against</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_fouls</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_fouls_against</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_shots_on_goal</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_shots_on_goal_against</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goals</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goals_against</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goal_attempts</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goal_attempts_against</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_expected_goals_(xg)</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_expected_goals_(xg)_against</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_ball_possession</t>
-        </is>
-      </c>
-      <c r="AJ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_ball_possession_against</t>
-        </is>
-      </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>mean_last_match_mean_rat_player_start_home_against</t>
@@ -620,97 +620,97 @@
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_age_player_sub</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_start</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_val_player_miss</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_miss</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_age_player_start</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_start</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>dif_n_player_miss</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_pot_player_miss</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_miss</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_sub</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_start</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_start</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_int_rep_player_sub</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_sub</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_start</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_rat_player_miss</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_sub</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_sub</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_int_rep_player_miss</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_start</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_rat_player_miss</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_start</t>
-        </is>
-      </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_sub</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_start</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_pot_player_miss</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_miss</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_sub</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_val_player_miss</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_sub</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_sub</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_n_player_miss</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_miss</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_start</t>
-        </is>
-      </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_sub</t>
-        </is>
-      </c>
-      <c r="BE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_start</t>
         </is>
       </c>
       <c r="BF1" s="1" t="inlineStr">
@@ -781,106 +781,106 @@
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>-3.5</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" t="n">
+        <v>-0.9650000000000001</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0.08499999999999996</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE2" t="n">
         <v>2</v>
       </c>
-      <c r="V2" t="n">
+      <c r="AF2" t="n">
         <v>4</v>
       </c>
-      <c r="W2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y2" t="n">
+      <c r="AG2" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AI2" t="n">
         <v>2</v>
       </c>
-      <c r="Z2" t="n">
+      <c r="AJ2" t="n">
         <v>-1</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>-3.5</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>-3</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>-0.9650000000000001</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>0.08499999999999996</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>-3.5</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>3.5</v>
       </c>
       <c r="AK2" t="n">
         <v>67.3</v>
       </c>
       <c r="AL2" t="inlineStr"/>
       <c r="AM2" t="n">
+        <v>1.396133704831463</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>-0.8969318181818178</v>
+      </c>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="n">
         <v>-0.005637626262625872</v>
       </c>
-      <c r="AN2" t="n">
+      <c r="AR2" t="n">
+        <v>-2.611155303030358</v>
+      </c>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="n">
+        <v>-27025643.90260153</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>-3.870460858585858</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>-4.758535353535351</v>
+      </c>
+      <c r="AY2" t="n">
         <v>-0.9745419048186075</v>
       </c>
-      <c r="AO2" t="inlineStr"/>
-      <c r="AP2" t="n">
+      <c r="AZ2" t="n">
+        <v>-5.792218297912967</v>
+      </c>
+      <c r="BA2" t="n">
         <v>-29998559.97474747</v>
       </c>
-      <c r="AQ2" t="inlineStr"/>
-      <c r="AR2" t="n">
-        <v>-4.758535353535351</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>-3.488853740214068</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>-2.611155303030358</v>
-      </c>
-      <c r="AU2" t="inlineStr"/>
-      <c r="AV2" t="inlineStr"/>
-      <c r="AW2" t="n">
-        <v>-5.792218297912967</v>
-      </c>
-      <c r="AX2" t="inlineStr"/>
-      <c r="AY2" t="n">
-        <v>-5.550613652343515</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>-27025643.90260153</v>
-      </c>
-      <c r="BA2" t="inlineStr"/>
       <c r="BB2" t="inlineStr"/>
       <c r="BC2" t="n">
-        <v>-3.870460858585858</v>
+        <v>-3.488853740214068</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.396133704831463</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>-0.8969318181818178</v>
-      </c>
+        <v>-5.550613652343515</v>
+      </c>
+      <c r="BE2" t="inlineStr"/>
       <c r="BF2" t="n">
         <v>0</v>
       </c>
@@ -947,58 +947,58 @@
         <v>0</v>
       </c>
       <c r="S3" t="n">
+        <v>-16.5</v>
+      </c>
+      <c r="T3" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="U3" t="n">
         <v>-0.5</v>
       </c>
-      <c r="T3" t="n">
+      <c r="V3" t="n">
         <v>1</v>
       </c>
-      <c r="U3" t="n">
+      <c r="W3" t="n">
+        <v>-0.54</v>
+      </c>
+      <c r="X3" t="n">
+        <v>-0.4749999999999999</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="n">
         <v>2</v>
       </c>
-      <c r="V3" t="n">
+      <c r="AF3" t="n">
         <v>4</v>
       </c>
-      <c r="W3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y3" t="n">
+      <c r="AG3" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AH3" t="n">
         <v>0.5</v>
       </c>
-      <c r="Z3" t="n">
+      <c r="AI3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AJ3" t="n">
         <v>-4.5</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>-5</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>-5</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>-0.54</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>-0.4749999999999999</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>-16.5</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>16.5</v>
       </c>
       <c r="AK3" t="n">
         <v>75.75</v>
@@ -1007,48 +1007,48 @@
         <v>70.44444444444446</v>
       </c>
       <c r="AM3" t="n">
+        <v>0.8993496927049485</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>-0.2765656565656569</v>
+      </c>
+      <c r="AO3" t="inlineStr"/>
+      <c r="AP3" t="inlineStr"/>
+      <c r="AQ3" t="n">
         <v>3.138640955004593</v>
       </c>
-      <c r="AN3" t="n">
+      <c r="AR3" t="n">
+        <v>0.1199265381083592</v>
+      </c>
+      <c r="AS3" t="inlineStr"/>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AU3" t="inlineStr"/>
+      <c r="AV3" t="n">
+        <v>-6141073.0806506</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>-7.440045913682283</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>-6.145206611570245</v>
+      </c>
+      <c r="AY3" t="n">
         <v>-0.252293233082707</v>
       </c>
-      <c r="AO3" t="inlineStr"/>
-      <c r="AP3" t="n">
+      <c r="AZ3" t="n">
+        <v>-7.46039936068253</v>
+      </c>
+      <c r="BA3" t="n">
         <v>-10305534.43526171</v>
       </c>
-      <c r="AQ3" t="inlineStr"/>
-      <c r="AR3" t="n">
-        <v>-6.145206611570245</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>1.793276122237813</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>0.1199265381083592</v>
-      </c>
-      <c r="AU3" t="inlineStr"/>
-      <c r="AV3" t="inlineStr"/>
-      <c r="AW3" t="n">
-        <v>-7.46039936068253</v>
-      </c>
-      <c r="AX3" t="inlineStr"/>
-      <c r="AY3" t="n">
-        <v>-8.423309501965107</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>-6141073.0806506</v>
-      </c>
-      <c r="BA3" t="inlineStr"/>
       <c r="BB3" t="inlineStr"/>
       <c r="BC3" t="n">
-        <v>-7.440045913682283</v>
+        <v>1.793276122237813</v>
       </c>
       <c r="BD3" t="n">
-        <v>0.8993496927049485</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>-0.2765656565656569</v>
-      </c>
+        <v>-8.423309501965107</v>
+      </c>
+      <c r="BE3" t="inlineStr"/>
       <c r="BF3" t="n">
         <v>0</v>
       </c>
@@ -1115,106 +1115,106 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>-0.6949999999999998</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0.405</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="n">
         <v>1</v>
       </c>
-      <c r="V4" t="n">
+      <c r="AF4" t="n">
         <v>-4</v>
       </c>
-      <c r="W4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y4" t="n">
+      <c r="AG4" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI4" t="n">
         <v>0.5</v>
       </c>
-      <c r="Z4" t="n">
+      <c r="AJ4" t="n">
         <v>-3</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>3</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>-3.5</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>-0.6949999999999998</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>0.405</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>-20</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>20</v>
       </c>
       <c r="AK4" t="inlineStr"/>
       <c r="AL4" t="n">
         <v>73.30000000000001</v>
       </c>
       <c r="AM4" t="n">
+        <v>1.132432904710576</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO4" t="inlineStr"/>
+      <c r="AP4" t="inlineStr"/>
+      <c r="AQ4" t="n">
         <v>-0.5104407713498667</v>
       </c>
-      <c r="AN4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO4" t="inlineStr"/>
-      <c r="AP4" t="n">
+      <c r="AR4" t="n">
+        <v>4.226639118457314</v>
+      </c>
+      <c r="AS4" t="inlineStr"/>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AU4" t="inlineStr"/>
+      <c r="AV4" t="n">
+        <v>811226.2712172545</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>3.362534435261722</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>2.889012855831041</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>1.773900124908025</v>
+      </c>
+      <c r="BA4" t="n">
         <v>1279902.548209367</v>
       </c>
-      <c r="AQ4" t="inlineStr"/>
-      <c r="AR4" t="n">
-        <v>2.889012855831041</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>0.8026378052119298</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>4.226639118457314</v>
-      </c>
-      <c r="AU4" t="inlineStr"/>
-      <c r="AV4" t="inlineStr"/>
-      <c r="AW4" t="n">
-        <v>1.773900124908025</v>
-      </c>
-      <c r="AX4" t="inlineStr"/>
-      <c r="AY4" t="n">
-        <v>3.620830167855843</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>811226.2712172545</v>
-      </c>
-      <c r="BA4" t="inlineStr"/>
       <c r="BB4" t="inlineStr"/>
       <c r="BC4" t="n">
-        <v>3.362534435261722</v>
+        <v>0.8026378052119298</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.132432904710576</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>0</v>
-      </c>
+        <v>3.620830167855843</v>
+      </c>
+      <c r="BE4" t="inlineStr"/>
       <c r="BF4" t="n">
         <v>0</v>
       </c>
@@ -1281,102 +1281,102 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
+        <v>-15.5</v>
+      </c>
+      <c r="T5" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="U5" t="n">
         <v>-1.5</v>
       </c>
-      <c r="T5" t="n">
+      <c r="V5" t="n">
         <v>1.5</v>
       </c>
-      <c r="U5" t="n">
+      <c r="W5" t="n">
+        <v>-1.69</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0.3899999999999999</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>-15.5</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="n">
         <v>4</v>
       </c>
-      <c r="V5" t="n">
+      <c r="AF5" t="n">
         <v>-5</v>
       </c>
-      <c r="W5" t="inlineStr"/>
-      <c r="X5" t="inlineStr"/>
-      <c r="Y5" t="n">
+      <c r="AG5" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AI5" t="n">
         <v>-10</v>
       </c>
-      <c r="Z5" t="n">
+      <c r="AJ5" t="n">
         <v>3.5</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>-6.5</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>-15.5</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>-1.69</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>0.3899999999999999</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>-15.5</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>15.5</v>
       </c>
       <c r="AK5" t="inlineStr"/>
       <c r="AL5" t="n">
         <v>73.44444444444444</v>
       </c>
       <c r="AM5" t="n">
+        <v>-0.5900616602371009</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>-0.4497359963269052</v>
+      </c>
+      <c r="AO5" t="inlineStr"/>
+      <c r="AP5" t="inlineStr"/>
+      <c r="AQ5" t="n">
         <v>0.9432889501071315</v>
       </c>
-      <c r="AN5" t="n">
+      <c r="AR5" t="n">
+        <v>1.552265074992306</v>
+      </c>
+      <c r="AS5" t="inlineStr"/>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AU5" t="inlineStr"/>
+      <c r="AV5" t="n">
+        <v>-5414020.928713912</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>-1.119111570247938</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>-1.446958218549142</v>
+      </c>
+      <c r="AY5" t="n">
         <v>-0.3725122668105127</v>
       </c>
-      <c r="AO5" t="inlineStr"/>
-      <c r="AP5" t="n">
+      <c r="AZ5" t="n">
+        <v>-1.933914509791705</v>
+      </c>
+      <c r="BA5" t="n">
         <v>-2737151.534282214</v>
       </c>
-      <c r="AQ5" t="inlineStr"/>
-      <c r="AR5" t="n">
-        <v>-1.446958218549142</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>2.34001411194393</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>1.552265074992306</v>
-      </c>
-      <c r="AU5" t="inlineStr"/>
-      <c r="AV5" t="inlineStr"/>
-      <c r="AW5" t="n">
-        <v>-1.933914509791705</v>
-      </c>
-      <c r="AX5" t="inlineStr"/>
-      <c r="AY5" t="n">
-        <v>-4.783938105429328</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>-5414020.928713912</v>
-      </c>
-      <c r="BA5" t="inlineStr"/>
       <c r="BB5" t="inlineStr"/>
       <c r="BC5" t="n">
-        <v>-1.119111570247938</v>
+        <v>2.34001411194393</v>
       </c>
       <c r="BD5" t="n">
-        <v>-0.5900616602371009</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>-0.4497359963269052</v>
-      </c>
+        <v>-4.783938105429328</v>
+      </c>
+      <c r="BE5" t="inlineStr"/>
       <c r="BF5" t="n">
         <v>0</v>
       </c>
@@ -1443,58 +1443,58 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>-11</v>
       </c>
       <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0.09999999999999992</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>-2</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="n">
         <v>-7</v>
       </c>
-      <c r="V6" t="n">
+      <c r="AF6" t="n">
         <v>7</v>
       </c>
-      <c r="W6" t="n">
-        <v>0</v>
-      </c>
-      <c r="X6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y6" t="n">
+      <c r="AG6" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="n">
         <v>-1</v>
       </c>
-      <c r="Z6" t="n">
+      <c r="AJ6" t="n">
         <v>3</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>-3</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>-2.5</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>0.09999999999999992</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>11</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>-11</v>
       </c>
       <c r="AK6" t="n">
         <v>75.66666666666667</v>
@@ -1503,48 +1503,48 @@
         <v>71.15000000000001</v>
       </c>
       <c r="AM6" t="n">
+        <v>-3.758762855221828</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>0.1262626262626256</v>
+      </c>
+      <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="inlineStr"/>
+      <c r="AQ6" t="n">
         <v>-2.265353535353537</v>
       </c>
-      <c r="AN6" t="n">
+      <c r="AR6" t="n">
+        <v>1.615252525252487</v>
+      </c>
+      <c r="AS6" t="inlineStr"/>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AU6" t="inlineStr"/>
+      <c r="AV6" t="n">
+        <v>4223050.754671885</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>1.917171717171712</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>-0.1992929292929233</v>
+      </c>
+      <c r="AY6" t="n">
         <v>-0.05653095528482521</v>
       </c>
-      <c r="AO6" t="inlineStr"/>
-      <c r="AP6" t="n">
+      <c r="AZ6" t="n">
+        <v>4.134947903403798</v>
+      </c>
+      <c r="BA6" t="n">
         <v>1402767.676767677</v>
       </c>
-      <c r="AQ6" t="inlineStr"/>
-      <c r="AR6" t="n">
-        <v>-0.1992929292929233</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>3.114283648068465</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>1.615252525252487</v>
-      </c>
-      <c r="AU6" t="inlineStr"/>
-      <c r="AV6" t="inlineStr"/>
-      <c r="AW6" t="n">
-        <v>4.134947903403798</v>
-      </c>
-      <c r="AX6" t="inlineStr"/>
-      <c r="AY6" t="n">
-        <v>0.2406514894634029</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>4223050.754671885</v>
-      </c>
-      <c r="BA6" t="inlineStr"/>
       <c r="BB6" t="inlineStr"/>
       <c r="BC6" t="n">
-        <v>1.917171717171712</v>
+        <v>3.114283648068465</v>
       </c>
       <c r="BD6" t="n">
-        <v>-3.758762855221828</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>0.1262626262626256</v>
-      </c>
+        <v>0.2406514894634029</v>
+      </c>
+      <c r="BE6" t="inlineStr"/>
       <c r="BF6" t="n">
         <v>0</v>
       </c>
@@ -1611,102 +1611,102 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="U7" t="n">
         <v>-2</v>
       </c>
-      <c r="T7" t="n">
+      <c r="V7" t="n">
         <v>1</v>
       </c>
-      <c r="U7" t="n">
+      <c r="W7" t="n">
+        <v>-1.575</v>
+      </c>
+      <c r="X7" t="n">
+        <v>-0.3799999999999999</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="inlineStr"/>
+      <c r="AE7" t="n">
         <v>-4</v>
       </c>
-      <c r="V7" t="n">
+      <c r="AF7" t="n">
         <v>-7</v>
       </c>
-      <c r="W7" t="inlineStr"/>
-      <c r="X7" t="inlineStr"/>
-      <c r="Y7" t="n">
+      <c r="AG7" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AI7" t="n">
         <v>7.5</v>
       </c>
-      <c r="Z7" t="n">
+      <c r="AJ7" t="n">
         <v>-0.5</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>-4.5</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>4</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>-1.575</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>-0.3799999999999999</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>0.5</v>
       </c>
       <c r="AK7" t="n">
         <v>73.40000000000001</v>
       </c>
       <c r="AL7" t="inlineStr"/>
       <c r="AM7" t="n">
+        <v>-1.710679569676692</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>-0.612979797979798</v>
+      </c>
+      <c r="AO7" t="inlineStr"/>
+      <c r="AP7" t="inlineStr"/>
+      <c r="AQ7" t="n">
         <v>-3.807095959595962</v>
       </c>
-      <c r="AN7" t="n">
+      <c r="AR7" t="n">
+        <v>-0.5165151515151649</v>
+      </c>
+      <c r="AS7" t="inlineStr"/>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AU7" t="inlineStr"/>
+      <c r="AV7" t="n">
+        <v>-6023583.352080092</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>-0.3543686868686819</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>-4.443333333333342</v>
+      </c>
+      <c r="AY7" t="n">
         <v>-0.2687044160212377</v>
       </c>
-      <c r="AO7" t="inlineStr"/>
-      <c r="AP7" t="n">
+      <c r="AZ7" t="n">
+        <v>-1.456300271478142</v>
+      </c>
+      <c r="BA7" t="n">
         <v>-6802058.080808081</v>
       </c>
-      <c r="AQ7" t="inlineStr"/>
-      <c r="AR7" t="n">
-        <v>-4.443333333333342</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>-3.202833973275261</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>-0.5165151515151649</v>
-      </c>
-      <c r="AU7" t="inlineStr"/>
-      <c r="AV7" t="inlineStr"/>
-      <c r="AW7" t="n">
-        <v>-1.456300271478142</v>
-      </c>
-      <c r="AX7" t="inlineStr"/>
-      <c r="AY7" t="n">
-        <v>-4.290863730305162</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>-6023583.352080092</v>
-      </c>
-      <c r="BA7" t="inlineStr"/>
       <c r="BB7" t="inlineStr"/>
       <c r="BC7" t="n">
-        <v>-0.3543686868686819</v>
+        <v>-3.202833973275261</v>
       </c>
       <c r="BD7" t="n">
-        <v>-1.710679569676692</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>-0.612979797979798</v>
-      </c>
+        <v>-4.290863730305162</v>
+      </c>
+      <c r="BE7" t="inlineStr"/>
       <c r="BF7" t="n">
         <v>0</v>
       </c>
@@ -1773,58 +1773,58 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="T8" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="U8" t="n">
         <v>-1.5</v>
       </c>
-      <c r="T8" t="n">
+      <c r="V8" t="n">
         <v>1.5</v>
       </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" t="n">
+      <c r="W8" t="n">
+        <v>-0.07499999999999996</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0.7749999999999999</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="n">
         <v>1</v>
       </c>
-      <c r="W8" t="n">
-        <v>0</v>
-      </c>
-      <c r="X8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y8" t="n">
+      <c r="AG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI8" t="n">
         <v>9.5</v>
       </c>
-      <c r="Z8" t="n">
+      <c r="AJ8" t="n">
         <v>5.5</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>4</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>-0.07499999999999996</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>0.7749999999999999</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>-6.5</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>6.5</v>
       </c>
       <c r="AK8" t="n">
         <v>70.77777777777777</v>
@@ -1833,48 +1833,48 @@
         <v>70.7625</v>
       </c>
       <c r="AM8" t="n">
+        <v>-1.460765399704023</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>-0.1590909090909087</v>
+      </c>
+      <c r="AO8" t="inlineStr"/>
+      <c r="AP8" t="inlineStr"/>
+      <c r="AQ8" t="n">
         <v>-1.008181818181821</v>
       </c>
-      <c r="AN8" t="n">
+      <c r="AR8" t="n">
+        <v>-0.9709090909090321</v>
+      </c>
+      <c r="AS8" t="inlineStr"/>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AU8" t="inlineStr"/>
+      <c r="AV8" t="n">
+        <v>1041966.018884497</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>2.139090909090925</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>0.2472727272727298</v>
+      </c>
+      <c r="AY8" t="n">
         <v>-0.03238968973623702</v>
       </c>
-      <c r="AO8" t="inlineStr"/>
-      <c r="AP8" t="n">
+      <c r="AZ8" t="n">
+        <v>2.223196358912475</v>
+      </c>
+      <c r="BA8" t="n">
         <v>746727.2727272715</v>
       </c>
-      <c r="AQ8" t="inlineStr"/>
-      <c r="AR8" t="n">
-        <v>0.2472727272727298</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>0.6536557482017713</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>-0.9709090909090321</v>
-      </c>
-      <c r="AU8" t="inlineStr"/>
-      <c r="AV8" t="inlineStr"/>
-      <c r="AW8" t="n">
-        <v>2.223196358912475</v>
-      </c>
-      <c r="AX8" t="inlineStr"/>
-      <c r="AY8" t="n">
-        <v>0.5338594199208018</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>1041966.018884497</v>
-      </c>
-      <c r="BA8" t="inlineStr"/>
       <c r="BB8" t="inlineStr"/>
       <c r="BC8" t="n">
-        <v>2.139090909090925</v>
+        <v>0.6536557482017713</v>
       </c>
       <c r="BD8" t="n">
-        <v>-1.460765399704023</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>-0.1590909090909087</v>
-      </c>
+        <v>0.5338594199208018</v>
+      </c>
+      <c r="BE8" t="inlineStr"/>
       <c r="BF8" t="n">
         <v>0</v>
       </c>
@@ -1941,106 +1941,106 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>-1.5</v>
       </c>
       <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>-0.07499999999999996</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0.3700000000000001</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>-4</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="n">
         <v>-7</v>
       </c>
-      <c r="V9" t="n">
+      <c r="AF9" t="n">
         <v>8</v>
       </c>
-      <c r="W9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y9" t="n">
+      <c r="AG9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AI9" t="n">
         <v>-4.5</v>
       </c>
-      <c r="Z9" t="n">
+      <c r="AJ9" t="n">
         <v>-3</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>-4</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>-0.07499999999999996</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>0.3700000000000001</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>-1.5</v>
       </c>
       <c r="AK9" t="n">
         <v>76</v>
       </c>
       <c r="AL9" t="inlineStr"/>
       <c r="AM9" t="n">
+        <v>-0.7593864445545115</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>0.3245454545454549</v>
+      </c>
+      <c r="AO9" t="inlineStr"/>
+      <c r="AP9" t="inlineStr"/>
+      <c r="AQ9" t="n">
         <v>1.224242424242426</v>
       </c>
-      <c r="AN9" t="n">
+      <c r="AR9" t="n">
+        <v>0.3784848484848737</v>
+      </c>
+      <c r="AS9" t="inlineStr"/>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AU9" t="inlineStr"/>
+      <c r="AV9" t="n">
+        <v>2389545.19919856</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>2.990909090909085</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>4.474848484848494</v>
+      </c>
+      <c r="AY9" t="n">
         <v>0.1572222222222224</v>
       </c>
-      <c r="AO9" t="inlineStr"/>
-      <c r="AP9" t="n">
+      <c r="AZ9" t="n">
+        <v>1.057601614072212</v>
+      </c>
+      <c r="BA9" t="n">
         <v>4433575.757575758</v>
       </c>
-      <c r="AQ9" t="inlineStr"/>
-      <c r="AR9" t="n">
-        <v>4.474848484848494</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>-0.5811148655266152</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>0.3784848484848737</v>
-      </c>
-      <c r="AU9" t="inlineStr"/>
-      <c r="AV9" t="inlineStr"/>
-      <c r="AW9" t="n">
-        <v>1.057601614072212</v>
-      </c>
-      <c r="AX9" t="inlineStr"/>
-      <c r="AY9" t="n">
-        <v>1.633245172194734</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>2389545.19919856</v>
-      </c>
-      <c r="BA9" t="inlineStr"/>
       <c r="BB9" t="inlineStr"/>
       <c r="BC9" t="n">
-        <v>2.990909090909085</v>
+        <v>-0.5811148655266152</v>
       </c>
       <c r="BD9" t="n">
-        <v>-0.7593864445545115</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>0.3245454545454549</v>
-      </c>
+        <v>1.633245172194734</v>
+      </c>
+      <c r="BE9" t="inlineStr"/>
       <c r="BF9" t="n">
         <v>0</v>
       </c>
@@ -2107,58 +2107,58 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
+        <v>-16</v>
+      </c>
+      <c r="T10" t="n">
+        <v>16</v>
+      </c>
+      <c r="U10" t="n">
         <v>-2</v>
       </c>
-      <c r="T10" t="n">
+      <c r="V10" t="n">
         <v>2.5</v>
       </c>
-      <c r="U10" t="n">
+      <c r="W10" t="n">
+        <v>-0.02499999999999991</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="n">
         <v>2</v>
       </c>
-      <c r="V10" t="n">
+      <c r="AF10" t="n">
         <v>5</v>
       </c>
-      <c r="W10" t="n">
-        <v>0</v>
-      </c>
-      <c r="X10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y10" t="n">
+      <c r="AG10" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI10" t="n">
         <v>-1.5</v>
       </c>
-      <c r="Z10" t="n">
+      <c r="AJ10" t="n">
         <v>-9.5</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>-3</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>-0.02499999999999991</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>-16</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>16</v>
       </c>
       <c r="AK10" t="n">
         <v>75.7625</v>
@@ -2167,48 +2167,48 @@
         <v>74.675</v>
       </c>
       <c r="AM10" t="n">
+        <v>2.243621600402463</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>0.8685858585858584</v>
+      </c>
+      <c r="AO10" t="inlineStr"/>
+      <c r="AP10" t="inlineStr"/>
+      <c r="AQ10" t="n">
         <v>4.935420875420874</v>
       </c>
-      <c r="AN10" t="n">
+      <c r="AR10" t="n">
+        <v>-1.359158249158241</v>
+      </c>
+      <c r="AS10" t="inlineStr"/>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AU10" t="inlineStr"/>
+      <c r="AV10" t="n">
+        <v>3449593.798976085</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>-0.4200505050504972</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>5.376414141414145</v>
+      </c>
+      <c r="AY10" t="n">
         <v>0.4076945923038937</v>
       </c>
-      <c r="AO10" t="inlineStr"/>
-      <c r="AP10" t="n">
+      <c r="AZ10" t="n">
+        <v>1.282416182091453</v>
+      </c>
+      <c r="BA10" t="n">
         <v>5541781.144781144</v>
       </c>
-      <c r="AQ10" t="inlineStr"/>
-      <c r="AR10" t="n">
-        <v>5.376414141414145</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>-3.456125283783763</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>-1.359158249158241</v>
-      </c>
-      <c r="AU10" t="inlineStr"/>
-      <c r="AV10" t="inlineStr"/>
-      <c r="AW10" t="n">
-        <v>1.282416182091453</v>
-      </c>
-      <c r="AX10" t="inlineStr"/>
-      <c r="AY10" t="n">
-        <v>4.410259403933679</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>3449593.798976085</v>
-      </c>
-      <c r="BA10" t="inlineStr"/>
       <c r="BB10" t="inlineStr"/>
       <c r="BC10" t="n">
-        <v>-0.4200505050504972</v>
+        <v>-3.456125283783763</v>
       </c>
       <c r="BD10" t="n">
-        <v>2.243621600402463</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>0.8685858585858584</v>
-      </c>
+        <v>4.410259403933679</v>
+      </c>
+      <c r="BE10" t="inlineStr"/>
       <c r="BF10" t="n">
         <v>0</v>
       </c>

--- a/data/france/p6_deployment/data_preparation/df_tagged.xlsx
+++ b/data/france/p6_deployment/data_preparation/df_tagged.xlsx
@@ -530,84 +530,84 @@
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_last_match_interceptions</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_interceptions_against</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_fouls</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_fouls_against</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_last_match_points</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_points_against</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_shots_on_goal</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_shots_on_goal_against</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goals</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goals_against</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_n_matches_last_days</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_n_matches_last_days_against</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_expected_goals_(xg)</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_expected_goals_(xg)_against</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_goal_attempts</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_goal_attempts_against</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goals</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goals_against</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_n_matches_last_days</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_n_matches_last_days_against</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_interceptions</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_interceptions_against</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_shots_on_goal</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_shots_on_goal_against</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_fouls</t>
-        </is>
-      </c>
-      <c r="AJ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_fouls_against</t>
-        </is>
-      </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>mean_last_match_mean_rat_player_start_home_against</t>
@@ -620,92 +620,92 @@
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
+          <t>dif_sum_rat_player_miss</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_sub</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_sub</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>dif_n_player_miss</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_start</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_val_player_miss</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_age_player_sub</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_start</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_start</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_sub</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_start</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_int_rep_player_start</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_val_player_miss</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_sub</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_miss</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_start</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_sub</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_hei_player_miss</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_start</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_start</t>
-        </is>
-      </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>dif_n_player_miss</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>dif_sum_pot_player_miss</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_miss</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_sub</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_start</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_start</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_sub</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_sub</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_start</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_rat_player_miss</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_sub</t>
-        </is>
-      </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_sub</t>
         </is>
       </c>
       <c r="BE1" s="1" t="inlineStr">
@@ -787,99 +787,99 @@
         <v>3.5</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W2" t="n">
+        <v>2</v>
+      </c>
+      <c r="X2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG2" t="n">
         <v>-0.9650000000000001</v>
       </c>
-      <c r="X2" t="n">
+      <c r="AH2" t="n">
         <v>0.08499999999999996</v>
       </c>
-      <c r="Y2" t="n">
+      <c r="AI2" t="n">
         <v>-1.5</v>
       </c>
-      <c r="Z2" t="n">
+      <c r="AJ2" t="n">
         <v>-2</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>-3</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>4</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>-3.5</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>-1</v>
       </c>
       <c r="AK2" t="n">
         <v>67.3</v>
       </c>
       <c r="AL2" t="inlineStr"/>
-      <c r="AM2" t="n">
-        <v>1.396133704831463</v>
-      </c>
+      <c r="AM2" t="inlineStr"/>
       <c r="AN2" t="n">
-        <v>-0.8969318181818178</v>
-      </c>
-      <c r="AO2" t="inlineStr"/>
+        <v>-5.398465618441094</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>-0.9785859179854277</v>
+      </c>
       <c r="AP2" t="inlineStr"/>
       <c r="AQ2" t="n">
-        <v>-0.005637626262625872</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>-2.611155303030358</v>
-      </c>
-      <c r="AS2" t="inlineStr"/>
-      <c r="AT2" t="inlineStr"/>
-      <c r="AU2" t="inlineStr"/>
+        <v>0.01890782828282767</v>
+      </c>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="n">
+        <v>1.310448337567149</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>-3.899652777777774</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>-4.793055555555554</v>
+      </c>
       <c r="AV2" t="n">
-        <v>-27025643.90260153</v>
+        <v>-5.576062809476767</v>
       </c>
       <c r="AW2" t="n">
-        <v>-3.870460858585858</v>
+        <v>-30070729.16666666</v>
       </c>
       <c r="AX2" t="n">
-        <v>-4.758535353535351</v>
+        <v>-0.898674242424242</v>
       </c>
       <c r="AY2" t="n">
-        <v>-0.9745419048186075</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>-5.792218297912967</v>
-      </c>
+        <v>-26665743.16964378</v>
+      </c>
+      <c r="AZ2" t="inlineStr"/>
       <c r="BA2" t="n">
-        <v>-29998559.97474747</v>
-      </c>
-      <c r="BB2" t="inlineStr"/>
-      <c r="BC2" t="n">
-        <v>-3.488853740214068</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>-5.550613652343515</v>
-      </c>
+        <v>-2.722064393939434</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>-3.441612703148451</v>
+      </c>
+      <c r="BC2" t="inlineStr"/>
+      <c r="BD2" t="inlineStr"/>
       <c r="BE2" t="inlineStr"/>
       <c r="BF2" t="n">
         <v>0</v>
@@ -888,23 +888,23 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>SU02594U</t>
+          <t>ChZKNjKb</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
         <v>45536.5</v>
       </c>
       <c r="C3" t="n">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="D3" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E3" t="n">
-        <v>431</v>
+        <v>194</v>
       </c>
       <c r="F3" t="n">
-        <v>370</v>
+        <v>228</v>
       </c>
       <c r="G3" t="n">
         <v>55</v>
@@ -926,19 +926,19 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>243</v>
+        <v>272</v>
       </c>
       <c r="M3" t="n">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="N3" t="n">
         <v>-4</v>
       </c>
       <c r="O3" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="Q3" t="n">
         <v>-1</v>
@@ -947,107 +947,105 @@
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>-16.5</v>
+        <v>-20</v>
       </c>
       <c r="T3" t="n">
-        <v>16.5</v>
+        <v>20</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.5</v>
+        <v>1</v>
       </c>
       <c r="V3" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.54</v>
+        <v>0.5</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.4749999999999999</v>
+        <v>-3</v>
       </c>
       <c r="Y3" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>-1</v>
+        <v>-1.5</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AE3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>-0.5</v>
+        <v>-0.6949999999999998</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.5</v>
+        <v>0.405</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.5</v>
+        <v>-3.5</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-4.5</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>75.75</v>
-      </c>
+        <v>7.5</v>
+      </c>
+      <c r="AK3" t="inlineStr"/>
       <c r="AL3" t="n">
-        <v>70.44444444444446</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>0.8993496927049485</v>
-      </c>
+        <v>73.30000000000001</v>
+      </c>
+      <c r="AM3" t="inlineStr"/>
       <c r="AN3" t="n">
-        <v>-0.2765656565656569</v>
-      </c>
-      <c r="AO3" t="inlineStr"/>
+        <v>3.620830167855843</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>0</v>
+      </c>
       <c r="AP3" t="inlineStr"/>
       <c r="AQ3" t="n">
-        <v>3.138640955004593</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>0.1199265381083592</v>
-      </c>
-      <c r="AS3" t="inlineStr"/>
-      <c r="AT3" t="inlineStr"/>
-      <c r="AU3" t="inlineStr"/>
+        <v>-0.5104407713498667</v>
+      </c>
+      <c r="AR3" t="inlineStr"/>
+      <c r="AS3" t="n">
+        <v>1.132432904710576</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>3.362534435261722</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>2.889012855831041</v>
+      </c>
       <c r="AV3" t="n">
-        <v>-6141073.0806506</v>
+        <v>1.773900124908025</v>
       </c>
       <c r="AW3" t="n">
-        <v>-7.440045913682283</v>
+        <v>1279902.548209367</v>
       </c>
       <c r="AX3" t="n">
-        <v>-6.145206611570245</v>
+        <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>-0.252293233082707</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>-7.46039936068253</v>
-      </c>
+        <v>811226.2712172545</v>
+      </c>
+      <c r="AZ3" t="inlineStr"/>
       <c r="BA3" t="n">
-        <v>-10305534.43526171</v>
-      </c>
-      <c r="BB3" t="inlineStr"/>
-      <c r="BC3" t="n">
-        <v>1.793276122237813</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>-8.423309501965107</v>
-      </c>
+        <v>4.226639118457314</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>0.8026378052119298</v>
+      </c>
+      <c r="BC3" t="inlineStr"/>
+      <c r="BD3" t="inlineStr"/>
       <c r="BE3" t="inlineStr"/>
       <c r="BF3" t="n">
         <v>0</v>
@@ -1056,7 +1054,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>ChZKNjKb</t>
+          <t>p6XSLUlB</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -1069,10 +1067,10 @@
         <v>133</v>
       </c>
       <c r="E4" t="n">
-        <v>194</v>
+        <v>826</v>
       </c>
       <c r="F4" t="n">
-        <v>228</v>
+        <v>399</v>
       </c>
       <c r="G4" t="n">
         <v>55</v>
@@ -1094,13 +1092,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>272</v>
+        <v>314</v>
       </c>
       <c r="M4" t="n">
-        <v>109</v>
+        <v>211</v>
       </c>
       <c r="N4" t="n">
-        <v>-4</v>
+        <v>4</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1109,111 +1107,111 @@
         <v>4</v>
       </c>
       <c r="Q4" t="n">
+        <v>1</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>-13</v>
+      </c>
+      <c r="T4" t="n">
+        <v>13</v>
+      </c>
+      <c r="U4" t="n">
+        <v>4</v>
+      </c>
+      <c r="V4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="W4" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="X4" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y4" t="n">
         <v>-1</v>
       </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="n">
-        <v>-20</v>
-      </c>
-      <c r="T4" t="n">
-        <v>20</v>
-      </c>
-      <c r="U4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W4" t="n">
-        <v>-0.6949999999999998</v>
-      </c>
-      <c r="X4" t="n">
-        <v>0.405</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>-3.5</v>
-      </c>
       <c r="Z4" t="n">
-        <v>7.5</v>
+        <v>0.5</v>
       </c>
       <c r="AA4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD4" t="n">
         <v>0.5</v>
       </c>
-      <c r="AB4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>0</v>
-      </c>
       <c r="AE4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>-1.5</v>
+        <v>-1.28</v>
       </c>
       <c r="AH4" t="n">
-        <v>3</v>
+        <v>0.8900000000000001</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.5</v>
+        <v>-10.5</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-3</v>
+        <v>6</v>
       </c>
       <c r="AK4" t="inlineStr"/>
       <c r="AL4" t="n">
-        <v>73.30000000000001</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>1.132432904710576</v>
-      </c>
+        <v>73.44444444444444</v>
+      </c>
+      <c r="AM4" t="inlineStr"/>
       <c r="AN4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO4" t="inlineStr"/>
+        <v>-4.899313581155695</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>-0.3715450339134552</v>
+      </c>
       <c r="AP4" t="inlineStr"/>
       <c r="AQ4" t="n">
-        <v>-0.5104407713498667</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>4.226639118457314</v>
-      </c>
-      <c r="AS4" t="inlineStr"/>
-      <c r="AT4" t="inlineStr"/>
-      <c r="AU4" t="inlineStr"/>
+        <v>0.9432889501071315</v>
+      </c>
+      <c r="AR4" t="inlineStr"/>
+      <c r="AS4" t="n">
+        <v>-0.7204621986200976</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>-1.119111570247938</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>-1.446958218549142</v>
+      </c>
       <c r="AV4" t="n">
-        <v>811226.2712172545</v>
+        <v>-1.889462175251651</v>
       </c>
       <c r="AW4" t="n">
-        <v>3.362534435261722</v>
+        <v>-2737151.534282214</v>
       </c>
       <c r="AX4" t="n">
-        <v>2.889012855831041</v>
+        <v>-0.4497359963269052</v>
       </c>
       <c r="AY4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>1.773900124908025</v>
-      </c>
+        <v>-5444322.632046318</v>
+      </c>
+      <c r="AZ4" t="inlineStr"/>
       <c r="BA4" t="n">
-        <v>1279902.548209367</v>
-      </c>
-      <c r="BB4" t="inlineStr"/>
-      <c r="BC4" t="n">
-        <v>0.8026378052119298</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>3.620830167855843</v>
-      </c>
+        <v>1.552265074992306</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>2.396033790770616</v>
+      </c>
+      <c r="BC4" t="inlineStr"/>
+      <c r="BD4" t="inlineStr"/>
       <c r="BE4" t="inlineStr"/>
       <c r="BF4" t="n">
         <v>0</v>
@@ -1222,23 +1220,23 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>p6XSLUlB</t>
+          <t>SU02594U</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
         <v>45536.5</v>
       </c>
       <c r="C5" t="n">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="D5" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E5" t="n">
-        <v>826</v>
+        <v>431</v>
       </c>
       <c r="F5" t="n">
-        <v>399</v>
+        <v>370</v>
       </c>
       <c r="G5" t="n">
         <v>55</v>
@@ -1260,122 +1258,128 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>12</v>
+        <v>243</v>
       </c>
       <c r="M5" t="n">
-        <v>211</v>
+        <v>127</v>
       </c>
       <c r="N5" t="n">
+        <v>-4</v>
+      </c>
+      <c r="O5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="P5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>-16.5</v>
+      </c>
+      <c r="T5" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2</v>
+      </c>
+      <c r="V5" t="n">
         <v>4</v>
       </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q5" t="n">
+      <c r="W5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="X5" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="Z5" t="n">
         <v>1</v>
       </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>-15.5</v>
-      </c>
-      <c r="T5" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="U5" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="W5" t="n">
-        <v>-1.69</v>
-      </c>
-      <c r="X5" t="n">
-        <v>0.3899999999999999</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>-15.5</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>8.5</v>
-      </c>
       <c r="AA5" t="n">
-        <v>-2</v>
+        <v>-0.5</v>
       </c>
       <c r="AB5" t="n">
         <v>0.5</v>
       </c>
-      <c r="AC5" t="inlineStr"/>
-      <c r="AD5" t="inlineStr"/>
+      <c r="AC5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
       <c r="AE5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>-0.54</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>-0.4749999999999999</v>
+      </c>
+      <c r="AI5" t="n">
         <v>-5</v>
       </c>
-      <c r="AG5" t="n">
-        <v>-6.5</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>-10</v>
-      </c>
       <c r="AJ5" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AK5" t="inlineStr"/>
+        <v>-5</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>75.75</v>
+      </c>
       <c r="AL5" t="n">
-        <v>73.44444444444444</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>-0.5900616602371009</v>
-      </c>
+        <v>70.44444444444446</v>
+      </c>
+      <c r="AM5" t="inlineStr"/>
       <c r="AN5" t="n">
-        <v>-0.4497359963269052</v>
-      </c>
-      <c r="AO5" t="inlineStr"/>
+        <v>-8.246009917491619</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>-0.252293233082707</v>
+      </c>
       <c r="AP5" t="inlineStr"/>
       <c r="AQ5" t="n">
-        <v>0.9432889501071315</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>1.552265074992306</v>
-      </c>
-      <c r="AS5" t="inlineStr"/>
-      <c r="AT5" t="inlineStr"/>
-      <c r="AU5" t="inlineStr"/>
+        <v>3.019797979797985</v>
+      </c>
+      <c r="AR5" t="inlineStr"/>
+      <c r="AS5" t="n">
+        <v>1.022496545851805</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>-7.439797979797987</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>-6.285454545454542</v>
+      </c>
       <c r="AV5" t="n">
-        <v>-5414020.928713912</v>
+        <v>-7.4462574880624</v>
       </c>
       <c r="AW5" t="n">
-        <v>-1.119111570247938</v>
+        <v>-10323848.48484848</v>
       </c>
       <c r="AX5" t="n">
-        <v>-1.446958218549142</v>
+        <v>-0.2756565656565659</v>
       </c>
       <c r="AY5" t="n">
-        <v>-0.3725122668105127</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>-1.933914509791705</v>
-      </c>
+        <v>-6117448.48604231</v>
+      </c>
+      <c r="AZ5" t="inlineStr"/>
       <c r="BA5" t="n">
-        <v>-2737151.534282214</v>
-      </c>
-      <c r="BB5" t="inlineStr"/>
-      <c r="BC5" t="n">
-        <v>2.34001411194393</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>-4.783938105429328</v>
-      </c>
+        <v>0.03959595959597095</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>1.976931741980394</v>
+      </c>
+      <c r="BC5" t="inlineStr"/>
+      <c r="BD5" t="inlineStr"/>
       <c r="BE5" t="inlineStr"/>
       <c r="BF5" t="n">
         <v>0</v>
@@ -1449,52 +1453,52 @@
         <v>-11</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X6" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="n">
         <v>0.75</v>
       </c>
-      <c r="X6" t="n">
+      <c r="AH6" t="n">
         <v>0.09999999999999992</v>
       </c>
-      <c r="Y6" t="n">
+      <c r="AI6" t="n">
         <v>-2</v>
       </c>
-      <c r="Z6" t="n">
+      <c r="AJ6" t="n">
         <v>-2.5</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>-7</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>7</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>-3</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>3</v>
       </c>
       <c r="AK6" t="n">
         <v>75.66666666666667</v>
@@ -1502,48 +1506,48 @@
       <c r="AL6" t="n">
         <v>71.15000000000001</v>
       </c>
-      <c r="AM6" t="n">
-        <v>-3.758762855221828</v>
-      </c>
+      <c r="AM6" t="inlineStr"/>
       <c r="AN6" t="n">
-        <v>0.1262626262626256</v>
-      </c>
-      <c r="AO6" t="inlineStr"/>
+        <v>0.4062794327371222</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>-0.02114550587202801</v>
+      </c>
       <c r="AP6" t="inlineStr"/>
       <c r="AQ6" t="n">
-        <v>-2.265353535353537</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>1.615252525252487</v>
-      </c>
-      <c r="AS6" t="inlineStr"/>
-      <c r="AT6" t="inlineStr"/>
-      <c r="AU6" t="inlineStr"/>
+        <v>-2.355443322109991</v>
+      </c>
+      <c r="AR6" t="inlineStr"/>
+      <c r="AS6" t="n">
+        <v>-3.579180950246482</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>1.918069584736259</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>-0.2315375982042411</v>
+      </c>
       <c r="AV6" t="n">
-        <v>4223050.754671885</v>
+        <v>4.177719892670879</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.917171717171712</v>
+        <v>1293984.287317621</v>
       </c>
       <c r="AX6" t="n">
-        <v>-0.1992929292929233</v>
+        <v>0.109988776655443</v>
       </c>
       <c r="AY6" t="n">
-        <v>-0.05653095528482521</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>4.134947903403798</v>
-      </c>
+        <v>4561028.616302093</v>
+      </c>
+      <c r="AZ6" t="inlineStr"/>
       <c r="BA6" t="n">
-        <v>1402767.676767677</v>
-      </c>
-      <c r="BB6" t="inlineStr"/>
-      <c r="BC6" t="n">
-        <v>3.114283648068465</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>0.2406514894634029</v>
-      </c>
+        <v>1.673512906846213</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>3.224204053409409</v>
+      </c>
+      <c r="BC6" t="inlineStr"/>
+      <c r="BD6" t="inlineStr"/>
       <c r="BE6" t="inlineStr"/>
       <c r="BF6" t="n">
         <v>0</v>
@@ -1559,7 +1563,7 @@
         <v>45535.66666666666</v>
       </c>
       <c r="C7" t="n">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D7" t="n">
         <v>133</v>
@@ -1593,7 +1597,7 @@
         <v>193</v>
       </c>
       <c r="M7" t="n">
-        <v>260</v>
+        <v>10</v>
       </c>
       <c r="N7" t="n">
         <v>-23</v>
@@ -1611,101 +1615,105 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.5</v>
+        <v>-9</v>
       </c>
       <c r="T7" t="n">
+        <v>9</v>
+      </c>
+      <c r="U7" t="n">
+        <v>-4</v>
+      </c>
+      <c r="V7" t="n">
+        <v>-7</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="X7" t="n">
+        <v>-2</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Z7" t="n">
         <v>0.5</v>
-      </c>
-      <c r="U7" t="n">
-        <v>-2</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1</v>
-      </c>
-      <c r="W7" t="n">
-        <v>-1.575</v>
-      </c>
-      <c r="X7" t="n">
-        <v>-0.3799999999999999</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>1</v>
       </c>
       <c r="AA7" t="n">
         <v>-4.5</v>
       </c>
       <c r="AB7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>-1.615</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>-0.23</v>
+      </c>
+      <c r="AI7" t="n">
         <v>-0.5</v>
       </c>
-      <c r="AC7" t="inlineStr"/>
-      <c r="AD7" t="inlineStr"/>
-      <c r="AE7" t="n">
-        <v>-4</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>-7</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>7.5</v>
-      </c>
       <c r="AJ7" t="n">
-        <v>-0.5</v>
+        <v>-1.5</v>
       </c>
       <c r="AK7" t="n">
         <v>73.40000000000001</v>
       </c>
       <c r="AL7" t="inlineStr"/>
-      <c r="AM7" t="n">
-        <v>-1.710679569676692</v>
-      </c>
+      <c r="AM7" t="inlineStr"/>
       <c r="AN7" t="n">
-        <v>-0.612979797979798</v>
-      </c>
-      <c r="AO7" t="inlineStr"/>
+        <v>-4.212442039814334</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>-0.3018339744191141</v>
+      </c>
       <c r="AP7" t="inlineStr"/>
       <c r="AQ7" t="n">
         <v>-3.807095959595962</v>
       </c>
-      <c r="AR7" t="n">
+      <c r="AR7" t="inlineStr"/>
+      <c r="AS7" t="n">
+        <v>-1.599923465711093</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>-0.3543686868686819</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>-4.443333333333342</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>-1.479639792294435</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>-6802058.080808081</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>-0.612979797979798</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>-6200863.172496652</v>
+      </c>
+      <c r="AZ7" t="inlineStr"/>
+      <c r="BA7" t="n">
         <v>-0.5165151515151649</v>
       </c>
-      <c r="AS7" t="inlineStr"/>
-      <c r="AT7" t="inlineStr"/>
-      <c r="AU7" t="inlineStr"/>
-      <c r="AV7" t="n">
-        <v>-6023583.352080092</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>-0.3543686868686819</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>-4.443333333333342</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>-0.2687044160212377</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>-1.456300271478142</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>-6802058.080808081</v>
-      </c>
-      <c r="BB7" t="inlineStr"/>
-      <c r="BC7" t="n">
-        <v>-3.202833973275261</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>-4.290863730305162</v>
-      </c>
+      <c r="BB7" t="n">
+        <v>-2.628283840267954</v>
+      </c>
+      <c r="BC7" t="inlineStr"/>
+      <c r="BD7" t="inlineStr"/>
       <c r="BE7" t="inlineStr"/>
       <c r="BF7" t="n">
         <v>0</v>
@@ -1779,52 +1787,52 @@
         <v>6.5</v>
       </c>
       <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1</v>
+      </c>
+      <c r="W8" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="X8" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="Y8" t="n">
         <v>-1.5</v>
       </c>
-      <c r="V8" t="n">
+      <c r="Z8" t="n">
         <v>1.5</v>
       </c>
-      <c r="W8" t="n">
+      <c r="AA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="n">
         <v>-0.07499999999999996</v>
       </c>
-      <c r="X8" t="n">
+      <c r="AH8" t="n">
         <v>0.7749999999999999</v>
       </c>
-      <c r="Y8" t="n">
+      <c r="AI8" t="n">
         <v>-0.5</v>
       </c>
-      <c r="Z8" t="n">
+      <c r="AJ8" t="n">
         <v>7.5</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>4</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>5.5</v>
       </c>
       <c r="AK8" t="n">
         <v>70.77777777777777</v>
@@ -1832,48 +1840,48 @@
       <c r="AL8" t="n">
         <v>70.7625</v>
       </c>
-      <c r="AM8" t="n">
-        <v>-1.460765399704023</v>
-      </c>
+      <c r="AM8" t="inlineStr"/>
       <c r="AN8" t="n">
-        <v>-0.1590909090909087</v>
-      </c>
-      <c r="AO8" t="inlineStr"/>
+        <v>0.5338594199208018</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>-0.03238968973623702</v>
+      </c>
       <c r="AP8" t="inlineStr"/>
       <c r="AQ8" t="n">
         <v>-1.008181818181821</v>
       </c>
-      <c r="AR8" t="n">
+      <c r="AR8" t="inlineStr"/>
+      <c r="AS8" t="n">
+        <v>-1.460765399704023</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>2.139090909090925</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>0.2472727272727298</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>2.223196358912475</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>746727.2727272715</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>-0.1590909090909087</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>1041966.018884497</v>
+      </c>
+      <c r="AZ8" t="inlineStr"/>
+      <c r="BA8" t="n">
         <v>-0.9709090909090321</v>
       </c>
-      <c r="AS8" t="inlineStr"/>
-      <c r="AT8" t="inlineStr"/>
-      <c r="AU8" t="inlineStr"/>
-      <c r="AV8" t="n">
-        <v>1041966.018884497</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>2.139090909090925</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>0.2472727272727298</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>-0.03238968973623702</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>2.223196358912475</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>746727.2727272715</v>
-      </c>
-      <c r="BB8" t="inlineStr"/>
-      <c r="BC8" t="n">
+      <c r="BB8" t="n">
         <v>0.6536557482017713</v>
       </c>
-      <c r="BD8" t="n">
-        <v>0.5338594199208018</v>
-      </c>
+      <c r="BC8" t="inlineStr"/>
+      <c r="BD8" t="inlineStr"/>
       <c r="BE8" t="inlineStr"/>
       <c r="BF8" t="n">
         <v>0</v>
@@ -1947,99 +1955,99 @@
         <v>-1.5</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W9" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="X9" t="n">
+        <v>-3</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="n">
         <v>-0.07499999999999996</v>
       </c>
-      <c r="X9" t="n">
+      <c r="AH9" t="n">
         <v>0.3700000000000001</v>
       </c>
-      <c r="Y9" t="n">
+      <c r="AI9" t="n">
         <v>-4</v>
       </c>
-      <c r="Z9" t="n">
+      <c r="AJ9" t="n">
         <v>1</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>-7</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>8</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>-4.5</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>-3</v>
       </c>
       <c r="AK9" t="n">
         <v>76</v>
       </c>
       <c r="AL9" t="inlineStr"/>
-      <c r="AM9" t="n">
-        <v>-0.7593864445545115</v>
-      </c>
+      <c r="AM9" t="inlineStr"/>
       <c r="AN9" t="n">
-        <v>0.3245454545454549</v>
-      </c>
-      <c r="AO9" t="inlineStr"/>
+        <v>1.677859880190184</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0.1572222222222224</v>
+      </c>
       <c r="AP9" t="inlineStr"/>
       <c r="AQ9" t="n">
-        <v>1.224242424242426</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>0.3784848484848737</v>
-      </c>
-      <c r="AS9" t="inlineStr"/>
-      <c r="AT9" t="inlineStr"/>
-      <c r="AU9" t="inlineStr"/>
+        <v>1.195867768595043</v>
+      </c>
+      <c r="AR9" t="inlineStr"/>
+      <c r="AS9" t="n">
+        <v>-0.7426420562845877</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>3.037603305785126</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>4.482148760330574</v>
+      </c>
       <c r="AV9" t="n">
-        <v>2389545.19919856</v>
+        <v>1.048833484263355</v>
       </c>
       <c r="AW9" t="n">
-        <v>2.990909090909085</v>
+        <v>4440793.388429752</v>
       </c>
       <c r="AX9" t="n">
-        <v>4.474848484848494</v>
+        <v>0.3245454545454549</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.1572222222222224</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>1.057601614072212</v>
-      </c>
+        <v>2394476.636987949</v>
+      </c>
+      <c r="AZ9" t="inlineStr"/>
       <c r="BA9" t="n">
-        <v>4433575.757575758</v>
-      </c>
-      <c r="BB9" t="inlineStr"/>
-      <c r="BC9" t="n">
-        <v>-0.5811148655266152</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>1.633245172194734</v>
-      </c>
+        <v>0.3688429752066327</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>-0.4433556915683425</v>
+      </c>
+      <c r="BC9" t="inlineStr"/>
+      <c r="BD9" t="inlineStr"/>
       <c r="BE9" t="inlineStr"/>
       <c r="BF9" t="n">
         <v>0</v>
@@ -2113,52 +2121,52 @@
         <v>16</v>
       </c>
       <c r="U10" t="n">
+        <v>2</v>
+      </c>
+      <c r="V10" t="n">
+        <v>5</v>
+      </c>
+      <c r="W10" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="X10" t="n">
+        <v>-9.5</v>
+      </c>
+      <c r="Y10" t="n">
         <v>-2</v>
       </c>
-      <c r="V10" t="n">
+      <c r="Z10" t="n">
         <v>2.5</v>
       </c>
-      <c r="W10" t="n">
+      <c r="AA10" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="n">
         <v>-0.02499999999999991</v>
       </c>
-      <c r="X10" t="n">
+      <c r="AH10" t="n">
         <v>1.07</v>
       </c>
-      <c r="Y10" t="n">
+      <c r="AI10" t="n">
         <v>-1</v>
       </c>
-      <c r="Z10" t="n">
+      <c r="AJ10" t="n">
         <v>8.5</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>5</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>-3</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>-9.5</v>
       </c>
       <c r="AK10" t="n">
         <v>75.7625</v>
@@ -2166,48 +2174,48 @@
       <c r="AL10" t="n">
         <v>74.675</v>
       </c>
-      <c r="AM10" t="n">
-        <v>2.243621600402463</v>
-      </c>
+      <c r="AM10" t="inlineStr"/>
       <c r="AN10" t="n">
-        <v>0.8685858585858584</v>
-      </c>
-      <c r="AO10" t="inlineStr"/>
+        <v>4.410259403933679</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0.4076945923038937</v>
+      </c>
       <c r="AP10" t="inlineStr"/>
       <c r="AQ10" t="n">
         <v>4.935420875420874</v>
       </c>
-      <c r="AR10" t="n">
+      <c r="AR10" t="inlineStr"/>
+      <c r="AS10" t="n">
+        <v>2.243621600402463</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>-0.4200505050504972</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>5.376414141414145</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>1.282416182091453</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>5541781.144781144</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>0.8685858585858584</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>3449593.798976085</v>
+      </c>
+      <c r="AZ10" t="inlineStr"/>
+      <c r="BA10" t="n">
         <v>-1.359158249158241</v>
       </c>
-      <c r="AS10" t="inlineStr"/>
-      <c r="AT10" t="inlineStr"/>
-      <c r="AU10" t="inlineStr"/>
-      <c r="AV10" t="n">
-        <v>3449593.798976085</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>-0.4200505050504972</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>5.376414141414145</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>0.4076945923038937</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>1.282416182091453</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>5541781.144781144</v>
-      </c>
-      <c r="BB10" t="inlineStr"/>
-      <c r="BC10" t="n">
+      <c r="BB10" t="n">
         <v>-3.456125283783763</v>
       </c>
-      <c r="BD10" t="n">
-        <v>4.410259403933679</v>
-      </c>
+      <c r="BC10" t="inlineStr"/>
+      <c r="BD10" t="inlineStr"/>
       <c r="BE10" t="inlineStr"/>
       <c r="BF10" t="n">
         <v>0</v>

--- a/data/france/p6_deployment/data_preparation/df_tagged.xlsx
+++ b/data/france/p6_deployment/data_preparation/df_tagged.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BF10"/>
+  <dimension ref="A1:BF9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -520,94 +520,94 @@
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_last_match_goals</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goals_against</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_last_match_ball_possession</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_ball_possession_against</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_n_matches_last_days</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_n_matches_last_days_against</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_interceptions</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_interceptions_against</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_points</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_points_against</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_expected_goals_(xg)</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_expected_goals_(xg)_against</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goal_attempts</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goal_attempts_against</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_shots_on_goal</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_shots_on_goal_against</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_fouls</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_fouls_against</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_points</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_points_against</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_shots_on_goal</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_shots_on_goal_against</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goals</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goals_against</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_n_matches_last_days</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_n_matches_last_days_against</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_expected_goals_(xg)</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_expected_goals_(xg)_against</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goal_attempts</t>
-        </is>
-      </c>
-      <c r="AJ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goal_attempts_against</t>
-        </is>
-      </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>mean_last_match_mean_rat_player_start_home_against</t>
@@ -620,97 +620,97 @@
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_rat_player_sub</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_miss</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_start</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_sub</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_start</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_start</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_sub</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_start</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_miss</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_sub</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_sub</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_pot_player_miss</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_start</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
           <t>dif_sum_rat_player_miss</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_sub</t>
-        </is>
-      </c>
-      <c r="AO1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_sub</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_start</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_sub</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_miss</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>dif_n_player_miss</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_start</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>dif_sum_val_player_miss</t>
-        </is>
-      </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_sub</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_start</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_start</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_sub</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_start</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_start</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_sub</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_miss</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_start</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_sub</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_miss</t>
-        </is>
-      </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_pot_player_miss</t>
-        </is>
-      </c>
-      <c r="BE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_miss</t>
         </is>
       </c>
       <c r="BF1" s="1" t="inlineStr">
@@ -729,7 +729,7 @@
         <v>45536.65625</v>
       </c>
       <c r="C2" t="n">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="D2" t="n">
         <v>133</v>
@@ -781,106 +781,120 @@
         <v>0</v>
       </c>
       <c r="S2" t="n">
+        <v>-3</v>
+      </c>
+      <c r="T2" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="U2" t="n">
         <v>-3.5</v>
       </c>
-      <c r="T2" t="n">
+      <c r="V2" t="n">
         <v>3.5</v>
       </c>
-      <c r="U2" t="n">
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" t="n">
         <v>2</v>
       </c>
-      <c r="V2" t="n">
+      <c r="Z2" t="n">
         <v>4</v>
       </c>
-      <c r="W2" t="n">
+      <c r="AA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>-0.9650000000000001</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0.08499999999999996</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AI2" t="n">
         <v>2</v>
       </c>
-      <c r="X2" t="n">
+      <c r="AJ2" t="n">
         <v>-1</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>-3.5</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>-3</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>-0.9650000000000001</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>0.08499999999999996</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>-2</v>
       </c>
       <c r="AK2" t="n">
         <v>67.3</v>
       </c>
       <c r="AL2" t="inlineStr"/>
-      <c r="AM2" t="inlineStr"/>
+      <c r="AM2" t="n">
+        <v>-5.417162004184704</v>
+      </c>
       <c r="AN2" t="n">
-        <v>-5.398465618441094</v>
+        <v>-9.099999999999994</v>
       </c>
       <c r="AO2" t="n">
-        <v>-0.9785859179854277</v>
-      </c>
-      <c r="AP2" t="inlineStr"/>
+        <v>-3.739718614718612</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>-5.682080002423135</v>
+      </c>
       <c r="AQ2" t="n">
-        <v>0.01890782828282767</v>
-      </c>
-      <c r="AR2" t="inlineStr"/>
+        <v>-4.545346320346326</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>-0.85573593073593</v>
+      </c>
       <c r="AS2" t="n">
-        <v>1.310448337567149</v>
+        <v>-0.9859498206376431</v>
       </c>
       <c r="AT2" t="n">
-        <v>-3.899652777777774</v>
+        <v>0.01251803751803493</v>
       </c>
       <c r="AU2" t="n">
-        <v>-4.793055555555554</v>
+        <v>1</v>
       </c>
       <c r="AV2" t="n">
-        <v>-5.576062809476767</v>
+        <v>1.46851475407977</v>
       </c>
       <c r="AW2" t="n">
-        <v>-30070729.16666666</v>
+        <v>-3.420809605961836</v>
       </c>
       <c r="AX2" t="n">
-        <v>-0.898674242424242</v>
+        <v>223</v>
       </c>
       <c r="AY2" t="n">
-        <v>-26665743.16964378</v>
-      </c>
-      <c r="AZ2" t="inlineStr"/>
+        <v>-28243968.25396825</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>218</v>
+      </c>
       <c r="BA2" t="n">
-        <v>-2.722064393939434</v>
+        <v>-2.71872294372298</v>
       </c>
       <c r="BB2" t="n">
-        <v>-3.441612703148451</v>
-      </c>
-      <c r="BC2" t="inlineStr"/>
-      <c r="BD2" t="inlineStr"/>
-      <c r="BE2" t="inlineStr"/>
+        <v>-27820655.55268987</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>-1.2</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>3</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>-20200000</v>
+      </c>
       <c r="BF2" t="n">
         <v>0</v>
       </c>
@@ -888,7 +902,7 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>ChZKNjKb</t>
+          <t>p6XSLUlB</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
@@ -901,10 +915,10 @@
         <v>133</v>
       </c>
       <c r="E3" t="n">
-        <v>194</v>
+        <v>826</v>
       </c>
       <c r="F3" t="n">
-        <v>228</v>
+        <v>399</v>
       </c>
       <c r="G3" t="n">
         <v>55</v>
@@ -926,13 +940,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>272</v>
+        <v>314</v>
       </c>
       <c r="M3" t="n">
-        <v>109</v>
+        <v>211</v>
       </c>
       <c r="N3" t="n">
-        <v>-4</v>
+        <v>4</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -941,112 +955,126 @@
         <v>4</v>
       </c>
       <c r="Q3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
         <v>-1</v>
       </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
-        <v>-20</v>
-      </c>
       <c r="T3" t="n">
-        <v>20</v>
+        <v>0.5</v>
       </c>
       <c r="U3" t="n">
-        <v>1</v>
+        <v>-13</v>
       </c>
       <c r="V3" t="n">
-        <v>-4</v>
+        <v>13</v>
       </c>
       <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AB3" t="n">
         <v>0.5</v>
       </c>
-      <c r="X3" t="n">
-        <v>-3</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>3</v>
-      </c>
       <c r="AC3" t="n">
-        <v>0.5</v>
+        <v>-1.28</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.5</v>
+        <v>0.8900000000000001</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>-10.5</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AG3" t="n">
-        <v>-0.6949999999999998</v>
+        <v>-5</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.405</v>
+        <v>4.5</v>
       </c>
       <c r="AI3" t="n">
-        <v>-3.5</v>
+        <v>-6.5</v>
       </c>
       <c r="AJ3" t="n">
-        <v>7.5</v>
+        <v>2</v>
       </c>
       <c r="AK3" t="inlineStr"/>
       <c r="AL3" t="n">
-        <v>73.30000000000001</v>
-      </c>
-      <c r="AM3" t="inlineStr"/>
+        <v>73.44444444444444</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>-4.897707391698617</v>
+      </c>
       <c r="AN3" t="n">
-        <v>3.620830167855843</v>
+        <v>-9</v>
       </c>
       <c r="AO3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP3" t="inlineStr"/>
+        <v>-1.170126262626269</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>-1.793329816707001</v>
+      </c>
       <c r="AQ3" t="n">
-        <v>-0.5104407713498667</v>
-      </c>
-      <c r="AR3" t="inlineStr"/>
+        <v>-1.42977272727272</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>-0.4506565656565653</v>
+      </c>
       <c r="AS3" t="n">
-        <v>1.132432904710576</v>
+        <v>-0.3794840912823367</v>
       </c>
       <c r="AT3" t="n">
-        <v>3.362534435261722</v>
+        <v>1.078434343434342</v>
       </c>
       <c r="AU3" t="n">
-        <v>2.889012855831041</v>
+        <v>1</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.773900124908025</v>
+        <v>-0.7825371477125849</v>
       </c>
       <c r="AW3" t="n">
-        <v>1279902.548209367</v>
+        <v>2.125061656991477</v>
       </c>
       <c r="AX3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AY3" t="n">
-        <v>811226.2712172545</v>
-      </c>
-      <c r="AZ3" t="inlineStr"/>
+        <v>-2638493.686868684</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>2</v>
+      </c>
       <c r="BA3" t="n">
-        <v>4.226639118457314</v>
+        <v>1.827020202020179</v>
       </c>
       <c r="BB3" t="n">
-        <v>0.8026378052119298</v>
-      </c>
-      <c r="BC3" t="inlineStr"/>
-      <c r="BD3" t="inlineStr"/>
-      <c r="BE3" t="inlineStr"/>
+        <v>-5511388.746081728</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>6600000</v>
+      </c>
       <c r="BF3" t="n">
         <v>0</v>
       </c>
@@ -1054,7 +1082,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>p6XSLUlB</t>
+          <t>SU02594U</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -1064,13 +1092,13 @@
         <v>101</v>
       </c>
       <c r="D4" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E4" t="n">
-        <v>826</v>
+        <v>431</v>
       </c>
       <c r="F4" t="n">
-        <v>399</v>
+        <v>370</v>
       </c>
       <c r="G4" t="n">
         <v>55</v>
@@ -1092,127 +1120,143 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>314</v>
+        <v>243</v>
       </c>
       <c r="M4" t="n">
-        <v>211</v>
+        <v>127</v>
       </c>
       <c r="N4" t="n">
+        <v>-4</v>
+      </c>
+      <c r="O4" t="n">
+        <v>-1</v>
+      </c>
+      <c r="P4" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>-1</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>-1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" t="n">
+        <v>-16.5</v>
+      </c>
+      <c r="V4" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z4" t="n">
         <v>4</v>
       </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q4" t="n">
+      <c r="AA4" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AB4" t="n">
         <v>1</v>
       </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="n">
-        <v>-13</v>
-      </c>
-      <c r="T4" t="n">
-        <v>13</v>
-      </c>
-      <c r="U4" t="n">
-        <v>4</v>
-      </c>
-      <c r="V4" t="n">
+      <c r="AC4" t="n">
+        <v>-0.54</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>-0.4749999999999999</v>
+      </c>
+      <c r="AE4" t="n">
         <v>-5</v>
       </c>
-      <c r="W4" t="n">
-        <v>-6.5</v>
-      </c>
-      <c r="X4" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>-1</v>
-      </c>
-      <c r="Z4" t="n">
+      <c r="AF4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AH4" t="n">
         <v>0.5</v>
       </c>
-      <c r="AA4" t="n">
-        <v>-5</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AD4" t="n">
+      <c r="AI4" t="n">
         <v>0.5</v>
       </c>
-      <c r="AE4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>-1.28</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>0.8900000000000001</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>-10.5</v>
-      </c>
       <c r="AJ4" t="n">
-        <v>6</v>
-      </c>
-      <c r="AK4" t="inlineStr"/>
+        <v>-4.5</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>75.75</v>
+      </c>
       <c r="AL4" t="n">
-        <v>73.44444444444444</v>
-      </c>
-      <c r="AM4" t="inlineStr"/>
+        <v>70.44444444444446</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>-8.259885114744009</v>
+      </c>
       <c r="AN4" t="n">
-        <v>-4.899313581155695</v>
+        <v>-3</v>
       </c>
       <c r="AO4" t="n">
-        <v>-0.3715450339134552</v>
-      </c>
-      <c r="AP4" t="inlineStr"/>
+        <v>-7.519270482603829</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>-7.462861614118282</v>
+      </c>
       <c r="AQ4" t="n">
-        <v>0.9432889501071315</v>
-      </c>
-      <c r="AR4" t="inlineStr"/>
+        <v>-6.3679797979798</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>-0.2770931537598207</v>
+      </c>
       <c r="AS4" t="n">
-        <v>-0.7204621986200976</v>
+        <v>-0.2644527986633252</v>
       </c>
       <c r="AT4" t="n">
-        <v>-1.119111570247938</v>
+        <v>3.00563411896746</v>
       </c>
       <c r="AU4" t="n">
-        <v>-1.446958218549142</v>
+        <v>-2.5</v>
       </c>
       <c r="AV4" t="n">
-        <v>-1.889462175251651</v>
+        <v>1.059668526729926</v>
       </c>
       <c r="AW4" t="n">
-        <v>-2737151.534282214</v>
+        <v>1.948313320927753</v>
       </c>
       <c r="AX4" t="n">
-        <v>-0.4497359963269052</v>
+        <v>-173</v>
       </c>
       <c r="AY4" t="n">
-        <v>-5444322.632046318</v>
-      </c>
-      <c r="AZ4" t="inlineStr"/>
+        <v>-10480124.57912458</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>-177</v>
+      </c>
       <c r="BA4" t="n">
-        <v>1.552265074992306</v>
+        <v>-0.2719640852974123</v>
       </c>
       <c r="BB4" t="n">
-        <v>2.396033790770616</v>
-      </c>
-      <c r="BC4" t="inlineStr"/>
-      <c r="BD4" t="inlineStr"/>
-      <c r="BE4" t="inlineStr"/>
+        <v>-6118962.769435978</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>-2</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>-50175000</v>
+      </c>
       <c r="BF4" t="n">
         <v>0</v>
       </c>
@@ -1220,23 +1264,23 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>SU02594U</t>
+          <t>ChZKNjKb</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
         <v>45536.5</v>
       </c>
       <c r="C5" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D5" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E5" t="n">
-        <v>431</v>
+        <v>194</v>
       </c>
       <c r="F5" t="n">
-        <v>370</v>
+        <v>228</v>
       </c>
       <c r="G5" t="n">
         <v>55</v>
@@ -1258,19 +1302,19 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>243</v>
+        <v>272</v>
       </c>
       <c r="M5" t="n">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="N5" t="n">
         <v>-4</v>
       </c>
       <c r="O5" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="Q5" t="n">
         <v>-1</v>
@@ -1279,108 +1323,120 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>-16.5</v>
+        <v>0.5</v>
       </c>
       <c r="T5" t="n">
-        <v>16.5</v>
+        <v>0.5</v>
       </c>
       <c r="U5" t="n">
-        <v>2</v>
+        <v>-20</v>
       </c>
       <c r="V5" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>-4</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>-0.6949999999999998</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0.405</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI5" t="n">
         <v>0.5</v>
       </c>
-      <c r="X5" t="n">
-        <v>-4.5</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>-0.54</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>-0.4749999999999999</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>-5</v>
-      </c>
       <c r="AJ5" t="n">
-        <v>-5</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>75.75</v>
-      </c>
+        <v>-3</v>
+      </c>
+      <c r="AK5" t="inlineStr"/>
       <c r="AL5" t="n">
-        <v>70.44444444444446</v>
-      </c>
-      <c r="AM5" t="inlineStr"/>
+        <v>73.30000000000001</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>3.442710054304243</v>
+      </c>
       <c r="AN5" t="n">
-        <v>-8.246009917491619</v>
+        <v>6.400000000000006</v>
       </c>
       <c r="AO5" t="n">
-        <v>-0.252293233082707</v>
-      </c>
-      <c r="AP5" t="inlineStr"/>
+        <v>3.352525252525254</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>1.848823465852448</v>
+      </c>
       <c r="AQ5" t="n">
-        <v>3.019797979797985</v>
-      </c>
-      <c r="AR5" t="inlineStr"/>
+        <v>2.792550505050514</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>0</v>
+      </c>
       <c r="AS5" t="n">
-        <v>1.022496545851805</v>
+        <v>0</v>
       </c>
       <c r="AT5" t="n">
-        <v>-7.439797979797987</v>
+        <v>-0.6563131313131372</v>
       </c>
       <c r="AU5" t="n">
-        <v>-6.285454545454542</v>
+        <v>-4.199999999999999</v>
       </c>
       <c r="AV5" t="n">
-        <v>-7.4462574880624</v>
+        <v>1.030842848777631</v>
       </c>
       <c r="AW5" t="n">
-        <v>-10323848.48484848</v>
+        <v>0.9255335445553214</v>
       </c>
       <c r="AX5" t="n">
-        <v>-0.2756565656565659</v>
+        <v>-289</v>
       </c>
       <c r="AY5" t="n">
-        <v>-6117448.48604231</v>
-      </c>
-      <c r="AZ5" t="inlineStr"/>
+        <v>1267471.590909091</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>-266</v>
+      </c>
       <c r="BA5" t="n">
-        <v>0.03959595959597095</v>
+        <v>4.312373737373747</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.976931741980394</v>
-      </c>
-      <c r="BC5" t="inlineStr"/>
-      <c r="BD5" t="inlineStr"/>
-      <c r="BE5" t="inlineStr"/>
+        <v>812125.8021031572</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>-4</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>-5750000</v>
+      </c>
       <c r="BF5" t="n">
         <v>0</v>
       </c>
@@ -1447,58 +1503,58 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="n">
         <v>11</v>
       </c>
-      <c r="T6" t="n">
+      <c r="V6" t="n">
         <v>-11</v>
       </c>
-      <c r="U6" t="n">
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
         <v>-7</v>
       </c>
-      <c r="V6" t="n">
+      <c r="Z6" t="n">
         <v>7</v>
       </c>
-      <c r="W6" t="n">
+      <c r="AA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0.09999999999999992</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="n">
         <v>-1</v>
       </c>
-      <c r="X6" t="n">
+      <c r="AJ6" t="n">
         <v>3</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>-3</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>0.09999999999999992</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>-2.5</v>
       </c>
       <c r="AK6" t="n">
         <v>75.66666666666667</v>
@@ -1506,49 +1562,63 @@
       <c r="AL6" t="n">
         <v>71.15000000000001</v>
       </c>
-      <c r="AM6" t="inlineStr"/>
+      <c r="AM6" t="n">
+        <v>0.4062794327371222</v>
+      </c>
       <c r="AN6" t="n">
-        <v>0.4062794327371222</v>
+        <v>-3</v>
       </c>
       <c r="AO6" t="n">
+        <v>1.918069584736259</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>4.177719892670879</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>-0.2315375982042411</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>0.109988776655443</v>
+      </c>
+      <c r="AS6" t="n">
         <v>-0.02114550587202801</v>
       </c>
-      <c r="AP6" t="inlineStr"/>
-      <c r="AQ6" t="n">
+      <c r="AT6" t="n">
         <v>-2.355443322109991</v>
       </c>
-      <c r="AR6" t="inlineStr"/>
-      <c r="AS6" t="n">
+      <c r="AU6" t="n">
+        <v>-6.333333333333332</v>
+      </c>
+      <c r="AV6" t="n">
         <v>-3.579180950246482</v>
       </c>
-      <c r="AT6" t="n">
-        <v>1.918069584736259</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>-0.2315375982042411</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>4.177719892670879</v>
-      </c>
       <c r="AW6" t="n">
+        <v>3.224204053409409</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>-151</v>
+      </c>
+      <c r="AY6" t="n">
         <v>1293984.287317621</v>
       </c>
-      <c r="AX6" t="n">
-        <v>0.109988776655443</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>4561028.616302093</v>
-      </c>
-      <c r="AZ6" t="inlineStr"/>
+      <c r="AZ6" t="n">
+        <v>-156</v>
+      </c>
       <c r="BA6" t="n">
         <v>1.673512906846213</v>
       </c>
       <c r="BB6" t="n">
-        <v>3.224204053409409</v>
-      </c>
-      <c r="BC6" t="inlineStr"/>
-      <c r="BD6" t="inlineStr"/>
-      <c r="BE6" t="inlineStr"/>
+        <v>4561028.616302093</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>-2</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>-18900000</v>
+      </c>
       <c r="BF6" t="n">
         <v>0</v>
       </c>
@@ -1563,7 +1633,7 @@
         <v>45535.66666666666</v>
       </c>
       <c r="C7" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D7" t="n">
         <v>133</v>
@@ -1615,106 +1685,114 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
+        <v>-3</v>
+      </c>
+      <c r="T7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U7" t="n">
         <v>-9</v>
       </c>
-      <c r="T7" t="n">
+      <c r="V7" t="n">
         <v>9</v>
       </c>
-      <c r="U7" t="n">
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
         <v>-4</v>
       </c>
-      <c r="V7" t="n">
+      <c r="Z7" t="n">
         <v>-7</v>
       </c>
-      <c r="W7" t="n">
+      <c r="AA7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>-1.615</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>-0.23</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AI7" t="n">
         <v>6.5</v>
       </c>
-      <c r="X7" t="n">
+      <c r="AJ7" t="n">
         <v>-2</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>-1</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>-4.5</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>-3</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>-1.615</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>-0.23</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>-1.5</v>
       </c>
       <c r="AK7" t="n">
         <v>73.40000000000001</v>
       </c>
       <c r="AL7" t="inlineStr"/>
-      <c r="AM7" t="inlineStr"/>
-      <c r="AN7" t="n">
-        <v>-4.212442039814334</v>
-      </c>
+      <c r="AM7" t="n">
+        <v>-4.308357116548549</v>
+      </c>
+      <c r="AN7" t="inlineStr"/>
       <c r="AO7" t="n">
-        <v>-0.3018339744191141</v>
-      </c>
-      <c r="AP7" t="inlineStr"/>
+        <v>-0.3233605900272352</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>-1.607007176623455</v>
+      </c>
       <c r="AQ7" t="n">
-        <v>-3.807095959595962</v>
-      </c>
-      <c r="AR7" t="inlineStr"/>
+        <v>-4.442520442520461</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>-0.6094436427769763</v>
+      </c>
       <c r="AS7" t="n">
-        <v>-1.599923465711093</v>
+        <v>-0.3194980668148886</v>
       </c>
       <c r="AT7" t="n">
-        <v>-0.3543686868686819</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>-4.443333333333342</v>
-      </c>
+        <v>-3.856693923360591</v>
+      </c>
+      <c r="AU7" t="inlineStr"/>
       <c r="AV7" t="n">
-        <v>-1.479639792294435</v>
+        <v>-1.557234185887101</v>
       </c>
       <c r="AW7" t="n">
-        <v>-6802058.080808081</v>
+        <v>-2.493507617934398</v>
       </c>
       <c r="AX7" t="n">
-        <v>-0.612979797979798</v>
+        <v>-74</v>
       </c>
       <c r="AY7" t="n">
-        <v>-6200863.172496652</v>
-      </c>
-      <c r="AZ7" t="inlineStr"/>
+        <v>-6712658.329324996</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>-63</v>
+      </c>
       <c r="BA7" t="n">
-        <v>-0.5165151515151649</v>
+        <v>-0.7151034151034139</v>
       </c>
       <c r="BB7" t="n">
-        <v>-2.628283840267954</v>
+        <v>-6495844.442103865</v>
       </c>
       <c r="BC7" t="inlineStr"/>
-      <c r="BD7" t="inlineStr"/>
-      <c r="BE7" t="inlineStr"/>
+      <c r="BD7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>-1000000</v>
+      </c>
       <c r="BF7" t="n">
         <v>0</v>
       </c>
@@ -1729,7 +1807,7 @@
         <v>45535.58333333334</v>
       </c>
       <c r="C8" t="n">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D8" t="n">
         <v>134</v>
@@ -1781,58 +1859,58 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U8" t="n">
         <v>-6.5</v>
       </c>
-      <c r="T8" t="n">
+      <c r="V8" t="n">
         <v>6.5</v>
       </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" t="n">
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
         <v>1</v>
       </c>
-      <c r="W8" t="n">
+      <c r="AA8" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>-0.07499999999999996</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0.7749999999999999</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI8" t="n">
         <v>9.5</v>
       </c>
-      <c r="X8" t="n">
+      <c r="AJ8" t="n">
         <v>5.5</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>4</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>-0.07499999999999996</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>0.7749999999999999</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>7.5</v>
       </c>
       <c r="AK8" t="n">
         <v>70.77777777777777</v>
@@ -1840,49 +1918,63 @@
       <c r="AL8" t="n">
         <v>70.7625</v>
       </c>
-      <c r="AM8" t="inlineStr"/>
+      <c r="AM8" t="n">
+        <v>0.5561400962083098</v>
+      </c>
       <c r="AN8" t="n">
-        <v>0.5338594199208018</v>
+        <v>18.5</v>
       </c>
       <c r="AO8" t="n">
-        <v>-0.03238968973623702</v>
-      </c>
-      <c r="AP8" t="inlineStr"/>
+        <v>2.142424242424241</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>2.161576201260758</v>
+      </c>
       <c r="AQ8" t="n">
-        <v>-1.008181818181821</v>
-      </c>
-      <c r="AR8" t="inlineStr"/>
+        <v>0.3222222222222086</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>-0.1494949494949489</v>
+      </c>
       <c r="AS8" t="n">
-        <v>-1.460765399704023</v>
+        <v>-0.03598854415137454</v>
       </c>
       <c r="AT8" t="n">
-        <v>2.139090909090925</v>
+        <v>-1.02121212121212</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.2472727272727298</v>
+        <v>4.5</v>
       </c>
       <c r="AV8" t="n">
-        <v>2.223196358912475</v>
+        <v>-1.265047974979776</v>
       </c>
       <c r="AW8" t="n">
-        <v>746727.2727272715</v>
+        <v>0.8250495967674567</v>
       </c>
       <c r="AX8" t="n">
-        <v>-0.1590909090909087</v>
+        <v>-219</v>
       </c>
       <c r="AY8" t="n">
-        <v>1041966.018884497</v>
-      </c>
-      <c r="AZ8" t="inlineStr"/>
+        <v>788686.8686868679</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>-206</v>
+      </c>
       <c r="BA8" t="n">
-        <v>-0.9709090909090321</v>
+        <v>-1.067676767676744</v>
       </c>
       <c r="BB8" t="n">
-        <v>0.6536557482017713</v>
-      </c>
-      <c r="BC8" t="inlineStr"/>
-      <c r="BD8" t="inlineStr"/>
-      <c r="BE8" t="inlineStr"/>
+        <v>1037184.465427219</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>-3</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>-6925000</v>
+      </c>
       <c r="BF8" t="n">
         <v>0</v>
       </c>
@@ -1897,7 +1989,7 @@
         <v>45535.5</v>
       </c>
       <c r="C9" t="n">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D9" t="n">
         <v>134</v>
@@ -1949,275 +2041,115 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
         <v>1.5</v>
       </c>
-      <c r="T9" t="n">
+      <c r="V9" t="n">
         <v>-1.5</v>
       </c>
-      <c r="U9" t="n">
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
         <v>-7</v>
       </c>
-      <c r="V9" t="n">
+      <c r="Z9" t="n">
         <v>8</v>
       </c>
-      <c r="W9" t="n">
+      <c r="AA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>-0.07499999999999996</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0.3700000000000001</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>-4</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AI9" t="n">
         <v>-4.5</v>
       </c>
-      <c r="X9" t="n">
+      <c r="AJ9" t="n">
         <v>-3</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>-0.07499999999999996</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>0.3700000000000001</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>-4</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>1</v>
       </c>
       <c r="AK9" t="n">
         <v>76</v>
       </c>
       <c r="AL9" t="inlineStr"/>
-      <c r="AM9" t="inlineStr"/>
-      <c r="AN9" t="n">
-        <v>1.677859880190184</v>
-      </c>
+      <c r="AM9" t="n">
+        <v>1.88483518883217</v>
+      </c>
+      <c r="AN9" t="inlineStr"/>
       <c r="AO9" t="n">
-        <v>0.1572222222222224</v>
-      </c>
-      <c r="AP9" t="inlineStr"/>
+        <v>2.993663911845729</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>1.103172108601967</v>
+      </c>
       <c r="AQ9" t="n">
-        <v>1.195867768595043</v>
-      </c>
-      <c r="AR9" t="inlineStr"/>
+        <v>4.479522497704309</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>0.3404040404040407</v>
+      </c>
       <c r="AS9" t="n">
-        <v>-0.7426420562845877</v>
+        <v>0.1500000000000001</v>
       </c>
       <c r="AT9" t="n">
-        <v>3.037603305785126</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>4.482148760330574</v>
-      </c>
+        <v>1.227180899908177</v>
+      </c>
+      <c r="AU9" t="inlineStr"/>
       <c r="AV9" t="n">
-        <v>1.048833484263355</v>
+        <v>-0.6131094284186247</v>
       </c>
       <c r="AW9" t="n">
-        <v>4440793.388429752</v>
+        <v>-0.4035585134378152</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.3245454545454549</v>
+        <v>82</v>
       </c>
       <c r="AY9" t="n">
-        <v>2394476.636987949</v>
-      </c>
-      <c r="AZ9" t="inlineStr"/>
+        <v>4474591.368227731</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>76</v>
+      </c>
       <c r="BA9" t="n">
-        <v>0.3688429752066327</v>
+        <v>0.2842975206611698</v>
       </c>
       <c r="BB9" t="n">
-        <v>-0.4433556915683425</v>
+        <v>2479137.13081511</v>
       </c>
       <c r="BC9" t="inlineStr"/>
-      <c r="BD9" t="inlineStr"/>
-      <c r="BE9" t="inlineStr"/>
+      <c r="BD9" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>11500000</v>
+      </c>
       <c r="BF9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>vmgpBDzg</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="n">
-        <v>45534.65625</v>
-      </c>
-      <c r="C10" t="n">
-        <v>101</v>
-      </c>
-      <c r="D10" t="n">
-        <v>133</v>
-      </c>
-      <c r="E10" t="n">
-        <v>56</v>
-      </c>
-      <c r="F10" t="n">
-        <v>516</v>
-      </c>
-      <c r="G10" t="n">
-        <v>55</v>
-      </c>
-      <c r="H10" t="n">
-        <v>551</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-      <c r="L10" t="n">
-        <v>165</v>
-      </c>
-      <c r="M10" t="n">
-        <v>211</v>
-      </c>
-      <c r="N10" t="n">
-        <v>20</v>
-      </c>
-      <c r="O10" t="n">
-        <v>2</v>
-      </c>
-      <c r="P10" t="n">
-        <v>15</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>-16</v>
-      </c>
-      <c r="T10" t="n">
-        <v>16</v>
-      </c>
-      <c r="U10" t="n">
-        <v>2</v>
-      </c>
-      <c r="V10" t="n">
-        <v>5</v>
-      </c>
-      <c r="W10" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="X10" t="n">
-        <v>-9.5</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>-2</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>-3</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>-0.02499999999999991</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>75.7625</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>74.675</v>
-      </c>
-      <c r="AM10" t="inlineStr"/>
-      <c r="AN10" t="n">
-        <v>4.410259403933679</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>0.4076945923038937</v>
-      </c>
-      <c r="AP10" t="inlineStr"/>
-      <c r="AQ10" t="n">
-        <v>4.935420875420874</v>
-      </c>
-      <c r="AR10" t="inlineStr"/>
-      <c r="AS10" t="n">
-        <v>2.243621600402463</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>-0.4200505050504972</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>5.376414141414145</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>1.282416182091453</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>5541781.144781144</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>0.8685858585858584</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>3449593.798976085</v>
-      </c>
-      <c r="AZ10" t="inlineStr"/>
-      <c r="BA10" t="n">
-        <v>-1.359158249158241</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>-3.456125283783763</v>
-      </c>
-      <c r="BC10" t="inlineStr"/>
-      <c r="BD10" t="inlineStr"/>
-      <c r="BE10" t="inlineStr"/>
-      <c r="BF10" t="n">
         <v>0</v>
       </c>
     </row>

--- a/data/france/p6_deployment/data_preparation/df_tagged.xlsx
+++ b/data/france/p6_deployment/data_preparation/df_tagged.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BF6"/>
+  <dimension ref="A1:BF10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -530,84 +530,84 @@
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_last_match_expected_goals_(xg)</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_expected_goals_(xg)_against</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_shots_on_goal</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_shots_on_goal_against</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_last_match_goal_attempts</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_goal_attempts_against</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_ball_possession</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_ball_possession_against</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_fouls</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_fouls_against</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goals</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goals_against</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_points</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_points_against</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_n_matches_last_days</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_n_matches_last_days_against</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_points</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_points_against</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_fouls</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_fouls_against</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_expected_goals_(xg)</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_expected_goals_(xg)_against</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goals</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goals_against</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_shots_on_goal</t>
-        </is>
-      </c>
-      <c r="AJ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_shots_on_goal_against</t>
-        </is>
-      </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>mean_last_match_mean_rat_player_start_home_against</t>
@@ -620,97 +620,97 @@
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_int_rep_player_sub</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_pot_player_miss</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_miss</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_start</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_n_player_miss</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_rat_player_miss</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_val_player_miss</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_pot_player_sub</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_sub</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_age_player_sub</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_sub</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_rat_player_start</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_rat_player_miss</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_miss</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_miss</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_start</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_val_player_start</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_miss</t>
-        </is>
-      </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_val_player_miss</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_start</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_sub</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_start</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>dif_n_player_miss</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_age_player_start</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_pot_player_miss</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_sub</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_sub</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_miss</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_pot_player_start</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_hei_player_sub</t>
-        </is>
-      </c>
-      <c r="BE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_miss</t>
         </is>
       </c>
       <c r="BF1" s="1" t="inlineStr">
@@ -722,23 +722,23 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>6ZfxDZ5t</t>
+          <t>Qw81zU34</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45536.65625</v>
+        <v>45550.65625</v>
       </c>
       <c r="C2" t="n">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="D2" t="n">
         <v>133</v>
       </c>
       <c r="E2" t="n">
-        <v>777</v>
+        <v>273</v>
       </c>
       <c r="F2" t="n">
-        <v>129</v>
+        <v>39</v>
       </c>
       <c r="G2" t="n">
         <v>55</v>
@@ -760,140 +760,128 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>243</v>
+        <v>67</v>
       </c>
       <c r="M2" t="n">
-        <v>234</v>
+        <v>260</v>
       </c>
       <c r="N2" t="n">
-        <v>-21</v>
+        <v>-10</v>
       </c>
       <c r="O2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>2</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0.2833333333333334</v>
+      </c>
+      <c r="V2" t="n">
+        <v>-1.756666666666667</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.333333333333334</v>
+      </c>
+      <c r="X2" t="n">
+        <v>-3.666666666666667</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.333333333333332</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>-7.666666666666666</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB2" t="n">
         <v>-5</v>
       </c>
-      <c r="P2" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>-2</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S2" t="n">
-        <v>2</v>
-      </c>
-      <c r="T2" t="n">
-        <v>4</v>
-      </c>
-      <c r="U2" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="V2" t="n">
-        <v>-2</v>
-      </c>
-      <c r="W2" t="n">
-        <v>-3.5</v>
-      </c>
-      <c r="X2" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>0</v>
-      </c>
       <c r="AC2" t="n">
-        <v>2</v>
+        <v>3.666666666666668</v>
       </c>
       <c r="AD2" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AE2" t="n">
-        <v>-0.9650000000000001</v>
+        <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.08499999999999996</v>
+        <v>-2.333333333333333</v>
       </c>
       <c r="AG2" t="n">
-        <v>-3</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="AH2" t="n">
-        <v>-0.5</v>
+        <v>-1.666666666666667</v>
       </c>
       <c r="AI2" t="n">
-        <v>-3.5</v>
+        <v>0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-1.5</v>
+        <v>0</v>
       </c>
       <c r="AK2" t="n">
-        <v>67.3</v>
-      </c>
-      <c r="AL2" t="inlineStr"/>
+        <v>72.26666666666667</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>73.84166666666667</v>
+      </c>
       <c r="AM2" t="n">
-        <v>-5.803943491101634</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>1.809980168180633</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>-3.997264309764319</v>
-      </c>
+        <v>-0.3533180185354099</v>
+      </c>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
       <c r="AP2" t="n">
-        <v>218</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>-23818703.7037037</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>-20200000</v>
-      </c>
+        <v>-0.3929292929292931</v>
+      </c>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="n">
-        <v>-0.7795454545454541</v>
+        <v>-1.750368230803005</v>
       </c>
       <c r="AU2" t="n">
-        <v>-0.9590722181060156</v>
+        <v>-0.2572413094152211</v>
       </c>
       <c r="AV2" t="n">
-        <v>-2.858207070707095</v>
+        <v>0.5101803993108298</v>
       </c>
       <c r="AW2" t="n">
-        <v>3</v>
+        <v>406481.3125682697</v>
       </c>
       <c r="AX2" t="n">
-        <v>-0.02630471380471633</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>223</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>-5.171740524219885</v>
-      </c>
+        <v>0.1481481481481524</v>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr"/>
       <c r="BA2" t="n">
-        <v>-28743871.8409166</v>
+        <v>-0.538383838383794</v>
       </c>
       <c r="BB2" t="n">
-        <v>-1.2</v>
+        <v>2081346.801346801</v>
       </c>
       <c r="BC2" t="n">
-        <v>-3.384427609427604</v>
+        <v>0.6158249158249198</v>
       </c>
       <c r="BD2" t="n">
-        <v>-3.294060175052152</v>
+        <v>-0.2427609427609525</v>
       </c>
       <c r="BE2" t="n">
-        <v>-9.099999999999994</v>
+        <v>-0.6834656486830113</v>
       </c>
       <c r="BF2" t="n">
         <v>0</v>
@@ -902,23 +890,23 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>SU02594U</t>
+          <t>E3tkRPQj</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45536.5</v>
+        <v>45550.5</v>
       </c>
       <c r="C3" t="n">
         <v>101</v>
       </c>
       <c r="D3" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E3" t="n">
-        <v>431</v>
+        <v>736</v>
       </c>
       <c r="F3" t="n">
-        <v>370</v>
+        <v>292</v>
       </c>
       <c r="G3" t="n">
         <v>55</v>
@@ -940,142 +928,128 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>243</v>
+        <v>165</v>
       </c>
       <c r="M3" t="n">
-        <v>127</v>
+        <v>163</v>
       </c>
       <c r="N3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O3" t="n">
+        <v>2</v>
+      </c>
+      <c r="P3" t="n">
+        <v>-2</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>-8</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.1166666666666669</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>3.666666666666667</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>12.66666666666667</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>-12.66666666666667</v>
+      </c>
+      <c r="AC3" t="n">
         <v>-4</v>
       </c>
-      <c r="O3" t="n">
-        <v>-1</v>
-      </c>
-      <c r="P3" t="n">
-        <v>-1</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>-1</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
+      <c r="AD3" t="n">
+        <v>4.333333333333332</v>
+      </c>
+      <c r="AE3" t="n">
         <v>2</v>
       </c>
-      <c r="T3" t="n">
-        <v>4</v>
-      </c>
-      <c r="U3" t="n">
-        <v>-5</v>
-      </c>
-      <c r="V3" t="n">
-        <v>-5</v>
-      </c>
-      <c r="W3" t="n">
-        <v>-16.5</v>
-      </c>
-      <c r="X3" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>-4.5</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>-0.54</v>
-      </c>
       <c r="AF3" t="n">
-        <v>-0.4749999999999999</v>
+        <v>-0.3333333333333335</v>
       </c>
       <c r="AG3" t="n">
-        <v>-1</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>-1.666666666666667</v>
       </c>
       <c r="AI3" t="n">
-        <v>-0.5</v>
+        <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>75.75</v>
+        <v>75.30185185185185</v>
       </c>
       <c r="AL3" t="n">
-        <v>70.44444444444446</v>
+        <v>75.24074074074075</v>
       </c>
       <c r="AM3" t="n">
-        <v>-7.462861614118282</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>1.059668526729926</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>-6.3679797979798</v>
-      </c>
+        <v>-0.01666666666666661</v>
+      </c>
+      <c r="AN3" t="inlineStr"/>
+      <c r="AO3" t="inlineStr"/>
       <c r="AP3" t="n">
-        <v>-177</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>-10480124.57912458</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>-2.5</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>-50175000</v>
-      </c>
+        <v>-0.06666666666666665</v>
+      </c>
+      <c r="AQ3" t="inlineStr"/>
+      <c r="AR3" t="inlineStr"/>
+      <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="n">
-        <v>-0.2770931537598207</v>
+        <v>5.990988480118915</v>
       </c>
       <c r="AU3" t="n">
-        <v>-0.2644527986633252</v>
+        <v>0.9837374581939855</v>
       </c>
       <c r="AV3" t="n">
-        <v>-0.2719640852974123</v>
+        <v>-5.292948717948711</v>
       </c>
       <c r="AW3" t="n">
-        <v>-2</v>
+        <v>1571606.74470457</v>
       </c>
       <c r="AX3" t="n">
-        <v>3.00563411896746</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>-173</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>-8.259885114744009</v>
-      </c>
+        <v>2.74444444444444</v>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr"/>
       <c r="BA3" t="n">
-        <v>-6118962.769435978</v>
+        <v>0.333333333333286</v>
       </c>
       <c r="BB3" t="n">
-        <v>-0.75</v>
+        <v>2651481.481481481</v>
       </c>
       <c r="BC3" t="n">
-        <v>-7.519270482603829</v>
+        <v>-4.088888888888889</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.948313320927753</v>
+        <v>7.303703703703704</v>
       </c>
       <c r="BE3" t="n">
-        <v>-3</v>
+        <v>-0.7434410999628085</v>
       </c>
       <c r="BF3" t="n">
         <v>0</v>
@@ -1084,11 +1058,11 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>ChZKNjKb</t>
+          <t>fJaIWo3T</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45536.5</v>
+        <v>45550.5</v>
       </c>
       <c r="C4" t="n">
         <v>107</v>
@@ -1097,10 +1071,10 @@
         <v>133</v>
       </c>
       <c r="E4" t="n">
-        <v>194</v>
+        <v>341</v>
       </c>
       <c r="F4" t="n">
-        <v>228</v>
+        <v>122</v>
       </c>
       <c r="G4" t="n">
         <v>55</v>
@@ -1122,140 +1096,126 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>272</v>
+        <v>152</v>
       </c>
       <c r="M4" t="n">
         <v>109</v>
       </c>
       <c r="N4" t="n">
-        <v>-4</v>
+        <v>5</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="P4" t="n">
         <v>4</v>
       </c>
       <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
         <v>-1</v>
       </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="n">
-        <v>1</v>
-      </c>
-      <c r="T4" t="n">
+      <c r="U4" t="n">
+        <v>-0.6166666666666669</v>
+      </c>
+      <c r="V4" t="n">
+        <v>-0.1833333333333333</v>
+      </c>
+      <c r="W4" t="n">
+        <v>-2.666666666666667</v>
+      </c>
+      <c r="X4" t="n">
+        <v>-2.333333333333333</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>-5.333333333333332</v>
+      </c>
+      <c r="Z4" t="n">
         <v>-4</v>
       </c>
-      <c r="U4" t="n">
-        <v>-3.5</v>
-      </c>
-      <c r="V4" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="W4" t="n">
-        <v>-20</v>
-      </c>
-      <c r="X4" t="n">
-        <v>20</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>0</v>
-      </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.333333333333336</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>-1.333333333333336</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.5</v>
+        <v>4.333333333333332</v>
       </c>
       <c r="AD4" t="n">
-        <v>-3</v>
+        <v>-0.3333333333333321</v>
       </c>
       <c r="AE4" t="n">
-        <v>-0.6949999999999998</v>
+        <v>-1.333333333333333</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.405</v>
+        <v>-0.3333333333333335</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.5</v>
+        <v>-1.333333333333333</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.5</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="AI4" t="n">
-        <v>-1.5</v>
+        <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>3</v>
-      </c>
-      <c r="AK4" t="inlineStr"/>
-      <c r="AL4" t="n">
-        <v>73.30000000000001</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>73.40000000000001</v>
+      </c>
+      <c r="AL4" t="inlineStr"/>
       <c r="AM4" t="n">
-        <v>1.848823465852448</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>1.030842848777631</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>2.792550505050514</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AN4" t="inlineStr"/>
+      <c r="AO4" t="inlineStr"/>
       <c r="AP4" t="n">
-        <v>-266</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>1267471.590909091</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>-4.199999999999999</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>-5750000</v>
-      </c>
+        <v>0.1074074074074074</v>
+      </c>
+      <c r="AQ4" t="inlineStr"/>
+      <c r="AR4" t="inlineStr"/>
+      <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>2.31679292929293</v>
       </c>
       <c r="AU4" t="n">
-        <v>0</v>
+        <v>2.04835858585858</v>
       </c>
       <c r="AV4" t="n">
-        <v>4.312373737373747</v>
+        <v>0.3494949494949537</v>
       </c>
       <c r="AW4" t="n">
-        <v>-4</v>
+        <v>767522.0959595959</v>
       </c>
       <c r="AX4" t="n">
-        <v>-0.6563131313131372</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>-289</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>3.442710054304243</v>
-      </c>
+        <v>1.510774410774417</v>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr"/>
       <c r="BA4" t="n">
-        <v>812125.8021031572</v>
+        <v>-4.936700336700312</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>2396026.936026935</v>
       </c>
       <c r="BC4" t="n">
-        <v>3.352525252525254</v>
+        <v>-1.689225589225586</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.9255335445553214</v>
+        <v>3.108080808080814</v>
       </c>
       <c r="BE4" t="n">
-        <v>6.400000000000006</v>
+        <v>-1.956944444444417</v>
       </c>
       <c r="BF4" t="n">
         <v>0</v>
@@ -1264,23 +1224,23 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>p6XSLUlB</t>
+          <t>M51AY7YG</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45536.5</v>
+        <v>45550.5</v>
       </c>
       <c r="C5" t="n">
         <v>101</v>
       </c>
       <c r="D5" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E5" t="n">
-        <v>826</v>
+        <v>858</v>
       </c>
       <c r="F5" t="n">
-        <v>399</v>
+        <v>579</v>
       </c>
       <c r="G5" t="n">
         <v>55</v>
@@ -1302,140 +1262,114 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>314</v>
+        <v>286</v>
       </c>
       <c r="M5" t="n">
         <v>211</v>
       </c>
       <c r="N5" t="n">
-        <v>4</v>
+        <v>-4</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="P5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>-9</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0.3833333333333333</v>
+      </c>
+      <c r="V5" t="n">
+        <v>-0.6033333333333331</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0.9999999999999996</v>
+      </c>
+      <c r="X5" t="n">
+        <v>-3.333333333333333</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>-0.3333333333333339</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>-7.333333333333334</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0.3333333333333357</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>-0.3333333333333357</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0.6666666666666661</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0.3333333333333335</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>-1.333333333333333</v>
+      </c>
+      <c r="AG5" t="n">
         <v>1</v>
       </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>4</v>
-      </c>
-      <c r="T5" t="n">
-        <v>-5</v>
-      </c>
-      <c r="U5" t="n">
-        <v>-10.5</v>
-      </c>
-      <c r="V5" t="n">
-        <v>6</v>
-      </c>
-      <c r="W5" t="n">
-        <v>-13</v>
-      </c>
-      <c r="X5" t="n">
-        <v>13</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA5" t="n">
+      <c r="AH5" t="n">
         <v>-1</v>
       </c>
-      <c r="AB5" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>-6.5</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>-1.28</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>0.8900000000000001</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>0.5</v>
-      </c>
       <c r="AI5" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AK5" t="inlineStr"/>
-      <c r="AL5" t="n">
-        <v>73.44444444444444</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>71.875</v>
+      </c>
+      <c r="AL5" t="inlineStr"/>
       <c r="AM5" t="n">
-        <v>-1.782703375247237</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>-0.7880377582131999</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>-1.409191919191912</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>77</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>-2591119.949494949</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>3</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>13100000</v>
-      </c>
+        <v>0.3271708683473391</v>
+      </c>
+      <c r="AN5" t="inlineStr"/>
+      <c r="AO5" t="inlineStr"/>
+      <c r="AP5" t="inlineStr"/>
+      <c r="AQ5" t="inlineStr"/>
+      <c r="AR5" t="inlineStr"/>
+      <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="n">
-        <v>-0.4481313131313127</v>
+        <v>-3.535247432306235</v>
       </c>
       <c r="AU5" t="n">
-        <v>-0.3917677027326152</v>
+        <v>2.664519140989739</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.918686868686819</v>
+        <v>3.793323996265173</v>
       </c>
       <c r="AW5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>1.071111111111108</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>81</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>-4.909598247756136</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>-5600695.1495548</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>-1.168989898989892</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>2.075687080950246</v>
-      </c>
+        <v>-523011.2044817931</v>
+      </c>
+      <c r="AX5" t="inlineStr"/>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr"/>
+      <c r="BA5" t="inlineStr"/>
+      <c r="BB5" t="inlineStr"/>
+      <c r="BC5" t="inlineStr"/>
+      <c r="BD5" t="inlineStr"/>
       <c r="BE5" t="n">
-        <v>-11.5</v>
+        <v>-0.7869281045751961</v>
       </c>
       <c r="BF5" t="n">
         <v>0</v>
@@ -1444,23 +1378,23 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>IgtCPCkn</t>
+          <t>hCffxjZi</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45536.41666666666</v>
+        <v>45550.41666666666</v>
       </c>
       <c r="C6" t="n">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D6" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E6" t="n">
-        <v>47</v>
+        <v>573</v>
       </c>
       <c r="F6" t="n">
-        <v>176</v>
+        <v>157</v>
       </c>
       <c r="G6" t="n">
         <v>55</v>
@@ -1482,144 +1416,786 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>165</v>
+        <v>12</v>
       </c>
       <c r="M6" t="n">
-        <v>7</v>
+        <v>141</v>
       </c>
       <c r="N6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="O6" t="n">
+        <v>3</v>
+      </c>
+      <c r="P6" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>3</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="n">
         <v>2</v>
       </c>
-      <c r="P6" t="n">
+      <c r="U6" t="n">
+        <v>0.5699999999999997</v>
+      </c>
+      <c r="V6" t="n">
+        <v>-0.5566666666666662</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="X6" t="n">
+        <v>-1.666666666666666</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>-1.333333333333329</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.333333333333329</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>-0.6666666666666661</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>-4</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>-1.666666666666667</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>-0.3333333333333335</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>73.44444444444444</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>71.48888888888888</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>0.3104395604395607</v>
+      </c>
+      <c r="AN6" t="inlineStr"/>
+      <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="n">
+        <v>0.3318181818181818</v>
+      </c>
+      <c r="AQ6" t="inlineStr"/>
+      <c r="AR6" t="inlineStr"/>
+      <c r="AS6" t="inlineStr"/>
+      <c r="AT6" t="n">
+        <v>1.412423687423683</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>2.440720390720401</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>-0.1996642246642288</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>3680289.987789988</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>1.401136363636368</v>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr"/>
+      <c r="BA6" t="n">
+        <v>-0.2825757575757564</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>3090909.090909091</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>-0.7098484848484823</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>1.621590909090912</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>0.05769230769229239</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>8MPiooIM</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45549.66666666666</v>
+      </c>
+      <c r="C7" t="n">
+        <v>101</v>
+      </c>
+      <c r="D7" t="n">
+        <v>135</v>
+      </c>
+      <c r="E7" t="n">
+        <v>206</v>
+      </c>
+      <c r="F7" t="n">
+        <v>133</v>
+      </c>
+      <c r="G7" t="n">
+        <v>55</v>
+      </c>
+      <c r="H7" t="n">
+        <v>551</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>243</v>
+      </c>
+      <c r="M7" t="n">
+        <v>226</v>
+      </c>
+      <c r="N7" t="n">
+        <v>17</v>
+      </c>
+      <c r="O7" t="n">
+        <v>5</v>
+      </c>
+      <c r="P7" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>3</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>-6</v>
+      </c>
+      <c r="T7" t="n">
+        <v>-4</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0.5033333333333334</v>
+      </c>
+      <c r="V7" t="n">
+        <v>-1.203333333333333</v>
+      </c>
+      <c r="W7" t="n">
+        <v>3.999999999999999</v>
+      </c>
+      <c r="X7" t="n">
+        <v>-2.333333333333333</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>-4.333333333333333</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>16.66666666666667</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>-16.66666666666666</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>2.333333333333333</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.333333333333334</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>2.666666666666666</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>-1.666666666666667</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>73.59090909090909</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>73.125</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0.8018793842323251</v>
+      </c>
+      <c r="AN7" t="inlineStr"/>
+      <c r="AO7" t="inlineStr"/>
+      <c r="AP7" t="n">
+        <v>0.7805555555555557</v>
+      </c>
+      <c r="AQ7" t="inlineStr"/>
+      <c r="AR7" t="inlineStr"/>
+      <c r="AS7" t="inlineStr"/>
+      <c r="AT7" t="n">
+        <v>10.10592784122196</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>9.754380042615338</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>-0.9742727860374885</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>27830481.69695228</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>7.43148148148147</v>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr"/>
+      <c r="BA7" t="n">
+        <v>1.66388888888892</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>40861481.48148148</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>-5.277777777777775</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>11.28703703703704</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>4.646029351911693</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>CGH7Enso</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45549.58333333334</v>
+      </c>
+      <c r="C8" t="n">
+        <v>101</v>
+      </c>
+      <c r="D8" t="n">
+        <v>134</v>
+      </c>
+      <c r="E8" t="n">
+        <v>342</v>
+      </c>
+      <c r="F8" t="n">
+        <v>33</v>
+      </c>
+      <c r="G8" t="n">
+        <v>55</v>
+      </c>
+      <c r="H8" t="n">
+        <v>551</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>198</v>
+      </c>
+      <c r="M8" t="n">
+        <v>83</v>
+      </c>
+      <c r="N8" t="n">
+        <v>-4</v>
+      </c>
+      <c r="O8" t="n">
+        <v>-2</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>-1</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3</v>
+      </c>
+      <c r="T8" t="n">
+        <v>-9</v>
+      </c>
+      <c r="U8" t="n">
+        <v>-0.4400000000000002</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0.5133333333333334</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>2.333333333333333</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>-2.666666666666666</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>-10.33333333333334</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>10.33333333333334</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0.3333333333333321</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>-0.3333333333333333</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>-1.333333333333333</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>72.59393939393941</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>75.83333333333334</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>-0.4074074074074074</v>
+      </c>
+      <c r="AN8" t="inlineStr"/>
+      <c r="AO8" t="inlineStr"/>
+      <c r="AP8" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="AQ8" t="inlineStr"/>
+      <c r="AR8" t="inlineStr"/>
+      <c r="AS8" t="inlineStr"/>
+      <c r="AT8" t="n">
+        <v>-10.80447330447331</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>-9.281577681577687</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>2.106204906204898</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>-10221755.65175565</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>-6.859722222222217</v>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr"/>
+      <c r="BA8" t="n">
+        <v>-0.8083333333333655</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>-10088645.83333333</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>2.824999999999999</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>-9.499999999999986</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>-1.251154401154452</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>0dMqm7mA</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45549.5</v>
+      </c>
+      <c r="C9" t="n">
+        <v>101</v>
+      </c>
+      <c r="D9" t="n">
+        <v>135</v>
+      </c>
+      <c r="E9" t="n">
+        <v>448</v>
+      </c>
+      <c r="F9" t="n">
+        <v>370</v>
+      </c>
+      <c r="G9" t="n">
+        <v>55</v>
+      </c>
+      <c r="H9" t="n">
+        <v>551</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>152</v>
+      </c>
+      <c r="M9" t="n">
+        <v>163</v>
+      </c>
+      <c r="N9" t="n">
+        <v>15</v>
+      </c>
+      <c r="O9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="P9" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>4</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0.7133333333333334</v>
+      </c>
+      <c r="V9" t="n">
+        <v>-0.4933333333333334</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="X9" t="n">
+        <v>-2.666666666666667</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0.6666666666666661</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>-7.666666666666667</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>11.66666666666666</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>-11.66666666666666</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>-2.666666666666666</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>-4.333333333333334</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK9" t="inlineStr"/>
+      <c r="AL9" t="n">
+        <v>69.56296296296297</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>0.5473484848484849</v>
+      </c>
+      <c r="AN9" t="inlineStr"/>
+      <c r="AO9" t="inlineStr"/>
+      <c r="AP9" t="inlineStr"/>
+      <c r="AQ9" t="inlineStr"/>
+      <c r="AR9" t="inlineStr"/>
+      <c r="AS9" t="inlineStr"/>
+      <c r="AT9" t="n">
+        <v>1.043939393939411</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>2.956439393939391</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>1.779545454545453</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>6377698.863636365</v>
+      </c>
+      <c r="AX9" t="inlineStr"/>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr"/>
+      <c r="BA9" t="inlineStr"/>
+      <c r="BB9" t="inlineStr"/>
+      <c r="BC9" t="inlineStr"/>
+      <c r="BD9" t="inlineStr"/>
+      <c r="BE9" t="n">
+        <v>-1.969696969696969</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>vsYzkTIc</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45548.65625</v>
+      </c>
+      <c r="C10" t="n">
+        <v>104</v>
+      </c>
+      <c r="D10" t="n">
+        <v>135</v>
+      </c>
+      <c r="E10" t="n">
+        <v>528</v>
+      </c>
+      <c r="F10" t="n">
+        <v>545</v>
+      </c>
+      <c r="G10" t="n">
+        <v>55</v>
+      </c>
+      <c r="H10" t="n">
+        <v>551</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>9</v>
+      </c>
+      <c r="M10" t="n">
+        <v>37</v>
+      </c>
+      <c r="N10" t="n">
+        <v>-10</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>11</v>
+      </c>
+      <c r="T10" t="n">
+        <v>-8</v>
+      </c>
+      <c r="U10" t="n">
+        <v>-0.4433333333333331</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.533333333333334</v>
+      </c>
+      <c r="W10" t="n">
+        <v>-2.333333333333333</v>
+      </c>
+      <c r="X10" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>-4</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>8.666666666666666</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>-12</v>
+      </c>
+      <c r="AB10" t="n">
         <v>12</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
-        <v>-7</v>
-      </c>
-      <c r="T6" t="n">
-        <v>7</v>
-      </c>
-      <c r="U6" t="n">
+      <c r="AC10" t="n">
+        <v>2.666666666666666</v>
+      </c>
+      <c r="AD10" t="n">
         <v>-2</v>
       </c>
-      <c r="V6" t="n">
-        <v>-2.5</v>
-      </c>
-      <c r="W6" t="n">
-        <v>11</v>
-      </c>
-      <c r="X6" t="n">
-        <v>-11</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>3</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>0.09999999999999992</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>-3</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>75.66666666666667</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>71.15000000000001</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>4.177719892670879</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>-3.579180950246482</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>-0.2315375982042411</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>-156</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>1293984.287317621</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>-8.333333333333332</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>-15900000</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>0.109988776655443</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>-0.02114550587202801</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>1.673512906846213</v>
-      </c>
-      <c r="AW6" t="n">
+      <c r="AE10" t="n">
+        <v>-1.666666666666667</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="AG10" t="n">
         <v>-2</v>
       </c>
-      <c r="AX6" t="n">
-        <v>-2.355443322109991</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>-148</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>0.4062794327371222</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>4561028.616302093</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>1.918069584736259</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>3.224204053409409</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>-3.333333333333343</v>
-      </c>
-      <c r="BF6" t="n">
+      <c r="AH10" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>73.95185185185186</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>74.52500000000001</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>-0.5399230399230397</v>
+      </c>
+      <c r="AN10" t="inlineStr"/>
+      <c r="AO10" t="inlineStr"/>
+      <c r="AP10" t="n">
+        <v>-0.1166666666666667</v>
+      </c>
+      <c r="AQ10" t="inlineStr"/>
+      <c r="AR10" t="inlineStr"/>
+      <c r="AS10" t="inlineStr"/>
+      <c r="AT10" t="n">
+        <v>-6.348371671901077</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>-6.806100217864923</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>0.004116798234448993</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>-7669380.075262426</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>-5.041666666666671</v>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr"/>
+      <c r="BA10" t="n">
+        <v>0.5833333333333428</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>-8711041.666666666</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>1.775000000000002</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>-6.191666666666663</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>3.175466146054362</v>
+      </c>
+      <c r="BF10" t="n">
         <v>0</v>
       </c>
     </row>

--- a/data/france/p6_deployment/data_preparation/df_tagged.xlsx
+++ b/data/france/p6_deployment/data_preparation/df_tagged.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BF10"/>
+  <dimension ref="A1:BF19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -520,94 +520,94 @@
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_last_match_shots_on_goal</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_shots_on_goal_against</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_expected_goals_(xg)</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_expected_goals_(xg)_against</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_last_match_interceptions</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_interceptions_against</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_expected_goals_(xg)</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_expected_goals_(xg)_against</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_shots_on_goal</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_shots_on_goal_against</t>
-        </is>
-      </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_last_match_n_matches_last_days</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_n_matches_last_days_against</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_points</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_points_against</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_last_match_goal_attempts</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_goal_attempts_against</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goals</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goals_against</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_fouls</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_fouls_against</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_ball_possession</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_ball_possession_against</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_fouls</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_fouls_against</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goals</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goals_against</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_points</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_points_against</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_n_matches_last_days</t>
-        </is>
-      </c>
-      <c r="AJ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_n_matches_last_days_against</t>
-        </is>
-      </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>mean_last_match_mean_rat_player_start_home_against</t>
@@ -620,97 +620,97 @@
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_hei_player_sub</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_miss</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_val_player_miss</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_sub</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_start</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_pot_player_miss</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_int_rep_player_sub</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_pot_player_miss</t>
-        </is>
-      </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_start</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_rat_player_miss</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_start</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_age_player_miss</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_start</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>dif_n_player_miss</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_rat_player_miss</t>
-        </is>
-      </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_val_player_miss</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_start</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_start</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_sub</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_sub</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_pot_player_sub</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_sub</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_sub</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_sub</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_start</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_start</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_hei_player_miss</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_miss</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_start</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_start</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_start</t>
-        </is>
-      </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_start</t>
-        </is>
-      </c>
-      <c r="BE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_sub</t>
         </is>
       </c>
       <c r="BF1" s="1" t="inlineStr">
@@ -722,23 +722,23 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Qw81zU34</t>
+          <t>S66OuPup</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45550.65625</v>
+        <v>45557.65625</v>
       </c>
       <c r="C2" t="n">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="D2" t="n">
         <v>133</v>
       </c>
       <c r="E2" t="n">
-        <v>273</v>
+        <v>56</v>
       </c>
       <c r="F2" t="n">
-        <v>39</v>
+        <v>303</v>
       </c>
       <c r="G2" t="n">
         <v>55</v>
@@ -760,129 +760,125 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>67</v>
+        <v>165</v>
       </c>
       <c r="M2" t="n">
         <v>260</v>
       </c>
       <c r="N2" t="n">
-        <v>-10</v>
+        <v>10</v>
       </c>
       <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q2" t="n">
         <v>1</v>
       </c>
-      <c r="P2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="n">
         <v>2</v>
       </c>
-      <c r="R2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0</v>
-      </c>
       <c r="T2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2833333333333334</v>
+        <v>-0.655</v>
       </c>
       <c r="V2" t="n">
-        <v>-1.756666666666667</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.333333333333334</v>
-      </c>
-      <c r="X2" t="n">
-        <v>-3.666666666666667</v>
-      </c>
+        <v>1.42</v>
+      </c>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
       <c r="Y2" t="n">
-        <v>1.333333333333332</v>
+        <v>-0.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>-7.666666666666666</v>
+        <v>-0.5</v>
       </c>
       <c r="AA2" t="n">
-        <v>5</v>
+        <v>-1.5</v>
       </c>
       <c r="AB2" t="n">
-        <v>-5</v>
+        <v>1.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>3.666666666666668</v>
+        <v>1.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AF2" t="n">
-        <v>-2.333333333333333</v>
+        <v>1.5</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.333333333333333</v>
+        <v>-1</v>
       </c>
       <c r="AH2" t="n">
-        <v>-1.666666666666667</v>
+        <v>-3.5</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>-22.5</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>22.5</v>
       </c>
       <c r="AK2" t="n">
-        <v>72.26666666666667</v>
+        <v>72.95</v>
       </c>
       <c r="AL2" t="n">
-        <v>73.84166666666667</v>
+        <v>73.53636363636363</v>
       </c>
       <c r="AM2" t="n">
-        <v>-0.3533180185354099</v>
+        <v>0.7185990338164743</v>
       </c>
       <c r="AN2" t="inlineStr"/>
       <c r="AO2" t="inlineStr"/>
       <c r="AP2" t="n">
-        <v>-0.3929292929292931</v>
-      </c>
-      <c r="AQ2" t="inlineStr"/>
+        <v>-3803539.196310935</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>-5257777.777777776</v>
+      </c>
       <c r="AR2" t="inlineStr"/>
-      <c r="AS2" t="inlineStr"/>
+      <c r="AS2" t="n">
+        <v>0.1249121651295564</v>
+      </c>
       <c r="AT2" t="n">
-        <v>-1.750368230803005</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>-0.2572413094152211</v>
-      </c>
+        <v>-0.118518518518556</v>
+      </c>
+      <c r="AU2" t="inlineStr"/>
       <c r="AV2" t="n">
-        <v>0.5101803993108298</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>406481.3125682697</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>0.1481481481481524</v>
-      </c>
-      <c r="AY2" t="inlineStr"/>
-      <c r="AZ2" t="inlineStr"/>
+        <v>0.3370370370370375</v>
+      </c>
+      <c r="AW2" t="inlineStr"/>
+      <c r="AX2" t="inlineStr"/>
+      <c r="AY2" t="n">
+        <v>2.214814814814815</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>-0.2222222222222143</v>
+      </c>
       <c r="BA2" t="n">
-        <v>-0.538383838383794</v>
+        <v>0.1637681159420197</v>
       </c>
       <c r="BB2" t="n">
-        <v>2081346.801346801</v>
+        <v>0.400911286780854</v>
       </c>
       <c r="BC2" t="n">
-        <v>0.6158249158249198</v>
+        <v>-0.2807586736934695</v>
       </c>
       <c r="BD2" t="n">
-        <v>-0.2427609427609525</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>-0.6834656486830113</v>
-      </c>
+        <v>-0.9888888888888943</v>
+      </c>
+      <c r="BE2" t="inlineStr"/>
       <c r="BF2" t="n">
         <v>0</v>
       </c>
@@ -890,23 +886,23 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>E3tkRPQj</t>
+          <t>EsTauGo1</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45550.5</v>
+        <v>45557.5</v>
       </c>
       <c r="C3" t="n">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="D3" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E3" t="n">
-        <v>736</v>
+        <v>242</v>
       </c>
       <c r="F3" t="n">
-        <v>292</v>
+        <v>228</v>
       </c>
       <c r="G3" t="n">
         <v>55</v>
@@ -928,129 +924,125 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>165</v>
+        <v>286</v>
       </c>
       <c r="M3" t="n">
-        <v>163</v>
+        <v>109</v>
       </c>
       <c r="N3" t="n">
+        <v>-3</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q3" t="n">
         <v>-1</v>
       </c>
-      <c r="O3" t="n">
-        <v>2</v>
-      </c>
-      <c r="P3" t="n">
-        <v>-2</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
       <c r="R3" t="n">
         <v>0</v>
       </c>
       <c r="S3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T3" t="n">
+        <v>-3</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0.3050000000000002</v>
+      </c>
+      <c r="V3" t="n">
+        <v>-0.6800000000000002</v>
+      </c>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AB3" t="n">
         <v>-1</v>
       </c>
-      <c r="T3" t="n">
-        <v>-8</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="V3" t="n">
-        <v>0.1166666666666669</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.333333333333333</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>3.666666666666667</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>2.333333333333334</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>12.66666666666667</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>-12.66666666666667</v>
-      </c>
       <c r="AC3" t="n">
-        <v>-4</v>
+        <v>-0.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>4.333333333333332</v>
+        <v>-5</v>
       </c>
       <c r="AE3" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="AF3" t="n">
-        <v>-0.3333333333333335</v>
+        <v>-0.5</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.333333333333333</v>
+        <v>5</v>
       </c>
       <c r="AH3" t="n">
-        <v>-1.666666666666667</v>
+        <v>6.5</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AK3" t="n">
-        <v>75.30185185185185</v>
+        <v>71.14090909090909</v>
       </c>
       <c r="AL3" t="n">
-        <v>75.24074074074075</v>
+        <v>72</v>
       </c>
       <c r="AM3" t="n">
-        <v>-0.01666666666666661</v>
+        <v>-0.03282828282826245</v>
       </c>
       <c r="AN3" t="inlineStr"/>
       <c r="AO3" t="inlineStr"/>
       <c r="AP3" t="n">
-        <v>-0.06666666666666665</v>
-      </c>
-      <c r="AQ3" t="inlineStr"/>
+        <v>2783603.896103896</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>3768257.575757576</v>
+      </c>
       <c r="AR3" t="inlineStr"/>
-      <c r="AS3" t="inlineStr"/>
+      <c r="AS3" t="n">
+        <v>0.1785714285714286</v>
+      </c>
       <c r="AT3" t="n">
-        <v>5.990988480118915</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>0.9837374581939855</v>
-      </c>
+        <v>-1.593939393939365</v>
+      </c>
+      <c r="AU3" t="inlineStr"/>
       <c r="AV3" t="n">
-        <v>-5.292948717948711</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>1571606.74470457</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>2.74444444444444</v>
-      </c>
-      <c r="AY3" t="inlineStr"/>
-      <c r="AZ3" t="inlineStr"/>
+        <v>0.4181818181818182</v>
+      </c>
+      <c r="AW3" t="inlineStr"/>
+      <c r="AX3" t="inlineStr"/>
+      <c r="AY3" t="n">
+        <v>0.7181818181818187</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>5.036363636363632</v>
+      </c>
       <c r="BA3" t="n">
-        <v>0.333333333333286</v>
+        <v>5.787878787878796</v>
       </c>
       <c r="BB3" t="n">
-        <v>2651481.481481481</v>
+        <v>0.1863275613275626</v>
       </c>
       <c r="BC3" t="n">
-        <v>-4.088888888888889</v>
+        <v>5.591450216450212</v>
       </c>
       <c r="BD3" t="n">
-        <v>7.303703703703704</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>-0.7434410999628085</v>
-      </c>
+        <v>4.724242424242433</v>
+      </c>
+      <c r="BE3" t="inlineStr"/>
       <c r="BF3" t="n">
         <v>0</v>
       </c>
@@ -1058,23 +1050,23 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>fJaIWo3T</t>
+          <t>nTCJapXF</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45550.5</v>
+        <v>45557.5</v>
       </c>
       <c r="C4" t="n">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D4" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E4" t="n">
-        <v>341</v>
+        <v>211</v>
       </c>
       <c r="F4" t="n">
-        <v>122</v>
+        <v>226</v>
       </c>
       <c r="G4" t="n">
         <v>55</v>
@@ -1096,127 +1088,125 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>152</v>
+        <v>9</v>
       </c>
       <c r="M4" t="n">
-        <v>109</v>
+        <v>260</v>
       </c>
       <c r="N4" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O4" t="n">
+        <v>2</v>
+      </c>
+      <c r="P4" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>1</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>4</v>
+      </c>
+      <c r="T4" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.175</v>
+      </c>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>-10</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>7</v>
+      </c>
+      <c r="AI4" t="n">
         <v>5</v>
       </c>
-      <c r="O4" t="n">
-        <v>-1</v>
-      </c>
-      <c r="P4" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" t="n">
-        <v>-1</v>
-      </c>
-      <c r="U4" t="n">
-        <v>-0.6166666666666669</v>
-      </c>
-      <c r="V4" t="n">
-        <v>-0.1833333333333333</v>
-      </c>
-      <c r="W4" t="n">
-        <v>-2.666666666666667</v>
-      </c>
-      <c r="X4" t="n">
-        <v>-2.333333333333333</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>-5.333333333333332</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>-4</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>1.333333333333336</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>-1.333333333333336</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>4.333333333333332</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>-0.3333333333333321</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>-1.333333333333333</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>-0.3333333333333335</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>-1.333333333333333</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>0.6666666666666667</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>0</v>
-      </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="AK4" t="n">
-        <v>73.40000000000001</v>
-      </c>
-      <c r="AL4" t="inlineStr"/>
+        <v>73.06944444444444</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>73.27272727272727</v>
+      </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>1.52916666666664</v>
       </c>
       <c r="AN4" t="inlineStr"/>
       <c r="AO4" t="inlineStr"/>
       <c r="AP4" t="n">
-        <v>0.1074074074074074</v>
-      </c>
-      <c r="AQ4" t="inlineStr"/>
+        <v>922222.2222222229</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>1145454.545454547</v>
+      </c>
       <c r="AR4" t="inlineStr"/>
-      <c r="AS4" t="inlineStr"/>
+      <c r="AS4" t="n">
+        <v>0.2569444444444444</v>
+      </c>
       <c r="AT4" t="n">
-        <v>2.31679292929293</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>2.04835858585858</v>
-      </c>
+        <v>-0.04242424242426068</v>
+      </c>
+      <c r="AU4" t="inlineStr"/>
       <c r="AV4" t="n">
-        <v>0.3494949494949537</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>767522.0959595959</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>1.510774410774417</v>
-      </c>
-      <c r="AY4" t="inlineStr"/>
-      <c r="AZ4" t="inlineStr"/>
+        <v>0.3090909090909091</v>
+      </c>
+      <c r="AW4" t="inlineStr"/>
+      <c r="AX4" t="inlineStr"/>
+      <c r="AY4" t="n">
+        <v>4.981818181818177</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>2.015151515151516</v>
+      </c>
       <c r="BA4" t="n">
-        <v>-4.936700336700312</v>
+        <v>-1.473611111111111</v>
       </c>
       <c r="BB4" t="n">
-        <v>2396026.936026935</v>
+        <v>-0.01249999999999929</v>
       </c>
       <c r="BC4" t="n">
-        <v>-1.689225589225586</v>
+        <v>-1.63055555555556</v>
       </c>
       <c r="BD4" t="n">
-        <v>3.108080808080814</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>-1.956944444444417</v>
-      </c>
+        <v>-3.090909090909093</v>
+      </c>
+      <c r="BE4" t="inlineStr"/>
       <c r="BF4" t="n">
         <v>0</v>
       </c>
@@ -1224,23 +1214,23 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>M51AY7YG</t>
+          <t>6HPisxHl</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45550.5</v>
+        <v>45557.5</v>
       </c>
       <c r="C5" t="n">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D5" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E5" t="n">
-        <v>858</v>
+        <v>431</v>
       </c>
       <c r="F5" t="n">
-        <v>579</v>
+        <v>599</v>
       </c>
       <c r="G5" t="n">
         <v>55</v>
@@ -1262,19 +1252,19 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>286</v>
+        <v>35</v>
       </c>
       <c r="M5" t="n">
-        <v>211</v>
+        <v>141</v>
       </c>
       <c r="N5" t="n">
-        <v>-4</v>
+        <v>-6</v>
       </c>
       <c r="O5" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="P5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q5" t="n">
         <v>-1</v>
@@ -1283,94 +1273,108 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>-9</v>
+        <v>2</v>
       </c>
       <c r="T5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U5" t="n">
+        <v>-0.1499999999999999</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="W5" t="n">
+        <v>7</v>
+      </c>
+      <c r="X5" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AF5" t="n">
         <v>2</v>
       </c>
-      <c r="U5" t="n">
-        <v>0.3833333333333333</v>
-      </c>
-      <c r="V5" t="n">
-        <v>-0.6033333333333331</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0.9999999999999996</v>
-      </c>
-      <c r="X5" t="n">
-        <v>-3.333333333333333</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>-0.3333333333333339</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>-7.333333333333334</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>0.3333333333333357</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>-0.3333333333333357</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>0.6666666666666661</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>-3</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>0.3333333333333335</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>-1.333333333333333</v>
-      </c>
       <c r="AG5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH5" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="AK5" t="n">
-        <v>71.875</v>
-      </c>
-      <c r="AL5" t="inlineStr"/>
+        <v>75.22727272727272</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>73.14090909090909</v>
+      </c>
       <c r="AM5" t="n">
-        <v>0.3271708683473391</v>
+        <v>-0.2221215780998307</v>
       </c>
       <c r="AN5" t="inlineStr"/>
       <c r="AO5" t="inlineStr"/>
-      <c r="AP5" t="inlineStr"/>
-      <c r="AQ5" t="inlineStr"/>
+      <c r="AP5" t="n">
+        <v>-2453913.546698873</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>-3342954.545454545</v>
+      </c>
       <c r="AR5" t="inlineStr"/>
-      <c r="AS5" t="inlineStr"/>
+      <c r="AS5" t="n">
+        <v>-0.3296296296296299</v>
+      </c>
       <c r="AT5" t="n">
-        <v>-3.535247432306235</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>2.664519140989739</v>
-      </c>
+        <v>2.0030303030303</v>
+      </c>
+      <c r="AU5" t="inlineStr"/>
       <c r="AV5" t="n">
-        <v>3.793323996265173</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>-523011.2044817931</v>
-      </c>
+        <v>-0.2969696969696973</v>
+      </c>
+      <c r="AW5" t="inlineStr"/>
       <c r="AX5" t="inlineStr"/>
-      <c r="AY5" t="inlineStr"/>
-      <c r="AZ5" t="inlineStr"/>
-      <c r="BA5" t="inlineStr"/>
-      <c r="BB5" t="inlineStr"/>
-      <c r="BC5" t="inlineStr"/>
-      <c r="BD5" t="inlineStr"/>
-      <c r="BE5" t="n">
-        <v>-0.7869281045751961</v>
-      </c>
+      <c r="AY5" t="n">
+        <v>0.6818181818181834</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>-4.875757575757575</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>-4.834983896940429</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>0.6430555555555486</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>-2.530696457326897</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>-3.409090909090907</v>
+      </c>
+      <c r="BE5" t="inlineStr"/>
       <c r="BF5" t="n">
         <v>0</v>
       </c>
@@ -1378,23 +1382,23 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hCffxjZi</t>
+          <t>6V4QeyWs</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45550.41666666666</v>
+        <v>45557.41666666666</v>
       </c>
       <c r="C6" t="n">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="D6" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E6" t="n">
-        <v>573</v>
+        <v>47</v>
       </c>
       <c r="F6" t="n">
-        <v>157</v>
+        <v>122</v>
       </c>
       <c r="G6" t="n">
         <v>55</v>
@@ -1416,129 +1420,125 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>12</v>
+        <v>67</v>
       </c>
       <c r="M6" t="n">
-        <v>141</v>
+        <v>109</v>
       </c>
       <c r="N6" t="n">
         <v>5</v>
       </c>
       <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="T6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>-0.9550000000000001</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.1799999999999999</v>
+      </c>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>-8.5</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AG6" t="n">
         <v>3</v>
       </c>
-      <c r="P6" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>3</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
-        <v>5</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0.5699999999999997</v>
-      </c>
-      <c r="V6" t="n">
-        <v>-0.5566666666666662</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.666666666666667</v>
-      </c>
-      <c r="X6" t="n">
-        <v>-1.666666666666666</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>8</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>-1.333333333333329</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.333333333333329</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>-0.6666666666666661</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>-4</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>-1.666666666666667</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>0.6666666666666667</v>
-      </c>
       <c r="AH6" t="n">
-        <v>-0.3333333333333335</v>
+        <v>6.5</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>-19</v>
       </c>
       <c r="AK6" t="n">
-        <v>73.44444444444444</v>
+        <v>75.81818181818181</v>
       </c>
       <c r="AL6" t="n">
-        <v>71.48888888888888</v>
+        <v>72.46060606060607</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.3104395604395607</v>
+        <v>1.684722222222206</v>
       </c>
       <c r="AN6" t="inlineStr"/>
       <c r="AO6" t="inlineStr"/>
       <c r="AP6" t="n">
-        <v>0.3318181818181818</v>
-      </c>
-      <c r="AQ6" t="inlineStr"/>
+        <v>10012105.42929293</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>9841212.121212121</v>
+      </c>
       <c r="AR6" t="inlineStr"/>
-      <c r="AS6" t="inlineStr"/>
+      <c r="AS6" t="n">
+        <v>0.4074074074074074</v>
+      </c>
       <c r="AT6" t="n">
-        <v>1.412423687423683</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>2.440720390720401</v>
-      </c>
+        <v>-2.384848484848476</v>
+      </c>
+      <c r="AU6" t="inlineStr"/>
       <c r="AV6" t="n">
-        <v>-0.1996642246642288</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>3680289.987789988</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>1.401136363636368</v>
-      </c>
-      <c r="AY6" t="inlineStr"/>
-      <c r="AZ6" t="inlineStr"/>
+        <v>0.3</v>
+      </c>
+      <c r="AW6" t="inlineStr"/>
+      <c r="AX6" t="inlineStr"/>
+      <c r="AY6" t="n">
+        <v>-1.781818181818174</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>4.384848484848476</v>
+      </c>
       <c r="BA6" t="n">
-        <v>-0.2825757575757564</v>
+        <v>5.922895622895624</v>
       </c>
       <c r="BB6" t="n">
-        <v>3090909.090909091</v>
+        <v>-1.6435606060606</v>
       </c>
       <c r="BC6" t="n">
-        <v>-0.7098484848484823</v>
+        <v>8.082996632996654</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.621590909090912</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>0.05769230769229239</v>
-      </c>
+        <v>6.296969696969697</v>
+      </c>
+      <c r="BE6" t="inlineStr"/>
       <c r="BF6" t="n">
         <v>0</v>
       </c>
@@ -1546,23 +1546,23 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>8MPiooIM</t>
+          <t>v39B1623</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45549.66666666666</v>
+        <v>45556.66666666666</v>
       </c>
       <c r="C7" t="n">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D7" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E7" t="n">
-        <v>206</v>
+        <v>826</v>
       </c>
       <c r="F7" t="n">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G7" t="n">
         <v>55</v>
@@ -1584,129 +1584,115 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>243</v>
+        <v>12</v>
       </c>
       <c r="M7" t="n">
-        <v>226</v>
+        <v>37</v>
       </c>
       <c r="N7" t="n">
-        <v>17</v>
+        <v>-9</v>
       </c>
       <c r="O7" t="n">
-        <v>5</v>
+        <v>-2</v>
       </c>
       <c r="P7" t="n">
+        <v>-3</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U7" t="n">
+        <v>-1.05</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.005</v>
+      </c>
+      <c r="W7" t="n">
         <v>8</v>
       </c>
-      <c r="Q7" t="n">
-        <v>3</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
+      <c r="X7" t="n">
+        <v>-2</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC7" t="n">
         <v>-6</v>
       </c>
-      <c r="T7" t="n">
-        <v>-4</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0.5033333333333334</v>
-      </c>
-      <c r="V7" t="n">
-        <v>-1.203333333333333</v>
-      </c>
-      <c r="W7" t="n">
-        <v>3.999999999999999</v>
-      </c>
-      <c r="X7" t="n">
-        <v>-2.333333333333333</v>
-      </c>
-      <c r="Y7" t="n">
+      <c r="AD7" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AH7" t="n">
         <v>4</v>
       </c>
-      <c r="Z7" t="n">
-        <v>-4.333333333333333</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>16.66666666666667</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>-16.66666666666666</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>2.333333333333333</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.333333333333334</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>2.666666666666666</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>-1.666666666666667</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>2</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>-2</v>
-      </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>-25</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>73.59090909090909</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="AK7" t="inlineStr"/>
       <c r="AL7" t="n">
-        <v>73.125</v>
+        <v>73.45454545454545</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.8018793842323251</v>
+        <v>0.03365384615381117</v>
       </c>
       <c r="AN7" t="inlineStr"/>
       <c r="AO7" t="inlineStr"/>
       <c r="AP7" t="n">
-        <v>0.7805555555555557</v>
+        <v>-29228367.41961741</v>
       </c>
       <c r="AQ7" t="inlineStr"/>
       <c r="AR7" t="inlineStr"/>
-      <c r="AS7" t="inlineStr"/>
-      <c r="AT7" t="n">
-        <v>10.10592784122196</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>9.754380042615338</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>-0.9742727860374885</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>27830481.69695228</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>7.43148148148147</v>
-      </c>
+      <c r="AS7" t="n">
+        <v>-1.048478835978836</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AU7" t="inlineStr"/>
+      <c r="AV7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr"/>
+      <c r="AX7" t="inlineStr"/>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr"/>
       <c r="BA7" t="n">
-        <v>1.66388888888892</v>
+        <v>-8.881471306471312</v>
       </c>
       <c r="BB7" t="n">
-        <v>40861481.48148148</v>
+        <v>-0.8031593406593416</v>
       </c>
       <c r="BC7" t="n">
-        <v>-5.277777777777775</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>11.28703703703704</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>4.646029351911693</v>
-      </c>
+        <v>-6.796550671550662</v>
+      </c>
+      <c r="BD7" t="inlineStr"/>
+      <c r="BE7" t="inlineStr"/>
       <c r="BF7" t="n">
         <v>0</v>
       </c>
@@ -1714,11 +1700,11 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>CGH7Enso</t>
+          <t>noOg1c8K</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45549.58333333334</v>
+        <v>45556.58333333334</v>
       </c>
       <c r="C8" t="n">
         <v>101</v>
@@ -1727,10 +1713,10 @@
         <v>134</v>
       </c>
       <c r="E8" t="n">
-        <v>342</v>
+        <v>573</v>
       </c>
       <c r="F8" t="n">
-        <v>33</v>
+        <v>176</v>
       </c>
       <c r="G8" t="n">
         <v>55</v>
@@ -1752,19 +1738,19 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>198</v>
+        <v>12</v>
       </c>
       <c r="M8" t="n">
         <v>83</v>
       </c>
       <c r="N8" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="O8" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="P8" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="Q8" t="n">
         <v>-1</v>
@@ -1773,108 +1759,108 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="T8" t="n">
-        <v>-9</v>
+        <v>-1</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4400000000000002</v>
+        <v>0.5550000000000002</v>
       </c>
       <c r="V8" t="n">
-        <v>0.5133333333333334</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="X8" t="n">
-        <v>2.333333333333333</v>
+        <v>1</v>
       </c>
       <c r="Y8" t="n">
-        <v>-2.666666666666666</v>
+        <v>1</v>
       </c>
       <c r="Z8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AA8" t="n">
-        <v>-10.33333333333334</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>10.33333333333334</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.3333333333333321</v>
+        <v>11</v>
       </c>
       <c r="AD8" t="n">
-        <v>-3</v>
+        <v>7</v>
       </c>
       <c r="AE8" t="n">
-        <v>-0.3333333333333333</v>
+        <v>2</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.666666666666667</v>
+        <v>-0.5</v>
       </c>
       <c r="AG8" t="n">
-        <v>-1.333333333333333</v>
+        <v>-4.5</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.666666666666667</v>
+        <v>0.5</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="AK8" t="n">
-        <v>72.59393939393941</v>
+        <v>75.21818181818182</v>
       </c>
       <c r="AL8" t="n">
-        <v>75.83333333333334</v>
+        <v>71.3</v>
       </c>
       <c r="AM8" t="n">
-        <v>-0.4074074074074074</v>
+        <v>0.5588050767078698</v>
       </c>
       <c r="AN8" t="inlineStr"/>
       <c r="AO8" t="inlineStr"/>
       <c r="AP8" t="n">
-        <v>-0.3</v>
-      </c>
-      <c r="AQ8" t="inlineStr"/>
+        <v>447032.8605750585</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>-3244242.424242422</v>
+      </c>
       <c r="AR8" t="inlineStr"/>
-      <c r="AS8" t="inlineStr"/>
+      <c r="AS8" t="n">
+        <v>0.3983126847576974</v>
+      </c>
       <c r="AT8" t="n">
-        <v>-10.80447330447331</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>-9.281577681577687</v>
-      </c>
+        <v>0.05151515151516151</v>
+      </c>
+      <c r="AU8" t="inlineStr"/>
       <c r="AV8" t="n">
-        <v>2.106204906204898</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>-10221755.65175565</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>-6.859722222222217</v>
-      </c>
-      <c r="AY8" t="inlineStr"/>
-      <c r="AZ8" t="inlineStr"/>
+        <v>0.336363636363636</v>
+      </c>
+      <c r="AW8" t="inlineStr"/>
+      <c r="AX8" t="inlineStr"/>
+      <c r="AY8" t="n">
+        <v>-1.033333333333339</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>-0.5121212121212011</v>
+      </c>
       <c r="BA8" t="n">
-        <v>-0.8083333333333655</v>
+        <v>-0.5391105058624248</v>
       </c>
       <c r="BB8" t="n">
-        <v>-10088645.83333333</v>
+        <v>-0.6741381664655322</v>
       </c>
       <c r="BC8" t="n">
-        <v>2.824999999999999</v>
+        <v>0.08129892273113626</v>
       </c>
       <c r="BD8" t="n">
-        <v>-9.499999999999986</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>-1.251154401154452</v>
-      </c>
+        <v>-0.5515151515151473</v>
+      </c>
+      <c r="BE8" t="inlineStr"/>
       <c r="BF8" t="n">
         <v>0</v>
       </c>
@@ -1882,23 +1868,23 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>0dMqm7mA</t>
+          <t>fiy8wfGD</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45549.5</v>
+        <v>45556.5</v>
       </c>
       <c r="C9" t="n">
         <v>101</v>
       </c>
       <c r="D9" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E9" t="n">
-        <v>448</v>
+        <v>777</v>
       </c>
       <c r="F9" t="n">
-        <v>370</v>
+        <v>516</v>
       </c>
       <c r="G9" t="n">
         <v>55</v>
@@ -1920,73 +1906,69 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>152</v>
+        <v>243</v>
       </c>
       <c r="M9" t="n">
-        <v>163</v>
+        <v>260</v>
       </c>
       <c r="N9" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="O9" t="n">
+        <v>4</v>
+      </c>
+      <c r="P9" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>3</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
         <v>-1</v>
       </c>
-      <c r="P9" t="n">
-        <v>14</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>4</v>
-      </c>
       <c r="T9" t="n">
-        <v>3</v>
+        <v>-4</v>
       </c>
       <c r="U9" t="n">
-        <v>0.7133333333333334</v>
+        <v>-0.7450000000000001</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.4933333333333334</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.333333333333333</v>
-      </c>
-      <c r="X9" t="n">
-        <v>-2.666666666666667</v>
-      </c>
+        <v>-0.6000000000000001</v>
+      </c>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
       <c r="Y9" t="n">
-        <v>0.6666666666666661</v>
+        <v>-0.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>-7.666666666666667</v>
+        <v>-0.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>11.66666666666666</v>
+        <v>1</v>
       </c>
       <c r="AB9" t="n">
-        <v>-11.66666666666666</v>
+        <v>-0.5</v>
       </c>
       <c r="AC9" t="n">
-        <v>-2.666666666666666</v>
+        <v>-3.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>-4.333333333333334</v>
+        <v>-5.5</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.333333333333333</v>
+        <v>-0.5</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AG9" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="AH9" t="n">
-        <v>-1</v>
+        <v>-2.5</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1994,41 +1976,55 @@
       <c r="AJ9" t="n">
         <v>0</v>
       </c>
-      <c r="AK9" t="inlineStr"/>
+      <c r="AK9" t="n">
+        <v>74.59999999999999</v>
+      </c>
       <c r="AL9" t="n">
-        <v>69.56296296296297</v>
+        <v>75.34999999999999</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.5473484848484849</v>
+        <v>-0.4610389610389802</v>
       </c>
       <c r="AN9" t="inlineStr"/>
       <c r="AO9" t="inlineStr"/>
-      <c r="AP9" t="inlineStr"/>
-      <c r="AQ9" t="inlineStr"/>
+      <c r="AP9" t="n">
+        <v>5404884.559884561</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>6165589.225589227</v>
+      </c>
       <c r="AR9" t="inlineStr"/>
-      <c r="AS9" t="inlineStr"/>
+      <c r="AS9" t="n">
+        <v>0.7010101010101009</v>
+      </c>
       <c r="AT9" t="n">
-        <v>1.043939393939411</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>2.956439393939391</v>
-      </c>
+        <v>-2.252861952861906</v>
+      </c>
+      <c r="AU9" t="inlineStr"/>
       <c r="AV9" t="n">
-        <v>1.779545454545453</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>6377698.863636365</v>
-      </c>
+        <v>0.271043771043771</v>
+      </c>
+      <c r="AW9" t="inlineStr"/>
       <c r="AX9" t="inlineStr"/>
-      <c r="AY9" t="inlineStr"/>
-      <c r="AZ9" t="inlineStr"/>
-      <c r="BA9" t="inlineStr"/>
-      <c r="BB9" t="inlineStr"/>
-      <c r="BC9" t="inlineStr"/>
-      <c r="BD9" t="inlineStr"/>
-      <c r="BE9" t="n">
-        <v>-1.969696969696969</v>
-      </c>
+      <c r="AY9" t="n">
+        <v>3.836700336700336</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>5.469023569023577</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>6.033405483405488</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>5.59004329004329</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>0.03150553150553037</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>0.2484848484848499</v>
+      </c>
+      <c r="BE9" t="inlineStr"/>
       <c r="BF9" t="n">
         <v>0</v>
       </c>
@@ -2036,23 +2032,23 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>vsYzkTIc</t>
+          <t>0K4Ww3Ad</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45548.65625</v>
+        <v>45555.65625</v>
       </c>
       <c r="C10" t="n">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="D10" t="n">
         <v>135</v>
       </c>
       <c r="E10" t="n">
-        <v>528</v>
+        <v>535</v>
       </c>
       <c r="F10" t="n">
-        <v>545</v>
+        <v>362</v>
       </c>
       <c r="G10" t="n">
         <v>55</v>
@@ -2074,128 +2070,1562 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="M10" t="n">
-        <v>37</v>
+        <v>226</v>
       </c>
       <c r="N10" t="n">
+        <v>5</v>
+      </c>
+      <c r="O10" t="n">
+        <v>2</v>
+      </c>
+      <c r="P10" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2</v>
+      </c>
+      <c r="T10" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="V10" t="n">
+        <v>-1.475</v>
+      </c>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AG10" t="n">
         <v>-10</v>
       </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>11</v>
-      </c>
-      <c r="T10" t="n">
-        <v>-8</v>
-      </c>
-      <c r="U10" t="n">
-        <v>-0.4433333333333331</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.533333333333334</v>
-      </c>
-      <c r="W10" t="n">
-        <v>-2.333333333333333</v>
-      </c>
-      <c r="X10" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>-4</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>8.666666666666666</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>-12</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>12</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>2.666666666666666</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>-1.666666666666667</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1.333333333333333</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>-2</v>
-      </c>
       <c r="AH10" t="n">
-        <v>2</v>
+        <v>8.5</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="AK10" t="n">
-        <v>73.95185185185186</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="AL10" t="n">
-        <v>74.52500000000001</v>
+        <v>75.5</v>
       </c>
       <c r="AM10" t="n">
-        <v>-0.5399230399230397</v>
+        <v>-0.451970687264776</v>
       </c>
       <c r="AN10" t="inlineStr"/>
       <c r="AO10" t="inlineStr"/>
       <c r="AP10" t="n">
-        <v>-0.1166666666666667</v>
-      </c>
-      <c r="AQ10" t="inlineStr"/>
+        <v>5609222.123192712</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>7849147.727272728</v>
+      </c>
       <c r="AR10" t="inlineStr"/>
-      <c r="AS10" t="inlineStr"/>
+      <c r="AS10" t="n">
+        <v>0.1357694592988714</v>
+      </c>
       <c r="AT10" t="n">
-        <v>-6.348371671901077</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>-6.806100217864923</v>
-      </c>
+        <v>1.462121212121218</v>
+      </c>
+      <c r="AU10" t="inlineStr"/>
       <c r="AV10" t="n">
-        <v>0.004116798234448993</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>-7669380.075262426</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>-5.041666666666671</v>
-      </c>
-      <c r="AY10" t="inlineStr"/>
-      <c r="AZ10" t="inlineStr"/>
+        <v>0.08712121212121238</v>
+      </c>
+      <c r="AW10" t="inlineStr"/>
+      <c r="AX10" t="inlineStr"/>
+      <c r="AY10" t="n">
+        <v>-1.890151515151516</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>3.356060606060609</v>
+      </c>
       <c r="BA10" t="n">
-        <v>0.5833333333333428</v>
+        <v>6.306694394929707</v>
       </c>
       <c r="BB10" t="n">
-        <v>-8711041.666666666</v>
+        <v>-1.772331154684096</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.775000000000002</v>
+        <v>5.526044761338881</v>
       </c>
       <c r="BD10" t="n">
-        <v>-6.191666666666663</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>3.175466146054362</v>
-      </c>
+        <v>4.155303030303031</v>
+      </c>
+      <c r="BE10" t="inlineStr"/>
       <c r="BF10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>Qw81zU34</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45550.65625</v>
+      </c>
+      <c r="C11" t="n">
+        <v>101</v>
+      </c>
+      <c r="D11" t="n">
+        <v>133</v>
+      </c>
+      <c r="E11" t="n">
+        <v>273</v>
+      </c>
+      <c r="F11" t="n">
+        <v>39</v>
+      </c>
+      <c r="G11" t="n">
+        <v>55</v>
+      </c>
+      <c r="H11" t="n">
+        <v>551</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>67</v>
+      </c>
+      <c r="M11" t="n">
+        <v>260</v>
+      </c>
+      <c r="N11" t="n">
+        <v>-10</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>9</v>
+      </c>
+      <c r="T11" t="n">
+        <v>-6</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0.3100000000000001</v>
+      </c>
+      <c r="V11" t="n">
+        <v>-1.49</v>
+      </c>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>6</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>-12</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>-4</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>-7</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>74.45454545454545</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>75.7</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>-0.7644064872325771</v>
+      </c>
+      <c r="AN11" t="inlineStr"/>
+      <c r="AO11" t="inlineStr"/>
+      <c r="AP11" t="n">
+        <v>718014.6966560017</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>1817575.757575756</v>
+      </c>
+      <c r="AR11" t="inlineStr"/>
+      <c r="AS11" t="n">
+        <v>-0.3577231946797166</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>-1.884848484848476</v>
+      </c>
+      <c r="AU11" t="inlineStr"/>
+      <c r="AV11" t="n">
+        <v>-0.4363636363636361</v>
+      </c>
+      <c r="AW11" t="inlineStr"/>
+      <c r="AX11" t="inlineStr"/>
+      <c r="AY11" t="n">
+        <v>0.2666666666666728</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>-0.05454545454546178</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>0.007850241545895642</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>0.5515245623941283</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>-1.616094955768858</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>-0.01515151515151558</v>
+      </c>
+      <c r="BE11" t="inlineStr"/>
+      <c r="BF11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>fJaIWo3T</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45550.5</v>
+      </c>
+      <c r="C12" t="n">
+        <v>107</v>
+      </c>
+      <c r="D12" t="n">
+        <v>133</v>
+      </c>
+      <c r="E12" t="n">
+        <v>341</v>
+      </c>
+      <c r="F12" t="n">
+        <v>122</v>
+      </c>
+      <c r="G12" t="n">
+        <v>55</v>
+      </c>
+      <c r="H12" t="n">
+        <v>551</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>152</v>
+      </c>
+      <c r="M12" t="n">
+        <v>109</v>
+      </c>
+      <c r="N12" t="n">
+        <v>5</v>
+      </c>
+      <c r="O12" t="n">
+        <v>-1</v>
+      </c>
+      <c r="P12" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>-3</v>
+      </c>
+      <c r="T12" t="n">
+        <v>-2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>-1.215</v>
+      </c>
+      <c r="V12" t="n">
+        <v>-0.4450000000000001</v>
+      </c>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>-9</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>-9</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>74.75252525252526</v>
+      </c>
+      <c r="AL12" t="inlineStr"/>
+      <c r="AM12" t="n">
+        <v>-1.708333333333314</v>
+      </c>
+      <c r="AN12" t="inlineStr"/>
+      <c r="AO12" t="inlineStr"/>
+      <c r="AP12" t="n">
+        <v>766410.9848484849</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>2200303.03030303</v>
+      </c>
+      <c r="AR12" t="inlineStr"/>
+      <c r="AS12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>-3.951515151515139</v>
+      </c>
+      <c r="AU12" t="inlineStr"/>
+      <c r="AV12" t="n">
+        <v>0.09696969696969715</v>
+      </c>
+      <c r="AW12" t="inlineStr"/>
+      <c r="AX12" t="inlineStr"/>
+      <c r="AY12" t="n">
+        <v>-2.003030303030293</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>1.24545454545455</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>2.038636363636357</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>0.2786616161616173</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>2.409848484848496</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>3.366666666666674</v>
+      </c>
+      <c r="BE12" t="inlineStr"/>
+      <c r="BF12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>E3tkRPQj</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45550.5</v>
+      </c>
+      <c r="C13" t="n">
+        <v>101</v>
+      </c>
+      <c r="D13" t="n">
+        <v>135</v>
+      </c>
+      <c r="E13" t="n">
+        <v>736</v>
+      </c>
+      <c r="F13" t="n">
+        <v>292</v>
+      </c>
+      <c r="G13" t="n">
+        <v>55</v>
+      </c>
+      <c r="H13" t="n">
+        <v>551</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>165</v>
+      </c>
+      <c r="M13" t="n">
+        <v>163</v>
+      </c>
+      <c r="N13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O13" t="n">
+        <v>2</v>
+      </c>
+      <c r="P13" t="n">
+        <v>-2</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3</v>
+      </c>
+      <c r="T13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0.1000000000000001</v>
+      </c>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>-10</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>10</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>26</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>-26</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>75.40000000000001</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>74.8</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>-1.342891649413389</v>
+      </c>
+      <c r="AN13" t="inlineStr"/>
+      <c r="AO13" t="inlineStr"/>
+      <c r="AP13" t="n">
+        <v>1484381.469979296</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>2424924.242424242</v>
+      </c>
+      <c r="AR13" t="inlineStr"/>
+      <c r="AS13" t="n">
+        <v>-0.01666666666666661</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>-0.3121212121212409</v>
+      </c>
+      <c r="AU13" t="inlineStr"/>
+      <c r="AV13" t="n">
+        <v>-0.06666666666666665</v>
+      </c>
+      <c r="AW13" t="inlineStr"/>
+      <c r="AX13" t="inlineStr"/>
+      <c r="AY13" t="n">
+        <v>-4.384848484848487</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>2.242424242424235</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>0.849137336093861</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>-5.908730158730151</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>6.560259949390399</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>7.293939393939397</v>
+      </c>
+      <c r="BE13" t="inlineStr"/>
+      <c r="BF13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>M51AY7YG</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45550.5</v>
+      </c>
+      <c r="C14" t="n">
+        <v>101</v>
+      </c>
+      <c r="D14" t="n">
+        <v>135</v>
+      </c>
+      <c r="E14" t="n">
+        <v>858</v>
+      </c>
+      <c r="F14" t="n">
+        <v>579</v>
+      </c>
+      <c r="G14" t="n">
+        <v>55</v>
+      </c>
+      <c r="H14" t="n">
+        <v>551</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>286</v>
+      </c>
+      <c r="M14" t="n">
+        <v>211</v>
+      </c>
+      <c r="N14" t="n">
+        <v>-4</v>
+      </c>
+      <c r="O14" t="n">
+        <v>-3</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>-1</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3</v>
+      </c>
+      <c r="T14" t="n">
+        <v>-7</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="V14" t="n">
+        <v>-1.05</v>
+      </c>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>-4</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>-6</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>-4</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>-4</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>-4</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>69</v>
+      </c>
+      <c r="AL14" t="inlineStr"/>
+      <c r="AM14" t="n">
+        <v>-1.697542735042731</v>
+      </c>
+      <c r="AN14" t="inlineStr"/>
+      <c r="AO14" t="inlineStr"/>
+      <c r="AP14" t="n">
+        <v>-540347.8581603584</v>
+      </c>
+      <c r="AQ14" t="inlineStr"/>
+      <c r="AR14" t="inlineStr"/>
+      <c r="AS14" t="n">
+        <v>0.3119047619047619</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AU14" t="inlineStr"/>
+      <c r="AV14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr"/>
+      <c r="AX14" t="inlineStr"/>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr"/>
+      <c r="BA14" t="n">
+        <v>2.022212047212051</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>3.14760378510379</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>-3.080764143264147</v>
+      </c>
+      <c r="BD14" t="inlineStr"/>
+      <c r="BE14" t="inlineStr"/>
+      <c r="BF14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>hCffxjZi</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45550.41666666666</v>
+      </c>
+      <c r="C15" t="n">
+        <v>104</v>
+      </c>
+      <c r="D15" t="n">
+        <v>134</v>
+      </c>
+      <c r="E15" t="n">
+        <v>573</v>
+      </c>
+      <c r="F15" t="n">
+        <v>157</v>
+      </c>
+      <c r="G15" t="n">
+        <v>55</v>
+      </c>
+      <c r="H15" t="n">
+        <v>551</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>12</v>
+      </c>
+      <c r="M15" t="n">
+        <v>141</v>
+      </c>
+      <c r="N15" t="n">
+        <v>5</v>
+      </c>
+      <c r="O15" t="n">
+        <v>3</v>
+      </c>
+      <c r="P15" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>3</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="n">
+        <v>-8</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="V15" t="n">
+        <v>-1.3</v>
+      </c>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
+      <c r="AA15" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>16</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>-6</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>19</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>-19</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>76.40000000000001</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>82.66666666666667</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>-0.720588235294116</v>
+      </c>
+      <c r="AN15" t="inlineStr"/>
+      <c r="AO15" t="inlineStr"/>
+      <c r="AP15" t="n">
+        <v>3182247.899159662</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>2704242.424242425</v>
+      </c>
+      <c r="AR15" t="inlineStr"/>
+      <c r="AS15" t="n">
+        <v>0.4190009337068159</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>-0.2727272727272521</v>
+      </c>
+      <c r="AU15" t="inlineStr"/>
+      <c r="AV15" t="n">
+        <v>0.2818181818181817</v>
+      </c>
+      <c r="AW15" t="inlineStr"/>
+      <c r="AX15" t="inlineStr"/>
+      <c r="AY15" t="n">
+        <v>-0.7848484848484816</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>1.663636363636371</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>2.25700280112045</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>-0.3385854341736696</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>1.491479925303452</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>1.242424242424249</v>
+      </c>
+      <c r="BE15" t="inlineStr"/>
+      <c r="BF15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>8MPiooIM</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45549.66666666666</v>
+      </c>
+      <c r="C16" t="n">
+        <v>101</v>
+      </c>
+      <c r="D16" t="n">
+        <v>135</v>
+      </c>
+      <c r="E16" t="n">
+        <v>206</v>
+      </c>
+      <c r="F16" t="n">
+        <v>133</v>
+      </c>
+      <c r="G16" t="n">
+        <v>55</v>
+      </c>
+      <c r="H16" t="n">
+        <v>551</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="L16" t="n">
+        <v>243</v>
+      </c>
+      <c r="M16" t="n">
+        <v>226</v>
+      </c>
+      <c r="N16" t="n">
+        <v>17</v>
+      </c>
+      <c r="O16" t="n">
+        <v>5</v>
+      </c>
+      <c r="P16" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>3</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>8</v>
+      </c>
+      <c r="T16" t="n">
+        <v>-8</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="V16" t="n">
+        <v>-1.55</v>
+      </c>
+      <c r="W16" t="inlineStr"/>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>-16</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>22</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>-22</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>73.90909090909091</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>75.81818181818181</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>3.285648148148198</v>
+      </c>
+      <c r="AN16" t="inlineStr"/>
+      <c r="AO16" t="inlineStr"/>
+      <c r="AP16" t="n">
+        <v>29731203.7037037</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>43341010.1010101</v>
+      </c>
+      <c r="AR16" t="inlineStr"/>
+      <c r="AS16" t="n">
+        <v>0.8259259259259257</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>0.6313131313131919</v>
+      </c>
+      <c r="AU16" t="inlineStr"/>
+      <c r="AV16" t="n">
+        <v>0.7550505050505047</v>
+      </c>
+      <c r="AW16" t="inlineStr"/>
+      <c r="AX16" t="inlineStr"/>
+      <c r="AY16" t="n">
+        <v>-4.671717171717173</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>7.807575757575748</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>10.02546296296298</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>-0.6083333333333343</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>10.06574074074074</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>11.22676767676766</v>
+      </c>
+      <c r="BE16" t="inlineStr"/>
+      <c r="BF16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>CGH7Enso</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45549.58333333334</v>
+      </c>
+      <c r="C17" t="n">
+        <v>101</v>
+      </c>
+      <c r="D17" t="n">
+        <v>134</v>
+      </c>
+      <c r="E17" t="n">
+        <v>342</v>
+      </c>
+      <c r="F17" t="n">
+        <v>33</v>
+      </c>
+      <c r="G17" t="n">
+        <v>55</v>
+      </c>
+      <c r="H17" t="n">
+        <v>551</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
+        <v>198</v>
+      </c>
+      <c r="M17" t="n">
+        <v>83</v>
+      </c>
+      <c r="N17" t="n">
+        <v>-4</v>
+      </c>
+      <c r="O17" t="n">
+        <v>-2</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>-1</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" t="n">
+        <v>-0.71</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="W17" t="inlineStr"/>
+      <c r="X17" t="inlineStr"/>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="inlineStr"/>
+      <c r="AA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>7</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>7</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>-22</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>22</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>74.09090909090909</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>75.8</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>-1.256060606060601</v>
+      </c>
+      <c r="AN17" t="inlineStr"/>
+      <c r="AO17" t="inlineStr"/>
+      <c r="AP17" t="n">
+        <v>-10922651.51515151</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>-10519166.66666667</v>
+      </c>
+      <c r="AR17" t="inlineStr"/>
+      <c r="AS17" t="n">
+        <v>-0.4074074074074074</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>-0.966666666666697</v>
+      </c>
+      <c r="AU17" t="inlineStr"/>
+      <c r="AV17" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="AW17" t="inlineStr"/>
+      <c r="AX17" t="inlineStr"/>
+      <c r="AY17" t="n">
+        <v>2.233333333333327</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>-6.599999999999994</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>-9.186026936026948</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>2.043434343434338</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>-10.72491582491584</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>-8.566666666666677</v>
+      </c>
+      <c r="BE17" t="inlineStr"/>
+      <c r="BF17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>0dMqm7mA</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45549.5</v>
+      </c>
+      <c r="C18" t="n">
+        <v>101</v>
+      </c>
+      <c r="D18" t="n">
+        <v>135</v>
+      </c>
+      <c r="E18" t="n">
+        <v>448</v>
+      </c>
+      <c r="F18" t="n">
+        <v>370</v>
+      </c>
+      <c r="G18" t="n">
+        <v>55</v>
+      </c>
+      <c r="H18" t="n">
+        <v>551</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="L18" t="n">
+        <v>152</v>
+      </c>
+      <c r="M18" t="n">
+        <v>163</v>
+      </c>
+      <c r="N18" t="n">
+        <v>15</v>
+      </c>
+      <c r="O18" t="n">
+        <v>-1</v>
+      </c>
+      <c r="P18" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T18" t="n">
+        <v>-4</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.045</v>
+      </c>
+      <c r="V18" t="n">
+        <v>-0.91</v>
+      </c>
+      <c r="W18" t="inlineStr"/>
+      <c r="X18" t="inlineStr"/>
+      <c r="Y18" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>16</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>-16</v>
+      </c>
+      <c r="AK18" t="inlineStr"/>
+      <c r="AL18" t="n">
+        <v>68.09999999999999</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>-0.8177114280055946</v>
+      </c>
+      <c r="AN18" t="inlineStr"/>
+      <c r="AO18" t="inlineStr"/>
+      <c r="AP18" t="n">
+        <v>2842952.564864328</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>5270505.050505048</v>
+      </c>
+      <c r="AR18" t="inlineStr"/>
+      <c r="AS18" t="n">
+        <v>0.2963012477718359</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>-0.6936026936026565</v>
+      </c>
+      <c r="AU18" t="inlineStr"/>
+      <c r="AV18" t="n">
+        <v>0.2508417508417502</v>
+      </c>
+      <c r="AW18" t="inlineStr"/>
+      <c r="AX18" t="inlineStr"/>
+      <c r="AY18" t="n">
+        <v>0.3670033670033668</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>2.882828282828271</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>0.2038671023965151</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>0.4678896811249729</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>1.472856011091309</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>1.458585858585863</v>
+      </c>
+      <c r="BE18" t="inlineStr"/>
+      <c r="BF18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>vsYzkTIc</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45548.65625</v>
+      </c>
+      <c r="C19" t="n">
+        <v>104</v>
+      </c>
+      <c r="D19" t="n">
+        <v>135</v>
+      </c>
+      <c r="E19" t="n">
+        <v>528</v>
+      </c>
+      <c r="F19" t="n">
+        <v>545</v>
+      </c>
+      <c r="G19" t="n">
+        <v>55</v>
+      </c>
+      <c r="H19" t="n">
+        <v>551</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="L19" t="n">
+        <v>9</v>
+      </c>
+      <c r="M19" t="n">
+        <v>37</v>
+      </c>
+      <c r="N19" t="n">
+        <v>-10</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>5</v>
+      </c>
+      <c r="U19" t="n">
+        <v>-0.3499999999999999</v>
+      </c>
+      <c r="V19" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="W19" t="inlineStr"/>
+      <c r="X19" t="inlineStr"/>
+      <c r="Y19" t="inlineStr"/>
+      <c r="Z19" t="inlineStr"/>
+      <c r="AA19" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>-13</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>13</v>
+      </c>
+      <c r="AK19" t="inlineStr"/>
+      <c r="AL19" t="inlineStr"/>
+      <c r="AM19" t="n">
+        <v>1.015389185977426</v>
+      </c>
+      <c r="AN19" t="inlineStr"/>
+      <c r="AO19" t="inlineStr"/>
+      <c r="AP19" t="n">
+        <v>-6844851.45573381</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>-7906555.134680135</v>
+      </c>
+      <c r="AR19" t="inlineStr"/>
+      <c r="AS19" t="n">
+        <v>-0.7010101010101009</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>-0.05168350168352731</v>
+      </c>
+      <c r="AU19" t="inlineStr"/>
+      <c r="AV19" t="n">
+        <v>-0.146043771043771</v>
+      </c>
+      <c r="AW19" t="inlineStr"/>
+      <c r="AX19" t="inlineStr"/>
+      <c r="AY19" t="n">
+        <v>0.7564814814814831</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>-5.161447811447815</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>-7.140106951871672</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>-1.052881758764116</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>-5.771122994652416</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>-5.500757575757575</v>
+      </c>
+      <c r="BE19" t="inlineStr"/>
+      <c r="BF19" t="n">
         <v>0</v>
       </c>
     </row>

--- a/data/france/p6_deployment/data_preparation/df_tagged.xlsx
+++ b/data/france/p6_deployment/data_preparation/df_tagged.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BF6"/>
+  <dimension ref="A1:BF19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -530,84 +530,84 @@
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_last_match_goal_attempts</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goal_attempts_against</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_interceptions</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_interceptions_against</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_shots_on_goal</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_shots_on_goal_against</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_n_matches_last_days</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_n_matches_last_days_against</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_last_match_goals</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_goals_against</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_n_matches_last_days</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_n_matches_last_days_against</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_fouls</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_fouls_against</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_interceptions</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_interceptions_against</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_ball_possession</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_ball_possession_against</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_points</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_points_against</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_shots_on_goal</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_shots_on_goal_against</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goal_attempts</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goal_attempts_against</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_ball_possession</t>
-        </is>
-      </c>
-      <c r="AJ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_ball_possession_against</t>
-        </is>
-      </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>mean_last_match_mean_rat_player_start_home_against</t>
@@ -620,97 +620,97 @@
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_age_player_sub</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_sub</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_start</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_start</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_n_player_miss</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_start</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_sub</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_rat_player_miss</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_start</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_pot_player_miss</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_start</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_val_player_miss</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_start</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_miss</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_miss</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_sub</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_sub</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_int_rep_player_miss</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_miss</t>
-        </is>
-      </c>
-      <c r="AO1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_pot_player_miss</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_val_player_sub</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_sub</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_start</t>
-        </is>
-      </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_start</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_sub</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_val_player_miss</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_start</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_rat_player_miss</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_start</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_sub</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_sub</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_sub</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_miss</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_start</t>
-        </is>
-      </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_start</t>
-        </is>
-      </c>
-      <c r="BE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_n_player_miss</t>
         </is>
       </c>
       <c r="BF1" s="1" t="inlineStr">
@@ -722,23 +722,23 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Qw81zU34</t>
+          <t>Ee8YgF0f</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45550.65625</v>
+        <v>45564.65625</v>
       </c>
       <c r="C2" t="n">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D2" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E2" t="n">
-        <v>273</v>
+        <v>736</v>
       </c>
       <c r="F2" t="n">
-        <v>39</v>
+        <v>303</v>
       </c>
       <c r="G2" t="n">
         <v>55</v>
@@ -760,134 +760,124 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>67</v>
+        <v>315</v>
       </c>
       <c r="M2" t="n">
-        <v>260</v>
+        <v>163</v>
       </c>
       <c r="N2" t="n">
-        <v>-10</v>
+        <v>-11</v>
       </c>
       <c r="O2" t="n">
+        <v>-2</v>
+      </c>
+      <c r="P2" t="n">
         <v>1</v>
       </c>
-      <c r="P2" t="n">
-        <v>0</v>
-      </c>
       <c r="Q2" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>0.3100000000000001</v>
+        <v>-0.8149999999999999</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.49</v>
+        <v>-0.06499999999999995</v>
       </c>
       <c r="U2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>-3</v>
+        <v>7.5</v>
       </c>
       <c r="W2" t="inlineStr"/>
       <c r="X2" t="inlineStr"/>
       <c r="Y2" t="n">
-        <v>-4</v>
+        <v>0.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>-7</v>
-      </c>
-      <c r="AA2" t="inlineStr"/>
-      <c r="AB2" t="inlineStr"/>
+        <v>0.5</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>-0.5</v>
+      </c>
       <c r="AC2" t="n">
-        <v>3</v>
+        <v>-2</v>
       </c>
       <c r="AD2" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>9</v>
+        <v>-2.5</v>
       </c>
       <c r="AF2" t="n">
-        <v>-6</v>
+        <v>6.5</v>
       </c>
       <c r="AG2" t="n">
-        <v>6</v>
+        <v>-7.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>-12</v>
+        <v>7.5</v>
       </c>
       <c r="AI2" t="n">
-        <v>-1</v>
+        <v>-0.3333333333333335</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="AK2" t="n">
-        <v>74.45454545454545</v>
+        <v>72.36666666666667</v>
       </c>
       <c r="AL2" t="n">
-        <v>75.7</v>
+        <v>74.4983164983165</v>
       </c>
       <c r="AM2" t="n">
-        <v>-1</v>
+        <v>-3.085385631525334</v>
       </c>
       <c r="AN2" t="n">
-        <v>-0.5</v>
+        <v>-0.927918364315417</v>
       </c>
       <c r="AO2" t="n">
-        <v>-10</v>
+        <v>-11242348.48484848</v>
       </c>
       <c r="AP2" t="n">
-        <v>718014.6966560017</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>0.5515245623941283</v>
-      </c>
+        <v>-3.802525252525253</v>
+      </c>
+      <c r="AQ2" t="inlineStr"/>
       <c r="AR2" t="n">
-        <v>1817575.757575756</v>
+        <v>0.2843434343434268</v>
       </c>
       <c r="AS2" t="n">
-        <v>-1.884848484848476</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>0.007850241545895642</v>
-      </c>
+        <v>-5.267968551056796</v>
+      </c>
+      <c r="AT2" t="inlineStr"/>
       <c r="AU2" t="n">
-        <v>-10400000</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>0.2666666666666728</v>
-      </c>
+        <v>-0.458333333333333</v>
+      </c>
+      <c r="AV2" t="inlineStr"/>
       <c r="AW2" t="n">
-        <v>-6</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>-0.4363636363636361</v>
-      </c>
+        <v>-6.520959595959596</v>
+      </c>
+      <c r="AX2" t="inlineStr"/>
       <c r="AY2" t="n">
-        <v>-0.3577231946797166</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>-1.616094955768858</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>-0.7644064872325771</v>
-      </c>
+        <v>1.652020202020196</v>
+      </c>
+      <c r="AZ2" t="inlineStr"/>
+      <c r="BA2" t="inlineStr"/>
       <c r="BB2" t="n">
-        <v>0.5</v>
+        <v>0.7920136236312771</v>
       </c>
       <c r="BC2" t="n">
-        <v>-0.05454545454546178</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>-0.01515151515151558</v>
-      </c>
+        <v>-0.3828765597147952</v>
+      </c>
+      <c r="BD2" t="inlineStr"/>
       <c r="BE2" t="n">
-        <v>0</v>
+        <v>-6488268.895626431</v>
       </c>
       <c r="BF2" t="n">
         <v>0</v>
@@ -896,23 +886,23 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>E3tkRPQj</t>
+          <t>zZA5hNtm</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45550.5</v>
+        <v>45564.5</v>
       </c>
       <c r="C3" t="n">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="D3" t="n">
         <v>135</v>
       </c>
       <c r="E3" t="n">
-        <v>736</v>
+        <v>858</v>
       </c>
       <c r="F3" t="n">
-        <v>292</v>
+        <v>362</v>
       </c>
       <c r="G3" t="n">
         <v>55</v>
@@ -934,19 +924,19 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="M3" t="n">
-        <v>163</v>
+        <v>204</v>
       </c>
       <c r="N3" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="O3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P3" t="n">
-        <v>-2</v>
+        <v>3</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -955,117 +945,103 @@
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>0.3</v>
+        <v>1.165</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1000000000000001</v>
+        <v>-1.405</v>
       </c>
       <c r="U3" t="n">
-        <v>3</v>
+        <v>6.5</v>
       </c>
       <c r="V3" t="n">
-        <v>-1</v>
-      </c>
-      <c r="W3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X3" t="n">
-        <v>0</v>
-      </c>
+        <v>-7</v>
+      </c>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr"/>
       <c r="Y3" t="n">
-        <v>-10</v>
+        <v>4</v>
       </c>
       <c r="Z3" t="n">
-        <v>10</v>
-      </c>
-      <c r="AA3" t="inlineStr"/>
-      <c r="AB3" t="inlineStr"/>
+        <v>-4</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>-0.5</v>
+      </c>
       <c r="AC3" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>-3</v>
+        <v>-1.5</v>
       </c>
       <c r="AE3" t="n">
-        <v>3</v>
+        <v>-9.5</v>
       </c>
       <c r="AF3" t="n">
-        <v>-1</v>
+        <v>-7</v>
       </c>
       <c r="AG3" t="n">
-        <v>4</v>
+        <v>-4.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>2</v>
+        <v>4.5</v>
       </c>
       <c r="AI3" t="n">
-        <v>26</v>
+        <v>1.166666666666667</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-26</v>
+        <v>-0.8333333333333335</v>
       </c>
       <c r="AK3" t="n">
-        <v>75.40000000000001</v>
+        <v>69</v>
       </c>
       <c r="AL3" t="n">
-        <v>74.8</v>
+        <v>75.00984848484849</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>0.2478018079701521</v>
       </c>
       <c r="AN3" t="n">
-        <v>10.33333333333334</v>
+        <v>1.682338049162723</v>
       </c>
       <c r="AO3" t="n">
-        <v>-137</v>
+        <v>2599573.863636363</v>
       </c>
       <c r="AP3" t="n">
-        <v>1484381.469979296</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>-5.908730158730151</v>
-      </c>
+        <v>-1.017045454545453</v>
+      </c>
+      <c r="AQ3" t="inlineStr"/>
       <c r="AR3" t="n">
-        <v>2424924.242424242</v>
+        <v>1.068181818181813</v>
       </c>
       <c r="AS3" t="n">
-        <v>-0.3121212121212409</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>0.849137336093861</v>
-      </c>
+        <v>4.609896851944058</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
       <c r="AU3" t="n">
-        <v>-1900000</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>-4.384848484848487</v>
-      </c>
+        <v>0.2613636363636367</v>
+      </c>
+      <c r="AV3" t="inlineStr"/>
       <c r="AW3" t="n">
-        <v>-135</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>-0.06666666666666665</v>
-      </c>
+        <v>2.14772727272728</v>
+      </c>
+      <c r="AX3" t="inlineStr"/>
       <c r="AY3" t="n">
-        <v>-0.01666666666666661</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>6.560259949390399</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>-1.342891649413389</v>
-      </c>
+        <v>0.176136363636374</v>
+      </c>
+      <c r="AZ3" t="inlineStr"/>
+      <c r="BA3" t="inlineStr"/>
       <c r="BB3" t="n">
-        <v>-4.666666666666668</v>
+        <v>0.8389689118501167</v>
       </c>
       <c r="BC3" t="n">
-        <v>2.242424242424235</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>7.293939393939397</v>
-      </c>
+        <v>0.2597222222222224</v>
+      </c>
+      <c r="BD3" t="inlineStr"/>
       <c r="BE3" t="n">
-        <v>-2</v>
+        <v>2183541.233475202</v>
       </c>
       <c r="BF3" t="n">
         <v>0</v>
@@ -1074,23 +1050,23 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>fJaIWo3T</t>
+          <t>p4Um50Qh</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45550.5</v>
+        <v>45564.5</v>
       </c>
       <c r="C4" t="n">
         <v>101</v>
       </c>
       <c r="D4" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E4" t="n">
-        <v>341</v>
+        <v>431</v>
       </c>
       <c r="F4" t="n">
-        <v>122</v>
+        <v>579</v>
       </c>
       <c r="G4" t="n">
         <v>55</v>
@@ -1112,136 +1088,110 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>152</v>
+        <v>315</v>
       </c>
       <c r="M4" t="n">
-        <v>109</v>
+        <v>10</v>
       </c>
       <c r="N4" t="n">
-        <v>5</v>
+        <v>-2</v>
       </c>
       <c r="O4" t="n">
         <v>-1</v>
       </c>
       <c r="P4" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>-2</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.1599999999999999</v>
+      </c>
+      <c r="T4" t="n">
+        <v>-0.3950000000000002</v>
+      </c>
+      <c r="U4" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="V4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE4" t="n">
         <v>4</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="n">
-        <v>-1.215</v>
-      </c>
-      <c r="T4" t="n">
-        <v>-0.4450000000000001</v>
-      </c>
-      <c r="U4" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="V4" t="n">
+      <c r="AF4" t="n">
         <v>1.5</v>
       </c>
-      <c r="W4" t="n">
-        <v>1</v>
-      </c>
-      <c r="X4" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AA4" t="inlineStr"/>
-      <c r="AB4" t="inlineStr"/>
-      <c r="AC4" t="n">
-        <v>-2.5</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>-3</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>-2</v>
-      </c>
       <c r="AG4" t="n">
-        <v>-9</v>
+        <v>4.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>-9</v>
+        <v>-4.5</v>
       </c>
       <c r="AI4" t="n">
-        <v>-3.5</v>
+        <v>-1.666666666666667</v>
       </c>
       <c r="AJ4" t="n">
-        <v>3.5</v>
+        <v>1.833333333333333</v>
       </c>
       <c r="AK4" t="n">
-        <v>74.75252525252526</v>
+        <v>74.40909090909092</v>
       </c>
       <c r="AL4" t="inlineStr"/>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>3.138950387847448</v>
       </c>
       <c r="AN4" t="n">
-        <v>-10</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>4</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>766410.9848484849</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>0.2786616161616173</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>2200303.03030303</v>
-      </c>
+        <v>-5.728816038678559</v>
+      </c>
+      <c r="AO4" t="inlineStr"/>
+      <c r="AP4" t="inlineStr"/>
+      <c r="AQ4" t="inlineStr"/>
+      <c r="AR4" t="inlineStr"/>
       <c r="AS4" t="n">
-        <v>-3.951515151515139</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>2.038636363636357</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>2400000</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>-2.003030303030293</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>0.09696969696969715</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>2.409848484848496</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>-1.708333333333314</v>
-      </c>
+        <v>-3.479064181413932</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AU4" t="inlineStr"/>
+      <c r="AV4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr"/>
+      <c r="AX4" t="inlineStr"/>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr"/>
+      <c r="BA4" t="inlineStr"/>
       <c r="BB4" t="n">
-        <v>4</v>
+        <v>-2.313829117209877</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.24545454545455</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>3.366666666666674</v>
-      </c>
+        <v>0.001412231559289934</v>
+      </c>
+      <c r="BD4" t="inlineStr"/>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>-3221128.03893854</v>
       </c>
       <c r="BF4" t="n">
         <v>0</v>
@@ -1250,23 +1200,23 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>M51AY7YG</t>
+          <t>bDeVnJAO</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45550.5</v>
+        <v>45564.41666666666</v>
       </c>
       <c r="C5" t="n">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="D5" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E5" t="n">
-        <v>858</v>
+        <v>341</v>
       </c>
       <c r="F5" t="n">
-        <v>579</v>
+        <v>39</v>
       </c>
       <c r="G5" t="n">
         <v>55</v>
@@ -1288,124 +1238,128 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>286</v>
+        <v>152</v>
       </c>
       <c r="M5" t="n">
-        <v>211</v>
+        <v>138</v>
       </c>
       <c r="N5" t="n">
-        <v>-4</v>
+        <v>-23</v>
       </c>
       <c r="O5" t="n">
         <v>-3</v>
       </c>
       <c r="P5" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0.84</v>
+        <v>0.345</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.05</v>
+        <v>-0.6733333333333335</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>-3.666666666666666</v>
       </c>
       <c r="V5" t="n">
-        <v>-2</v>
+        <v>-9.333333333333332</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="Y5" t="n">
-        <v>-4</v>
+        <v>1.166666666666667</v>
       </c>
       <c r="Z5" t="n">
-        <v>-4</v>
-      </c>
-      <c r="AA5" t="inlineStr"/>
-      <c r="AB5" t="inlineStr"/>
+        <v>-3.5</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>-0.5</v>
+      </c>
       <c r="AC5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD5" t="n">
-        <v>-1</v>
+        <v>-0.5</v>
       </c>
       <c r="AE5" t="n">
-        <v>3</v>
+        <v>-1.5</v>
       </c>
       <c r="AF5" t="n">
-        <v>-7</v>
+        <v>-1.166666666666666</v>
       </c>
       <c r="AG5" t="n">
-        <v>-4</v>
+        <v>-5.333333333333336</v>
       </c>
       <c r="AH5" t="n">
-        <v>-6</v>
+        <v>5.333333333333336</v>
       </c>
       <c r="AI5" t="n">
-        <v>4</v>
+        <v>0.8333333333333333</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-4</v>
+        <v>-0.6666666666666667</v>
       </c>
       <c r="AK5" t="n">
-        <v>69</v>
-      </c>
-      <c r="AL5" t="inlineStr"/>
+        <v>73.62289562289563</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>76.03181818181818</v>
+      </c>
       <c r="AM5" t="n">
-        <v>0.3999999999999999</v>
+        <v>-0.3403477159534525</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.699999999999989</v>
+        <v>-3.545211907573531</v>
       </c>
       <c r="AO5" t="n">
-        <v>210</v>
+        <v>-4842765.151515152</v>
       </c>
       <c r="AP5" t="n">
-        <v>-540347.8581603584</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>3.14760378510379</v>
-      </c>
-      <c r="AR5" t="inlineStr"/>
-      <c r="AS5" t="inlineStr"/>
-      <c r="AT5" t="n">
-        <v>2.022212047212051</v>
-      </c>
+        <v>-3.435353535353535</v>
+      </c>
+      <c r="AQ5" t="inlineStr"/>
+      <c r="AR5" t="n">
+        <v>-0.7873106060606005</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>-3.376833263990022</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
       <c r="AU5" t="n">
-        <v>-75000</v>
+        <v>-0.773800505050505</v>
       </c>
       <c r="AV5" t="inlineStr"/>
       <c r="AW5" t="n">
-        <v>206</v>
+        <v>-3.889267676767673</v>
       </c>
       <c r="AX5" t="inlineStr"/>
       <c r="AY5" t="n">
-        <v>0.3119047619047619</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>-3.080764143264147</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>-1.697542735042731</v>
-      </c>
+        <v>-1.004861111111126</v>
+      </c>
+      <c r="AZ5" t="inlineStr"/>
+      <c r="BA5" t="inlineStr"/>
       <c r="BB5" t="n">
-        <v>3</v>
-      </c>
-      <c r="BC5" t="inlineStr"/>
+        <v>-0.911699122908999</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>-0.549316101518619</v>
+      </c>
       <c r="BD5" t="inlineStr"/>
       <c r="BE5" t="n">
-        <v>3</v>
+        <v>-3755888.471469303</v>
       </c>
       <c r="BF5" t="n">
         <v>0</v>
@@ -1414,20 +1368,20 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hCffxjZi</t>
+          <t>lxyu7Met</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45550.41666666666</v>
+        <v>45563.66666666666</v>
       </c>
       <c r="C6" t="n">
         <v>101</v>
       </c>
       <c r="D6" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E6" t="n">
-        <v>573</v>
+        <v>47</v>
       </c>
       <c r="F6" t="n">
         <v>157</v>
@@ -1452,136 +1406,2260 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>12</v>
+        <v>128</v>
       </c>
       <c r="M6" t="n">
-        <v>141</v>
+        <v>234</v>
       </c>
       <c r="N6" t="n">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="O6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P6" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="Q6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>1.76</v>
+        <v>0.9300000000000002</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.3</v>
+        <v>-0.6899999999999997</v>
       </c>
       <c r="U6" t="n">
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="V6" t="n">
-        <v>-6</v>
+        <v>-6.5</v>
       </c>
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr"/>
       <c r="Y6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>-4</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>-4</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>22</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>-22</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>-2.333333333333333</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>73.53522727272727</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>79.28333333333333</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>-2.797321428571426</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>5.300099206349216</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>7104848.484848484</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>-2.435858585858583</v>
+      </c>
+      <c r="AQ6" t="inlineStr"/>
+      <c r="AR6" t="n">
+        <v>3.790151515151507</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>3.365277777777777</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AU6" t="n">
+        <v>0.03080808080808062</v>
+      </c>
+      <c r="AV6" t="inlineStr"/>
+      <c r="AW6" t="n">
+        <v>2.131060606060601</v>
+      </c>
+      <c r="AX6" t="inlineStr"/>
+      <c r="AY6" t="n">
+        <v>2.878787878787875</v>
+      </c>
+      <c r="AZ6" t="inlineStr"/>
+      <c r="BA6" t="inlineStr"/>
+      <c r="BB6" t="n">
+        <v>1.683333333333309</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>0.09662698412698401</v>
+      </c>
+      <c r="BD6" t="inlineStr"/>
+      <c r="BE6" t="n">
+        <v>9075744.047619047</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>xb7MlutC</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45563.58333333334</v>
+      </c>
+      <c r="C7" t="n">
+        <v>102</v>
+      </c>
+      <c r="D7" t="n">
+        <v>133</v>
+      </c>
+      <c r="E7" t="n">
+        <v>194</v>
+      </c>
+      <c r="F7" t="n">
+        <v>545</v>
+      </c>
+      <c r="G7" t="n">
+        <v>55</v>
+      </c>
+      <c r="H7" t="n">
+        <v>551</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>152</v>
+      </c>
+      <c r="M7" t="n">
+        <v>204</v>
+      </c>
+      <c r="N7" t="n">
+        <v>-5</v>
+      </c>
+      <c r="O7" t="n">
+        <v>-2</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>-0.05500000000000016</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.3399999999999999</v>
+      </c>
+      <c r="U7" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="V7" t="n">
+        <v>5</v>
+      </c>
+      <c r="W7" t="n">
+        <v>2</v>
+      </c>
+      <c r="X7" t="n">
+        <v>-8</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>-33.5</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>69.59999999999999</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>71</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>-1.598106060606064</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>-5.377840909090907</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>-7191464.646464647</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>0.05202020202020208</v>
+      </c>
+      <c r="AQ7" t="inlineStr"/>
+      <c r="AR7" t="n">
+        <v>-5.054545454545448</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>-5.752840909090907</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AU7" t="n">
+        <v>-0.3032828282828282</v>
+      </c>
+      <c r="AV7" t="inlineStr"/>
+      <c r="AW7" t="n">
+        <v>-4.281313131313141</v>
+      </c>
+      <c r="AX7" t="inlineStr"/>
+      <c r="AY7" t="n">
+        <v>3.191919191919197</v>
+      </c>
+      <c r="AZ7" t="inlineStr"/>
+      <c r="BA7" t="inlineStr"/>
+      <c r="BB7" t="n">
+        <v>1.265719696969711</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>-0.6507575757575756</v>
+      </c>
+      <c r="BD7" t="inlineStr"/>
+      <c r="BE7" t="n">
+        <v>-6822511.837121211</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>v3PZcqJP</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45563.5</v>
+      </c>
+      <c r="C8" t="n">
+        <v>104</v>
+      </c>
+      <c r="D8" t="n">
+        <v>133</v>
+      </c>
+      <c r="E8" t="n">
+        <v>273</v>
+      </c>
+      <c r="F8" t="n">
+        <v>370</v>
+      </c>
+      <c r="G8" t="n">
+        <v>55</v>
+      </c>
+      <c r="H8" t="n">
+        <v>551</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>97</v>
+      </c>
+      <c r="M8" t="n">
+        <v>163</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O8" t="n">
         <v>-3</v>
       </c>
-      <c r="Z6" t="n">
+      <c r="P8" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>-1</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>-0.395</v>
+      </c>
+      <c r="T8" t="n">
+        <v>-1.126666666666666</v>
+      </c>
+      <c r="U8" t="n">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="V8" t="n">
+        <v>-4.333333333333334</v>
+      </c>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="n">
         <v>3</v>
       </c>
-      <c r="AA6" t="inlineStr"/>
-      <c r="AB6" t="inlineStr"/>
-      <c r="AC6" t="n">
+      <c r="Z8" t="n">
+        <v>-3.833333333333333</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>-0.6666666666666667</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>-1.666666666666667</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>-1.333333333333334</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>-5.833333333333334</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>75.67171717171718</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>71.1037037037037</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>1.241081468299132</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>-0.1876154386586393</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>1217045.454545453</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>2.677272727272733</v>
+      </c>
+      <c r="AQ8" t="inlineStr"/>
+      <c r="AR8" t="n">
+        <v>0.1159090909090992</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>0.4598437599850911</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AU8" t="n">
+        <v>0.1318181818181821</v>
+      </c>
+      <c r="AV8" t="inlineStr"/>
+      <c r="AW8" t="n">
+        <v>2.220454545454544</v>
+      </c>
+      <c r="AX8" t="inlineStr"/>
+      <c r="AY8" t="n">
+        <v>-2.711363636363586</v>
+      </c>
+      <c r="AZ8" t="inlineStr"/>
+      <c r="BA8" t="inlineStr"/>
+      <c r="BB8" t="n">
+        <v>-0.239146338099772</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>-0.005612001405513656</v>
+      </c>
+      <c r="BD8" t="inlineStr"/>
+      <c r="BE8" t="n">
+        <v>-358065.314729318</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>zBdshgV6</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45562.66666666666</v>
+      </c>
+      <c r="C9" t="n">
+        <v>101</v>
+      </c>
+      <c r="D9" t="n">
+        <v>135</v>
+      </c>
+      <c r="E9" t="n">
+        <v>206</v>
+      </c>
+      <c r="F9" t="n">
+        <v>399</v>
+      </c>
+      <c r="G9" t="n">
+        <v>55</v>
+      </c>
+      <c r="H9" t="n">
+        <v>551</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>40</v>
+      </c>
+      <c r="M9" t="n">
+        <v>234</v>
+      </c>
+      <c r="N9" t="n">
+        <v>11</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1.645</v>
+      </c>
+      <c r="T9" t="n">
+        <v>-0.615</v>
+      </c>
+      <c r="U9" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="V9" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>-8</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>25</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>-25</v>
+      </c>
+      <c r="AI9" t="n">
         <v>3</v>
       </c>
-      <c r="AD6" t="n">
+      <c r="AJ9" t="n">
         <v>-3</v>
       </c>
-      <c r="AE6" t="n">
+      <c r="AK9" t="n">
+        <v>74.40454545454546</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>69.72727272727273</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>-0.6117485810113514</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>6.4954512506757</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>39057037.03703704</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>-1.718518518518518</v>
+      </c>
+      <c r="AQ9" t="inlineStr"/>
+      <c r="AR9" t="n">
+        <v>7.275925925925904</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>5.660829770504691</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AU9" t="n">
+        <v>0.4824074074074072</v>
+      </c>
+      <c r="AV9" t="inlineStr"/>
+      <c r="AW9" t="n">
+        <v>6.438888888888897</v>
+      </c>
+      <c r="AX9" t="inlineStr"/>
+      <c r="AY9" t="n">
+        <v>2.889814814814827</v>
+      </c>
+      <c r="AZ9" t="inlineStr"/>
+      <c r="BA9" t="inlineStr"/>
+      <c r="BB9" t="n">
+        <v>3.800400971792243</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>0.4593682429111996</v>
+      </c>
+      <c r="BD9" t="inlineStr"/>
+      <c r="BE9" t="n">
+        <v>25131457.61155339</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>MRfkjXaJ</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45562.58333333334</v>
+      </c>
+      <c r="C10" t="n">
+        <v>101</v>
+      </c>
+      <c r="D10" t="n">
+        <v>134</v>
+      </c>
+      <c r="E10" t="n">
+        <v>342</v>
+      </c>
+      <c r="F10" t="n">
+        <v>133</v>
+      </c>
+      <c r="G10" t="n">
+        <v>55</v>
+      </c>
+      <c r="H10" t="n">
+        <v>551</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>128</v>
+      </c>
+      <c r="M10" t="n">
+        <v>7</v>
+      </c>
+      <c r="N10" t="n">
+        <v>-2</v>
+      </c>
+      <c r="O10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="P10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.6399999999999999</v>
+      </c>
+      <c r="T10" t="n">
+        <v>-0.6100000000000001</v>
+      </c>
+      <c r="U10" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="V10" t="n">
+        <v>-10.5</v>
+      </c>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>75.29545454545455</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>78.90909090909091</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>-0.1747159090909136</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>-3.426136363636374</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>-3844943.181818183</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>-2.665909090909089</v>
+      </c>
+      <c r="AQ10" t="inlineStr"/>
+      <c r="AR10" t="n">
+        <v>-2.545454545454547</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>-4.346117424242422</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AU10" t="n">
+        <v>-0.3795454545454546</v>
+      </c>
+      <c r="AV10" t="inlineStr"/>
+      <c r="AW10" t="n">
+        <v>-5.490909090909099</v>
+      </c>
+      <c r="AX10" t="inlineStr"/>
+      <c r="AY10" t="n">
+        <v>0.4454545454545382</v>
+      </c>
+      <c r="AZ10" t="inlineStr"/>
+      <c r="BA10" t="inlineStr"/>
+      <c r="BB10" t="n">
+        <v>0.377462121212119</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>-0.2495265151515151</v>
+      </c>
+      <c r="BD10" t="inlineStr"/>
+      <c r="BE10" t="n">
+        <v>-2609782.196969697</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>S66OuPup</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45557.65625</v>
+      </c>
+      <c r="C11" t="n">
+        <v>104</v>
+      </c>
+      <c r="D11" t="n">
+        <v>133</v>
+      </c>
+      <c r="E11" t="n">
+        <v>56</v>
+      </c>
+      <c r="F11" t="n">
+        <v>303</v>
+      </c>
+      <c r="G11" t="n">
+        <v>55</v>
+      </c>
+      <c r="H11" t="n">
+        <v>551</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>97</v>
+      </c>
+      <c r="M11" t="n">
+        <v>163</v>
+      </c>
+      <c r="N11" t="n">
+        <v>10</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>-0.655</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V11" t="n">
+        <v>10</v>
+      </c>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>-22.5</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>72.95</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>73.53636363636363</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>0.4400023505345558</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>0.4984093229032851</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>-5334999.999999998</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>2.244444444444447</v>
+      </c>
+      <c r="AQ11" t="inlineStr"/>
+      <c r="AR11" t="n">
+        <v>-1.01944444444446</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>0.4850551891236989</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AU11" t="n">
+        <v>0.4194444444444447</v>
+      </c>
+      <c r="AV11" t="inlineStr"/>
+      <c r="AW11" t="n">
+        <v>-0.2222222222222285</v>
+      </c>
+      <c r="AX11" t="inlineStr"/>
+      <c r="AY11" t="n">
+        <v>0.6888888888888971</v>
+      </c>
+      <c r="AZ11" t="inlineStr"/>
+      <c r="BA11" t="inlineStr"/>
+      <c r="BB11" t="n">
+        <v>-0.1677070713869</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>0.1664395418038238</v>
+      </c>
+      <c r="BD11" t="inlineStr"/>
+      <c r="BE11" t="n">
+        <v>-2566121.889493263</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>6HPisxHl</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45557.5</v>
+      </c>
+      <c r="C12" t="n">
+        <v>101</v>
+      </c>
+      <c r="D12" t="n">
+        <v>134</v>
+      </c>
+      <c r="E12" t="n">
+        <v>431</v>
+      </c>
+      <c r="F12" t="n">
+        <v>599</v>
+      </c>
+      <c r="G12" t="n">
+        <v>55</v>
+      </c>
+      <c r="H12" t="n">
+        <v>551</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>315</v>
+      </c>
+      <c r="M12" t="n">
+        <v>10</v>
+      </c>
+      <c r="N12" t="n">
+        <v>-6</v>
+      </c>
+      <c r="O12" t="n">
+        <v>-2</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>-1</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>-0.1499999999999999</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V12" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="W12" t="n">
+        <v>7</v>
+      </c>
+      <c r="X12" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>-10</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>75.22727272727272</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>73.14090909090909</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>0.6417343911248672</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>-2.666598194388342</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>-3272178.03030303</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>0.4962121212121176</v>
+      </c>
+      <c r="AQ12" t="inlineStr"/>
+      <c r="AR12" t="n">
+        <v>-3.137626262626256</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>-5.043420585244007</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AU12" t="n">
+        <v>-0.3085858585858587</v>
+      </c>
+      <c r="AV12" t="inlineStr"/>
+      <c r="AW12" t="n">
+        <v>-4.664393939393946</v>
+      </c>
+      <c r="AX12" t="inlineStr"/>
+      <c r="AY12" t="n">
+        <v>1.411363636363603</v>
+      </c>
+      <c r="AZ12" t="inlineStr"/>
+      <c r="BA12" t="inlineStr"/>
+      <c r="BB12" t="n">
+        <v>-0.5891918027699319</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>-0.2325163398692813</v>
+      </c>
+      <c r="BD12" t="inlineStr"/>
+      <c r="BE12" t="n">
+        <v>-2335036.553213009</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>EsTauGo1</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45557.5</v>
+      </c>
+      <c r="C13" t="n">
+        <v>106</v>
+      </c>
+      <c r="D13" t="n">
+        <v>134</v>
+      </c>
+      <c r="E13" t="n">
+        <v>242</v>
+      </c>
+      <c r="F13" t="n">
+        <v>228</v>
+      </c>
+      <c r="G13" t="n">
+        <v>55</v>
+      </c>
+      <c r="H13" t="n">
+        <v>551</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>249</v>
+      </c>
+      <c r="M13" t="n">
+        <v>60</v>
+      </c>
+      <c r="N13" t="n">
+        <v>-3</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
         <v>5</v>
       </c>
-      <c r="AF6" t="n">
-        <v>-8</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>16</v>
-      </c>
-      <c r="AH6" t="n">
+      <c r="Q13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.3050000000000002</v>
+      </c>
+      <c r="T13" t="n">
+        <v>-0.6800000000000002</v>
+      </c>
+      <c r="U13" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="V13" t="n">
         <v>-5</v>
       </c>
-      <c r="AI6" t="n">
-        <v>19</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>-19</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>76.40000000000001</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>82.66666666666667</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>-0.3999999999999999</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>1.400000000000006</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>-225</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>3182247.899159662</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>-0.3385854341736696</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>2704242.424242425</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>-0.2727272727272521</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>2.25700280112045</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>-11200000</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>-0.7848484848484816</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>-213</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>0.2818181818181817</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>0.4190009337068159</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>1.491479925303452</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>-0.720588235294116</v>
-      </c>
-      <c r="BB6" t="n">
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>71.14090909090909</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>72</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>0.6647456709956749</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>5.343587662337654</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>3469185.606060606</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>0.5563131313131287</v>
+      </c>
+      <c r="AQ13" t="inlineStr"/>
+      <c r="AR13" t="n">
+        <v>4.596212121212119</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>5.774242424242416</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AU13" t="n">
+        <v>0.3691919191919193</v>
+      </c>
+      <c r="AV13" t="inlineStr"/>
+      <c r="AW13" t="n">
+        <v>4.603030303030295</v>
+      </c>
+      <c r="AX13" t="inlineStr"/>
+      <c r="AY13" t="n">
+        <v>-1.892424242424227</v>
+      </c>
+      <c r="AZ13" t="inlineStr"/>
+      <c r="BA13" t="inlineStr"/>
+      <c r="BB13" t="n">
+        <v>-0.328787878787864</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>0.2589285714285716</v>
+      </c>
+      <c r="BD13" t="inlineStr"/>
+      <c r="BE13" t="n">
+        <v>2612494.588744589</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>nTCJapXF</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45557.5</v>
+      </c>
+      <c r="C14" t="n">
+        <v>103</v>
+      </c>
+      <c r="D14" t="n">
+        <v>134</v>
+      </c>
+      <c r="E14" t="n">
+        <v>211</v>
+      </c>
+      <c r="F14" t="n">
+        <v>226</v>
+      </c>
+      <c r="G14" t="n">
+        <v>55</v>
+      </c>
+      <c r="H14" t="n">
+        <v>551</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>40</v>
+      </c>
+      <c r="M14" t="n">
+        <v>166</v>
+      </c>
+      <c r="N14" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O14" t="n">
+        <v>2</v>
+      </c>
+      <c r="P14" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0.175</v>
+      </c>
+      <c r="U14" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="V14" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>-10</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>7</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>73.06944444444444</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>73.27272727272727</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>0.5715073529411789</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>-1.803130570409962</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>1020340.90909091</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>4.836363636363632</v>
+      </c>
+      <c r="AQ14" t="inlineStr"/>
+      <c r="AR14" t="n">
+        <v>-2.786931818181813</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>-0.8552083333333371</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AU14" t="n">
+        <v>0.2755681818181819</v>
+      </c>
+      <c r="AV14" t="inlineStr"/>
+      <c r="AW14" t="n">
+        <v>2.048863636363649</v>
+      </c>
+      <c r="AX14" t="inlineStr"/>
+      <c r="AY14" t="n">
+        <v>0.08693181818182438</v>
+      </c>
+      <c r="AZ14" t="inlineStr"/>
+      <c r="BA14" t="inlineStr"/>
+      <c r="BB14" t="n">
+        <v>1.20101938502674</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>0.2495265151515151</v>
+      </c>
+      <c r="BD14" t="inlineStr"/>
+      <c r="BE14" t="n">
+        <v>854968.8057041001</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>6V4QeyWs</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45557.41666666666</v>
+      </c>
+      <c r="C15" t="n">
+        <v>105</v>
+      </c>
+      <c r="D15" t="n">
+        <v>133</v>
+      </c>
+      <c r="E15" t="n">
+        <v>47</v>
+      </c>
+      <c r="F15" t="n">
+        <v>122</v>
+      </c>
+      <c r="G15" t="n">
+        <v>55</v>
+      </c>
+      <c r="H15" t="n">
+        <v>551</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>128</v>
+      </c>
+      <c r="M15" t="n">
+        <v>166</v>
+      </c>
+      <c r="N15" t="n">
+        <v>5</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>-0.105</v>
+      </c>
+      <c r="T15" t="n">
+        <v>-0.21</v>
+      </c>
+      <c r="U15" t="n">
+        <v>4</v>
+      </c>
+      <c r="V15" t="n">
+        <v>-7</v>
+      </c>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>7</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>-17</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>75.81818181818181</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>72.75</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>-2.14517045454545</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>8.337247474747471</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>10010454.54545455</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>-1.540909090909089</v>
+      </c>
+      <c r="AQ15" t="inlineStr"/>
+      <c r="AR15" t="n">
+        <v>6.297727272727258</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>5.792171717171698</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AU15" t="n">
+        <v>0.3999999999999999</v>
+      </c>
+      <c r="AV15" t="inlineStr"/>
+      <c r="AW15" t="n">
+        <v>4.572727272727263</v>
+      </c>
+      <c r="AX15" t="inlineStr"/>
+      <c r="AY15" t="n">
+        <v>-1.868181818181824</v>
+      </c>
+      <c r="AZ15" t="inlineStr"/>
+      <c r="BA15" t="inlineStr"/>
+      <c r="BB15" t="n">
+        <v>1.313541666666652</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>0.3555555555555556</v>
+      </c>
+      <c r="BD15" t="inlineStr"/>
+      <c r="BE15" t="n">
+        <v>10844704.0719697</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>v39B1623</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45556.66666666666</v>
+      </c>
+      <c r="C16" t="n">
+        <v>101</v>
+      </c>
+      <c r="D16" t="n">
+        <v>133</v>
+      </c>
+      <c r="E16" t="n">
+        <v>826</v>
+      </c>
+      <c r="F16" t="n">
+        <v>129</v>
+      </c>
+      <c r="G16" t="n">
+        <v>55</v>
+      </c>
+      <c r="H16" t="n">
+        <v>551</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="L16" t="n">
+        <v>168</v>
+      </c>
+      <c r="M16" t="n">
+        <v>7</v>
+      </c>
+      <c r="N16" t="n">
+        <v>-9</v>
+      </c>
+      <c r="O16" t="n">
+        <v>-2</v>
+      </c>
+      <c r="P16" t="n">
+        <v>-3</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>-1</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>-1.05</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1.005</v>
+      </c>
+      <c r="U16" t="n">
+        <v>-6</v>
+      </c>
+      <c r="V16" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="W16" t="n">
+        <v>8</v>
+      </c>
+      <c r="X16" t="n">
+        <v>-2</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC16" t="n">
         <v>-2.5</v>
       </c>
-      <c r="BC6" t="n">
-        <v>1.663636363636371</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>1.242424242424249</v>
-      </c>
-      <c r="BE6" t="n">
+      <c r="AD16" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>-25</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AK16" t="inlineStr"/>
+      <c r="AL16" t="n">
+        <v>73.45454545454545</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>0.02263049450549204</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>-6.972413003663007</v>
+      </c>
+      <c r="AO16" t="inlineStr"/>
+      <c r="AP16" t="inlineStr"/>
+      <c r="AQ16" t="inlineStr"/>
+      <c r="AR16" t="inlineStr"/>
+      <c r="AS16" t="n">
+        <v>-7.97360347985348</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AU16" t="inlineStr"/>
+      <c r="AV16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr"/>
+      <c r="AX16" t="inlineStr"/>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr"/>
+      <c r="BA16" t="inlineStr"/>
+      <c r="BB16" t="n">
+        <v>0.1971153846153584</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>-0.9738591269841266</v>
+      </c>
+      <c r="BD16" t="inlineStr"/>
+      <c r="BE16" t="n">
+        <v>-27738306.81471306</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>noOg1c8K</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45556.58333333334</v>
+      </c>
+      <c r="C17" t="n">
+        <v>101</v>
+      </c>
+      <c r="D17" t="n">
+        <v>134</v>
+      </c>
+      <c r="E17" t="n">
+        <v>573</v>
+      </c>
+      <c r="F17" t="n">
+        <v>176</v>
+      </c>
+      <c r="G17" t="n">
+        <v>55</v>
+      </c>
+      <c r="H17" t="n">
+        <v>551</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
+        <v>249</v>
+      </c>
+      <c r="M17" t="n">
+        <v>138</v>
+      </c>
+      <c r="N17" t="n">
         <v>-3</v>
       </c>
-      <c r="BF6" t="n">
+      <c r="O17" t="n">
+        <v>-3</v>
+      </c>
+      <c r="P17" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>-1</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0.1850000000000001</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="U17" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="V17" t="n">
+        <v>5</v>
+      </c>
+      <c r="W17" t="n">
+        <v>-3</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>-6</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>74.53333333333333</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>71.3</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>-0.7819194143228358</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>-0.2021837026884725</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>-3157500</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>-1.015909090909094</v>
+      </c>
+      <c r="AQ17" t="inlineStr"/>
+      <c r="AR17" t="n">
+        <v>-0.4386363636363626</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>-0.8385434057125991</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AU17" t="n">
+        <v>0.4090909090909087</v>
+      </c>
+      <c r="AV17" t="inlineStr"/>
+      <c r="AW17" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AX17" t="inlineStr"/>
+      <c r="AY17" t="n">
+        <v>0.2022727272727138</v>
+      </c>
+      <c r="AZ17" t="inlineStr"/>
+      <c r="BA17" t="inlineStr"/>
+      <c r="BB17" t="n">
+        <v>-0.1993172451006444</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>0.3645239872524837</v>
+      </c>
+      <c r="BD17" t="inlineStr"/>
+      <c r="BE17" t="n">
+        <v>311590.4349049795</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>fiy8wfGD</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45556.5</v>
+      </c>
+      <c r="C18" t="n">
+        <v>106</v>
+      </c>
+      <c r="D18" t="n">
+        <v>133</v>
+      </c>
+      <c r="E18" t="n">
+        <v>777</v>
+      </c>
+      <c r="F18" t="n">
+        <v>516</v>
+      </c>
+      <c r="G18" t="n">
+        <v>55</v>
+      </c>
+      <c r="H18" t="n">
+        <v>551</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="L18" t="n">
+        <v>272</v>
+      </c>
+      <c r="M18" t="n">
+        <v>32</v>
+      </c>
+      <c r="N18" t="n">
+        <v>3</v>
+      </c>
+      <c r="O18" t="n">
+        <v>4</v>
+      </c>
+      <c r="P18" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>3</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>-0.7450000000000001</v>
+      </c>
+      <c r="T18" t="n">
+        <v>-0.6000000000000001</v>
+      </c>
+      <c r="U18" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="V18" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="W18" t="inlineStr"/>
+      <c r="X18" t="inlineStr"/>
+      <c r="Y18" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>-4</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>74.59999999999999</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>75.34999999999999</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>5.192532467532466</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>0.3361291486291407</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>5995025.252525252</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>4.391414141414142</v>
+      </c>
+      <c r="AQ18" t="inlineStr"/>
+      <c r="AR18" t="n">
+        <v>-0.2803030303030312</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>6.275054112554116</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AU18" t="n">
+        <v>0.3032828282828282</v>
+      </c>
+      <c r="AV18" t="inlineStr"/>
+      <c r="AW18" t="n">
+        <v>5.410101010101016</v>
+      </c>
+      <c r="AX18" t="inlineStr"/>
+      <c r="AY18" t="n">
+        <v>-1.772979797979787</v>
+      </c>
+      <c r="AZ18" t="inlineStr"/>
+      <c r="BA18" t="inlineStr"/>
+      <c r="BB18" t="n">
+        <v>-1.517654220779235</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>0.6507575757575756</v>
+      </c>
+      <c r="BD18" t="inlineStr"/>
+      <c r="BE18" t="n">
+        <v>6077491.544913419</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>0K4Ww3Ad</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45555.65625</v>
+      </c>
+      <c r="C19" t="n">
+        <v>101</v>
+      </c>
+      <c r="D19" t="n">
+        <v>135</v>
+      </c>
+      <c r="E19" t="n">
+        <v>535</v>
+      </c>
+      <c r="F19" t="n">
+        <v>362</v>
+      </c>
+      <c r="G19" t="n">
+        <v>55</v>
+      </c>
+      <c r="H19" t="n">
+        <v>551</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="L19" t="n">
+        <v>314</v>
+      </c>
+      <c r="M19" t="n">
+        <v>204</v>
+      </c>
+      <c r="N19" t="n">
+        <v>5</v>
+      </c>
+      <c r="O19" t="n">
+        <v>2</v>
+      </c>
+      <c r="P19" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="T19" t="n">
+        <v>-1.475</v>
+      </c>
+      <c r="U19" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="V19" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="W19" t="inlineStr"/>
+      <c r="X19" t="inlineStr"/>
+      <c r="Y19" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>-10</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>-10</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>72.40000000000001</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>75.5</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>-2.119458156222866</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>5.611316787787359</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>8181392.045454547</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>-2.14886363636364</v>
+      </c>
+      <c r="AQ19" t="inlineStr"/>
+      <c r="AR19" t="n">
+        <v>4.247727272727275</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>5.73701380319028</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AU19" t="n">
+        <v>0.08409090909090922</v>
+      </c>
+      <c r="AV19" t="inlineStr"/>
+      <c r="AW19" t="n">
+        <v>3.404545454545456</v>
+      </c>
+      <c r="AX19" t="inlineStr"/>
+      <c r="AY19" t="n">
+        <v>1.046590909090895</v>
+      </c>
+      <c r="AZ19" t="inlineStr"/>
+      <c r="BA19" t="inlineStr"/>
+      <c r="BB19" t="n">
+        <v>-0.9954465469171225</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>0.1813725490196081</v>
+      </c>
+      <c r="BD19" t="inlineStr"/>
+      <c r="BE19" t="n">
+        <v>5722956.802184744</v>
+      </c>
+      <c r="BF19" t="n">
         <v>0</v>
       </c>
     </row>

--- a/data/france/p6_deployment/data_preparation/df_tagged.xlsx
+++ b/data/france/p6_deployment/data_preparation/df_tagged.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DR10"/>
+  <dimension ref="A1:DR5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -960,77 +960,77 @@
       </c>
       <c r="DC1" s="1" t="inlineStr">
         <is>
+          <t>dif_sum_rat_player_miss</t>
+        </is>
+      </c>
+      <c r="DD1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_start</t>
+        </is>
+      </c>
+      <c r="DE1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_miss</t>
+        </is>
+      </c>
+      <c r="DF1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_sub</t>
+        </is>
+      </c>
+      <c r="DG1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_360_matches_mean_rat_player_start</t>
+        </is>
+      </c>
+      <c r="DH1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_start</t>
+        </is>
+      </c>
+      <c r="DI1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_miss</t>
+        </is>
+      </c>
+      <c r="DJ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_wage_player_start</t>
+        </is>
+      </c>
+      <c r="DK1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_wage_player_sub</t>
+        </is>
+      </c>
+      <c r="DL1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_miss</t>
+        </is>
+      </c>
+      <c r="DM1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_sub</t>
+        </is>
+      </c>
+      <c r="DN1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_start</t>
+        </is>
+      </c>
+      <c r="DO1" s="1" t="inlineStr">
+        <is>
           <t>dif_n_player_miss</t>
         </is>
       </c>
-      <c r="DD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_360_matches_mean_rat_player_start</t>
-        </is>
-      </c>
-      <c r="DE1" s="1" t="inlineStr">
+      <c r="DP1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_wage_player_miss</t>
         </is>
       </c>
-      <c r="DF1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_sub</t>
-        </is>
-      </c>
-      <c r="DG1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_wage_player_start</t>
-        </is>
-      </c>
-      <c r="DH1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_wage_player_sub</t>
-        </is>
-      </c>
-      <c r="DI1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_miss</t>
-        </is>
-      </c>
-      <c r="DJ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_start</t>
-        </is>
-      </c>
-      <c r="DK1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_start</t>
-        </is>
-      </c>
-      <c r="DL1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_rat_player_miss</t>
-        </is>
-      </c>
-      <c r="DM1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_miss</t>
-        </is>
-      </c>
-      <c r="DN1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_miss</t>
-        </is>
-      </c>
-      <c r="DO1" s="1" t="inlineStr">
+      <c r="DQ1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_age_player_sub</t>
-        </is>
-      </c>
-      <c r="DP1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_sub</t>
-        </is>
-      </c>
-      <c r="DQ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_start</t>
         </is>
       </c>
       <c r="DR1" s="1" t="inlineStr">
@@ -1357,45 +1357,45 @@
       <c r="DA2" t="inlineStr"/>
       <c r="DB2" t="inlineStr"/>
       <c r="DC2" t="n">
-        <v>-2</v>
+        <v>-164</v>
       </c>
       <c r="DD2" t="n">
+        <v>-3.905000000000001</v>
+      </c>
+      <c r="DE2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DF2" t="n">
+        <v>1.756458704694012</v>
+      </c>
+      <c r="DG2" t="n">
         <v>-4.782428451178447</v>
       </c>
-      <c r="DE2" t="inlineStr"/>
-      <c r="DF2" t="n">
-        <v>-5.321919191919193</v>
-      </c>
-      <c r="DG2" t="n">
-        <v>-29409.16666666666</v>
-      </c>
-      <c r="DH2" t="inlineStr"/>
+      <c r="DH2" t="n">
+        <v>1.632222222222225</v>
+      </c>
       <c r="DI2" t="n">
         <v>-3.25</v>
       </c>
       <c r="DJ2" t="n">
+        <v>-29409.16666666666</v>
+      </c>
+      <c r="DK2" t="inlineStr"/>
+      <c r="DL2" t="n">
+        <v>-8.75</v>
+      </c>
+      <c r="DM2" t="n">
+        <v>-5.321919191919193</v>
+      </c>
+      <c r="DN2" t="n">
         <v>-6.365555555555559</v>
       </c>
-      <c r="DK2" t="n">
-        <v>-3.905000000000001</v>
-      </c>
-      <c r="DL2" t="n">
-        <v>-164</v>
-      </c>
-      <c r="DM2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="DN2" t="n">
-        <v>-8.75</v>
-      </c>
       <c r="DO2" t="n">
+        <v>-2</v>
+      </c>
+      <c r="DP2" t="inlineStr"/>
+      <c r="DQ2" t="n">
         <v>-3.081828579916817</v>
-      </c>
-      <c r="DP2" t="n">
-        <v>1.756458704694012</v>
-      </c>
-      <c r="DQ2" t="n">
-        <v>1.632222222222225</v>
       </c>
       <c r="DR2" t="n">
         <v>0</v>
@@ -1719,43 +1719,43 @@
       <c r="DA3" t="inlineStr"/>
       <c r="DB3" t="inlineStr"/>
       <c r="DC3" t="n">
-        <v>3</v>
+        <v>189</v>
       </c>
       <c r="DD3" t="n">
+        <v>0.9916666666666671</v>
+      </c>
+      <c r="DE3" t="n">
+        <v>-12.5</v>
+      </c>
+      <c r="DF3" t="n">
+        <v>-2.204396627101232</v>
+      </c>
+      <c r="DG3" t="n">
         <v>-4.700053051523625</v>
       </c>
-      <c r="DE3" t="inlineStr"/>
-      <c r="DF3" t="n">
-        <v>-4.04102912290891</v>
-      </c>
-      <c r="DG3" t="inlineStr"/>
-      <c r="DH3" t="inlineStr"/>
+      <c r="DH3" t="n">
+        <v>2.39500000000001</v>
+      </c>
       <c r="DI3" t="n">
         <v>-3.25</v>
       </c>
-      <c r="DJ3" t="n">
+      <c r="DJ3" t="inlineStr"/>
+      <c r="DK3" t="inlineStr"/>
+      <c r="DL3" t="n">
+        <v>-8.25</v>
+      </c>
+      <c r="DM3" t="n">
+        <v>-4.04102912290891</v>
+      </c>
+      <c r="DN3" t="n">
         <v>-6.021666666666675</v>
       </c>
-      <c r="DK3" t="n">
-        <v>0.9916666666666671</v>
-      </c>
-      <c r="DL3" t="n">
-        <v>189</v>
-      </c>
-      <c r="DM3" t="n">
-        <v>-12.5</v>
-      </c>
-      <c r="DN3" t="n">
-        <v>-8.25</v>
-      </c>
       <c r="DO3" t="n">
+        <v>3</v>
+      </c>
+      <c r="DP3" t="inlineStr"/>
+      <c r="DQ3" t="n">
         <v>2.838938088055738</v>
-      </c>
-      <c r="DP3" t="n">
-        <v>-2.204396627101232</v>
-      </c>
-      <c r="DQ3" t="n">
-        <v>2.39500000000001</v>
       </c>
       <c r="DR3" t="n">
         <v>0</v>
@@ -2079,49 +2079,49 @@
       <c r="DA4" t="inlineStr"/>
       <c r="DB4" t="inlineStr"/>
       <c r="DC4" t="n">
-        <v>-1</v>
+        <v>82</v>
       </c>
       <c r="DD4" t="n">
+        <v>-0.976515151515148</v>
+      </c>
+      <c r="DE4" t="n">
+        <v>-0.1999999999999886</v>
+      </c>
+      <c r="DF4" t="n">
+        <v>0.9289529072578944</v>
+      </c>
+      <c r="DG4" t="n">
         <v>3.069618983957227</v>
       </c>
-      <c r="DE4" t="n">
-        <v>12750</v>
-      </c>
-      <c r="DF4" t="n">
+      <c r="DH4" t="n">
+        <v>-0.03636363636360329</v>
+      </c>
+      <c r="DI4" t="n">
+        <v>-1.199999999999999</v>
+      </c>
+      <c r="DJ4" t="n">
+        <v>9150</v>
+      </c>
+      <c r="DK4" t="n">
+        <v>13261.53846153846</v>
+      </c>
+      <c r="DL4" t="n">
+        <v>2.400000000000006</v>
+      </c>
+      <c r="DM4" t="n">
         <v>4.472361925999707</v>
       </c>
-      <c r="DG4" t="n">
-        <v>9150</v>
-      </c>
-      <c r="DH4" t="n">
-        <v>13261.53846153846</v>
-      </c>
-      <c r="DI4" t="n">
-        <v>-0.6666666666666679</v>
-      </c>
-      <c r="DJ4" t="n">
+      <c r="DN4" t="n">
         <v>2.140909090909105</v>
       </c>
-      <c r="DK4" t="n">
-        <v>-0.976515151515148</v>
-      </c>
-      <c r="DL4" t="n">
-        <v>-61</v>
-      </c>
-      <c r="DM4" t="n">
-        <v>-2.666666666666657</v>
-      </c>
-      <c r="DN4" t="n">
-        <v>3</v>
-      </c>
       <c r="DO4" t="n">
+        <v>1</v>
+      </c>
+      <c r="DP4" t="n">
+        <v>13150</v>
+      </c>
+      <c r="DQ4" t="n">
         <v>0.1626858908205655</v>
-      </c>
-      <c r="DP4" t="n">
-        <v>0.9289529072578944</v>
-      </c>
-      <c r="DQ4" t="n">
-        <v>-0.03636363636360329</v>
       </c>
       <c r="DR4" t="n">
         <v>0</v>
@@ -2446,1860 +2446,38 @@
       <c r="DB5" t="inlineStr"/>
       <c r="DC5" t="inlineStr"/>
       <c r="DD5" t="n">
-        <v>-3.075609031491382</v>
+        <v>-3.926060606060606</v>
       </c>
       <c r="DE5" t="inlineStr"/>
       <c r="DF5" t="n">
-        <v>-3.402218490891272</v>
+        <v>-0.534622456221939</v>
       </c>
       <c r="DG5" t="n">
-        <v>-20514.39393939394</v>
+        <v>-3.075609031491382</v>
       </c>
       <c r="DH5" t="n">
-        <v>-8143.140255894328</v>
+        <v>-0.8705555555555691</v>
       </c>
       <c r="DI5" t="inlineStr"/>
       <c r="DJ5" t="n">
+        <v>-20514.39393939394</v>
+      </c>
+      <c r="DK5" t="n">
+        <v>-8143.140255894328</v>
+      </c>
+      <c r="DL5" t="inlineStr"/>
+      <c r="DM5" t="n">
+        <v>-3.402218490891272</v>
+      </c>
+      <c r="DN5" t="n">
         <v>-4.044747474747481</v>
       </c>
-      <c r="DK5" t="n">
-        <v>-3.926060606060606</v>
-      </c>
-      <c r="DL5" t="inlineStr"/>
-      <c r="DM5" t="inlineStr"/>
-      <c r="DN5" t="inlineStr"/>
-      <c r="DO5" t="n">
+      <c r="DO5" t="inlineStr"/>
+      <c r="DP5" t="inlineStr"/>
+      <c r="DQ5" t="n">
         <v>-0.2000977216349398</v>
       </c>
-      <c r="DP5" t="n">
-        <v>-0.534622456221939</v>
-      </c>
-      <c r="DQ5" t="n">
-        <v>-0.8705555555555691</v>
-      </c>
       <c r="DR5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>lxyu7Met</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="n">
-        <v>45563.66666666666</v>
-      </c>
-      <c r="C6" t="n">
-        <v>102</v>
-      </c>
-      <c r="D6" t="n">
-        <v>133</v>
-      </c>
-      <c r="E6" t="n">
-        <v>47</v>
-      </c>
-      <c r="F6" t="n">
-        <v>157</v>
-      </c>
-      <c r="G6" t="n">
-        <v>55</v>
-      </c>
-      <c r="H6" t="n">
-        <v>551</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-      <c r="L6" t="n">
-        <v>67</v>
-      </c>
-      <c r="M6" t="n">
-        <v>109</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1.095</v>
-      </c>
-      <c r="P6" t="n">
-        <v>-1.06</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0.8795833333333333</v>
-      </c>
-      <c r="R6" t="n">
-        <v>-0.8650833333333334</v>
-      </c>
-      <c r="S6" t="n">
-        <v>1.333333333333333</v>
-      </c>
-      <c r="T6" t="n">
-        <v>-1.666666666666667</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.033088235294118</v>
-      </c>
-      <c r="V6" t="n">
-        <v>-1.128676470588235</v>
-      </c>
-      <c r="W6" t="n">
-        <v>0.833333333333333</v>
-      </c>
-      <c r="X6" t="n">
-        <v>-4.666666666666666</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.9375</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>-2.1875</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>4.666666666666666</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>-6.666666666666666</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>6.9375</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>-7.5</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.666666666666667</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>-3.833333333333333</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>0.4485294117647058</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>-1.011029411764706</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>2.333333333333333</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>-2.666666666666667</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>0.5845588235294117</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>-0.7169117647058822</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>8.194139194139193</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>-8.015151515151516</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>8.542972973238866</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>-8.303386101289062</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>431.0265151515151</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>-308.0265486725664</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>369.370882979869</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>-383.3229617797426</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>35.5</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>-62</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>37.75416666666666</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>-32.64166666666667</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>-39</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>16.0625</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>-26.25833333333333</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>21.83333333333334</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>-0.6666666666666643</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>6.485294117647058</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>2.341911764705884</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>22.33333333333334</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>-22.33333333333334</v>
-      </c>
-      <c r="BI6" t="n">
-        <v>14.375</v>
-      </c>
-      <c r="BJ6" t="n">
-        <v>-14.375</v>
-      </c>
-      <c r="BK6" t="n">
-        <v>84</v>
-      </c>
-      <c r="BL6" t="n">
-        <v>-136</v>
-      </c>
-      <c r="BM6" t="n">
-        <v>140.152380952381</v>
-      </c>
-      <c r="BN6" t="n">
-        <v>-100.0571428571428</v>
-      </c>
-      <c r="BO6" t="n">
-        <v>0.5716666666666667</v>
-      </c>
-      <c r="BP6" t="n">
-        <v>-2.773333333333333</v>
-      </c>
-      <c r="BQ6" t="n">
-        <v>-0.1879166666666668</v>
-      </c>
-      <c r="BR6" t="n">
-        <v>-0.3224166666666667</v>
-      </c>
-      <c r="BS6" t="n">
-        <v>-2.5</v>
-      </c>
-      <c r="BT6" t="n">
-        <v>1.666666666666667</v>
-      </c>
-      <c r="BU6" t="n">
-        <v>-0.575</v>
-      </c>
-      <c r="BV6" t="n">
-        <v>0.5166666666666666</v>
-      </c>
-      <c r="BW6" t="inlineStr"/>
-      <c r="BX6" t="inlineStr"/>
-      <c r="BY6" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="BZ6" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="CA6" t="n">
-        <v>5.333333333333332</v>
-      </c>
-      <c r="CB6" t="n">
-        <v>18.83333333333333</v>
-      </c>
-      <c r="CC6" t="n">
-        <v>6.242647058823529</v>
-      </c>
-      <c r="CD6" t="n">
-        <v>-0.286764705882355</v>
-      </c>
-      <c r="CE6" t="n">
-        <v>-38.51851851851852</v>
-      </c>
-      <c r="CF6" t="n">
-        <v>-29.80363636363636</v>
-      </c>
-      <c r="CG6" t="n">
-        <v>-5.530292441694757</v>
-      </c>
-      <c r="CH6" t="n">
-        <v>2.363568927990858</v>
-      </c>
-      <c r="CI6" t="n">
-        <v>-0.02109107276531833</v>
-      </c>
-      <c r="CJ6" t="n">
-        <v>0.002361381423661435</v>
-      </c>
-      <c r="CK6" t="n">
-        <v>0.006984839587167162</v>
-      </c>
-      <c r="CL6" t="n">
-        <v>-0.006924301346088284</v>
-      </c>
-      <c r="CM6" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="CN6" t="n">
-        <v>-1</v>
-      </c>
-      <c r="CO6" t="n">
-        <v>0.2610294117647058</v>
-      </c>
-      <c r="CP6" t="n">
-        <v>-0.2279411764705883</v>
-      </c>
-      <c r="CQ6" t="n">
-        <v>2.773333333333333</v>
-      </c>
-      <c r="CR6" t="n">
-        <v>-0.5716666666666667</v>
-      </c>
-      <c r="CS6" t="n">
-        <v>0.3224166666666667</v>
-      </c>
-      <c r="CT6" t="n">
-        <v>0.1879166666666668</v>
-      </c>
-      <c r="CU6" t="n">
-        <v>3.345</v>
-      </c>
-      <c r="CV6" t="n">
-        <v>-3.345</v>
-      </c>
-      <c r="CW6" t="n">
-        <v>0.1345</v>
-      </c>
-      <c r="CX6" t="n">
-        <v>-0.1345</v>
-      </c>
-      <c r="CY6" t="n">
-        <v>74.04575757575756</v>
-      </c>
-      <c r="CZ6" t="n">
-        <v>75.12222222222222</v>
-      </c>
-      <c r="DA6" t="inlineStr"/>
-      <c r="DB6" t="inlineStr"/>
-      <c r="DC6" t="n">
-        <v>-2</v>
-      </c>
-      <c r="DD6" t="n">
-        <v>3.270409982174698</v>
-      </c>
-      <c r="DE6" t="n">
-        <v>-250</v>
-      </c>
-      <c r="DF6" t="n">
-        <v>3.266825396825396</v>
-      </c>
-      <c r="DG6" t="n">
-        <v>24108.38383838384</v>
-      </c>
-      <c r="DH6" t="n">
-        <v>19438.01587301587</v>
-      </c>
-      <c r="DI6" t="n">
-        <v>-5.5</v>
-      </c>
-      <c r="DJ6" t="n">
-        <v>2.638181818181806</v>
-      </c>
-      <c r="DK6" t="n">
-        <v>-1.901464646464646</v>
-      </c>
-      <c r="DL6" t="n">
-        <v>-150</v>
-      </c>
-      <c r="DM6" t="n">
-        <v>-1</v>
-      </c>
-      <c r="DN6" t="n">
-        <v>-2.5</v>
-      </c>
-      <c r="DO6" t="n">
-        <v>-2.742619047619048</v>
-      </c>
-      <c r="DP6" t="n">
-        <v>1.08793650793649</v>
-      </c>
-      <c r="DQ6" t="n">
-        <v>2.919696969696986</v>
-      </c>
-      <c r="DR6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>xb7MlutC</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="n">
-        <v>45563.58333333334</v>
-      </c>
-      <c r="C7" t="n">
-        <v>102</v>
-      </c>
-      <c r="D7" t="n">
-        <v>133</v>
-      </c>
-      <c r="E7" t="n">
-        <v>194</v>
-      </c>
-      <c r="F7" t="n">
-        <v>545</v>
-      </c>
-      <c r="G7" t="n">
-        <v>55</v>
-      </c>
-      <c r="H7" t="n">
-        <v>551</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-      <c r="L7" t="n">
-        <v>67</v>
-      </c>
-      <c r="M7" t="n">
-        <v>258</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>-0.05500000000000016</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0.3399999999999999</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0.3139166666666666</v>
-      </c>
-      <c r="R7" t="n">
-        <v>-0.100583333333333</v>
-      </c>
-      <c r="S7" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="T7" t="n">
-        <v>1</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="V7" t="n">
-        <v>-0.1139705882352942</v>
-      </c>
-      <c r="W7" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.109803921568628</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>-0.02745098039215677</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>-5.5</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>1.490196078431373</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>0.09803921568627594</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>0.1838235294117647</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>0.3088235294117647</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>-0.1029411764705883</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>0.2720588235294117</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>17.29090909090909</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>-7.85</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>10.40567073993545</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>-9.266255661263401</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>631.0213523131673</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>-872.010101010101</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>538.846517446803</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>-502.4618199865471</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>-74</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>39</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>-12.63529411764706</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>20.12941176470588</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>-63</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>19</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>1.13725490196078</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>1.584313725490198</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>1</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>-2.856617647058826</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>0.680147058823529</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>-33.5</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>33.5</v>
-      </c>
-      <c r="BI7" t="n">
-        <v>-14.28235294117647</v>
-      </c>
-      <c r="BJ7" t="n">
-        <v>14.28235294117647</v>
-      </c>
-      <c r="BK7" t="n">
-        <v>-372</v>
-      </c>
-      <c r="BL7" t="n">
-        <v>590</v>
-      </c>
-      <c r="BM7" t="n">
-        <v>-140.9732142857143</v>
-      </c>
-      <c r="BN7" t="n">
-        <v>138.75</v>
-      </c>
-      <c r="BO7" t="n">
-        <v>1.055</v>
-      </c>
-      <c r="BP7" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="BQ7" t="n">
-        <v>-0.1847499999999999</v>
-      </c>
-      <c r="BR7" t="n">
-        <v>0.36725</v>
-      </c>
-      <c r="BS7" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="BT7" t="n">
-        <v>1</v>
-      </c>
-      <c r="BU7" t="n">
-        <v>0.3686274509803922</v>
-      </c>
-      <c r="BV7" t="n">
-        <v>-0.2588235294117645</v>
-      </c>
-      <c r="BW7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY7" t="n">
-        <v>-0.3</v>
-      </c>
-      <c r="BZ7" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="CA7" t="n">
-        <v>-2</v>
-      </c>
-      <c r="CB7" t="n">
-        <v>-2</v>
-      </c>
-      <c r="CC7" t="n">
-        <v>-0.988970588235297</v>
-      </c>
-      <c r="CD7" t="n">
-        <v>-8.444852941176471</v>
-      </c>
-      <c r="CE7" t="n">
-        <v>22.94327731092437</v>
-      </c>
-      <c r="CF7" t="n">
-        <v>-6.97719298245614</v>
-      </c>
-      <c r="CG7" t="n">
-        <v>3.652054439981056</v>
-      </c>
-      <c r="CH7" t="n">
-        <v>-1.880642257828328</v>
-      </c>
-      <c r="CI7" t="n">
-        <v>0.01759390883502419</v>
-      </c>
-      <c r="CJ7" t="n">
-        <v>0.07162870945479642</v>
-      </c>
-      <c r="CK7" t="n">
-        <v>0.005636839110454567</v>
-      </c>
-      <c r="CL7" t="n">
-        <v>0.01164139150968586</v>
-      </c>
-      <c r="CM7" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="CN7" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="CO7" t="n">
-        <v>-0.2242647058823529</v>
-      </c>
-      <c r="CP7" t="n">
-        <v>0.1433823529411765</v>
-      </c>
-      <c r="CQ7" t="n">
-        <v>-1.66</v>
-      </c>
-      <c r="CR7" t="n">
-        <v>-1.055</v>
-      </c>
-      <c r="CS7" t="n">
-        <v>-0.36725</v>
-      </c>
-      <c r="CT7" t="n">
-        <v>0.1847499999999999</v>
-      </c>
-      <c r="CU7" t="n">
-        <v>-0.605</v>
-      </c>
-      <c r="CV7" t="n">
-        <v>0.605</v>
-      </c>
-      <c r="CW7" t="n">
-        <v>-0.5519999999999999</v>
-      </c>
-      <c r="CX7" t="n">
-        <v>0.5519999999999999</v>
-      </c>
-      <c r="CY7" t="n">
-        <v>74.20713804713805</v>
-      </c>
-      <c r="CZ7" t="n">
-        <v>74.3839057239057</v>
-      </c>
-      <c r="DA7" t="inlineStr"/>
-      <c r="DB7" t="inlineStr"/>
-      <c r="DC7" t="n">
-        <v>-3</v>
-      </c>
-      <c r="DD7" t="n">
-        <v>-5.009172608437325</v>
-      </c>
-      <c r="DE7" t="n">
-        <v>-25000</v>
-      </c>
-      <c r="DF7" t="n">
-        <v>-5.501789635485281</v>
-      </c>
-      <c r="DG7" t="n">
-        <v>-14441.41414141414</v>
-      </c>
-      <c r="DH7" t="n">
-        <v>-16372.62983091787</v>
-      </c>
-      <c r="DI7" t="n">
-        <v>-8.5</v>
-      </c>
-      <c r="DJ7" t="n">
-        <v>-4.370505050505045</v>
-      </c>
-      <c r="DK7" t="n">
-        <v>-0.04929292929292828</v>
-      </c>
-      <c r="DL7" t="n">
-        <v>-241</v>
-      </c>
-      <c r="DM7" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="DN7" t="n">
-        <v>-12.25</v>
-      </c>
-      <c r="DO7" t="n">
-        <v>-1.732108036890651</v>
-      </c>
-      <c r="DP7" t="n">
-        <v>0.8633003952569425</v>
-      </c>
-      <c r="DQ7" t="n">
-        <v>3.371717171717194</v>
-      </c>
-      <c r="DR7" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>v3PZcqJP</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="n">
-        <v>45563.5</v>
-      </c>
-      <c r="C8" t="n">
-        <v>102</v>
-      </c>
-      <c r="D8" t="n">
-        <v>133</v>
-      </c>
-      <c r="E8" t="n">
-        <v>273</v>
-      </c>
-      <c r="F8" t="n">
-        <v>370</v>
-      </c>
-      <c r="G8" t="n">
-        <v>55</v>
-      </c>
-      <c r="H8" t="n">
-        <v>551</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-      <c r="L8" t="n">
-        <v>249</v>
-      </c>
-      <c r="M8" t="n">
-        <v>226</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>-0.395</v>
-      </c>
-      <c r="P8" t="n">
-        <v>-1.126666666666666</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0.3789783281733747</v>
-      </c>
-      <c r="R8" t="n">
-        <v>-0.08052631578947378</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0.6666666666666667</v>
-      </c>
-      <c r="T8" t="n">
-        <v>-0.8333333333333333</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0.3294117647058823</v>
-      </c>
-      <c r="V8" t="n">
-        <v>-0.2264705882352942</v>
-      </c>
-      <c r="W8" t="n">
-        <v>3</v>
-      </c>
-      <c r="X8" t="n">
-        <v>-3.833333333333333</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.535294117647059</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>-0.6941176470588237</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>5.666666666666666</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>-4.333333333333334</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>3.623529411764707</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>-2.458823529411765</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>-0.6666666666666667</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>-1.666666666666667</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>0.2970588235294116</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>-0.2411764705882353</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>0.5235294117647058</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>-0.5088235294117647</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>8.77651515151515</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>-8.210119047619047</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>10.05284994230359</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>-9.062951937768114</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>526.0264227642276</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>-412.0383747178329</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>498.6455594082427</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>-451.8443733882388</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>45.16666666666667</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>34.33333333333333</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>18.09999999999999</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>-3.64411764705882</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>23</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>4.333333333333336</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>15.9735294117647</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>-3.805882352941175</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>4.166666666666664</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>1.166666666666668</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>4.632352941176471</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>-0.235294117647058</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BH8" t="n">
-        <v>-4.5</v>
-      </c>
-      <c r="BI8" t="n">
-        <v>-0.9676470588235304</v>
-      </c>
-      <c r="BJ8" t="n">
-        <v>0.9676470588235304</v>
-      </c>
-      <c r="BK8" t="n">
-        <v>-44</v>
-      </c>
-      <c r="BL8" t="n">
-        <v>-22</v>
-      </c>
-      <c r="BM8" t="n">
-        <v>-37.52777777777777</v>
-      </c>
-      <c r="BN8" t="n">
-        <v>2.8125</v>
-      </c>
-      <c r="BO8" t="n">
-        <v>-0.2716666666666666</v>
-      </c>
-      <c r="BP8" t="n">
-        <v>-0.5400000000000001</v>
-      </c>
-      <c r="BQ8" t="n">
-        <v>-0.1003405572755419</v>
-      </c>
-      <c r="BR8" t="n">
-        <v>-0.2290712074303405</v>
-      </c>
-      <c r="BS8" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BT8" t="n">
-        <v>-2.5</v>
-      </c>
-      <c r="BU8" t="n">
-        <v>-0.3777777777777778</v>
-      </c>
-      <c r="BV8" t="n">
-        <v>0.1555555555555554</v>
-      </c>
-      <c r="BW8" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="BX8" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="BY8" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="BZ8" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="CA8" t="n">
-        <v>-5.166666666666668</v>
-      </c>
-      <c r="CB8" t="n">
-        <v>-9</v>
-      </c>
-      <c r="CC8" t="n">
-        <v>1.364705882352943</v>
-      </c>
-      <c r="CD8" t="n">
-        <v>-0.8117647058823536</v>
-      </c>
-      <c r="CE8" t="n">
-        <v>17.41428571428572</v>
-      </c>
-      <c r="CF8" t="n">
-        <v>14.52747252747253</v>
-      </c>
-      <c r="CG8" t="n">
-        <v>1.205864358346425</v>
-      </c>
-      <c r="CH8" t="n">
-        <v>-0.3962024292621749</v>
-      </c>
-      <c r="CI8" t="n">
-        <v>-0.06311914003723511</v>
-      </c>
-      <c r="CJ8" t="n">
-        <v>-0.04139066229142319</v>
-      </c>
-      <c r="CK8" t="n">
-        <v>0.002561026643014934</v>
-      </c>
-      <c r="CL8" t="n">
-        <v>-0.01211082292910576</v>
-      </c>
-      <c r="CM8" t="n">
-        <v>1</v>
-      </c>
-      <c r="CN8" t="n">
-        <v>0.1666666666666667</v>
-      </c>
-      <c r="CO8" t="n">
-        <v>0.2205882352941176</v>
-      </c>
-      <c r="CP8" t="n">
-        <v>-0.2323529411764706</v>
-      </c>
-      <c r="CQ8" t="n">
-        <v>0.5400000000000001</v>
-      </c>
-      <c r="CR8" t="n">
-        <v>0.2716666666666666</v>
-      </c>
-      <c r="CS8" t="n">
-        <v>0.2290712074303405</v>
-      </c>
-      <c r="CT8" t="n">
-        <v>0.1003405572755419</v>
-      </c>
-      <c r="CU8" t="n">
-        <v>0.2683333333333335</v>
-      </c>
-      <c r="CV8" t="n">
-        <v>-0.2683333333333335</v>
-      </c>
-      <c r="CW8" t="n">
-        <v>0.1287306501547987</v>
-      </c>
-      <c r="CX8" t="n">
-        <v>-0.1287306501547987</v>
-      </c>
-      <c r="CY8" t="n">
-        <v>75.16844919786095</v>
-      </c>
-      <c r="CZ8" t="n">
-        <v>74.02520202020202</v>
-      </c>
-      <c r="DA8" t="inlineStr"/>
-      <c r="DB8" t="inlineStr"/>
-      <c r="DC8" t="n">
-        <v>0</v>
-      </c>
-      <c r="DD8" t="n">
-        <v>1.743556149732612</v>
-      </c>
-      <c r="DE8" t="n">
-        <v>-16333.33333333334</v>
-      </c>
-      <c r="DF8" t="n">
-        <v>0.9573486921985932</v>
-      </c>
-      <c r="DG8" t="n">
-        <v>661.8181818181838</v>
-      </c>
-      <c r="DH8" t="n">
-        <v>7201.99757317808</v>
-      </c>
-      <c r="DI8" t="n">
-        <v>-2</v>
-      </c>
-      <c r="DJ8" t="n">
-        <v>1.958181818181814</v>
-      </c>
-      <c r="DK8" t="n">
-        <v>2.450909090909093</v>
-      </c>
-      <c r="DL8" t="n">
-        <v>-5</v>
-      </c>
-      <c r="DM8" t="n">
-        <v>-2.666666666666657</v>
-      </c>
-      <c r="DN8" t="n">
-        <v>-1.666666666666671</v>
-      </c>
-      <c r="DO8" t="n">
-        <v>1.726549385165619</v>
-      </c>
-      <c r="DP8" t="n">
-        <v>-0.1176328599534884</v>
-      </c>
-      <c r="DQ8" t="n">
-        <v>-2.532727272727271</v>
-      </c>
-      <c r="DR8" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>zBdshgV6</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="n">
-        <v>45562.66666666666</v>
-      </c>
-      <c r="C9" t="n">
-        <v>101</v>
-      </c>
-      <c r="D9" t="n">
-        <v>133</v>
-      </c>
-      <c r="E9" t="n">
-        <v>206</v>
-      </c>
-      <c r="F9" t="n">
-        <v>399</v>
-      </c>
-      <c r="G9" t="n">
-        <v>55</v>
-      </c>
-      <c r="H9" t="n">
-        <v>551</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-      <c r="L9" t="n">
-        <v>12</v>
-      </c>
-      <c r="M9" t="n">
-        <v>83</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>1.645</v>
-      </c>
-      <c r="P9" t="n">
-        <v>-0.615</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0.7881286549707602</v>
-      </c>
-      <c r="R9" t="n">
-        <v>-0.3394444444444441</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2</v>
-      </c>
-      <c r="T9" t="n">
-        <v>-1</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0.9078947368421053</v>
-      </c>
-      <c r="V9" t="n">
-        <v>-0.6789473684210527</v>
-      </c>
-      <c r="W9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="X9" t="n">
-        <v>-3</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.473684210526316</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>-1.157894736842105</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>-4.5</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>2.789473684210526</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>-1.631578947368421</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>1.134210526315789</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>-0.2447368421052631</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>3</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>-3</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>0.9657894736842105</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>-1.078947368421053</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>11.25757575757576</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>-4.358585858585858</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>11.13506751841399</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>-7.429701731017521</v>
-      </c>
-      <c r="AQ9" t="inlineStr"/>
-      <c r="AR9" t="inlineStr"/>
-      <c r="AS9" t="n">
-        <v>465.3194258103033</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>-343.3607135324642</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>-6.5</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>29.36842105263158</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>-19.47368421052632</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>30</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>-5.5</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>16.63157894736842</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>-8.421052631578945</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>8</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>-19</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>3.002631578947369</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>-4.873684210526314</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>25</v>
-      </c>
-      <c r="BH9" t="n">
-        <v>-25</v>
-      </c>
-      <c r="BI9" t="n">
-        <v>14.68421052631578</v>
-      </c>
-      <c r="BJ9" t="n">
-        <v>-14.68421052631579</v>
-      </c>
-      <c r="BK9" t="inlineStr"/>
-      <c r="BL9" t="inlineStr"/>
-      <c r="BM9" t="n">
-        <v>210.4575163398692</v>
-      </c>
-      <c r="BN9" t="n">
-        <v>-100.281045751634</v>
-      </c>
-      <c r="BO9" t="n">
-        <v>1.855</v>
-      </c>
-      <c r="BP9" t="n">
-        <v>-1.385</v>
-      </c>
-      <c r="BQ9" t="n">
-        <v>0.4516374269005846</v>
-      </c>
-      <c r="BR9" t="n">
-        <v>0.0002631578947368263</v>
-      </c>
-      <c r="BS9" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BT9" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="BU9" t="n">
-        <v>-0.3651315789473686</v>
-      </c>
-      <c r="BV9" t="n">
-        <v>0.07565789473684204</v>
-      </c>
-      <c r="BW9" t="inlineStr"/>
-      <c r="BX9" t="inlineStr"/>
-      <c r="BY9" t="n">
-        <v>-0.09999999999999998</v>
-      </c>
-      <c r="BZ9" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="CA9" t="n">
-        <v>-6.5</v>
-      </c>
-      <c r="CB9" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="CC9" t="n">
-        <v>-4.202631578947368</v>
-      </c>
-      <c r="CD9" t="n">
-        <v>5.476315789473688</v>
-      </c>
-      <c r="CE9" t="inlineStr"/>
-      <c r="CF9" t="inlineStr"/>
-      <c r="CG9" t="n">
-        <v>-0.00362970222342085</v>
-      </c>
-      <c r="CH9" t="n">
-        <v>5.73964047971209</v>
-      </c>
-      <c r="CI9" t="n">
-        <v>-0.08351370851370851</v>
-      </c>
-      <c r="CJ9" t="n">
-        <v>0.02884628814861373</v>
-      </c>
-      <c r="CK9" t="n">
-        <v>-0.00604441160136189</v>
-      </c>
-      <c r="CL9" t="n">
-        <v>0.001355781349031471</v>
-      </c>
-      <c r="CM9" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="CN9" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO9" t="n">
-        <v>0.06315789473684208</v>
-      </c>
-      <c r="CP9" t="n">
-        <v>-0.3</v>
-      </c>
-      <c r="CQ9" t="n">
-        <v>1.385</v>
-      </c>
-      <c r="CR9" t="n">
-        <v>-1.855</v>
-      </c>
-      <c r="CS9" t="n">
-        <v>-0.0002631578947368263</v>
-      </c>
-      <c r="CT9" t="n">
-        <v>-0.4516374269005846</v>
-      </c>
-      <c r="CU9" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="CV9" t="n">
-        <v>-3.24</v>
-      </c>
-      <c r="CW9" t="n">
-        <v>0.4513742690058479</v>
-      </c>
-      <c r="CX9" t="n">
-        <v>-0.4513742690058479</v>
-      </c>
-      <c r="CY9" t="n">
-        <v>73.96895268474216</v>
-      </c>
-      <c r="CZ9" t="n">
-        <v>74.45713383838384</v>
-      </c>
-      <c r="DA9" t="inlineStr"/>
-      <c r="DB9" t="inlineStr"/>
-      <c r="DC9" t="n">
-        <v>2</v>
-      </c>
-      <c r="DD9" t="n">
-        <v>6.49310473152579</v>
-      </c>
-      <c r="DE9" t="n">
-        <v>86333.33333333333</v>
-      </c>
-      <c r="DF9" t="n">
-        <v>5.692529362622238</v>
-      </c>
-      <c r="DG9" t="n">
-        <v>43829.16666666667</v>
-      </c>
-      <c r="DH9" t="n">
-        <v>43529.69089390142</v>
-      </c>
-      <c r="DI9" t="n">
-        <v>7</v>
-      </c>
-      <c r="DJ9" t="n">
-        <v>5.674166666666679</v>
-      </c>
-      <c r="DK9" t="n">
-        <v>-2.291388888888889</v>
-      </c>
-      <c r="DL9" t="n">
-        <v>176</v>
-      </c>
-      <c r="DM9" t="n">
-        <v>-4</v>
-      </c>
-      <c r="DN9" t="n">
-        <v>10.66666666666667</v>
-      </c>
-      <c r="DO9" t="n">
-        <v>-0.2356173522040379</v>
-      </c>
-      <c r="DP9" t="n">
-        <v>3.35964850852622</v>
-      </c>
-      <c r="DQ9" t="n">
-        <v>2.572361111111093</v>
-      </c>
-      <c r="DR9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>MRfkjXaJ</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="n">
-        <v>45562.58333333334</v>
-      </c>
-      <c r="C10" t="n">
-        <v>101</v>
-      </c>
-      <c r="D10" t="n">
-        <v>133</v>
-      </c>
-      <c r="E10" t="n">
-        <v>342</v>
-      </c>
-      <c r="F10" t="n">
-        <v>133</v>
-      </c>
-      <c r="G10" t="n">
-        <v>55</v>
-      </c>
-      <c r="H10" t="n">
-        <v>551</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-      <c r="L10" t="n">
-        <v>286</v>
-      </c>
-      <c r="M10" t="n">
-        <v>127</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0.6399999999999999</v>
-      </c>
-      <c r="P10" t="n">
-        <v>-0.6100000000000001</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0.5113333333333334</v>
-      </c>
-      <c r="R10" t="n">
-        <v>-0.5159999999999999</v>
-      </c>
-      <c r="S10" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="T10" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0.7463235294117647</v>
-      </c>
-      <c r="V10" t="n">
-        <v>-0.5441176470588236</v>
-      </c>
-      <c r="W10" t="n">
-        <v>2</v>
-      </c>
-      <c r="X10" t="n">
-        <v>-5.5</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>0.3014705882352944</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>-1.75</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>-10.5</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>3.172794117647058</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>-3.908088235294118</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>0.3529411764705883</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>-0.5955882352941178</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>0.7205882352941178</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>-0.7904411764705883</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>6.14375</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>-8.659090909090908</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>9.331972627786225</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>-6.894003055767762</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>327.0383747178329</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>-526.0338733431516</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>437.2178924612557</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>-410.9630549796363</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>2</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>-15.5</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>17.50735294117646</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>-7.654411764705884</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>32</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>-17.5</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>22.33823529411764</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>-3.904411764705884</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>12</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>-6.5</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>-23.52573529411764</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>-31.30514705882353</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>2</v>
-      </c>
-      <c r="BH10" t="n">
-        <v>-2</v>
-      </c>
-      <c r="BI10" t="n">
-        <v>5.419117647058826</v>
-      </c>
-      <c r="BJ10" t="n">
-        <v>-5.419117647058826</v>
-      </c>
-      <c r="BK10" t="n">
-        <v>110</v>
-      </c>
-      <c r="BL10" t="n">
-        <v>-143</v>
-      </c>
-      <c r="BM10" t="n">
-        <v>100.0708333333333</v>
-      </c>
-      <c r="BN10" t="n">
-        <v>-18.36666666666667</v>
-      </c>
-      <c r="BO10" t="n">
-        <v>-0.1399999999999999</v>
-      </c>
-      <c r="BP10" t="n">
-        <v>0.1099999999999999</v>
-      </c>
-      <c r="BQ10" t="n">
-        <v>0.08866666666666656</v>
-      </c>
-      <c r="BR10" t="n">
-        <v>-0.2173333333333332</v>
-      </c>
-      <c r="BS10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT10" t="n">
-        <v>-2</v>
-      </c>
-      <c r="BU10" t="n">
-        <v>-1.57563025210084</v>
-      </c>
-      <c r="BV10" t="n">
-        <v>-0.1764705882352939</v>
-      </c>
-      <c r="BW10" t="inlineStr"/>
-      <c r="BX10" t="inlineStr"/>
-      <c r="BY10" t="n">
-        <v>-0.4642857142857143</v>
-      </c>
-      <c r="BZ10" t="n">
-        <v>0.1785714285714286</v>
-      </c>
-      <c r="CA10" t="n">
-        <v>9</v>
-      </c>
-      <c r="CB10" t="n">
-        <v>13</v>
-      </c>
-      <c r="CC10" t="n">
-        <v>-3.525735294117645</v>
-      </c>
-      <c r="CD10" t="n">
-        <v>2.147058823529413</v>
-      </c>
-      <c r="CE10" t="n">
-        <v>-24.65128205128205</v>
-      </c>
-      <c r="CF10" t="n">
-        <v>-12.95824175824176</v>
-      </c>
-      <c r="CG10" t="n">
-        <v>-0.8304905603068722</v>
-      </c>
-      <c r="CH10" t="n">
-        <v>1.781276689014177</v>
-      </c>
-      <c r="CI10" t="n">
-        <v>0.01007368282213002</v>
-      </c>
-      <c r="CJ10" t="n">
-        <v>-0.01986585682237856</v>
-      </c>
-      <c r="CK10" t="n">
-        <v>-0.006664377878282245</v>
-      </c>
-      <c r="CL10" t="n">
-        <v>-0.01406441410841039</v>
-      </c>
-      <c r="CM10" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN10" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO10" t="n">
-        <v>0.08088235294117646</v>
-      </c>
-      <c r="CP10" t="n">
-        <v>-0.04779411764705882</v>
-      </c>
-      <c r="CQ10" t="n">
-        <v>-0.1099999999999999</v>
-      </c>
-      <c r="CR10" t="n">
-        <v>0.1399999999999999</v>
-      </c>
-      <c r="CS10" t="n">
-        <v>0.2173333333333332</v>
-      </c>
-      <c r="CT10" t="n">
-        <v>-0.08866666666666656</v>
-      </c>
-      <c r="CU10" t="n">
-        <v>-0.2499999999999999</v>
-      </c>
-      <c r="CV10" t="n">
-        <v>0.2499999999999999</v>
-      </c>
-      <c r="CW10" t="n">
-        <v>0.306</v>
-      </c>
-      <c r="CX10" t="n">
-        <v>-0.306</v>
-      </c>
-      <c r="CY10" t="n">
-        <v>67.91701388888887</v>
-      </c>
-      <c r="CZ10" t="n">
-        <v>76.02363636363636</v>
-      </c>
-      <c r="DA10" t="inlineStr"/>
-      <c r="DB10" t="inlineStr"/>
-      <c r="DC10" t="n">
-        <v>0</v>
-      </c>
-      <c r="DD10" t="n">
-        <v>-6.131216577540116</v>
-      </c>
-      <c r="DE10" t="inlineStr"/>
-      <c r="DF10" t="n">
-        <v>-4.381655844155844</v>
-      </c>
-      <c r="DG10" t="n">
-        <v>-11861.36363636364</v>
-      </c>
-      <c r="DH10" t="inlineStr"/>
-      <c r="DI10" t="n">
-        <v>-3.5</v>
-      </c>
-      <c r="DJ10" t="n">
-        <v>-5.223636363636373</v>
-      </c>
-      <c r="DK10" t="n">
-        <v>-2.490909090909089</v>
-      </c>
-      <c r="DL10" t="n">
-        <v>-25</v>
-      </c>
-      <c r="DM10" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="DN10" t="n">
-        <v>-12.5</v>
-      </c>
-      <c r="DO10" t="n">
-        <v>-0.4159632034632068</v>
-      </c>
-      <c r="DP10" t="n">
-        <v>-0.2027922077922142</v>
-      </c>
-      <c r="DQ10" t="n">
-        <v>1.058181818181822</v>
-      </c>
-      <c r="DR10" t="n">
         <v>0</v>
       </c>
     </row>

--- a/data/france/p6_deployment/data_preparation/df_tagged.xlsx
+++ b/data/france/p6_deployment/data_preparation/df_tagged.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BV11"/>
+  <dimension ref="A1:BV15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -690,135 +690,135 @@
       </c>
       <c r="BA1" s="1" t="inlineStr">
         <is>
+          <t>dif_sum_wage_player_miss</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_pot_player_miss</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_sub</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_sub</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_value_player_start</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_wage_player_start</t>
+        </is>
+      </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
+          <t>dif_n_player_miss</t>
+        </is>
+      </c>
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_start</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_value_player_miss</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_start</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_start</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_rat_player_miss</t>
+        </is>
+      </c>
+      <c r="BM1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_start</t>
+        </is>
+      </c>
+      <c r="BN1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_wage_player_sub</t>
+        </is>
+      </c>
+      <c r="BO1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_miss</t>
+        </is>
+      </c>
+      <c r="BP1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rep_player_sub</t>
+        </is>
+      </c>
+      <c r="BQ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_rep_player_miss</t>
+        </is>
+      </c>
+      <c r="BR1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_miss</t>
+        </is>
+      </c>
+      <c r="BS1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_sub</t>
+        </is>
+      </c>
+      <c r="BT1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_sub</t>
+        </is>
+      </c>
+      <c r="BU1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_value_player_sub</t>
+        </is>
+      </c>
+      <c r="BV1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_rep_player_start</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_start</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_wage_player_start</t>
-        </is>
-      </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_wage_player_miss</t>
-        </is>
-      </c>
-      <c r="BE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_value_player_miss</t>
-        </is>
-      </c>
-      <c r="BF1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_miss</t>
-        </is>
-      </c>
-      <c r="BG1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_sub</t>
-        </is>
-      </c>
-      <c r="BH1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_start</t>
-        </is>
-      </c>
-      <c r="BI1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_sub</t>
-        </is>
-      </c>
-      <c r="BJ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_sub</t>
-        </is>
-      </c>
-      <c r="BK1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_rat_player_miss</t>
-        </is>
-      </c>
-      <c r="BL1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rep_player_sub</t>
-        </is>
-      </c>
-      <c r="BM1" s="1" t="inlineStr">
-        <is>
-          <t>dif_n_player_miss</t>
-        </is>
-      </c>
-      <c r="BN1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_start</t>
-        </is>
-      </c>
-      <c r="BO1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_wage_player_sub</t>
-        </is>
-      </c>
-      <c r="BP1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_value_player_sub</t>
-        </is>
-      </c>
-      <c r="BQ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_value_player_start</t>
-        </is>
-      </c>
-      <c r="BR1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_pot_player_miss</t>
-        </is>
-      </c>
-      <c r="BS1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_rep_player_miss</t>
-        </is>
-      </c>
-      <c r="BT1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_start</t>
-        </is>
-      </c>
-      <c r="BU1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_miss</t>
-        </is>
-      </c>
-      <c r="BV1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_sub</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>vwbmU7aL</t>
+          <t>nVutWTU8</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45583.65625</v>
+        <v>45585.65625</v>
       </c>
       <c r="C2" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D2" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E2" t="n">
-        <v>47</v>
+        <v>242</v>
       </c>
       <c r="F2" t="n">
-        <v>545</v>
+        <v>303</v>
       </c>
       <c r="G2" t="n">
         <v>55</v>
@@ -843,124 +843,122 @@
         <v>67</v>
       </c>
       <c r="M2" t="n">
-        <v>204</v>
+        <v>32</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.8216666666666665</v>
+        <v>0.2675000000000003</v>
       </c>
       <c r="P2" t="n">
-        <v>0.6910000000000001</v>
+        <v>0.3312337662337661</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.25</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>0.7142857142857142</v>
+        <v>0.1677018633540371</v>
       </c>
       <c r="S2" t="n">
-        <v>-2.166666666666667</v>
+        <v>1</v>
       </c>
       <c r="T2" t="n">
-        <v>1.924242424242424</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="U2" t="n">
-        <v>-6.333333333333336</v>
+        <v>2</v>
       </c>
       <c r="V2" t="n">
-        <v>3.926406926406926</v>
+        <v>-0.07575757575757436</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.3333333333333335</v>
+        <v>-1.833333333333333</v>
       </c>
       <c r="X2" t="n">
-        <v>0.8614718614718613</v>
+        <v>-0.2898550724637678</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.25</v>
+        <v>-1.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.149350649350649</v>
+        <v>0.0931677018633541</v>
       </c>
       <c r="AA2" t="n">
-        <v>23.72417582417582</v>
+        <v>13.64837662337662</v>
       </c>
       <c r="AB2" t="n">
-        <v>18.96545986160999</v>
+        <v>22.51874260109906</v>
       </c>
       <c r="AC2" t="n">
-        <v>960.051069202665</v>
+        <v>1013.039105890922</v>
       </c>
       <c r="AD2" t="n">
-        <v>950.6766004231388</v>
+        <v>949.6529071761213</v>
       </c>
       <c r="AE2" t="n">
-        <v>-21</v>
+        <v>60</v>
       </c>
       <c r="AF2" t="n">
-        <v>9.476190476190482</v>
+        <v>-18.5</v>
       </c>
       <c r="AG2" t="n">
-        <v>-39</v>
+        <v>36</v>
       </c>
       <c r="AH2" t="n">
-        <v>4.794486215538839</v>
+        <v>-2.600000000000009</v>
       </c>
       <c r="AI2" t="n">
-        <v>11.58333333333334</v>
+        <v>6.416666666666664</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-2.168831168831169</v>
+        <v>1.77432712215321</v>
       </c>
       <c r="AK2" t="n">
-        <v>-11.5</v>
+        <v>0.1666666666666714</v>
       </c>
       <c r="AL2" t="n">
-        <v>-6.852813852813853</v>
+        <v>-14.95670995670996</v>
       </c>
       <c r="AM2" t="n">
-        <v>-170.5</v>
+        <v>-174</v>
       </c>
       <c r="AN2" t="n">
-        <v>-82.54761904761904</v>
+        <v>-162.1578947368421</v>
       </c>
       <c r="AO2" t="n">
-        <v>-0.6666666666666665</v>
+        <v>1.75</v>
       </c>
       <c r="AP2" t="n">
-        <v>-0.05476190476190479</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>0</v>
-      </c>
+        <v>-0.4285714285714284</v>
+      </c>
+      <c r="AQ2" t="inlineStr"/>
       <c r="AR2" t="n">
-        <v>-0.6</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="AS2" t="n">
-        <v>-9.833333333333332</v>
+        <v>-3</v>
       </c>
       <c r="AT2" t="n">
-        <v>10.72077922077923</v>
+        <v>-0.9006211180124311</v>
       </c>
       <c r="AU2" t="n">
-        <v>24.70105664488017</v>
+        <v>11.02929292929293</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.7955410317106217</v>
+        <v>4.933930510137722</v>
       </c>
       <c r="AW2" t="n">
-        <v>-0.01604152717055943</v>
+        <v>0.2498401260104655</v>
       </c>
       <c r="AX2" t="n">
-        <v>-0.02103249985862573</v>
+        <v>0.0177163195716263</v>
       </c>
       <c r="AY2" t="n">
-        <v>-0.08333333333333331</v>
+        <v>0.25</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.1038961038961038</v>
+        <v>0.3995859213250518</v>
       </c>
       <c r="BA2" t="inlineStr"/>
       <c r="BB2" t="inlineStr"/>
@@ -988,23 +986,23 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>OUcd1IPH</t>
+          <t>vPIEF8pS</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45571.65625</v>
+        <v>45585.5</v>
       </c>
       <c r="C3" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D3" t="n">
         <v>133</v>
       </c>
       <c r="E3" t="n">
-        <v>535</v>
+        <v>341</v>
       </c>
       <c r="F3" t="n">
-        <v>129</v>
+        <v>292</v>
       </c>
       <c r="G3" t="n">
         <v>55</v>
@@ -1026,119 +1024,127 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>97</v>
+        <v>243</v>
       </c>
       <c r="M3" t="n">
-        <v>211</v>
+        <v>32</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>1.175</v>
+        <v>1.204166666666667</v>
       </c>
       <c r="P3" t="n">
-        <v>0.1932380952380953</v>
+        <v>0.4747941176470589</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.5</v>
+        <v>0.75</v>
       </c>
       <c r="R3" t="n">
-        <v>0.2673913043478259</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="S3" t="n">
-        <v>1.166666666666666</v>
+        <v>3.916666666666667</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.0239130434782604</v>
+        <v>1.852813852813854</v>
       </c>
       <c r="U3" t="n">
-        <v>-2.5</v>
+        <v>5.333333333333334</v>
       </c>
       <c r="V3" t="n">
-        <v>2.886956521739128</v>
+        <v>3.803030303030303</v>
       </c>
       <c r="W3" t="n">
-        <v>2.333333333333333</v>
+        <v>0.4166666666666666</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.05</v>
+        <v>-0.1580952380952381</v>
       </c>
       <c r="Y3" t="n">
-        <v>-0.5</v>
+        <v>0.25</v>
       </c>
       <c r="Z3" t="n">
-        <v>-1.297826086956522</v>
+        <v>-0.5942857142857145</v>
       </c>
       <c r="AA3" t="n">
-        <v>18.98333333333333</v>
+        <v>12.33495670995671</v>
       </c>
       <c r="AB3" t="n">
-        <v>20.07730644939295</v>
-      </c>
-      <c r="AC3" t="inlineStr"/>
+        <v>16.45948040267177</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>857.0465757170743</v>
+      </c>
       <c r="AD3" t="n">
-        <v>1106.84557920803</v>
+        <v>918.225894011082</v>
       </c>
       <c r="AE3" t="n">
-        <v>-46.5</v>
+        <v>45.83333333333334</v>
       </c>
       <c r="AF3" t="n">
-        <v>-25.15789473684211</v>
+        <v>-1.992857142857133</v>
       </c>
       <c r="AG3" t="n">
-        <v>17.5</v>
+        <v>7.833333333333336</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.739234449760765</v>
+        <v>5.997619047619047</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.1666666666666679</v>
+        <v>16.75</v>
       </c>
       <c r="AJ3" t="n">
-        <v>2.939130434782601</v>
+        <v>1.647619047619044</v>
       </c>
       <c r="AK3" t="n">
-        <v>-25</v>
+        <v>17.33333333333334</v>
       </c>
       <c r="AL3" t="n">
-        <v>-25.05217391304348</v>
-      </c>
-      <c r="AM3" t="inlineStr"/>
+        <v>-4.389610389610382</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>111</v>
+      </c>
       <c r="AN3" t="n">
-        <v>-296.6825396825398</v>
+        <v>-56.47631578947363</v>
       </c>
       <c r="AO3" t="n">
-        <v>2.166666666666667</v>
+        <v>2</v>
       </c>
       <c r="AP3" t="n">
-        <v>-0.7428571428571427</v>
-      </c>
-      <c r="AQ3" t="inlineStr"/>
+        <v>0.6839826839826839</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>1</v>
+      </c>
       <c r="AR3" t="n">
-        <v>0.25</v>
+        <v>0.6</v>
       </c>
       <c r="AS3" t="n">
-        <v>-5.333333333333334</v>
+        <v>-1.416666666666666</v>
       </c>
       <c r="AT3" t="n">
-        <v>0.3304347826086982</v>
-      </c>
-      <c r="AU3" t="inlineStr"/>
+        <v>4.590476190476199</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>-3.813967019822289</v>
+      </c>
       <c r="AV3" t="n">
-        <v>8.346570588191877</v>
+        <v>-1.130663267998857</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.06493494966151531</v>
+        <v>-0.01884092027781634</v>
       </c>
       <c r="AX3" t="n">
-        <v>0.0441937315738896</v>
+        <v>0.01341845613566123</v>
       </c>
       <c r="AY3" t="n">
-        <v>0.5</v>
+        <v>0.5833333333333333</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.1956521739130435</v>
+        <v>0.2</v>
       </c>
       <c r="BA3" t="inlineStr"/>
       <c r="BB3" t="inlineStr"/>
@@ -1166,23 +1172,23 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>rZUMHwAb</t>
+          <t>h8K6HUFF</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45571.5</v>
+        <v>45585.5</v>
       </c>
       <c r="C4" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D4" t="n">
         <v>133</v>
       </c>
       <c r="E4" t="n">
-        <v>211</v>
+        <v>342</v>
       </c>
       <c r="F4" t="n">
-        <v>122</v>
+        <v>579</v>
       </c>
       <c r="G4" t="n">
         <v>55</v>
@@ -1204,130 +1210,134 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>128</v>
+        <v>272</v>
       </c>
       <c r="M4" t="n">
-        <v>204</v>
+        <v>10</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>0.8233333333333328</v>
+        <v>0.2433333333333327</v>
       </c>
       <c r="P4" t="n">
-        <v>1.532606516290727</v>
+        <v>0.9547023809523807</v>
       </c>
       <c r="Q4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R4" t="n">
-        <v>2.077922077922078</v>
+        <v>1.090909090909091</v>
       </c>
       <c r="S4" t="n">
-        <v>6.333333333333332</v>
+        <v>0.333333333333333</v>
       </c>
       <c r="T4" t="n">
-        <v>4.831818181818182</v>
+        <v>2.067099567099568</v>
       </c>
       <c r="U4" t="n">
-        <v>10.33333333333333</v>
+        <v>4</v>
       </c>
       <c r="V4" t="n">
-        <v>12.10909090909091</v>
+        <v>8.283549783549784</v>
       </c>
       <c r="W4" t="n">
-        <v>1.333333333333333</v>
+        <v>-0.6666666666666667</v>
       </c>
       <c r="X4" t="n">
-        <v>1.257575757575757</v>
+        <v>1.227272727272727</v>
       </c>
       <c r="Y4" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.097402597402597</v>
+        <v>1.5</v>
       </c>
       <c r="AA4" t="n">
-        <v>12.8256253006253</v>
+        <v>21.324185999186</v>
       </c>
       <c r="AB4" t="n">
-        <v>15.15757425466121</v>
+        <v>16.95514331622656</v>
       </c>
       <c r="AC4" t="n">
-        <v>977.046065597882</v>
+        <v>1116.578180758256</v>
       </c>
       <c r="AD4" t="n">
-        <v>789.7665696532363</v>
+        <v>826.0456466161302</v>
       </c>
       <c r="AE4" t="n">
-        <v>84.5</v>
+        <v>-8</v>
       </c>
       <c r="AF4" t="n">
-        <v>46.4360902255639</v>
+        <v>34.77619047619046</v>
       </c>
       <c r="AG4" t="n">
-        <v>22.5</v>
+        <v>14</v>
       </c>
       <c r="AH4" t="n">
-        <v>34.63157894736842</v>
+        <v>27.96428571428572</v>
       </c>
       <c r="AI4" t="n">
-        <v>15</v>
+        <v>7.666666666666664</v>
       </c>
       <c r="AJ4" t="n">
-        <v>9.623376623376622</v>
+        <v>7.40909090909091</v>
       </c>
       <c r="AK4" t="n">
-        <v>10</v>
+        <v>-7.333333333333343</v>
       </c>
       <c r="AL4" t="n">
-        <v>21.24545454545455</v>
+        <v>14.67532467532467</v>
       </c>
       <c r="AM4" t="n">
-        <v>52</v>
+        <v>-264</v>
       </c>
       <c r="AN4" t="n">
-        <v>210.6888888888889</v>
+        <v>130.7869674185463</v>
       </c>
       <c r="AO4" t="n">
-        <v>-1.333333333333333</v>
+        <v>2.166666666666667</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.2727272727272729</v>
+        <v>-1.466666666666667</v>
       </c>
       <c r="AQ4" t="inlineStr"/>
       <c r="AR4" t="n">
         <v>-1.5</v>
       </c>
       <c r="AS4" t="n">
-        <v>-5.999999999999998</v>
+        <v>-0.6666666666666643</v>
       </c>
       <c r="AT4" t="n">
-        <v>0.298701298701296</v>
+        <v>-5.681818181818176</v>
       </c>
       <c r="AU4" t="n">
-        <v>-13.4021645021645</v>
+        <v>-26.32571317571317</v>
       </c>
       <c r="AV4" t="n">
-        <v>-6.044117766739793</v>
+        <v>-3.162634977319126</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.1489057239057239</v>
+        <v>0.04019339286734013</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.0202282440576764</v>
+        <v>-0.008130857806083018</v>
       </c>
       <c r="AY4" t="n">
-        <v>0.6666666666666666</v>
+        <v>0</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.5627705627705628</v>
+        <v>0.1818181818181819</v>
       </c>
       <c r="BA4" t="inlineStr"/>
       <c r="BB4" t="inlineStr"/>
-      <c r="BC4" t="inlineStr"/>
-      <c r="BD4" t="inlineStr"/>
+      <c r="BC4" t="n">
+        <v>-5.52950178476496</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>4.119552669552668</v>
+      </c>
       <c r="BE4" t="inlineStr"/>
       <c r="BF4" t="inlineStr"/>
       <c r="BG4" t="inlineStr"/>
@@ -1339,34 +1349,42 @@
       <c r="BM4" t="inlineStr"/>
       <c r="BN4" t="inlineStr"/>
       <c r="BO4" t="inlineStr"/>
-      <c r="BP4" t="inlineStr"/>
+      <c r="BP4" t="n">
+        <v>0</v>
+      </c>
       <c r="BQ4" t="inlineStr"/>
       <c r="BR4" t="inlineStr"/>
-      <c r="BS4" t="inlineStr"/>
-      <c r="BT4" t="inlineStr"/>
-      <c r="BU4" t="inlineStr"/>
+      <c r="BS4" t="n">
+        <v>-5.746164654059399</v>
+      </c>
+      <c r="BT4" t="n">
+        <v>-0.2351826536037152</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>-757402.9771398194</v>
+      </c>
       <c r="BV4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>WhWcJjo3</t>
+          <t>WMcg8Qx2</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45571.5</v>
+        <v>45585.5</v>
       </c>
       <c r="C5" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D5" t="n">
         <v>133</v>
       </c>
       <c r="E5" t="n">
-        <v>826</v>
+        <v>858</v>
       </c>
       <c r="F5" t="n">
-        <v>157</v>
+        <v>370</v>
       </c>
       <c r="G5" t="n">
         <v>55</v>
@@ -1388,127 +1406,127 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>35</v>
+        <v>168</v>
       </c>
       <c r="M5" t="n">
-        <v>234</v>
+        <v>163</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>1.5</v>
+        <v>1.046666666666666</v>
       </c>
       <c r="P5" t="n">
-        <v>0.9404999999999997</v>
+        <v>-0.280828157349897</v>
       </c>
       <c r="Q5" t="n">
         <v>2</v>
       </c>
       <c r="R5" t="n">
-        <v>1.240909090909091</v>
+        <v>-0.25</v>
       </c>
       <c r="S5" t="n">
-        <v>1.666666666666667</v>
+        <v>3.416666666666667</v>
       </c>
       <c r="T5" t="n">
-        <v>1.140476190476191</v>
+        <v>-1.321428571428572</v>
       </c>
       <c r="U5" t="n">
-        <v>0.6666666666666679</v>
+        <v>8.333333333333334</v>
       </c>
       <c r="V5" t="n">
-        <v>5.69761904761905</v>
+        <v>0.6904761904761898</v>
       </c>
       <c r="W5" t="n">
-        <v>3</v>
+        <v>0.3333333333333335</v>
       </c>
       <c r="X5" t="n">
-        <v>0.3181818181818183</v>
+        <v>-0.7440476190476191</v>
       </c>
       <c r="Y5" t="n">
-        <v>3</v>
+        <v>0.75</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.4363636363636365</v>
+        <v>-1.410714285714286</v>
       </c>
       <c r="AA5" t="n">
-        <v>20.9541847041847</v>
+        <v>16.97682329244829</v>
       </c>
       <c r="AB5" t="n">
-        <v>18.72831971010709</v>
+        <v>20.70092448025401</v>
       </c>
       <c r="AC5" t="n">
-        <v>1062.036649682667</v>
+        <v>1019.071876069671</v>
       </c>
       <c r="AD5" t="n">
-        <v>805.5768135399308</v>
+        <v>998.0526490373254</v>
       </c>
       <c r="AE5" t="n">
-        <v>23.5</v>
+        <v>-48.16666666666666</v>
       </c>
       <c r="AF5" t="n">
-        <v>37.39999999999999</v>
+        <v>-7.576086956521735</v>
       </c>
       <c r="AG5" t="n">
-        <v>-4</v>
+        <v>2.166666666666664</v>
       </c>
       <c r="AH5" t="n">
-        <v>30.67105263157895</v>
+        <v>2.945652173913047</v>
       </c>
       <c r="AI5" t="n">
-        <v>9.333333333333329</v>
+        <v>4.75</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.822727272727263</v>
+        <v>2.303571428571423</v>
       </c>
       <c r="AK5" t="n">
-        <v>-5.999999999999993</v>
+        <v>1.5</v>
       </c>
       <c r="AL5" t="n">
-        <v>12.0952380952381</v>
+        <v>-9.023809523809518</v>
       </c>
       <c r="AM5" t="n">
-        <v>-348</v>
+        <v>-115.5</v>
       </c>
       <c r="AN5" t="n">
-        <v>107.3040935672514</v>
+        <v>-118.421052631579</v>
       </c>
       <c r="AO5" t="n">
-        <v>-1</v>
+        <v>3.000000000000001</v>
       </c>
       <c r="AP5" t="n">
-        <v>-0.338345864661654</v>
+        <v>-0.1385281385281385</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="AR5" t="n">
-        <v>-0.25</v>
+        <v>0.7</v>
       </c>
       <c r="AS5" t="n">
-        <v>-2.000000000000002</v>
+        <v>8.916666666666668</v>
       </c>
       <c r="AT5" t="n">
-        <v>-1.227272727272727</v>
+        <v>7.666666666666668</v>
       </c>
       <c r="AU5" t="n">
-        <v>3.172786690433753</v>
+        <v>-59.46730769230769</v>
       </c>
       <c r="AV5" t="n">
-        <v>-3.321614195664901</v>
+        <v>-2.172860380457625</v>
       </c>
       <c r="AW5" t="n">
-        <v>-0.06763903654885545</v>
+        <v>-0.01613637689317193</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.02955321374852892</v>
+        <v>0.02000766868186468</v>
       </c>
       <c r="AY5" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.5833333333333333</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.2363636363636363</v>
+        <v>-0.1488095238095238</v>
       </c>
       <c r="BA5" t="inlineStr"/>
       <c r="BB5" t="inlineStr"/>
@@ -1536,23 +1554,23 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>4nvCemgd</t>
+          <t>b9aoAn8k</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45571.5</v>
+        <v>45585.41666666666</v>
       </c>
       <c r="C6" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D6" t="n">
         <v>133</v>
       </c>
       <c r="E6" t="n">
-        <v>736</v>
+        <v>194</v>
       </c>
       <c r="F6" t="n">
-        <v>176</v>
+        <v>39</v>
       </c>
       <c r="G6" t="n">
         <v>55</v>
@@ -1574,157 +1592,145 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>312</v>
+        <v>198</v>
       </c>
       <c r="M6" t="n">
-        <v>163</v>
+        <v>138</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.1633333333333332</v>
+        <v>-0.7133333333333333</v>
       </c>
       <c r="P6" t="n">
-        <v>0.2500238095238099</v>
+        <v>0.3479999999999996</v>
       </c>
       <c r="Q6" t="n">
         <v>-1</v>
       </c>
       <c r="R6" t="n">
-        <v>0.5785714285714285</v>
+        <v>0.6883116883116883</v>
       </c>
       <c r="S6" t="n">
-        <v>2.333333333333333</v>
+        <v>1.000000000000001</v>
       </c>
       <c r="T6" t="n">
-        <v>1.061904761904762</v>
+        <v>0.7214285714285715</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.666666666666666</v>
+        <v>3.333333333333332</v>
       </c>
       <c r="V6" t="n">
-        <v>0.6261904761904766</v>
+        <v>3.397619047619049</v>
       </c>
       <c r="W6" t="n">
-        <v>0.6666666666666666</v>
+        <v>-0.6666666666666666</v>
       </c>
       <c r="X6" t="n">
-        <v>0.1904761904761905</v>
+        <v>-0.1904761904761905</v>
       </c>
       <c r="Y6" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.5785714285714285</v>
+        <v>-0.974025974025974</v>
       </c>
       <c r="AA6" t="n">
-        <v>19.12065897065897</v>
+        <v>17.72994227994228</v>
       </c>
       <c r="AB6" t="n">
-        <v>20.24061302687353</v>
+        <v>19.07079056533327</v>
       </c>
       <c r="AC6" t="n">
-        <v>947.0370781359841</v>
+        <v>1307.559727809067</v>
       </c>
       <c r="AD6" t="n">
-        <v>962.6491064253298</v>
+        <v>991.4230134947686</v>
       </c>
       <c r="AE6" t="n">
-        <v>3</v>
+        <v>-29.5</v>
       </c>
       <c r="AF6" t="n">
-        <v>-12.81578947368421</v>
+        <v>-14.8315789473684</v>
       </c>
       <c r="AG6" t="n">
-        <v>-12.5</v>
+        <v>-4.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>-2.368421052631582</v>
+        <v>1.421052631578945</v>
       </c>
       <c r="AI6" t="n">
-        <v>13.66666666666666</v>
+        <v>-4</v>
       </c>
       <c r="AJ6" t="n">
-        <v>-0.2999999999999972</v>
+        <v>-0.5324675324675354</v>
       </c>
       <c r="AK6" t="n">
-        <v>-2.666666666666657</v>
+        <v>-26.66666666666667</v>
       </c>
       <c r="AL6" t="n">
-        <v>-15.33333333333333</v>
+        <v>-15.37619047619049</v>
       </c>
       <c r="AM6" t="n">
-        <v>-135</v>
+        <v>-580</v>
       </c>
       <c r="AN6" t="n">
-        <v>-152.3567251461988</v>
+        <v>-156</v>
       </c>
       <c r="AO6" t="n">
-        <v>-0.6666666666666667</v>
+        <v>0.5</v>
       </c>
       <c r="AP6" t="n">
-        <v>-0.8547619047619046</v>
+        <v>0.2222222222222223</v>
       </c>
       <c r="AQ6" t="inlineStr"/>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>-0.75</v>
       </c>
       <c r="AS6" t="n">
-        <v>-8.333333333333334</v>
+        <v>-1.333333333333336</v>
       </c>
       <c r="AT6" t="n">
-        <v>-0.4880952380952408</v>
+        <v>4.40909090909091</v>
       </c>
       <c r="AU6" t="n">
-        <v>17.4546783625731</v>
+        <v>15.44088345864661</v>
       </c>
       <c r="AV6" t="n">
-        <v>5.217937060246109</v>
+        <v>2.593518384197457</v>
       </c>
       <c r="AW6" t="n">
-        <v>-0.08528693528693526</v>
+        <v>-0.0396253353120958</v>
       </c>
       <c r="AX6" t="n">
-        <v>-0.008239073080847904</v>
+        <v>-0.01161466584378629</v>
       </c>
       <c r="AY6" t="n">
         <v>0</v>
       </c>
       <c r="AZ6" t="n">
-        <v>-0.2</v>
+        <v>-0.2835497835497836</v>
       </c>
       <c r="BA6" t="inlineStr"/>
       <c r="BB6" t="inlineStr"/>
       <c r="BC6" t="inlineStr"/>
-      <c r="BD6" t="n">
-        <v>-6000</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>-1400000</v>
-      </c>
+      <c r="BD6" t="inlineStr"/>
+      <c r="BE6" t="inlineStr"/>
       <c r="BF6" t="inlineStr"/>
       <c r="BG6" t="inlineStr"/>
       <c r="BH6" t="inlineStr"/>
       <c r="BI6" t="inlineStr"/>
       <c r="BJ6" t="inlineStr"/>
-      <c r="BK6" t="n">
-        <v>-64</v>
-      </c>
+      <c r="BK6" t="inlineStr"/>
       <c r="BL6" t="inlineStr"/>
-      <c r="BM6" t="n">
-        <v>-1</v>
-      </c>
+      <c r="BM6" t="inlineStr"/>
       <c r="BN6" t="inlineStr"/>
       <c r="BO6" t="inlineStr"/>
       <c r="BP6" t="inlineStr"/>
       <c r="BQ6" t="inlineStr"/>
-      <c r="BR6" t="n">
-        <v>-76</v>
-      </c>
-      <c r="BS6" t="n">
-        <v>-1</v>
-      </c>
+      <c r="BR6" t="inlineStr"/>
+      <c r="BS6" t="inlineStr"/>
       <c r="BT6" t="inlineStr"/>
       <c r="BU6" t="inlineStr"/>
       <c r="BV6" t="inlineStr"/>
@@ -1732,11 +1738,11 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>IHSe3ve5</t>
+          <t>S2WzL3M7</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45571.41666666666</v>
+        <v>45584.66666666666</v>
       </c>
       <c r="C7" t="n">
         <v>102</v>
@@ -1745,10 +1751,10 @@
         <v>133</v>
       </c>
       <c r="E7" t="n">
-        <v>56</v>
+        <v>206</v>
       </c>
       <c r="F7" t="n">
-        <v>599</v>
+        <v>516</v>
       </c>
       <c r="G7" t="n">
         <v>55</v>
@@ -1770,119 +1776,123 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>152</v>
+        <v>40</v>
       </c>
       <c r="M7" t="n">
-        <v>226</v>
+        <v>258</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.1133333333333331</v>
+        <v>2.4</v>
       </c>
       <c r="P7" t="n">
-        <v>0.4725833333333327</v>
+        <v>1.395833333333333</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R7" t="n">
-        <v>0.5357142857142858</v>
+        <v>1.891304347826087</v>
       </c>
       <c r="S7" t="n">
-        <v>1.333333333333333</v>
+        <v>6.333333333333334</v>
       </c>
       <c r="T7" t="n">
-        <v>0.5749999999999997</v>
+        <v>3.257575757575758</v>
       </c>
       <c r="U7" t="n">
-        <v>0.6666666666666661</v>
+        <v>16</v>
       </c>
       <c r="V7" t="n">
-        <v>1.741666666666665</v>
+        <v>9.848484848484848</v>
       </c>
       <c r="W7" t="n">
-        <v>-1.333333333333333</v>
+        <v>3.666666666666667</v>
       </c>
       <c r="X7" t="n">
-        <v>0.2499999999999998</v>
+        <v>1.846014492753623</v>
       </c>
       <c r="Y7" t="n">
-        <v>-2</v>
+        <v>4</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.25</v>
+        <v>2.402173913043478</v>
       </c>
       <c r="AA7" t="n">
-        <v>15.57640692640693</v>
+        <v>15.82806637806638</v>
       </c>
       <c r="AB7" t="n">
-        <v>19.29995453130965</v>
-      </c>
-      <c r="AC7" t="inlineStr"/>
+        <v>15.80386235225362</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>795.0576828669612</v>
+      </c>
       <c r="AD7" t="n">
-        <v>843.9063364604394</v>
+        <v>733.6018746331549</v>
       </c>
       <c r="AE7" t="n">
-        <v>39.5</v>
+        <v>86</v>
       </c>
       <c r="AF7" t="n">
-        <v>26.21739130434781</v>
+        <v>87.59006211180125</v>
       </c>
       <c r="AG7" t="n">
-        <v>22</v>
+        <v>84</v>
       </c>
       <c r="AH7" t="n">
-        <v>25.39588100686499</v>
+        <v>52.10144927536233</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>9.666666666666675</v>
       </c>
       <c r="AJ7" t="n">
-        <v>8.541666666666671</v>
+        <v>8.251811594202906</v>
       </c>
       <c r="AK7" t="n">
-        <v>10</v>
+        <v>36.66666666666666</v>
       </c>
       <c r="AL7" t="n">
-        <v>13.78333333333333</v>
-      </c>
-      <c r="AM7" t="inlineStr"/>
+        <v>43.86363636363636</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>202</v>
+      </c>
       <c r="AN7" t="n">
-        <v>127.2222222222222</v>
+        <v>464.1636363636364</v>
       </c>
       <c r="AO7" t="n">
         <v>-1.333333333333333</v>
       </c>
       <c r="AP7" t="n">
-        <v>-0.8581235697940504</v>
+        <v>-0.4318181818181819</v>
       </c>
       <c r="AQ7" t="inlineStr"/>
-      <c r="AR7" t="n">
-        <v>0.9166666666666666</v>
-      </c>
+      <c r="AR7" t="inlineStr"/>
       <c r="AS7" t="n">
-        <v>6.333333333333334</v>
+        <v>-1.666666666666663</v>
       </c>
       <c r="AT7" t="n">
-        <v>-9.624999999999996</v>
-      </c>
-      <c r="AU7" t="inlineStr"/>
+        <v>-6.036231884057976</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>-11.2068376068376</v>
+      </c>
       <c r="AV7" t="n">
-        <v>0.3886073861305288</v>
+        <v>-11.34529829707059</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.07928069062305482</v>
+        <v>0.0445958295958296</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.03009688049080859</v>
+        <v>0.01949881360720211</v>
       </c>
       <c r="AY7" t="n">
-        <v>-0.3333333333333333</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.2202380952380953</v>
+        <v>0.3804347826086957</v>
       </c>
       <c r="BA7" t="inlineStr"/>
       <c r="BB7" t="inlineStr"/>
@@ -1910,23 +1920,23 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>8Kp3c9Oq</t>
+          <t>OAZJOoNr</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45570.66666666666</v>
+        <v>45584.58333333334</v>
       </c>
       <c r="C8" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D8" t="n">
         <v>133</v>
       </c>
       <c r="E8" t="n">
-        <v>573</v>
+        <v>528</v>
       </c>
       <c r="F8" t="n">
-        <v>33</v>
+        <v>176</v>
       </c>
       <c r="G8" t="n">
         <v>55</v>
@@ -1948,125 +1958,125 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>40</v>
+        <v>272</v>
       </c>
       <c r="M8" t="n">
-        <v>234</v>
+        <v>163</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.563333333333333</v>
+        <v>-0.163333333333333</v>
       </c>
       <c r="P8" t="n">
-        <v>0.546190476190476</v>
+        <v>0.5589210526315789</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2</v>
+        <v>0.25</v>
       </c>
       <c r="R8" t="n">
-        <v>0.4415584415584415</v>
+        <v>0.8628571428571428</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.5</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="T8" t="n">
-        <v>0.9393939393939394</v>
+        <v>1.508333333333333</v>
       </c>
       <c r="U8" t="n">
-        <v>-7.5</v>
+        <v>-1.333333333333334</v>
       </c>
       <c r="V8" t="n">
-        <v>3.222943722943723</v>
+        <v>2.733333333333334</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.5</v>
+        <v>-1.110223024625157e-16</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.05844155844155874</v>
+        <v>0.52</v>
       </c>
       <c r="Y8" t="n">
-        <v>-1</v>
+        <v>0.25</v>
       </c>
       <c r="Z8" t="n">
-        <v>-0.7922077922077921</v>
+        <v>0.9828571428571429</v>
       </c>
       <c r="AA8" t="n">
-        <v>25.36421911421911</v>
+        <v>21.0459743959744</v>
       </c>
       <c r="AB8" t="n">
-        <v>20.39186050590554</v>
+        <v>20.25060286391169</v>
       </c>
       <c r="AC8" t="n">
-        <v>1012.073091915415</v>
+        <v>1201.0526310704</v>
       </c>
       <c r="AD8" t="n">
-        <v>929.8989235672777</v>
+        <v>890.0762537686242</v>
       </c>
       <c r="AE8" t="n">
-        <v>-30</v>
+        <v>-10.5</v>
       </c>
       <c r="AF8" t="n">
-        <v>-5.813636363636363</v>
+        <v>-1.794050343249424</v>
       </c>
       <c r="AG8" t="n">
-        <v>11.5</v>
+        <v>-20</v>
       </c>
       <c r="AH8" t="n">
-        <v>8.009090909090915</v>
+        <v>5.501144164759722</v>
       </c>
       <c r="AI8" t="n">
-        <v>-15.5</v>
+        <v>6.083333333333336</v>
       </c>
       <c r="AJ8" t="n">
-        <v>6.097402597402592</v>
+        <v>2.291428571428577</v>
       </c>
       <c r="AK8" t="n">
-        <v>-34.33333333333333</v>
+        <v>-18</v>
       </c>
       <c r="AL8" t="n">
-        <v>-8.069264069264065</v>
+        <v>-2.75</v>
       </c>
       <c r="AM8" t="n">
-        <v>-188.5</v>
+        <v>-581</v>
       </c>
       <c r="AN8" t="n">
-        <v>-63.14047619047614</v>
+        <v>-21.50505050505052</v>
       </c>
       <c r="AO8" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>-0.6666666666666665</v>
       </c>
       <c r="AP8" t="n">
-        <v>-1.380952380952381</v>
+        <v>-0.6891304347826086</v>
       </c>
       <c r="AQ8" t="inlineStr"/>
       <c r="AR8" t="n">
-        <v>-1.6</v>
+        <v>0</v>
       </c>
       <c r="AS8" t="n">
-        <v>-4.833333333333336</v>
+        <v>-1.583333333333334</v>
       </c>
       <c r="AT8" t="n">
-        <v>-9.62770562770563</v>
+        <v>0.3447619047619099</v>
       </c>
       <c r="AU8" t="n">
-        <v>10.40568181818182</v>
+        <v>40.22222222222222</v>
       </c>
       <c r="AV8" t="n">
-        <v>5.381365545048045</v>
+        <v>2.572943978029102</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.005492187016459711</v>
+        <v>0.002445702445702448</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.01502607798626984</v>
+        <v>-0.01043226675908079</v>
       </c>
       <c r="AY8" t="n">
-        <v>-0.3333333333333334</v>
+        <v>-0.25</v>
       </c>
       <c r="AZ8" t="n">
-        <v>-0.03896103896103895</v>
+        <v>-0.07047619047619047</v>
       </c>
       <c r="BA8" t="inlineStr"/>
       <c r="BB8" t="inlineStr"/>
@@ -2094,23 +2104,23 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>Wf14adfU</t>
+          <t>WzwSMPie</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45570.58333333334</v>
+        <v>45584.5</v>
       </c>
       <c r="C9" t="n">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D9" t="n">
         <v>133</v>
       </c>
       <c r="E9" t="n">
-        <v>777</v>
+        <v>211</v>
       </c>
       <c r="F9" t="n">
-        <v>226</v>
+        <v>399</v>
       </c>
       <c r="G9" t="n">
         <v>55</v>
@@ -2132,151 +2142,139 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>198</v>
+        <v>128</v>
       </c>
       <c r="M9" t="n">
-        <v>138</v>
+        <v>211</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.7916666666666667</v>
+        <v>1.106666666666666</v>
       </c>
       <c r="P9" t="n">
-        <v>1.216499999999999</v>
+        <v>0.8141866028708137</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.5</v>
+        <v>0.25</v>
       </c>
       <c r="R9" t="n">
-        <v>1.12987012987013</v>
+        <v>0.8068181818181818</v>
       </c>
       <c r="S9" t="n">
-        <v>2.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="T9" t="n">
-        <v>3.35</v>
+        <v>1.932608695652174</v>
       </c>
       <c r="U9" t="n">
-        <v>-2</v>
+        <v>6.333333333333334</v>
       </c>
       <c r="V9" t="n">
-        <v>8.721428571428572</v>
+        <v>4.939130434782609</v>
       </c>
       <c r="W9" t="n">
-        <v>1</v>
+        <v>2.333333333333333</v>
       </c>
       <c r="X9" t="n">
-        <v>1.614718614718615</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.5</v>
+        <v>3.75</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.428571428571429</v>
+        <v>1.340909090909091</v>
       </c>
       <c r="AA9" t="n">
-        <v>18.38396464646465</v>
+        <v>16.59060846560847</v>
       </c>
       <c r="AB9" t="n">
-        <v>16.15955627910672</v>
+        <v>18.4174195101337</v>
       </c>
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="n">
-        <v>817.9126110509915</v>
+        <v>858.213203771831</v>
       </c>
       <c r="AE9" t="n">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="AF9" t="n">
-        <v>42.37631578947369</v>
+        <v>15.80622009569377</v>
       </c>
       <c r="AG9" t="n">
-        <v>65</v>
+        <v>7</v>
       </c>
       <c r="AH9" t="n">
-        <v>28.30789473684211</v>
+        <v>13.54066985645933</v>
       </c>
       <c r="AI9" t="n">
-        <v>10.33333333333333</v>
+        <v>8.583333333333329</v>
       </c>
       <c r="AJ9" t="n">
-        <v>10.24675324675324</v>
+        <v>7.746212121212121</v>
       </c>
       <c r="AK9" t="n">
-        <v>14.33333333333333</v>
+        <v>10</v>
       </c>
       <c r="AL9" t="n">
-        <v>16.84761904761905</v>
+        <v>7.613043478260877</v>
       </c>
       <c r="AM9" t="inlineStr"/>
       <c r="AN9" t="n">
-        <v>162.030959752322</v>
+        <v>66.68888888888893</v>
       </c>
       <c r="AO9" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="AP9" t="n">
-        <v>-1.128947368421053</v>
+        <v>0.2826086956521738</v>
       </c>
       <c r="AQ9" t="inlineStr"/>
       <c r="AR9" t="n">
-        <v>2</v>
+        <v>-0.2666666666666667</v>
       </c>
       <c r="AS9" t="n">
-        <v>-10</v>
+        <v>-11</v>
       </c>
       <c r="AT9" t="n">
-        <v>-7.878787878787879</v>
+        <v>-3.242424242424242</v>
       </c>
       <c r="AU9" t="inlineStr"/>
       <c r="AV9" t="n">
-        <v>-1.497586666422736</v>
+        <v>-0.9438844726253528</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.08476864107553615</v>
+        <v>0.04561031130798572</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.005907889198362756</v>
+        <v>0.003771053847910898</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.8333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.7056277056277056</v>
+        <v>0.4469696969696969</v>
       </c>
       <c r="BA9" t="inlineStr"/>
       <c r="BB9" t="inlineStr"/>
       <c r="BC9" t="inlineStr"/>
-      <c r="BD9" t="n">
-        <v>9000</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>5500000</v>
-      </c>
+      <c r="BD9" t="inlineStr"/>
+      <c r="BE9" t="inlineStr"/>
       <c r="BF9" t="inlineStr"/>
       <c r="BG9" t="inlineStr"/>
       <c r="BH9" t="inlineStr"/>
       <c r="BI9" t="inlineStr"/>
       <c r="BJ9" t="inlineStr"/>
-      <c r="BK9" t="n">
-        <v>75</v>
-      </c>
+      <c r="BK9" t="inlineStr"/>
       <c r="BL9" t="inlineStr"/>
-      <c r="BM9" t="n">
-        <v>1</v>
-      </c>
+      <c r="BM9" t="inlineStr"/>
       <c r="BN9" t="inlineStr"/>
       <c r="BO9" t="inlineStr"/>
       <c r="BP9" t="inlineStr"/>
       <c r="BQ9" t="inlineStr"/>
-      <c r="BR9" t="n">
-        <v>76</v>
-      </c>
-      <c r="BS9" t="n">
-        <v>2</v>
-      </c>
+      <c r="BR9" t="inlineStr"/>
+      <c r="BS9" t="inlineStr"/>
       <c r="BT9" t="inlineStr"/>
       <c r="BU9" t="inlineStr"/>
       <c r="BV9" t="inlineStr"/>
@@ -2284,23 +2282,23 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>z9REJaun</t>
+          <t>vwbmU7aL</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45570.5</v>
+        <v>45583.65625</v>
       </c>
       <c r="C10" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D10" t="n">
         <v>133</v>
       </c>
       <c r="E10" t="n">
-        <v>528</v>
+        <v>47</v>
       </c>
       <c r="F10" t="n">
-        <v>228</v>
+        <v>545</v>
       </c>
       <c r="G10" t="n">
         <v>55</v>
@@ -2322,205 +2320,171 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>168</v>
+        <v>67</v>
       </c>
       <c r="M10" t="n">
-        <v>7</v>
+        <v>127</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>0.6766666666666663</v>
+        <v>-0.8216666666666665</v>
       </c>
       <c r="P10" t="n">
-        <v>0.6171895424836602</v>
+        <v>0.6910000000000001</v>
       </c>
       <c r="Q10" t="n">
-        <v>1</v>
+        <v>-1.25</v>
       </c>
       <c r="R10" t="n">
-        <v>0.8649999999999999</v>
+        <v>0.7142857142857142</v>
       </c>
       <c r="S10" t="n">
-        <v>2.833333333333333</v>
+        <v>-2.166666666666667</v>
       </c>
       <c r="T10" t="n">
-        <v>1.173913043478261</v>
+        <v>1.924242424242424</v>
       </c>
       <c r="U10" t="n">
-        <v>3.5</v>
+        <v>-6.333333333333336</v>
       </c>
       <c r="V10" t="n">
-        <v>1.913043478260871</v>
+        <v>3.926406926406926</v>
       </c>
       <c r="W10" t="n">
-        <v>1.166666666666667</v>
+        <v>-0.3333333333333335</v>
       </c>
       <c r="X10" t="n">
-        <v>0.09833333333333338</v>
+        <v>0.8614718614718613</v>
       </c>
       <c r="Y10" t="n">
-        <v>3</v>
+        <v>1.25</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.3899999999999999</v>
+        <v>1.149350649350649</v>
       </c>
       <c r="AA10" t="n">
-        <v>21.5752886002886</v>
+        <v>23.72417582417582</v>
       </c>
       <c r="AB10" t="n">
-        <v>20.99905549125498</v>
-      </c>
-      <c r="AC10" t="inlineStr"/>
+        <v>18.96545986160999</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>960.051069202665</v>
+      </c>
       <c r="AD10" t="n">
-        <v>898.6705264082855</v>
+        <v>950.6766004231388</v>
       </c>
       <c r="AE10" t="n">
-        <v>-74</v>
+        <v>-21</v>
       </c>
       <c r="AF10" t="n">
-        <v>-13.47826086956522</v>
+        <v>9.476190476190482</v>
       </c>
       <c r="AG10" t="n">
-        <v>-22</v>
+        <v>-39</v>
       </c>
       <c r="AH10" t="n">
-        <v>0.9604743083003981</v>
+        <v>4.794486215538839</v>
       </c>
       <c r="AI10" t="n">
-        <v>6.666666666666671</v>
+        <v>11.58333333333334</v>
       </c>
       <c r="AJ10" t="n">
-        <v>-0.4416666666666664</v>
+        <v>-2.168831168831169</v>
       </c>
       <c r="AK10" t="n">
-        <v>-19</v>
+        <v>-11.5</v>
       </c>
       <c r="AL10" t="n">
-        <v>-4.260869565217391</v>
-      </c>
-      <c r="AM10" t="inlineStr"/>
+        <v>-6.852813852813853</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>-170.5</v>
+      </c>
       <c r="AN10" t="n">
-        <v>-44.12727272727278</v>
+        <v>-82.54761904761904</v>
       </c>
       <c r="AO10" t="n">
-        <v>-1.333333333333333</v>
+        <v>-0.6666666666666665</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.2272727272727271</v>
-      </c>
-      <c r="AQ10" t="inlineStr"/>
+        <v>-0.05476190476190479</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>0</v>
+      </c>
       <c r="AR10" t="n">
-        <v>-0.8333333333333334</v>
+        <v>-0.6</v>
       </c>
       <c r="AS10" t="n">
-        <v>-1.166666666666666</v>
+        <v>-9.833333333333332</v>
       </c>
       <c r="AT10" t="n">
-        <v>5.138333333333328</v>
-      </c>
-      <c r="AU10" t="inlineStr"/>
+        <v>10.72077922077923</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>24.70105664488017</v>
+      </c>
       <c r="AV10" t="n">
-        <v>1.100414175159726</v>
+        <v>0.7955410317106217</v>
       </c>
       <c r="AW10" t="n">
-        <v>-0.04204754199286732</v>
+        <v>-0.01604152717055943</v>
       </c>
       <c r="AX10" t="n">
-        <v>-0.01046394944056821</v>
+        <v>-0.02103249985862573</v>
       </c>
       <c r="AY10" t="n">
-        <v>0.3333333333333333</v>
+        <v>-0.08333333333333331</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>0.534722222222257</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>1337.962962962963</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>21000</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>4325000</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>6</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>0.6433612440191396</v>
-      </c>
-      <c r="BH10" t="n">
-        <v>2.523148148148152</v>
-      </c>
-      <c r="BI10" t="n">
-        <v>1.018054447988675</v>
-      </c>
-      <c r="BJ10" t="n">
-        <v>2.217533891547049</v>
-      </c>
-      <c r="BK10" t="n">
-        <v>151</v>
-      </c>
-      <c r="BL10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM10" t="n">
-        <v>2</v>
-      </c>
-      <c r="BN10" t="n">
-        <v>1.488425925925924</v>
-      </c>
+        <v>0.1038961038961038</v>
+      </c>
+      <c r="BA10" t="inlineStr"/>
+      <c r="BB10" t="inlineStr"/>
+      <c r="BC10" t="inlineStr"/>
+      <c r="BD10" t="inlineStr"/>
+      <c r="BE10" t="inlineStr"/>
+      <c r="BF10" t="inlineStr"/>
+      <c r="BG10" t="inlineStr"/>
+      <c r="BH10" t="inlineStr"/>
+      <c r="BI10" t="inlineStr"/>
+      <c r="BJ10" t="inlineStr"/>
+      <c r="BK10" t="inlineStr"/>
+      <c r="BL10" t="inlineStr"/>
+      <c r="BM10" t="inlineStr"/>
+      <c r="BN10" t="inlineStr"/>
       <c r="BO10" t="inlineStr"/>
-      <c r="BP10" t="n">
-        <v>343227.9206539073</v>
-      </c>
-      <c r="BQ10" t="n">
-        <v>549942.1296296297</v>
-      </c>
-      <c r="BR10" t="n">
-        <v>135</v>
-      </c>
-      <c r="BS10" t="n">
-        <v>2</v>
-      </c>
-      <c r="BT10" t="n">
-        <v>-0.8055555555555571</v>
-      </c>
-      <c r="BU10" t="n">
-        <v>-6.25</v>
-      </c>
-      <c r="BV10" t="n">
-        <v>1.955979753677127</v>
-      </c>
+      <c r="BP10" t="inlineStr"/>
+      <c r="BQ10" t="inlineStr"/>
+      <c r="BR10" t="inlineStr"/>
+      <c r="BS10" t="inlineStr"/>
+      <c r="BT10" t="inlineStr"/>
+      <c r="BU10" t="inlineStr"/>
+      <c r="BV10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>xYNVFHvB</t>
+          <t>OUcd1IPH</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45569.65625</v>
+        <v>45571.65625</v>
       </c>
       <c r="C11" t="n">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D11" t="n">
         <v>133</v>
       </c>
       <c r="E11" t="n">
-        <v>448</v>
+        <v>535</v>
       </c>
       <c r="F11" t="n">
-        <v>292</v>
+        <v>129</v>
       </c>
       <c r="G11" t="n">
         <v>55</v>
@@ -2542,158 +2506,886 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>312</v>
+        <v>97</v>
       </c>
       <c r="M11" t="n">
-        <v>10</v>
+        <v>211</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>1.32</v>
+        <v>1.175</v>
       </c>
       <c r="P11" t="n">
-        <v>1.017730263157894</v>
+        <v>0.1932380952380953</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.5</v>
+        <v>-0.5</v>
       </c>
       <c r="R11" t="n">
-        <v>1.263157894736842</v>
+        <v>0.2673913043478259</v>
       </c>
       <c r="S11" t="n">
-        <v>7.5</v>
+        <v>1.166666666666666</v>
       </c>
       <c r="T11" t="n">
-        <v>3.411027568922306</v>
+        <v>-0.0239130434782604</v>
       </c>
       <c r="U11" t="n">
-        <v>3</v>
+        <v>-2.5</v>
       </c>
       <c r="V11" t="n">
-        <v>5.478696741854636</v>
+        <v>2.886956521739128</v>
       </c>
       <c r="W11" t="n">
-        <v>2</v>
+        <v>2.333333333333333</v>
       </c>
       <c r="X11" t="n">
-        <v>1.135964912280702</v>
+        <v>-1.05</v>
       </c>
       <c r="Y11" t="n">
-        <v>3</v>
+        <v>-0.5</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.703947368421053</v>
+        <v>-1.297826086956522</v>
       </c>
       <c r="AA11" t="n">
-        <v>17.48011363636364</v>
+        <v>18.98333333333333</v>
       </c>
       <c r="AB11" t="n">
-        <v>17.08503329438756</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>791.0454982459589</v>
-      </c>
+        <v>20.07730644939295</v>
+      </c>
+      <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="n">
-        <v>877.5748420809521</v>
+        <v>1106.84557920803</v>
       </c>
       <c r="AE11" t="n">
-        <v>66</v>
+        <v>-46.5</v>
       </c>
       <c r="AF11" t="n">
-        <v>10.01503759398497</v>
+        <v>-25.15789473684211</v>
       </c>
       <c r="AG11" t="n">
-        <v>8.5</v>
+        <v>17.5</v>
       </c>
       <c r="AH11" t="n">
-        <v>7.468671679197996</v>
+        <v>1.739234449760765</v>
       </c>
       <c r="AI11" t="n">
-        <v>10.5</v>
+        <v>0.1666666666666679</v>
       </c>
       <c r="AJ11" t="n">
-        <v>5.679824561403512</v>
+        <v>2.939130434782601</v>
       </c>
       <c r="AK11" t="n">
-        <v>40</v>
+        <v>-25</v>
       </c>
       <c r="AL11" t="n">
-        <v>2.461152882205511</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>151</v>
-      </c>
+        <v>-25.05217391304348</v>
+      </c>
+      <c r="AM11" t="inlineStr"/>
       <c r="AN11" t="n">
-        <v>-4.394444444444389</v>
+        <v>-296.6825396825398</v>
       </c>
       <c r="AO11" t="n">
-        <v>2.5</v>
+        <v>2.166666666666667</v>
       </c>
       <c r="AP11" t="n">
-        <v>-0.5764411027568923</v>
+        <v>-0.7428571428571427</v>
       </c>
       <c r="AQ11" t="inlineStr"/>
       <c r="AR11" t="n">
-        <v>0.6071428571428571</v>
+        <v>0.25</v>
       </c>
       <c r="AS11" t="n">
-        <v>-1.5</v>
+        <v>-5.333333333333334</v>
       </c>
       <c r="AT11" t="n">
-        <v>2.640350877192983</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>-40.71992481203009</v>
-      </c>
+        <v>0.3304347826086982</v>
+      </c>
+      <c r="AU11" t="inlineStr"/>
       <c r="AV11" t="n">
-        <v>-2.483924943959689</v>
+        <v>8.346570588191877</v>
       </c>
       <c r="AW11" t="n">
-        <v>-0.06216402815932984</v>
+        <v>0.06493494966151531</v>
       </c>
       <c r="AX11" t="n">
-        <v>-0.01762318718887493</v>
+        <v>0.0441937315738896</v>
       </c>
       <c r="AY11" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.4714912280701754</v>
+        <v>0.1956521739130435</v>
       </c>
       <c r="BA11" t="inlineStr"/>
       <c r="BB11" t="inlineStr"/>
       <c r="BC11" t="inlineStr"/>
       <c r="BD11" t="inlineStr"/>
-      <c r="BE11" t="n">
-        <v>-2200000</v>
-      </c>
+      <c r="BE11" t="inlineStr"/>
       <c r="BF11" t="inlineStr"/>
       <c r="BG11" t="inlineStr"/>
       <c r="BH11" t="inlineStr"/>
       <c r="BI11" t="inlineStr"/>
       <c r="BJ11" t="inlineStr"/>
-      <c r="BK11" t="n">
-        <v>-188</v>
-      </c>
+      <c r="BK11" t="inlineStr"/>
       <c r="BL11" t="inlineStr"/>
-      <c r="BM11" t="n">
-        <v>-3</v>
-      </c>
+      <c r="BM11" t="inlineStr"/>
       <c r="BN11" t="inlineStr"/>
       <c r="BO11" t="inlineStr"/>
       <c r="BP11" t="inlineStr"/>
       <c r="BQ11" t="inlineStr"/>
-      <c r="BR11" t="n">
-        <v>-217</v>
-      </c>
-      <c r="BS11" t="n">
-        <v>-3</v>
-      </c>
+      <c r="BR11" t="inlineStr"/>
+      <c r="BS11" t="inlineStr"/>
       <c r="BT11" t="inlineStr"/>
       <c r="BU11" t="inlineStr"/>
       <c r="BV11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>rZUMHwAb</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45571.5</v>
+      </c>
+      <c r="C12" t="n">
+        <v>104</v>
+      </c>
+      <c r="D12" t="n">
+        <v>133</v>
+      </c>
+      <c r="E12" t="n">
+        <v>211</v>
+      </c>
+      <c r="F12" t="n">
+        <v>122</v>
+      </c>
+      <c r="G12" t="n">
+        <v>55</v>
+      </c>
+      <c r="H12" t="n">
+        <v>551</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>128</v>
+      </c>
+      <c r="M12" t="n">
+        <v>204</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.8233333333333328</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1.532606516290727</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1</v>
+      </c>
+      <c r="R12" t="n">
+        <v>2.077922077922078</v>
+      </c>
+      <c r="S12" t="n">
+        <v>6.333333333333332</v>
+      </c>
+      <c r="T12" t="n">
+        <v>4.831818181818182</v>
+      </c>
+      <c r="U12" t="n">
+        <v>10.33333333333333</v>
+      </c>
+      <c r="V12" t="n">
+        <v>12.10909090909091</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.257575757575757</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2.097402597402597</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>12.8256253006253</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>15.15757425466121</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>977.046065597882</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>789.7665696532363</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>84.5</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>46.4360902255639</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>34.63157894736842</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>15</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>9.623376623376622</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>10</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>21.24545454545455</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>52</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>210.6888888888889</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>-1.333333333333333</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>0.2727272727272729</v>
+      </c>
+      <c r="AQ12" t="inlineStr"/>
+      <c r="AR12" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>-5.999999999999998</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>0.298701298701296</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>-13.4021645021645</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>-6.044117766739793</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>0.1489057239057239</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>0.0202282440576764</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>0.5627705627705628</v>
+      </c>
+      <c r="BA12" t="inlineStr"/>
+      <c r="BB12" t="inlineStr"/>
+      <c r="BC12" t="inlineStr"/>
+      <c r="BD12" t="inlineStr"/>
+      <c r="BE12" t="inlineStr"/>
+      <c r="BF12" t="inlineStr"/>
+      <c r="BG12" t="inlineStr"/>
+      <c r="BH12" t="inlineStr"/>
+      <c r="BI12" t="inlineStr"/>
+      <c r="BJ12" t="inlineStr"/>
+      <c r="BK12" t="inlineStr"/>
+      <c r="BL12" t="inlineStr"/>
+      <c r="BM12" t="inlineStr"/>
+      <c r="BN12" t="inlineStr"/>
+      <c r="BO12" t="inlineStr"/>
+      <c r="BP12" t="inlineStr"/>
+      <c r="BQ12" t="inlineStr"/>
+      <c r="BR12" t="inlineStr"/>
+      <c r="BS12" t="inlineStr"/>
+      <c r="BT12" t="inlineStr"/>
+      <c r="BU12" t="inlineStr"/>
+      <c r="BV12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>WhWcJjo3</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45571.5</v>
+      </c>
+      <c r="C13" t="n">
+        <v>101</v>
+      </c>
+      <c r="D13" t="n">
+        <v>133</v>
+      </c>
+      <c r="E13" t="n">
+        <v>826</v>
+      </c>
+      <c r="F13" t="n">
+        <v>157</v>
+      </c>
+      <c r="G13" t="n">
+        <v>55</v>
+      </c>
+      <c r="H13" t="n">
+        <v>551</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>35</v>
+      </c>
+      <c r="M13" t="n">
+        <v>234</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0.9404999999999997</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>2</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.240909090909091</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.140476190476191</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0.6666666666666679</v>
+      </c>
+      <c r="V13" t="n">
+        <v>5.69761904761905</v>
+      </c>
+      <c r="W13" t="n">
+        <v>3</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0.3181818181818183</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0.4363636363636365</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>20.9541847041847</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>18.72831971010709</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1062.036649682667</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>805.5768135399308</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>37.39999999999999</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>-4</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>30.67105263157895</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>9.333333333333329</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1.822727272727263</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>-5.999999999999993</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>12.0952380952381</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>-348</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>107.3040935672514</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>-0.338345864661654</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>-2.000000000000002</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>-1.227272727272727</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>3.172786690433753</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>-3.321614195664901</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>-0.06763903654885545</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>0.02955321374852892</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>0.2363636363636363</v>
+      </c>
+      <c r="BA13" t="inlineStr"/>
+      <c r="BB13" t="inlineStr"/>
+      <c r="BC13" t="inlineStr"/>
+      <c r="BD13" t="inlineStr"/>
+      <c r="BE13" t="inlineStr"/>
+      <c r="BF13" t="inlineStr"/>
+      <c r="BG13" t="inlineStr"/>
+      <c r="BH13" t="inlineStr"/>
+      <c r="BI13" t="inlineStr"/>
+      <c r="BJ13" t="inlineStr"/>
+      <c r="BK13" t="inlineStr"/>
+      <c r="BL13" t="inlineStr"/>
+      <c r="BM13" t="inlineStr"/>
+      <c r="BN13" t="inlineStr"/>
+      <c r="BO13" t="inlineStr"/>
+      <c r="BP13" t="inlineStr"/>
+      <c r="BQ13" t="inlineStr"/>
+      <c r="BR13" t="inlineStr"/>
+      <c r="BS13" t="inlineStr"/>
+      <c r="BT13" t="inlineStr"/>
+      <c r="BU13" t="inlineStr"/>
+      <c r="BV13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>4nvCemgd</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45571.5</v>
+      </c>
+      <c r="C14" t="n">
+        <v>101</v>
+      </c>
+      <c r="D14" t="n">
+        <v>133</v>
+      </c>
+      <c r="E14" t="n">
+        <v>736</v>
+      </c>
+      <c r="F14" t="n">
+        <v>176</v>
+      </c>
+      <c r="G14" t="n">
+        <v>55</v>
+      </c>
+      <c r="H14" t="n">
+        <v>551</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>312</v>
+      </c>
+      <c r="M14" t="n">
+        <v>163</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>-0.1633333333333332</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0.2500238095238099</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>-1</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0.5785714285714285</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.333333333333333</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1.061904761904762</v>
+      </c>
+      <c r="U14" t="n">
+        <v>-1.666666666666666</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0.6261904761904766</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0.5785714285714285</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>19.12065897065897</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>20.24061302687353</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>947.0370781359841</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>962.6491064253298</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>-12.81578947368421</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>-12.5</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>-2.368421052631582</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>13.66666666666666</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>-0.2999999999999972</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>-2.666666666666657</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>-15.33333333333333</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>-135</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>-152.3567251461988</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>-0.6666666666666667</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>-0.8547619047619046</v>
+      </c>
+      <c r="AQ14" t="inlineStr"/>
+      <c r="AR14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>-8.333333333333334</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>-0.4880952380952408</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>17.4546783625731</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>5.217937060246109</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>-0.08528693528693526</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>-0.008239073080847904</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>-6000</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>-76</v>
+      </c>
+      <c r="BC14" t="inlineStr"/>
+      <c r="BD14" t="inlineStr"/>
+      <c r="BE14" t="inlineStr"/>
+      <c r="BF14" t="inlineStr"/>
+      <c r="BG14" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BH14" t="inlineStr"/>
+      <c r="BI14" t="n">
+        <v>-1400000</v>
+      </c>
+      <c r="BJ14" t="inlineStr"/>
+      <c r="BK14" t="inlineStr"/>
+      <c r="BL14" t="n">
+        <v>-64</v>
+      </c>
+      <c r="BM14" t="inlineStr"/>
+      <c r="BN14" t="inlineStr"/>
+      <c r="BO14" t="inlineStr"/>
+      <c r="BP14" t="inlineStr"/>
+      <c r="BQ14" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BR14" t="inlineStr"/>
+      <c r="BS14" t="inlineStr"/>
+      <c r="BT14" t="inlineStr"/>
+      <c r="BU14" t="inlineStr"/>
+      <c r="BV14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>IHSe3ve5</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45571.41666666666</v>
+      </c>
+      <c r="C15" t="n">
+        <v>102</v>
+      </c>
+      <c r="D15" t="n">
+        <v>133</v>
+      </c>
+      <c r="E15" t="n">
+        <v>56</v>
+      </c>
+      <c r="F15" t="n">
+        <v>599</v>
+      </c>
+      <c r="G15" t="n">
+        <v>55</v>
+      </c>
+      <c r="H15" t="n">
+        <v>551</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>152</v>
+      </c>
+      <c r="M15" t="n">
+        <v>226</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>-0.1133333333333331</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0.4725833333333327</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0.5357142857142858</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0.5749999999999997</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0.6666666666666661</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.741666666666665</v>
+      </c>
+      <c r="W15" t="n">
+        <v>-1.333333333333333</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0.2499999999999998</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>-2</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>15.57640692640693</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>19.29995453130965</v>
+      </c>
+      <c r="AC15" t="inlineStr"/>
+      <c r="AD15" t="n">
+        <v>843.9063364604394</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>39.5</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>26.21739130434781</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>22</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>25.39588100686499</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>8.541666666666671</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>10</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>13.78333333333333</v>
+      </c>
+      <c r="AM15" t="inlineStr"/>
+      <c r="AN15" t="n">
+        <v>127.2222222222222</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>-1.333333333333333</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>-0.8581235697940504</v>
+      </c>
+      <c r="AQ15" t="inlineStr"/>
+      <c r="AR15" t="n">
+        <v>0.9166666666666666</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>6.333333333333334</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>-9.624999999999996</v>
+      </c>
+      <c r="AU15" t="inlineStr"/>
+      <c r="AV15" t="n">
+        <v>0.3886073861305288</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>0.07928069062305482</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>0.03009688049080859</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>-0.3333333333333333</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>0.2202380952380953</v>
+      </c>
+      <c r="BA15" t="inlineStr"/>
+      <c r="BB15" t="inlineStr"/>
+      <c r="BC15" t="inlineStr"/>
+      <c r="BD15" t="inlineStr"/>
+      <c r="BE15" t="inlineStr"/>
+      <c r="BF15" t="inlineStr"/>
+      <c r="BG15" t="inlineStr"/>
+      <c r="BH15" t="inlineStr"/>
+      <c r="BI15" t="inlineStr"/>
+      <c r="BJ15" t="inlineStr"/>
+      <c r="BK15" t="inlineStr"/>
+      <c r="BL15" t="inlineStr"/>
+      <c r="BM15" t="inlineStr"/>
+      <c r="BN15" t="inlineStr"/>
+      <c r="BO15" t="inlineStr"/>
+      <c r="BP15" t="inlineStr"/>
+      <c r="BQ15" t="inlineStr"/>
+      <c r="BR15" t="inlineStr"/>
+      <c r="BS15" t="inlineStr"/>
+      <c r="BT15" t="inlineStr"/>
+      <c r="BU15" t="inlineStr"/>
+      <c r="BV15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/france/p6_deployment/data_preparation/df_tagged.xlsx
+++ b/data/france/p6_deployment/data_preparation/df_tagged.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BV15"/>
+  <dimension ref="A1:DI19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,325 +500,520 @@
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_120_matches_expected_goals_(xg)</t>
+          <t>dif_mean_last_60_matches_expected_goals_(xg)</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_480_matches_expected_goals_(xg)</t>
+          <t>dif_mean_last_60_matches_expected_goals_(xg)_against</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_120_matches_expected_points</t>
+          <t>dif_mean_last_360_matches_expected_goals_(xg)</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_480_matches_expected_points</t>
+          <t>dif_mean_last_360_matches_expected_goals_(xg)_against</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_120_matches_shots_on_goal</t>
+          <t>dif_mean_last_60_matches_expected_points</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_480_matches_shots_on_goal</t>
+          <t>dif_mean_last_60_matches_expected_points_against</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_120_matches_goal_attempts</t>
+          <t>dif_mean_last_360_matches_expected_points</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_480_matches_goal_attempts</t>
+          <t>dif_mean_last_360_matches_expected_points_against</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_120_matches_goals</t>
+          <t>dif_mean_last_60_matches_shots_on_goal</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_480_matches_goals</t>
+          <t>dif_mean_last_60_matches_shots_on_goal_against</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_120_matches_points</t>
+          <t>dif_mean_last_360_matches_shots_on_goal</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_480_matches_points</t>
+          <t>dif_mean_last_360_matches_shots_on_goal_against</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_120_matches_goal_ratio</t>
+          <t>dif_mean_last_60_matches_goal_attempts</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_480_matches_goal_ratio</t>
+          <t>dif_mean_last_60_matches_goal_attempts_against</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_120_matches_PPS</t>
+          <t>dif_mean_last_360_matches_goal_attempts</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_480_matches_PPS</t>
+          <t>dif_mean_last_360_matches_goal_attempts_against</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_120_matches_attacks</t>
+          <t>dif_mean_last_60_matches_goals</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_480_matches_attacks</t>
+          <t>dif_mean_last_60_matches_goals_against</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_120_matches_dangerous_attacks</t>
+          <t>dif_mean_last_360_matches_goals</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_480_matches_dangerous_attacks</t>
+          <t>dif_mean_last_360_matches_goals_against</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_120_matches_dead_balls</t>
+          <t>dif_mean_last_60_matches_points</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_480_matches_dead_balls</t>
+          <t>dif_mean_last_60_matches_points_against</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_120_matches_ball_possession</t>
+          <t>dif_mean_last_360_matches_points</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_480_matches_ball_possession</t>
+          <t>dif_mean_last_360_matches_points_against</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_120_matches_total_passes</t>
+          <t>dif_mean_last_60_matches_goal_ratio</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_480_matches_total_passes</t>
+          <t>dif_mean_last_60_matches_goal_ratio_against</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_120_matches_yellow_cards</t>
+          <t>dif_mean_last_360_matches_goal_ratio</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_480_matches_yellow_cards</t>
+          <t>dif_mean_last_360_matches_goal_ratio_against</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_120_matches_red_cards</t>
+          <t>dif_mean_last_60_matches_PPS</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_480_matches_red_cards</t>
+          <t>dif_mean_last_60_matches_PPS_against</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_120_matches_defensive_actions</t>
+          <t>dif_mean_last_360_matches_PPS</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_480_matches_defensive_actions</t>
+          <t>dif_mean_last_360_matches_PPS_against</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_120_matches_PPDA</t>
+          <t>dif_mean_last_60_matches_attacks</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_480_matches_PPDA</t>
+          <t>dif_mean_last_60_matches_attacks_against</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_120_matches_KGP</t>
+          <t>dif_mean_last_360_matches_attacks</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_480_matches_KGP</t>
+          <t>dif_mean_last_360_matches_attacks_against</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_120_matches_clean_sheet</t>
+          <t>dif_mean_last_60_matches_dangerous_attacks</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_480_matches_clean_sheet</t>
+          <t>dif_mean_last_60_matches_dangerous_attacks_against</t>
         </is>
       </c>
       <c r="BA1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_last_360_matches_dangerous_attacks</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_360_matches_dangerous_attacks_against</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_dead_balls</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_dead_balls_against</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_360_matches_dead_balls</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_360_matches_dead_balls_against</t>
+        </is>
+      </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_ball_possession</t>
+        </is>
+      </c>
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_ball_possession_against</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_360_matches_ball_possession</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_360_matches_ball_possession_against</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_total_passes</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_total_passes_against</t>
+        </is>
+      </c>
+      <c r="BM1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_360_matches_total_passes</t>
+        </is>
+      </c>
+      <c r="BN1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_360_matches_total_passes_against</t>
+        </is>
+      </c>
+      <c r="BO1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_yellow_cards</t>
+        </is>
+      </c>
+      <c r="BP1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_yellow_cards_against</t>
+        </is>
+      </c>
+      <c r="BQ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_360_matches_yellow_cards</t>
+        </is>
+      </c>
+      <c r="BR1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_360_matches_yellow_cards_against</t>
+        </is>
+      </c>
+      <c r="BS1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_red_cards</t>
+        </is>
+      </c>
+      <c r="BT1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_red_cards_against</t>
+        </is>
+      </c>
+      <c r="BU1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_360_matches_red_cards</t>
+        </is>
+      </c>
+      <c r="BV1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_360_matches_red_cards_against</t>
+        </is>
+      </c>
+      <c r="BW1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_defensive_actions</t>
+        </is>
+      </c>
+      <c r="BX1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_defensive_actions_against</t>
+        </is>
+      </c>
+      <c r="BY1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_360_matches_defensive_actions</t>
+        </is>
+      </c>
+      <c r="BZ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_360_matches_defensive_actions_against</t>
+        </is>
+      </c>
+      <c r="CA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_PPDA</t>
+        </is>
+      </c>
+      <c r="CB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_PPDA_against</t>
+        </is>
+      </c>
+      <c r="CC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_360_matches_PPDA</t>
+        </is>
+      </c>
+      <c r="CD1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_360_matches_PPDA_against</t>
+        </is>
+      </c>
+      <c r="CE1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_KGP</t>
+        </is>
+      </c>
+      <c r="CF1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_KGP_against</t>
+        </is>
+      </c>
+      <c r="CG1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_360_matches_KGP</t>
+        </is>
+      </c>
+      <c r="CH1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_360_matches_KGP_against</t>
+        </is>
+      </c>
+      <c r="CI1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_clean_sheet</t>
+        </is>
+      </c>
+      <c r="CJ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_clean_sheet_against</t>
+        </is>
+      </c>
+      <c r="CK1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_360_matches_clean_sheet</t>
+        </is>
+      </c>
+      <c r="CL1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_360_matches_clean_sheet_against</t>
+        </is>
+      </c>
+      <c r="CM1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_360_matches_mean_rat_player_start_against</t>
+        </is>
+      </c>
+      <c r="CN1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_start</t>
+        </is>
+      </c>
+      <c r="CO1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_sub</t>
+        </is>
+      </c>
+      <c r="CP1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_sub</t>
+        </is>
+      </c>
+      <c r="CQ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_value_player_miss</t>
+        </is>
+      </c>
+      <c r="CR1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rep_player_start</t>
+        </is>
+      </c>
+      <c r="CS1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_miss</t>
+        </is>
+      </c>
+      <c r="CT1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_rat_player_miss</t>
+        </is>
+      </c>
+      <c r="CU1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_start</t>
+        </is>
+      </c>
+      <c r="CV1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_value_player_sub</t>
+        </is>
+      </c>
+      <c r="CW1" s="1" t="inlineStr">
+        <is>
           <t>dif_sum_wage_player_miss</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="CX1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_sub</t>
+        </is>
+      </c>
+      <c r="CY1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_miss</t>
+        </is>
+      </c>
+      <c r="CZ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_sub</t>
+        </is>
+      </c>
+      <c r="DA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_n_player_miss</t>
+        </is>
+      </c>
+      <c r="DB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_rep_player_miss</t>
+        </is>
+      </c>
+      <c r="DC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_start</t>
+        </is>
+      </c>
+      <c r="DD1" s="1" t="inlineStr">
         <is>
           <t>dif_sum_pot_player_miss</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_sub</t>
-        </is>
-      </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_sub</t>
-        </is>
-      </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="DE1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_wage_player_start</t>
+        </is>
+      </c>
+      <c r="DF1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_start</t>
+        </is>
+      </c>
+      <c r="DG1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rep_player_sub</t>
+        </is>
+      </c>
+      <c r="DH1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_wage_player_sub</t>
+        </is>
+      </c>
+      <c r="DI1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_value_player_start</t>
-        </is>
-      </c>
-      <c r="BF1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_wage_player_start</t>
-        </is>
-      </c>
-      <c r="BG1" s="1" t="inlineStr">
-        <is>
-          <t>dif_n_player_miss</t>
-        </is>
-      </c>
-      <c r="BH1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_start</t>
-        </is>
-      </c>
-      <c r="BI1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_value_player_miss</t>
-        </is>
-      </c>
-      <c r="BJ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_start</t>
-        </is>
-      </c>
-      <c r="BK1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_start</t>
-        </is>
-      </c>
-      <c r="BL1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_rat_player_miss</t>
-        </is>
-      </c>
-      <c r="BM1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_start</t>
-        </is>
-      </c>
-      <c r="BN1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_wage_player_sub</t>
-        </is>
-      </c>
-      <c r="BO1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_miss</t>
-        </is>
-      </c>
-      <c r="BP1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rep_player_sub</t>
-        </is>
-      </c>
-      <c r="BQ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_rep_player_miss</t>
-        </is>
-      </c>
-      <c r="BR1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_miss</t>
-        </is>
-      </c>
-      <c r="BS1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_sub</t>
-        </is>
-      </c>
-      <c r="BT1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_sub</t>
-        </is>
-      </c>
-      <c r="BU1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_value_player_sub</t>
-        </is>
-      </c>
-      <c r="BV1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rep_player_start</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>nVutWTU8</t>
+          <t>AsQgyP6l</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45585.65625</v>
+        <v>45592.69791666666</v>
       </c>
       <c r="C2" t="n">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D2" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E2" t="n">
-        <v>242</v>
+        <v>448</v>
       </c>
       <c r="F2" t="n">
-        <v>303</v>
+        <v>129</v>
       </c>
       <c r="G2" t="n">
         <v>55</v>
@@ -840,169 +1035,272 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>67</v>
+        <v>313</v>
       </c>
       <c r="M2" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>0.2675000000000003</v>
+        <v>-0.02000000000000024</v>
       </c>
       <c r="P2" t="n">
-        <v>0.3312337662337661</v>
+        <v>0.5033333333333332</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>0.08139705882352932</v>
       </c>
       <c r="R2" t="n">
-        <v>0.1677018633540371</v>
+        <v>-0.4243014705882351</v>
       </c>
       <c r="S2" t="n">
+        <v>-0.6666666666666667</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0.3333333333333334</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0.506578947368421</v>
+      </c>
+      <c r="V2" t="n">
+        <v>-0.3322368421052632</v>
+      </c>
+      <c r="W2" t="n">
+        <v>-2.166666666666667</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0.8333333333333335</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>-1.519736842105263</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>-1.789473684210527</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>-0.6666666666666661</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>-1.174342105263158</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>-2.529605263157896</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>-0.1666666666666667</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>-0.924342105263158</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0.305921052631579</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>-0.1666666666666666</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>-0.6414473684210527</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0.4144736842105263</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>11.2125</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>-9.75</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>11.23671571484071</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>-8.53026607352418</v>
+      </c>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="n">
+        <v>673.7801040097427</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>-413.4716574192664</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>-8</v>
+      </c>
+      <c r="AV2" t="n">
         <v>1</v>
       </c>
-      <c r="T2" t="n">
-        <v>1.333333333333333</v>
-      </c>
-      <c r="U2" t="n">
-        <v>2</v>
-      </c>
-      <c r="V2" t="n">
-        <v>-0.07575757575757436</v>
-      </c>
-      <c r="W2" t="n">
-        <v>-1.833333333333333</v>
-      </c>
-      <c r="X2" t="n">
-        <v>-0.2898550724637678</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>0.0931677018633541</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>13.64837662337662</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>22.51874260109906</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>1013.039105890922</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>949.6529071761213</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>60</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>-18.5</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>36</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>-2.600000000000009</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>6.416666666666664</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>1.77432712215321</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>0.1666666666666714</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>-14.95670995670996</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>-174</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>-162.1578947368421</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>-0.4285714285714284</v>
-      </c>
-      <c r="AQ2" t="inlineStr"/>
-      <c r="AR2" t="n">
-        <v>0.1428571428571428</v>
-      </c>
-      <c r="AS2" t="n">
+      <c r="AW2" t="n">
+        <v>-18.69411764705883</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>9.129411764705878</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>-15</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>-26</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>-4.450980392156865</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>-7.580392156862743</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>-5.666666666666664</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>4.243421052631579</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>3.779605263157894</v>
+      </c>
+      <c r="BG2" t="n">
         <v>-3</v>
       </c>
-      <c r="AT2" t="n">
-        <v>-0.9006211180124311</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>11.02929292929293</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>4.933930510137722</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>0.2498401260104655</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>0.0177163195716263</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>0.3995859213250518</v>
-      </c>
-      <c r="BA2" t="inlineStr"/>
-      <c r="BB2" t="inlineStr"/>
-      <c r="BC2" t="inlineStr"/>
-      <c r="BD2" t="inlineStr"/>
-      <c r="BE2" t="inlineStr"/>
-      <c r="BF2" t="inlineStr"/>
-      <c r="BG2" t="inlineStr"/>
-      <c r="BH2" t="inlineStr"/>
-      <c r="BI2" t="inlineStr"/>
-      <c r="BJ2" t="inlineStr"/>
+      <c r="BH2" t="n">
+        <v>3</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>-11.20065789473684</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>11.20065789473684</v>
+      </c>
       <c r="BK2" t="inlineStr"/>
       <c r="BL2" t="inlineStr"/>
-      <c r="BM2" t="inlineStr"/>
-      <c r="BN2" t="inlineStr"/>
-      <c r="BO2" t="inlineStr"/>
-      <c r="BP2" t="inlineStr"/>
-      <c r="BQ2" t="inlineStr"/>
-      <c r="BR2" t="inlineStr"/>
+      <c r="BM2" t="n">
+        <v>-220.2589285714286</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>75.20535714285717</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>2.833333333333333</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>0.5845588235294117</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>1.022058823529412</v>
+      </c>
       <c r="BS2" t="inlineStr"/>
       <c r="BT2" t="inlineStr"/>
-      <c r="BU2" t="inlineStr"/>
-      <c r="BV2" t="inlineStr"/>
+      <c r="BU2" t="n">
+        <v>0.2142857142857143</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>0.2142857142857143</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>7.833333333333334</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>-2.666666666666666</v>
+      </c>
+      <c r="BY2" t="n">
+        <v>4.779605263157897</v>
+      </c>
+      <c r="BZ2" t="n">
+        <v>-1.694078947368418</v>
+      </c>
+      <c r="CA2" t="inlineStr"/>
+      <c r="CB2" t="inlineStr"/>
+      <c r="CC2" t="n">
+        <v>1.677124895559439</v>
+      </c>
+      <c r="CD2" t="n">
+        <v>-1.855937955180851</v>
+      </c>
+      <c r="CE2" t="n">
+        <v>-0.00572969329288844</v>
+      </c>
+      <c r="CF2" t="n">
+        <v>0.04024767801857584</v>
+      </c>
+      <c r="CG2" t="n">
+        <v>0.01128032512844909</v>
+      </c>
+      <c r="CH2" t="n">
+        <v>-0.02561094532549806</v>
+      </c>
+      <c r="CI2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="CJ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK2" t="n">
+        <v>-0.1085526315789473</v>
+      </c>
+      <c r="CL2" t="n">
+        <v>0.07236842105263158</v>
+      </c>
+      <c r="CM2" t="n">
+        <v>0.4413580246913682</v>
+      </c>
+      <c r="CN2" t="inlineStr"/>
+      <c r="CO2" t="inlineStr"/>
+      <c r="CP2" t="inlineStr"/>
+      <c r="CQ2" t="inlineStr"/>
+      <c r="CR2" t="inlineStr"/>
+      <c r="CS2" t="inlineStr"/>
+      <c r="CT2" t="inlineStr"/>
+      <c r="CU2" t="inlineStr"/>
+      <c r="CV2" t="inlineStr"/>
+      <c r="CW2" t="inlineStr"/>
+      <c r="CX2" t="inlineStr"/>
+      <c r="CY2" t="inlineStr"/>
+      <c r="CZ2" t="inlineStr"/>
+      <c r="DA2" t="inlineStr"/>
+      <c r="DB2" t="inlineStr"/>
+      <c r="DC2" t="inlineStr"/>
+      <c r="DD2" t="inlineStr"/>
+      <c r="DE2" t="inlineStr"/>
+      <c r="DF2" t="inlineStr"/>
+      <c r="DG2" t="inlineStr"/>
+      <c r="DH2" t="inlineStr"/>
+      <c r="DI2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>vPIEF8pS</t>
+          <t>KdJMr7EE</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45585.5</v>
+        <v>45592.54166666666</v>
       </c>
       <c r="C3" t="n">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D3" t="n">
         <v>133</v>
       </c>
       <c r="E3" t="n">
-        <v>341</v>
+        <v>535</v>
       </c>
       <c r="F3" t="n">
-        <v>292</v>
+        <v>33</v>
       </c>
       <c r="G3" t="n">
         <v>55</v>
@@ -1024,171 +1322,260 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>243</v>
+        <v>193</v>
       </c>
       <c r="M3" t="n">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>1.204166666666667</v>
+        <v>0.6700000000000002</v>
       </c>
       <c r="P3" t="n">
-        <v>0.4747941176470589</v>
+        <v>-0.04500000000000015</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.75</v>
+        <v>0.09183823529411783</v>
       </c>
       <c r="R3" t="n">
-        <v>0.5714285714285714</v>
+        <v>-0.6772426470588235</v>
       </c>
       <c r="S3" t="n">
-        <v>3.916666666666667</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>1.852813852813854</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>5.333333333333334</v>
+        <v>0.5833333333333333</v>
       </c>
       <c r="V3" t="n">
-        <v>3.803030303030303</v>
+        <v>-0.5416666666666667</v>
       </c>
       <c r="W3" t="n">
-        <v>0.4166666666666666</v>
+        <v>2</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.1580952380952381</v>
+        <v>2.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.25</v>
+        <v>0.03472222222222232</v>
       </c>
       <c r="Z3" t="n">
-        <v>-0.5942857142857145</v>
+        <v>-1.729166666666667</v>
       </c>
       <c r="AA3" t="n">
-        <v>12.33495670995671</v>
+        <v>1</v>
       </c>
       <c r="AB3" t="n">
-        <v>16.45948040267177</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>857.0465757170743</v>
+        <v>1.930555555555555</v>
       </c>
       <c r="AD3" t="n">
-        <v>918.225894011082</v>
+        <v>-3.569444444444445</v>
       </c>
       <c r="AE3" t="n">
-        <v>45.83333333333334</v>
+        <v>2</v>
       </c>
       <c r="AF3" t="n">
-        <v>-1.992857142857133</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>7.833333333333336</v>
+        <v>-0.4722222222222223</v>
       </c>
       <c r="AH3" t="n">
-        <v>5.997619047619047</v>
+        <v>-0.5833333333333333</v>
       </c>
       <c r="AI3" t="n">
-        <v>16.75</v>
+        <v>-1</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.647619047619044</v>
+        <v>0.5</v>
       </c>
       <c r="AK3" t="n">
-        <v>17.33333333333334</v>
+        <v>-0.4027777777777777</v>
       </c>
       <c r="AL3" t="n">
-        <v>-4.389610389610382</v>
+        <v>0.3263888888888888</v>
       </c>
       <c r="AM3" t="n">
-        <v>111</v>
+        <v>8.875</v>
       </c>
       <c r="AN3" t="n">
-        <v>-56.47631578947363</v>
+        <v>-12.10989010989011</v>
       </c>
       <c r="AO3" t="n">
-        <v>2</v>
+        <v>9.418279935485312</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.6839826839826839</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>0.6</v>
-      </c>
+        <v>-9.305024064533869</v>
+      </c>
+      <c r="AQ3" t="inlineStr"/>
+      <c r="AR3" t="inlineStr"/>
       <c r="AS3" t="n">
-        <v>-1.416666666666666</v>
+        <v>485.6576335498609</v>
       </c>
       <c r="AT3" t="n">
-        <v>4.590476190476199</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>-3.813967019822289</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>-1.130663267998857</v>
-      </c>
+        <v>-446.1917969351238</v>
+      </c>
+      <c r="AU3" t="inlineStr"/>
+      <c r="AV3" t="inlineStr"/>
       <c r="AW3" t="n">
-        <v>-0.01884092027781634</v>
+        <v>-7.180672268907571</v>
       </c>
       <c r="AX3" t="n">
-        <v>0.01341845613566123</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>0.5833333333333333</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="BA3" t="inlineStr"/>
-      <c r="BB3" t="inlineStr"/>
-      <c r="BC3" t="inlineStr"/>
-      <c r="BD3" t="inlineStr"/>
-      <c r="BE3" t="inlineStr"/>
-      <c r="BF3" t="inlineStr"/>
-      <c r="BG3" t="inlineStr"/>
-      <c r="BH3" t="inlineStr"/>
-      <c r="BI3" t="inlineStr"/>
-      <c r="BJ3" t="inlineStr"/>
+        <v>-9.941176470588232</v>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr"/>
+      <c r="BA3" t="n">
+        <v>3.676470588235297</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>-14.77731092436974</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>-8.5</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>-14.5</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>0.5763888888888857</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>-7.722222222222221</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>-1.513888888888886</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>1.513888888888886</v>
+      </c>
       <c r="BK3" t="inlineStr"/>
       <c r="BL3" t="inlineStr"/>
-      <c r="BM3" t="inlineStr"/>
-      <c r="BN3" t="inlineStr"/>
-      <c r="BO3" t="inlineStr"/>
-      <c r="BP3" t="inlineStr"/>
-      <c r="BQ3" t="inlineStr"/>
-      <c r="BR3" t="inlineStr"/>
+      <c r="BM3" t="n">
+        <v>-5.836538461538453</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>26.12019230769232</v>
+      </c>
+      <c r="BO3" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="BP3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BQ3" t="n">
+        <v>-1.205882352941177</v>
+      </c>
+      <c r="BR3" t="n">
+        <v>0.01102941176470607</v>
+      </c>
       <c r="BS3" t="inlineStr"/>
       <c r="BT3" t="inlineStr"/>
-      <c r="BU3" t="inlineStr"/>
-      <c r="BV3" t="inlineStr"/>
+      <c r="BU3" t="n">
+        <v>-0.1666666666666667</v>
+      </c>
+      <c r="BV3" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="BW3" t="n">
+        <v>-10.5</v>
+      </c>
+      <c r="BX3" t="n">
+        <v>-2</v>
+      </c>
+      <c r="BY3" t="n">
+        <v>-6.993055555555557</v>
+      </c>
+      <c r="BZ3" t="n">
+        <v>-1.020833333333336</v>
+      </c>
+      <c r="CA3" t="inlineStr"/>
+      <c r="CB3" t="inlineStr"/>
+      <c r="CC3" t="n">
+        <v>1.795369455627839</v>
+      </c>
+      <c r="CD3" t="n">
+        <v>-1.448432787193692</v>
+      </c>
+      <c r="CE3" t="inlineStr"/>
+      <c r="CF3" t="inlineStr"/>
+      <c r="CG3" t="n">
+        <v>0.009663247437253178</v>
+      </c>
+      <c r="CH3" t="n">
+        <v>-0.02738583721765527</v>
+      </c>
+      <c r="CI3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK3" t="n">
+        <v>0.2291666666666667</v>
+      </c>
+      <c r="CL3" t="n">
+        <v>0.006944444444444448</v>
+      </c>
+      <c r="CM3" t="n">
+        <v>0.1657994082236485</v>
+      </c>
+      <c r="CN3" t="inlineStr"/>
+      <c r="CO3" t="inlineStr"/>
+      <c r="CP3" t="inlineStr"/>
+      <c r="CQ3" t="inlineStr"/>
+      <c r="CR3" t="inlineStr"/>
+      <c r="CS3" t="inlineStr"/>
+      <c r="CT3" t="inlineStr"/>
+      <c r="CU3" t="inlineStr"/>
+      <c r="CV3" t="inlineStr"/>
+      <c r="CW3" t="inlineStr"/>
+      <c r="CX3" t="inlineStr"/>
+      <c r="CY3" t="inlineStr"/>
+      <c r="CZ3" t="inlineStr"/>
+      <c r="DA3" t="inlineStr"/>
+      <c r="DB3" t="inlineStr"/>
+      <c r="DC3" t="inlineStr"/>
+      <c r="DD3" t="inlineStr"/>
+      <c r="DE3" t="inlineStr"/>
+      <c r="DF3" t="inlineStr"/>
+      <c r="DG3" t="inlineStr"/>
+      <c r="DH3" t="inlineStr"/>
+      <c r="DI3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>h8K6HUFF</t>
+          <t>vNHAXt6D</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45585.5</v>
+        <v>45592.54166666666</v>
       </c>
       <c r="C4" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D4" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E4" t="n">
-        <v>342</v>
+        <v>242</v>
       </c>
       <c r="F4" t="n">
-        <v>579</v>
+        <v>226</v>
       </c>
       <c r="G4" t="n">
         <v>55</v>
@@ -1210,169 +1597,248 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>272</v>
+        <v>12</v>
       </c>
       <c r="M4" t="n">
-        <v>10</v>
+        <v>127</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>0.2433333333333327</v>
+        <v>-0.1649999999999998</v>
       </c>
       <c r="P4" t="n">
-        <v>0.9547023809523807</v>
+        <v>0.28</v>
       </c>
       <c r="Q4" t="n">
-        <v>2</v>
+        <v>0.3983529411764708</v>
       </c>
       <c r="R4" t="n">
-        <v>1.090909090909091</v>
+        <v>-0.1180784313725494</v>
       </c>
       <c r="S4" t="n">
-        <v>0.333333333333333</v>
+        <v>-1</v>
       </c>
       <c r="T4" t="n">
-        <v>2.067099567099568</v>
+        <v>0.5</v>
       </c>
       <c r="U4" t="n">
-        <v>4</v>
+        <v>0.1013071895424835</v>
       </c>
       <c r="V4" t="n">
-        <v>8.283549783549784</v>
+        <v>-0.05555555555555558</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.6666666666666667</v>
+        <v>3</v>
       </c>
       <c r="X4" t="n">
-        <v>1.227272727272727</v>
+        <v>0.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>-1</v>
+        <v>1.599264705882353</v>
       </c>
       <c r="Z4" t="n">
+        <v>0.1360294117647056</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>3.246323529411764</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>-0.1139705882352935</v>
+      </c>
+      <c r="AE4" t="n">
         <v>1.5</v>
       </c>
-      <c r="AA4" t="n">
-        <v>21.324185999186</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>16.95514331622656</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>1116.578180758256</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>826.0456466161302</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>-8</v>
-      </c>
       <c r="AF4" t="n">
-        <v>34.77619047619046</v>
+        <v>0.5</v>
       </c>
       <c r="AG4" t="n">
-        <v>14</v>
+        <v>-0.2941176470588236</v>
       </c>
       <c r="AH4" t="n">
-        <v>27.96428571428572</v>
+        <v>0.2941176470588234</v>
       </c>
       <c r="AI4" t="n">
-        <v>7.666666666666664</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="AJ4" t="n">
-        <v>7.40909090909091</v>
+        <v>-1.666666666666667</v>
       </c>
       <c r="AK4" t="n">
-        <v>-7.333333333333343</v>
+        <v>-0.5294117647058822</v>
       </c>
       <c r="AL4" t="n">
-        <v>14.67532467532467</v>
+        <v>0.1470588235294117</v>
       </c>
       <c r="AM4" t="n">
-        <v>-264</v>
+        <v>8.242857142857142</v>
       </c>
       <c r="AN4" t="n">
-        <v>130.7869674185463</v>
+        <v>-6.823863636363637</v>
       </c>
       <c r="AO4" t="n">
-        <v>2.166666666666667</v>
+        <v>9.59915329768271</v>
       </c>
       <c r="AP4" t="n">
-        <v>-1.466666666666667</v>
+        <v>-11.3653925296195</v>
       </c>
       <c r="AQ4" t="inlineStr"/>
-      <c r="AR4" t="n">
-        <v>-1.5</v>
-      </c>
+      <c r="AR4" t="inlineStr"/>
       <c r="AS4" t="n">
-        <v>-0.6666666666666643</v>
+        <v>407.7337269386269</v>
       </c>
       <c r="AT4" t="n">
-        <v>-5.681818181818176</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>-26.32571317571317</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>-3.162634977319126</v>
-      </c>
+        <v>-467.4994028131933</v>
+      </c>
+      <c r="AU4" t="inlineStr"/>
+      <c r="AV4" t="inlineStr"/>
       <c r="AW4" t="n">
-        <v>0.04019339286734013</v>
+        <v>-0.2053571428571388</v>
       </c>
       <c r="AX4" t="n">
-        <v>-0.008130857806083018</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>0.1818181818181819</v>
-      </c>
-      <c r="BA4" t="inlineStr"/>
-      <c r="BB4" t="inlineStr"/>
+        <v>-9.008928571428569</v>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr"/>
+      <c r="BA4" t="n">
+        <v>8.991071428571431</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>-7.053571428571431</v>
+      </c>
       <c r="BC4" t="n">
-        <v>-5.52950178476496</v>
+        <v>-3.333333333333336</v>
       </c>
       <c r="BD4" t="n">
-        <v>4.119552669552668</v>
-      </c>
-      <c r="BE4" t="inlineStr"/>
-      <c r="BF4" t="inlineStr"/>
-      <c r="BG4" t="inlineStr"/>
-      <c r="BH4" t="inlineStr"/>
-      <c r="BI4" t="inlineStr"/>
-      <c r="BJ4" t="inlineStr"/>
+        <v>-11.83333333333333</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>3.70261437908497</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>-1.36274509803922</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>-11.5</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>1.702205882352942</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>-1.702205882352942</v>
+      </c>
       <c r="BK4" t="inlineStr"/>
       <c r="BL4" t="inlineStr"/>
-      <c r="BM4" t="inlineStr"/>
-      <c r="BN4" t="inlineStr"/>
-      <c r="BO4" t="inlineStr"/>
+      <c r="BM4" t="n">
+        <v>-21.61538461538464</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>-22.66153846153844</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>1</v>
+      </c>
       <c r="BP4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ4" t="inlineStr"/>
-      <c r="BR4" t="inlineStr"/>
-      <c r="BS4" t="n">
-        <v>-5.746164654059399</v>
-      </c>
-      <c r="BT4" t="n">
-        <v>-0.2351826536037152</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>-0.164705882352941</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>0.8745098039215686</v>
+      </c>
+      <c r="BS4" t="inlineStr"/>
+      <c r="BT4" t="inlineStr"/>
       <c r="BU4" t="n">
-        <v>-757402.9771398194</v>
-      </c>
-      <c r="BV4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="BV4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW4" t="n">
+        <v>-5.166666666666666</v>
+      </c>
+      <c r="BX4" t="n">
+        <v>-2.666666666666666</v>
+      </c>
+      <c r="BY4" t="n">
+        <v>-2.071895424836605</v>
+      </c>
+      <c r="BZ4" t="n">
+        <v>1.928104575163395</v>
+      </c>
+      <c r="CA4" t="inlineStr"/>
+      <c r="CB4" t="inlineStr"/>
+      <c r="CC4" t="n">
+        <v>1.034254582393276</v>
+      </c>
+      <c r="CD4" t="n">
+        <v>-0.416751592459164</v>
+      </c>
+      <c r="CE4" t="inlineStr"/>
+      <c r="CF4" t="inlineStr"/>
+      <c r="CG4" t="n">
+        <v>0.01640937459512249</v>
+      </c>
+      <c r="CH4" t="n">
+        <v>-0.02393637884377205</v>
+      </c>
+      <c r="CI4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ4" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="CK4" t="n">
+        <v>0.1013071895424837</v>
+      </c>
+      <c r="CL4" t="n">
+        <v>-0.07189542483660133</v>
+      </c>
+      <c r="CM4" t="n">
+        <v>1.046899551066218</v>
+      </c>
+      <c r="CN4" t="inlineStr"/>
+      <c r="CO4" t="inlineStr"/>
+      <c r="CP4" t="inlineStr"/>
+      <c r="CQ4" t="inlineStr"/>
+      <c r="CR4" t="inlineStr"/>
+      <c r="CS4" t="inlineStr"/>
+      <c r="CT4" t="inlineStr"/>
+      <c r="CU4" t="inlineStr"/>
+      <c r="CV4" t="inlineStr"/>
+      <c r="CW4" t="inlineStr"/>
+      <c r="CX4" t="inlineStr"/>
+      <c r="CY4" t="inlineStr"/>
+      <c r="CZ4" t="inlineStr"/>
+      <c r="DA4" t="inlineStr"/>
+      <c r="DB4" t="inlineStr"/>
+      <c r="DC4" t="inlineStr"/>
+      <c r="DD4" t="inlineStr"/>
+      <c r="DE4" t="inlineStr"/>
+      <c r="DF4" t="inlineStr"/>
+      <c r="DG4" t="inlineStr"/>
+      <c r="DH4" t="inlineStr"/>
+      <c r="DI4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>WMcg8Qx2</t>
+          <t>h2acepbK</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45585.5</v>
+        <v>45592.54166666666</v>
       </c>
       <c r="C5" t="n">
         <v>102</v>
@@ -1381,10 +1847,10 @@
         <v>133</v>
       </c>
       <c r="E5" t="n">
-        <v>858</v>
+        <v>736</v>
       </c>
       <c r="F5" t="n">
-        <v>370</v>
+        <v>599</v>
       </c>
       <c r="G5" t="n">
         <v>55</v>
@@ -1406,171 +1872,272 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>168</v>
+        <v>312</v>
       </c>
       <c r="M5" t="n">
-        <v>163</v>
+        <v>141</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>1.046666666666666</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.280828157349897</v>
+        <v>-0.5033333333333333</v>
       </c>
       <c r="Q5" t="n">
+        <v>0.3656617647058823</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.00768382352941166</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.3333333333333334</v>
+      </c>
+      <c r="T5" t="n">
+        <v>-0.6666666666666667</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0.4705882352941178</v>
+      </c>
+      <c r="V5" t="n">
+        <v>-0.411764705882353</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1</v>
+      </c>
+      <c r="X5" t="n">
+        <v>-0.333333333333333</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.327205882352941</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0.2757352941176472</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>3.323529411764707</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.397058823529411</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>-0.3333333333333333</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0.4705882352941178</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0.1176470588235294</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0.3333333333333335</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>-0.6666666666666666</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0.2941176470588234</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>-0.2352941176470589</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>7.572619047619047</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>-9.625490196078433</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>7.898432531520767</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>-9.582360965219422</v>
+      </c>
+      <c r="AQ5" t="inlineStr"/>
+      <c r="AR5" t="inlineStr"/>
+      <c r="AS5" t="n">
+        <v>403.3444973257274</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>-470.2368251815295</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>45</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>-60</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>5.223809523809521</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>-16.26666666666667</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>-7</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>-21</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>2.857142857142854</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>-8.69047619047619</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>-5.333333333333336</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>-4</v>
+      </c>
+      <c r="BE5" t="n">
         <v>2</v>
       </c>
-      <c r="R5" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="S5" t="n">
-        <v>3.416666666666667</v>
-      </c>
-      <c r="T5" t="n">
-        <v>-1.321428571428572</v>
-      </c>
-      <c r="U5" t="n">
-        <v>8.333333333333334</v>
-      </c>
-      <c r="V5" t="n">
-        <v>0.6904761904761898</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0.3333333333333335</v>
-      </c>
-      <c r="X5" t="n">
-        <v>-0.7440476190476191</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>-1.410714285714286</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>16.97682329244829</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>20.70092448025401</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>1019.071876069671</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>998.0526490373254</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>-48.16666666666666</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>-7.576086956521735</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>2.166666666666664</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>2.945652173913047</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>2.303571428571423</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>-9.023809523809518</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>-115.5</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>-118.421052631579</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>3.000000000000001</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>-0.1385281385281385</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>8.916666666666668</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>7.666666666666668</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>-59.46730769230769</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>-2.172860380457625</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>-0.01613637689317193</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>0.02000766868186468</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>0.5833333333333333</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>-0.1488095238095238</v>
-      </c>
-      <c r="BA5" t="inlineStr"/>
-      <c r="BB5" t="inlineStr"/>
-      <c r="BC5" t="inlineStr"/>
-      <c r="BD5" t="inlineStr"/>
-      <c r="BE5" t="inlineStr"/>
-      <c r="BF5" t="inlineStr"/>
-      <c r="BG5" t="inlineStr"/>
-      <c r="BH5" t="inlineStr"/>
-      <c r="BI5" t="inlineStr"/>
-      <c r="BJ5" t="inlineStr"/>
+      <c r="BF5" t="n">
+        <v>-2.529411764705884</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>3.333333333333336</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>-3.333333333333336</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>2.136029411764703</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>-2.136029411764703</v>
+      </c>
       <c r="BK5" t="inlineStr"/>
       <c r="BL5" t="inlineStr"/>
-      <c r="BM5" t="inlineStr"/>
-      <c r="BN5" t="inlineStr"/>
-      <c r="BO5" t="inlineStr"/>
-      <c r="BP5" t="inlineStr"/>
-      <c r="BQ5" t="inlineStr"/>
-      <c r="BR5" t="inlineStr"/>
+      <c r="BM5" t="n">
+        <v>-2.626373626373606</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>-40.37362637362645</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>-0.3999999999999999</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>0.2156862745098038</v>
+      </c>
       <c r="BS5" t="inlineStr"/>
       <c r="BT5" t="inlineStr"/>
-      <c r="BU5" t="inlineStr"/>
-      <c r="BV5" t="inlineStr"/>
+      <c r="BU5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BV5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BW5" t="n">
+        <v>1.666666666666668</v>
+      </c>
+      <c r="BX5" t="n">
+        <v>3.333333333333332</v>
+      </c>
+      <c r="BY5" t="n">
+        <v>2.647058823529413</v>
+      </c>
+      <c r="BZ5" t="n">
+        <v>6.52941176470588</v>
+      </c>
+      <c r="CA5" t="inlineStr"/>
+      <c r="CB5" t="inlineStr"/>
+      <c r="CC5" t="n">
+        <v>-0.4484297445664289</v>
+      </c>
+      <c r="CD5" t="n">
+        <v>-1.77383962890849</v>
+      </c>
+      <c r="CE5" t="n">
+        <v>0.01106427818756586</v>
+      </c>
+      <c r="CF5" t="n">
+        <v>-0.04144144144144145</v>
+      </c>
+      <c r="CG5" t="n">
+        <v>0.008024737532382469</v>
+      </c>
+      <c r="CH5" t="n">
+        <v>0.005151816045285598</v>
+      </c>
+      <c r="CI5" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="CJ5" t="n">
+        <v>-0.3333333333333333</v>
+      </c>
+      <c r="CK5" t="n">
+        <v>-0.1176470588235294</v>
+      </c>
+      <c r="CL5" t="n">
+        <v>-0.2352941176470588</v>
+      </c>
+      <c r="CM5" t="n">
+        <v>2.091806958473626</v>
+      </c>
+      <c r="CN5" t="inlineStr"/>
+      <c r="CO5" t="inlineStr"/>
+      <c r="CP5" t="inlineStr"/>
+      <c r="CQ5" t="inlineStr"/>
+      <c r="CR5" t="inlineStr"/>
+      <c r="CS5" t="inlineStr"/>
+      <c r="CT5" t="inlineStr"/>
+      <c r="CU5" t="inlineStr"/>
+      <c r="CV5" t="inlineStr"/>
+      <c r="CW5" t="inlineStr"/>
+      <c r="CX5" t="inlineStr"/>
+      <c r="CY5" t="inlineStr"/>
+      <c r="CZ5" t="inlineStr"/>
+      <c r="DA5" t="inlineStr"/>
+      <c r="DB5" t="inlineStr"/>
+      <c r="DC5" t="inlineStr"/>
+      <c r="DD5" t="inlineStr"/>
+      <c r="DE5" t="inlineStr"/>
+      <c r="DF5" t="inlineStr"/>
+      <c r="DG5" t="inlineStr"/>
+      <c r="DH5" t="inlineStr"/>
+      <c r="DI5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>b9aoAn8k</t>
+          <t>WdE2Z2y1</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45585.41666666666</v>
+        <v>45592.45833333334</v>
       </c>
       <c r="C6" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D6" t="n">
         <v>133</v>
       </c>
       <c r="E6" t="n">
-        <v>194</v>
+        <v>56</v>
       </c>
       <c r="F6" t="n">
-        <v>39</v>
+        <v>228</v>
       </c>
       <c r="G6" t="n">
         <v>55</v>
@@ -1592,169 +2159,276 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>198</v>
+        <v>165</v>
       </c>
       <c r="M6" t="n">
-        <v>138</v>
+        <v>109</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.7133333333333333</v>
+        <v>1.516666666666667</v>
       </c>
       <c r="P6" t="n">
-        <v>0.3479999999999996</v>
+        <v>-0.9233333333333331</v>
       </c>
       <c r="Q6" t="n">
+        <v>0.7670555555555554</v>
+      </c>
+      <c r="R6" t="n">
+        <v>-0.1551111111111112</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2</v>
+      </c>
+      <c r="T6" t="n">
+        <v>-2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0.6000000000000001</v>
+      </c>
+      <c r="V6" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0.333333333333333</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0.9777777777777779</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0.3888888888888893</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>9.666666666666668</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>-4.666666666666666</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0.8722222222222218</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.161111111111111</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="AF6" t="n">
         <v>-1</v>
       </c>
-      <c r="R6" t="n">
-        <v>0.6883116883116883</v>
-      </c>
-      <c r="S6" t="n">
-        <v>1.000000000000001</v>
-      </c>
-      <c r="T6" t="n">
-        <v>0.7214285714285715</v>
-      </c>
-      <c r="U6" t="n">
-        <v>3.333333333333332</v>
-      </c>
-      <c r="V6" t="n">
-        <v>3.397619047619049</v>
-      </c>
-      <c r="W6" t="n">
-        <v>-0.6666666666666666</v>
-      </c>
-      <c r="X6" t="n">
-        <v>-0.1904761904761905</v>
-      </c>
-      <c r="Y6" t="n">
+      <c r="AG6" t="n">
+        <v>0.3499999999999999</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>-0.04999999999999982</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0.6499999999999999</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>-0.55</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>7.85427807486631</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>-8.925074925074924</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>10.76994678116002</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>-11.42324403991071</v>
+      </c>
+      <c r="AQ6" t="inlineStr"/>
+      <c r="AR6" t="inlineStr"/>
+      <c r="AS6" t="n">
+        <v>500.2442801626408</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>-444.7188794087336</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>32</v>
+      </c>
+      <c r="AV6" t="n">
         <v>-1</v>
       </c>
-      <c r="Z6" t="n">
-        <v>-0.974025974025974</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>17.72994227994228</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>19.07079056533327</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>1307.559727809067</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>991.4230134947686</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>-29.5</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>-14.8315789473684</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>-4.5</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>1.421052631578945</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>-4</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>-0.5324675324675354</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>-26.66666666666667</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>-15.37619047619049</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>-580</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>-156</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>0.2222222222222223</v>
-      </c>
-      <c r="AQ6" t="inlineStr"/>
-      <c r="AR6" t="n">
-        <v>-0.75</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>-1.333333333333336</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>4.40909090909091</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>15.44088345864661</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>2.593518384197457</v>
-      </c>
       <c r="AW6" t="n">
-        <v>-0.0396253353120958</v>
+        <v>-10.48611111111111</v>
       </c>
       <c r="AX6" t="n">
-        <v>-0.01161466584378629</v>
+        <v>10.53472222222223</v>
       </c>
       <c r="AY6" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AZ6" t="n">
-        <v>-0.2835497835497836</v>
-      </c>
-      <c r="BA6" t="inlineStr"/>
-      <c r="BB6" t="inlineStr"/>
-      <c r="BC6" t="inlineStr"/>
-      <c r="BD6" t="inlineStr"/>
-      <c r="BE6" t="inlineStr"/>
-      <c r="BF6" t="inlineStr"/>
-      <c r="BG6" t="inlineStr"/>
-      <c r="BH6" t="inlineStr"/>
-      <c r="BI6" t="inlineStr"/>
-      <c r="BJ6" t="inlineStr"/>
+        <v>-15</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>-4.993055555555557</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>-9.5625</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>-6.333333333333329</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>-5</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>21.75</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>5.666666666666664</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>-5.666666666666664</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>-3.711111111111116</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>3.711111111111116</v>
+      </c>
       <c r="BK6" t="inlineStr"/>
       <c r="BL6" t="inlineStr"/>
-      <c r="BM6" t="inlineStr"/>
-      <c r="BN6" t="inlineStr"/>
-      <c r="BO6" t="inlineStr"/>
-      <c r="BP6" t="inlineStr"/>
-      <c r="BQ6" t="inlineStr"/>
-      <c r="BR6" t="inlineStr"/>
-      <c r="BS6" t="inlineStr"/>
-      <c r="BT6" t="inlineStr"/>
-      <c r="BU6" t="inlineStr"/>
-      <c r="BV6" t="inlineStr"/>
+      <c r="BM6" t="n">
+        <v>-28.09821428571433</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>45.35714285714283</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>-0.666666666666667</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>-0.2588235294117645</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>0.2588235294117649</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>1</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="BW6" t="n">
+        <v>-1.333333333333332</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>-7</v>
+      </c>
+      <c r="BY6" t="n">
+        <v>3.550000000000001</v>
+      </c>
+      <c r="BZ6" t="n">
+        <v>4.949999999999996</v>
+      </c>
+      <c r="CA6" t="inlineStr"/>
+      <c r="CB6" t="inlineStr"/>
+      <c r="CC6" t="n">
+        <v>1.522908226265324</v>
+      </c>
+      <c r="CD6" t="n">
+        <v>-1.335746138506565</v>
+      </c>
+      <c r="CE6" t="n">
+        <v>0.04444444444444444</v>
+      </c>
+      <c r="CF6" t="n">
+        <v>0.0148489503328213</v>
+      </c>
+      <c r="CG6" t="n">
+        <v>0.01851880179134279</v>
+      </c>
+      <c r="CH6" t="n">
+        <v>0.01551371275855187</v>
+      </c>
+      <c r="CI6" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="CJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK6" t="n">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="CL6" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="CM6" t="n">
+        <v>6.682192437192427</v>
+      </c>
+      <c r="CN6" t="inlineStr"/>
+      <c r="CO6" t="inlineStr"/>
+      <c r="CP6" t="inlineStr"/>
+      <c r="CQ6" t="inlineStr"/>
+      <c r="CR6" t="inlineStr"/>
+      <c r="CS6" t="inlineStr"/>
+      <c r="CT6" t="inlineStr"/>
+      <c r="CU6" t="inlineStr"/>
+      <c r="CV6" t="inlineStr"/>
+      <c r="CW6" t="inlineStr"/>
+      <c r="CX6" t="inlineStr"/>
+      <c r="CY6" t="inlineStr"/>
+      <c r="CZ6" t="inlineStr"/>
+      <c r="DA6" t="inlineStr"/>
+      <c r="DB6" t="inlineStr"/>
+      <c r="DC6" t="inlineStr"/>
+      <c r="DD6" t="inlineStr"/>
+      <c r="DE6" t="inlineStr"/>
+      <c r="DF6" t="inlineStr"/>
+      <c r="DG6" t="inlineStr"/>
+      <c r="DH6" t="inlineStr"/>
+      <c r="DI6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>S2WzL3M7</t>
+          <t>vaZNtoqR</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45584.66666666666</v>
+        <v>45591.66666666666</v>
       </c>
       <c r="C7" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D7" t="n">
         <v>133</v>
       </c>
       <c r="E7" t="n">
-        <v>206</v>
+        <v>273</v>
       </c>
       <c r="F7" t="n">
-        <v>516</v>
+        <v>545</v>
       </c>
       <c r="G7" t="n">
         <v>55</v>
@@ -1776,167 +2450,284 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>40</v>
+        <v>312</v>
       </c>
       <c r="M7" t="n">
-        <v>258</v>
+        <v>127</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>2.4</v>
+        <v>-1.47</v>
       </c>
       <c r="P7" t="n">
-        <v>1.395833333333333</v>
+        <v>-0.4299999999999999</v>
       </c>
       <c r="Q7" t="n">
+        <v>0.56375</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.009374999999999911</v>
+      </c>
+      <c r="S7" t="n">
+        <v>-0.6666666666666667</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.3333333333333334</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0.4513888888888888</v>
+      </c>
+      <c r="V7" t="n">
+        <v>-0.2986111111111112</v>
+      </c>
+      <c r="W7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>2.077205882352941</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>-0.2977941176470589</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AB7" t="n">
         <v>3</v>
       </c>
-      <c r="R7" t="n">
-        <v>1.891304347826087</v>
-      </c>
-      <c r="S7" t="n">
-        <v>6.333333333333334</v>
-      </c>
-      <c r="T7" t="n">
-        <v>3.257575757575758</v>
-      </c>
-      <c r="U7" t="n">
-        <v>16</v>
-      </c>
-      <c r="V7" t="n">
-        <v>9.848484848484848</v>
-      </c>
-      <c r="W7" t="n">
-        <v>3.666666666666667</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1.846014492753623</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2.402173913043478</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>15.82806637806638</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>15.80386235225362</v>
-      </c>
       <c r="AC7" t="n">
-        <v>795.0576828669612</v>
+        <v>3.860294117647058</v>
       </c>
       <c r="AD7" t="n">
-        <v>733.6018746331549</v>
+        <v>0.5514705882352935</v>
       </c>
       <c r="AE7" t="n">
-        <v>86</v>
+        <v>-1.5</v>
       </c>
       <c r="AF7" t="n">
-        <v>87.59006211180125</v>
+        <v>-0.5</v>
       </c>
       <c r="AG7" t="n">
-        <v>84</v>
+        <v>0.3786764705882353</v>
       </c>
       <c r="AH7" t="n">
-        <v>52.10144927536233</v>
+        <v>0.1801470588235294</v>
       </c>
       <c r="AI7" t="n">
-        <v>9.666666666666675</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="AJ7" t="n">
-        <v>8.251811594202906</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="AK7" t="n">
-        <v>36.66666666666666</v>
+        <v>0.3055555555555556</v>
       </c>
       <c r="AL7" t="n">
-        <v>43.86363636363636</v>
+        <v>-0.2777777777777777</v>
       </c>
       <c r="AM7" t="n">
-        <v>202</v>
+        <v>15.06439393939394</v>
       </c>
       <c r="AN7" t="n">
-        <v>464.1636363636364</v>
+        <v>-10.67142857142857</v>
       </c>
       <c r="AO7" t="n">
-        <v>-1.333333333333333</v>
+        <v>10.88691366339199</v>
       </c>
       <c r="AP7" t="n">
-        <v>-0.4318181818181819</v>
-      </c>
-      <c r="AQ7" t="inlineStr"/>
-      <c r="AR7" t="inlineStr"/>
+        <v>-9.512088994596734</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>673.0264227642276</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>-412.0390070921986</v>
+      </c>
       <c r="AS7" t="n">
-        <v>-1.666666666666663</v>
+        <v>550.0974765100746</v>
       </c>
       <c r="AT7" t="n">
-        <v>-6.036231884057976</v>
+        <v>-449.60468631619</v>
       </c>
       <c r="AU7" t="n">
-        <v>-11.2068376068376</v>
+        <v>-11</v>
       </c>
       <c r="AV7" t="n">
-        <v>-11.34529829707059</v>
+        <v>58</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.0445958295958296</v>
+        <v>9.012500000000003</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.01949881360720211</v>
+        <v>12.30833333333334</v>
       </c>
       <c r="AY7" t="n">
-        <v>0.3333333333333333</v>
+        <v>-6</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.3804347826086957</v>
-      </c>
-      <c r="BA7" t="inlineStr"/>
-      <c r="BB7" t="inlineStr"/>
-      <c r="BC7" t="inlineStr"/>
-      <c r="BD7" t="inlineStr"/>
-      <c r="BE7" t="inlineStr"/>
-      <c r="BF7" t="inlineStr"/>
-      <c r="BG7" t="inlineStr"/>
-      <c r="BH7" t="inlineStr"/>
-      <c r="BI7" t="inlineStr"/>
-      <c r="BJ7" t="inlineStr"/>
-      <c r="BK7" t="inlineStr"/>
-      <c r="BL7" t="inlineStr"/>
-      <c r="BM7" t="inlineStr"/>
-      <c r="BN7" t="inlineStr"/>
-      <c r="BO7" t="inlineStr"/>
-      <c r="BP7" t="inlineStr"/>
-      <c r="BQ7" t="inlineStr"/>
-      <c r="BR7" t="inlineStr"/>
+        <v>26</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>8.929166666666667</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>3.470833333333331</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>20.16666666666667</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>13.83333333333333</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>3.722222222222221</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>2.916666666666668</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>-12</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>12</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>-8.860294117647058</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>8.860294117647058</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>-199</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>139</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>-86.92857142857144</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>92.03571428571428</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>0.2689075630252102</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>0.0840336134453783</v>
+      </c>
       <c r="BS7" t="inlineStr"/>
       <c r="BT7" t="inlineStr"/>
-      <c r="BU7" t="inlineStr"/>
-      <c r="BV7" t="inlineStr"/>
+      <c r="BU7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="BW7" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="BX7" t="n">
+        <v>5</v>
+      </c>
+      <c r="BY7" t="n">
+        <v>5.409722222222221</v>
+      </c>
+      <c r="BZ7" t="n">
+        <v>-0.5694444444444429</v>
+      </c>
+      <c r="CA7" t="n">
+        <v>6.571428571428573</v>
+      </c>
+      <c r="CB7" t="n">
+        <v>-22.44047619047619</v>
+      </c>
+      <c r="CC7" t="n">
+        <v>1.614214789552781</v>
+      </c>
+      <c r="CD7" t="n">
+        <v>-3.125570349122063</v>
+      </c>
+      <c r="CE7" t="n">
+        <v>-0.05520614954577219</v>
+      </c>
+      <c r="CF7" t="n">
+        <v>0.001068376068376068</v>
+      </c>
+      <c r="CG7" t="n">
+        <v>0.008368212744801477</v>
+      </c>
+      <c r="CH7" t="n">
+        <v>0.005919345640475256</v>
+      </c>
+      <c r="CI7" t="n">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="CJ7" t="n">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="CK7" t="n">
+        <v>0.05555555555555558</v>
+      </c>
+      <c r="CL7" t="n">
+        <v>-0.09027777777777779</v>
+      </c>
+      <c r="CM7" t="n">
+        <v>1.502411616161623</v>
+      </c>
+      <c r="CN7" t="inlineStr"/>
+      <c r="CO7" t="inlineStr"/>
+      <c r="CP7" t="inlineStr"/>
+      <c r="CQ7" t="inlineStr"/>
+      <c r="CR7" t="inlineStr"/>
+      <c r="CS7" t="inlineStr"/>
+      <c r="CT7" t="inlineStr"/>
+      <c r="CU7" t="inlineStr"/>
+      <c r="CV7" t="inlineStr"/>
+      <c r="CW7" t="inlineStr"/>
+      <c r="CX7" t="inlineStr"/>
+      <c r="CY7" t="inlineStr"/>
+      <c r="CZ7" t="inlineStr"/>
+      <c r="DA7" t="inlineStr"/>
+      <c r="DB7" t="inlineStr"/>
+      <c r="DC7" t="inlineStr"/>
+      <c r="DD7" t="inlineStr"/>
+      <c r="DE7" t="inlineStr"/>
+      <c r="DF7" t="inlineStr"/>
+      <c r="DG7" t="inlineStr"/>
+      <c r="DH7" t="inlineStr"/>
+      <c r="DI7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>OAZJOoNr</t>
+          <t>hQspntL6</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45584.58333333334</v>
+        <v>45591.58333333334</v>
       </c>
       <c r="C8" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D8" t="n">
         <v>133</v>
       </c>
       <c r="E8" t="n">
-        <v>528</v>
+        <v>826</v>
       </c>
       <c r="F8" t="n">
-        <v>176</v>
+        <v>133</v>
       </c>
       <c r="G8" t="n">
         <v>55</v>
@@ -1958,157 +2749,260 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>272</v>
+        <v>12</v>
       </c>
       <c r="M8" t="n">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.163333333333333</v>
+        <v>0.9149999999999997</v>
       </c>
       <c r="P8" t="n">
-        <v>0.5589210526315789</v>
+        <v>-1.58</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.25</v>
+        <v>0.2337916666666666</v>
       </c>
       <c r="R8" t="n">
-        <v>0.8628571428571428</v>
+        <v>-0.1236250000000001</v>
       </c>
       <c r="S8" t="n">
-        <v>1.333333333333333</v>
+        <v>1.666666666666667</v>
       </c>
       <c r="T8" t="n">
-        <v>1.508333333333333</v>
+        <v>-2.333333333333333</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.333333333333334</v>
+        <v>0.1838235294117647</v>
       </c>
       <c r="V8" t="n">
-        <v>2.733333333333334</v>
+        <v>-0.1691176470588236</v>
       </c>
       <c r="W8" t="n">
-        <v>-1.110223024625157e-16</v>
+        <v>0.833333333333333</v>
       </c>
       <c r="X8" t="n">
-        <v>0.52</v>
+        <v>-2.5</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.25</v>
+        <v>-1.1875</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.9828571428571429</v>
+        <v>-1.1875</v>
       </c>
       <c r="AA8" t="n">
-        <v>21.0459743959744</v>
+        <v>5.833333333333334</v>
       </c>
       <c r="AB8" t="n">
-        <v>20.25060286391169</v>
+        <v>-7.166666666666666</v>
       </c>
       <c r="AC8" t="n">
-        <v>1201.0526310704</v>
+        <v>0.9191176470588243</v>
       </c>
       <c r="AD8" t="n">
-        <v>890.0762537686242</v>
+        <v>-0.9375</v>
       </c>
       <c r="AE8" t="n">
-        <v>-10.5</v>
+        <v>1.833333333333333</v>
       </c>
       <c r="AF8" t="n">
-        <v>-1.794050343249424</v>
+        <v>-1.666666666666667</v>
       </c>
       <c r="AG8" t="n">
-        <v>-20</v>
+        <v>-0.4595588235294117</v>
       </c>
       <c r="AH8" t="n">
-        <v>5.501144164759722</v>
+        <v>-0.400735294117647</v>
       </c>
       <c r="AI8" t="n">
-        <v>6.083333333333336</v>
+        <v>2.333333333333333</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2.291428571428577</v>
+        <v>-2.666666666666667</v>
       </c>
       <c r="AK8" t="n">
-        <v>-18</v>
+        <v>0.03308823529411775</v>
       </c>
       <c r="AL8" t="n">
-        <v>-2.75</v>
+        <v>-0.1654411764705883</v>
       </c>
       <c r="AM8" t="n">
-        <v>-581</v>
+        <v>5.266835016835016</v>
       </c>
       <c r="AN8" t="n">
-        <v>-21.50505050505052</v>
+        <v>-9.224242424242425</v>
       </c>
       <c r="AO8" t="n">
-        <v>-0.6666666666666665</v>
+        <v>9.268325693591754</v>
       </c>
       <c r="AP8" t="n">
-        <v>-0.6891304347826086</v>
+        <v>-10.07758148714031</v>
       </c>
       <c r="AQ8" t="inlineStr"/>
-      <c r="AR8" t="n">
-        <v>0</v>
-      </c>
+      <c r="AR8" t="inlineStr"/>
       <c r="AS8" t="n">
-        <v>-1.583333333333334</v>
+        <v>434.4315121758588</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.3447619047619099</v>
+        <v>-433.6458755835624</v>
       </c>
       <c r="AU8" t="n">
-        <v>40.22222222222222</v>
+        <v>1</v>
       </c>
       <c r="AV8" t="n">
-        <v>2.572943978029102</v>
+        <v>-42</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.002445702445702448</v>
+        <v>-8.776785714285708</v>
       </c>
       <c r="AX8" t="n">
-        <v>-0.01043226675908079</v>
+        <v>-12.16964285714286</v>
       </c>
       <c r="AY8" t="n">
-        <v>-0.25</v>
+        <v>13</v>
       </c>
       <c r="AZ8" t="n">
-        <v>-0.07047619047619047</v>
-      </c>
-      <c r="BA8" t="inlineStr"/>
-      <c r="BB8" t="inlineStr"/>
-      <c r="BC8" t="inlineStr"/>
-      <c r="BD8" t="inlineStr"/>
-      <c r="BE8" t="inlineStr"/>
-      <c r="BF8" t="inlineStr"/>
-      <c r="BG8" t="inlineStr"/>
-      <c r="BH8" t="inlineStr"/>
-      <c r="BI8" t="inlineStr"/>
-      <c r="BJ8" t="inlineStr"/>
+        <v>-31</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>8.026785714285715</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>-2.571428571428569</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>-3.166666666666668</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>-8.166666666666664</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>1.926470588235297</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>-3.459558823529413</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>-2.996323529411768</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>2.996323529411768</v>
+      </c>
       <c r="BK8" t="inlineStr"/>
       <c r="BL8" t="inlineStr"/>
-      <c r="BM8" t="inlineStr"/>
-      <c r="BN8" t="inlineStr"/>
-      <c r="BO8" t="inlineStr"/>
-      <c r="BP8" t="inlineStr"/>
-      <c r="BQ8" t="inlineStr"/>
-      <c r="BR8" t="inlineStr"/>
+      <c r="BM8" t="n">
+        <v>-8.620512820512772</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>4.779487179487205</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>0.8333333333333335</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>0.6666666666666665</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>-0.2830882352941178</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>-0.2389705882352939</v>
+      </c>
       <c r="BS8" t="inlineStr"/>
       <c r="BT8" t="inlineStr"/>
-      <c r="BU8" t="inlineStr"/>
-      <c r="BV8" t="inlineStr"/>
+      <c r="BU8" t="n">
+        <v>-0.2142857142857143</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>-0.0714285714285714</v>
+      </c>
+      <c r="BW8" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>-1.833333333333334</v>
+      </c>
+      <c r="BY8" t="n">
+        <v>-3.75</v>
+      </c>
+      <c r="BZ8" t="n">
+        <v>3.117647058823529</v>
+      </c>
+      <c r="CA8" t="inlineStr"/>
+      <c r="CB8" t="inlineStr"/>
+      <c r="CC8" t="n">
+        <v>-0.8257298928883436</v>
+      </c>
+      <c r="CD8" t="n">
+        <v>-1.935260435705221</v>
+      </c>
+      <c r="CE8" t="n">
+        <v>-0.007542426147077314</v>
+      </c>
+      <c r="CF8" t="n">
+        <v>-0.005194805194805197</v>
+      </c>
+      <c r="CG8" t="n">
+        <v>0.003334736430559385</v>
+      </c>
+      <c r="CH8" t="n">
+        <v>-0.02010224215892942</v>
+      </c>
+      <c r="CI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ8" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="CK8" t="n">
+        <v>-0.04411764705882354</v>
+      </c>
+      <c r="CL8" t="n">
+        <v>0.07720588235294118</v>
+      </c>
+      <c r="CM8" t="n">
+        <v>-0.8393418310084968</v>
+      </c>
+      <c r="CN8" t="inlineStr"/>
+      <c r="CO8" t="inlineStr"/>
+      <c r="CP8" t="inlineStr"/>
+      <c r="CQ8" t="inlineStr"/>
+      <c r="CR8" t="inlineStr"/>
+      <c r="CS8" t="inlineStr"/>
+      <c r="CT8" t="inlineStr"/>
+      <c r="CU8" t="inlineStr"/>
+      <c r="CV8" t="inlineStr"/>
+      <c r="CW8" t="inlineStr"/>
+      <c r="CX8" t="inlineStr"/>
+      <c r="CY8" t="inlineStr"/>
+      <c r="CZ8" t="inlineStr"/>
+      <c r="DA8" t="inlineStr"/>
+      <c r="DB8" t="inlineStr"/>
+      <c r="DC8" t="inlineStr"/>
+      <c r="DD8" t="inlineStr"/>
+      <c r="DE8" t="inlineStr"/>
+      <c r="DF8" t="inlineStr"/>
+      <c r="DG8" t="inlineStr"/>
+      <c r="DH8" t="inlineStr"/>
+      <c r="DI8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>WzwSMPie</t>
+          <t>p0vxl2jf</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45584.5</v>
+        <v>45591.5</v>
       </c>
       <c r="C9" t="n">
         <v>101</v>
@@ -2117,10 +3011,10 @@
         <v>133</v>
       </c>
       <c r="E9" t="n">
-        <v>211</v>
+        <v>431</v>
       </c>
       <c r="F9" t="n">
-        <v>399</v>
+        <v>362</v>
       </c>
       <c r="G9" t="n">
         <v>55</v>
@@ -2142,163 +3036,300 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>128</v>
+        <v>313</v>
       </c>
       <c r="M9" t="n">
-        <v>211</v>
+        <v>109</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>1.106666666666666</v>
+        <v>0.5966666666666665</v>
       </c>
       <c r="P9" t="n">
-        <v>0.8141866028708137</v>
+        <v>-1.016666666666666</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.25</v>
+        <v>-0.106437908496732</v>
       </c>
       <c r="R9" t="n">
-        <v>0.8068181818181818</v>
+        <v>-0.336045751633987</v>
       </c>
       <c r="S9" t="n">
-        <v>6</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="T9" t="n">
-        <v>1.932608695652174</v>
+        <v>-0.6666666666666665</v>
       </c>
       <c r="U9" t="n">
-        <v>6.333333333333334</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="V9" t="n">
-        <v>4.939130434782609</v>
+        <v>-0.1393188854489165</v>
       </c>
       <c r="W9" t="n">
-        <v>2.333333333333333</v>
+        <v>2</v>
       </c>
       <c r="X9" t="n">
-        <v>0.5833333333333334</v>
+        <v>-0.666666666666667</v>
       </c>
       <c r="Y9" t="n">
-        <v>3.75</v>
+        <v>-1.075163398692811</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.340909090909091</v>
+        <v>0.3202614379084965</v>
       </c>
       <c r="AA9" t="n">
-        <v>16.59060846560847</v>
+        <v>4.333333333333333</v>
       </c>
       <c r="AB9" t="n">
-        <v>18.4174195101337</v>
-      </c>
-      <c r="AC9" t="inlineStr"/>
+        <v>-4.000000000000002</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>-2.813725490196077</v>
+      </c>
       <c r="AD9" t="n">
-        <v>858.213203771831</v>
+        <v>-0.6372549019607838</v>
       </c>
       <c r="AE9" t="n">
-        <v>20</v>
+        <v>0.3333333333333334</v>
       </c>
       <c r="AF9" t="n">
-        <v>15.80622009569377</v>
+        <v>-2</v>
       </c>
       <c r="AG9" t="n">
-        <v>7</v>
+        <v>0.148606811145511</v>
       </c>
       <c r="AH9" t="n">
-        <v>13.54066985645933</v>
+        <v>-0.2848297213622291</v>
       </c>
       <c r="AI9" t="n">
-        <v>8.583333333333329</v>
+        <v>0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>7.746212121212121</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>10</v>
+        <v>0.5541795665634675</v>
       </c>
       <c r="AL9" t="n">
-        <v>7.613043478260877</v>
-      </c>
-      <c r="AM9" t="inlineStr"/>
+        <v>-0.4674922600619196</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>4.928571428571429</v>
+      </c>
       <c r="AN9" t="n">
-        <v>66.68888888888893</v>
+        <v>-11.30492424242424</v>
       </c>
       <c r="AO9" t="n">
-        <v>-2</v>
+        <v>11.26153870639165</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.2826086956521738</v>
+        <v>-9.452578916181857</v>
       </c>
       <c r="AQ9" t="inlineStr"/>
-      <c r="AR9" t="n">
-        <v>-0.2666666666666667</v>
-      </c>
+      <c r="AR9" t="inlineStr"/>
       <c r="AS9" t="n">
-        <v>-11</v>
+        <v>460.6923759362616</v>
       </c>
       <c r="AT9" t="n">
-        <v>-3.242424242424242</v>
-      </c>
-      <c r="AU9" t="inlineStr"/>
+        <v>-422.385875144499</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>4</v>
+      </c>
       <c r="AV9" t="n">
-        <v>-0.9438844726253528</v>
+        <v>-10</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.04561031130798572</v>
+        <v>9.770833333333329</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.003771053847910898</v>
+        <v>-6.995833333333337</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.5</v>
+        <v>21</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.4469696969696969</v>
-      </c>
-      <c r="BA9" t="inlineStr"/>
-      <c r="BB9" t="inlineStr"/>
-      <c r="BC9" t="inlineStr"/>
-      <c r="BD9" t="inlineStr"/>
-      <c r="BE9" t="inlineStr"/>
-      <c r="BF9" t="inlineStr"/>
-      <c r="BG9" t="inlineStr"/>
-      <c r="BH9" t="inlineStr"/>
-      <c r="BI9" t="inlineStr"/>
-      <c r="BJ9" t="inlineStr"/>
+        <v>-14</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>-0.3041666666666671</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>-7.8125</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>10.66666666666667</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>-7.666666666666664</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>0.708978328173373</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>-1.981424148606811</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>8</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>-8</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>-0.5947712418300597</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>0.5947712418300597</v>
+      </c>
       <c r="BK9" t="inlineStr"/>
       <c r="BL9" t="inlineStr"/>
-      <c r="BM9" t="inlineStr"/>
-      <c r="BN9" t="inlineStr"/>
-      <c r="BO9" t="inlineStr"/>
-      <c r="BP9" t="inlineStr"/>
-      <c r="BQ9" t="inlineStr"/>
-      <c r="BR9" t="inlineStr"/>
-      <c r="BS9" t="inlineStr"/>
-      <c r="BT9" t="inlineStr"/>
-      <c r="BU9" t="inlineStr"/>
-      <c r="BV9" t="inlineStr"/>
+      <c r="BM9" t="n">
+        <v>-28.34285714285716</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>20.54761904761904</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>-0.333333333333333</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>3</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>-0.1527777777777777</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>-6.000000000000002</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>2</v>
+      </c>
+      <c r="BY9" t="n">
+        <v>-4.953560371517028</v>
+      </c>
+      <c r="BZ9" t="n">
+        <v>0.2507739938080533</v>
+      </c>
+      <c r="CA9" t="inlineStr"/>
+      <c r="CB9" t="inlineStr"/>
+      <c r="CC9" t="n">
+        <v>1.975198648523987</v>
+      </c>
+      <c r="CD9" t="n">
+        <v>0.3095709048119044</v>
+      </c>
+      <c r="CE9" t="n">
+        <v>0.05017921146953405</v>
+      </c>
+      <c r="CF9" t="n">
+        <v>0.007309941520467836</v>
+      </c>
+      <c r="CG9" t="n">
+        <v>0.006545213407907424</v>
+      </c>
+      <c r="CH9" t="n">
+        <v>-5.032095036568845e-05</v>
+      </c>
+      <c r="CI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ9" t="n">
+        <v>-0.6666666666666666</v>
+      </c>
+      <c r="CK9" t="n">
+        <v>-0.1269349845201238</v>
+      </c>
+      <c r="CL9" t="n">
+        <v>-0.2445820433436532</v>
+      </c>
+      <c r="CM9" t="n">
+        <v>-0.2854090354090459</v>
+      </c>
+      <c r="CN9" t="n">
+        <v>-0.1381944444444443</v>
+      </c>
+      <c r="CO9" t="n">
+        <v>0.4695134114251758</v>
+      </c>
+      <c r="CP9" t="n">
+        <v>-0.267136241848533</v>
+      </c>
+      <c r="CQ9" t="inlineStr"/>
+      <c r="CR9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS9" t="inlineStr"/>
+      <c r="CT9" t="inlineStr"/>
+      <c r="CU9" t="n">
+        <v>-2.306944444444454</v>
+      </c>
+      <c r="CV9" t="n">
+        <v>-574442.438866192</v>
+      </c>
+      <c r="CW9" t="inlineStr"/>
+      <c r="CX9" t="n">
+        <v>-1.647934081405936</v>
+      </c>
+      <c r="CY9" t="inlineStr"/>
+      <c r="CZ9" t="n">
+        <v>-2.072122162435463</v>
+      </c>
+      <c r="DA9" t="inlineStr"/>
+      <c r="DB9" t="inlineStr"/>
+      <c r="DC9" t="n">
+        <v>0.5722222222221944</v>
+      </c>
+      <c r="DD9" t="inlineStr"/>
+      <c r="DE9" t="inlineStr"/>
+      <c r="DF9" t="n">
+        <v>-1.364583333333343</v>
+      </c>
+      <c r="DG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH9" t="inlineStr"/>
+      <c r="DI9" t="n">
+        <v>-654722.2222222222</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>vwbmU7aL</t>
+          <t>lYpTkOLs</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45583.65625</v>
+        <v>45590.65625</v>
       </c>
       <c r="C10" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D10" t="n">
         <v>133</v>
       </c>
       <c r="E10" t="n">
-        <v>47</v>
+        <v>573</v>
       </c>
       <c r="F10" t="n">
-        <v>545</v>
+        <v>122</v>
       </c>
       <c r="G10" t="n">
         <v>55</v>
@@ -2320,171 +3351,284 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>67</v>
+        <v>249</v>
       </c>
       <c r="M10" t="n">
-        <v>127</v>
+        <v>166</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.8216666666666665</v>
+        <v>0.4733333333333335</v>
       </c>
       <c r="P10" t="n">
-        <v>0.6910000000000001</v>
+        <v>-0.9533333333333333</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.25</v>
+        <v>0.7439338235294118</v>
       </c>
       <c r="R10" t="n">
-        <v>0.7142857142857142</v>
+        <v>-0.6155882352941175</v>
       </c>
       <c r="S10" t="n">
-        <v>-2.166666666666667</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="T10" t="n">
-        <v>1.924242424242424</v>
+        <v>-1.666666666666667</v>
       </c>
       <c r="U10" t="n">
-        <v>-6.333333333333336</v>
+        <v>0.8194444444444444</v>
       </c>
       <c r="V10" t="n">
-        <v>3.926406926406926</v>
+        <v>-1.076388888888889</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.3333333333333335</v>
+        <v>3.333333333333333</v>
       </c>
       <c r="X10" t="n">
-        <v>0.8614718614718613</v>
+        <v>-2</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.25</v>
+        <v>2.534722222222222</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.149350649350649</v>
+        <v>-1.236111111111111</v>
       </c>
       <c r="AA10" t="n">
-        <v>23.72417582417582</v>
+        <v>3</v>
       </c>
       <c r="AB10" t="n">
-        <v>18.96545986160999</v>
+        <v>-2.666666666666666</v>
       </c>
       <c r="AC10" t="n">
-        <v>960.051069202665</v>
+        <v>4.604166666666666</v>
       </c>
       <c r="AD10" t="n">
-        <v>950.6766004231388</v>
+        <v>-3.166666666666666</v>
       </c>
       <c r="AE10" t="n">
-        <v>-21</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="AF10" t="n">
-        <v>9.476190476190482</v>
+        <v>-1.333333333333333</v>
       </c>
       <c r="AG10" t="n">
-        <v>-39</v>
+        <v>0.9305555555555556</v>
       </c>
       <c r="AH10" t="n">
-        <v>4.794486215538839</v>
+        <v>-0.3611111111111112</v>
       </c>
       <c r="AI10" t="n">
-        <v>11.58333333333334</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="AJ10" t="n">
-        <v>-2.168831168831169</v>
+        <v>-1.666666666666667</v>
       </c>
       <c r="AK10" t="n">
-        <v>-11.5</v>
+        <v>0.8472222222222222</v>
       </c>
       <c r="AL10" t="n">
-        <v>-6.852813852813853</v>
+        <v>-0.6944444444444444</v>
       </c>
       <c r="AM10" t="n">
-        <v>-170.5</v>
+        <v>7.896103896103896</v>
       </c>
       <c r="AN10" t="n">
-        <v>-82.54761904761904</v>
+        <v>-7.302777777777778</v>
       </c>
       <c r="AO10" t="n">
-        <v>-0.6666666666666665</v>
+        <v>8.107616104655579</v>
       </c>
       <c r="AP10" t="n">
-        <v>-0.05476190476190479</v>
+        <v>-9.445362057771758</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0</v>
+        <v>432.0265486725664</v>
       </c>
       <c r="AR10" t="n">
-        <v>-0.6</v>
+        <v>-431.0307692307692</v>
       </c>
       <c r="AS10" t="n">
-        <v>-9.833333333333332</v>
+        <v>398.3697597851033</v>
       </c>
       <c r="AT10" t="n">
-        <v>10.72077922077923</v>
+        <v>-450.8179628826593</v>
       </c>
       <c r="AU10" t="n">
-        <v>24.70105664488017</v>
+        <v>22</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.7955410317106217</v>
+        <v>-10</v>
       </c>
       <c r="AW10" t="n">
-        <v>-0.01604152717055943</v>
+        <v>6.651785714285708</v>
       </c>
       <c r="AX10" t="n">
-        <v>-0.02103249985862573</v>
+        <v>-18.40178571428571</v>
       </c>
       <c r="AY10" t="n">
-        <v>-0.08333333333333331</v>
+        <v>26</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.1038961038961038</v>
-      </c>
-      <c r="BA10" t="inlineStr"/>
-      <c r="BB10" t="inlineStr"/>
-      <c r="BC10" t="inlineStr"/>
-      <c r="BD10" t="inlineStr"/>
-      <c r="BE10" t="inlineStr"/>
-      <c r="BF10" t="inlineStr"/>
-      <c r="BG10" t="inlineStr"/>
-      <c r="BH10" t="inlineStr"/>
-      <c r="BI10" t="inlineStr"/>
-      <c r="BJ10" t="inlineStr"/>
-      <c r="BK10" t="inlineStr"/>
-      <c r="BL10" t="inlineStr"/>
-      <c r="BM10" t="inlineStr"/>
-      <c r="BN10" t="inlineStr"/>
-      <c r="BO10" t="inlineStr"/>
-      <c r="BP10" t="inlineStr"/>
-      <c r="BQ10" t="inlineStr"/>
-      <c r="BR10" t="inlineStr"/>
+        <v>-4</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>6.919642857142854</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>-9.098214285714285</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>4.333333333333329</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>-2.333333333333336</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>2.402777777777779</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>-2.930555555555557</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>6</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>-6</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>3.756944444444443</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>-3.756944444444443</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>14</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>-76</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>23.90952380952382</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>-43.0761904761905</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>0.3333333333333335</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>0.06944444444444464</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>0.2152777777777777</v>
+      </c>
       <c r="BS10" t="inlineStr"/>
       <c r="BT10" t="inlineStr"/>
-      <c r="BU10" t="inlineStr"/>
-      <c r="BV10" t="inlineStr"/>
+      <c r="BU10" t="n">
+        <v>-0.6666666666666667</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>0.2666666666666666</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>-0.3333333333333339</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY10" t="n">
+        <v>1.166666666666664</v>
+      </c>
+      <c r="BZ10" t="n">
+        <v>2.388888888888886</v>
+      </c>
+      <c r="CA10" t="n">
+        <v>-6.909090909090907</v>
+      </c>
+      <c r="CB10" t="n">
+        <v>18.93650793650794</v>
+      </c>
+      <c r="CC10" t="n">
+        <v>-1.236931585512867</v>
+      </c>
+      <c r="CD10" t="n">
+        <v>1.435993950383676</v>
+      </c>
+      <c r="CE10" t="n">
+        <v>-0.04511278195488722</v>
+      </c>
+      <c r="CF10" t="n">
+        <v>0.03749357986646122</v>
+      </c>
+      <c r="CG10" t="n">
+        <v>-0.004674997571059013</v>
+      </c>
+      <c r="CH10" t="n">
+        <v>0.01126606579179607</v>
+      </c>
+      <c r="CI10" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="CJ10" t="n">
+        <v>-0.6666666666666666</v>
+      </c>
+      <c r="CK10" t="n">
+        <v>0.08333333333333334</v>
+      </c>
+      <c r="CL10" t="n">
+        <v>-0.3263888888888889</v>
+      </c>
+      <c r="CM10" t="n">
+        <v>-0.2142135642135656</v>
+      </c>
+      <c r="CN10" t="inlineStr"/>
+      <c r="CO10" t="inlineStr"/>
+      <c r="CP10" t="inlineStr"/>
+      <c r="CQ10" t="inlineStr"/>
+      <c r="CR10" t="inlineStr"/>
+      <c r="CS10" t="inlineStr"/>
+      <c r="CT10" t="inlineStr"/>
+      <c r="CU10" t="inlineStr"/>
+      <c r="CV10" t="inlineStr"/>
+      <c r="CW10" t="inlineStr"/>
+      <c r="CX10" t="inlineStr"/>
+      <c r="CY10" t="inlineStr"/>
+      <c r="CZ10" t="inlineStr"/>
+      <c r="DA10" t="inlineStr"/>
+      <c r="DB10" t="inlineStr"/>
+      <c r="DC10" t="inlineStr"/>
+      <c r="DD10" t="inlineStr"/>
+      <c r="DE10" t="inlineStr"/>
+      <c r="DF10" t="inlineStr"/>
+      <c r="DG10" t="inlineStr"/>
+      <c r="DH10" t="inlineStr"/>
+      <c r="DI10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>OUcd1IPH</t>
+          <t>nVutWTU8</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45571.65625</v>
+        <v>45585.65625</v>
       </c>
       <c r="C11" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D11" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E11" t="n">
-        <v>535</v>
+        <v>242</v>
       </c>
       <c r="F11" t="n">
-        <v>129</v>
+        <v>303</v>
       </c>
       <c r="G11" t="n">
         <v>55</v>
@@ -2506,163 +3650,272 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>97</v>
+        <v>12</v>
       </c>
       <c r="M11" t="n">
-        <v>211</v>
+        <v>32</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>1.175</v>
+        <v>0.4700000000000002</v>
       </c>
       <c r="P11" t="n">
-        <v>0.1932380952380953</v>
+        <v>-0.2266666666666668</v>
       </c>
       <c r="Q11" t="n">
+        <v>0.3791830065359474</v>
+      </c>
+      <c r="R11" t="n">
+        <v>-0.09392156862745105</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0.3333333333333334</v>
+      </c>
+      <c r="T11" t="n">
+        <v>-0.6666666666666667</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0.2777777777777777</v>
+      </c>
+      <c r="V11" t="n">
+        <v>-0.2222222222222223</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="X11" t="n">
+        <v>-0.333333333333333</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.444444444444445</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>-0.3431372549019613</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.666666666666666</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>2.395424836601308</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1.166666666666667</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>-0.3333333333333335</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>0.2222222222222223</v>
+      </c>
+      <c r="AI11" t="n">
         <v>-0.5</v>
       </c>
-      <c r="R11" t="n">
-        <v>0.2673913043478259</v>
-      </c>
-      <c r="S11" t="n">
-        <v>1.166666666666666</v>
-      </c>
-      <c r="T11" t="n">
-        <v>-0.0239130434782604</v>
-      </c>
-      <c r="U11" t="n">
-        <v>-2.5</v>
-      </c>
-      <c r="V11" t="n">
-        <v>2.886956521739128</v>
-      </c>
-      <c r="W11" t="n">
-        <v>2.333333333333333</v>
-      </c>
-      <c r="X11" t="n">
-        <v>-1.05</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>-1.297826086956522</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>18.98333333333333</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>20.07730644939295</v>
-      </c>
-      <c r="AC11" t="inlineStr"/>
-      <c r="AD11" t="n">
-        <v>1106.84557920803</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>-46.5</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>-25.15789473684211</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>1.739234449760765</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>0.1666666666666679</v>
-      </c>
       <c r="AJ11" t="n">
-        <v>2.939130434782601</v>
+        <v>0.5</v>
       </c>
       <c r="AK11" t="n">
-        <v>-25</v>
+        <v>-0.2222222222222221</v>
       </c>
       <c r="AL11" t="n">
-        <v>-25.05217391304348</v>
-      </c>
-      <c r="AM11" t="inlineStr"/>
+        <v>-0.05555555555555558</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>7.576190476190476</v>
+      </c>
       <c r="AN11" t="n">
-        <v>-296.6825396825398</v>
+        <v>-6.815295815295816</v>
       </c>
       <c r="AO11" t="n">
-        <v>2.166666666666667</v>
+        <v>10.39966258300237</v>
       </c>
       <c r="AP11" t="n">
-        <v>-0.7428571428571427</v>
+        <v>-11.68271075329899</v>
       </c>
       <c r="AQ11" t="inlineStr"/>
-      <c r="AR11" t="n">
-        <v>0.25</v>
-      </c>
+      <c r="AR11" t="inlineStr"/>
       <c r="AS11" t="n">
-        <v>-5.333333333333334</v>
+        <v>505.8280759025849</v>
       </c>
       <c r="AT11" t="n">
-        <v>0.3304347826086982</v>
-      </c>
-      <c r="AU11" t="inlineStr"/>
+        <v>-472.2830291640987</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>5</v>
+      </c>
       <c r="AV11" t="n">
-        <v>8.346570588191877</v>
+        <v>-13</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.06493494966151531</v>
+        <v>-11.95294117647059</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.0441937315738896</v>
+        <v>11.02352941176471</v>
       </c>
       <c r="AY11" t="n">
-        <v>0.5</v>
+        <v>17</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.1956521739130435</v>
-      </c>
-      <c r="BA11" t="inlineStr"/>
-      <c r="BB11" t="inlineStr"/>
-      <c r="BC11" t="inlineStr"/>
-      <c r="BD11" t="inlineStr"/>
-      <c r="BE11" t="inlineStr"/>
-      <c r="BF11" t="inlineStr"/>
-      <c r="BG11" t="inlineStr"/>
-      <c r="BH11" t="inlineStr"/>
-      <c r="BI11" t="inlineStr"/>
-      <c r="BJ11" t="inlineStr"/>
+        <v>14</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>1.274509803921568</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>4.752941176470586</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>3.833333333333332</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>5.666666666666671</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>4.166666666666664</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>-4.166666666666664</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>-9.310457516339866</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>9.310457516339866</v>
+      </c>
       <c r="BK11" t="inlineStr"/>
       <c r="BL11" t="inlineStr"/>
-      <c r="BM11" t="inlineStr"/>
-      <c r="BN11" t="inlineStr"/>
-      <c r="BO11" t="inlineStr"/>
-      <c r="BP11" t="inlineStr"/>
-      <c r="BQ11" t="inlineStr"/>
-      <c r="BR11" t="inlineStr"/>
+      <c r="BM11" t="n">
+        <v>-124.0267857142857</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>86.03571428571428</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>-0.3333333333333335</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>0.2847222222222223</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>0.5694444444444446</v>
+      </c>
       <c r="BS11" t="inlineStr"/>
       <c r="BT11" t="inlineStr"/>
-      <c r="BU11" t="inlineStr"/>
-      <c r="BV11" t="inlineStr"/>
+      <c r="BU11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BV11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BW11" t="n">
+        <v>2.666666666666666</v>
+      </c>
+      <c r="BX11" t="n">
+        <v>2.166666666666668</v>
+      </c>
+      <c r="BY11" t="n">
+        <v>3.111111111111107</v>
+      </c>
+      <c r="BZ11" t="n">
+        <v>5.111111111111107</v>
+      </c>
+      <c r="CA11" t="inlineStr"/>
+      <c r="CB11" t="inlineStr"/>
+      <c r="CC11" t="n">
+        <v>3.359339009783454</v>
+      </c>
+      <c r="CD11" t="n">
+        <v>-3.66809184575258</v>
+      </c>
+      <c r="CE11" t="n">
+        <v>0.02115158636897768</v>
+      </c>
+      <c r="CF11" t="n">
+        <v>-0.04403131115459882</v>
+      </c>
+      <c r="CG11" t="n">
+        <v>-0.001002559179439241</v>
+      </c>
+      <c r="CH11" t="n">
+        <v>-0.02789839281873106</v>
+      </c>
+      <c r="CI11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ11" t="n">
+        <v>-0.3333333333333333</v>
+      </c>
+      <c r="CK11" t="n">
+        <v>0.2777777777777778</v>
+      </c>
+      <c r="CL11" t="n">
+        <v>-0.1111111111111111</v>
+      </c>
+      <c r="CM11" t="n">
+        <v>-0.06015151515150308</v>
+      </c>
+      <c r="CN11" t="inlineStr"/>
+      <c r="CO11" t="inlineStr"/>
+      <c r="CP11" t="inlineStr"/>
+      <c r="CQ11" t="inlineStr"/>
+      <c r="CR11" t="inlineStr"/>
+      <c r="CS11" t="inlineStr"/>
+      <c r="CT11" t="inlineStr"/>
+      <c r="CU11" t="inlineStr"/>
+      <c r="CV11" t="inlineStr"/>
+      <c r="CW11" t="inlineStr"/>
+      <c r="CX11" t="inlineStr"/>
+      <c r="CY11" t="inlineStr"/>
+      <c r="CZ11" t="inlineStr"/>
+      <c r="DA11" t="inlineStr"/>
+      <c r="DB11" t="inlineStr"/>
+      <c r="DC11" t="inlineStr"/>
+      <c r="DD11" t="inlineStr"/>
+      <c r="DE11" t="inlineStr"/>
+      <c r="DF11" t="inlineStr"/>
+      <c r="DG11" t="inlineStr"/>
+      <c r="DH11" t="inlineStr"/>
+      <c r="DI11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>rZUMHwAb</t>
+          <t>h8K6HUFF</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45571.5</v>
+        <v>45585.5</v>
       </c>
       <c r="C12" t="n">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="D12" t="n">
         <v>133</v>
       </c>
       <c r="E12" t="n">
-        <v>211</v>
+        <v>342</v>
       </c>
       <c r="F12" t="n">
-        <v>122</v>
+        <v>579</v>
       </c>
       <c r="G12" t="n">
         <v>55</v>
@@ -2684,169 +3937,296 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>128</v>
+        <v>272</v>
       </c>
       <c r="M12" t="n">
-        <v>204</v>
+        <v>234</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>0.8233333333333328</v>
+        <v>-0.2866666666666668</v>
       </c>
       <c r="P12" t="n">
-        <v>1.532606516290727</v>
+        <v>0.07833333333333359</v>
       </c>
       <c r="Q12" t="n">
-        <v>1</v>
+        <v>0.245625</v>
       </c>
       <c r="R12" t="n">
-        <v>2.077922077922078</v>
+        <v>-0.7668749999999998</v>
       </c>
       <c r="S12" t="n">
-        <v>6.333333333333332</v>
+        <v>0.5</v>
       </c>
       <c r="T12" t="n">
-        <v>4.831818181818182</v>
+        <v>-0.5</v>
       </c>
       <c r="U12" t="n">
-        <v>10.33333333333333</v>
+        <v>0.7647058823529411</v>
       </c>
       <c r="V12" t="n">
-        <v>12.10909090909091</v>
+        <v>-0.6470588235294118</v>
       </c>
       <c r="W12" t="n">
-        <v>1.333333333333333</v>
+        <v>-2.166666666666667</v>
       </c>
       <c r="X12" t="n">
-        <v>1.257575757575757</v>
+        <v>0.166666666666667</v>
       </c>
       <c r="Y12" t="n">
-        <v>2</v>
+        <v>0.867647058823529</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.097402597402597</v>
+        <v>-1.525735294117647</v>
       </c>
       <c r="AA12" t="n">
-        <v>12.8256253006253</v>
+        <v>-0.6666666666666661</v>
       </c>
       <c r="AB12" t="n">
-        <v>15.15757425466121</v>
+        <v>-2.5</v>
       </c>
       <c r="AC12" t="n">
-        <v>977.046065597882</v>
+        <v>1.992647058823529</v>
       </c>
       <c r="AD12" t="n">
-        <v>789.7665696532363</v>
+        <v>-4.926470588235293</v>
       </c>
       <c r="AE12" t="n">
-        <v>84.5</v>
+        <v>-0.8333333333333335</v>
       </c>
       <c r="AF12" t="n">
-        <v>46.4360902255639</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="AG12" t="n">
-        <v>22.5</v>
+        <v>0.5294117647058822</v>
       </c>
       <c r="AH12" t="n">
-        <v>34.63157894736842</v>
+        <v>-0.8823529411764706</v>
       </c>
       <c r="AI12" t="n">
-        <v>15</v>
+        <v>-0.8333333333333335</v>
       </c>
       <c r="AJ12" t="n">
-        <v>9.623376623376622</v>
+        <v>1.166666666666667</v>
       </c>
       <c r="AK12" t="n">
+        <v>0.9999999999999998</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>-0.9411764705882354</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>11.50512820512821</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>-11.14715608465609</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>10.90354699099958</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>-7.261091049527098</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>570.0346534653465</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>-567.0416666666666</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>437.2449444882971</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>-420.7210156827956</v>
+      </c>
+      <c r="AU12" t="n">
         <v>10</v>
       </c>
-      <c r="AL12" t="n">
-        <v>21.24545454545455</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>52</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>210.6888888888889</v>
-      </c>
-      <c r="AO12" t="n">
+      <c r="AV12" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>29.69166666666666</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>-5.995833333333337</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>24</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>20.7125</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>-4.899999999999999</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>4.333333333333336</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>-20.58823529411765</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>-26.47058823529412</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>-5.833333333333336</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>5.833333333333336</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>5.805147058823529</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>-5.805147058823529</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>-178</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>131</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>90.14285714285717</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>-6.508928571428555</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>0.8333333333333333</v>
+      </c>
+      <c r="BP12" t="n">
         <v>-1.333333333333333</v>
       </c>
-      <c r="AP12" t="n">
-        <v>0.2727272727272729</v>
-      </c>
-      <c r="AQ12" t="inlineStr"/>
-      <c r="AR12" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>-5.999999999999998</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>0.298701298701296</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>-13.4021645021645</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>-6.044117766739793</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>0.1489057239057239</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>0.0202282440576764</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>0.5627705627705628</v>
-      </c>
-      <c r="BA12" t="inlineStr"/>
-      <c r="BB12" t="inlineStr"/>
-      <c r="BC12" t="inlineStr"/>
-      <c r="BD12" t="inlineStr"/>
-      <c r="BE12" t="inlineStr"/>
-      <c r="BF12" t="inlineStr"/>
-      <c r="BG12" t="inlineStr"/>
-      <c r="BH12" t="inlineStr"/>
-      <c r="BI12" t="inlineStr"/>
-      <c r="BJ12" t="inlineStr"/>
-      <c r="BK12" t="inlineStr"/>
-      <c r="BL12" t="inlineStr"/>
-      <c r="BM12" t="inlineStr"/>
-      <c r="BN12" t="inlineStr"/>
-      <c r="BO12" t="inlineStr"/>
-      <c r="BP12" t="inlineStr"/>
-      <c r="BQ12" t="inlineStr"/>
-      <c r="BR12" t="inlineStr"/>
+      <c r="BQ12" t="n">
+        <v>-0.9916666666666667</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>0.3041666666666667</v>
+      </c>
       <c r="BS12" t="inlineStr"/>
       <c r="BT12" t="inlineStr"/>
-      <c r="BU12" t="inlineStr"/>
-      <c r="BV12" t="inlineStr"/>
+      <c r="BU12" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="BV12" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="BW12" t="n">
+        <v>6.666666666666666</v>
+      </c>
+      <c r="BX12" t="n">
+        <v>4.666666666666666</v>
+      </c>
+      <c r="BY12" t="n">
+        <v>4.117647058823529</v>
+      </c>
+      <c r="BZ12" t="n">
+        <v>5.764705882352942</v>
+      </c>
+      <c r="CA12" t="n">
+        <v>-32.53174603174602</v>
+      </c>
+      <c r="CB12" t="n">
+        <v>-9.350649350649352</v>
+      </c>
+      <c r="CC12" t="n">
+        <v>-2.783078009544985</v>
+      </c>
+      <c r="CD12" t="n">
+        <v>1.452384001430049</v>
+      </c>
+      <c r="CE12" t="n">
+        <v>0.03899419729206964</v>
+      </c>
+      <c r="CF12" t="n">
+        <v>-0.0517114162738266</v>
+      </c>
+      <c r="CG12" t="n">
+        <v>-0.02443249040090192</v>
+      </c>
+      <c r="CH12" t="n">
+        <v>-0.007921616824987272</v>
+      </c>
+      <c r="CI12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="CJ12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="CK12" t="n">
+        <v>0.2941176470588235</v>
+      </c>
+      <c r="CL12" t="n">
+        <v>0.05882352941176472</v>
+      </c>
+      <c r="CM12" t="n">
+        <v>-7.369191919191906</v>
+      </c>
+      <c r="CN12" t="inlineStr"/>
+      <c r="CO12" t="n">
+        <v>4.119552669552668</v>
+      </c>
+      <c r="CP12" t="n">
+        <v>-5.52950178476496</v>
+      </c>
+      <c r="CQ12" t="inlineStr"/>
+      <c r="CR12" t="inlineStr"/>
+      <c r="CS12" t="inlineStr"/>
+      <c r="CT12" t="inlineStr"/>
+      <c r="CU12" t="inlineStr"/>
+      <c r="CV12" t="n">
+        <v>-757402.9771398194</v>
+      </c>
+      <c r="CW12" t="inlineStr"/>
+      <c r="CX12" t="n">
+        <v>-5.746164654059399</v>
+      </c>
+      <c r="CY12" t="inlineStr"/>
+      <c r="CZ12" t="n">
+        <v>-0.2351826536037152</v>
+      </c>
+      <c r="DA12" t="inlineStr"/>
+      <c r="DB12" t="inlineStr"/>
+      <c r="DC12" t="inlineStr"/>
+      <c r="DD12" t="inlineStr"/>
+      <c r="DE12" t="inlineStr"/>
+      <c r="DF12" t="inlineStr"/>
+      <c r="DG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH12" t="inlineStr"/>
+      <c r="DI12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>WhWcJjo3</t>
+          <t>WMcg8Qx2</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45571.5</v>
+        <v>45585.5</v>
       </c>
       <c r="C13" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D13" t="n">
         <v>133</v>
       </c>
       <c r="E13" t="n">
-        <v>826</v>
+        <v>858</v>
       </c>
       <c r="F13" t="n">
-        <v>157</v>
+        <v>370</v>
       </c>
       <c r="G13" t="n">
         <v>55</v>
@@ -2868,171 +4248,288 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>35</v>
+        <v>165</v>
       </c>
       <c r="M13" t="n">
-        <v>234</v>
+        <v>37</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>1.5</v>
+        <v>0.1066666666666665</v>
       </c>
       <c r="P13" t="n">
-        <v>0.9404999999999997</v>
+        <v>-0.5166666666666665</v>
       </c>
       <c r="Q13" t="n">
-        <v>2</v>
+        <v>-0.1622039473684209</v>
       </c>
       <c r="R13" t="n">
-        <v>1.240909090909091</v>
+        <v>-0.06032894736842098</v>
       </c>
       <c r="S13" t="n">
-        <v>1.666666666666667</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="T13" t="n">
-        <v>1.140476190476191</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="U13" t="n">
-        <v>0.6666666666666679</v>
+        <v>0.05000000000000004</v>
       </c>
       <c r="V13" t="n">
-        <v>5.69761904761905</v>
+        <v>0.01249999999999996</v>
       </c>
       <c r="W13" t="n">
+        <v>-0.666666666666667</v>
+      </c>
+      <c r="X13" t="n">
+        <v>-3</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>-0.1375000000000002</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-0.1624999999999996</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0.3333333333333339</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>-6.666666666666668</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>0.5374999999999996</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>-2.8125</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>0.3333333333333335</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>-0.675</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>11.55787037037037</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>-6.496103896103896</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>10.48894446921972</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>-8.740371723864371</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>372.0416666666667</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>-570.0220440881764</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>475.4789564311403</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>-489.317151717499</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>36</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>5.936842105263167</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>3.171929824561403</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>10.51228070175438</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>-0.2947368421052587</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>5.333333333333336</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>2.333333333333332</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>5.799999999999997</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>0.8875000000000028</v>
+      </c>
+      <c r="BG13" t="n">
         <v>3</v>
       </c>
-      <c r="X13" t="n">
-        <v>0.3181818181818183</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>0.4363636363636365</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>20.9541847041847</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>18.72831971010709</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>1062.036649682667</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>805.5768135399308</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>37.39999999999999</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>-4</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>30.67105263157895</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>9.333333333333329</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>1.822727272727263</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>-5.999999999999993</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>12.0952380952381</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>-348</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>107.3040935672514</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>-0.338345864661654</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>-2.000000000000002</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>-1.227272727272727</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>3.172786690433753</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>-3.321614195664901</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>-0.06763903654885545</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>0.02955321374852892</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>0.2363636363636363</v>
-      </c>
-      <c r="BA13" t="inlineStr"/>
-      <c r="BB13" t="inlineStr"/>
-      <c r="BC13" t="inlineStr"/>
-      <c r="BD13" t="inlineStr"/>
-      <c r="BE13" t="inlineStr"/>
-      <c r="BF13" t="inlineStr"/>
-      <c r="BG13" t="inlineStr"/>
-      <c r="BH13" t="inlineStr"/>
-      <c r="BI13" t="inlineStr"/>
-      <c r="BJ13" t="inlineStr"/>
-      <c r="BK13" t="inlineStr"/>
-      <c r="BL13" t="inlineStr"/>
-      <c r="BM13" t="inlineStr"/>
-      <c r="BN13" t="inlineStr"/>
-      <c r="BO13" t="inlineStr"/>
-      <c r="BP13" t="inlineStr"/>
-      <c r="BQ13" t="inlineStr"/>
-      <c r="BR13" t="inlineStr"/>
-      <c r="BS13" t="inlineStr"/>
-      <c r="BT13" t="inlineStr"/>
-      <c r="BU13" t="inlineStr"/>
-      <c r="BV13" t="inlineStr"/>
+      <c r="BH13" t="n">
+        <v>-3</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>-3.512500000000003</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>3.512500000000003</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>71</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>83</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>-62.38888888888891</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>33.72222222222223</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>-0.333333333333333</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>-3.333333333333334</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>-0.2916666666666665</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>-0.5277777777777777</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="BT13" t="n">
+        <v>-0.1666666666666666</v>
+      </c>
+      <c r="BU13" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="BV13" t="n">
+        <v>-0.3333333333333334</v>
+      </c>
+      <c r="BW13" t="n">
+        <v>4.333333333333334</v>
+      </c>
+      <c r="BX13" t="n">
+        <v>-8.666666666666666</v>
+      </c>
+      <c r="BY13" t="n">
+        <v>0.1749999999999972</v>
+      </c>
+      <c r="BZ13" t="n">
+        <v>-9.325000000000003</v>
+      </c>
+      <c r="CA13" t="n">
+        <v>-43.57142857142858</v>
+      </c>
+      <c r="CB13" t="n">
+        <v>45.89285714285714</v>
+      </c>
+      <c r="CC13" t="n">
+        <v>-1.354529717010276</v>
+      </c>
+      <c r="CD13" t="n">
+        <v>3.543068832862286</v>
+      </c>
+      <c r="CE13" t="n">
+        <v>-0.05860488709310664</v>
+      </c>
+      <c r="CF13" t="n">
+        <v>-0.04919614519014369</v>
+      </c>
+      <c r="CG13" t="n">
+        <v>0.001149639935408113</v>
+      </c>
+      <c r="CH13" t="n">
+        <v>-0.03306673946694113</v>
+      </c>
+      <c r="CI13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ13" t="n">
+        <v>-0.6666666666666666</v>
+      </c>
+      <c r="CK13" t="n">
+        <v>-0.0625</v>
+      </c>
+      <c r="CL13" t="n">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="CM13" t="n">
+        <v>0.4784473523109938</v>
+      </c>
+      <c r="CN13" t="inlineStr"/>
+      <c r="CO13" t="inlineStr"/>
+      <c r="CP13" t="inlineStr"/>
+      <c r="CQ13" t="inlineStr"/>
+      <c r="CR13" t="inlineStr"/>
+      <c r="CS13" t="inlineStr"/>
+      <c r="CT13" t="inlineStr"/>
+      <c r="CU13" t="inlineStr"/>
+      <c r="CV13" t="inlineStr"/>
+      <c r="CW13" t="inlineStr"/>
+      <c r="CX13" t="inlineStr"/>
+      <c r="CY13" t="inlineStr"/>
+      <c r="CZ13" t="inlineStr"/>
+      <c r="DA13" t="inlineStr"/>
+      <c r="DB13" t="inlineStr"/>
+      <c r="DC13" t="inlineStr"/>
+      <c r="DD13" t="inlineStr"/>
+      <c r="DE13" t="inlineStr"/>
+      <c r="DF13" t="inlineStr"/>
+      <c r="DG13" t="inlineStr"/>
+      <c r="DH13" t="inlineStr"/>
+      <c r="DI13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>4nvCemgd</t>
+          <t>vPIEF8pS</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>45571.5</v>
+        <v>45585.5</v>
       </c>
       <c r="C14" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D14" t="n">
         <v>133</v>
       </c>
       <c r="E14" t="n">
-        <v>736</v>
+        <v>341</v>
       </c>
       <c r="F14" t="n">
-        <v>176</v>
+        <v>292</v>
       </c>
       <c r="G14" t="n">
         <v>55</v>
@@ -3054,169 +4551,276 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>312</v>
+        <v>243</v>
       </c>
       <c r="M14" t="n">
-        <v>163</v>
+        <v>32</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.1633333333333332</v>
+        <v>0.7266666666666667</v>
       </c>
       <c r="P14" t="n">
-        <v>0.2500238095238099</v>
+        <v>-0.4233333333333333</v>
       </c>
       <c r="Q14" t="n">
+        <v>0.2203308823529413</v>
+      </c>
+      <c r="R14" t="n">
+        <v>-0.3887132352941176</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="T14" t="n">
+        <v>-0.3333333333333334</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0.3205882352941178</v>
+      </c>
+      <c r="V14" t="n">
+        <v>-0.3852941176470588</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="X14" t="n">
+        <v>-2.333333333333333</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0.5882352941176472</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-0.6470588235294121</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0.3333333333333339</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>-5.333333333333334</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>2.117647058823529</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>-1.882352941176471</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>0.3333333333333335</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>-0.1411764705882352</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>0.1794117647058822</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>0.3333333333333334</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>-0.3764705882352941</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>0.3823529411764706</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>7.688888888888888</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>-4.532575757575757</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>8.542339724865677</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>-7.62633396015749</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>419.0307692307692</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>-432.0234541577825</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>460.7645967968647</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>-438.2959450123855</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>-22.5</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>11.8125</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>4.875</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>-6</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>7.875</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>-4.625</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>5.666666666666671</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>-10</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>28.93235294117647</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>25.5764705882353</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>5.666666666666664</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>-5.666666666666671</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>0.4117647058823479</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>-0.4117647058823479</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>88</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>-31</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>4.799999999999955</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>13.93333333333328</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>-1.333333333333333</v>
+      </c>
+      <c r="BQ14" t="n">
+        <v>0.9411764705882351</v>
+      </c>
+      <c r="BR14" t="n">
+        <v>-0.0588235294117645</v>
+      </c>
+      <c r="BS14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT14" t="n">
         <v>-1</v>
       </c>
-      <c r="R14" t="n">
-        <v>0.5785714285714285</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2.333333333333333</v>
-      </c>
-      <c r="T14" t="n">
-        <v>1.061904761904762</v>
-      </c>
-      <c r="U14" t="n">
-        <v>-1.666666666666666</v>
-      </c>
-      <c r="V14" t="n">
-        <v>0.6261904761904766</v>
-      </c>
-      <c r="W14" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="X14" t="n">
-        <v>0.1904761904761905</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>0.5785714285714285</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>19.12065897065897</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>20.24061302687353</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>947.0370781359841</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>962.6491064253298</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>3</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>-12.81578947368421</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>-12.5</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>-2.368421052631582</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>13.66666666666666</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>-0.2999999999999972</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>-2.666666666666657</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>-15.33333333333333</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>-135</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>-152.3567251461988</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>-0.6666666666666667</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>-0.8547619047619046</v>
-      </c>
-      <c r="AQ14" t="inlineStr"/>
-      <c r="AR14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>-8.333333333333334</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>-0.4880952380952408</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>17.4546783625731</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>5.217937060246109</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>-0.08528693528693526</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>-0.008239073080847904</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>-6000</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>-76</v>
-      </c>
-      <c r="BC14" t="inlineStr"/>
-      <c r="BD14" t="inlineStr"/>
-      <c r="BE14" t="inlineStr"/>
-      <c r="BF14" t="inlineStr"/>
-      <c r="BG14" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BH14" t="inlineStr"/>
-      <c r="BI14" t="n">
-        <v>-1400000</v>
-      </c>
-      <c r="BJ14" t="inlineStr"/>
-      <c r="BK14" t="inlineStr"/>
-      <c r="BL14" t="n">
-        <v>-64</v>
-      </c>
-      <c r="BM14" t="inlineStr"/>
-      <c r="BN14" t="inlineStr"/>
-      <c r="BO14" t="inlineStr"/>
-      <c r="BP14" t="inlineStr"/>
-      <c r="BQ14" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BR14" t="inlineStr"/>
-      <c r="BS14" t="inlineStr"/>
-      <c r="BT14" t="inlineStr"/>
-      <c r="BU14" t="inlineStr"/>
-      <c r="BV14" t="inlineStr"/>
+      <c r="BU14" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="BV14" t="n">
+        <v>-0.3333333333333334</v>
+      </c>
+      <c r="BW14" t="n">
+        <v>-3</v>
+      </c>
+      <c r="BX14" t="n">
+        <v>1.333333333333334</v>
+      </c>
+      <c r="BY14" t="n">
+        <v>10.88235294117647</v>
+      </c>
+      <c r="BZ14" t="n">
+        <v>4.944117647058825</v>
+      </c>
+      <c r="CA14" t="n">
+        <v>6.601503759398494</v>
+      </c>
+      <c r="CB14" t="n">
+        <v>11.27272727272727</v>
+      </c>
+      <c r="CC14" t="n">
+        <v>-1.571739150485717</v>
+      </c>
+      <c r="CD14" t="n">
+        <v>1.808255012982031</v>
+      </c>
+      <c r="CE14" t="n">
+        <v>-0.00359429303091275</v>
+      </c>
+      <c r="CF14" t="n">
+        <v>0.02424749163879598</v>
+      </c>
+      <c r="CG14" t="n">
+        <v>0.02081111118892805</v>
+      </c>
+      <c r="CH14" t="n">
+        <v>-0.0106483159014366</v>
+      </c>
+      <c r="CI14" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="CJ14" t="n">
+        <v>-0.3333333333333333</v>
+      </c>
+      <c r="CK14" t="n">
+        <v>0.08529411764705883</v>
+      </c>
+      <c r="CL14" t="n">
+        <v>-0.1558823529411765</v>
+      </c>
+      <c r="CM14" t="n">
+        <v>6.573720538720536</v>
+      </c>
+      <c r="CN14" t="inlineStr"/>
+      <c r="CO14" t="inlineStr"/>
+      <c r="CP14" t="inlineStr"/>
+      <c r="CQ14" t="inlineStr"/>
+      <c r="CR14" t="inlineStr"/>
+      <c r="CS14" t="inlineStr"/>
+      <c r="CT14" t="inlineStr"/>
+      <c r="CU14" t="inlineStr"/>
+      <c r="CV14" t="inlineStr"/>
+      <c r="CW14" t="inlineStr"/>
+      <c r="CX14" t="inlineStr"/>
+      <c r="CY14" t="inlineStr"/>
+      <c r="CZ14" t="inlineStr"/>
+      <c r="DA14" t="inlineStr"/>
+      <c r="DB14" t="inlineStr"/>
+      <c r="DC14" t="inlineStr"/>
+      <c r="DD14" t="inlineStr"/>
+      <c r="DE14" t="inlineStr"/>
+      <c r="DF14" t="inlineStr"/>
+      <c r="DG14" t="inlineStr"/>
+      <c r="DH14" t="inlineStr"/>
+      <c r="DI14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>IHSe3ve5</t>
+          <t>b9aoAn8k</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>45571.41666666666</v>
+        <v>45585.41666666666</v>
       </c>
       <c r="C15" t="n">
         <v>102</v>
@@ -3225,10 +4829,10 @@
         <v>133</v>
       </c>
       <c r="E15" t="n">
-        <v>56</v>
+        <v>194</v>
       </c>
       <c r="F15" t="n">
-        <v>599</v>
+        <v>39</v>
       </c>
       <c r="G15" t="n">
         <v>55</v>
@@ -3250,142 +4854,1395 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>152</v>
+        <v>9</v>
       </c>
       <c r="M15" t="n">
-        <v>226</v>
+        <v>141</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.1133333333333331</v>
+        <v>1.01</v>
       </c>
       <c r="P15" t="n">
-        <v>0.4725833333333327</v>
+        <v>1.44</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>0.1126249999999998</v>
       </c>
       <c r="R15" t="n">
-        <v>0.5357142857142858</v>
+        <v>0.02520833333333306</v>
       </c>
       <c r="S15" t="n">
-        <v>1.333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="T15" t="n">
-        <v>0.5749999999999997</v>
+        <v>0.5</v>
       </c>
       <c r="U15" t="n">
-        <v>0.6666666666666661</v>
+        <v>0.2430555555555556</v>
       </c>
       <c r="V15" t="n">
-        <v>1.741666666666665</v>
+        <v>-0.09027777777777768</v>
       </c>
       <c r="W15" t="n">
-        <v>-1.333333333333333</v>
+        <v>4</v>
       </c>
       <c r="X15" t="n">
-        <v>0.2499999999999998</v>
+        <v>2</v>
       </c>
       <c r="Y15" t="n">
-        <v>-2</v>
+        <v>0.454901960784313</v>
       </c>
       <c r="Z15" t="n">
-        <v>0.25</v>
+        <v>-0.4745098039215687</v>
       </c>
       <c r="AA15" t="n">
-        <v>15.57640692640693</v>
+        <v>8.5</v>
       </c>
       <c r="AB15" t="n">
-        <v>19.29995453130965</v>
-      </c>
-      <c r="AC15" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.494117647058824</v>
+      </c>
       <c r="AD15" t="n">
-        <v>843.9063364604394</v>
+        <v>-1.509803921568627</v>
       </c>
       <c r="AE15" t="n">
-        <v>39.5</v>
+        <v>0.5</v>
       </c>
       <c r="AF15" t="n">
-        <v>26.21739130434781</v>
+        <v>1.5</v>
       </c>
       <c r="AG15" t="n">
-        <v>22</v>
+        <v>-0.5416666666666667</v>
       </c>
       <c r="AH15" t="n">
-        <v>25.39588100686499</v>
+        <v>-0.00694444444444442</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="AJ15" t="n">
-        <v>8.541666666666671</v>
+        <v>1</v>
       </c>
       <c r="AK15" t="n">
-        <v>10</v>
+        <v>-0.8680555555555554</v>
       </c>
       <c r="AL15" t="n">
-        <v>13.78333333333333</v>
-      </c>
-      <c r="AM15" t="inlineStr"/>
+        <v>0.8611111111111112</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>4.162337662337662</v>
+      </c>
       <c r="AN15" t="n">
-        <v>127.2222222222222</v>
+        <v>-10.14166666666667</v>
       </c>
       <c r="AO15" t="n">
-        <v>-1.333333333333333</v>
+        <v>9.292785585873821</v>
       </c>
       <c r="AP15" t="n">
-        <v>-0.8581235697940504</v>
+        <v>-9.406338321121602</v>
       </c>
       <c r="AQ15" t="inlineStr"/>
-      <c r="AR15" t="n">
-        <v>0.9166666666666666</v>
-      </c>
+      <c r="AR15" t="inlineStr"/>
       <c r="AS15" t="n">
-        <v>6.333333333333334</v>
+        <v>488.7210407521562</v>
       </c>
       <c r="AT15" t="n">
-        <v>-9.624999999999996</v>
-      </c>
-      <c r="AU15" t="inlineStr"/>
+        <v>-497.4170454536711</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>-37</v>
+      </c>
       <c r="AV15" t="n">
-        <v>0.3886073861305288</v>
+        <v>-67</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.07928069062305482</v>
+        <v>-9.767857142857139</v>
       </c>
       <c r="AX15" t="n">
-        <v>0.03009688049080859</v>
+        <v>-2.053571428571431</v>
       </c>
       <c r="AY15" t="n">
-        <v>-0.3333333333333333</v>
+        <v>-8</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0.2202380952380953</v>
-      </c>
-      <c r="BA15" t="inlineStr"/>
-      <c r="BB15" t="inlineStr"/>
-      <c r="BC15" t="inlineStr"/>
-      <c r="BD15" t="inlineStr"/>
-      <c r="BE15" t="inlineStr"/>
-      <c r="BF15" t="inlineStr"/>
-      <c r="BG15" t="inlineStr"/>
-      <c r="BH15" t="inlineStr"/>
-      <c r="BI15" t="inlineStr"/>
-      <c r="BJ15" t="inlineStr"/>
+        <v>-41</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>-5.053571428571431</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>-9.642857142857146</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>-6</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>-16.5</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>1.222222222222221</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>-1.083333333333336</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>-7</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>7</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>-7.172549019607843</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>7.172549019607843</v>
+      </c>
       <c r="BK15" t="inlineStr"/>
       <c r="BL15" t="inlineStr"/>
-      <c r="BM15" t="inlineStr"/>
-      <c r="BN15" t="inlineStr"/>
-      <c r="BO15" t="inlineStr"/>
-      <c r="BP15" t="inlineStr"/>
-      <c r="BQ15" t="inlineStr"/>
-      <c r="BR15" t="inlineStr"/>
+      <c r="BM15" t="n">
+        <v>-88.25961538461536</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>52.34615384615387</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ15" t="n">
+        <v>0.6333333333333333</v>
+      </c>
+      <c r="BR15" t="n">
+        <v>0.02380952380952395</v>
+      </c>
       <c r="BS15" t="inlineStr"/>
       <c r="BT15" t="inlineStr"/>
-      <c r="BU15" t="inlineStr"/>
-      <c r="BV15" t="inlineStr"/>
+      <c r="BU15" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="BV15" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="BW15" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="BX15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BY15" t="n">
+        <v>0.05555555555555713</v>
+      </c>
+      <c r="BZ15" t="n">
+        <v>-3.618055555555557</v>
+      </c>
+      <c r="CA15" t="inlineStr"/>
+      <c r="CB15" t="inlineStr"/>
+      <c r="CC15" t="n">
+        <v>-0.04150228786468269</v>
+      </c>
+      <c r="CD15" t="n">
+        <v>-2.390922353384758</v>
+      </c>
+      <c r="CE15" t="n">
+        <v>0.05062724014336917</v>
+      </c>
+      <c r="CF15" t="n">
+        <v>0.07002096436058701</v>
+      </c>
+      <c r="CG15" t="n">
+        <v>0.006762084044263525</v>
+      </c>
+      <c r="CH15" t="n">
+        <v>0.009853599171512899</v>
+      </c>
+      <c r="CI15" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="CJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK15" t="n">
+        <v>-0.2083333333333333</v>
+      </c>
+      <c r="CL15" t="n">
+        <v>0.2708333333333334</v>
+      </c>
+      <c r="CM15" t="n">
+        <v>0.2746347402597422</v>
+      </c>
+      <c r="CN15" t="inlineStr"/>
+      <c r="CO15" t="inlineStr"/>
+      <c r="CP15" t="inlineStr"/>
+      <c r="CQ15" t="inlineStr"/>
+      <c r="CR15" t="inlineStr"/>
+      <c r="CS15" t="inlineStr"/>
+      <c r="CT15" t="inlineStr"/>
+      <c r="CU15" t="inlineStr"/>
+      <c r="CV15" t="inlineStr"/>
+      <c r="CW15" t="inlineStr"/>
+      <c r="CX15" t="inlineStr"/>
+      <c r="CY15" t="inlineStr"/>
+      <c r="CZ15" t="inlineStr"/>
+      <c r="DA15" t="inlineStr"/>
+      <c r="DB15" t="inlineStr"/>
+      <c r="DC15" t="inlineStr"/>
+      <c r="DD15" t="inlineStr"/>
+      <c r="DE15" t="inlineStr"/>
+      <c r="DF15" t="inlineStr"/>
+      <c r="DG15" t="inlineStr"/>
+      <c r="DH15" t="inlineStr"/>
+      <c r="DI15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>S2WzL3M7</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45584.66666666666</v>
+      </c>
+      <c r="C16" t="n">
+        <v>101</v>
+      </c>
+      <c r="D16" t="n">
+        <v>133</v>
+      </c>
+      <c r="E16" t="n">
+        <v>206</v>
+      </c>
+      <c r="F16" t="n">
+        <v>516</v>
+      </c>
+      <c r="G16" t="n">
+        <v>55</v>
+      </c>
+      <c r="H16" t="n">
+        <v>551</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="L16" t="n">
+        <v>193</v>
+      </c>
+      <c r="M16" t="n">
+        <v>83</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.7716666666666669</v>
+      </c>
+      <c r="P16" t="n">
+        <v>-1.475</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.7804024767801854</v>
+      </c>
+      <c r="R16" t="n">
+        <v>-0.5253560371517026</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2</v>
+      </c>
+      <c r="T16" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.157894736842105</v>
+      </c>
+      <c r="V16" t="n">
+        <v>-0.736842105263158</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="X16" t="n">
+        <v>-5.833333333333334</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>2.078947368421052</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>-0.8187134502923974</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>8.833333333333332</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>-9.833333333333332</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>5.55263157894737</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>-3.751461988304094</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>-2.833333333333333</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>1.157894736842105</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>-0.368421052631579</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>1.263157894736842</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>-1.105263157894737</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>9.727272727272727</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>-6.258333333333333</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>9.333897927770712</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>-7.581828016038542</v>
+      </c>
+      <c r="AQ16" t="inlineStr"/>
+      <c r="AR16" t="inlineStr"/>
+      <c r="AS16" t="n">
+        <v>411.1511681236645</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>-350.7346896426638</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>66</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>-42.5</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>48.2091503267974</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>-28.00980392156862</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>44</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>-42</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>31.56535947712418</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>-17.71568627450981</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>4.333333333333336</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>-7.666666666666668</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>3.052631578947366</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>-7.684210526315788</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>22.66666666666667</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>-22.66666666666666</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>18.66666666666666</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>-18.66666666666666</v>
+      </c>
+      <c r="BK16" t="inlineStr"/>
+      <c r="BL16" t="inlineStr"/>
+      <c r="BM16" t="n">
+        <v>257.9191176470588</v>
+      </c>
+      <c r="BN16" t="n">
+        <v>-116.9558823529412</v>
+      </c>
+      <c r="BO16" t="n">
+        <v>-0.6666666666666667</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>0.8333333333333335</v>
+      </c>
+      <c r="BQ16" t="n">
+        <v>-0.3194444444444444</v>
+      </c>
+      <c r="BR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS16" t="inlineStr"/>
+      <c r="BT16" t="inlineStr"/>
+      <c r="BU16" t="inlineStr"/>
+      <c r="BV16" t="inlineStr"/>
+      <c r="BW16" t="n">
+        <v>1.833333333333334</v>
+      </c>
+      <c r="BX16" t="n">
+        <v>-1.166666666666668</v>
+      </c>
+      <c r="BY16" t="n">
+        <v>-2.105263157894733</v>
+      </c>
+      <c r="BZ16" t="n">
+        <v>5.842105263157897</v>
+      </c>
+      <c r="CA16" t="inlineStr"/>
+      <c r="CB16" t="inlineStr"/>
+      <c r="CC16" t="n">
+        <v>-0.849337259451902</v>
+      </c>
+      <c r="CD16" t="n">
+        <v>6.137027258442622</v>
+      </c>
+      <c r="CE16" t="n">
+        <v>-0.008910533910533897</v>
+      </c>
+      <c r="CF16" t="n">
+        <v>-0.059009009009009</v>
+      </c>
+      <c r="CG16" t="n">
+        <v>0.01848478049114897</v>
+      </c>
+      <c r="CH16" t="n">
+        <v>-0.006724680424551301</v>
+      </c>
+      <c r="CI16" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="CJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK16" t="n">
+        <v>0.1052631578947368</v>
+      </c>
+      <c r="CL16" t="n">
+        <v>-0.1578947368421053</v>
+      </c>
+      <c r="CM16" t="n">
+        <v>0.1266478891478897</v>
+      </c>
+      <c r="CN16" t="inlineStr"/>
+      <c r="CO16" t="inlineStr"/>
+      <c r="CP16" t="inlineStr"/>
+      <c r="CQ16" t="inlineStr"/>
+      <c r="CR16" t="inlineStr"/>
+      <c r="CS16" t="inlineStr"/>
+      <c r="CT16" t="inlineStr"/>
+      <c r="CU16" t="inlineStr"/>
+      <c r="CV16" t="inlineStr"/>
+      <c r="CW16" t="inlineStr"/>
+      <c r="CX16" t="inlineStr"/>
+      <c r="CY16" t="inlineStr"/>
+      <c r="CZ16" t="inlineStr"/>
+      <c r="DA16" t="inlineStr"/>
+      <c r="DB16" t="inlineStr"/>
+      <c r="DC16" t="inlineStr"/>
+      <c r="DD16" t="inlineStr"/>
+      <c r="DE16" t="inlineStr"/>
+      <c r="DF16" t="inlineStr"/>
+      <c r="DG16" t="inlineStr"/>
+      <c r="DH16" t="inlineStr"/>
+      <c r="DI16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>OAZJOoNr</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45584.58333333334</v>
+      </c>
+      <c r="C17" t="n">
+        <v>103</v>
+      </c>
+      <c r="D17" t="n">
+        <v>133</v>
+      </c>
+      <c r="E17" t="n">
+        <v>528</v>
+      </c>
+      <c r="F17" t="n">
+        <v>176</v>
+      </c>
+      <c r="G17" t="n">
+        <v>55</v>
+      </c>
+      <c r="H17" t="n">
+        <v>551</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
+        <v>272</v>
+      </c>
+      <c r="M17" t="n">
+        <v>83</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.3300000000000001</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0.09999999999999987</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.2209210526315788</v>
+      </c>
+      <c r="R17" t="n">
+        <v>-0.2493749999999999</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0.5249999999999999</v>
+      </c>
+      <c r="V17" t="n">
+        <v>-0.375</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="X17" t="n">
+        <v>-0.666666666666667</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0.7532894736842106</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>-0.5559210526315788</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>2.333333333333332</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>2.069078947368421</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0.09210526315789558</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>-0.3333333333333333</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>0.2124999999999999</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>-0.02500000000000002</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>0.5249999999999999</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>-0.1875</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>9.187749287749288</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>-12.23322510822511</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>10.55953111216269</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>-10.17164467476968</v>
+      </c>
+      <c r="AQ17" t="inlineStr"/>
+      <c r="AR17" t="inlineStr"/>
+      <c r="AS17" t="n">
+        <v>486.4973203477294</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>-413.6211560597191</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>22</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>-16.92063492063491</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>-10.98412698412699</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>8.428571428571431</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>5.031746031746032</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>-5.666666666666671</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>-21.4625</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>-23.8875</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>-11.33333333333334</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>11.33333333333334</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>-3.64473684210526</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>3.64473684210526</v>
+      </c>
+      <c r="BK17" t="inlineStr"/>
+      <c r="BL17" t="inlineStr"/>
+      <c r="BM17" t="n">
+        <v>-43.7194570135747</v>
+      </c>
+      <c r="BN17" t="n">
+        <v>18.89140271493216</v>
+      </c>
+      <c r="BO17" t="n">
+        <v>-1.666666666666667</v>
+      </c>
+      <c r="BP17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ17" t="n">
+        <v>-0.6458333333333335</v>
+      </c>
+      <c r="BR17" t="n">
+        <v>-0.1041666666666667</v>
+      </c>
+      <c r="BS17" t="inlineStr"/>
+      <c r="BT17" t="inlineStr"/>
+      <c r="BU17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV17" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="BW17" t="n">
+        <v>-8.666666666666666</v>
+      </c>
+      <c r="BX17" t="n">
+        <v>-4.333333333333332</v>
+      </c>
+      <c r="BY17" t="n">
+        <v>1.662500000000001</v>
+      </c>
+      <c r="BZ17" t="n">
+        <v>-1.137500000000003</v>
+      </c>
+      <c r="CA17" t="inlineStr"/>
+      <c r="CB17" t="inlineStr"/>
+      <c r="CC17" t="n">
+        <v>2.105403936099762</v>
+      </c>
+      <c r="CD17" t="n">
+        <v>-0.6085766224868099</v>
+      </c>
+      <c r="CE17" t="n">
+        <v>-0.01509750412189437</v>
+      </c>
+      <c r="CF17" t="n">
+        <v>0.0001613111369208886</v>
+      </c>
+      <c r="CG17" t="n">
+        <v>-0.006438656243849317</v>
+      </c>
+      <c r="CH17" t="n">
+        <v>-0.0004009730058165198</v>
+      </c>
+      <c r="CI17" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="CJ17" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="CK17" t="n">
+        <v>-0.03749999999999998</v>
+      </c>
+      <c r="CL17" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="CM17" t="n">
+        <v>-5.003814935064923</v>
+      </c>
+      <c r="CN17" t="inlineStr"/>
+      <c r="CO17" t="inlineStr"/>
+      <c r="CP17" t="inlineStr"/>
+      <c r="CQ17" t="inlineStr"/>
+      <c r="CR17" t="inlineStr"/>
+      <c r="CS17" t="inlineStr"/>
+      <c r="CT17" t="inlineStr"/>
+      <c r="CU17" t="inlineStr"/>
+      <c r="CV17" t="inlineStr"/>
+      <c r="CW17" t="inlineStr"/>
+      <c r="CX17" t="inlineStr"/>
+      <c r="CY17" t="inlineStr"/>
+      <c r="CZ17" t="inlineStr"/>
+      <c r="DA17" t="inlineStr"/>
+      <c r="DB17" t="inlineStr"/>
+      <c r="DC17" t="inlineStr"/>
+      <c r="DD17" t="inlineStr"/>
+      <c r="DE17" t="inlineStr"/>
+      <c r="DF17" t="inlineStr"/>
+      <c r="DG17" t="inlineStr"/>
+      <c r="DH17" t="inlineStr"/>
+      <c r="DI17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>WzwSMPie</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45584.5</v>
+      </c>
+      <c r="C18" t="n">
+        <v>102</v>
+      </c>
+      <c r="D18" t="n">
+        <v>133</v>
+      </c>
+      <c r="E18" t="n">
+        <v>211</v>
+      </c>
+      <c r="F18" t="n">
+        <v>399</v>
+      </c>
+      <c r="G18" t="n">
+        <v>55</v>
+      </c>
+      <c r="H18" t="n">
+        <v>551</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="L18" t="n">
+        <v>9</v>
+      </c>
+      <c r="M18" t="n">
+        <v>60</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.3533333333333333</v>
+      </c>
+      <c r="P18" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.1722222222222223</v>
+      </c>
+      <c r="R18" t="n">
+        <v>-0.4071527777777777</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="T18" t="n">
+        <v>-0.3333333333333335</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0.1333333333333333</v>
+      </c>
+      <c r="V18" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0.666666666666667</v>
+      </c>
+      <c r="X18" t="n">
+        <v>-6.333333333333334</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0.3343653250773997</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>-1.718266253869969</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>-4.333333333333332</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.588235294117647</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>-1.953560371517028</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>-2.666666666666667</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>0.1166666666666667</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>-0.5111111111111111</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>0.5944444444444443</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>-0.7222222222222222</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>10.99242424242424</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>-9.627946127946128</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>10.67861941373141</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>-8.248999976631556</v>
+      </c>
+      <c r="AQ18" t="inlineStr"/>
+      <c r="AR18" t="inlineStr"/>
+      <c r="AS18" t="n">
+        <v>454.7815894144367</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>-391.7421059894216</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>-25.5</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>17</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>19.93333333333334</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>-3.911111111111111</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>3.344444444444449</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>-10.01111111111111</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>5.666666666666671</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>-1.50555555555556</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>5.666666666666664</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>-5.666666666666664</v>
+      </c>
+      <c r="BI18" t="n">
+        <v>5.996904024767801</v>
+      </c>
+      <c r="BJ18" t="n">
+        <v>-5.996904024767801</v>
+      </c>
+      <c r="BK18" t="inlineStr"/>
+      <c r="BL18" t="inlineStr"/>
+      <c r="BM18" t="n">
+        <v>60.04464285714289</v>
+      </c>
+      <c r="BN18" t="n">
+        <v>-61.42857142857144</v>
+      </c>
+      <c r="BO18" t="n">
+        <v>-1.333333333333333</v>
+      </c>
+      <c r="BP18" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="BQ18" t="n">
+        <v>0.1362229102167181</v>
+      </c>
+      <c r="BR18" t="n">
+        <v>-0.1424148606811146</v>
+      </c>
+      <c r="BS18" t="inlineStr"/>
+      <c r="BT18" t="inlineStr"/>
+      <c r="BU18" t="n">
+        <v>0.06666666666666665</v>
+      </c>
+      <c r="BV18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW18" t="n">
+        <v>-0.3333333333333321</v>
+      </c>
+      <c r="BX18" t="n">
+        <v>9.333333333333334</v>
+      </c>
+      <c r="BY18" t="n">
+        <v>-3.62222222222222</v>
+      </c>
+      <c r="BZ18" t="n">
+        <v>0.6388888888888857</v>
+      </c>
+      <c r="CA18" t="inlineStr"/>
+      <c r="CB18" t="inlineStr"/>
+      <c r="CC18" t="n">
+        <v>-0.3056074425732227</v>
+      </c>
+      <c r="CD18" t="n">
+        <v>1.504467570693496</v>
+      </c>
+      <c r="CE18" t="n">
+        <v>-0.1261904761904762</v>
+      </c>
+      <c r="CF18" t="n">
+        <v>0.06563307493540051</v>
+      </c>
+      <c r="CG18" t="n">
+        <v>0.004140809268385129</v>
+      </c>
+      <c r="CH18" t="n">
+        <v>-0.001730423466328145</v>
+      </c>
+      <c r="CI18" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK18" t="n">
+        <v>0.4111111111111111</v>
+      </c>
+      <c r="CL18" t="n">
+        <v>-0.1333333333333333</v>
+      </c>
+      <c r="CM18" t="n">
+        <v>0.8760541927208578</v>
+      </c>
+      <c r="CN18" t="inlineStr"/>
+      <c r="CO18" t="inlineStr"/>
+      <c r="CP18" t="inlineStr"/>
+      <c r="CQ18" t="inlineStr"/>
+      <c r="CR18" t="inlineStr"/>
+      <c r="CS18" t="inlineStr"/>
+      <c r="CT18" t="inlineStr"/>
+      <c r="CU18" t="inlineStr"/>
+      <c r="CV18" t="inlineStr"/>
+      <c r="CW18" t="inlineStr"/>
+      <c r="CX18" t="inlineStr"/>
+      <c r="CY18" t="inlineStr"/>
+      <c r="CZ18" t="inlineStr"/>
+      <c r="DA18" t="inlineStr"/>
+      <c r="DB18" t="inlineStr"/>
+      <c r="DC18" t="inlineStr"/>
+      <c r="DD18" t="inlineStr"/>
+      <c r="DE18" t="inlineStr"/>
+      <c r="DF18" t="inlineStr"/>
+      <c r="DG18" t="inlineStr"/>
+      <c r="DH18" t="inlineStr"/>
+      <c r="DI18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>vwbmU7aL</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45583.65625</v>
+      </c>
+      <c r="C19" t="n">
+        <v>102</v>
+      </c>
+      <c r="D19" t="n">
+        <v>133</v>
+      </c>
+      <c r="E19" t="n">
+        <v>47</v>
+      </c>
+      <c r="F19" t="n">
+        <v>545</v>
+      </c>
+      <c r="G19" t="n">
+        <v>55</v>
+      </c>
+      <c r="H19" t="n">
+        <v>551</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="L19" t="n">
+        <v>249</v>
+      </c>
+      <c r="M19" t="n">
+        <v>127</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>-0.7383333333333333</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0.1083333333333334</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0.5531250000000001</v>
+      </c>
+      <c r="R19" t="n">
+        <v>-0.2531249999999999</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0.5698529411764706</v>
+      </c>
+      <c r="V19" t="n">
+        <v>-0.3676470588235294</v>
+      </c>
+      <c r="W19" t="n">
+        <v>-2.333333333333333</v>
+      </c>
+      <c r="X19" t="n">
+        <v>-1.166666666666667</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.639705882352941</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>-0.4227941176470589</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>-1.833333333333334</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.166666666666666</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>4.172794117647058</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>-0.8860294117647065</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>0.5661764705882353</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>-0.06985294117647056</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>0.8333333333333335</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>-1.166666666666667</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>0.4669117647058822</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>-0.4816176470588236</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>15.20634920634921</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>-7.838095238095239</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>10.87881564364036</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>-8.324588994596734</v>
+      </c>
+      <c r="AQ19" t="inlineStr"/>
+      <c r="AR19" t="inlineStr"/>
+      <c r="AS19" t="n">
+        <v>550.0999835594115</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>-395.7255654370691</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>-53</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>14.24107142857143</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>1.160714285714292</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>-37</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>6.705357142857146</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>-1.348214285714285</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>16.83333333333334</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>3.333333333333336</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>4.422794117647058</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>6.411764705882351</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>-3.833333333333336</v>
+      </c>
+      <c r="BH19" t="n">
+        <v>3.833333333333336</v>
+      </c>
+      <c r="BI19" t="n">
+        <v>-3.735294117647058</v>
+      </c>
+      <c r="BJ19" t="n">
+        <v>3.735294117647058</v>
+      </c>
+      <c r="BK19" t="inlineStr"/>
+      <c r="BL19" t="inlineStr"/>
+      <c r="BM19" t="n">
+        <v>-58.19230769230768</v>
+      </c>
+      <c r="BN19" t="n">
+        <v>36.94230769230768</v>
+      </c>
+      <c r="BO19" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP19" t="n">
+        <v>1.833333333333333</v>
+      </c>
+      <c r="BQ19" t="n">
+        <v>0.411764705882353</v>
+      </c>
+      <c r="BR19" t="n">
+        <v>0.2078431372549021</v>
+      </c>
+      <c r="BS19" t="inlineStr"/>
+      <c r="BT19" t="inlineStr"/>
+      <c r="BU19" t="n">
+        <v>-0.09999999999999998</v>
+      </c>
+      <c r="BV19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BW19" t="n">
+        <v>4.333333333333332</v>
+      </c>
+      <c r="BX19" t="n">
+        <v>8</v>
+      </c>
+      <c r="BY19" t="n">
+        <v>9.356617647058826</v>
+      </c>
+      <c r="BZ19" t="n">
+        <v>-3.860294117647058</v>
+      </c>
+      <c r="CA19" t="inlineStr"/>
+      <c r="CB19" t="inlineStr"/>
+      <c r="CC19" t="n">
+        <v>-2.505651327915452</v>
+      </c>
+      <c r="CD19" t="n">
+        <v>-3.287719499264897</v>
+      </c>
+      <c r="CE19" t="n">
+        <v>-0.02529358626919602</v>
+      </c>
+      <c r="CF19" t="n">
+        <v>0.03595997498436523</v>
+      </c>
+      <c r="CG19" t="n">
+        <v>-0.003458401694340994</v>
+      </c>
+      <c r="CH19" t="n">
+        <v>0.008415766432708645</v>
+      </c>
+      <c r="CI19" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="CJ19" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="CK19" t="n">
+        <v>-0.03308823529411764</v>
+      </c>
+      <c r="CL19" t="n">
+        <v>-0.1691176470588235</v>
+      </c>
+      <c r="CM19" t="n">
+        <v>-0.6024915824915809</v>
+      </c>
+      <c r="CN19" t="inlineStr"/>
+      <c r="CO19" t="inlineStr"/>
+      <c r="CP19" t="inlineStr"/>
+      <c r="CQ19" t="inlineStr"/>
+      <c r="CR19" t="inlineStr"/>
+      <c r="CS19" t="inlineStr"/>
+      <c r="CT19" t="inlineStr"/>
+      <c r="CU19" t="inlineStr"/>
+      <c r="CV19" t="inlineStr"/>
+      <c r="CW19" t="inlineStr"/>
+      <c r="CX19" t="inlineStr"/>
+      <c r="CY19" t="inlineStr"/>
+      <c r="CZ19" t="inlineStr"/>
+      <c r="DA19" t="inlineStr"/>
+      <c r="DB19" t="inlineStr"/>
+      <c r="DC19" t="inlineStr"/>
+      <c r="DD19" t="inlineStr"/>
+      <c r="DE19" t="inlineStr"/>
+      <c r="DF19" t="inlineStr"/>
+      <c r="DG19" t="inlineStr"/>
+      <c r="DH19" t="inlineStr"/>
+      <c r="DI19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/france/p6_deployment/data_preparation/df_tagged.xlsx
+++ b/data/france/p6_deployment/data_preparation/df_tagged.xlsx
@@ -885,112 +885,112 @@
       </c>
       <c r="CN1" s="1" t="inlineStr">
         <is>
+          <t>dif_sum_value_player_miss</t>
+        </is>
+      </c>
+      <c r="CO1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_value_player_sub</t>
+        </is>
+      </c>
+      <c r="CP1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_sub</t>
+        </is>
+      </c>
+      <c r="CQ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_rep_player_miss</t>
+        </is>
+      </c>
+      <c r="CR1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_sub</t>
+        </is>
+      </c>
+      <c r="CS1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_age_player_start</t>
         </is>
       </c>
-      <c r="CO1" s="1" t="inlineStr">
+      <c r="CT1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_miss</t>
+        </is>
+      </c>
+      <c r="CU1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_miss</t>
+        </is>
+      </c>
+      <c r="CV1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_pot_player_miss</t>
+        </is>
+      </c>
+      <c r="CW1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_wage_player_sub</t>
+        </is>
+      </c>
+      <c r="CX1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rep_player_start</t>
+        </is>
+      </c>
+      <c r="CY1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_start</t>
+        </is>
+      </c>
+      <c r="CZ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_wage_player_miss</t>
+        </is>
+      </c>
+      <c r="DA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_value_player_start</t>
+        </is>
+      </c>
+      <c r="DB1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_age_player_sub</t>
         </is>
       </c>
-      <c r="CP1" s="1" t="inlineStr">
+      <c r="DC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_wage_player_start</t>
+        </is>
+      </c>
+      <c r="DD1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_rat_player_miss</t>
+        </is>
+      </c>
+      <c r="DE1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rep_player_sub</t>
+        </is>
+      </c>
+      <c r="DF1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_start</t>
+        </is>
+      </c>
+      <c r="DG1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_hei_player_sub</t>
         </is>
       </c>
-      <c r="CQ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_value_player_miss</t>
-        </is>
-      </c>
-      <c r="CR1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rep_player_start</t>
-        </is>
-      </c>
-      <c r="CS1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_miss</t>
-        </is>
-      </c>
-      <c r="CT1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_rat_player_miss</t>
-        </is>
-      </c>
-      <c r="CU1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_start</t>
-        </is>
-      </c>
-      <c r="CV1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_value_player_sub</t>
-        </is>
-      </c>
-      <c r="CW1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_wage_player_miss</t>
-        </is>
-      </c>
-      <c r="CX1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_sub</t>
-        </is>
-      </c>
-      <c r="CY1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_miss</t>
-        </is>
-      </c>
-      <c r="CZ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_sub</t>
-        </is>
-      </c>
-      <c r="DA1" s="1" t="inlineStr">
+      <c r="DH1" s="1" t="inlineStr">
         <is>
           <t>dif_n_player_miss</t>
         </is>
       </c>
-      <c r="DB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_rep_player_miss</t>
-        </is>
-      </c>
-      <c r="DC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_start</t>
-        </is>
-      </c>
-      <c r="DD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_pot_player_miss</t>
-        </is>
-      </c>
-      <c r="DE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_wage_player_start</t>
-        </is>
-      </c>
-      <c r="DF1" s="1" t="inlineStr">
+      <c r="DI1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_pot_player_start</t>
-        </is>
-      </c>
-      <c r="DG1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rep_player_sub</t>
-        </is>
-      </c>
-      <c r="DH1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_wage_player_sub</t>
-        </is>
-      </c>
-      <c r="DI1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_value_player_start</t>
         </is>
       </c>
     </row>
@@ -3263,51 +3263,51 @@
       <c r="CM9" t="n">
         <v>-0.2854090354090459</v>
       </c>
-      <c r="CN9" t="n">
-        <v>-0.1381944444444443</v>
-      </c>
+      <c r="CN9" t="inlineStr"/>
       <c r="CO9" t="n">
-        <v>0.4695134114251758</v>
+        <v>-574442.438866192</v>
       </c>
       <c r="CP9" t="n">
-        <v>-0.267136241848533</v>
+        <v>-2.072122162435463</v>
       </c>
       <c r="CQ9" t="inlineStr"/>
       <c r="CR9" t="n">
-        <v>0</v>
-      </c>
-      <c r="CS9" t="inlineStr"/>
+        <v>-1.647934081405936</v>
+      </c>
+      <c r="CS9" t="n">
+        <v>-0.1381944444444443</v>
+      </c>
       <c r="CT9" t="inlineStr"/>
-      <c r="CU9" t="n">
-        <v>-2.306944444444454</v>
-      </c>
-      <c r="CV9" t="n">
-        <v>-574442.438866192</v>
-      </c>
+      <c r="CU9" t="inlineStr"/>
+      <c r="CV9" t="inlineStr"/>
       <c r="CW9" t="inlineStr"/>
       <c r="CX9" t="n">
-        <v>-1.647934081405936</v>
-      </c>
-      <c r="CY9" t="inlineStr"/>
-      <c r="CZ9" t="n">
-        <v>-2.072122162435463</v>
-      </c>
-      <c r="DA9" t="inlineStr"/>
-      <c r="DB9" t="inlineStr"/>
-      <c r="DC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY9" t="n">
+        <v>-2.306944444444454</v>
+      </c>
+      <c r="CZ9" t="inlineStr"/>
+      <c r="DA9" t="n">
+        <v>-654722.2222222222</v>
+      </c>
+      <c r="DB9" t="n">
+        <v>0.4695134114251758</v>
+      </c>
+      <c r="DC9" t="inlineStr"/>
+      <c r="DD9" t="inlineStr"/>
+      <c r="DE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF9" t="n">
         <v>0.5722222222221944</v>
       </c>
-      <c r="DD9" t="inlineStr"/>
-      <c r="DE9" t="inlineStr"/>
-      <c r="DF9" t="n">
-        <v>-1.364583333333343</v>
-      </c>
       <c r="DG9" t="n">
-        <v>0</v>
+        <v>-0.267136241848533</v>
       </c>
       <c r="DH9" t="inlineStr"/>
       <c r="DI9" t="n">
-        <v>-654722.2222222222</v>
+        <v>-1.364583333333343</v>
       </c>
     </row>
     <row r="10">
@@ -4174,35 +4174,35 @@
       </c>
       <c r="CN12" t="inlineStr"/>
       <c r="CO12" t="n">
-        <v>4.119552669552668</v>
+        <v>-757402.9771398194</v>
       </c>
       <c r="CP12" t="n">
-        <v>-5.52950178476496</v>
+        <v>-0.2351826536037152</v>
       </c>
       <c r="CQ12" t="inlineStr"/>
-      <c r="CR12" t="inlineStr"/>
+      <c r="CR12" t="n">
+        <v>-5.746164654059399</v>
+      </c>
       <c r="CS12" t="inlineStr"/>
       <c r="CT12" t="inlineStr"/>
       <c r="CU12" t="inlineStr"/>
-      <c r="CV12" t="n">
-        <v>-757402.9771398194</v>
-      </c>
+      <c r="CV12" t="inlineStr"/>
       <c r="CW12" t="inlineStr"/>
-      <c r="CX12" t="n">
-        <v>-5.746164654059399</v>
-      </c>
+      <c r="CX12" t="inlineStr"/>
       <c r="CY12" t="inlineStr"/>
-      <c r="CZ12" t="n">
-        <v>-0.2351826536037152</v>
-      </c>
+      <c r="CZ12" t="inlineStr"/>
       <c r="DA12" t="inlineStr"/>
-      <c r="DB12" t="inlineStr"/>
+      <c r="DB12" t="n">
+        <v>4.119552669552668</v>
+      </c>
       <c r="DC12" t="inlineStr"/>
       <c r="DD12" t="inlineStr"/>
-      <c r="DE12" t="inlineStr"/>
+      <c r="DE12" t="n">
+        <v>0</v>
+      </c>
       <c r="DF12" t="inlineStr"/>
       <c r="DG12" t="n">
-        <v>0</v>
+        <v>-5.52950178476496</v>
       </c>
       <c r="DH12" t="inlineStr"/>
       <c r="DI12" t="inlineStr"/>

--- a/data/france/p6_deployment/data_preparation/df_tagged.xlsx
+++ b/data/france/p6_deployment/data_preparation/df_tagged.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DI19"/>
+  <dimension ref="A1:BV19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -505,492 +505,297 @@
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_60_matches_expected_goals_(xg)_against</t>
+          <t>dif_mean_last_360_matches_expected_goals_(xg)</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_360_matches_expected_goals_(xg)</t>
+          <t>dif_mean_last_60_matches_expected_points</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_360_matches_expected_goals_(xg)_against</t>
+          <t>dif_mean_last_360_matches_expected_points</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_60_matches_expected_points</t>
+          <t>dif_mean_last_60_matches_shots_on_goal</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_60_matches_expected_points_against</t>
+          <t>dif_mean_last_360_matches_shots_on_goal</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_360_matches_expected_points</t>
+          <t>dif_mean_last_60_matches_goal_attempts</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_360_matches_expected_points_against</t>
+          <t>dif_mean_last_360_matches_goal_attempts</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_60_matches_shots_on_goal</t>
+          <t>dif_mean_last_60_matches_goals</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_60_matches_shots_on_goal_against</t>
+          <t>dif_mean_last_360_matches_goals</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_360_matches_shots_on_goal</t>
+          <t>dif_mean_last_60_matches_points</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_360_matches_shots_on_goal_against</t>
+          <t>dif_mean_last_360_matches_points</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_60_matches_goal_attempts</t>
+          <t>dif_mean_last_60_matches_goal_ratio</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_60_matches_goal_attempts_against</t>
+          <t>dif_mean_last_360_matches_goal_ratio</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_360_matches_goal_attempts</t>
+          <t>dif_mean_last_60_matches_PPS</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_360_matches_goal_attempts_against</t>
+          <t>dif_mean_last_360_matches_PPS</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_60_matches_goals</t>
+          <t>dif_mean_last_60_matches_attacks</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_60_matches_goals_against</t>
+          <t>dif_mean_last_360_matches_attacks</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_360_matches_goals</t>
+          <t>dif_mean_last_60_matches_dangerous_attacks</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_360_matches_goals_against</t>
+          <t>dif_mean_last_360_matches_dangerous_attacks</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_60_matches_points</t>
+          <t>dif_mean_last_60_matches_dead_balls</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_60_matches_points_against</t>
+          <t>dif_mean_last_360_matches_dead_balls</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_360_matches_points</t>
+          <t>dif_mean_last_60_matches_ball_possession</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_360_matches_points_against</t>
+          <t>dif_mean_last_360_matches_ball_possession</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_60_matches_goal_ratio</t>
+          <t>dif_mean_last_60_matches_total_passes</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_60_matches_goal_ratio_against</t>
+          <t>dif_mean_last_360_matches_total_passes</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_360_matches_goal_ratio</t>
+          <t>dif_mean_last_60_matches_yellow_cards</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_360_matches_goal_ratio_against</t>
+          <t>dif_mean_last_360_matches_yellow_cards</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_60_matches_PPS</t>
+          <t>dif_mean_last_60_matches_red_cards</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_60_matches_PPS_against</t>
+          <t>dif_mean_last_360_matches_red_cards</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_360_matches_PPS</t>
+          <t>dif_mean_last_60_matches_defensive_actions</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_360_matches_PPS_against</t>
+          <t>dif_mean_last_360_matches_defensive_actions</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_60_matches_attacks</t>
+          <t>dif_mean_last_60_matches_PPDA</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_60_matches_attacks_against</t>
+          <t>dif_mean_last_360_matches_PPDA</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_360_matches_attacks</t>
+          <t>dif_mean_last_60_matches_KGP</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_360_matches_attacks_against</t>
+          <t>dif_mean_last_360_matches_KGP</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_60_matches_dangerous_attacks</t>
+          <t>dif_mean_last_60_matches_clean_sheet</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_60_matches_dangerous_attacks_against</t>
+          <t>dif_mean_last_360_matches_clean_sheet</t>
         </is>
       </c>
       <c r="BA1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_360_matches_dangerous_attacks</t>
+          <t>dif_mean_hei_player_miss</t>
         </is>
       </c>
       <c r="BB1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_360_matches_dangerous_attacks_against</t>
+          <t>dif_mean_wage_player_start</t>
         </is>
       </c>
       <c r="BC1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_60_matches_dead_balls</t>
+          <t>dif_sum_wage_player_miss</t>
         </is>
       </c>
       <c r="BD1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_60_matches_dead_balls_against</t>
+          <t>dif_sum_rat_player_miss</t>
         </is>
       </c>
       <c r="BE1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_360_matches_dead_balls</t>
+          <t>dif_sum_rep_player_miss</t>
         </is>
       </c>
       <c r="BF1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_360_matches_dead_balls_against</t>
+          <t>dif_mean_age_player_miss</t>
         </is>
       </c>
       <c r="BG1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_60_matches_ball_possession</t>
+          <t>dif_mean_pot_player_sub</t>
         </is>
       </c>
       <c r="BH1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_60_matches_ball_possession_against</t>
+          <t>dif_sum_value_player_miss</t>
         </is>
       </c>
       <c r="BI1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_360_matches_ball_possession</t>
+          <t>dif_sum_pot_player_miss</t>
         </is>
       </c>
       <c r="BJ1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_360_matches_ball_possession_against</t>
+          <t>dif_mean_hei_player_start</t>
         </is>
       </c>
       <c r="BK1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_60_matches_total_passes</t>
+          <t>dif_mean_hei_player_sub</t>
         </is>
       </c>
       <c r="BL1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_60_matches_total_passes_against</t>
+          <t>dif_mean_rat_player_sub</t>
         </is>
       </c>
       <c r="BM1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_360_matches_total_passes</t>
+          <t>dif_mean_rep_player_sub</t>
         </is>
       </c>
       <c r="BN1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_360_matches_total_passes_against</t>
+          <t>dif_mean_pot_player_start</t>
         </is>
       </c>
       <c r="BO1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_60_matches_yellow_cards</t>
+          <t>dif_mean_value_player_sub</t>
         </is>
       </c>
       <c r="BP1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_60_matches_yellow_cards_against</t>
+          <t>dif_mean_rep_player_start</t>
         </is>
       </c>
       <c r="BQ1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_360_matches_yellow_cards</t>
+          <t>dif_mean_rat_player_start</t>
         </is>
       </c>
       <c r="BR1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_360_matches_yellow_cards_against</t>
+          <t>dif_n_player_miss</t>
         </is>
       </c>
       <c r="BS1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_60_matches_red_cards</t>
+          <t>dif_mean_age_player_sub</t>
         </is>
       </c>
       <c r="BT1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_60_matches_red_cards_against</t>
+          <t>dif_mean_age_player_start</t>
         </is>
       </c>
       <c r="BU1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_360_matches_red_cards</t>
+          <t>dif_mean_wage_player_sub</t>
         </is>
       </c>
       <c r="BV1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_360_matches_red_cards_against</t>
-        </is>
-      </c>
-      <c r="BW1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_60_matches_defensive_actions</t>
-        </is>
-      </c>
-      <c r="BX1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_60_matches_defensive_actions_against</t>
-        </is>
-      </c>
-      <c r="BY1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_360_matches_defensive_actions</t>
-        </is>
-      </c>
-      <c r="BZ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_360_matches_defensive_actions_against</t>
-        </is>
-      </c>
-      <c r="CA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_60_matches_PPDA</t>
-        </is>
-      </c>
-      <c r="CB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_60_matches_PPDA_against</t>
-        </is>
-      </c>
-      <c r="CC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_360_matches_PPDA</t>
-        </is>
-      </c>
-      <c r="CD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_360_matches_PPDA_against</t>
-        </is>
-      </c>
-      <c r="CE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_60_matches_KGP</t>
-        </is>
-      </c>
-      <c r="CF1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_60_matches_KGP_against</t>
-        </is>
-      </c>
-      <c r="CG1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_360_matches_KGP</t>
-        </is>
-      </c>
-      <c r="CH1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_360_matches_KGP_against</t>
-        </is>
-      </c>
-      <c r="CI1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_60_matches_clean_sheet</t>
-        </is>
-      </c>
-      <c r="CJ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_60_matches_clean_sheet_against</t>
-        </is>
-      </c>
-      <c r="CK1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_360_matches_clean_sheet</t>
-        </is>
-      </c>
-      <c r="CL1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_360_matches_clean_sheet_against</t>
-        </is>
-      </c>
-      <c r="CM1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_360_matches_mean_rat_player_start_against</t>
-        </is>
-      </c>
-      <c r="CN1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_value_player_miss</t>
-        </is>
-      </c>
-      <c r="CO1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_value_player_sub</t>
-        </is>
-      </c>
-      <c r="CP1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_sub</t>
-        </is>
-      </c>
-      <c r="CQ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_rep_player_miss</t>
-        </is>
-      </c>
-      <c r="CR1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_sub</t>
-        </is>
-      </c>
-      <c r="CS1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_start</t>
-        </is>
-      </c>
-      <c r="CT1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_miss</t>
-        </is>
-      </c>
-      <c r="CU1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_miss</t>
-        </is>
-      </c>
-      <c r="CV1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_pot_player_miss</t>
-        </is>
-      </c>
-      <c r="CW1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_wage_player_sub</t>
-        </is>
-      </c>
-      <c r="CX1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rep_player_start</t>
-        </is>
-      </c>
-      <c r="CY1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_start</t>
-        </is>
-      </c>
-      <c r="CZ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_wage_player_miss</t>
-        </is>
-      </c>
-      <c r="DA1" s="1" t="inlineStr">
-        <is>
           <t>dif_mean_value_player_start</t>
-        </is>
-      </c>
-      <c r="DB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_sub</t>
-        </is>
-      </c>
-      <c r="DC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_wage_player_start</t>
-        </is>
-      </c>
-      <c r="DD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_rat_player_miss</t>
-        </is>
-      </c>
-      <c r="DE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rep_player_sub</t>
-        </is>
-      </c>
-      <c r="DF1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_start</t>
-        </is>
-      </c>
-      <c r="DG1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_sub</t>
-        </is>
-      </c>
-      <c r="DH1" s="1" t="inlineStr">
-        <is>
-          <t>dif_n_player_miss</t>
-        </is>
-      </c>
-      <c r="DI1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_start</t>
         </is>
       </c>
     </row>
@@ -1044,263 +849,198 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.02000000000000024</v>
+        <v>-0.5233333333333334</v>
       </c>
       <c r="P2" t="n">
-        <v>0.5033333333333332</v>
+        <v>0.5056985294117644</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.08139705882352932</v>
+        <v>-1</v>
       </c>
       <c r="R2" t="n">
-        <v>-0.4243014705882351</v>
+        <v>0.8388157894736842</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.6666666666666667</v>
+        <v>-3</v>
       </c>
       <c r="T2" t="n">
-        <v>0.3333333333333334</v>
+        <v>0.2697368421052637</v>
       </c>
       <c r="U2" t="n">
-        <v>0.506578947368421</v>
+        <v>-3.666666666666666</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.3322368421052632</v>
+        <v>1.355263157894738</v>
       </c>
       <c r="W2" t="n">
-        <v>-2.166666666666667</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="X2" t="n">
-        <v>0.8333333333333335</v>
+        <v>-1.230263157894737</v>
       </c>
       <c r="Y2" t="n">
-        <v>-1.519736842105263</v>
+        <v>0.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>-1.789473684210527</v>
+        <v>-1.055921052631579</v>
       </c>
       <c r="AA2" t="n">
-        <v>-0.6666666666666661</v>
+        <v>20.9625</v>
       </c>
       <c r="AB2" t="n">
-        <v>3</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>-1.174342105263158</v>
-      </c>
+        <v>19.76698178836489</v>
+      </c>
+      <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="n">
-        <v>-2.529605263157896</v>
+        <v>1087.251761429009</v>
       </c>
       <c r="AE2" t="n">
-        <v>-0.1666666666666667</v>
+        <v>-9</v>
       </c>
       <c r="AF2" t="n">
-        <v>-0.5</v>
+        <v>-27.82352941176471</v>
       </c>
       <c r="AG2" t="n">
-        <v>-0.924342105263158</v>
+        <v>11</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.305921052631579</v>
+        <v>3.129411764705878</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.3333333333333333</v>
+        <v>-15.16666666666666</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-0.1666666666666666</v>
+        <v>0.463815789473685</v>
       </c>
       <c r="AK2" t="n">
-        <v>-0.6414473684210527</v>
+        <v>-6</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.4144736842105263</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>11.2125</v>
-      </c>
+        <v>-22.40131578947368</v>
+      </c>
+      <c r="AM2" t="inlineStr"/>
       <c r="AN2" t="n">
-        <v>-9.75</v>
+        <v>-295.4642857142857</v>
       </c>
       <c r="AO2" t="n">
-        <v>11.23671571484071</v>
+        <v>3.833333333333333</v>
       </c>
       <c r="AP2" t="n">
-        <v>-8.53026607352418</v>
+        <v>-0.4375</v>
       </c>
       <c r="AQ2" t="inlineStr"/>
-      <c r="AR2" t="inlineStr"/>
+      <c r="AR2" t="n">
+        <v>0</v>
+      </c>
       <c r="AS2" t="n">
-        <v>673.7801040097427</v>
+        <v>10.5</v>
       </c>
       <c r="AT2" t="n">
-        <v>-413.4716574192664</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>-8</v>
-      </c>
+        <v>6.473684210526315</v>
+      </c>
+      <c r="AU2" t="inlineStr"/>
       <c r="AV2" t="n">
-        <v>1</v>
+        <v>3.53306285074029</v>
       </c>
       <c r="AW2" t="n">
-        <v>-18.69411764705883</v>
+        <v>-0.0459773713114643</v>
       </c>
       <c r="AX2" t="n">
-        <v>9.129411764705878</v>
+        <v>0.03689127045394714</v>
       </c>
       <c r="AY2" t="n">
-        <v>-15</v>
+        <v>0.5</v>
       </c>
       <c r="AZ2" t="n">
-        <v>-26</v>
+        <v>-0.1809210526315789</v>
       </c>
       <c r="BA2" t="n">
-        <v>-4.450980392156865</v>
+        <v>-6.102643678160916</v>
       </c>
       <c r="BB2" t="n">
-        <v>-7.580392156862743</v>
+        <v>-48065.97222222223</v>
       </c>
       <c r="BC2" t="n">
-        <v>-5.666666666666664</v>
+        <v>-138387.5862068966</v>
       </c>
       <c r="BD2" t="n">
-        <v>9.5</v>
+        <v>20.01379310344828</v>
       </c>
       <c r="BE2" t="n">
-        <v>4.243421052631579</v>
+        <v>-2.208275862068965</v>
       </c>
       <c r="BF2" t="n">
-        <v>3.779605263157894</v>
+        <v>-2.068689655172413</v>
       </c>
       <c r="BG2" t="n">
-        <v>-3</v>
+        <v>-5.09639138639136</v>
       </c>
       <c r="BH2" t="n">
-        <v>3</v>
+        <v>-72102827.5862069</v>
       </c>
       <c r="BI2" t="n">
-        <v>-11.20065789473684</v>
+        <v>30.42206896551727</v>
       </c>
       <c r="BJ2" t="n">
-        <v>11.20065789473684</v>
-      </c>
-      <c r="BK2" t="inlineStr"/>
-      <c r="BL2" t="inlineStr"/>
+        <v>-2.31018518518519</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>-1.090574980574956</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>-4.999770784770789</v>
+      </c>
       <c r="BM2" t="n">
-        <v>-220.2589285714286</v>
+        <v>-0.8302397602397602</v>
       </c>
       <c r="BN2" t="n">
-        <v>75.20535714285717</v>
+        <v>-5.71643518518519</v>
       </c>
       <c r="BO2" t="n">
-        <v>2.833333333333333</v>
+        <v>-36818643.71739371</v>
       </c>
       <c r="BP2" t="n">
-        <v>-1</v>
+        <v>-0.8935185185185184</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0.5845588235294117</v>
+        <v>-4.030092592592595</v>
       </c>
       <c r="BR2" t="n">
-        <v>1.022058823529412</v>
-      </c>
-      <c r="BS2" t="inlineStr"/>
-      <c r="BT2" t="inlineStr"/>
+        <v>0.6662068965517243</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>0.6932856032856058</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>2.387731481481481</v>
+      </c>
       <c r="BU2" t="n">
-        <v>0.2142857142857143</v>
+        <v>-56098.50468975468</v>
       </c>
       <c r="BV2" t="n">
-        <v>0.2142857142857143</v>
-      </c>
-      <c r="BW2" t="n">
-        <v>7.833333333333334</v>
-      </c>
-      <c r="BX2" t="n">
-        <v>-2.666666666666666</v>
-      </c>
-      <c r="BY2" t="n">
-        <v>4.779605263157897</v>
-      </c>
-      <c r="BZ2" t="n">
-        <v>-1.694078947368418</v>
-      </c>
-      <c r="CA2" t="inlineStr"/>
-      <c r="CB2" t="inlineStr"/>
-      <c r="CC2" t="n">
-        <v>1.677124895559439</v>
-      </c>
-      <c r="CD2" t="n">
-        <v>-1.855937955180851</v>
-      </c>
-      <c r="CE2" t="n">
-        <v>-0.00572969329288844</v>
-      </c>
-      <c r="CF2" t="n">
-        <v>0.04024767801857584</v>
-      </c>
-      <c r="CG2" t="n">
-        <v>0.01128032512844909</v>
-      </c>
-      <c r="CH2" t="n">
-        <v>-0.02561094532549806</v>
-      </c>
-      <c r="CI2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="CJ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CK2" t="n">
-        <v>-0.1085526315789473</v>
-      </c>
-      <c r="CL2" t="n">
-        <v>0.07236842105263158</v>
-      </c>
-      <c r="CM2" t="n">
-        <v>0.4413580246913682</v>
-      </c>
-      <c r="CN2" t="inlineStr"/>
-      <c r="CO2" t="inlineStr"/>
-      <c r="CP2" t="inlineStr"/>
-      <c r="CQ2" t="inlineStr"/>
-      <c r="CR2" t="inlineStr"/>
-      <c r="CS2" t="inlineStr"/>
-      <c r="CT2" t="inlineStr"/>
-      <c r="CU2" t="inlineStr"/>
-      <c r="CV2" t="inlineStr"/>
-      <c r="CW2" t="inlineStr"/>
-      <c r="CX2" t="inlineStr"/>
-      <c r="CY2" t="inlineStr"/>
-      <c r="CZ2" t="inlineStr"/>
-      <c r="DA2" t="inlineStr"/>
-      <c r="DB2" t="inlineStr"/>
-      <c r="DC2" t="inlineStr"/>
-      <c r="DD2" t="inlineStr"/>
-      <c r="DE2" t="inlineStr"/>
-      <c r="DF2" t="inlineStr"/>
-      <c r="DG2" t="inlineStr"/>
-      <c r="DH2" t="inlineStr"/>
-      <c r="DI2" t="inlineStr"/>
+        <v>-39862586.80555555</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>KdJMr7EE</t>
+          <t>vNHAXt6D</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
         <v>45592.54166666666</v>
       </c>
       <c r="C3" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D3" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E3" t="n">
-        <v>535</v>
+        <v>242</v>
       </c>
       <c r="F3" t="n">
-        <v>33</v>
+        <v>226</v>
       </c>
       <c r="G3" t="n">
         <v>55</v>
@@ -1322,260 +1062,199 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>193</v>
+        <v>12</v>
       </c>
       <c r="M3" t="n">
-        <v>60</v>
+        <v>127</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>0.6700000000000002</v>
+        <v>-0.4449999999999998</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.04500000000000015</v>
+        <v>0.5164313725490202</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.09183823529411783</v>
+        <v>-1.5</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.6772426470588235</v>
+        <v>0.1568627450980391</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>1.463235294117648</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5833333333333333</v>
+        <v>2</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.5416666666666667</v>
+        <v>3.360294117647058</v>
       </c>
       <c r="W3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X3" t="n">
-        <v>2.5</v>
+        <v>-0.588235294117647</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.03472222222222232</v>
+        <v>3</v>
       </c>
       <c r="Z3" t="n">
-        <v>-1.729166666666667</v>
+        <v>-0.6764705882352939</v>
       </c>
       <c r="AA3" t="n">
+        <v>15.06672077922078</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>20.96454582730221</v>
+      </c>
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="n">
+        <v>875.2331297518202</v>
+      </c>
+      <c r="AE3" t="inlineStr"/>
+      <c r="AF3" t="n">
+        <v>8.803571428571431</v>
+      </c>
+      <c r="AG3" t="inlineStr"/>
+      <c r="AH3" t="n">
+        <v>16.04464285714286</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>8.499999999999996</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>5.06535947712419</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>23</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>3.404411764705884</v>
+      </c>
+      <c r="AM3" t="inlineStr"/>
+      <c r="AN3" t="n">
+        <v>1.0461538461538</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>-1.03921568627451</v>
+      </c>
+      <c r="AQ3" t="inlineStr"/>
+      <c r="AR3" t="n">
         <v>1</v>
       </c>
-      <c r="AB3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>1.930555555555555</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>-3.569444444444445</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>-0.4722222222222223</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>-0.5833333333333333</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AJ3" t="n">
+      <c r="AS3" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>-4</v>
+      </c>
+      <c r="AU3" t="inlineStr"/>
+      <c r="AV3" t="n">
+        <v>1.45100617485244</v>
+      </c>
+      <c r="AW3" t="inlineStr"/>
+      <c r="AX3" t="n">
+        <v>0.04034575343889454</v>
+      </c>
+      <c r="AY3" t="n">
         <v>0.5</v>
       </c>
-      <c r="AK3" t="n">
-        <v>-0.4027777777777777</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>0.3263888888888888</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>8.875</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>-12.10989010989011</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>9.418279935485312</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>-9.305024064533869</v>
-      </c>
-      <c r="AQ3" t="inlineStr"/>
-      <c r="AR3" t="inlineStr"/>
-      <c r="AS3" t="n">
-        <v>485.6576335498609</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>-446.1917969351238</v>
-      </c>
-      <c r="AU3" t="inlineStr"/>
-      <c r="AV3" t="inlineStr"/>
-      <c r="AW3" t="n">
-        <v>-7.180672268907571</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>-9.941176470588232</v>
-      </c>
-      <c r="AY3" t="inlineStr"/>
-      <c r="AZ3" t="inlineStr"/>
+      <c r="AZ3" t="n">
+        <v>0.173202614379085</v>
+      </c>
       <c r="BA3" t="n">
-        <v>3.676470588235297</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>-14.77731092436974</v>
-      </c>
+        <v>-2.322222222222251</v>
+      </c>
+      <c r="BB3" t="inlineStr"/>
       <c r="BC3" t="n">
-        <v>-8.5</v>
+        <v>19003.49650349651</v>
       </c>
       <c r="BD3" t="n">
-        <v>-14.5</v>
+        <v>57.29166666666666</v>
       </c>
       <c r="BE3" t="n">
-        <v>0.5763888888888857</v>
+        <v>1.493589743589743</v>
       </c>
       <c r="BF3" t="n">
-        <v>-7.722222222222221</v>
+        <v>2.597649572649566</v>
       </c>
       <c r="BG3" t="n">
-        <v>-6.5</v>
+        <v>-0.7604441912254316</v>
       </c>
       <c r="BH3" t="n">
-        <v>6.5</v>
+        <v>834134.615384616</v>
       </c>
       <c r="BI3" t="n">
-        <v>-1.513888888888886</v>
+        <v>55.58974358974356</v>
       </c>
       <c r="BJ3" t="n">
-        <v>1.513888888888886</v>
-      </c>
-      <c r="BK3" t="inlineStr"/>
-      <c r="BL3" t="inlineStr"/>
+        <v>-5.716005291005217</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>-0.7497044448607255</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>1.122746472277726</v>
+      </c>
       <c r="BM3" t="n">
-        <v>-5.836538461538453</v>
+        <v>0.20987234987235</v>
       </c>
       <c r="BN3" t="n">
-        <v>26.12019230769232</v>
+        <v>-0.6893518518518675</v>
       </c>
       <c r="BO3" t="n">
-        <v>-1.5</v>
+        <v>261340.3909458597</v>
       </c>
       <c r="BP3" t="n">
-        <v>-1</v>
+        <v>0.3944444444444444</v>
       </c>
       <c r="BQ3" t="n">
-        <v>-1.205882352941177</v>
+        <v>4.035978835978838</v>
       </c>
       <c r="BR3" t="n">
-        <v>0.01102941176470607</v>
-      </c>
-      <c r="BS3" t="inlineStr"/>
-      <c r="BT3" t="inlineStr"/>
+        <v>0.8012820512820511</v>
+      </c>
+      <c r="BS3" t="n">
+        <v>2.014719308469306</v>
+      </c>
+      <c r="BT3" t="n">
+        <v>3.606349206349201</v>
+      </c>
       <c r="BU3" t="n">
-        <v>-0.1666666666666667</v>
+        <v>2967.451487906033</v>
       </c>
       <c r="BV3" t="n">
-        <v>0.1666666666666667</v>
-      </c>
-      <c r="BW3" t="n">
-        <v>-10.5</v>
-      </c>
-      <c r="BX3" t="n">
-        <v>-2</v>
-      </c>
-      <c r="BY3" t="n">
-        <v>-6.993055555555557</v>
-      </c>
-      <c r="BZ3" t="n">
-        <v>-1.020833333333336</v>
-      </c>
-      <c r="CA3" t="inlineStr"/>
-      <c r="CB3" t="inlineStr"/>
-      <c r="CC3" t="n">
-        <v>1.795369455627839</v>
-      </c>
-      <c r="CD3" t="n">
-        <v>-1.448432787193692</v>
-      </c>
-      <c r="CE3" t="inlineStr"/>
-      <c r="CF3" t="inlineStr"/>
-      <c r="CG3" t="n">
-        <v>0.009663247437253178</v>
-      </c>
-      <c r="CH3" t="n">
-        <v>-0.02738583721765527</v>
-      </c>
-      <c r="CI3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CJ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CK3" t="n">
-        <v>0.2291666666666667</v>
-      </c>
-      <c r="CL3" t="n">
-        <v>0.006944444444444448</v>
-      </c>
-      <c r="CM3" t="n">
-        <v>0.1657994082236485</v>
-      </c>
-      <c r="CN3" t="inlineStr"/>
-      <c r="CO3" t="inlineStr"/>
-      <c r="CP3" t="inlineStr"/>
-      <c r="CQ3" t="inlineStr"/>
-      <c r="CR3" t="inlineStr"/>
-      <c r="CS3" t="inlineStr"/>
-      <c r="CT3" t="inlineStr"/>
-      <c r="CU3" t="inlineStr"/>
-      <c r="CV3" t="inlineStr"/>
-      <c r="CW3" t="inlineStr"/>
-      <c r="CX3" t="inlineStr"/>
-      <c r="CY3" t="inlineStr"/>
-      <c r="CZ3" t="inlineStr"/>
-      <c r="DA3" t="inlineStr"/>
-      <c r="DB3" t="inlineStr"/>
-      <c r="DC3" t="inlineStr"/>
-      <c r="DD3" t="inlineStr"/>
-      <c r="DE3" t="inlineStr"/>
-      <c r="DF3" t="inlineStr"/>
-      <c r="DG3" t="inlineStr"/>
-      <c r="DH3" t="inlineStr"/>
-      <c r="DI3" t="inlineStr"/>
+        <v>2958549.933862433</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>vNHAXt6D</t>
+          <t>h2acepbK</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
         <v>45592.54166666666</v>
       </c>
       <c r="C4" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D4" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E4" t="n">
-        <v>242</v>
+        <v>736</v>
       </c>
       <c r="F4" t="n">
-        <v>226</v>
+        <v>599</v>
       </c>
       <c r="G4" t="n">
         <v>55</v>
@@ -1597,260 +1276,207 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>12</v>
+        <v>312</v>
       </c>
       <c r="M4" t="n">
-        <v>127</v>
+        <v>141</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.1649999999999998</v>
+        <v>0.8366666666666666</v>
       </c>
       <c r="P4" t="n">
-        <v>0.28</v>
+        <v>0.3579779411764706</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.3983529411764708</v>
+        <v>1</v>
       </c>
       <c r="R4" t="n">
-        <v>-0.1180784313725494</v>
+        <v>0.8823529411764708</v>
       </c>
       <c r="S4" t="n">
-        <v>-1</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5</v>
+        <v>1.051470588235294</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1013071895424835</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.05555555555555558</v>
+        <v>1.926470588235295</v>
       </c>
       <c r="W4" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="X4" t="n">
-        <v>0.5</v>
+        <v>0.3529411764705883</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.599264705882353</v>
+        <v>1</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.1360294117647056</v>
+        <v>0.5294117647058822</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.5</v>
+        <v>17.19810924369748</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>3.246323529411764</v>
-      </c>
+        <v>17.48079349674019</v>
+      </c>
+      <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="n">
-        <v>-0.1139705882352935</v>
+        <v>873.581322507257</v>
       </c>
       <c r="AE4" t="n">
+        <v>105</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>21.49047619047619</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>11.54761904761904</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>-1.333333333333336</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>4.529411764705884</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>6.666666666666671</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>4.272058823529406</v>
+      </c>
+      <c r="AM4" t="inlineStr"/>
+      <c r="AN4" t="n">
+        <v>37.74725274725284</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>-0.6666666666666667</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>-0.6156862745098037</v>
+      </c>
+      <c r="AQ4" t="inlineStr"/>
+      <c r="AR4" t="n">
         <v>1.5</v>
       </c>
-      <c r="AF4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>-0.2941176470588236</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>0.2941176470588234</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>1.333333333333333</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>-1.666666666666667</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>-0.5294117647058822</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>0.1470588235294117</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>8.242857142857142</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>-6.823863636363637</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>9.59915329768271</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>-11.3653925296195</v>
-      </c>
-      <c r="AQ4" t="inlineStr"/>
-      <c r="AR4" t="inlineStr"/>
       <c r="AS4" t="n">
-        <v>407.7337269386269</v>
+        <v>-1.666666666666664</v>
       </c>
       <c r="AT4" t="n">
-        <v>-467.4994028131933</v>
+        <v>-3.882352941176467</v>
       </c>
       <c r="AU4" t="inlineStr"/>
-      <c r="AV4" t="inlineStr"/>
+      <c r="AV4" t="n">
+        <v>1.325409884342061</v>
+      </c>
       <c r="AW4" t="n">
-        <v>-0.2053571428571388</v>
+        <v>0.05250571962900731</v>
       </c>
       <c r="AX4" t="n">
-        <v>-9.008928571428569</v>
-      </c>
-      <c r="AY4" t="inlineStr"/>
-      <c r="AZ4" t="inlineStr"/>
+        <v>0.00287292148709687</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>0.1176470588235294</v>
+      </c>
       <c r="BA4" t="n">
-        <v>8.991071428571431</v>
+        <v>5.914000000000016</v>
       </c>
       <c r="BB4" t="n">
-        <v>-7.053571428571431</v>
+        <v>-8770.098039215691</v>
       </c>
       <c r="BC4" t="n">
-        <v>-3.333333333333336</v>
+        <v>-17360</v>
       </c>
       <c r="BD4" t="n">
-        <v>-11.83333333333333</v>
+        <v>-9</v>
       </c>
       <c r="BE4" t="n">
-        <v>3.70261437908497</v>
+        <v>0.96</v>
       </c>
       <c r="BF4" t="n">
-        <v>-1.36274509803922</v>
+        <v>1.472666666666669</v>
       </c>
       <c r="BG4" t="n">
-        <v>11.5</v>
+        <v>1.2514085798461</v>
       </c>
       <c r="BH4" t="n">
-        <v>-11.5</v>
+        <v>-6925200</v>
       </c>
       <c r="BI4" t="n">
-        <v>1.702205882352942</v>
+        <v>-6.400000000000006</v>
       </c>
       <c r="BJ4" t="n">
-        <v>-1.702205882352942</v>
-      </c>
-      <c r="BK4" t="inlineStr"/>
-      <c r="BL4" t="inlineStr"/>
+        <v>0.6577995642701921</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>-0.1992296014171018</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>0.8397403753653805</v>
+      </c>
       <c r="BM4" t="n">
-        <v>-21.61538461538464</v>
+        <v>0.1163046675546675</v>
       </c>
       <c r="BN4" t="n">
-        <v>-22.66153846153844</v>
+        <v>0.7790305010893235</v>
       </c>
       <c r="BO4" t="n">
-        <v>1</v>
+        <v>-923884.3948297072</v>
       </c>
       <c r="BP4" t="n">
-        <v>1</v>
+        <v>-0.1965250544662311</v>
       </c>
       <c r="BQ4" t="n">
-        <v>-0.164705882352941</v>
+        <v>-2.434302832244001</v>
       </c>
       <c r="BR4" t="n">
-        <v>0.8745098039215686</v>
-      </c>
-      <c r="BS4" t="inlineStr"/>
-      <c r="BT4" t="inlineStr"/>
+        <v>-0.07999999999999963</v>
+      </c>
+      <c r="BS4" t="n">
+        <v>-0.3839595820845823</v>
+      </c>
+      <c r="BT4" t="n">
+        <v>-1.954520697167755</v>
+      </c>
       <c r="BU4" t="n">
-        <v>1</v>
+        <v>-5082.021748093177</v>
       </c>
       <c r="BV4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW4" t="n">
-        <v>-5.166666666666666</v>
-      </c>
-      <c r="BX4" t="n">
-        <v>-2.666666666666666</v>
-      </c>
-      <c r="BY4" t="n">
-        <v>-2.071895424836605</v>
-      </c>
-      <c r="BZ4" t="n">
-        <v>1.928104575163395</v>
-      </c>
-      <c r="CA4" t="inlineStr"/>
-      <c r="CB4" t="inlineStr"/>
-      <c r="CC4" t="n">
-        <v>1.034254582393276</v>
-      </c>
-      <c r="CD4" t="n">
-        <v>-0.416751592459164</v>
-      </c>
-      <c r="CE4" t="inlineStr"/>
-      <c r="CF4" t="inlineStr"/>
-      <c r="CG4" t="n">
-        <v>0.01640937459512249</v>
-      </c>
-      <c r="CH4" t="n">
-        <v>-0.02393637884377205</v>
-      </c>
-      <c r="CI4" t="n">
-        <v>0</v>
-      </c>
-      <c r="CJ4" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="CK4" t="n">
-        <v>0.1013071895424837</v>
-      </c>
-      <c r="CL4" t="n">
-        <v>-0.07189542483660133</v>
-      </c>
-      <c r="CM4" t="n">
-        <v>1.046899551066218</v>
-      </c>
-      <c r="CN4" t="inlineStr"/>
-      <c r="CO4" t="inlineStr"/>
-      <c r="CP4" t="inlineStr"/>
-      <c r="CQ4" t="inlineStr"/>
-      <c r="CR4" t="inlineStr"/>
-      <c r="CS4" t="inlineStr"/>
-      <c r="CT4" t="inlineStr"/>
-      <c r="CU4" t="inlineStr"/>
-      <c r="CV4" t="inlineStr"/>
-      <c r="CW4" t="inlineStr"/>
-      <c r="CX4" t="inlineStr"/>
-      <c r="CY4" t="inlineStr"/>
-      <c r="CZ4" t="inlineStr"/>
-      <c r="DA4" t="inlineStr"/>
-      <c r="DB4" t="inlineStr"/>
-      <c r="DC4" t="inlineStr"/>
-      <c r="DD4" t="inlineStr"/>
-      <c r="DE4" t="inlineStr"/>
-      <c r="DF4" t="inlineStr"/>
-      <c r="DG4" t="inlineStr"/>
-      <c r="DH4" t="inlineStr"/>
-      <c r="DI4" t="inlineStr"/>
+        <v>-1895626.089324619</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>h2acepbK</t>
+          <t>KdJMr7EE</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
         <v>45592.54166666666</v>
       </c>
       <c r="C5" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D5" t="n">
         <v>133</v>
       </c>
       <c r="E5" t="n">
-        <v>736</v>
+        <v>535</v>
       </c>
       <c r="F5" t="n">
-        <v>599</v>
+        <v>33</v>
       </c>
       <c r="G5" t="n">
         <v>55</v>
@@ -1872,251 +1498,180 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>312</v>
+        <v>193</v>
       </c>
       <c r="M5" t="n">
-        <v>141</v>
+        <v>60</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.7150000000000003</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.5033333333333333</v>
+        <v>0.7690808823529414</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.3656617647058823</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.00768382352941166</v>
+        <v>1.125</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3333333333333334</v>
+        <v>-0.5</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.6666666666666667</v>
+        <v>1.763888888888889</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4705882352941178</v>
+        <v>1</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.411764705882353</v>
+        <v>5.5</v>
       </c>
       <c r="W5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.333333333333333</v>
+        <v>0.1111111111111109</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.327205882352941</v>
+        <v>-1.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.2757352941176472</v>
+        <v>-0.7291666666666665</v>
       </c>
       <c r="AA5" t="n">
-        <v>1</v>
+        <v>20.98489010989011</v>
       </c>
       <c r="AB5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>3.323529411764707</v>
-      </c>
+        <v>18.72330400001918</v>
+      </c>
+      <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="n">
-        <v>1.397058823529411</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>0</v>
-      </c>
+        <v>931.8494304849846</v>
+      </c>
+      <c r="AE5" t="inlineStr"/>
       <c r="AF5" t="n">
+        <v>2.760504201680661</v>
+      </c>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="n">
+        <v>18.45378151260504</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>6</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>8.298611111111107</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>-13</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>-3.027777777777771</v>
+      </c>
+      <c r="AM5" t="inlineStr"/>
+      <c r="AN5" t="n">
+        <v>-31.95673076923077</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>-1.216911764705883</v>
+      </c>
+      <c r="AQ5" t="inlineStr"/>
+      <c r="AR5" t="n">
         <v>-0.3333333333333333</v>
       </c>
-      <c r="AG5" t="n">
-        <v>0.4705882352941178</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>0.1176470588235294</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>0.3333333333333335</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>-0.6666666666666666</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>0.2941176470588234</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>-0.2352941176470589</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>7.572619047619047</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>-9.625490196078433</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>7.898432531520767</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>-9.582360965219422</v>
-      </c>
-      <c r="AQ5" t="inlineStr"/>
-      <c r="AR5" t="inlineStr"/>
       <c r="AS5" t="n">
-        <v>403.3444973257274</v>
+        <v>-8.5</v>
       </c>
       <c r="AT5" t="n">
-        <v>-470.2368251815295</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>45</v>
-      </c>
+        <v>-5.972222222222221</v>
+      </c>
+      <c r="AU5" t="inlineStr"/>
       <c r="AV5" t="n">
-        <v>-60</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>5.223809523809521</v>
-      </c>
+        <v>3.243802242821531</v>
+      </c>
+      <c r="AW5" t="inlineStr"/>
       <c r="AX5" t="n">
-        <v>-16.26666666666667</v>
+        <v>0.03704908465490844</v>
       </c>
       <c r="AY5" t="n">
-        <v>-7</v>
+        <v>0</v>
       </c>
       <c r="AZ5" t="n">
-        <v>-21</v>
+        <v>0.2222222222222222</v>
       </c>
       <c r="BA5" t="n">
-        <v>2.857142857142854</v>
+        <v>-1.827604395604453</v>
       </c>
       <c r="BB5" t="n">
-        <v>-8.69047619047619</v>
+        <v>-8794.074675324671</v>
       </c>
       <c r="BC5" t="n">
-        <v>-5.333333333333336</v>
+        <v>-87121.53846153847</v>
       </c>
       <c r="BD5" t="n">
-        <v>-4</v>
+        <v>-130.6415384615385</v>
       </c>
       <c r="BE5" t="n">
-        <v>2</v>
+        <v>-2.375384615384615</v>
       </c>
       <c r="BF5" t="n">
-        <v>-2.529411764705884</v>
+        <v>-0.1662820512820531</v>
       </c>
       <c r="BG5" t="n">
-        <v>3.333333333333336</v>
+        <v>-2.49605181744721</v>
       </c>
       <c r="BH5" t="n">
-        <v>-3.333333333333336</v>
+        <v>-39052000</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.136029411764703</v>
+        <v>-141.3707692307692</v>
       </c>
       <c r="BJ5" t="n">
-        <v>-2.136029411764703</v>
-      </c>
-      <c r="BK5" t="inlineStr"/>
-      <c r="BL5" t="inlineStr"/>
+        <v>5.821614959114953</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>2.19232793012921</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>1.488875486398697</v>
+      </c>
       <c r="BM5" t="n">
-        <v>-2.626373626373606</v>
+        <v>0.2101319403563982</v>
       </c>
       <c r="BN5" t="n">
-        <v>-40.37362637362645</v>
+        <v>-0.8677158489658439</v>
       </c>
       <c r="BO5" t="n">
-        <v>0</v>
+        <v>-1140548.900603126</v>
       </c>
       <c r="BP5" t="n">
-        <v>0.6666666666666667</v>
+        <v>-0.001031144781144855</v>
       </c>
       <c r="BQ5" t="n">
-        <v>-0.3999999999999999</v>
+        <v>0.6239868927368946</v>
       </c>
       <c r="BR5" t="n">
-        <v>0.2156862745098038</v>
-      </c>
-      <c r="BS5" t="inlineStr"/>
-      <c r="BT5" t="inlineStr"/>
+        <v>-1.664615384615385</v>
+      </c>
+      <c r="BS5" t="n">
+        <v>1.361343361210675</v>
+      </c>
+      <c r="BT5" t="n">
+        <v>1.030645743145747</v>
+      </c>
       <c r="BU5" t="n">
-        <v>0.5</v>
+        <v>8455.476273000786</v>
       </c>
       <c r="BV5" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BW5" t="n">
-        <v>1.666666666666668</v>
-      </c>
-      <c r="BX5" t="n">
-        <v>3.333333333333332</v>
-      </c>
-      <c r="BY5" t="n">
-        <v>2.647058823529413</v>
-      </c>
-      <c r="BZ5" t="n">
-        <v>6.52941176470588</v>
-      </c>
-      <c r="CA5" t="inlineStr"/>
-      <c r="CB5" t="inlineStr"/>
-      <c r="CC5" t="n">
-        <v>-0.4484297445664289</v>
-      </c>
-      <c r="CD5" t="n">
-        <v>-1.77383962890849</v>
-      </c>
-      <c r="CE5" t="n">
-        <v>0.01106427818756586</v>
-      </c>
-      <c r="CF5" t="n">
-        <v>-0.04144144144144145</v>
-      </c>
-      <c r="CG5" t="n">
-        <v>0.008024737532382469</v>
-      </c>
-      <c r="CH5" t="n">
-        <v>0.005151816045285598</v>
-      </c>
-      <c r="CI5" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="CJ5" t="n">
-        <v>-0.3333333333333333</v>
-      </c>
-      <c r="CK5" t="n">
-        <v>-0.1176470588235294</v>
-      </c>
-      <c r="CL5" t="n">
-        <v>-0.2352941176470588</v>
-      </c>
-      <c r="CM5" t="n">
-        <v>2.091806958473626</v>
-      </c>
-      <c r="CN5" t="inlineStr"/>
-      <c r="CO5" t="inlineStr"/>
-      <c r="CP5" t="inlineStr"/>
-      <c r="CQ5" t="inlineStr"/>
-      <c r="CR5" t="inlineStr"/>
-      <c r="CS5" t="inlineStr"/>
-      <c r="CT5" t="inlineStr"/>
-      <c r="CU5" t="inlineStr"/>
-      <c r="CV5" t="inlineStr"/>
-      <c r="CW5" t="inlineStr"/>
-      <c r="CX5" t="inlineStr"/>
-      <c r="CY5" t="inlineStr"/>
-      <c r="CZ5" t="inlineStr"/>
-      <c r="DA5" t="inlineStr"/>
-      <c r="DB5" t="inlineStr"/>
-      <c r="DC5" t="inlineStr"/>
-      <c r="DD5" t="inlineStr"/>
-      <c r="DE5" t="inlineStr"/>
-      <c r="DF5" t="inlineStr"/>
-      <c r="DG5" t="inlineStr"/>
-      <c r="DH5" t="inlineStr"/>
-      <c r="DI5" t="inlineStr"/>
+        <v>-3487930.194805196</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -2168,246 +1723,175 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>1.516666666666667</v>
+        <v>2.44</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.9233333333333331</v>
+        <v>0.9221666666666666</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.7670555555555554</v>
+        <v>4</v>
       </c>
       <c r="R6" t="n">
-        <v>-0.1551111111111112</v>
+        <v>1.2</v>
       </c>
       <c r="S6" t="n">
-        <v>2</v>
+        <v>4.666666666666667</v>
       </c>
       <c r="T6" t="n">
+        <v>0.5888888888888886</v>
+      </c>
+      <c r="U6" t="n">
+        <v>14.33333333333333</v>
+      </c>
+      <c r="V6" t="n">
+        <v>-0.2888888888888896</v>
+      </c>
+      <c r="W6" t="n">
+        <v>2.333333333333333</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0.3999999999999997</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>16.77935299994123</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>22.19319082107072</v>
+      </c>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="n">
+        <v>944.9631595713745</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>33</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>-21.02083333333334</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>47</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>4.569444444444443</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>-1.333333333333329</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0.1500000000000021</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>11.33333333333333</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>-7.422222222222231</v>
+      </c>
+      <c r="AM6" t="inlineStr"/>
+      <c r="AN6" t="n">
+        <v>-73.45535714285717</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>-0.666666666666667</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>-0.5176470588235293</v>
+      </c>
+      <c r="AQ6" t="n">
         <v>-2</v>
       </c>
-      <c r="U6" t="n">
-        <v>0.6000000000000001</v>
-      </c>
-      <c r="V6" t="n">
-        <v>-0.6</v>
-      </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="n">
-        <v>0.333333333333333</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>0.9777777777777779</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>0.3888888888888893</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>9.666666666666668</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>-4.666666666666666</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>0.8722222222222218</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.161111111111111</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.333333333333333</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>0.3499999999999999</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>-0.04999999999999982</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>2</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>0.6499999999999999</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>-0.55</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>7.85427807486631</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>-8.925074925074924</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>10.76994678116002</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>-11.42324403991071</v>
-      </c>
-      <c r="AQ6" t="inlineStr"/>
-      <c r="AR6" t="inlineStr"/>
+      <c r="AR6" t="n">
+        <v>-0.8</v>
+      </c>
       <c r="AS6" t="n">
-        <v>500.2442801626408</v>
+        <v>5.666666666666668</v>
       </c>
       <c r="AT6" t="n">
-        <v>-444.7188794087336</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>32</v>
-      </c>
+        <v>-1.399999999999995</v>
+      </c>
+      <c r="AU6" t="inlineStr"/>
       <c r="AV6" t="n">
-        <v>-1</v>
+        <v>2.858654364771889</v>
       </c>
       <c r="AW6" t="n">
-        <v>-10.48611111111111</v>
+        <v>0.02959549411162314</v>
       </c>
       <c r="AX6" t="n">
-        <v>10.53472222222223</v>
+        <v>0.003005089032790918</v>
       </c>
       <c r="AY6" t="n">
-        <v>32</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="AZ6" t="n">
-        <v>-15</v>
+        <v>0.25</v>
       </c>
       <c r="BA6" t="n">
-        <v>-4.993055555555557</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>-9.5625</v>
-      </c>
+        <v>-8.363784461152903</v>
+      </c>
+      <c r="BB6" t="inlineStr"/>
       <c r="BC6" t="n">
-        <v>-6.333333333333329</v>
+        <v>68277.77777777778</v>
       </c>
       <c r="BD6" t="n">
-        <v>-5</v>
+        <v>-29.81954887218046</v>
       </c>
       <c r="BE6" t="n">
-        <v>21.75</v>
+        <v>0.9172932330827068</v>
       </c>
       <c r="BF6" t="n">
-        <v>21.6</v>
+        <v>1.141979949874685</v>
       </c>
       <c r="BG6" t="n">
-        <v>5.666666666666664</v>
+        <v>7.265411038418563</v>
       </c>
       <c r="BH6" t="n">
-        <v>-5.666666666666664</v>
+        <v>17580451.12781955</v>
       </c>
       <c r="BI6" t="n">
-        <v>-3.711111111111116</v>
+        <v>-41.29323308270676</v>
       </c>
       <c r="BJ6" t="n">
-        <v>3.711111111111116</v>
-      </c>
-      <c r="BK6" t="inlineStr"/>
-      <c r="BL6" t="inlineStr"/>
+        <v>-0.4286412512219044</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>-3.424483069144685</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>12.92485347568055</v>
+      </c>
       <c r="BM6" t="n">
-        <v>-28.09821428571433</v>
+        <v>0.9983333333333335</v>
       </c>
       <c r="BN6" t="n">
-        <v>45.35714285714283</v>
+        <v>7.61312724014337</v>
       </c>
       <c r="BO6" t="n">
-        <v>-0.666666666666667</v>
+        <v>13474549.55028263</v>
       </c>
       <c r="BP6" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="BQ6" t="n">
-        <v>-0.2588235294117645</v>
+        <v>6.041035353535349</v>
       </c>
       <c r="BR6" t="n">
-        <v>0.2588235294117649</v>
+        <v>-0.7142857142857144</v>
       </c>
       <c r="BS6" t="n">
-        <v>-1</v>
+        <v>4.763631210059785</v>
       </c>
       <c r="BT6" t="n">
-        <v>1</v>
-      </c>
-      <c r="BU6" t="n">
-        <v>-0.4</v>
-      </c>
+        <v>-1.451857282502445</v>
+      </c>
+      <c r="BU6" t="inlineStr"/>
       <c r="BV6" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="BW6" t="n">
-        <v>-1.333333333333332</v>
-      </c>
-      <c r="BX6" t="n">
-        <v>-7</v>
-      </c>
-      <c r="BY6" t="n">
-        <v>3.550000000000001</v>
-      </c>
-      <c r="BZ6" t="n">
-        <v>4.949999999999996</v>
-      </c>
-      <c r="CA6" t="inlineStr"/>
-      <c r="CB6" t="inlineStr"/>
-      <c r="CC6" t="n">
-        <v>1.522908226265324</v>
-      </c>
-      <c r="CD6" t="n">
-        <v>-1.335746138506565</v>
-      </c>
-      <c r="CE6" t="n">
-        <v>0.04444444444444444</v>
-      </c>
-      <c r="CF6" t="n">
-        <v>0.0148489503328213</v>
-      </c>
-      <c r="CG6" t="n">
-        <v>0.01851880179134279</v>
-      </c>
-      <c r="CH6" t="n">
-        <v>0.01551371275855187</v>
-      </c>
-      <c r="CI6" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="CJ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="CK6" t="n">
-        <v>0.09999999999999998</v>
-      </c>
-      <c r="CL6" t="n">
-        <v>-0.15</v>
-      </c>
-      <c r="CM6" t="n">
-        <v>6.682192437192427</v>
-      </c>
-      <c r="CN6" t="inlineStr"/>
-      <c r="CO6" t="inlineStr"/>
-      <c r="CP6" t="inlineStr"/>
-      <c r="CQ6" t="inlineStr"/>
-      <c r="CR6" t="inlineStr"/>
-      <c r="CS6" t="inlineStr"/>
-      <c r="CT6" t="inlineStr"/>
-      <c r="CU6" t="inlineStr"/>
-      <c r="CV6" t="inlineStr"/>
-      <c r="CW6" t="inlineStr"/>
-      <c r="CX6" t="inlineStr"/>
-      <c r="CY6" t="inlineStr"/>
-      <c r="CZ6" t="inlineStr"/>
-      <c r="DA6" t="inlineStr"/>
-      <c r="DB6" t="inlineStr"/>
-      <c r="DC6" t="inlineStr"/>
-      <c r="DD6" t="inlineStr"/>
-      <c r="DE6" t="inlineStr"/>
-      <c r="DF6" t="inlineStr"/>
-      <c r="DG6" t="inlineStr"/>
-      <c r="DH6" t="inlineStr"/>
-      <c r="DI6" t="inlineStr"/>
+        <v>10804150.37471489</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -2459,254 +1943,183 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.47</v>
+        <v>-1.04</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.4299999999999999</v>
+        <v>0.5543750000000001</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.56375</v>
+        <v>-1</v>
       </c>
       <c r="R7" t="n">
-        <v>0.009374999999999911</v>
+        <v>0.75</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.6666666666666667</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>0.3333333333333334</v>
+        <v>2.375</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4513888888888888</v>
+        <v>-3.5</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.2986111111111112</v>
+        <v>3.308823529411764</v>
       </c>
       <c r="W7" t="n">
         <v>-1</v>
       </c>
       <c r="X7" t="n">
-        <v>-1</v>
+        <v>0.1985294117647058</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.077205882352941</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>-0.2977941176470589</v>
+        <v>0.5833333333333333</v>
       </c>
       <c r="AA7" t="n">
-        <v>-0.5</v>
+        <v>25.73582251082251</v>
       </c>
       <c r="AB7" t="n">
-        <v>3</v>
+        <v>20.39900265798872</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.860294117647058</v>
+        <v>1085.065429856426</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.5514705882352935</v>
+        <v>999.7021628262645</v>
       </c>
       <c r="AE7" t="n">
-        <v>-1.5</v>
+        <v>-69</v>
       </c>
       <c r="AF7" t="n">
-        <v>-0.5</v>
+        <v>-3.295833333333334</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.3786764705882353</v>
+        <v>-32</v>
       </c>
       <c r="AH7" t="n">
-        <v>0.1801470588235294</v>
+        <v>5.458333333333336</v>
       </c>
       <c r="AI7" t="n">
-        <v>-0.3333333333333333</v>
+        <v>6.333333333333336</v>
       </c>
       <c r="AJ7" t="n">
-        <v>-0.3333333333333333</v>
+        <v>0.8055555555555536</v>
       </c>
       <c r="AK7" t="n">
-        <v>0.3055555555555556</v>
+        <v>-24</v>
       </c>
       <c r="AL7" t="n">
-        <v>-0.2777777777777777</v>
+        <v>-17.72058823529412</v>
       </c>
       <c r="AM7" t="n">
-        <v>15.06439393939394</v>
+        <v>-338</v>
       </c>
       <c r="AN7" t="n">
-        <v>-10.67142857142857</v>
+        <v>-178.9642857142857</v>
       </c>
       <c r="AO7" t="n">
-        <v>10.88691366339199</v>
+        <v>1.5</v>
       </c>
       <c r="AP7" t="n">
-        <v>-9.512088994596734</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>673.0264227642276</v>
-      </c>
+        <v>0.1848739495798319</v>
+      </c>
+      <c r="AQ7" t="inlineStr"/>
       <c r="AR7" t="n">
-        <v>-412.0390070921986</v>
+        <v>1</v>
       </c>
       <c r="AS7" t="n">
-        <v>550.0974765100746</v>
+        <v>4.5</v>
       </c>
       <c r="AT7" t="n">
-        <v>-449.60468631619</v>
+        <v>5.979166666666664</v>
       </c>
       <c r="AU7" t="n">
-        <v>-11</v>
+        <v>29.01190476190476</v>
       </c>
       <c r="AV7" t="n">
-        <v>58</v>
+        <v>4.739785138674844</v>
       </c>
       <c r="AW7" t="n">
-        <v>9.012500000000003</v>
+        <v>-0.05627452561414825</v>
       </c>
       <c r="AX7" t="n">
-        <v>12.30833333333334</v>
+        <v>0.002448867104326222</v>
       </c>
       <c r="AY7" t="n">
-        <v>-6</v>
+        <v>0</v>
       </c>
       <c r="AZ7" t="n">
-        <v>26</v>
+        <v>0.1458333333333334</v>
       </c>
       <c r="BA7" t="n">
-        <v>8.929166666666667</v>
+        <v>-10.04230137678417</v>
       </c>
       <c r="BB7" t="n">
-        <v>3.470833333333331</v>
+        <v>3166.98717948718</v>
       </c>
       <c r="BC7" t="n">
-        <v>20.16666666666667</v>
+        <v>41872.67904509284</v>
       </c>
       <c r="BD7" t="n">
-        <v>13.83333333333333</v>
+        <v>104.8010610079575</v>
       </c>
       <c r="BE7" t="n">
-        <v>3.722222222222221</v>
+        <v>0.9801061007957557</v>
       </c>
       <c r="BF7" t="n">
-        <v>2.916666666666668</v>
+        <v>1.678672476948336</v>
       </c>
       <c r="BG7" t="n">
-        <v>-12</v>
+        <v>-1.811064495932925</v>
       </c>
       <c r="BH7" t="n">
-        <v>12</v>
+        <v>5825994.694960212</v>
       </c>
       <c r="BI7" t="n">
-        <v>-8.860294117647058</v>
+        <v>103.7758620689655</v>
       </c>
       <c r="BJ7" t="n">
-        <v>8.860294117647058</v>
+        <v>-1.010540154290112</v>
       </c>
       <c r="BK7" t="n">
-        <v>-199</v>
+        <v>-0.7967608049845012</v>
       </c>
       <c r="BL7" t="n">
-        <v>139</v>
+        <v>0.06106032734321332</v>
       </c>
       <c r="BM7" t="n">
-        <v>-86.92857142857144</v>
+        <v>0.1389316823527349</v>
       </c>
       <c r="BN7" t="n">
-        <v>92.03571428571428</v>
+        <v>-1.113660644910638</v>
       </c>
       <c r="BO7" t="n">
-        <v>2</v>
+        <v>-1170630.297455954</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.5</v>
+        <v>-0.2436147186147186</v>
       </c>
       <c r="BQ7" t="n">
-        <v>0.2689075630252102</v>
+        <v>1.222213897213905</v>
       </c>
       <c r="BR7" t="n">
-        <v>0.0840336134453783</v>
-      </c>
-      <c r="BS7" t="inlineStr"/>
-      <c r="BT7" t="inlineStr"/>
+        <v>1.424403183023873</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>0.7011796682849329</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>1.841065878565875</v>
+      </c>
       <c r="BU7" t="n">
-        <v>0.5</v>
+        <v>-86.68256816282883</v>
       </c>
       <c r="BV7" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="BW7" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="BX7" t="n">
-        <v>5</v>
-      </c>
-      <c r="BY7" t="n">
-        <v>5.409722222222221</v>
-      </c>
-      <c r="BZ7" t="n">
-        <v>-0.5694444444444429</v>
-      </c>
-      <c r="CA7" t="n">
-        <v>6.571428571428573</v>
-      </c>
-      <c r="CB7" t="n">
-        <v>-22.44047619047619</v>
-      </c>
-      <c r="CC7" t="n">
-        <v>1.614214789552781</v>
-      </c>
-      <c r="CD7" t="n">
-        <v>-3.125570349122063</v>
-      </c>
-      <c r="CE7" t="n">
-        <v>-0.05520614954577219</v>
-      </c>
-      <c r="CF7" t="n">
-        <v>0.001068376068376068</v>
-      </c>
-      <c r="CG7" t="n">
-        <v>0.008368212744801477</v>
-      </c>
-      <c r="CH7" t="n">
-        <v>0.005919345640475256</v>
-      </c>
-      <c r="CI7" t="n">
-        <v>0.6666666666666667</v>
-      </c>
-      <c r="CJ7" t="n">
-        <v>0.6666666666666667</v>
-      </c>
-      <c r="CK7" t="n">
-        <v>0.05555555555555558</v>
-      </c>
-      <c r="CL7" t="n">
-        <v>-0.09027777777777779</v>
-      </c>
-      <c r="CM7" t="n">
-        <v>1.502411616161623</v>
-      </c>
-      <c r="CN7" t="inlineStr"/>
-      <c r="CO7" t="inlineStr"/>
-      <c r="CP7" t="inlineStr"/>
-      <c r="CQ7" t="inlineStr"/>
-      <c r="CR7" t="inlineStr"/>
-      <c r="CS7" t="inlineStr"/>
-      <c r="CT7" t="inlineStr"/>
-      <c r="CU7" t="inlineStr"/>
-      <c r="CV7" t="inlineStr"/>
-      <c r="CW7" t="inlineStr"/>
-      <c r="CX7" t="inlineStr"/>
-      <c r="CY7" t="inlineStr"/>
-      <c r="CZ7" t="inlineStr"/>
-      <c r="DA7" t="inlineStr"/>
-      <c r="DB7" t="inlineStr"/>
-      <c r="DC7" t="inlineStr"/>
-      <c r="DD7" t="inlineStr"/>
-      <c r="DE7" t="inlineStr"/>
-      <c r="DF7" t="inlineStr"/>
-      <c r="DG7" t="inlineStr"/>
-      <c r="DH7" t="inlineStr"/>
-      <c r="DI7" t="inlineStr"/>
+        <v>136668.9733877219</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -2758,242 +2171,177 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>0.9149999999999997</v>
+        <v>2.495</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.58</v>
+        <v>0.3574166666666667</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.2337916666666666</v>
+        <v>4</v>
       </c>
       <c r="R8" t="n">
-        <v>-0.1236250000000001</v>
+        <v>0.3529411764705883</v>
       </c>
       <c r="S8" t="n">
-        <v>1.666666666666667</v>
+        <v>3.333333333333333</v>
       </c>
       <c r="T8" t="n">
-        <v>-2.333333333333333</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1838235294117647</v>
+        <v>13</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.1691176470588236</v>
+        <v>1.856617647058824</v>
       </c>
       <c r="W8" t="n">
-        <v>0.833333333333333</v>
+        <v>3.5</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.5</v>
+        <v>-0.05882352941176472</v>
       </c>
       <c r="Y8" t="n">
-        <v>-1.1875</v>
+        <v>5</v>
       </c>
       <c r="Z8" t="n">
-        <v>-1.1875</v>
+        <v>0.1985294117647061</v>
       </c>
       <c r="AA8" t="n">
-        <v>5.833333333333334</v>
+        <v>14.49107744107744</v>
       </c>
       <c r="AB8" t="n">
-        <v>-7.166666666666666</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>0.9191176470588243</v>
-      </c>
+        <v>19.34590718073206</v>
+      </c>
+      <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="n">
-        <v>-0.9375</v>
+        <v>868.0773877594212</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.833333333333333</v>
+        <v>43</v>
       </c>
       <c r="AF8" t="n">
-        <v>-1.666666666666667</v>
+        <v>3.392857142857153</v>
       </c>
       <c r="AG8" t="n">
-        <v>-0.4595588235294117</v>
+        <v>44</v>
       </c>
       <c r="AH8" t="n">
-        <v>-0.400735294117647</v>
+        <v>10.59821428571428</v>
       </c>
       <c r="AI8" t="n">
-        <v>2.333333333333333</v>
+        <v>4.999999999999996</v>
       </c>
       <c r="AJ8" t="n">
-        <v>-2.666666666666667</v>
+        <v>5.38602941176471</v>
       </c>
       <c r="AK8" t="n">
-        <v>0.03308823529411775</v>
+        <v>-13</v>
       </c>
       <c r="AL8" t="n">
-        <v>-0.1654411764705883</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>5.266835016835016</v>
-      </c>
+        <v>-5.992647058823536</v>
+      </c>
+      <c r="AM8" t="inlineStr"/>
       <c r="AN8" t="n">
-        <v>-9.224242424242425</v>
+        <v>-13.39999999999998</v>
       </c>
       <c r="AO8" t="n">
-        <v>9.268325693591754</v>
+        <v>0.166666666666667</v>
       </c>
       <c r="AP8" t="n">
-        <v>-10.07758148714031</v>
+        <v>-0.04411764705882382</v>
       </c>
       <c r="AQ8" t="inlineStr"/>
-      <c r="AR8" t="inlineStr"/>
+      <c r="AR8" t="n">
+        <v>-0.1428571428571429</v>
+      </c>
       <c r="AS8" t="n">
-        <v>434.4315121758588</v>
+        <v>1.333333333333334</v>
       </c>
       <c r="AT8" t="n">
-        <v>-433.6458755835624</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>1</v>
-      </c>
+        <v>-6.867647058823529</v>
+      </c>
+      <c r="AU8" t="inlineStr"/>
       <c r="AV8" t="n">
-        <v>-42</v>
+        <v>1.109530542816877</v>
       </c>
       <c r="AW8" t="n">
-        <v>-8.776785714285708</v>
+        <v>-0.002347620952272117</v>
       </c>
       <c r="AX8" t="n">
-        <v>-12.16964285714286</v>
+        <v>0.02343697858948881</v>
       </c>
       <c r="AY8" t="n">
-        <v>13</v>
+        <v>0.5</v>
       </c>
       <c r="AZ8" t="n">
-        <v>-31</v>
+        <v>-0.1213235294117647</v>
       </c>
       <c r="BA8" t="n">
-        <v>8.026785714285715</v>
+        <v>-4.160148148148153</v>
       </c>
       <c r="BB8" t="n">
-        <v>-2.571428571428569</v>
+        <v>1152.660533910534</v>
       </c>
       <c r="BC8" t="n">
-        <v>-3.166666666666668</v>
+        <v>-7055.555555555555</v>
       </c>
       <c r="BD8" t="n">
-        <v>-8.166666666666664</v>
+        <v>8.766666666666666</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.926470588235297</v>
+        <v>0.02222222222222237</v>
       </c>
       <c r="BF8" t="n">
-        <v>-3.459558823529413</v>
+        <v>-5.084777777777781</v>
       </c>
       <c r="BG8" t="n">
-        <v>-6.5</v>
+        <v>1.340140856342543</v>
       </c>
       <c r="BH8" t="n">
-        <v>6.5</v>
+        <v>-720666.666666667</v>
       </c>
       <c r="BI8" t="n">
-        <v>-2.996323529411768</v>
+        <v>21.41111111111113</v>
       </c>
       <c r="BJ8" t="n">
-        <v>2.996323529411768</v>
-      </c>
-      <c r="BK8" t="inlineStr"/>
-      <c r="BL8" t="inlineStr"/>
+        <v>3.311724386724364</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>4.259690943043893</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>-0.739847272242244</v>
+      </c>
       <c r="BM8" t="n">
-        <v>-8.620512820512772</v>
+        <v>-0.1620821661998135</v>
       </c>
       <c r="BN8" t="n">
-        <v>4.779487179487205</v>
+        <v>2.664898989898987</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.8333333333333335</v>
+        <v>203668.7941843402</v>
       </c>
       <c r="BP8" t="n">
-        <v>0.6666666666666665</v>
+        <v>-0.05216450216450208</v>
       </c>
       <c r="BQ8" t="n">
-        <v>-0.2830882352941178</v>
+        <v>0.8255772005772002</v>
       </c>
       <c r="BR8" t="n">
-        <v>-0.2389705882352939</v>
-      </c>
-      <c r="BS8" t="inlineStr"/>
-      <c r="BT8" t="inlineStr"/>
+        <v>0.22</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>-1.398419367747096</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>-0.4637806637806605</v>
+      </c>
       <c r="BU8" t="n">
-        <v>-0.2142857142857143</v>
+        <v>-1836.431061313417</v>
       </c>
       <c r="BV8" t="n">
-        <v>-0.0714285714285714</v>
-      </c>
-      <c r="BW8" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="BX8" t="n">
-        <v>-1.833333333333334</v>
-      </c>
-      <c r="BY8" t="n">
-        <v>-3.75</v>
-      </c>
-      <c r="BZ8" t="n">
-        <v>3.117647058823529</v>
-      </c>
-      <c r="CA8" t="inlineStr"/>
-      <c r="CB8" t="inlineStr"/>
-      <c r="CC8" t="n">
-        <v>-0.8257298928883436</v>
-      </c>
-      <c r="CD8" t="n">
-        <v>-1.935260435705221</v>
-      </c>
-      <c r="CE8" t="n">
-        <v>-0.007542426147077314</v>
-      </c>
-      <c r="CF8" t="n">
-        <v>-0.005194805194805197</v>
-      </c>
-      <c r="CG8" t="n">
-        <v>0.003334736430559385</v>
-      </c>
-      <c r="CH8" t="n">
-        <v>-0.02010224215892942</v>
-      </c>
-      <c r="CI8" t="n">
-        <v>0</v>
-      </c>
-      <c r="CJ8" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="CK8" t="n">
-        <v>-0.04411764705882354</v>
-      </c>
-      <c r="CL8" t="n">
-        <v>0.07720588235294118</v>
-      </c>
-      <c r="CM8" t="n">
-        <v>-0.8393418310084968</v>
-      </c>
-      <c r="CN8" t="inlineStr"/>
-      <c r="CO8" t="inlineStr"/>
-      <c r="CP8" t="inlineStr"/>
-      <c r="CQ8" t="inlineStr"/>
-      <c r="CR8" t="inlineStr"/>
-      <c r="CS8" t="inlineStr"/>
-      <c r="CT8" t="inlineStr"/>
-      <c r="CU8" t="inlineStr"/>
-      <c r="CV8" t="inlineStr"/>
-      <c r="CW8" t="inlineStr"/>
-      <c r="CX8" t="inlineStr"/>
-      <c r="CY8" t="inlineStr"/>
-      <c r="CZ8" t="inlineStr"/>
-      <c r="DA8" t="inlineStr"/>
-      <c r="DB8" t="inlineStr"/>
-      <c r="DC8" t="inlineStr"/>
-      <c r="DD8" t="inlineStr"/>
-      <c r="DE8" t="inlineStr"/>
-      <c r="DF8" t="inlineStr"/>
-      <c r="DG8" t="inlineStr"/>
-      <c r="DH8" t="inlineStr"/>
-      <c r="DI8" t="inlineStr"/>
+        <v>2948543.47041847</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -3045,269 +2393,176 @@
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>0.5966666666666665</v>
+        <v>1.613333333333333</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.016666666666666</v>
+        <v>0.229607843137255</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.106437908496732</v>
+        <v>1</v>
       </c>
       <c r="R9" t="n">
-        <v>-0.336045751633987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S9" t="n">
-        <v>0.3333333333333333</v>
+        <v>2.666666666666667</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6666666666666665</v>
+        <v>-1.395424836601307</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1764705882352942</v>
+        <v>8.333333333333336</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.1393188854489165</v>
+        <v>-2.176470588235293</v>
       </c>
       <c r="W9" t="n">
-        <v>2</v>
+        <v>2.333333333333333</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.666666666666667</v>
+        <v>0.4334365325077401</v>
       </c>
       <c r="Y9" t="n">
-        <v>-1.075163398692811</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.3202614379084965</v>
+        <v>1.021671826625387</v>
       </c>
       <c r="AA9" t="n">
-        <v>4.333333333333333</v>
+        <v>16.23349567099567</v>
       </c>
       <c r="AB9" t="n">
-        <v>-4.000000000000002</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>-2.813725490196077</v>
-      </c>
+        <v>20.7141176225735</v>
+      </c>
+      <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="n">
-        <v>-0.6372549019607838</v>
+        <v>883.0782510807605</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.3333333333333334</v>
+        <v>14</v>
       </c>
       <c r="AF9" t="n">
-        <v>-2</v>
+        <v>16.76666666666667</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.148606811145511</v>
+        <v>35</v>
       </c>
       <c r="AH9" t="n">
-        <v>-0.2848297213622291</v>
+        <v>7.508333333333333</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>18.33333333333333</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>2.690402476780184</v>
       </c>
       <c r="AK9" t="n">
-        <v>0.5541795665634675</v>
+        <v>16</v>
       </c>
       <c r="AL9" t="n">
-        <v>-0.4674922600619196</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>4.928571428571429</v>
-      </c>
+        <v>-1.189542483660119</v>
+      </c>
+      <c r="AM9" t="inlineStr"/>
       <c r="AN9" t="n">
-        <v>-11.30492424242424</v>
+        <v>-48.89047619047619</v>
       </c>
       <c r="AO9" t="n">
-        <v>11.26153870639165</v>
+        <v>-3.333333333333333</v>
       </c>
       <c r="AP9" t="n">
-        <v>-9.452578916181857</v>
-      </c>
-      <c r="AQ9" t="inlineStr"/>
-      <c r="AR9" t="inlineStr"/>
+        <v>-1.090277777777778</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>-0.5</v>
+      </c>
       <c r="AS9" t="n">
-        <v>460.6923759362616</v>
+        <v>-8.000000000000002</v>
       </c>
       <c r="AT9" t="n">
-        <v>-422.385875144499</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>4</v>
-      </c>
+        <v>-5.204334365325082</v>
+      </c>
+      <c r="AU9" t="inlineStr"/>
       <c r="AV9" t="n">
-        <v>-10</v>
+        <v>1.665627743712083</v>
       </c>
       <c r="AW9" t="n">
-        <v>9.770833333333329</v>
+        <v>0.04286926994906622</v>
       </c>
       <c r="AX9" t="n">
-        <v>-6.995833333333337</v>
+        <v>0.006595534358273113</v>
       </c>
       <c r="AY9" t="n">
-        <v>21</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="AZ9" t="n">
-        <v>-14</v>
+        <v>0.1176470588235294</v>
       </c>
       <c r="BA9" t="n">
-        <v>-0.3041666666666671</v>
+        <v>2.817460317460331</v>
       </c>
       <c r="BB9" t="n">
-        <v>-7.8125</v>
+        <v>-1349.819877092604</v>
       </c>
       <c r="BC9" t="n">
-        <v>10.66666666666667</v>
+        <v>-15555.55555555555</v>
       </c>
       <c r="BD9" t="n">
-        <v>-7.666666666666664</v>
+        <v>-4.301587301587318</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.708978328173373</v>
+        <v>0.1587301587301591</v>
       </c>
       <c r="BF9" t="n">
-        <v>-1.981424148606811</v>
+        <v>-4.376984126984127</v>
       </c>
       <c r="BG9" t="n">
-        <v>8</v>
+        <v>-2.001235675657284</v>
       </c>
       <c r="BH9" t="n">
-        <v>-8</v>
+        <v>-1856746.031746032</v>
       </c>
       <c r="BI9" t="n">
-        <v>-0.5947712418300597</v>
+        <v>14.4126984126984</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.5947712418300597</v>
-      </c>
-      <c r="BK9" t="inlineStr"/>
-      <c r="BL9" t="inlineStr"/>
+        <v>1.263060754604879</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>0.6823762791304944</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>-2.967303154601225</v>
+      </c>
       <c r="BM9" t="n">
-        <v>-28.34285714285716</v>
+        <v>0</v>
       </c>
       <c r="BN9" t="n">
-        <v>20.54761904761904</v>
+        <v>-1.559944574420669</v>
       </c>
       <c r="BO9" t="n">
-        <v>-0.333333333333333</v>
+        <v>-604334.0089166118</v>
       </c>
       <c r="BP9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BQ9" t="n">
-        <v>-0.1527777777777777</v>
+        <v>-1.096812797088532</v>
       </c>
       <c r="BR9" t="n">
-        <v>0.9375</v>
+        <v>0.1587301587301591</v>
       </c>
       <c r="BS9" t="n">
-        <v>0</v>
+        <v>-0.6001194282154003</v>
       </c>
       <c r="BT9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU9" t="n">
-        <v>-0.25</v>
-      </c>
+        <v>1.544796772875809</v>
+      </c>
+      <c r="BU9" t="inlineStr"/>
       <c r="BV9" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="BW9" t="n">
-        <v>-6.000000000000002</v>
-      </c>
-      <c r="BX9" t="n">
-        <v>2</v>
-      </c>
-      <c r="BY9" t="n">
-        <v>-4.953560371517028</v>
-      </c>
-      <c r="BZ9" t="n">
-        <v>0.2507739938080533</v>
-      </c>
-      <c r="CA9" t="inlineStr"/>
-      <c r="CB9" t="inlineStr"/>
-      <c r="CC9" t="n">
-        <v>1.975198648523987</v>
-      </c>
-      <c r="CD9" t="n">
-        <v>0.3095709048119044</v>
-      </c>
-      <c r="CE9" t="n">
-        <v>0.05017921146953405</v>
-      </c>
-      <c r="CF9" t="n">
-        <v>0.007309941520467836</v>
-      </c>
-      <c r="CG9" t="n">
-        <v>0.006545213407907424</v>
-      </c>
-      <c r="CH9" t="n">
-        <v>-5.032095036568845e-05</v>
-      </c>
-      <c r="CI9" t="n">
-        <v>0</v>
-      </c>
-      <c r="CJ9" t="n">
-        <v>-0.6666666666666666</v>
-      </c>
-      <c r="CK9" t="n">
-        <v>-0.1269349845201238</v>
-      </c>
-      <c r="CL9" t="n">
-        <v>-0.2445820433436532</v>
-      </c>
-      <c r="CM9" t="n">
-        <v>-0.2854090354090459</v>
-      </c>
-      <c r="CN9" t="inlineStr"/>
-      <c r="CO9" t="n">
-        <v>-574442.438866192</v>
-      </c>
-      <c r="CP9" t="n">
-        <v>-2.072122162435463</v>
-      </c>
-      <c r="CQ9" t="inlineStr"/>
-      <c r="CR9" t="n">
-        <v>-1.647934081405936</v>
-      </c>
-      <c r="CS9" t="n">
-        <v>-0.1381944444444443</v>
-      </c>
-      <c r="CT9" t="inlineStr"/>
-      <c r="CU9" t="inlineStr"/>
-      <c r="CV9" t="inlineStr"/>
-      <c r="CW9" t="inlineStr"/>
-      <c r="CX9" t="n">
-        <v>0</v>
-      </c>
-      <c r="CY9" t="n">
-        <v>-2.306944444444454</v>
-      </c>
-      <c r="CZ9" t="inlineStr"/>
-      <c r="DA9" t="n">
-        <v>-654722.2222222222</v>
-      </c>
-      <c r="DB9" t="n">
-        <v>0.4695134114251758</v>
-      </c>
-      <c r="DC9" t="inlineStr"/>
-      <c r="DD9" t="inlineStr"/>
-      <c r="DE9" t="n">
-        <v>0</v>
-      </c>
-      <c r="DF9" t="n">
-        <v>0.5722222222221944</v>
-      </c>
-      <c r="DG9" t="n">
-        <v>-0.267136241848533</v>
-      </c>
-      <c r="DH9" t="inlineStr"/>
-      <c r="DI9" t="n">
-        <v>-1.364583333333343</v>
+        <v>-546856.7104872246</v>
       </c>
     </row>
     <row r="10">
@@ -3360,254 +2615,183 @@
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>0.4733333333333335</v>
+        <v>1.426666666666667</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.9533333333333333</v>
+        <v>1.359522058823529</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.7439338235294118</v>
+        <v>3</v>
       </c>
       <c r="R10" t="n">
-        <v>-0.6155882352941175</v>
+        <v>1.895833333333333</v>
       </c>
       <c r="S10" t="n">
-        <v>1.333333333333333</v>
+        <v>5.333333333333334</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.666666666666667</v>
+        <v>3.770833333333333</v>
       </c>
       <c r="U10" t="n">
-        <v>0.8194444444444444</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.076388888888889</v>
+        <v>7.770833333333332</v>
       </c>
       <c r="W10" t="n">
-        <v>3.333333333333333</v>
+        <v>2.666666666666667</v>
       </c>
       <c r="X10" t="n">
-        <v>-2</v>
+        <v>1.291666666666667</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.534722222222222</v>
+        <v>3</v>
       </c>
       <c r="Z10" t="n">
-        <v>-1.236111111111111</v>
+        <v>1.541666666666667</v>
       </c>
       <c r="AA10" t="n">
-        <v>3</v>
+        <v>15.19888167388167</v>
       </c>
       <c r="AB10" t="n">
-        <v>-2.666666666666666</v>
+        <v>17.55297816242734</v>
       </c>
       <c r="AC10" t="n">
-        <v>4.604166666666666</v>
+        <v>863.0573179033356</v>
       </c>
       <c r="AD10" t="n">
-        <v>-3.166666666666666</v>
+        <v>849.1877226677626</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.333333333333333</v>
+        <v>32</v>
       </c>
       <c r="AF10" t="n">
+        <v>25.05357142857142</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>30</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>16.01785714285714</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>6.666666666666664</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>5.333333333333336</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>12</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>7.513888888888886</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>90</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>66.98571428571432</v>
+      </c>
+      <c r="AO10" t="n">
         <v>-1.333333333333333</v>
       </c>
-      <c r="AG10" t="n">
-        <v>0.9305555555555556</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>-0.3611111111111112</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>1.333333333333333</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>-1.666666666666667</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>0.8472222222222222</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>-0.6944444444444444</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>7.896103896103896</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>-7.302777777777778</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>8.107616104655579</v>
-      </c>
       <c r="AP10" t="n">
-        <v>-9.445362057771758</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>432.0265486725664</v>
-      </c>
+        <v>-0.145833333333333</v>
+      </c>
+      <c r="AQ10" t="inlineStr"/>
       <c r="AR10" t="n">
-        <v>-431.0307692307692</v>
+        <v>-0.9333333333333333</v>
       </c>
       <c r="AS10" t="n">
-        <v>398.3697597851033</v>
+        <v>-1.333333333333334</v>
       </c>
       <c r="AT10" t="n">
-        <v>-450.8179628826593</v>
+        <v>-1.222222222222221</v>
       </c>
       <c r="AU10" t="n">
-        <v>22</v>
+        <v>-25.84559884559884</v>
       </c>
       <c r="AV10" t="n">
-        <v>-10</v>
+        <v>-2.672925535896542</v>
       </c>
       <c r="AW10" t="n">
-        <v>6.651785714285708</v>
+        <v>-0.08260636182134844</v>
       </c>
       <c r="AX10" t="n">
-        <v>-18.40178571428571</v>
+        <v>-0.01594106336285508</v>
       </c>
       <c r="AY10" t="n">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="AZ10" t="n">
-        <v>-4</v>
+        <v>0.4097222222222222</v>
       </c>
       <c r="BA10" t="n">
-        <v>6.919642857142854</v>
+        <v>-2.319444444444429</v>
       </c>
       <c r="BB10" t="n">
-        <v>-9.098214285714285</v>
+        <v>24872.94142404437</v>
       </c>
       <c r="BC10" t="n">
-        <v>4.333333333333329</v>
+        <v>15685.18518518519</v>
       </c>
       <c r="BD10" t="n">
-        <v>-2.333333333333336</v>
+        <v>-24.4074074074074</v>
       </c>
       <c r="BE10" t="n">
-        <v>2.402777777777779</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="BF10" t="n">
-        <v>-2.930555555555557</v>
+        <v>-2.569444444444443</v>
       </c>
       <c r="BG10" t="n">
-        <v>6</v>
+        <v>7.364615726895053</v>
       </c>
       <c r="BH10" t="n">
-        <v>-6</v>
+        <v>9208796.296296295</v>
       </c>
       <c r="BI10" t="n">
-        <v>3.756944444444443</v>
+        <v>-26.87037037037037</v>
       </c>
       <c r="BJ10" t="n">
-        <v>-3.756944444444443</v>
+        <v>-4.637184343434313</v>
       </c>
       <c r="BK10" t="n">
-        <v>14</v>
+        <v>1.135705242135828</v>
       </c>
       <c r="BL10" t="n">
-        <v>-76</v>
+        <v>6.768493045366284</v>
       </c>
       <c r="BM10" t="n">
-        <v>23.90952380952382</v>
+        <v>0.2661090362070757</v>
       </c>
       <c r="BN10" t="n">
-        <v>-43.0761904761905</v>
+        <v>7.476994949494937</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.3333333333333335</v>
+        <v>8557743.478787716</v>
       </c>
       <c r="BP10" t="n">
-        <v>1.666666666666667</v>
+        <v>0.4703030303030304</v>
       </c>
       <c r="BQ10" t="n">
-        <v>0.06944444444444464</v>
+        <v>8.799760101010094</v>
       </c>
       <c r="BR10" t="n">
-        <v>0.2152777777777777</v>
-      </c>
-      <c r="BS10" t="inlineStr"/>
-      <c r="BT10" t="inlineStr"/>
+        <v>-0.4814814814814814</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>-1.924816376355604</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>0.2106186868686848</v>
+      </c>
       <c r="BU10" t="n">
-        <v>-0.6666666666666667</v>
+        <v>17877.66439909297</v>
       </c>
       <c r="BV10" t="n">
-        <v>0.2666666666666666</v>
-      </c>
-      <c r="BW10" t="n">
-        <v>-0.3333333333333339</v>
-      </c>
-      <c r="BX10" t="n">
-        <v>1</v>
-      </c>
-      <c r="BY10" t="n">
-        <v>1.166666666666664</v>
-      </c>
-      <c r="BZ10" t="n">
-        <v>2.388888888888886</v>
-      </c>
-      <c r="CA10" t="n">
-        <v>-6.909090909090907</v>
-      </c>
-      <c r="CB10" t="n">
-        <v>18.93650793650794</v>
-      </c>
-      <c r="CC10" t="n">
-        <v>-1.236931585512867</v>
-      </c>
-      <c r="CD10" t="n">
-        <v>1.435993950383676</v>
-      </c>
-      <c r="CE10" t="n">
-        <v>-0.04511278195488722</v>
-      </c>
-      <c r="CF10" t="n">
-        <v>0.03749357986646122</v>
-      </c>
-      <c r="CG10" t="n">
-        <v>-0.004674997571059013</v>
-      </c>
-      <c r="CH10" t="n">
-        <v>0.01126606579179607</v>
-      </c>
-      <c r="CI10" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="CJ10" t="n">
-        <v>-0.6666666666666666</v>
-      </c>
-      <c r="CK10" t="n">
-        <v>0.08333333333333334</v>
-      </c>
-      <c r="CL10" t="n">
-        <v>-0.3263888888888889</v>
-      </c>
-      <c r="CM10" t="n">
-        <v>-0.2142135642135656</v>
-      </c>
-      <c r="CN10" t="inlineStr"/>
-      <c r="CO10" t="inlineStr"/>
-      <c r="CP10" t="inlineStr"/>
-      <c r="CQ10" t="inlineStr"/>
-      <c r="CR10" t="inlineStr"/>
-      <c r="CS10" t="inlineStr"/>
-      <c r="CT10" t="inlineStr"/>
-      <c r="CU10" t="inlineStr"/>
-      <c r="CV10" t="inlineStr"/>
-      <c r="CW10" t="inlineStr"/>
-      <c r="CX10" t="inlineStr"/>
-      <c r="CY10" t="inlineStr"/>
-      <c r="CZ10" t="inlineStr"/>
-      <c r="DA10" t="inlineStr"/>
-      <c r="DB10" t="inlineStr"/>
-      <c r="DC10" t="inlineStr"/>
-      <c r="DD10" t="inlineStr"/>
-      <c r="DE10" t="inlineStr"/>
-      <c r="DF10" t="inlineStr"/>
-      <c r="DG10" t="inlineStr"/>
-      <c r="DH10" t="inlineStr"/>
-      <c r="DI10" t="inlineStr"/>
+        <v>11441312.18434343</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -3659,263 +2843,198 @@
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>0.4700000000000002</v>
+        <v>0.696666666666667</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.2266666666666668</v>
+        <v>0.4731045751633984</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.3791830065359474</v>
+        <v>1</v>
       </c>
       <c r="R11" t="n">
-        <v>-0.09392156862745105</v>
+        <v>0.5</v>
       </c>
       <c r="S11" t="n">
-        <v>0.3333333333333334</v>
+        <v>0.833333333333333</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6666666666666667</v>
+        <v>1.787581699346406</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2777777777777777</v>
+        <v>4.666666666666666</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.2222222222222223</v>
+        <v>0.3954248366013076</v>
       </c>
       <c r="W11" t="n">
-        <v>0.5</v>
+        <v>-1.166666666666667</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.333333333333333</v>
+        <v>-0.5555555555555558</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.444444444444445</v>
+        <v>-1</v>
       </c>
       <c r="Z11" t="n">
-        <v>-0.3431372549019613</v>
+        <v>-0.1666666666666665</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.666666666666666</v>
+        <v>14.39148629148629</v>
       </c>
       <c r="AB11" t="n">
-        <v>-3</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>2.395424836601308</v>
-      </c>
+        <v>22.08237333630136</v>
+      </c>
+      <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="n">
-        <v>2</v>
+        <v>978.1111050666836</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.166666666666667</v>
+        <v>-22.9764705882353</v>
       </c>
       <c r="AG11" t="n">
-        <v>-0.3333333333333335</v>
+        <v>3</v>
       </c>
       <c r="AH11" t="n">
-        <v>0.2222222222222223</v>
+        <v>-3.478431372549018</v>
       </c>
       <c r="AI11" t="n">
-        <v>-0.5</v>
+        <v>16.66666666666667</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.5</v>
+        <v>1.166666666666671</v>
       </c>
       <c r="AK11" t="n">
-        <v>-0.2222222222222221</v>
+        <v>8.333333333333329</v>
       </c>
       <c r="AL11" t="n">
-        <v>-0.05555555555555558</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>7.576190476190476</v>
-      </c>
+        <v>-18.62091503267973</v>
+      </c>
+      <c r="AM11" t="inlineStr"/>
       <c r="AN11" t="n">
-        <v>-6.815295815295816</v>
+        <v>-210.0624999999999</v>
       </c>
       <c r="AO11" t="n">
-        <v>10.39966258300237</v>
+        <v>0.8333333333333335</v>
       </c>
       <c r="AP11" t="n">
-        <v>-11.68271075329899</v>
+        <v>-0.2847222222222223</v>
       </c>
       <c r="AQ11" t="inlineStr"/>
-      <c r="AR11" t="inlineStr"/>
+      <c r="AR11" t="n">
+        <v>0</v>
+      </c>
       <c r="AS11" t="n">
-        <v>505.8280759025849</v>
+        <v>0.4999999999999982</v>
       </c>
       <c r="AT11" t="n">
-        <v>-472.2830291640987</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>5</v>
-      </c>
+        <v>-2</v>
+      </c>
+      <c r="AU11" t="inlineStr"/>
       <c r="AV11" t="n">
-        <v>-13</v>
+        <v>7.027430855536034</v>
       </c>
       <c r="AW11" t="n">
-        <v>-11.95294117647059</v>
+        <v>0.06518289752357651</v>
       </c>
       <c r="AX11" t="n">
-        <v>11.02352941176471</v>
+        <v>0.02689583363929181</v>
       </c>
       <c r="AY11" t="n">
-        <v>17</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="AZ11" t="n">
-        <v>14</v>
+        <v>0.3888888888888889</v>
       </c>
       <c r="BA11" t="n">
-        <v>1.274509803921568</v>
+        <v>-5.168333333333351</v>
       </c>
       <c r="BB11" t="n">
-        <v>4.752941176470586</v>
+        <v>-21103.78086419753</v>
       </c>
       <c r="BC11" t="n">
-        <v>20.5</v>
+        <v>-51209.23076923077</v>
       </c>
       <c r="BD11" t="n">
-        <v>3.833333333333332</v>
+        <v>-52.60000000000002</v>
       </c>
       <c r="BE11" t="n">
-        <v>5.666666666666671</v>
+        <v>-1.163076923076924</v>
       </c>
       <c r="BF11" t="n">
-        <v>4.5</v>
+        <v>0.9512051282051246</v>
       </c>
       <c r="BG11" t="n">
-        <v>4.166666666666664</v>
+        <v>-3.533981573981578</v>
       </c>
       <c r="BH11" t="n">
-        <v>-4.166666666666664</v>
+        <v>-26914115.38461538</v>
       </c>
       <c r="BI11" t="n">
-        <v>-9.310457516339866</v>
+        <v>-55.1369230769231</v>
       </c>
       <c r="BJ11" t="n">
-        <v>9.310457516339866</v>
-      </c>
-      <c r="BK11" t="inlineStr"/>
-      <c r="BL11" t="inlineStr"/>
+        <v>-2.53611111111104</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>-2.713100233100278</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>-6.309208569208565</v>
+      </c>
       <c r="BM11" t="n">
-        <v>-124.0267857142857</v>
+        <v>0.02857364857364875</v>
       </c>
       <c r="BN11" t="n">
-        <v>86.03571428571428</v>
+        <v>-3.784027777777794</v>
       </c>
       <c r="BO11" t="n">
-        <v>0.5</v>
+        <v>-7336053.779553778</v>
       </c>
       <c r="BP11" t="n">
-        <v>-0.3333333333333335</v>
+        <v>0.2138888888888888</v>
       </c>
       <c r="BQ11" t="n">
-        <v>0.2847222222222223</v>
+        <v>-3.879166666666663</v>
       </c>
       <c r="BR11" t="n">
-        <v>0.5694444444444446</v>
-      </c>
-      <c r="BS11" t="inlineStr"/>
-      <c r="BT11" t="inlineStr"/>
+        <v>-0.6953846153846155</v>
+      </c>
+      <c r="BS11" t="n">
+        <v>-0.5777067377067411</v>
+      </c>
+      <c r="BT11" t="n">
+        <v>0.7854166666666664</v>
+      </c>
       <c r="BU11" t="n">
-        <v>0.5</v>
+        <v>-18169.35226389772</v>
       </c>
       <c r="BV11" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="BW11" t="n">
-        <v>2.666666666666666</v>
-      </c>
-      <c r="BX11" t="n">
-        <v>2.166666666666668</v>
-      </c>
-      <c r="BY11" t="n">
-        <v>3.111111111111107</v>
-      </c>
-      <c r="BZ11" t="n">
-        <v>5.111111111111107</v>
-      </c>
-      <c r="CA11" t="inlineStr"/>
-      <c r="CB11" t="inlineStr"/>
-      <c r="CC11" t="n">
-        <v>3.359339009783454</v>
-      </c>
-      <c r="CD11" t="n">
-        <v>-3.66809184575258</v>
-      </c>
-      <c r="CE11" t="n">
-        <v>0.02115158636897768</v>
-      </c>
-      <c r="CF11" t="n">
-        <v>-0.04403131115459882</v>
-      </c>
-      <c r="CG11" t="n">
-        <v>-0.001002559179439241</v>
-      </c>
-      <c r="CH11" t="n">
-        <v>-0.02789839281873106</v>
-      </c>
-      <c r="CI11" t="n">
-        <v>0</v>
-      </c>
-      <c r="CJ11" t="n">
-        <v>-0.3333333333333333</v>
-      </c>
-      <c r="CK11" t="n">
-        <v>0.2777777777777778</v>
-      </c>
-      <c r="CL11" t="n">
-        <v>-0.1111111111111111</v>
-      </c>
-      <c r="CM11" t="n">
-        <v>-0.06015151515150308</v>
-      </c>
-      <c r="CN11" t="inlineStr"/>
-      <c r="CO11" t="inlineStr"/>
-      <c r="CP11" t="inlineStr"/>
-      <c r="CQ11" t="inlineStr"/>
-      <c r="CR11" t="inlineStr"/>
-      <c r="CS11" t="inlineStr"/>
-      <c r="CT11" t="inlineStr"/>
-      <c r="CU11" t="inlineStr"/>
-      <c r="CV11" t="inlineStr"/>
-      <c r="CW11" t="inlineStr"/>
-      <c r="CX11" t="inlineStr"/>
-      <c r="CY11" t="inlineStr"/>
-      <c r="CZ11" t="inlineStr"/>
-      <c r="DA11" t="inlineStr"/>
-      <c r="DB11" t="inlineStr"/>
-      <c r="DC11" t="inlineStr"/>
-      <c r="DD11" t="inlineStr"/>
-      <c r="DE11" t="inlineStr"/>
-      <c r="DF11" t="inlineStr"/>
-      <c r="DG11" t="inlineStr"/>
-      <c r="DH11" t="inlineStr"/>
-      <c r="DI11" t="inlineStr"/>
+        <v>-8849739.583333334</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>h8K6HUFF</t>
+          <t>vPIEF8pS</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
         <v>45585.5</v>
       </c>
       <c r="C12" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D12" t="n">
         <v>133</v>
       </c>
       <c r="E12" t="n">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="F12" t="n">
-        <v>579</v>
+        <v>292</v>
       </c>
       <c r="G12" t="n">
         <v>55</v>
@@ -3937,275 +3056,190 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>272</v>
+        <v>243</v>
       </c>
       <c r="M12" t="n">
-        <v>234</v>
+        <v>32</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.2866666666666668</v>
+        <v>1.15</v>
       </c>
       <c r="P12" t="n">
-        <v>0.07833333333333359</v>
+        <v>0.6090441176470589</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.245625</v>
+        <v>1</v>
       </c>
       <c r="R12" t="n">
-        <v>-0.7668749999999998</v>
+        <v>0.7058823529411766</v>
       </c>
       <c r="S12" t="n">
-        <v>0.5</v>
+        <v>4</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5</v>
+        <v>1.235294117647059</v>
       </c>
       <c r="U12" t="n">
-        <v>0.7647058823529411</v>
+        <v>5.666666666666668</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.6470588235294118</v>
+        <v>4</v>
       </c>
       <c r="W12" t="n">
-        <v>-2.166666666666667</v>
+        <v>0.3333333333333331</v>
       </c>
       <c r="X12" t="n">
-        <v>0.166666666666667</v>
+        <v>-0.3205882352941174</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.867647058823529</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>-1.525735294117647</v>
+        <v>-0.7588235294117647</v>
       </c>
       <c r="AA12" t="n">
-        <v>-0.6666666666666661</v>
+        <v>12.22146464646465</v>
       </c>
       <c r="AB12" t="n">
-        <v>-2.5</v>
+        <v>16.16867368502317</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.992647058823529</v>
+        <v>851.0542233885517</v>
       </c>
       <c r="AD12" t="n">
-        <v>-4.926470588235293</v>
+        <v>899.0605418092503</v>
       </c>
       <c r="AE12" t="n">
-        <v>-0.8333333333333335</v>
+        <v>40</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.1666666666666667</v>
+        <v>6.9375</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.5294117647058822</v>
+        <v>5.5</v>
       </c>
       <c r="AH12" t="n">
-        <v>-0.8823529411764706</v>
+        <v>12.5</v>
       </c>
       <c r="AI12" t="n">
-        <v>-0.8333333333333335</v>
+        <v>15.66666666666667</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.166666666666667</v>
+        <v>3.355882352941174</v>
       </c>
       <c r="AK12" t="n">
-        <v>0.9999999999999998</v>
+        <v>11.33333333333334</v>
       </c>
       <c r="AL12" t="n">
-        <v>-0.9411764705882354</v>
+        <v>0.8235294117646959</v>
       </c>
       <c r="AM12" t="n">
-        <v>11.50512820512821</v>
+        <v>119</v>
       </c>
       <c r="AN12" t="n">
-        <v>-11.14715608465609</v>
+        <v>-9.133333333333326</v>
       </c>
       <c r="AO12" t="n">
-        <v>10.90354699099958</v>
+        <v>2.666666666666667</v>
       </c>
       <c r="AP12" t="n">
-        <v>-7.261091049527098</v>
+        <v>0.9999999999999996</v>
       </c>
       <c r="AQ12" t="n">
-        <v>570.0346534653465</v>
+        <v>1</v>
       </c>
       <c r="AR12" t="n">
-        <v>-567.0416666666666</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="AS12" t="n">
-        <v>437.2449444882971</v>
+        <v>-4.333333333333334</v>
       </c>
       <c r="AT12" t="n">
-        <v>-420.7210156827956</v>
+        <v>5.938235294117646</v>
       </c>
       <c r="AU12" t="n">
-        <v>10</v>
+        <v>-4.67122351332878</v>
       </c>
       <c r="AV12" t="n">
-        <v>4.5</v>
+        <v>-3.379994163467748</v>
       </c>
       <c r="AW12" t="n">
-        <v>29.69166666666666</v>
+        <v>-0.02784178466970873</v>
       </c>
       <c r="AX12" t="n">
-        <v>-5.995833333333337</v>
+        <v>0.03145942709036465</v>
       </c>
       <c r="AY12" t="n">
-        <v>24</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="AZ12" t="n">
-        <v>-4.5</v>
+        <v>0.2411764705882353</v>
       </c>
       <c r="BA12" t="n">
-        <v>20.7125</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>-4.899999999999999</v>
-      </c>
+        <v>-0.231349206349222</v>
+      </c>
+      <c r="BB12" t="inlineStr"/>
       <c r="BC12" t="n">
-        <v>9.5</v>
+        <v>26227.27272727273</v>
       </c>
       <c r="BD12" t="n">
-        <v>4.333333333333336</v>
+        <v>5.565476190476204</v>
       </c>
       <c r="BE12" t="n">
-        <v>-20.58823529411765</v>
+        <v>-0.1309523809523809</v>
       </c>
       <c r="BF12" t="n">
-        <v>-26.47058823529412</v>
+        <v>-0.08968253968253492</v>
       </c>
       <c r="BG12" t="n">
-        <v>-5.833333333333336</v>
+        <v>6.094886910240689</v>
       </c>
       <c r="BH12" t="n">
-        <v>5.833333333333336</v>
+        <v>8236607.142857143</v>
       </c>
       <c r="BI12" t="n">
-        <v>5.805147058823529</v>
+        <v>4.976190476190482</v>
       </c>
       <c r="BJ12" t="n">
-        <v>-5.805147058823529</v>
+        <v>2.261270442520384</v>
       </c>
       <c r="BK12" t="n">
-        <v>-178</v>
+        <v>-0.9575889889818541</v>
       </c>
       <c r="BL12" t="n">
-        <v>131</v>
+        <v>2.37392463277115</v>
       </c>
       <c r="BM12" t="n">
-        <v>90.14285714285717</v>
+        <v>0</v>
       </c>
       <c r="BN12" t="n">
-        <v>-6.508928571428555</v>
+        <v>5.900076283670032</v>
       </c>
       <c r="BO12" t="n">
-        <v>0.8333333333333333</v>
+        <v>1759844.137796214</v>
       </c>
       <c r="BP12" t="n">
-        <v>-1.333333333333333</v>
+        <v>0</v>
       </c>
       <c r="BQ12" t="n">
-        <v>-0.9916666666666667</v>
+        <v>-0.06655017436267485</v>
       </c>
       <c r="BR12" t="n">
-        <v>0.3041666666666667</v>
-      </c>
-      <c r="BS12" t="inlineStr"/>
-      <c r="BT12" t="inlineStr"/>
-      <c r="BU12" t="n">
-        <v>-0.75</v>
-      </c>
+        <v>-0.1309523809523809</v>
+      </c>
+      <c r="BS12" t="n">
+        <v>-3.110993051066579</v>
+      </c>
+      <c r="BT12" t="n">
+        <v>-5.163096365440108</v>
+      </c>
+      <c r="BU12" t="inlineStr"/>
       <c r="BV12" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="BW12" t="n">
-        <v>6.666666666666666</v>
-      </c>
-      <c r="BX12" t="n">
-        <v>4.666666666666666</v>
-      </c>
-      <c r="BY12" t="n">
-        <v>4.117647058823529</v>
-      </c>
-      <c r="BZ12" t="n">
-        <v>5.764705882352942</v>
-      </c>
-      <c r="CA12" t="n">
-        <v>-32.53174603174602</v>
-      </c>
-      <c r="CB12" t="n">
-        <v>-9.350649350649352</v>
-      </c>
-      <c r="CC12" t="n">
-        <v>-2.783078009544985</v>
-      </c>
-      <c r="CD12" t="n">
-        <v>1.452384001430049</v>
-      </c>
-      <c r="CE12" t="n">
-        <v>0.03899419729206964</v>
-      </c>
-      <c r="CF12" t="n">
-        <v>-0.0517114162738266</v>
-      </c>
-      <c r="CG12" t="n">
-        <v>-0.02443249040090192</v>
-      </c>
-      <c r="CH12" t="n">
-        <v>-0.007921616824987272</v>
-      </c>
-      <c r="CI12" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="CJ12" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="CK12" t="n">
-        <v>0.2941176470588235</v>
-      </c>
-      <c r="CL12" t="n">
-        <v>0.05882352941176472</v>
-      </c>
-      <c r="CM12" t="n">
-        <v>-7.369191919191906</v>
-      </c>
-      <c r="CN12" t="inlineStr"/>
-      <c r="CO12" t="n">
-        <v>-757402.9771398194</v>
-      </c>
-      <c r="CP12" t="n">
-        <v>-0.2351826536037152</v>
-      </c>
-      <c r="CQ12" t="inlineStr"/>
-      <c r="CR12" t="n">
-        <v>-5.746164654059399</v>
-      </c>
-      <c r="CS12" t="inlineStr"/>
-      <c r="CT12" t="inlineStr"/>
-      <c r="CU12" t="inlineStr"/>
-      <c r="CV12" t="inlineStr"/>
-      <c r="CW12" t="inlineStr"/>
-      <c r="CX12" t="inlineStr"/>
-      <c r="CY12" t="inlineStr"/>
-      <c r="CZ12" t="inlineStr"/>
-      <c r="DA12" t="inlineStr"/>
-      <c r="DB12" t="n">
-        <v>4.119552669552668</v>
-      </c>
-      <c r="DC12" t="inlineStr"/>
-      <c r="DD12" t="inlineStr"/>
-      <c r="DE12" t="n">
-        <v>0</v>
-      </c>
-      <c r="DF12" t="inlineStr"/>
-      <c r="DG12" t="n">
-        <v>-5.52950178476496</v>
-      </c>
-      <c r="DH12" t="inlineStr"/>
-      <c r="DI12" t="inlineStr"/>
+        <v>2334251.518157769</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -4257,279 +3291,206 @@
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>0.1066666666666665</v>
+        <v>0.623333333333333</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.5166666666666665</v>
+        <v>-0.1018749999999999</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.1622039473684209</v>
+        <v>1</v>
       </c>
       <c r="R13" t="n">
-        <v>-0.06032894736842098</v>
+        <v>0.03750000000000009</v>
       </c>
       <c r="S13" t="n">
-        <v>0.6666666666666667</v>
+        <v>2.333333333333333</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.3333333333333333</v>
+        <v>0.02499999999999947</v>
       </c>
       <c r="U13" t="n">
-        <v>0.05000000000000004</v>
+        <v>7.000000000000002</v>
       </c>
       <c r="V13" t="n">
-        <v>0.01249999999999996</v>
+        <v>3.35</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.666666666666667</v>
+        <v>2.220446049250313e-16</v>
       </c>
       <c r="X13" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="Y13" t="n">
-        <v>-0.1375000000000002</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>-0.1624999999999996</v>
+        <v>-1.575</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.3333333333333339</v>
+        <v>18.05397426647427</v>
       </c>
       <c r="AB13" t="n">
-        <v>-6.666666666666668</v>
+        <v>19.22931619308409</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.5374999999999996</v>
+        <v>942.063710754843</v>
       </c>
       <c r="AD13" t="n">
-        <v>-2.8125</v>
+        <v>964.7961081486393</v>
       </c>
       <c r="AE13" t="n">
-        <v>0.3333333333333335</v>
+        <v>-37</v>
       </c>
       <c r="AF13" t="n">
+        <v>2.764912280701765</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>10.80701754385964</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>3.000000000000004</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>4.912499999999994</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>6</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>-7.025000000000006</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>-12</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>-96.11111111111114</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>3.000000000000001</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>0.2361111111111112</v>
+      </c>
+      <c r="AQ13" t="n">
         <v>0.3333333333333333</v>
       </c>
-      <c r="AG13" t="n">
-        <v>-0.675</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>0.325</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>-0.7</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>0.875</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>11.55787037037037</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>-6.496103896103896</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>10.48894446921972</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>-8.740371723864371</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>372.0416666666667</v>
-      </c>
       <c r="AR13" t="n">
-        <v>-570.0220440881764</v>
+        <v>0.5</v>
       </c>
       <c r="AS13" t="n">
-        <v>475.4789564311403</v>
+        <v>13</v>
       </c>
       <c r="AT13" t="n">
-        <v>-489.317151717499</v>
+        <v>9.5</v>
       </c>
       <c r="AU13" t="n">
-        <v>-1</v>
+        <v>-89.46428571428572</v>
       </c>
       <c r="AV13" t="n">
-        <v>36</v>
+        <v>-4.897598549872562</v>
       </c>
       <c r="AW13" t="n">
-        <v>5.936842105263167</v>
+        <v>-0.009408741902962953</v>
       </c>
       <c r="AX13" t="n">
-        <v>3.171929824561403</v>
+        <v>0.03421637940234924</v>
       </c>
       <c r="AY13" t="n">
-        <v>20.5</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="AZ13" t="n">
-        <v>17</v>
+        <v>-0.1625</v>
       </c>
       <c r="BA13" t="n">
-        <v>10.51228070175438</v>
+        <v>0.6411282051282399</v>
       </c>
       <c r="BB13" t="n">
-        <v>-0.2947368421052587</v>
+        <v>-9217.794011544011</v>
       </c>
       <c r="BC13" t="n">
-        <v>5.333333333333336</v>
+        <v>-19238.46153846153</v>
       </c>
       <c r="BD13" t="n">
-        <v>2.333333333333332</v>
+        <v>-27.27846153846156</v>
       </c>
       <c r="BE13" t="n">
-        <v>5.799999999999997</v>
+        <v>-0.5846153846153848</v>
       </c>
       <c r="BF13" t="n">
-        <v>0.8875000000000028</v>
+        <v>1.26528205128205</v>
       </c>
       <c r="BG13" t="n">
-        <v>3</v>
+        <v>-3.506343503310418</v>
       </c>
       <c r="BH13" t="n">
-        <v>-3</v>
+        <v>-13814000</v>
       </c>
       <c r="BI13" t="n">
-        <v>-3.512500000000003</v>
+        <v>-35.38923076923078</v>
       </c>
       <c r="BJ13" t="n">
-        <v>3.512500000000003</v>
+        <v>-2.753651996151973</v>
       </c>
       <c r="BK13" t="n">
-        <v>71</v>
+        <v>1.669127070505766</v>
       </c>
       <c r="BL13" t="n">
-        <v>83</v>
+        <v>-1.899572166667767</v>
       </c>
       <c r="BM13" t="n">
-        <v>-62.38888888888891</v>
+        <v>-0.1075786822110349</v>
       </c>
       <c r="BN13" t="n">
-        <v>33.72222222222223</v>
+        <v>-2.812839706589727</v>
       </c>
       <c r="BO13" t="n">
-        <v>-0.333333333333333</v>
+        <v>-3636399.219205133</v>
       </c>
       <c r="BP13" t="n">
-        <v>-3.333333333333334</v>
+        <v>0.04325336700336724</v>
       </c>
       <c r="BQ13" t="n">
-        <v>-0.2916666666666665</v>
+        <v>-2.077320226070228</v>
       </c>
       <c r="BR13" t="n">
-        <v>-0.5277777777777777</v>
+        <v>-0.2953846153846156</v>
       </c>
       <c r="BS13" t="n">
-        <v>0.1666666666666667</v>
+        <v>2.780382777625427</v>
       </c>
       <c r="BT13" t="n">
-        <v>-0.1666666666666666</v>
+        <v>0.8230579605579571</v>
       </c>
       <c r="BU13" t="n">
-        <v>0.1666666666666667</v>
+        <v>-7174.325479349991</v>
       </c>
       <c r="BV13" t="n">
-        <v>-0.3333333333333334</v>
-      </c>
-      <c r="BW13" t="n">
-        <v>4.333333333333334</v>
-      </c>
-      <c r="BX13" t="n">
-        <v>-8.666666666666666</v>
-      </c>
-      <c r="BY13" t="n">
-        <v>0.1749999999999972</v>
-      </c>
-      <c r="BZ13" t="n">
-        <v>-9.325000000000003</v>
-      </c>
-      <c r="CA13" t="n">
-        <v>-43.57142857142858</v>
-      </c>
-      <c r="CB13" t="n">
-        <v>45.89285714285714</v>
-      </c>
-      <c r="CC13" t="n">
-        <v>-1.354529717010276</v>
-      </c>
-      <c r="CD13" t="n">
-        <v>3.543068832862286</v>
-      </c>
-      <c r="CE13" t="n">
-        <v>-0.05860488709310664</v>
-      </c>
-      <c r="CF13" t="n">
-        <v>-0.04919614519014369</v>
-      </c>
-      <c r="CG13" t="n">
-        <v>0.001149639935408113</v>
-      </c>
-      <c r="CH13" t="n">
-        <v>-0.03306673946694113</v>
-      </c>
-      <c r="CI13" t="n">
-        <v>0</v>
-      </c>
-      <c r="CJ13" t="n">
-        <v>-0.6666666666666666</v>
-      </c>
-      <c r="CK13" t="n">
-        <v>-0.0625</v>
-      </c>
-      <c r="CL13" t="n">
-        <v>0.09999999999999998</v>
-      </c>
-      <c r="CM13" t="n">
-        <v>0.4784473523109938</v>
-      </c>
-      <c r="CN13" t="inlineStr"/>
-      <c r="CO13" t="inlineStr"/>
-      <c r="CP13" t="inlineStr"/>
-      <c r="CQ13" t="inlineStr"/>
-      <c r="CR13" t="inlineStr"/>
-      <c r="CS13" t="inlineStr"/>
-      <c r="CT13" t="inlineStr"/>
-      <c r="CU13" t="inlineStr"/>
-      <c r="CV13" t="inlineStr"/>
-      <c r="CW13" t="inlineStr"/>
-      <c r="CX13" t="inlineStr"/>
-      <c r="CY13" t="inlineStr"/>
-      <c r="CZ13" t="inlineStr"/>
-      <c r="DA13" t="inlineStr"/>
-      <c r="DB13" t="inlineStr"/>
-      <c r="DC13" t="inlineStr"/>
-      <c r="DD13" t="inlineStr"/>
-      <c r="DE13" t="inlineStr"/>
-      <c r="DF13" t="inlineStr"/>
-      <c r="DG13" t="inlineStr"/>
-      <c r="DH13" t="inlineStr"/>
-      <c r="DI13" t="inlineStr"/>
+        <v>-4688518.879268879</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>vPIEF8pS</t>
+          <t>h8K6HUFF</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
         <v>45585.5</v>
       </c>
       <c r="C14" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D14" t="n">
         <v>133</v>
       </c>
       <c r="E14" t="n">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="F14" t="n">
-        <v>292</v>
+        <v>579</v>
       </c>
       <c r="G14" t="n">
         <v>55</v>
@@ -4551,267 +3512,190 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>243</v>
+        <v>272</v>
       </c>
       <c r="M14" t="n">
-        <v>32</v>
+        <v>234</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>0.7266666666666667</v>
+        <v>-0.3650000000000004</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.4233333333333333</v>
+        <v>1.0125</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.2203308823529413</v>
+        <v>1</v>
       </c>
       <c r="R14" t="n">
-        <v>-0.3887132352941176</v>
+        <v>1.411764705882353</v>
       </c>
       <c r="S14" t="n">
-        <v>0.6666666666666667</v>
+        <v>-2.333333333333334</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.3333333333333334</v>
+        <v>2.393382352941176</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3205882352941178</v>
+        <v>1.833333333333334</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.3852941176470588</v>
+        <v>6.919117647058822</v>
       </c>
       <c r="W14" t="n">
-        <v>1.666666666666667</v>
+        <v>-1</v>
       </c>
       <c r="X14" t="n">
-        <v>-2.333333333333333</v>
+        <v>1.411764705882353</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.5882352941176472</v>
+        <v>-2</v>
       </c>
       <c r="Z14" t="n">
-        <v>-0.6470588235294121</v>
+        <v>1.941176470588235</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.3333333333333339</v>
+        <v>22.65228428978429</v>
       </c>
       <c r="AB14" t="n">
-        <v>-5.333333333333334</v>
+        <v>18.16463804052668</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.117647058823529</v>
+        <v>1137.076320132013</v>
       </c>
       <c r="AD14" t="n">
-        <v>-1.882352941176471</v>
+        <v>857.9659601710927</v>
       </c>
       <c r="AE14" t="n">
-        <v>0.6666666666666666</v>
+        <v>5.5</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.3333333333333335</v>
+        <v>35.6875</v>
       </c>
       <c r="AG14" t="n">
-        <v>-0.1411764705882352</v>
+        <v>28.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>0.1794117647058822</v>
+        <v>25.6125</v>
       </c>
       <c r="AI14" t="n">
-        <v>0.3333333333333334</v>
+        <v>5.166666666666664</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0.3333333333333333</v>
+        <v>5.882352941176467</v>
       </c>
       <c r="AK14" t="n">
-        <v>-0.3764705882352941</v>
+        <v>-11.66666666666667</v>
       </c>
       <c r="AL14" t="n">
-        <v>0.3823529411764706</v>
+        <v>11.61029411764706</v>
       </c>
       <c r="AM14" t="n">
-        <v>7.688888888888888</v>
+        <v>-309</v>
       </c>
       <c r="AN14" t="n">
-        <v>-4.532575757575757</v>
+        <v>96.65178571428572</v>
       </c>
       <c r="AO14" t="n">
-        <v>8.542339724865677</v>
+        <v>2.166666666666667</v>
       </c>
       <c r="AP14" t="n">
-        <v>-7.62633396015749</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>419.0307692307692</v>
-      </c>
+        <v>-1.295833333333333</v>
+      </c>
+      <c r="AQ14" t="inlineStr"/>
       <c r="AR14" t="n">
-        <v>-432.0234541577825</v>
+        <v>-1.5</v>
       </c>
       <c r="AS14" t="n">
-        <v>460.7645967968647</v>
+        <v>2</v>
       </c>
       <c r="AT14" t="n">
-        <v>-438.2959450123855</v>
+        <v>-1.647058823529413</v>
       </c>
       <c r="AU14" t="n">
-        <v>17.5</v>
+        <v>-23.18109668109667</v>
       </c>
       <c r="AV14" t="n">
-        <v>-22.5</v>
+        <v>-4.235462010975034</v>
       </c>
       <c r="AW14" t="n">
-        <v>11.8125</v>
+        <v>0.09070561356589624</v>
       </c>
       <c r="AX14" t="n">
-        <v>4.875</v>
+        <v>-0.01651087357591465</v>
       </c>
       <c r="AY14" t="n">
-        <v>-0.5</v>
+        <v>0</v>
       </c>
       <c r="AZ14" t="n">
-        <v>-6</v>
+        <v>0.2352941176470588</v>
       </c>
       <c r="BA14" t="n">
-        <v>7.875</v>
+        <v>6.647714285714272</v>
       </c>
       <c r="BB14" t="n">
-        <v>-4.625</v>
+        <v>-12166.32924068269</v>
       </c>
       <c r="BC14" t="n">
-        <v>5.666666666666671</v>
+        <v>-11222.22222222222</v>
       </c>
       <c r="BD14" t="n">
-        <v>-10</v>
+        <v>62.11428571428573</v>
       </c>
       <c r="BE14" t="n">
-        <v>28.93235294117647</v>
+        <v>0.9142857142857144</v>
       </c>
       <c r="BF14" t="n">
-        <v>25.5764705882353</v>
+        <v>2.605809523809526</v>
       </c>
       <c r="BG14" t="n">
-        <v>5.666666666666664</v>
+        <v>-3.756669541819917</v>
       </c>
       <c r="BH14" t="n">
-        <v>-5.666666666666671</v>
+        <v>-681714.2857142859</v>
       </c>
       <c r="BI14" t="n">
-        <v>0.4117647058823479</v>
+        <v>65.91428571428571</v>
       </c>
       <c r="BJ14" t="n">
-        <v>-0.4117647058823479</v>
+        <v>-3.79635874877809</v>
       </c>
       <c r="BK14" t="n">
-        <v>88</v>
+        <v>-4.504008994347373</v>
       </c>
       <c r="BL14" t="n">
-        <v>-31</v>
+        <v>-4.0311686684243</v>
       </c>
       <c r="BM14" t="n">
-        <v>4.799999999999955</v>
+        <v>0</v>
       </c>
       <c r="BN14" t="n">
-        <v>13.93333333333328</v>
+        <v>-6.950627240143376</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.333333333333333</v>
+        <v>-1574543.881348393</v>
       </c>
       <c r="BP14" t="n">
-        <v>-1.333333333333333</v>
+        <v>-0.125</v>
       </c>
       <c r="BQ14" t="n">
-        <v>0.9411764705882351</v>
+        <v>-4.828535353535344</v>
       </c>
       <c r="BR14" t="n">
-        <v>-0.0588235294117645</v>
+        <v>0.9942857142857144</v>
       </c>
       <c r="BS14" t="n">
-        <v>0</v>
+        <v>0.05987219130075871</v>
       </c>
       <c r="BT14" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BU14" t="n">
-        <v>0.3333333333333333</v>
-      </c>
+        <v>0.7018572825024449</v>
+      </c>
+      <c r="BU14" t="inlineStr"/>
       <c r="BV14" t="n">
-        <v>-0.3333333333333334</v>
-      </c>
-      <c r="BW14" t="n">
-        <v>-3</v>
-      </c>
-      <c r="BX14" t="n">
-        <v>1.333333333333334</v>
-      </c>
-      <c r="BY14" t="n">
-        <v>10.88235294117647</v>
-      </c>
-      <c r="BZ14" t="n">
-        <v>4.944117647058825</v>
-      </c>
-      <c r="CA14" t="n">
-        <v>6.601503759398494</v>
-      </c>
-      <c r="CB14" t="n">
-        <v>11.27272727272727</v>
-      </c>
-      <c r="CC14" t="n">
-        <v>-1.571739150485717</v>
-      </c>
-      <c r="CD14" t="n">
-        <v>1.808255012982031</v>
-      </c>
-      <c r="CE14" t="n">
-        <v>-0.00359429303091275</v>
-      </c>
-      <c r="CF14" t="n">
-        <v>0.02424749163879598</v>
-      </c>
-      <c r="CG14" t="n">
-        <v>0.02081111118892805</v>
-      </c>
-      <c r="CH14" t="n">
-        <v>-0.0106483159014366</v>
-      </c>
-      <c r="CI14" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="CJ14" t="n">
-        <v>-0.3333333333333333</v>
-      </c>
-      <c r="CK14" t="n">
-        <v>0.08529411764705883</v>
-      </c>
-      <c r="CL14" t="n">
-        <v>-0.1558823529411765</v>
-      </c>
-      <c r="CM14" t="n">
-        <v>6.573720538720536</v>
-      </c>
-      <c r="CN14" t="inlineStr"/>
-      <c r="CO14" t="inlineStr"/>
-      <c r="CP14" t="inlineStr"/>
-      <c r="CQ14" t="inlineStr"/>
-      <c r="CR14" t="inlineStr"/>
-      <c r="CS14" t="inlineStr"/>
-      <c r="CT14" t="inlineStr"/>
-      <c r="CU14" t="inlineStr"/>
-      <c r="CV14" t="inlineStr"/>
-      <c r="CW14" t="inlineStr"/>
-      <c r="CX14" t="inlineStr"/>
-      <c r="CY14" t="inlineStr"/>
-      <c r="CZ14" t="inlineStr"/>
-      <c r="DA14" t="inlineStr"/>
-      <c r="DB14" t="inlineStr"/>
-      <c r="DC14" t="inlineStr"/>
-      <c r="DD14" t="inlineStr"/>
-      <c r="DE14" t="inlineStr"/>
-      <c r="DF14" t="inlineStr"/>
-      <c r="DG14" t="inlineStr"/>
-      <c r="DH14" t="inlineStr"/>
-      <c r="DI14" t="inlineStr"/>
+        <v>-4847900.37471489</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
@@ -4863,242 +3747,175 @@
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>1.01</v>
+        <v>-0.4299999999999998</v>
       </c>
       <c r="P15" t="n">
-        <v>1.44</v>
+        <v>0.0874166666666667</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.1126249999999998</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0.02520833333333306</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S15" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="T15" t="n">
-        <v>0.5</v>
+        <v>0.9294117647058817</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2430555555555556</v>
+        <v>6.5</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.09027777777777768</v>
+        <v>3.003921568627451</v>
       </c>
       <c r="W15" t="n">
-        <v>4</v>
+        <v>-1</v>
       </c>
       <c r="X15" t="n">
-        <v>2</v>
+        <v>-0.5347222222222223</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.454901960784313</v>
+        <v>-1.5</v>
       </c>
       <c r="Z15" t="n">
-        <v>-0.4745098039215687</v>
+        <v>-1.729166666666667</v>
       </c>
       <c r="AA15" t="n">
-        <v>8.5</v>
+        <v>14.30400432900433</v>
       </c>
       <c r="AB15" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1.494117647058824</v>
-      </c>
+        <v>18.69912390699542</v>
+      </c>
+      <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="n">
-        <v>-1.509803921568627</v>
+        <v>986.1380862058272</v>
       </c>
       <c r="AE15" t="n">
-        <v>0.5</v>
+        <v>30</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.5</v>
+        <v>-7.714285714285708</v>
       </c>
       <c r="AG15" t="n">
-        <v>-0.5416666666666667</v>
+        <v>33</v>
       </c>
       <c r="AH15" t="n">
-        <v>-0.00694444444444442</v>
+        <v>4.589285714285715</v>
       </c>
       <c r="AI15" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>2.305555555555557</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>-14</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>-14.34509803921569</v>
+      </c>
+      <c r="AM15" t="inlineStr"/>
+      <c r="AN15" t="n">
+        <v>-140.6057692307692</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>0.6095238095238094</v>
+      </c>
+      <c r="AQ15" t="inlineStr"/>
+      <c r="AR15" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>-4</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>3.673611111111114</v>
+      </c>
+      <c r="AU15" t="inlineStr"/>
+      <c r="AV15" t="n">
+        <v>2.349420065520075</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>-0.01939372421721783</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>-0.003091515127249374</v>
+      </c>
+      <c r="AY15" t="n">
         <v>-0.5</v>
       </c>
-      <c r="AJ15" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>-0.8680555555555554</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>0.8611111111111112</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>4.162337662337662</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>-10.14166666666667</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>9.292785585873821</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>-9.406338321121602</v>
-      </c>
-      <c r="AQ15" t="inlineStr"/>
-      <c r="AR15" t="inlineStr"/>
-      <c r="AS15" t="n">
-        <v>488.7210407521562</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>-497.4170454536711</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>-37</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>-67</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>-9.767857142857139</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>-2.053571428571431</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>-8</v>
-      </c>
       <c r="AZ15" t="n">
-        <v>-41</v>
+        <v>-0.4791666666666666</v>
       </c>
       <c r="BA15" t="n">
-        <v>-5.053571428571431</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>-9.642857142857146</v>
-      </c>
+        <v>7.788255360623793</v>
+      </c>
+      <c r="BB15" t="inlineStr"/>
       <c r="BC15" t="n">
-        <v>-6</v>
+        <v>-58777.77777777778</v>
       </c>
       <c r="BD15" t="n">
-        <v>-16.5</v>
+        <v>-21.11695906432749</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.222222222222221</v>
+        <v>-1.742690058479532</v>
       </c>
       <c r="BF15" t="n">
-        <v>-1.083333333333336</v>
+        <v>-0.07967836257309813</v>
       </c>
       <c r="BG15" t="n">
-        <v>-7</v>
+        <v>-6.675503267096332</v>
       </c>
       <c r="BH15" t="n">
-        <v>7</v>
+        <v>-16496125.73099415</v>
       </c>
       <c r="BI15" t="n">
-        <v>-7.172549019607843</v>
+        <v>-19.03216374269007</v>
       </c>
       <c r="BJ15" t="n">
-        <v>7.172549019607843</v>
-      </c>
-      <c r="BK15" t="inlineStr"/>
-      <c r="BL15" t="inlineStr"/>
+        <v>5.610972222222188</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>3.161621762740197</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>-12.31076247165532</v>
+      </c>
       <c r="BM15" t="n">
-        <v>-88.25961538461536</v>
+        <v>-0.9983333333333335</v>
       </c>
       <c r="BN15" t="n">
-        <v>52.34615384615387</v>
+        <v>-4.982222222222219</v>
       </c>
       <c r="BO15" t="n">
-        <v>-0.5</v>
+        <v>-13352829.06857919</v>
       </c>
       <c r="BP15" t="n">
-        <v>1</v>
+        <v>-0.75</v>
       </c>
       <c r="BQ15" t="n">
-        <v>0.6333333333333333</v>
+        <v>-8.106805555555553</v>
       </c>
       <c r="BR15" t="n">
-        <v>0.02380952380952395</v>
-      </c>
-      <c r="BS15" t="inlineStr"/>
-      <c r="BT15" t="inlineStr"/>
+        <v>-0.1111111111111112</v>
+      </c>
+      <c r="BS15" t="n">
+        <v>-3.574557002625617</v>
+      </c>
+      <c r="BT15" t="n">
+        <v>-1.338194444444447</v>
+      </c>
       <c r="BU15" t="n">
-        <v>-0.3</v>
+        <v>-40422.8231292517</v>
       </c>
       <c r="BV15" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="BW15" t="n">
-        <v>-2.5</v>
-      </c>
-      <c r="BX15" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="BY15" t="n">
-        <v>0.05555555555555713</v>
-      </c>
-      <c r="BZ15" t="n">
-        <v>-3.618055555555557</v>
-      </c>
-      <c r="CA15" t="inlineStr"/>
-      <c r="CB15" t="inlineStr"/>
-      <c r="CC15" t="n">
-        <v>-0.04150228786468269</v>
-      </c>
-      <c r="CD15" t="n">
-        <v>-2.390922353384758</v>
-      </c>
-      <c r="CE15" t="n">
-        <v>0.05062724014336917</v>
-      </c>
-      <c r="CF15" t="n">
-        <v>0.07002096436058701</v>
-      </c>
-      <c r="CG15" t="n">
-        <v>0.006762084044263525</v>
-      </c>
-      <c r="CH15" t="n">
-        <v>0.009853599171512899</v>
-      </c>
-      <c r="CI15" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="CJ15" t="n">
-        <v>0</v>
-      </c>
-      <c r="CK15" t="n">
-        <v>-0.2083333333333333</v>
-      </c>
-      <c r="CL15" t="n">
-        <v>0.2708333333333334</v>
-      </c>
-      <c r="CM15" t="n">
-        <v>0.2746347402597422</v>
-      </c>
-      <c r="CN15" t="inlineStr"/>
-      <c r="CO15" t="inlineStr"/>
-      <c r="CP15" t="inlineStr"/>
-      <c r="CQ15" t="inlineStr"/>
-      <c r="CR15" t="inlineStr"/>
-      <c r="CS15" t="inlineStr"/>
-      <c r="CT15" t="inlineStr"/>
-      <c r="CU15" t="inlineStr"/>
-      <c r="CV15" t="inlineStr"/>
-      <c r="CW15" t="inlineStr"/>
-      <c r="CX15" t="inlineStr"/>
-      <c r="CY15" t="inlineStr"/>
-      <c r="CZ15" t="inlineStr"/>
-      <c r="DA15" t="inlineStr"/>
-      <c r="DB15" t="inlineStr"/>
-      <c r="DC15" t="inlineStr"/>
-      <c r="DD15" t="inlineStr"/>
-      <c r="DE15" t="inlineStr"/>
-      <c r="DF15" t="inlineStr"/>
-      <c r="DG15" t="inlineStr"/>
-      <c r="DH15" t="inlineStr"/>
-      <c r="DI15" t="inlineStr"/>
+        <v>-10700940.97222222</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -5150,238 +3967,175 @@
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>0.7716666666666669</v>
+        <v>2.246666666666667</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.475</v>
+        <v>1.305758513931888</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.7804024767801854</v>
+        <v>3</v>
       </c>
       <c r="R16" t="n">
-        <v>-0.5253560371517026</v>
+        <v>1.894736842105263</v>
       </c>
       <c r="S16" t="n">
-        <v>2</v>
+        <v>6.333333333333334</v>
       </c>
       <c r="T16" t="n">
-        <v>-1</v>
+        <v>2.89766081871345</v>
       </c>
       <c r="U16" t="n">
-        <v>1.157894736842105</v>
+        <v>18.66666666666666</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.736842105263158</v>
+        <v>9.304093567251464</v>
       </c>
       <c r="W16" t="n">
-        <v>0.5</v>
+        <v>3.833333333333333</v>
       </c>
       <c r="X16" t="n">
-        <v>-5.833333333333334</v>
+        <v>1.526315789473684</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.078947368421052</v>
+        <v>4.5</v>
       </c>
       <c r="Z16" t="n">
-        <v>-0.8187134502923974</v>
+        <v>2.368421052631579</v>
       </c>
       <c r="AA16" t="n">
-        <v>8.833333333333332</v>
+        <v>15.98560606060606</v>
       </c>
       <c r="AB16" t="n">
-        <v>-9.833333333333332</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>5.55263157894737</v>
-      </c>
+        <v>16.91572594380926</v>
+      </c>
+      <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="n">
-        <v>-3.751461988304094</v>
+        <v>761.8858577663283</v>
       </c>
       <c r="AE16" t="n">
-        <v>1</v>
+        <v>108.5</v>
       </c>
       <c r="AF16" t="n">
-        <v>-2.833333333333333</v>
+        <v>76.21895424836602</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.157894736842105</v>
+        <v>86</v>
       </c>
       <c r="AH16" t="n">
-        <v>-0.368421052631579</v>
+        <v>49.28104575163399</v>
       </c>
       <c r="AI16" t="n">
-        <v>2.5</v>
+        <v>12</v>
       </c>
       <c r="AJ16" t="n">
-        <v>-2</v>
+        <v>10.73684210526315</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.263157894736842</v>
+        <v>45.33333333333334</v>
       </c>
       <c r="AL16" t="n">
-        <v>-1.105263157894737</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>9.727272727272727</v>
-      </c>
+        <v>37.33333333333333</v>
+      </c>
+      <c r="AM16" t="inlineStr"/>
       <c r="AN16" t="n">
-        <v>-6.258333333333333</v>
+        <v>374.8749999999999</v>
       </c>
       <c r="AO16" t="n">
-        <v>9.333897927770712</v>
+        <v>-1.5</v>
       </c>
       <c r="AP16" t="n">
-        <v>-7.581828016038542</v>
+        <v>-0.3194444444444444</v>
       </c>
       <c r="AQ16" t="inlineStr"/>
       <c r="AR16" t="inlineStr"/>
       <c r="AS16" t="n">
-        <v>411.1511681236645</v>
+        <v>3.000000000000002</v>
       </c>
       <c r="AT16" t="n">
-        <v>-350.7346896426638</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>66</v>
-      </c>
+        <v>-7.94736842105263</v>
+      </c>
+      <c r="AU16" t="inlineStr"/>
       <c r="AV16" t="n">
-        <v>-42.5</v>
+        <v>-6.986364517894524</v>
       </c>
       <c r="AW16" t="n">
-        <v>48.2091503267974</v>
+        <v>0.05009847509847511</v>
       </c>
       <c r="AX16" t="n">
-        <v>-28.00980392156862</v>
+        <v>0.02520946091570027</v>
       </c>
       <c r="AY16" t="n">
-        <v>44</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="AZ16" t="n">
-        <v>-42</v>
+        <v>0.2631578947368421</v>
       </c>
       <c r="BA16" t="n">
-        <v>31.56535947712418</v>
+        <v>5.479310344827582</v>
       </c>
       <c r="BB16" t="n">
-        <v>-17.71568627450981</v>
+        <v>72247.87581699347</v>
       </c>
       <c r="BC16" t="n">
-        <v>4.333333333333336</v>
+        <v>195387.5862068966</v>
       </c>
       <c r="BD16" t="n">
-        <v>-7.666666666666668</v>
+        <v>109.8262068965518</v>
       </c>
       <c r="BE16" t="n">
-        <v>3.052631578947366</v>
+        <v>3.688275862068966</v>
       </c>
       <c r="BF16" t="n">
-        <v>-7.684210526315788</v>
+        <v>0.03402298850574681</v>
       </c>
       <c r="BG16" t="n">
-        <v>22.66666666666667</v>
+        <v>8.374460169460136</v>
       </c>
       <c r="BH16" t="n">
-        <v>-22.66666666666666</v>
+        <v>102434027.5862069</v>
       </c>
       <c r="BI16" t="n">
-        <v>18.66666666666666</v>
+        <v>113.6579310344827</v>
       </c>
       <c r="BJ16" t="n">
-        <v>-18.66666666666666</v>
-      </c>
-      <c r="BK16" t="inlineStr"/>
-      <c r="BL16" t="inlineStr"/>
+        <v>1.429793028322365</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>1.469083879083882</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>8.87080012580013</v>
+      </c>
       <c r="BM16" t="n">
-        <v>257.9191176470588</v>
+        <v>0.6860839160839161</v>
       </c>
       <c r="BN16" t="n">
-        <v>-116.9558823529412</v>
+        <v>8.620969498910696</v>
       </c>
       <c r="BO16" t="n">
-        <v>-0.6666666666666667</v>
+        <v>43620631.03100602</v>
       </c>
       <c r="BP16" t="n">
-        <v>0.8333333333333335</v>
+        <v>0.8320806100217866</v>
       </c>
       <c r="BQ16" t="n">
-        <v>-0.3194444444444444</v>
+        <v>10.06448801742918</v>
       </c>
       <c r="BR16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS16" t="inlineStr"/>
-      <c r="BT16" t="inlineStr"/>
-      <c r="BU16" t="inlineStr"/>
-      <c r="BV16" t="inlineStr"/>
-      <c r="BW16" t="n">
-        <v>1.833333333333334</v>
-      </c>
-      <c r="BX16" t="n">
-        <v>-1.166666666666668</v>
-      </c>
-      <c r="BY16" t="n">
-        <v>-2.105263157894733</v>
-      </c>
-      <c r="BZ16" t="n">
-        <v>5.842105263157897</v>
-      </c>
-      <c r="CA16" t="inlineStr"/>
-      <c r="CB16" t="inlineStr"/>
-      <c r="CC16" t="n">
-        <v>-0.849337259451902</v>
-      </c>
-      <c r="CD16" t="n">
-        <v>6.137027258442622</v>
-      </c>
-      <c r="CE16" t="n">
-        <v>-0.008910533910533897</v>
-      </c>
-      <c r="CF16" t="n">
-        <v>-0.059009009009009</v>
-      </c>
-      <c r="CG16" t="n">
-        <v>0.01848478049114897</v>
-      </c>
-      <c r="CH16" t="n">
-        <v>-0.006724680424551301</v>
-      </c>
-      <c r="CI16" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="CJ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="CK16" t="n">
-        <v>0.1052631578947368</v>
-      </c>
-      <c r="CL16" t="n">
-        <v>-0.1578947368421053</v>
-      </c>
-      <c r="CM16" t="n">
-        <v>0.1266478891478897</v>
-      </c>
-      <c r="CN16" t="inlineStr"/>
-      <c r="CO16" t="inlineStr"/>
-      <c r="CP16" t="inlineStr"/>
-      <c r="CQ16" t="inlineStr"/>
-      <c r="CR16" t="inlineStr"/>
-      <c r="CS16" t="inlineStr"/>
-      <c r="CT16" t="inlineStr"/>
-      <c r="CU16" t="inlineStr"/>
-      <c r="CV16" t="inlineStr"/>
-      <c r="CW16" t="inlineStr"/>
-      <c r="CX16" t="inlineStr"/>
-      <c r="CY16" t="inlineStr"/>
-      <c r="CZ16" t="inlineStr"/>
-      <c r="DA16" t="inlineStr"/>
-      <c r="DB16" t="inlineStr"/>
-      <c r="DC16" t="inlineStr"/>
-      <c r="DD16" t="inlineStr"/>
-      <c r="DE16" t="inlineStr"/>
-      <c r="DF16" t="inlineStr"/>
-      <c r="DG16" t="inlineStr"/>
-      <c r="DH16" t="inlineStr"/>
-      <c r="DI16" t="inlineStr"/>
+        <v>1.173793103448276</v>
+      </c>
+      <c r="BS16" t="n">
+        <v>-1.126496281496284</v>
+      </c>
+      <c r="BT16" t="n">
+        <v>-0.5278867102396525</v>
+      </c>
+      <c r="BU16" t="n">
+        <v>72606.41749123891</v>
+      </c>
+      <c r="BV16" t="n">
+        <v>51059297.38562091</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
@@ -5433,242 +4187,177 @@
         <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>0.3300000000000001</v>
+        <v>0.2300000000000002</v>
       </c>
       <c r="P17" t="n">
-        <v>0.09999999999999987</v>
+        <v>0.4702960526315787</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.2209210526315788</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>-0.2493749999999999</v>
+        <v>0.8999999999999999</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>1.309210526315789</v>
       </c>
       <c r="U17" t="n">
-        <v>0.5249999999999999</v>
+        <v>-0.6666666666666679</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.375</v>
+        <v>1.976973684210526</v>
       </c>
       <c r="W17" t="n">
-        <v>1.333333333333333</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.666666666666667</v>
+        <v>0.2374999999999999</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.7532894736842106</v>
+        <v>1</v>
       </c>
       <c r="Z17" t="n">
-        <v>-0.5559210526315788</v>
+        <v>0.7124999999999999</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.333333333333332</v>
+        <v>21.4209743959744</v>
       </c>
       <c r="AB17" t="n">
-        <v>3</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>2.069078947368421</v>
-      </c>
+        <v>20.73117578693237</v>
+      </c>
+      <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="n">
-        <v>0.09210526315789558</v>
+        <v>900.1184764074485</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>-1.5</v>
       </c>
       <c r="AF17" t="n">
-        <v>-0.3333333333333333</v>
+        <v>-5.936507936507923</v>
       </c>
       <c r="AG17" t="n">
-        <v>0.2124999999999999</v>
+        <v>-32</v>
       </c>
       <c r="AH17" t="n">
-        <v>-0.02500000000000002</v>
+        <v>3.396825396825399</v>
       </c>
       <c r="AI17" t="n">
-        <v>1</v>
+        <v>5.666666666666671</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>2.424999999999999</v>
       </c>
       <c r="AK17" t="n">
-        <v>0.5249999999999999</v>
+        <v>-22.66666666666667</v>
       </c>
       <c r="AL17" t="n">
-        <v>-0.1875</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>9.187749287749288</v>
-      </c>
+        <v>-7.28947368421052</v>
+      </c>
+      <c r="AM17" t="inlineStr"/>
       <c r="AN17" t="n">
-        <v>-12.23322510822511</v>
+        <v>-62.61085972850685</v>
       </c>
       <c r="AO17" t="n">
-        <v>10.55953111216269</v>
+        <v>-1.666666666666666</v>
       </c>
       <c r="AP17" t="n">
-        <v>-10.17164467476968</v>
+        <v>-0.5416666666666667</v>
       </c>
       <c r="AQ17" t="inlineStr"/>
-      <c r="AR17" t="inlineStr"/>
+      <c r="AR17" t="n">
+        <v>0.5</v>
+      </c>
       <c r="AS17" t="n">
-        <v>486.4973203477294</v>
+        <v>-4.333333333333334</v>
       </c>
       <c r="AT17" t="n">
-        <v>-413.6211560597191</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>20.5</v>
-      </c>
+        <v>2.800000000000004</v>
+      </c>
+      <c r="AU17" t="inlineStr"/>
       <c r="AV17" t="n">
-        <v>22</v>
+        <v>2.713980558586572</v>
       </c>
       <c r="AW17" t="n">
-        <v>-16.92063492063491</v>
+        <v>-0.01525881525881526</v>
       </c>
       <c r="AX17" t="n">
-        <v>-10.98412698412699</v>
+        <v>-0.006037683238032797</v>
       </c>
       <c r="AY17" t="n">
-        <v>-6.5</v>
+        <v>0</v>
       </c>
       <c r="AZ17" t="n">
-        <v>25.5</v>
+        <v>-0.09999999999999998</v>
       </c>
       <c r="BA17" t="n">
-        <v>8.428571428571431</v>
+        <v>6.671611721611754</v>
       </c>
       <c r="BB17" t="n">
-        <v>5.031746031746032</v>
+        <v>-22737.98121070848</v>
       </c>
       <c r="BC17" t="n">
-        <v>0</v>
+        <v>-47769.23076923077</v>
       </c>
       <c r="BD17" t="n">
-        <v>-5.666666666666671</v>
+        <v>73.92307692307693</v>
       </c>
       <c r="BE17" t="n">
-        <v>-21.4625</v>
+        <v>1.192307692307693</v>
       </c>
       <c r="BF17" t="n">
-        <v>-23.8875</v>
+        <v>1.556959706959709</v>
       </c>
       <c r="BG17" t="n">
-        <v>-11.33333333333334</v>
+        <v>-2.941750115782611</v>
       </c>
       <c r="BH17" t="n">
-        <v>11.33333333333334</v>
+        <v>-12309615.38461538</v>
       </c>
       <c r="BI17" t="n">
-        <v>-3.64473684210526</v>
+        <v>72.5</v>
       </c>
       <c r="BJ17" t="n">
-        <v>3.64473684210526</v>
-      </c>
-      <c r="BK17" t="inlineStr"/>
-      <c r="BL17" t="inlineStr"/>
+        <v>1.559943324649197</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>2.631666165934774</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>-6.079671349533939</v>
+      </c>
       <c r="BM17" t="n">
-        <v>-43.7194570135747</v>
+        <v>-0.4044737791448316</v>
       </c>
       <c r="BN17" t="n">
-        <v>18.89140271493216</v>
+        <v>-6.267232848850497</v>
       </c>
       <c r="BO17" t="n">
-        <v>-1.666666666666667</v>
+        <v>-5064862.877168411</v>
       </c>
       <c r="BP17" t="n">
-        <v>0</v>
+        <v>-0.1499999999999999</v>
       </c>
       <c r="BQ17" t="n">
-        <v>-0.6458333333333335</v>
+        <v>-6.459368001279771</v>
       </c>
       <c r="BR17" t="n">
-        <v>-0.1041666666666667</v>
-      </c>
-      <c r="BS17" t="inlineStr"/>
-      <c r="BT17" t="inlineStr"/>
+        <v>1.230769230769231</v>
+      </c>
+      <c r="BS17" t="n">
+        <v>-2.02149270792847</v>
+      </c>
+      <c r="BT17" t="n">
+        <v>0.1879119246766372</v>
+      </c>
       <c r="BU17" t="n">
-        <v>0</v>
+        <v>-18191.85636929767</v>
       </c>
       <c r="BV17" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="BW17" t="n">
-        <v>-8.666666666666666</v>
-      </c>
-      <c r="BX17" t="n">
-        <v>-4.333333333333332</v>
-      </c>
-      <c r="BY17" t="n">
-        <v>1.662500000000001</v>
-      </c>
-      <c r="BZ17" t="n">
-        <v>-1.137500000000003</v>
-      </c>
-      <c r="CA17" t="inlineStr"/>
-      <c r="CB17" t="inlineStr"/>
-      <c r="CC17" t="n">
-        <v>2.105403936099762</v>
-      </c>
-      <c r="CD17" t="n">
-        <v>-0.6085766224868099</v>
-      </c>
-      <c r="CE17" t="n">
-        <v>-0.01509750412189437</v>
-      </c>
-      <c r="CF17" t="n">
-        <v>0.0001613111369208886</v>
-      </c>
-      <c r="CG17" t="n">
-        <v>-0.006438656243849317</v>
-      </c>
-      <c r="CH17" t="n">
-        <v>-0.0004009730058165198</v>
-      </c>
-      <c r="CI17" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="CJ17" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="CK17" t="n">
-        <v>-0.03749999999999998</v>
-      </c>
-      <c r="CL17" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="CM17" t="n">
-        <v>-5.003814935064923</v>
-      </c>
-      <c r="CN17" t="inlineStr"/>
-      <c r="CO17" t="inlineStr"/>
-      <c r="CP17" t="inlineStr"/>
-      <c r="CQ17" t="inlineStr"/>
-      <c r="CR17" t="inlineStr"/>
-      <c r="CS17" t="inlineStr"/>
-      <c r="CT17" t="inlineStr"/>
-      <c r="CU17" t="inlineStr"/>
-      <c r="CV17" t="inlineStr"/>
-      <c r="CW17" t="inlineStr"/>
-      <c r="CX17" t="inlineStr"/>
-      <c r="CY17" t="inlineStr"/>
-      <c r="CZ17" t="inlineStr"/>
-      <c r="DA17" t="inlineStr"/>
-      <c r="DB17" t="inlineStr"/>
-      <c r="DC17" t="inlineStr"/>
-      <c r="DD17" t="inlineStr"/>
-      <c r="DE17" t="inlineStr"/>
-      <c r="DF17" t="inlineStr"/>
-      <c r="DG17" t="inlineStr"/>
-      <c r="DH17" t="inlineStr"/>
-      <c r="DI17" t="inlineStr"/>
+        <v>-10475333.09623383</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
@@ -5720,242 +4409,177 @@
         <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>0.3533333333333333</v>
+        <v>1.453333333333333</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.1</v>
+        <v>0.579375</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.1722222222222223</v>
+        <v>1</v>
       </c>
       <c r="R18" t="n">
-        <v>-0.4071527777777777</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S18" t="n">
-        <v>0.6666666666666666</v>
+        <v>7.000000000000001</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3333333333333335</v>
+        <v>2.052631578947369</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1333333333333333</v>
+        <v>4.333333333333332</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.2</v>
+        <v>3.541795665634675</v>
       </c>
       <c r="W18" t="n">
-        <v>0.666666666666667</v>
+        <v>4.333333333333333</v>
       </c>
       <c r="X18" t="n">
-        <v>-6.333333333333334</v>
+        <v>0.6277777777777778</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.3343653250773997</v>
+        <v>6</v>
       </c>
       <c r="Z18" t="n">
-        <v>-1.718266253869969</v>
+        <v>1.316666666666666</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>20.62037037037037</v>
       </c>
       <c r="AB18" t="n">
-        <v>-4.333333333333332</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>1.588235294117647</v>
-      </c>
+        <v>18.92761939036297</v>
+      </c>
+      <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="n">
-        <v>-1.953560371517028</v>
+        <v>846.5236954038583</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.666666666666667</v>
+        <v>-42.5</v>
       </c>
       <c r="AF18" t="n">
-        <v>-2.666666666666667</v>
+        <v>23.84444444444445</v>
       </c>
       <c r="AG18" t="n">
-        <v>0.1166666666666667</v>
+        <v>-8.5</v>
       </c>
       <c r="AH18" t="n">
-        <v>-0.5111111111111111</v>
+        <v>13.35555555555556</v>
       </c>
       <c r="AI18" t="n">
-        <v>3</v>
+        <v>2.333333333333329</v>
       </c>
       <c r="AJ18" t="n">
-        <v>-3</v>
+        <v>7.25555555555556</v>
       </c>
       <c r="AK18" t="n">
-        <v>0.5944444444444443</v>
+        <v>11.33333333333333</v>
       </c>
       <c r="AL18" t="n">
-        <v>-0.7222222222222222</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>10.99242424242424</v>
-      </c>
+        <v>11.9938080495356</v>
+      </c>
+      <c r="AM18" t="inlineStr"/>
       <c r="AN18" t="n">
-        <v>-9.627946127946128</v>
+        <v>121.4732142857143</v>
       </c>
       <c r="AO18" t="n">
-        <v>10.67861941373141</v>
+        <v>-1.666666666666667</v>
       </c>
       <c r="AP18" t="n">
-        <v>-8.248999976631556</v>
+        <v>0.2786377708978327</v>
       </c>
       <c r="AQ18" t="inlineStr"/>
-      <c r="AR18" t="inlineStr"/>
+      <c r="AR18" t="n">
+        <v>0.06666666666666665</v>
+      </c>
       <c r="AS18" t="n">
-        <v>454.7815894144367</v>
+        <v>-9.666666666666666</v>
       </c>
       <c r="AT18" t="n">
-        <v>-391.7421059894216</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>-25.5</v>
-      </c>
+        <v>-4.261111111111106</v>
+      </c>
+      <c r="AU18" t="inlineStr"/>
       <c r="AV18" t="n">
-        <v>17</v>
+        <v>-1.810075013266719</v>
       </c>
       <c r="AW18" t="n">
-        <v>19.93333333333334</v>
+        <v>-0.1918235511258767</v>
       </c>
       <c r="AX18" t="n">
-        <v>-3.911111111111111</v>
+        <v>0.005871232734713273</v>
       </c>
       <c r="AY18" t="n">
         <v>1</v>
       </c>
       <c r="AZ18" t="n">
-        <v>9.5</v>
+        <v>0.5444444444444445</v>
       </c>
       <c r="BA18" t="n">
-        <v>3.344444444444449</v>
+        <v>0.407407407407419</v>
       </c>
       <c r="BB18" t="n">
-        <v>-10.01111111111111</v>
+        <v>-14548.75010610305</v>
       </c>
       <c r="BC18" t="n">
-        <v>8</v>
+        <v>-6907.407407407409</v>
       </c>
       <c r="BD18" t="n">
-        <v>5.666666666666671</v>
+        <v>4.462962962962962</v>
       </c>
       <c r="BE18" t="n">
-        <v>5.75</v>
+        <v>0.2222222222222221</v>
       </c>
       <c r="BF18" t="n">
-        <v>-1.50555555555556</v>
+        <v>3.986111111111111</v>
       </c>
       <c r="BG18" t="n">
-        <v>5.666666666666664</v>
+        <v>-5.53799481273991</v>
       </c>
       <c r="BH18" t="n">
-        <v>-5.666666666666664</v>
+        <v>-8890740.740740739</v>
       </c>
       <c r="BI18" t="n">
-        <v>5.996904024767801</v>
+        <v>-0.1296296296296333</v>
       </c>
       <c r="BJ18" t="n">
-        <v>-5.996904024767801</v>
-      </c>
-      <c r="BK18" t="inlineStr"/>
-      <c r="BL18" t="inlineStr"/>
+        <v>-0.06051226551224431</v>
+      </c>
+      <c r="BK18" t="n">
+        <v>-0.6285258844278587</v>
+      </c>
+      <c r="BL18" t="n">
+        <v>-2.611568108724967</v>
+      </c>
       <c r="BM18" t="n">
-        <v>60.04464285714289</v>
+        <v>-0.1040268700072622</v>
       </c>
       <c r="BN18" t="n">
-        <v>-61.42857142857144</v>
+        <v>-5.822171717171699</v>
       </c>
       <c r="BO18" t="n">
-        <v>-1.333333333333333</v>
+        <v>-7308588.873327112</v>
       </c>
       <c r="BP18" t="n">
-        <v>0.3333333333333333</v>
+        <v>-0.2931385281385284</v>
       </c>
       <c r="BQ18" t="n">
-        <v>0.1362229102167181</v>
+        <v>-2.731031746031746</v>
       </c>
       <c r="BR18" t="n">
-        <v>-0.1424148606811146</v>
-      </c>
-      <c r="BS18" t="inlineStr"/>
-      <c r="BT18" t="inlineStr"/>
+        <v>0.09259259259259256</v>
+      </c>
+      <c r="BS18" t="n">
+        <v>2.074289345367774</v>
+      </c>
+      <c r="BT18" t="n">
+        <v>2.341356421356423</v>
+      </c>
       <c r="BU18" t="n">
-        <v>0.06666666666666665</v>
+        <v>-9460.526610644258</v>
       </c>
       <c r="BV18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW18" t="n">
-        <v>-0.3333333333333321</v>
-      </c>
-      <c r="BX18" t="n">
-        <v>9.333333333333334</v>
-      </c>
-      <c r="BY18" t="n">
-        <v>-3.62222222222222</v>
-      </c>
-      <c r="BZ18" t="n">
-        <v>0.6388888888888857</v>
-      </c>
-      <c r="CA18" t="inlineStr"/>
-      <c r="CB18" t="inlineStr"/>
-      <c r="CC18" t="n">
-        <v>-0.3056074425732227</v>
-      </c>
-      <c r="CD18" t="n">
-        <v>1.504467570693496</v>
-      </c>
-      <c r="CE18" t="n">
-        <v>-0.1261904761904762</v>
-      </c>
-      <c r="CF18" t="n">
-        <v>0.06563307493540051</v>
-      </c>
-      <c r="CG18" t="n">
-        <v>0.004140809268385129</v>
-      </c>
-      <c r="CH18" t="n">
-        <v>-0.001730423466328145</v>
-      </c>
-      <c r="CI18" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ18" t="n">
-        <v>0</v>
-      </c>
-      <c r="CK18" t="n">
-        <v>0.4111111111111111</v>
-      </c>
-      <c r="CL18" t="n">
-        <v>-0.1333333333333333</v>
-      </c>
-      <c r="CM18" t="n">
-        <v>0.8760541927208578</v>
-      </c>
-      <c r="CN18" t="inlineStr"/>
-      <c r="CO18" t="inlineStr"/>
-      <c r="CP18" t="inlineStr"/>
-      <c r="CQ18" t="inlineStr"/>
-      <c r="CR18" t="inlineStr"/>
-      <c r="CS18" t="inlineStr"/>
-      <c r="CT18" t="inlineStr"/>
-      <c r="CU18" t="inlineStr"/>
-      <c r="CV18" t="inlineStr"/>
-      <c r="CW18" t="inlineStr"/>
-      <c r="CX18" t="inlineStr"/>
-      <c r="CY18" t="inlineStr"/>
-      <c r="CZ18" t="inlineStr"/>
-      <c r="DA18" t="inlineStr"/>
-      <c r="DB18" t="inlineStr"/>
-      <c r="DC18" t="inlineStr"/>
-      <c r="DD18" t="inlineStr"/>
-      <c r="DE18" t="inlineStr"/>
-      <c r="DF18" t="inlineStr"/>
-      <c r="DG18" t="inlineStr"/>
-      <c r="DH18" t="inlineStr"/>
-      <c r="DI18" t="inlineStr"/>
+        <v>-9645164.682539683</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
@@ -6007,242 +4631,177 @@
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.7383333333333333</v>
+        <v>-0.8466666666666667</v>
       </c>
       <c r="P19" t="n">
-        <v>0.1083333333333334</v>
+        <v>0.80625</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.5531250000000001</v>
+        <v>-0.5</v>
       </c>
       <c r="R19" t="n">
-        <v>-0.2531249999999999</v>
+        <v>0.9375</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>-1.166666666666667</v>
       </c>
       <c r="T19" t="n">
-        <v>0.5</v>
+        <v>2.0625</v>
       </c>
       <c r="U19" t="n">
-        <v>0.5698529411764706</v>
+        <v>-3</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.3676470588235294</v>
+        <v>5.058823529411764</v>
       </c>
       <c r="W19" t="n">
-        <v>-2.333333333333333</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.166666666666667</v>
+        <v>0.6360294117647058</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.639705882352941</v>
+        <v>2</v>
       </c>
       <c r="Z19" t="n">
-        <v>-0.4227941176470589</v>
+        <v>0.9485294117647058</v>
       </c>
       <c r="AA19" t="n">
-        <v>-1.833333333333334</v>
+        <v>23.04444444444444</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.166666666666666</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>4.172794117647058</v>
-      </c>
+        <v>19.20340463823709</v>
+      </c>
+      <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="n">
-        <v>-0.8860294117647065</v>
+        <v>945.8255489964806</v>
       </c>
       <c r="AE19" t="n">
-        <v>0.5</v>
+        <v>-52</v>
       </c>
       <c r="AF19" t="n">
-        <v>0.5</v>
+        <v>13.08035714285714</v>
       </c>
       <c r="AG19" t="n">
-        <v>0.5661764705882353</v>
+        <v>-51</v>
       </c>
       <c r="AH19" t="n">
-        <v>-0.06985294117647056</v>
+        <v>8.053571428571431</v>
       </c>
       <c r="AI19" t="n">
-        <v>0.8333333333333335</v>
+        <v>13.5</v>
       </c>
       <c r="AJ19" t="n">
-        <v>-1.166666666666667</v>
+        <v>-1.988970588235293</v>
       </c>
       <c r="AK19" t="n">
-        <v>0.4669117647058822</v>
+        <v>-7.666666666666671</v>
       </c>
       <c r="AL19" t="n">
-        <v>-0.4816176470588236</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>15.20634920634921</v>
-      </c>
+        <v>-7.470588235294116</v>
+      </c>
+      <c r="AM19" t="inlineStr"/>
       <c r="AN19" t="n">
-        <v>-7.838095238095239</v>
+        <v>-95.13461538461536</v>
       </c>
       <c r="AO19" t="n">
-        <v>10.87881564364036</v>
+        <v>-0.8333333333333335</v>
       </c>
       <c r="AP19" t="n">
-        <v>-8.324588994596734</v>
+        <v>0.2039215686274509</v>
       </c>
       <c r="AQ19" t="inlineStr"/>
-      <c r="AR19" t="inlineStr"/>
+      <c r="AR19" t="n">
+        <v>-0.6</v>
+      </c>
       <c r="AS19" t="n">
-        <v>550.0999835594115</v>
+        <v>-3.666666666666668</v>
       </c>
       <c r="AT19" t="n">
-        <v>-395.7255654370691</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>-53</v>
-      </c>
+        <v>13.21691176470588</v>
+      </c>
+      <c r="AU19" t="inlineStr"/>
       <c r="AV19" t="n">
-        <v>-1</v>
+        <v>0.7820681713494455</v>
       </c>
       <c r="AW19" t="n">
-        <v>14.24107142857143</v>
+        <v>-0.06125356125356125</v>
       </c>
       <c r="AX19" t="n">
-        <v>1.160714285714292</v>
+        <v>-0.01187416812704964</v>
       </c>
       <c r="AY19" t="n">
-        <v>-37</v>
+        <v>0</v>
       </c>
       <c r="AZ19" t="n">
-        <v>14</v>
+        <v>0.1360294117647059</v>
       </c>
       <c r="BA19" t="n">
-        <v>6.705357142857146</v>
+        <v>-7.477523809523802</v>
       </c>
       <c r="BB19" t="n">
-        <v>-1.348214285714285</v>
+        <v>14124.36868686869</v>
       </c>
       <c r="BC19" t="n">
-        <v>16.83333333333334</v>
+        <v>154160</v>
       </c>
       <c r="BD19" t="n">
-        <v>3.333333333333336</v>
+        <v>251.68</v>
       </c>
       <c r="BE19" t="n">
-        <v>4.422794117647058</v>
+        <v>3.76</v>
       </c>
       <c r="BF19" t="n">
-        <v>6.411764705882351</v>
+        <v>-4.96833333333333</v>
       </c>
       <c r="BG19" t="n">
-        <v>-3.833333333333336</v>
+        <v>3.587291963466768</v>
       </c>
       <c r="BH19" t="n">
-        <v>3.833333333333336</v>
+        <v>62652000</v>
       </c>
       <c r="BI19" t="n">
-        <v>-3.735294117647058</v>
+        <v>275.64</v>
       </c>
       <c r="BJ19" t="n">
-        <v>3.735294117647058</v>
-      </c>
-      <c r="BK19" t="inlineStr"/>
-      <c r="BL19" t="inlineStr"/>
+        <v>-1.951530182780175</v>
+      </c>
+      <c r="BK19" t="n">
+        <v>-0.5176458583883345</v>
+      </c>
+      <c r="BL19" t="n">
+        <v>-3.480107538660164</v>
+      </c>
       <c r="BM19" t="n">
-        <v>-58.19230769230768</v>
+        <v>-0.158945477037582</v>
       </c>
       <c r="BN19" t="n">
-        <v>36.94230769230768</v>
+        <v>0.05090488215489586</v>
       </c>
       <c r="BO19" t="n">
-        <v>1</v>
+        <v>1416256.325780528</v>
       </c>
       <c r="BP19" t="n">
-        <v>1.833333333333333</v>
+        <v>0.002681577681577618</v>
       </c>
       <c r="BQ19" t="n">
-        <v>0.411764705882353</v>
+        <v>-0.6321308321308265</v>
       </c>
       <c r="BR19" t="n">
-        <v>0.2078431372549021</v>
-      </c>
-      <c r="BS19" t="inlineStr"/>
-      <c r="BT19" t="inlineStr"/>
+        <v>3.28</v>
+      </c>
+      <c r="BS19" t="n">
+        <v>-5.763555351290311</v>
+      </c>
+      <c r="BT19" t="n">
+        <v>-0.5274170274170302</v>
+      </c>
       <c r="BU19" t="n">
-        <v>-0.09999999999999998</v>
+        <v>-7210.476190476191</v>
       </c>
       <c r="BV19" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="BW19" t="n">
-        <v>4.333333333333332</v>
-      </c>
-      <c r="BX19" t="n">
-        <v>8</v>
-      </c>
-      <c r="BY19" t="n">
-        <v>9.356617647058826</v>
-      </c>
-      <c r="BZ19" t="n">
-        <v>-3.860294117647058</v>
-      </c>
-      <c r="CA19" t="inlineStr"/>
-      <c r="CB19" t="inlineStr"/>
-      <c r="CC19" t="n">
-        <v>-2.505651327915452</v>
-      </c>
-      <c r="CD19" t="n">
-        <v>-3.287719499264897</v>
-      </c>
-      <c r="CE19" t="n">
-        <v>-0.02529358626919602</v>
-      </c>
-      <c r="CF19" t="n">
-        <v>0.03595997498436523</v>
-      </c>
-      <c r="CG19" t="n">
-        <v>-0.003458401694340994</v>
-      </c>
-      <c r="CH19" t="n">
-        <v>0.008415766432708645</v>
-      </c>
-      <c r="CI19" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="CJ19" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="CK19" t="n">
-        <v>-0.03308823529411764</v>
-      </c>
-      <c r="CL19" t="n">
-        <v>-0.1691176470588235</v>
-      </c>
-      <c r="CM19" t="n">
-        <v>-0.6024915824915809</v>
-      </c>
-      <c r="CN19" t="inlineStr"/>
-      <c r="CO19" t="inlineStr"/>
-      <c r="CP19" t="inlineStr"/>
-      <c r="CQ19" t="inlineStr"/>
-      <c r="CR19" t="inlineStr"/>
-      <c r="CS19" t="inlineStr"/>
-      <c r="CT19" t="inlineStr"/>
-      <c r="CU19" t="inlineStr"/>
-      <c r="CV19" t="inlineStr"/>
-      <c r="CW19" t="inlineStr"/>
-      <c r="CX19" t="inlineStr"/>
-      <c r="CY19" t="inlineStr"/>
-      <c r="CZ19" t="inlineStr"/>
-      <c r="DA19" t="inlineStr"/>
-      <c r="DB19" t="inlineStr"/>
-      <c r="DC19" t="inlineStr"/>
-      <c r="DD19" t="inlineStr"/>
-      <c r="DE19" t="inlineStr"/>
-      <c r="DF19" t="inlineStr"/>
-      <c r="DG19" t="inlineStr"/>
-      <c r="DH19" t="inlineStr"/>
-      <c r="DI19" t="inlineStr"/>
+        <v>2132384.785353534</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/france/p6_deployment/data_preparation/df_tagged.xlsx
+++ b/data/france/p6_deployment/data_preparation/df_tagged.xlsx
@@ -690,112 +690,112 @@
       </c>
       <c r="BA1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_wage_player_start</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_wage_player_miss</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_sub</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rep_player_sub</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_wage_player_sub</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_start</t>
+        </is>
+      </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_pot_player_miss</t>
+        </is>
+      </c>
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_value_player_miss</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_miss</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_rat_player_miss</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_value_player_start</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rep_player_start</t>
+        </is>
+      </c>
+      <c r="BM1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_start</t>
+        </is>
+      </c>
+      <c r="BN1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_start</t>
+        </is>
+      </c>
+      <c r="BO1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_rep_player_miss</t>
+        </is>
+      </c>
+      <c r="BP1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_sub</t>
+        </is>
+      </c>
+      <c r="BQ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_sub</t>
+        </is>
+      </c>
+      <c r="BR1" s="1" t="inlineStr">
+        <is>
+          <t>dif_n_player_miss</t>
+        </is>
+      </c>
+      <c r="BS1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_start</t>
+        </is>
+      </c>
+      <c r="BT1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_sub</t>
+        </is>
+      </c>
+      <c r="BU1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_value_player_sub</t>
+        </is>
+      </c>
+      <c r="BV1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_hei_player_miss</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_wage_player_start</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_wage_player_miss</t>
-        </is>
-      </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_rat_player_miss</t>
-        </is>
-      </c>
-      <c r="BE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_rep_player_miss</t>
-        </is>
-      </c>
-      <c r="BF1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_miss</t>
-        </is>
-      </c>
-      <c r="BG1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_sub</t>
-        </is>
-      </c>
-      <c r="BH1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_value_player_miss</t>
-        </is>
-      </c>
-      <c r="BI1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_pot_player_miss</t>
-        </is>
-      </c>
-      <c r="BJ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_start</t>
-        </is>
-      </c>
-      <c r="BK1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_sub</t>
-        </is>
-      </c>
-      <c r="BL1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_sub</t>
-        </is>
-      </c>
-      <c r="BM1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rep_player_sub</t>
-        </is>
-      </c>
-      <c r="BN1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_start</t>
-        </is>
-      </c>
-      <c r="BO1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_value_player_sub</t>
-        </is>
-      </c>
-      <c r="BP1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rep_player_start</t>
-        </is>
-      </c>
-      <c r="BQ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_start</t>
-        </is>
-      </c>
-      <c r="BR1" s="1" t="inlineStr">
-        <is>
-          <t>dif_n_player_miss</t>
-        </is>
-      </c>
-      <c r="BS1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_sub</t>
-        </is>
-      </c>
-      <c r="BT1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_start</t>
-        </is>
-      </c>
-      <c r="BU1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_wage_player_sub</t>
-        </is>
-      </c>
-      <c r="BV1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_value_player_start</t>
         </is>
       </c>
     </row>
@@ -955,70 +955,70 @@
         <v>-0.1809210526315789</v>
       </c>
       <c r="BA2" t="n">
-        <v>-6.102643678160916</v>
+        <v>-48065.97222222223</v>
       </c>
       <c r="BB2" t="n">
-        <v>-48065.97222222223</v>
+        <v>-138387.5862068966</v>
       </c>
       <c r="BC2" t="n">
-        <v>-138387.5862068966</v>
+        <v>-1.090574980574956</v>
       </c>
       <c r="BD2" t="n">
-        <v>20.01379310344828</v>
+        <v>-0.8302397602397602</v>
       </c>
       <c r="BE2" t="n">
-        <v>-2.208275862068965</v>
+        <v>-56098.50468975468</v>
       </c>
       <c r="BF2" t="n">
-        <v>-2.068689655172413</v>
+        <v>-5.71643518518519</v>
       </c>
       <c r="BG2" t="n">
-        <v>-5.09639138639136</v>
+        <v>30.42206896551727</v>
       </c>
       <c r="BH2" t="n">
         <v>-72102827.5862069</v>
       </c>
       <c r="BI2" t="n">
-        <v>30.42206896551727</v>
+        <v>-2.068689655172413</v>
       </c>
       <c r="BJ2" t="n">
+        <v>20.01379310344828</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>-39862586.80555555</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>-0.8935185185185184</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>2.387731481481481</v>
+      </c>
+      <c r="BN2" t="n">
         <v>-2.31018518518519</v>
       </c>
-      <c r="BK2" t="n">
-        <v>-1.090574980574956</v>
-      </c>
-      <c r="BL2" t="n">
+      <c r="BO2" t="n">
+        <v>-2.208275862068965</v>
+      </c>
+      <c r="BP2" t="n">
         <v>-4.999770784770789</v>
       </c>
-      <c r="BM2" t="n">
-        <v>-0.8302397602397602</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>-5.71643518518519</v>
-      </c>
-      <c r="BO2" t="n">
-        <v>-36818643.71739371</v>
-      </c>
-      <c r="BP2" t="n">
-        <v>-0.8935185185185184</v>
-      </c>
       <c r="BQ2" t="n">
-        <v>-4.030092592592595</v>
+        <v>0.6932856032856058</v>
       </c>
       <c r="BR2" t="n">
         <v>0.6662068965517243</v>
       </c>
       <c r="BS2" t="n">
-        <v>0.6932856032856058</v>
+        <v>-4.030092592592595</v>
       </c>
       <c r="BT2" t="n">
-        <v>2.387731481481481</v>
+        <v>-5.09639138639136</v>
       </c>
       <c r="BU2" t="n">
-        <v>-56098.50468975468</v>
+        <v>-36818643.71739371</v>
       </c>
       <c r="BV2" t="n">
-        <v>-39862586.80555555</v>
+        <v>-6.102643678160916</v>
       </c>
     </row>
     <row r="3">
@@ -1170,69 +1170,69 @@
       <c r="AZ3" t="n">
         <v>0.173202614379085</v>
       </c>
-      <c r="BA3" t="n">
-        <v>-2.322222222222251</v>
-      </c>
-      <c r="BB3" t="inlineStr"/>
+      <c r="BA3" t="inlineStr"/>
+      <c r="BB3" t="n">
+        <v>19003.49650349651</v>
+      </c>
       <c r="BC3" t="n">
-        <v>19003.49650349651</v>
+        <v>-0.7497044448607255</v>
       </c>
       <c r="BD3" t="n">
-        <v>57.29166666666666</v>
+        <v>0.20987234987235</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.493589743589743</v>
+        <v>2967.451487906033</v>
       </c>
       <c r="BF3" t="n">
-        <v>2.597649572649566</v>
+        <v>-0.6893518518518675</v>
       </c>
       <c r="BG3" t="n">
-        <v>-0.7604441912254316</v>
+        <v>55.58974358974356</v>
       </c>
       <c r="BH3" t="n">
         <v>834134.615384616</v>
       </c>
       <c r="BI3" t="n">
-        <v>55.58974358974356</v>
+        <v>2.597649572649566</v>
       </c>
       <c r="BJ3" t="n">
+        <v>57.29166666666666</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>2958549.933862433</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>0.3944444444444444</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>3.606349206349201</v>
+      </c>
+      <c r="BN3" t="n">
         <v>-5.716005291005217</v>
       </c>
-      <c r="BK3" t="n">
-        <v>-0.7497044448607255</v>
-      </c>
-      <c r="BL3" t="n">
+      <c r="BO3" t="n">
+        <v>1.493589743589743</v>
+      </c>
+      <c r="BP3" t="n">
         <v>1.122746472277726</v>
       </c>
-      <c r="BM3" t="n">
-        <v>0.20987234987235</v>
-      </c>
-      <c r="BN3" t="n">
-        <v>-0.6893518518518675</v>
-      </c>
-      <c r="BO3" t="n">
-        <v>261340.3909458597</v>
-      </c>
-      <c r="BP3" t="n">
-        <v>0.3944444444444444</v>
-      </c>
       <c r="BQ3" t="n">
-        <v>4.035978835978838</v>
+        <v>2.014719308469306</v>
       </c>
       <c r="BR3" t="n">
         <v>0.8012820512820511</v>
       </c>
       <c r="BS3" t="n">
-        <v>2.014719308469306</v>
+        <v>4.035978835978838</v>
       </c>
       <c r="BT3" t="n">
-        <v>3.606349206349201</v>
+        <v>-0.7604441912254316</v>
       </c>
       <c r="BU3" t="n">
-        <v>2967.451487906033</v>
+        <v>261340.3909458597</v>
       </c>
       <c r="BV3" t="n">
-        <v>2958549.933862433</v>
+        <v>-2.322222222222251</v>
       </c>
     </row>
     <row r="4">
@@ -1391,70 +1391,70 @@
         <v>0.1176470588235294</v>
       </c>
       <c r="BA4" t="n">
-        <v>5.914000000000016</v>
+        <v>-8770.098039215691</v>
       </c>
       <c r="BB4" t="n">
-        <v>-8770.098039215691</v>
+        <v>-17360</v>
       </c>
       <c r="BC4" t="n">
-        <v>-17360</v>
+        <v>-0.1992296014171018</v>
       </c>
       <c r="BD4" t="n">
-        <v>-9</v>
+        <v>0.1163046675546675</v>
       </c>
       <c r="BE4" t="n">
-        <v>0.96</v>
+        <v>-5082.021748093177</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.472666666666669</v>
+        <v>0.7790305010893235</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.2514085798461</v>
+        <v>-6.400000000000006</v>
       </c>
       <c r="BH4" t="n">
         <v>-6925200</v>
       </c>
       <c r="BI4" t="n">
-        <v>-6.400000000000006</v>
+        <v>1.472666666666669</v>
       </c>
       <c r="BJ4" t="n">
+        <v>-9</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>-1895626.089324619</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>-0.1965250544662311</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>-1.954520697167755</v>
+      </c>
+      <c r="BN4" t="n">
         <v>0.6577995642701921</v>
       </c>
-      <c r="BK4" t="n">
-        <v>-0.1992296014171018</v>
-      </c>
-      <c r="BL4" t="n">
+      <c r="BO4" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="BP4" t="n">
         <v>0.8397403753653805</v>
       </c>
-      <c r="BM4" t="n">
-        <v>0.1163046675546675</v>
-      </c>
-      <c r="BN4" t="n">
-        <v>0.7790305010893235</v>
-      </c>
-      <c r="BO4" t="n">
-        <v>-923884.3948297072</v>
-      </c>
-      <c r="BP4" t="n">
-        <v>-0.1965250544662311</v>
-      </c>
       <c r="BQ4" t="n">
-        <v>-2.434302832244001</v>
+        <v>-0.3839595820845823</v>
       </c>
       <c r="BR4" t="n">
         <v>-0.07999999999999963</v>
       </c>
       <c r="BS4" t="n">
-        <v>-0.3839595820845823</v>
+        <v>-2.434302832244001</v>
       </c>
       <c r="BT4" t="n">
-        <v>-1.954520697167755</v>
+        <v>1.2514085798461</v>
       </c>
       <c r="BU4" t="n">
-        <v>-5082.021748093177</v>
+        <v>-923884.3948297072</v>
       </c>
       <c r="BV4" t="n">
-        <v>-1895626.089324619</v>
+        <v>5.914000000000016</v>
       </c>
     </row>
     <row r="5">
@@ -1607,70 +1607,70 @@
         <v>0.2222222222222222</v>
       </c>
       <c r="BA5" t="n">
-        <v>-1.827604395604453</v>
+        <v>-8794.074675324671</v>
       </c>
       <c r="BB5" t="n">
-        <v>-8794.074675324671</v>
+        <v>-87121.53846153847</v>
       </c>
       <c r="BC5" t="n">
-        <v>-87121.53846153847</v>
+        <v>2.19232793012921</v>
       </c>
       <c r="BD5" t="n">
-        <v>-130.6415384615385</v>
+        <v>0.2101319403563982</v>
       </c>
       <c r="BE5" t="n">
-        <v>-2.375384615384615</v>
+        <v>8455.476273000786</v>
       </c>
       <c r="BF5" t="n">
-        <v>-0.1662820512820531</v>
+        <v>-0.8677158489658439</v>
       </c>
       <c r="BG5" t="n">
-        <v>-2.49605181744721</v>
+        <v>-141.3707692307692</v>
       </c>
       <c r="BH5" t="n">
         <v>-39052000</v>
       </c>
       <c r="BI5" t="n">
-        <v>-141.3707692307692</v>
+        <v>-0.1662820512820531</v>
       </c>
       <c r="BJ5" t="n">
+        <v>-130.6415384615385</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>-3487930.194805196</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>-0.001031144781144855</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>1.030645743145747</v>
+      </c>
+      <c r="BN5" t="n">
         <v>5.821614959114953</v>
       </c>
-      <c r="BK5" t="n">
-        <v>2.19232793012921</v>
-      </c>
-      <c r="BL5" t="n">
+      <c r="BO5" t="n">
+        <v>-2.375384615384615</v>
+      </c>
+      <c r="BP5" t="n">
         <v>1.488875486398697</v>
       </c>
-      <c r="BM5" t="n">
-        <v>0.2101319403563982</v>
-      </c>
-      <c r="BN5" t="n">
-        <v>-0.8677158489658439</v>
-      </c>
-      <c r="BO5" t="n">
-        <v>-1140548.900603126</v>
-      </c>
-      <c r="BP5" t="n">
-        <v>-0.001031144781144855</v>
-      </c>
       <c r="BQ5" t="n">
-        <v>0.6239868927368946</v>
+        <v>1.361343361210675</v>
       </c>
       <c r="BR5" t="n">
         <v>-1.664615384615385</v>
       </c>
       <c r="BS5" t="n">
-        <v>1.361343361210675</v>
+        <v>0.6239868927368946</v>
       </c>
       <c r="BT5" t="n">
-        <v>1.030645743145747</v>
+        <v>-2.49605181744721</v>
       </c>
       <c r="BU5" t="n">
-        <v>8455.476273000786</v>
+        <v>-1140548.900603126</v>
       </c>
       <c r="BV5" t="n">
-        <v>-3487930.194805196</v>
+        <v>-1.827604395604453</v>
       </c>
     </row>
     <row r="6">
@@ -1830,67 +1830,67 @@
       <c r="AZ6" t="n">
         <v>0.25</v>
       </c>
-      <c r="BA6" t="n">
-        <v>-8.363784461152903</v>
-      </c>
-      <c r="BB6" t="inlineStr"/>
+      <c r="BA6" t="inlineStr"/>
+      <c r="BB6" t="n">
+        <v>68277.77777777778</v>
+      </c>
       <c r="BC6" t="n">
-        <v>68277.77777777778</v>
+        <v>-3.424483069144685</v>
       </c>
       <c r="BD6" t="n">
-        <v>-29.81954887218046</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>0.9172932330827068</v>
-      </c>
+        <v>0.9983333333333335</v>
+      </c>
+      <c r="BE6" t="inlineStr"/>
       <c r="BF6" t="n">
-        <v>1.141979949874685</v>
+        <v>7.61312724014337</v>
       </c>
       <c r="BG6" t="n">
-        <v>7.265411038418563</v>
+        <v>-41.29323308270676</v>
       </c>
       <c r="BH6" t="n">
         <v>17580451.12781955</v>
       </c>
       <c r="BI6" t="n">
-        <v>-41.29323308270676</v>
+        <v>1.141979949874685</v>
       </c>
       <c r="BJ6" t="n">
+        <v>-29.81954887218046</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>10804150.37471489</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>-1.451857282502445</v>
+      </c>
+      <c r="BN6" t="n">
         <v>-0.4286412512219044</v>
       </c>
-      <c r="BK6" t="n">
-        <v>-3.424483069144685</v>
-      </c>
-      <c r="BL6" t="n">
+      <c r="BO6" t="n">
+        <v>0.9172932330827068</v>
+      </c>
+      <c r="BP6" t="n">
         <v>12.92485347568055</v>
       </c>
-      <c r="BM6" t="n">
-        <v>0.9983333333333335</v>
-      </c>
-      <c r="BN6" t="n">
-        <v>7.61312724014337</v>
-      </c>
-      <c r="BO6" t="n">
-        <v>13474549.55028263</v>
-      </c>
-      <c r="BP6" t="n">
-        <v>0.75</v>
-      </c>
       <c r="BQ6" t="n">
-        <v>6.041035353535349</v>
+        <v>4.763631210059785</v>
       </c>
       <c r="BR6" t="n">
         <v>-0.7142857142857144</v>
       </c>
       <c r="BS6" t="n">
-        <v>4.763631210059785</v>
+        <v>6.041035353535349</v>
       </c>
       <c r="BT6" t="n">
-        <v>-1.451857282502445</v>
-      </c>
-      <c r="BU6" t="inlineStr"/>
+        <v>7.265411038418563</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>13474549.55028263</v>
+      </c>
       <c r="BV6" t="n">
-        <v>10804150.37471489</v>
+        <v>-8.363784461152903</v>
       </c>
     </row>
     <row r="7">
@@ -2055,70 +2055,70 @@
         <v>0.1458333333333334</v>
       </c>
       <c r="BA7" t="n">
-        <v>-10.04230137678417</v>
+        <v>3166.98717948718</v>
       </c>
       <c r="BB7" t="n">
-        <v>3166.98717948718</v>
+        <v>41872.67904509284</v>
       </c>
       <c r="BC7" t="n">
-        <v>41872.67904509284</v>
+        <v>-0.7967608049845012</v>
       </c>
       <c r="BD7" t="n">
-        <v>104.8010610079575</v>
+        <v>0.1389316823527349</v>
       </c>
       <c r="BE7" t="n">
-        <v>0.9801061007957557</v>
+        <v>-86.68256816282883</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.678672476948336</v>
+        <v>-1.113660644910638</v>
       </c>
       <c r="BG7" t="n">
-        <v>-1.811064495932925</v>
+        <v>103.7758620689655</v>
       </c>
       <c r="BH7" t="n">
         <v>5825994.694960212</v>
       </c>
       <c r="BI7" t="n">
-        <v>103.7758620689655</v>
+        <v>1.678672476948336</v>
       </c>
       <c r="BJ7" t="n">
+        <v>104.8010610079575</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>136668.9733877219</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>-0.2436147186147186</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>1.841065878565875</v>
+      </c>
+      <c r="BN7" t="n">
         <v>-1.010540154290112</v>
       </c>
-      <c r="BK7" t="n">
-        <v>-0.7967608049845012</v>
-      </c>
-      <c r="BL7" t="n">
+      <c r="BO7" t="n">
+        <v>0.9801061007957557</v>
+      </c>
+      <c r="BP7" t="n">
         <v>0.06106032734321332</v>
       </c>
-      <c r="BM7" t="n">
-        <v>0.1389316823527349</v>
-      </c>
-      <c r="BN7" t="n">
-        <v>-1.113660644910638</v>
-      </c>
-      <c r="BO7" t="n">
-        <v>-1170630.297455954</v>
-      </c>
-      <c r="BP7" t="n">
-        <v>-0.2436147186147186</v>
-      </c>
       <c r="BQ7" t="n">
-        <v>1.222213897213905</v>
+        <v>0.7011796682849329</v>
       </c>
       <c r="BR7" t="n">
         <v>1.424403183023873</v>
       </c>
       <c r="BS7" t="n">
-        <v>0.7011796682849329</v>
+        <v>1.222213897213905</v>
       </c>
       <c r="BT7" t="n">
-        <v>1.841065878565875</v>
+        <v>-1.811064495932925</v>
       </c>
       <c r="BU7" t="n">
-        <v>-86.68256816282883</v>
+        <v>-1170630.297455954</v>
       </c>
       <c r="BV7" t="n">
-        <v>136668.9733877219</v>
+        <v>-10.04230137678417</v>
       </c>
     </row>
     <row r="8">
@@ -2277,70 +2277,70 @@
         <v>-0.1213235294117647</v>
       </c>
       <c r="BA8" t="n">
-        <v>-4.160148148148153</v>
+        <v>1152.660533910534</v>
       </c>
       <c r="BB8" t="n">
-        <v>1152.660533910534</v>
+        <v>-7055.555555555555</v>
       </c>
       <c r="BC8" t="n">
-        <v>-7055.555555555555</v>
+        <v>4.259690943043893</v>
       </c>
       <c r="BD8" t="n">
-        <v>8.766666666666666</v>
+        <v>-0.1620821661998135</v>
       </c>
       <c r="BE8" t="n">
-        <v>0.02222222222222237</v>
+        <v>-1836.431061313417</v>
       </c>
       <c r="BF8" t="n">
-        <v>-5.084777777777781</v>
+        <v>2.664898989898987</v>
       </c>
       <c r="BG8" t="n">
-        <v>1.340140856342543</v>
+        <v>21.41111111111113</v>
       </c>
       <c r="BH8" t="n">
         <v>-720666.666666667</v>
       </c>
       <c r="BI8" t="n">
-        <v>21.41111111111113</v>
+        <v>-5.084777777777781</v>
       </c>
       <c r="BJ8" t="n">
+        <v>8.766666666666666</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>2948543.47041847</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>-0.05216450216450208</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>-0.4637806637806605</v>
+      </c>
+      <c r="BN8" t="n">
         <v>3.311724386724364</v>
       </c>
-      <c r="BK8" t="n">
-        <v>4.259690943043893</v>
-      </c>
-      <c r="BL8" t="n">
+      <c r="BO8" t="n">
+        <v>0.02222222222222237</v>
+      </c>
+      <c r="BP8" t="n">
         <v>-0.739847272242244</v>
       </c>
-      <c r="BM8" t="n">
-        <v>-0.1620821661998135</v>
-      </c>
-      <c r="BN8" t="n">
-        <v>2.664898989898987</v>
-      </c>
-      <c r="BO8" t="n">
-        <v>203668.7941843402</v>
-      </c>
-      <c r="BP8" t="n">
-        <v>-0.05216450216450208</v>
-      </c>
       <c r="BQ8" t="n">
-        <v>0.8255772005772002</v>
+        <v>-1.398419367747096</v>
       </c>
       <c r="BR8" t="n">
         <v>0.22</v>
       </c>
       <c r="BS8" t="n">
-        <v>-1.398419367747096</v>
+        <v>0.8255772005772002</v>
       </c>
       <c r="BT8" t="n">
-        <v>-0.4637806637806605</v>
+        <v>1.340140856342543</v>
       </c>
       <c r="BU8" t="n">
-        <v>-1836.431061313417</v>
+        <v>203668.7941843402</v>
       </c>
       <c r="BV8" t="n">
-        <v>2948543.47041847</v>
+        <v>-4.160148148148153</v>
       </c>
     </row>
     <row r="9">
@@ -2501,68 +2501,68 @@
         <v>0.1176470588235294</v>
       </c>
       <c r="BA9" t="n">
-        <v>2.817460317460331</v>
+        <v>-1349.819877092604</v>
       </c>
       <c r="BB9" t="n">
-        <v>-1349.819877092604</v>
+        <v>-15555.55555555555</v>
       </c>
       <c r="BC9" t="n">
-        <v>-15555.55555555555</v>
+        <v>0.6823762791304944</v>
       </c>
       <c r="BD9" t="n">
-        <v>-4.301587301587318</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>0.1587301587301591</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="BE9" t="inlineStr"/>
       <c r="BF9" t="n">
-        <v>-4.376984126984127</v>
+        <v>-1.559944574420669</v>
       </c>
       <c r="BG9" t="n">
-        <v>-2.001235675657284</v>
+        <v>14.4126984126984</v>
       </c>
       <c r="BH9" t="n">
         <v>-1856746.031746032</v>
       </c>
       <c r="BI9" t="n">
-        <v>14.4126984126984</v>
+        <v>-4.376984126984127</v>
       </c>
       <c r="BJ9" t="n">
+        <v>-4.301587301587318</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>-546856.7104872246</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>1.544796772875809</v>
+      </c>
+      <c r="BN9" t="n">
         <v>1.263060754604879</v>
       </c>
-      <c r="BK9" t="n">
-        <v>0.6823762791304944</v>
-      </c>
-      <c r="BL9" t="n">
+      <c r="BO9" t="n">
+        <v>0.1587301587301591</v>
+      </c>
+      <c r="BP9" t="n">
         <v>-2.967303154601225</v>
       </c>
-      <c r="BM9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN9" t="n">
-        <v>-1.559944574420669</v>
-      </c>
-      <c r="BO9" t="n">
-        <v>-604334.0089166118</v>
-      </c>
-      <c r="BP9" t="n">
-        <v>0</v>
-      </c>
       <c r="BQ9" t="n">
-        <v>-1.096812797088532</v>
+        <v>-0.6001194282154003</v>
       </c>
       <c r="BR9" t="n">
         <v>0.1587301587301591</v>
       </c>
       <c r="BS9" t="n">
-        <v>-0.6001194282154003</v>
+        <v>-1.096812797088532</v>
       </c>
       <c r="BT9" t="n">
-        <v>1.544796772875809</v>
-      </c>
-      <c r="BU9" t="inlineStr"/>
+        <v>-2.001235675657284</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>-604334.0089166118</v>
+      </c>
       <c r="BV9" t="n">
-        <v>-546856.7104872246</v>
+        <v>2.817460317460331</v>
       </c>
     </row>
     <row r="10">
@@ -2727,70 +2727,70 @@
         <v>0.4097222222222222</v>
       </c>
       <c r="BA10" t="n">
-        <v>-2.319444444444429</v>
+        <v>24872.94142404437</v>
       </c>
       <c r="BB10" t="n">
-        <v>24872.94142404437</v>
+        <v>15685.18518518519</v>
       </c>
       <c r="BC10" t="n">
-        <v>15685.18518518519</v>
+        <v>1.135705242135828</v>
       </c>
       <c r="BD10" t="n">
-        <v>-24.4074074074074</v>
+        <v>0.2661090362070757</v>
       </c>
       <c r="BE10" t="n">
-        <v>-0.3333333333333333</v>
+        <v>17877.66439909297</v>
       </c>
       <c r="BF10" t="n">
-        <v>-2.569444444444443</v>
+        <v>7.476994949494937</v>
       </c>
       <c r="BG10" t="n">
-        <v>7.364615726895053</v>
+        <v>-26.87037037037037</v>
       </c>
       <c r="BH10" t="n">
         <v>9208796.296296295</v>
       </c>
       <c r="BI10" t="n">
-        <v>-26.87037037037037</v>
+        <v>-2.569444444444443</v>
       </c>
       <c r="BJ10" t="n">
+        <v>-24.4074074074074</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>11441312.18434343</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>0.4703030303030304</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>0.2106186868686848</v>
+      </c>
+      <c r="BN10" t="n">
         <v>-4.637184343434313</v>
       </c>
-      <c r="BK10" t="n">
-        <v>1.135705242135828</v>
-      </c>
-      <c r="BL10" t="n">
+      <c r="BO10" t="n">
+        <v>-0.3333333333333333</v>
+      </c>
+      <c r="BP10" t="n">
         <v>6.768493045366284</v>
       </c>
-      <c r="BM10" t="n">
-        <v>0.2661090362070757</v>
-      </c>
-      <c r="BN10" t="n">
-        <v>7.476994949494937</v>
-      </c>
-      <c r="BO10" t="n">
-        <v>8557743.478787716</v>
-      </c>
-      <c r="BP10" t="n">
-        <v>0.4703030303030304</v>
-      </c>
       <c r="BQ10" t="n">
-        <v>8.799760101010094</v>
+        <v>-1.924816376355604</v>
       </c>
       <c r="BR10" t="n">
         <v>-0.4814814814814814</v>
       </c>
       <c r="BS10" t="n">
-        <v>-1.924816376355604</v>
+        <v>8.799760101010094</v>
       </c>
       <c r="BT10" t="n">
-        <v>0.2106186868686848</v>
+        <v>7.364615726895053</v>
       </c>
       <c r="BU10" t="n">
-        <v>17877.66439909297</v>
+        <v>8557743.478787716</v>
       </c>
       <c r="BV10" t="n">
-        <v>11441312.18434343</v>
+        <v>-2.319444444444429</v>
       </c>
     </row>
     <row r="11">
@@ -2949,70 +2949,70 @@
         <v>0.3888888888888889</v>
       </c>
       <c r="BA11" t="n">
-        <v>-5.168333333333351</v>
+        <v>-21103.78086419753</v>
       </c>
       <c r="BB11" t="n">
-        <v>-21103.78086419753</v>
+        <v>-51209.23076923077</v>
       </c>
       <c r="BC11" t="n">
-        <v>-51209.23076923077</v>
+        <v>-2.713100233100278</v>
       </c>
       <c r="BD11" t="n">
-        <v>-52.60000000000002</v>
+        <v>0.02857364857364875</v>
       </c>
       <c r="BE11" t="n">
-        <v>-1.163076923076924</v>
+        <v>-18169.35226389772</v>
       </c>
       <c r="BF11" t="n">
-        <v>0.9512051282051246</v>
+        <v>-3.784027777777794</v>
       </c>
       <c r="BG11" t="n">
-        <v>-3.533981573981578</v>
+        <v>-55.1369230769231</v>
       </c>
       <c r="BH11" t="n">
         <v>-26914115.38461538</v>
       </c>
       <c r="BI11" t="n">
-        <v>-55.1369230769231</v>
+        <v>0.9512051282051246</v>
       </c>
       <c r="BJ11" t="n">
+        <v>-52.60000000000002</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>-8849739.583333334</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>0.2138888888888888</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>0.7854166666666664</v>
+      </c>
+      <c r="BN11" t="n">
         <v>-2.53611111111104</v>
       </c>
-      <c r="BK11" t="n">
-        <v>-2.713100233100278</v>
-      </c>
-      <c r="BL11" t="n">
+      <c r="BO11" t="n">
+        <v>-1.163076923076924</v>
+      </c>
+      <c r="BP11" t="n">
         <v>-6.309208569208565</v>
       </c>
-      <c r="BM11" t="n">
-        <v>0.02857364857364875</v>
-      </c>
-      <c r="BN11" t="n">
-        <v>-3.784027777777794</v>
-      </c>
-      <c r="BO11" t="n">
-        <v>-7336053.779553778</v>
-      </c>
-      <c r="BP11" t="n">
-        <v>0.2138888888888888</v>
-      </c>
       <c r="BQ11" t="n">
-        <v>-3.879166666666663</v>
+        <v>-0.5777067377067411</v>
       </c>
       <c r="BR11" t="n">
         <v>-0.6953846153846155</v>
       </c>
       <c r="BS11" t="n">
-        <v>-0.5777067377067411</v>
+        <v>-3.879166666666663</v>
       </c>
       <c r="BT11" t="n">
-        <v>0.7854166666666664</v>
+        <v>-3.533981573981578</v>
       </c>
       <c r="BU11" t="n">
-        <v>-18169.35226389772</v>
+        <v>-7336053.779553778</v>
       </c>
       <c r="BV11" t="n">
-        <v>-8849739.583333334</v>
+        <v>-5.168333333333351</v>
       </c>
     </row>
     <row r="12">
@@ -3178,67 +3178,67 @@
       <c r="AZ12" t="n">
         <v>0.2411764705882353</v>
       </c>
-      <c r="BA12" t="n">
-        <v>-0.231349206349222</v>
-      </c>
-      <c r="BB12" t="inlineStr"/>
+      <c r="BA12" t="inlineStr"/>
+      <c r="BB12" t="n">
+        <v>26227.27272727273</v>
+      </c>
       <c r="BC12" t="n">
-        <v>26227.27272727273</v>
+        <v>-0.9575889889818541</v>
       </c>
       <c r="BD12" t="n">
-        <v>5.565476190476204</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>-0.1309523809523809</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="BE12" t="inlineStr"/>
       <c r="BF12" t="n">
-        <v>-0.08968253968253492</v>
+        <v>5.900076283670032</v>
       </c>
       <c r="BG12" t="n">
-        <v>6.094886910240689</v>
+        <v>4.976190476190482</v>
       </c>
       <c r="BH12" t="n">
         <v>8236607.142857143</v>
       </c>
       <c r="BI12" t="n">
-        <v>4.976190476190482</v>
+        <v>-0.08968253968253492</v>
       </c>
       <c r="BJ12" t="n">
+        <v>5.565476190476204</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>2334251.518157769</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>-5.163096365440108</v>
+      </c>
+      <c r="BN12" t="n">
         <v>2.261270442520384</v>
       </c>
-      <c r="BK12" t="n">
-        <v>-0.9575889889818541</v>
-      </c>
-      <c r="BL12" t="n">
+      <c r="BO12" t="n">
+        <v>-0.1309523809523809</v>
+      </c>
+      <c r="BP12" t="n">
         <v>2.37392463277115</v>
       </c>
-      <c r="BM12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN12" t="n">
-        <v>5.900076283670032</v>
-      </c>
-      <c r="BO12" t="n">
-        <v>1759844.137796214</v>
-      </c>
-      <c r="BP12" t="n">
-        <v>0</v>
-      </c>
       <c r="BQ12" t="n">
-        <v>-0.06655017436267485</v>
+        <v>-3.110993051066579</v>
       </c>
       <c r="BR12" t="n">
         <v>-0.1309523809523809</v>
       </c>
       <c r="BS12" t="n">
-        <v>-3.110993051066579</v>
+        <v>-0.06655017436267485</v>
       </c>
       <c r="BT12" t="n">
-        <v>-5.163096365440108</v>
-      </c>
-      <c r="BU12" t="inlineStr"/>
+        <v>6.094886910240689</v>
+      </c>
+      <c r="BU12" t="n">
+        <v>1759844.137796214</v>
+      </c>
       <c r="BV12" t="n">
-        <v>2334251.518157769</v>
+        <v>-0.231349206349222</v>
       </c>
     </row>
     <row r="13">
@@ -3405,70 +3405,70 @@
         <v>-0.1625</v>
       </c>
       <c r="BA13" t="n">
-        <v>0.6411282051282399</v>
+        <v>-9217.794011544011</v>
       </c>
       <c r="BB13" t="n">
-        <v>-9217.794011544011</v>
+        <v>-19238.46153846153</v>
       </c>
       <c r="BC13" t="n">
-        <v>-19238.46153846153</v>
+        <v>1.669127070505766</v>
       </c>
       <c r="BD13" t="n">
-        <v>-27.27846153846156</v>
+        <v>-0.1075786822110349</v>
       </c>
       <c r="BE13" t="n">
-        <v>-0.5846153846153848</v>
+        <v>-7174.325479349991</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.26528205128205</v>
+        <v>-2.812839706589727</v>
       </c>
       <c r="BG13" t="n">
-        <v>-3.506343503310418</v>
+        <v>-35.38923076923078</v>
       </c>
       <c r="BH13" t="n">
         <v>-13814000</v>
       </c>
       <c r="BI13" t="n">
-        <v>-35.38923076923078</v>
+        <v>1.26528205128205</v>
       </c>
       <c r="BJ13" t="n">
+        <v>-27.27846153846156</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>-4688518.879268879</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>0.04325336700336724</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>0.8230579605579571</v>
+      </c>
+      <c r="BN13" t="n">
         <v>-2.753651996151973</v>
       </c>
-      <c r="BK13" t="n">
-        <v>1.669127070505766</v>
-      </c>
-      <c r="BL13" t="n">
+      <c r="BO13" t="n">
+        <v>-0.5846153846153848</v>
+      </c>
+      <c r="BP13" t="n">
         <v>-1.899572166667767</v>
       </c>
-      <c r="BM13" t="n">
-        <v>-0.1075786822110349</v>
-      </c>
-      <c r="BN13" t="n">
-        <v>-2.812839706589727</v>
-      </c>
-      <c r="BO13" t="n">
-        <v>-3636399.219205133</v>
-      </c>
-      <c r="BP13" t="n">
-        <v>0.04325336700336724</v>
-      </c>
       <c r="BQ13" t="n">
-        <v>-2.077320226070228</v>
+        <v>2.780382777625427</v>
       </c>
       <c r="BR13" t="n">
         <v>-0.2953846153846156</v>
       </c>
       <c r="BS13" t="n">
-        <v>2.780382777625427</v>
+        <v>-2.077320226070228</v>
       </c>
       <c r="BT13" t="n">
-        <v>0.8230579605579571</v>
+        <v>-3.506343503310418</v>
       </c>
       <c r="BU13" t="n">
-        <v>-7174.325479349991</v>
+        <v>-3636399.219205133</v>
       </c>
       <c r="BV13" t="n">
-        <v>-4688518.879268879</v>
+        <v>0.6411282051282399</v>
       </c>
     </row>
     <row r="14">
@@ -3633,68 +3633,68 @@
         <v>0.2352941176470588</v>
       </c>
       <c r="BA14" t="n">
-        <v>6.647714285714272</v>
+        <v>-12166.32924068269</v>
       </c>
       <c r="BB14" t="n">
-        <v>-12166.32924068269</v>
+        <v>-11222.22222222222</v>
       </c>
       <c r="BC14" t="n">
-        <v>-11222.22222222222</v>
+        <v>-4.504008994347373</v>
       </c>
       <c r="BD14" t="n">
-        <v>62.11428571428573</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>0.9142857142857144</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="BE14" t="inlineStr"/>
       <c r="BF14" t="n">
-        <v>2.605809523809526</v>
+        <v>-6.950627240143376</v>
       </c>
       <c r="BG14" t="n">
-        <v>-3.756669541819917</v>
+        <v>65.91428571428571</v>
       </c>
       <c r="BH14" t="n">
         <v>-681714.2857142859</v>
       </c>
       <c r="BI14" t="n">
-        <v>65.91428571428571</v>
+        <v>2.605809523809526</v>
       </c>
       <c r="BJ14" t="n">
+        <v>62.11428571428573</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>-4847900.37471489</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>-0.125</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>0.7018572825024449</v>
+      </c>
+      <c r="BN14" t="n">
         <v>-3.79635874877809</v>
       </c>
-      <c r="BK14" t="n">
-        <v>-4.504008994347373</v>
-      </c>
-      <c r="BL14" t="n">
+      <c r="BO14" t="n">
+        <v>0.9142857142857144</v>
+      </c>
+      <c r="BP14" t="n">
         <v>-4.0311686684243</v>
       </c>
-      <c r="BM14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN14" t="n">
-        <v>-6.950627240143376</v>
-      </c>
-      <c r="BO14" t="n">
-        <v>-1574543.881348393</v>
-      </c>
-      <c r="BP14" t="n">
-        <v>-0.125</v>
-      </c>
       <c r="BQ14" t="n">
-        <v>-4.828535353535344</v>
+        <v>0.05987219130075871</v>
       </c>
       <c r="BR14" t="n">
         <v>0.9942857142857144</v>
       </c>
       <c r="BS14" t="n">
-        <v>0.05987219130075871</v>
+        <v>-4.828535353535344</v>
       </c>
       <c r="BT14" t="n">
-        <v>0.7018572825024449</v>
-      </c>
-      <c r="BU14" t="inlineStr"/>
+        <v>-3.756669541819917</v>
+      </c>
+      <c r="BU14" t="n">
+        <v>-1574543.881348393</v>
+      </c>
       <c r="BV14" t="n">
-        <v>-4847900.37471489</v>
+        <v>6.647714285714272</v>
       </c>
     </row>
     <row r="15">
@@ -3852,69 +3852,69 @@
       <c r="AZ15" t="n">
         <v>-0.4791666666666666</v>
       </c>
-      <c r="BA15" t="n">
-        <v>7.788255360623793</v>
-      </c>
-      <c r="BB15" t="inlineStr"/>
+      <c r="BA15" t="inlineStr"/>
+      <c r="BB15" t="n">
+        <v>-58777.77777777778</v>
+      </c>
       <c r="BC15" t="n">
-        <v>-58777.77777777778</v>
+        <v>3.161621762740197</v>
       </c>
       <c r="BD15" t="n">
-        <v>-21.11695906432749</v>
+        <v>-0.9983333333333335</v>
       </c>
       <c r="BE15" t="n">
-        <v>-1.742690058479532</v>
+        <v>-40422.8231292517</v>
       </c>
       <c r="BF15" t="n">
-        <v>-0.07967836257309813</v>
+        <v>-4.982222222222219</v>
       </c>
       <c r="BG15" t="n">
-        <v>-6.675503267096332</v>
+        <v>-19.03216374269007</v>
       </c>
       <c r="BH15" t="n">
         <v>-16496125.73099415</v>
       </c>
       <c r="BI15" t="n">
-        <v>-19.03216374269007</v>
+        <v>-0.07967836257309813</v>
       </c>
       <c r="BJ15" t="n">
+        <v>-21.11695906432749</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>-10700940.97222222</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>-1.338194444444447</v>
+      </c>
+      <c r="BN15" t="n">
         <v>5.610972222222188</v>
       </c>
-      <c r="BK15" t="n">
-        <v>3.161621762740197</v>
-      </c>
-      <c r="BL15" t="n">
+      <c r="BO15" t="n">
+        <v>-1.742690058479532</v>
+      </c>
+      <c r="BP15" t="n">
         <v>-12.31076247165532</v>
       </c>
-      <c r="BM15" t="n">
-        <v>-0.9983333333333335</v>
-      </c>
-      <c r="BN15" t="n">
-        <v>-4.982222222222219</v>
-      </c>
-      <c r="BO15" t="n">
-        <v>-13352829.06857919</v>
-      </c>
-      <c r="BP15" t="n">
-        <v>-0.75</v>
-      </c>
       <c r="BQ15" t="n">
-        <v>-8.106805555555553</v>
+        <v>-3.574557002625617</v>
       </c>
       <c r="BR15" t="n">
         <v>-0.1111111111111112</v>
       </c>
       <c r="BS15" t="n">
-        <v>-3.574557002625617</v>
+        <v>-8.106805555555553</v>
       </c>
       <c r="BT15" t="n">
-        <v>-1.338194444444447</v>
+        <v>-6.675503267096332</v>
       </c>
       <c r="BU15" t="n">
-        <v>-40422.8231292517</v>
+        <v>-13352829.06857919</v>
       </c>
       <c r="BV15" t="n">
-        <v>-10700940.97222222</v>
+        <v>7.788255360623793</v>
       </c>
     </row>
     <row r="16">
@@ -4071,70 +4071,70 @@
         <v>0.2631578947368421</v>
       </c>
       <c r="BA16" t="n">
-        <v>5.479310344827582</v>
+        <v>72247.87581699347</v>
       </c>
       <c r="BB16" t="n">
-        <v>72247.87581699347</v>
+        <v>195387.5862068966</v>
       </c>
       <c r="BC16" t="n">
-        <v>195387.5862068966</v>
+        <v>1.469083879083882</v>
       </c>
       <c r="BD16" t="n">
-        <v>109.8262068965518</v>
+        <v>0.6860839160839161</v>
       </c>
       <c r="BE16" t="n">
-        <v>3.688275862068966</v>
+        <v>72606.41749123891</v>
       </c>
       <c r="BF16" t="n">
-        <v>0.03402298850574681</v>
+        <v>8.620969498910696</v>
       </c>
       <c r="BG16" t="n">
-        <v>8.374460169460136</v>
+        <v>113.6579310344827</v>
       </c>
       <c r="BH16" t="n">
         <v>102434027.5862069</v>
       </c>
       <c r="BI16" t="n">
-        <v>113.6579310344827</v>
+        <v>0.03402298850574681</v>
       </c>
       <c r="BJ16" t="n">
+        <v>109.8262068965518</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>51059297.38562091</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>0.8320806100217866</v>
+      </c>
+      <c r="BM16" t="n">
+        <v>-0.5278867102396525</v>
+      </c>
+      <c r="BN16" t="n">
         <v>1.429793028322365</v>
       </c>
-      <c r="BK16" t="n">
-        <v>1.469083879083882</v>
-      </c>
-      <c r="BL16" t="n">
+      <c r="BO16" t="n">
+        <v>3.688275862068966</v>
+      </c>
+      <c r="BP16" t="n">
         <v>8.87080012580013</v>
       </c>
-      <c r="BM16" t="n">
-        <v>0.6860839160839161</v>
-      </c>
-      <c r="BN16" t="n">
-        <v>8.620969498910696</v>
-      </c>
-      <c r="BO16" t="n">
-        <v>43620631.03100602</v>
-      </c>
-      <c r="BP16" t="n">
-        <v>0.8320806100217866</v>
-      </c>
       <c r="BQ16" t="n">
-        <v>10.06448801742918</v>
+        <v>-1.126496281496284</v>
       </c>
       <c r="BR16" t="n">
         <v>1.173793103448276</v>
       </c>
       <c r="BS16" t="n">
-        <v>-1.126496281496284</v>
+        <v>10.06448801742918</v>
       </c>
       <c r="BT16" t="n">
-        <v>-0.5278867102396525</v>
+        <v>8.374460169460136</v>
       </c>
       <c r="BU16" t="n">
-        <v>72606.41749123891</v>
+        <v>43620631.03100602</v>
       </c>
       <c r="BV16" t="n">
-        <v>51059297.38562091</v>
+        <v>5.479310344827582</v>
       </c>
     </row>
     <row r="17">
@@ -4293,70 +4293,70 @@
         <v>-0.09999999999999998</v>
       </c>
       <c r="BA17" t="n">
-        <v>6.671611721611754</v>
+        <v>-22737.98121070848</v>
       </c>
       <c r="BB17" t="n">
-        <v>-22737.98121070848</v>
+        <v>-47769.23076923077</v>
       </c>
       <c r="BC17" t="n">
-        <v>-47769.23076923077</v>
+        <v>2.631666165934774</v>
       </c>
       <c r="BD17" t="n">
-        <v>73.92307692307693</v>
+        <v>-0.4044737791448316</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.192307692307693</v>
+        <v>-18191.85636929767</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.556959706959709</v>
+        <v>-6.267232848850497</v>
       </c>
       <c r="BG17" t="n">
-        <v>-2.941750115782611</v>
+        <v>72.5</v>
       </c>
       <c r="BH17" t="n">
         <v>-12309615.38461538</v>
       </c>
       <c r="BI17" t="n">
-        <v>72.5</v>
+        <v>1.556959706959709</v>
       </c>
       <c r="BJ17" t="n">
+        <v>73.92307692307693</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>-10475333.09623383</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>-0.1499999999999999</v>
+      </c>
+      <c r="BM17" t="n">
+        <v>0.1879119246766372</v>
+      </c>
+      <c r="BN17" t="n">
         <v>1.559943324649197</v>
       </c>
-      <c r="BK17" t="n">
-        <v>2.631666165934774</v>
-      </c>
-      <c r="BL17" t="n">
+      <c r="BO17" t="n">
+        <v>1.192307692307693</v>
+      </c>
+      <c r="BP17" t="n">
         <v>-6.079671349533939</v>
       </c>
-      <c r="BM17" t="n">
-        <v>-0.4044737791448316</v>
-      </c>
-      <c r="BN17" t="n">
-        <v>-6.267232848850497</v>
-      </c>
-      <c r="BO17" t="n">
-        <v>-5064862.877168411</v>
-      </c>
-      <c r="BP17" t="n">
-        <v>-0.1499999999999999</v>
-      </c>
       <c r="BQ17" t="n">
-        <v>-6.459368001279771</v>
+        <v>-2.02149270792847</v>
       </c>
       <c r="BR17" t="n">
         <v>1.230769230769231</v>
       </c>
       <c r="BS17" t="n">
-        <v>-2.02149270792847</v>
+        <v>-6.459368001279771</v>
       </c>
       <c r="BT17" t="n">
-        <v>0.1879119246766372</v>
+        <v>-2.941750115782611</v>
       </c>
       <c r="BU17" t="n">
-        <v>-18191.85636929767</v>
+        <v>-5064862.877168411</v>
       </c>
       <c r="BV17" t="n">
-        <v>-10475333.09623383</v>
+        <v>6.671611721611754</v>
       </c>
     </row>
     <row r="18">
@@ -4515,70 +4515,70 @@
         <v>0.5444444444444445</v>
       </c>
       <c r="BA18" t="n">
-        <v>0.407407407407419</v>
+        <v>-14548.75010610305</v>
       </c>
       <c r="BB18" t="n">
-        <v>-14548.75010610305</v>
+        <v>-6907.407407407409</v>
       </c>
       <c r="BC18" t="n">
-        <v>-6907.407407407409</v>
+        <v>-0.6285258844278587</v>
       </c>
       <c r="BD18" t="n">
-        <v>4.462962962962962</v>
+        <v>-0.1040268700072622</v>
       </c>
       <c r="BE18" t="n">
-        <v>0.2222222222222221</v>
+        <v>-9460.526610644258</v>
       </c>
       <c r="BF18" t="n">
-        <v>3.986111111111111</v>
+        <v>-5.822171717171699</v>
       </c>
       <c r="BG18" t="n">
-        <v>-5.53799481273991</v>
+        <v>-0.1296296296296333</v>
       </c>
       <c r="BH18" t="n">
         <v>-8890740.740740739</v>
       </c>
       <c r="BI18" t="n">
-        <v>-0.1296296296296333</v>
+        <v>3.986111111111111</v>
       </c>
       <c r="BJ18" t="n">
+        <v>4.462962962962962</v>
+      </c>
+      <c r="BK18" t="n">
+        <v>-9645164.682539683</v>
+      </c>
+      <c r="BL18" t="n">
+        <v>-0.2931385281385284</v>
+      </c>
+      <c r="BM18" t="n">
+        <v>2.341356421356423</v>
+      </c>
+      <c r="BN18" t="n">
         <v>-0.06051226551224431</v>
       </c>
-      <c r="BK18" t="n">
-        <v>-0.6285258844278587</v>
-      </c>
-      <c r="BL18" t="n">
+      <c r="BO18" t="n">
+        <v>0.2222222222222221</v>
+      </c>
+      <c r="BP18" t="n">
         <v>-2.611568108724967</v>
       </c>
-      <c r="BM18" t="n">
-        <v>-0.1040268700072622</v>
-      </c>
-      <c r="BN18" t="n">
-        <v>-5.822171717171699</v>
-      </c>
-      <c r="BO18" t="n">
-        <v>-7308588.873327112</v>
-      </c>
-      <c r="BP18" t="n">
-        <v>-0.2931385281385284</v>
-      </c>
       <c r="BQ18" t="n">
-        <v>-2.731031746031746</v>
+        <v>2.074289345367774</v>
       </c>
       <c r="BR18" t="n">
         <v>0.09259259259259256</v>
       </c>
       <c r="BS18" t="n">
-        <v>2.074289345367774</v>
+        <v>-2.731031746031746</v>
       </c>
       <c r="BT18" t="n">
-        <v>2.341356421356423</v>
+        <v>-5.53799481273991</v>
       </c>
       <c r="BU18" t="n">
-        <v>-9460.526610644258</v>
+        <v>-7308588.873327112</v>
       </c>
       <c r="BV18" t="n">
-        <v>-9645164.682539683</v>
+        <v>0.407407407407419</v>
       </c>
     </row>
     <row r="19">
@@ -4737,70 +4737,70 @@
         <v>0.1360294117647059</v>
       </c>
       <c r="BA19" t="n">
-        <v>-7.477523809523802</v>
+        <v>14124.36868686869</v>
       </c>
       <c r="BB19" t="n">
-        <v>14124.36868686869</v>
+        <v>154160</v>
       </c>
       <c r="BC19" t="n">
-        <v>154160</v>
+        <v>-0.5176458583883345</v>
       </c>
       <c r="BD19" t="n">
-        <v>251.68</v>
+        <v>-0.158945477037582</v>
       </c>
       <c r="BE19" t="n">
-        <v>3.76</v>
+        <v>-7210.476190476191</v>
       </c>
       <c r="BF19" t="n">
-        <v>-4.96833333333333</v>
+        <v>0.05090488215489586</v>
       </c>
       <c r="BG19" t="n">
-        <v>3.587291963466768</v>
+        <v>275.64</v>
       </c>
       <c r="BH19" t="n">
         <v>62652000</v>
       </c>
       <c r="BI19" t="n">
-        <v>275.64</v>
+        <v>-4.96833333333333</v>
       </c>
       <c r="BJ19" t="n">
+        <v>251.68</v>
+      </c>
+      <c r="BK19" t="n">
+        <v>2132384.785353534</v>
+      </c>
+      <c r="BL19" t="n">
+        <v>0.002681577681577618</v>
+      </c>
+      <c r="BM19" t="n">
+        <v>-0.5274170274170302</v>
+      </c>
+      <c r="BN19" t="n">
         <v>-1.951530182780175</v>
       </c>
-      <c r="BK19" t="n">
-        <v>-0.5176458583883345</v>
-      </c>
-      <c r="BL19" t="n">
+      <c r="BO19" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="BP19" t="n">
         <v>-3.480107538660164</v>
       </c>
-      <c r="BM19" t="n">
-        <v>-0.158945477037582</v>
-      </c>
-      <c r="BN19" t="n">
-        <v>0.05090488215489586</v>
-      </c>
-      <c r="BO19" t="n">
-        <v>1416256.325780528</v>
-      </c>
-      <c r="BP19" t="n">
-        <v>0.002681577681577618</v>
-      </c>
       <c r="BQ19" t="n">
-        <v>-0.6321308321308265</v>
+        <v>-5.763555351290311</v>
       </c>
       <c r="BR19" t="n">
         <v>3.28</v>
       </c>
       <c r="BS19" t="n">
-        <v>-5.763555351290311</v>
+        <v>-0.6321308321308265</v>
       </c>
       <c r="BT19" t="n">
-        <v>-0.5274170274170302</v>
+        <v>3.587291963466768</v>
       </c>
       <c r="BU19" t="n">
-        <v>-7210.476190476191</v>
+        <v>1416256.325780528</v>
       </c>
       <c r="BV19" t="n">
-        <v>2132384.785353534</v>
+        <v>-7.477523809523802</v>
       </c>
     </row>
   </sheetData>

--- a/data/france/p6_deployment/data_preparation/df_tagged.xlsx
+++ b/data/france/p6_deployment/data_preparation/df_tagged.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BV6"/>
+  <dimension ref="A1:BV19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -690,132 +690,132 @@
       </c>
       <c r="BA1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_age_player_start</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rep_player_start</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_sub</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_wage_player_sub</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rep_player_sub</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_miss</t>
+        </is>
+      </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_start</t>
+        </is>
+      </c>
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_wage_player_start</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_value_player_miss</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_start</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>dif_n_player_miss</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_rat_player_start</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_wage_player_sub</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BM1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_sub</t>
+        </is>
+      </c>
+      <c r="BN1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_wage_player_miss</t>
+        </is>
+      </c>
+      <c r="BO1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_rep_player_miss</t>
+        </is>
+      </c>
+      <c r="BP1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_miss</t>
+        </is>
+      </c>
+      <c r="BQ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_sub</t>
+        </is>
+      </c>
+      <c r="BR1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_rat_player_miss</t>
+        </is>
+      </c>
+      <c r="BS1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_value_player_start</t>
+        </is>
+      </c>
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>dif_sum_pot_player_miss</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_sub</t>
-        </is>
-      </c>
-      <c r="BE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rep_player_start</t>
-        </is>
-      </c>
-      <c r="BF1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_rep_player_miss</t>
-        </is>
-      </c>
-      <c r="BG1" s="1" t="inlineStr">
-        <is>
-          <t>dif_n_player_miss</t>
-        </is>
-      </c>
-      <c r="BH1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rep_player_sub</t>
-        </is>
-      </c>
-      <c r="BI1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_value_player_start</t>
-        </is>
-      </c>
-      <c r="BJ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_sub</t>
-        </is>
-      </c>
-      <c r="BK1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_start</t>
-        </is>
-      </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_hei_player_sub</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_sub</t>
-        </is>
-      </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BV1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_value_player_sub</t>
-        </is>
-      </c>
-      <c r="BO1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_value_player_miss</t>
-        </is>
-      </c>
-      <c r="BP1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_wage_player_start</t>
-        </is>
-      </c>
-      <c r="BQ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_start</t>
-        </is>
-      </c>
-      <c r="BR1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_start</t>
-        </is>
-      </c>
-      <c r="BS1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_rat_player_miss</t>
-        </is>
-      </c>
-      <c r="BT1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_miss</t>
-        </is>
-      </c>
-      <c r="BU1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_miss</t>
-        </is>
-      </c>
-      <c r="BV1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_wage_player_miss</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>nVutWTU8</t>
+          <t>UTsToXQN</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45585.65625</v>
+        <v>45599.69791666666</v>
       </c>
       <c r="C2" t="n">
         <v>103</v>
       </c>
       <c r="D2" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E2" t="n">
-        <v>242</v>
+        <v>858</v>
       </c>
       <c r="F2" t="n">
         <v>303</v>
@@ -840,207 +840,209 @@
         </is>
       </c>
       <c r="L2" t="n">
+        <v>168</v>
+      </c>
+      <c r="M2" t="n">
+        <v>258</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.8733333333333334</v>
+      </c>
+      <c r="P2" t="n">
+        <v>-0.1976388888888887</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>2</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0.02960526315789469</v>
+      </c>
+      <c r="S2" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0.9583333333333339</v>
+      </c>
+      <c r="U2" t="n">
+        <v>8.333333333333332</v>
+      </c>
+      <c r="V2" t="n">
+        <v>-0.02777777777777857</v>
+      </c>
+      <c r="W2" t="n">
+        <v>-2</v>
+      </c>
+      <c r="X2" t="n">
+        <v>-1.463815789473684</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>-2</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>-1.6875</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>16.94552438302438</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>19.81343443096458</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>1085.583999518684</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>1002.848719162645</v>
+      </c>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="n">
+        <v>-19.65714285714286</v>
+      </c>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="n">
+        <v>-6.209523809523802</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>3.999999999999993</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>1.098684210526315</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>-8.666666666666657</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>-20.73611111111111</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>-404.5</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>-213.1047619047619</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>0.5441176470588234</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AS2" t="n">
         <v>12</v>
       </c>
-      <c r="M2" t="n">
-        <v>32</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0.696666666666667</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0.4731045751633984</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>1</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0.833333333333333</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1.787581699346406</v>
-      </c>
-      <c r="U2" t="n">
-        <v>4.666666666666666</v>
-      </c>
-      <c r="V2" t="n">
-        <v>0.3954248366013076</v>
-      </c>
-      <c r="W2" t="n">
-        <v>-1.166666666666667</v>
-      </c>
-      <c r="X2" t="n">
-        <v>-0.5555555555555558</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>-0.1666666666666665</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>14.39148629148629</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>22.08237333630136</v>
-      </c>
-      <c r="AC2" t="inlineStr"/>
-      <c r="AD2" t="n">
-        <v>978.1111050666836</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>18</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>-22.9764705882353</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>3</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>-3.478431372549018</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>16.66666666666667</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>1.166666666666671</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>8.333333333333329</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>-18.62091503267973</v>
-      </c>
-      <c r="AM2" t="inlineStr"/>
-      <c r="AN2" t="n">
-        <v>-210.0624999999999</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>0.8333333333333335</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>-0.2847222222222223</v>
-      </c>
-      <c r="AQ2" t="inlineStr"/>
-      <c r="AR2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>0.4999999999999982</v>
-      </c>
       <c r="AT2" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AU2" t="inlineStr"/>
+        <v>3.60526315789474</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>-2.100754411755156</v>
+      </c>
       <c r="AV2" t="n">
-        <v>7.027430855536034</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>0.06518289752357651</v>
-      </c>
+        <v>2.606813562749183</v>
+      </c>
+      <c r="AW2" t="inlineStr"/>
       <c r="AX2" t="n">
-        <v>0.02689583363929181</v>
+        <v>0.04008347344833654</v>
       </c>
       <c r="AY2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.3888888888888889</v>
+        <v>-0.03947368421052633</v>
       </c>
       <c r="BA2" t="n">
-        <v>-3.879166666666663</v>
+        <v>0.09467592592592666</v>
       </c>
       <c r="BB2" t="n">
-        <v>-18169.35226389772</v>
+        <v>0.2579629629629629</v>
       </c>
       <c r="BC2" t="n">
-        <v>-55.1369230769231</v>
+        <v>0.81717026029526</v>
       </c>
       <c r="BD2" t="n">
-        <v>-6.309208569208565</v>
+        <v>-11425.89105339105</v>
       </c>
       <c r="BE2" t="n">
-        <v>0.2138888888888888</v>
+        <v>0.02785117660117664</v>
       </c>
       <c r="BF2" t="n">
-        <v>-1.163076923076924</v>
+        <v>-5.290666666666681</v>
       </c>
       <c r="BG2" t="n">
-        <v>-0.6953846153846155</v>
+        <v>-3.683564814814829</v>
       </c>
       <c r="BH2" t="n">
-        <v>0.02857364857364875</v>
+        <v>-15411.80555555555</v>
       </c>
       <c r="BI2" t="n">
-        <v>-8849739.583333334</v>
+        <v>-23406000</v>
       </c>
       <c r="BJ2" t="n">
-        <v>-3.533981573981578</v>
+        <v>0.2225925925926333</v>
       </c>
       <c r="BK2" t="n">
-        <v>-2.53611111111104</v>
+        <v>-1.76</v>
       </c>
       <c r="BL2" t="n">
-        <v>-2.713100233100278</v>
+        <v>-3.600092592592588</v>
       </c>
       <c r="BM2" t="n">
-        <v>-0.5777067377067411</v>
+        <v>-4.710769716394722</v>
       </c>
       <c r="BN2" t="n">
-        <v>-7336053.779553778</v>
+        <v>-39640</v>
       </c>
       <c r="BO2" t="n">
-        <v>-26914115.38461538</v>
+        <v>-2.44</v>
       </c>
       <c r="BP2" t="n">
-        <v>-21103.78086419753</v>
+        <v>0.5619999999999976</v>
       </c>
       <c r="BQ2" t="n">
-        <v>-3.784027777777794</v>
+        <v>-4.529477362914875</v>
       </c>
       <c r="BR2" t="n">
-        <v>0.7854166666666664</v>
+        <v>-120.84</v>
       </c>
       <c r="BS2" t="n">
-        <v>-52.60000000000002</v>
+        <v>-9301084.490740741</v>
       </c>
       <c r="BT2" t="n">
-        <v>0.9512051282051246</v>
+        <v>-137.68</v>
       </c>
       <c r="BU2" t="n">
-        <v>-5.168333333333351</v>
+        <v>-0.1792792970918242</v>
       </c>
       <c r="BV2" t="n">
-        <v>-51209.23076923077</v>
+        <v>-5878102.918782605</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>vPIEF8pS</t>
+          <t>Y1lKmgdB</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45585.5</v>
+        <v>45599.54166666666</v>
       </c>
       <c r="C3" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D3" t="n">
         <v>133</v>
       </c>
       <c r="E3" t="n">
-        <v>341</v>
+        <v>194</v>
       </c>
       <c r="F3" t="n">
-        <v>292</v>
+        <v>157</v>
       </c>
       <c r="G3" t="n">
         <v>55</v>
@@ -1062,202 +1064,198 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>243</v>
+        <v>198</v>
       </c>
       <c r="M3" t="n">
-        <v>32</v>
+        <v>258</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>1.15</v>
+        <v>-1.126666666666666</v>
       </c>
       <c r="P3" t="n">
-        <v>0.6090441176470589</v>
+        <v>0.9549166666666671</v>
       </c>
       <c r="Q3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0.7058823529411766</v>
+        <v>1.411764705882353</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>-4.166666666666666</v>
       </c>
       <c r="T3" t="n">
-        <v>1.235294117647059</v>
+        <v>1.5</v>
       </c>
       <c r="U3" t="n">
-        <v>5.666666666666668</v>
+        <v>-3.666666666666666</v>
       </c>
       <c r="V3" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="W3" t="n">
-        <v>0.3333333333333331</v>
+        <v>-1.5</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.3205882352941174</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>-0.7588235294117647</v>
+        <v>-0.5294117647058825</v>
       </c>
       <c r="AA3" t="n">
-        <v>12.22146464646465</v>
+        <v>21.23761423761424</v>
       </c>
       <c r="AB3" t="n">
-        <v>16.16867368502317</v>
+        <v>17.91499910531935</v>
       </c>
       <c r="AC3" t="n">
-        <v>851.0542233885517</v>
+        <v>922.0529513128304</v>
       </c>
       <c r="AD3" t="n">
-        <v>899.0605418092503</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>40</v>
-      </c>
+        <v>866.2312035376042</v>
+      </c>
+      <c r="AE3" t="inlineStr"/>
       <c r="AF3" t="n">
-        <v>6.9375</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>5.5</v>
-      </c>
+        <v>15.42857142857144</v>
+      </c>
+      <c r="AG3" t="inlineStr"/>
       <c r="AH3" t="n">
-        <v>12.5</v>
+        <v>31</v>
       </c>
       <c r="AI3" t="n">
-        <v>15.66666666666667</v>
+        <v>-1.5</v>
       </c>
       <c r="AJ3" t="n">
-        <v>3.355882352941174</v>
+        <v>2.823529411764703</v>
       </c>
       <c r="AK3" t="n">
-        <v>11.33333333333334</v>
+        <v>-14.66666666666667</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.8235294117646959</v>
+        <v>2.625</v>
       </c>
       <c r="AM3" t="n">
-        <v>119</v>
+        <v>-197</v>
       </c>
       <c r="AN3" t="n">
-        <v>-9.133333333333326</v>
+        <v>-19.76923076923077</v>
       </c>
       <c r="AO3" t="n">
-        <v>2.666666666666667</v>
+        <v>-1</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.9999999999999996</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>1</v>
-      </c>
+        <v>-0.4375</v>
+      </c>
+      <c r="AQ3" t="inlineStr"/>
       <c r="AR3" t="n">
-        <v>0.6666666666666667</v>
+        <v>-1.666666666666667</v>
       </c>
       <c r="AS3" t="n">
-        <v>-4.333333333333334</v>
+        <v>4.999999999999998</v>
       </c>
       <c r="AT3" t="n">
-        <v>5.938235294117646</v>
+        <v>2.823529411764699</v>
       </c>
       <c r="AU3" t="n">
-        <v>-4.67122351332878</v>
+        <v>-4.217684087249303</v>
       </c>
       <c r="AV3" t="n">
-        <v>-3.379994163467748</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>-0.02784178466970873</v>
-      </c>
+        <v>-0.4674721059058093</v>
+      </c>
+      <c r="AW3" t="inlineStr"/>
       <c r="AX3" t="n">
-        <v>0.03145942709036465</v>
+        <v>0.02013651507394308</v>
       </c>
       <c r="AY3" t="n">
-        <v>0.6666666666666666</v>
+        <v>-0.6666666666666667</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.2411764705882353</v>
+        <v>-0.2941176470588235</v>
       </c>
       <c r="BA3" t="n">
-        <v>-0.06655017436267485</v>
-      </c>
-      <c r="BB3" t="inlineStr"/>
+        <v>-2.724305555555556</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>-0.3944444444444444</v>
+      </c>
       <c r="BC3" t="n">
-        <v>-87.16666666666666</v>
+        <v>1.053402260333648</v>
       </c>
       <c r="BD3" t="n">
-        <v>2.37392463277115</v>
+        <v>-6538.369855252973</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>-0.20987234987235</v>
       </c>
       <c r="BF3" t="n">
-        <v>-1.416666666666667</v>
+        <v>6.268518518518533</v>
       </c>
       <c r="BG3" t="n">
-        <v>-1.416666666666667</v>
+        <v>-3.46555555555554</v>
       </c>
       <c r="BH3" t="n">
-        <v>0</v>
+        <v>-11227.23765432099</v>
       </c>
       <c r="BI3" t="n">
-        <v>2334251.518157769</v>
+        <v>-6879273.504273505</v>
       </c>
       <c r="BJ3" t="n">
-        <v>6.094886910240689</v>
+        <v>6.508194444444371</v>
       </c>
       <c r="BK3" t="n">
-        <v>2.261270442520384</v>
+        <v>-1.495726495726496</v>
       </c>
       <c r="BL3" t="n">
-        <v>-0.9575889889818541</v>
+        <v>-6.810972222222219</v>
       </c>
       <c r="BM3" t="n">
-        <v>-3.110993051066579</v>
+        <v>-2.924944955837802</v>
       </c>
       <c r="BN3" t="n">
-        <v>1759844.137796214</v>
+        <v>-31730.76923076923</v>
       </c>
       <c r="BO3" t="n">
-        <v>6443750</v>
-      </c>
-      <c r="BP3" t="inlineStr"/>
+        <v>-2.188034188034188</v>
+      </c>
+      <c r="BP3" t="n">
+        <v>-0.7837606837606828</v>
+      </c>
       <c r="BQ3" t="n">
-        <v>5.900076283670032</v>
+        <v>-4.171182587775647</v>
       </c>
       <c r="BR3" t="n">
-        <v>-5.163096365440108</v>
+        <v>-109.2222222222222</v>
       </c>
       <c r="BS3" t="n">
-        <v>-80.29166666666666</v>
+        <v>-5175420.138888888</v>
       </c>
       <c r="BT3" t="n">
-        <v>-1.827777777777772</v>
+        <v>-117.034188034188</v>
       </c>
       <c r="BU3" t="n">
-        <v>-1.219444444444434</v>
+        <v>1.158863409981876</v>
       </c>
       <c r="BV3" t="n">
-        <v>26227.27272727273</v>
+        <v>-1700310.64256076</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>h8K6HUFF</t>
+          <t>EuWhpKkJ</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45585.5</v>
+        <v>45599.54166666666</v>
       </c>
       <c r="C4" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D4" t="n">
         <v>133</v>
@@ -1266,7 +1264,7 @@
         <v>342</v>
       </c>
       <c r="F4" t="n">
-        <v>579</v>
+        <v>399</v>
       </c>
       <c r="G4" t="n">
         <v>55</v>
@@ -1288,211 +1286,205 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>272</v>
+        <v>128</v>
       </c>
       <c r="M4" t="n">
-        <v>234</v>
+        <v>211</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.3650000000000004</v>
+        <v>1.883333333333333</v>
       </c>
       <c r="P4" t="n">
-        <v>1.0125</v>
+        <v>0.9348366013071896</v>
       </c>
       <c r="Q4" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="R4" t="n">
-        <v>1.411764705882353</v>
+        <v>1.235294117647059</v>
       </c>
       <c r="S4" t="n">
-        <v>-2.333333333333334</v>
+        <v>0.166666666666667</v>
       </c>
       <c r="T4" t="n">
-        <v>2.393382352941176</v>
+        <v>1.764705882352941</v>
       </c>
       <c r="U4" t="n">
-        <v>1.833333333333334</v>
+        <v>7.666666666666666</v>
       </c>
       <c r="V4" t="n">
-        <v>6.919117647058822</v>
+        <v>4.058823529411766</v>
       </c>
       <c r="W4" t="n">
-        <v>-1</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="X4" t="n">
-        <v>1.411764705882353</v>
+        <v>1.102941176470588</v>
       </c>
       <c r="Y4" t="n">
-        <v>-2</v>
+        <v>2.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.941176470588235</v>
+        <v>2.117647058823529</v>
       </c>
       <c r="AA4" t="n">
-        <v>22.65228428978429</v>
+        <v>19.04786324786325</v>
       </c>
       <c r="AB4" t="n">
-        <v>18.16463804052668</v>
+        <v>18.04814810282205</v>
       </c>
       <c r="AC4" t="n">
-        <v>1137.076320132013</v>
+        <v>872.0664825060937</v>
       </c>
       <c r="AD4" t="n">
-        <v>857.9659601710927</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>5.5</v>
-      </c>
+        <v>873.6203422637333</v>
+      </c>
+      <c r="AE4" t="inlineStr"/>
       <c r="AF4" t="n">
-        <v>35.6875</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>28.5</v>
-      </c>
+        <v>20.89411764705883</v>
+      </c>
+      <c r="AG4" t="inlineStr"/>
       <c r="AH4" t="n">
-        <v>25.6125</v>
+        <v>16.01568627450981</v>
       </c>
       <c r="AI4" t="n">
-        <v>5.166666666666664</v>
+        <v>-7.5</v>
       </c>
       <c r="AJ4" t="n">
-        <v>5.882352941176467</v>
+        <v>4.494117647058827</v>
       </c>
       <c r="AK4" t="n">
-        <v>-11.66666666666667</v>
+        <v>-5.333333333333329</v>
       </c>
       <c r="AL4" t="n">
-        <v>11.61029411764706</v>
+        <v>9.164086687306508</v>
       </c>
       <c r="AM4" t="n">
-        <v>-309</v>
+        <v>-104</v>
       </c>
       <c r="AN4" t="n">
-        <v>96.65178571428572</v>
+        <v>89.375</v>
       </c>
       <c r="AO4" t="n">
-        <v>2.166666666666667</v>
+        <v>0.3333333333333335</v>
       </c>
       <c r="AP4" t="n">
-        <v>-1.295833333333333</v>
+        <v>-0.929824561403509</v>
       </c>
       <c r="AQ4" t="inlineStr"/>
       <c r="AR4" t="n">
-        <v>-1.5</v>
+        <v>0</v>
       </c>
       <c r="AS4" t="n">
-        <v>2</v>
+        <v>-1.166666666666668</v>
       </c>
       <c r="AT4" t="n">
-        <v>-1.647058823529413</v>
+        <v>-3.964705882352945</v>
       </c>
       <c r="AU4" t="n">
-        <v>-23.18109668109667</v>
+        <v>12.03655788655789</v>
       </c>
       <c r="AV4" t="n">
-        <v>-4.235462010975034</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>0.09070561356589624</v>
-      </c>
+        <v>-0.01481299233423528</v>
+      </c>
+      <c r="AW4" t="inlineStr"/>
       <c r="AX4" t="n">
-        <v>-0.01651087357591465</v>
+        <v>-0.02067489693449977</v>
       </c>
       <c r="AY4" t="n">
         <v>0</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.2352941176470588</v>
+        <v>0.3441176470588235</v>
       </c>
       <c r="BA4" t="n">
-        <v>-4.828535353535344</v>
-      </c>
-      <c r="BB4" t="inlineStr"/>
+        <v>2.579433040078207</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>-0.4703030303030304</v>
+      </c>
       <c r="BC4" t="n">
-        <v>224.2</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>-4.0311686684243</v>
-      </c>
+        <v>0.758852295126804</v>
+      </c>
+      <c r="BD4" t="inlineStr"/>
       <c r="BE4" t="n">
-        <v>-0.125</v>
+        <v>-0.2661090362070757</v>
       </c>
       <c r="BF4" t="n">
-        <v>3.2</v>
+        <v>2.663392857142867</v>
       </c>
       <c r="BG4" t="n">
-        <v>3.28</v>
+        <v>-10.10789996741609</v>
       </c>
       <c r="BH4" t="n">
-        <v>0</v>
+        <v>-25562.4188128752</v>
       </c>
       <c r="BI4" t="n">
-        <v>-4847900.37471489</v>
+        <v>-9607142.857142856</v>
       </c>
       <c r="BJ4" t="n">
-        <v>-3.756669541819917</v>
+        <v>-0.5451466275659698</v>
       </c>
       <c r="BK4" t="n">
-        <v>-3.79635874877809</v>
+        <v>1.357142857142857</v>
       </c>
       <c r="BL4" t="n">
-        <v>-4.504008994347373</v>
+        <v>-6.73398989898989</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.05987219130075871</v>
+        <v>-7.366801082474453</v>
       </c>
       <c r="BN4" t="n">
-        <v>-1574543.881348393</v>
+        <v>-21142.85714285714</v>
       </c>
       <c r="BO4" t="n">
-        <v>1654000</v>
+        <v>1.214285714285714</v>
       </c>
       <c r="BP4" t="n">
-        <v>-12166.32924068269</v>
+        <v>1.756250000000001</v>
       </c>
       <c r="BQ4" t="n">
-        <v>-6.950627240143376</v>
+        <v>-7.991734302705666</v>
       </c>
       <c r="BR4" t="n">
-        <v>0.7018572825024449</v>
+        <v>79.75</v>
       </c>
       <c r="BS4" t="n">
-        <v>211.4</v>
+        <v>-11544521.5868361</v>
       </c>
       <c r="BT4" t="n">
-        <v>4.332000000000001</v>
+        <v>91.25</v>
       </c>
       <c r="BU4" t="n">
-        <v>7.145333333333326</v>
+        <v>-0.8747277246890519</v>
       </c>
       <c r="BV4" t="n">
-        <v>-11222.22222222222</v>
+        <v>-8681282.028538868</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>WMcg8Qx2</t>
+          <t>4Md3iycn</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45585.5</v>
+        <v>45599.45833333334</v>
       </c>
       <c r="C5" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D5" t="n">
         <v>133</v>
       </c>
       <c r="E5" t="n">
-        <v>858</v>
+        <v>341</v>
       </c>
       <c r="F5" t="n">
-        <v>370</v>
+        <v>579</v>
       </c>
       <c r="G5" t="n">
         <v>55</v>
@@ -1514,215 +1506,211 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="M5" t="n">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>0.623333333333333</v>
+        <v>0.8166666666666665</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.1018749999999999</v>
+        <v>0.868125</v>
       </c>
       <c r="Q5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R5" t="n">
-        <v>0.03750000000000009</v>
+        <v>1.235294117647059</v>
       </c>
       <c r="S5" t="n">
-        <v>2.333333333333333</v>
+        <v>3</v>
       </c>
       <c r="T5" t="n">
-        <v>0.02499999999999947</v>
+        <v>1.647058823529412</v>
       </c>
       <c r="U5" t="n">
         <v>7.000000000000002</v>
       </c>
       <c r="V5" t="n">
-        <v>3.35</v>
+        <v>2.863970588235293</v>
       </c>
       <c r="W5" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>-0.3333333333333335</v>
       </c>
       <c r="X5" t="n">
+        <v>-0.1176470588235294</v>
+      </c>
+      <c r="Y5" t="n">
         <v>-1</v>
       </c>
-      <c r="Y5" t="n">
-        <v>0</v>
-      </c>
       <c r="Z5" t="n">
-        <v>-1.575</v>
+        <v>-0.3529411764705883</v>
       </c>
       <c r="AA5" t="n">
-        <v>18.05397426647427</v>
+        <v>16.68835978835979</v>
       </c>
       <c r="AB5" t="n">
-        <v>19.22931619308409</v>
+        <v>18.71150218923322</v>
       </c>
       <c r="AC5" t="n">
-        <v>942.063710754843</v>
+        <v>866.0748082913971</v>
       </c>
       <c r="AD5" t="n">
-        <v>964.7961081486393</v>
+        <v>867.2883567094977</v>
       </c>
       <c r="AE5" t="n">
-        <v>-37</v>
+        <v>30</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.764912280701765</v>
+        <v>7.24761904761904</v>
       </c>
       <c r="AG5" t="n">
-        <v>3.5</v>
+        <v>8</v>
       </c>
       <c r="AH5" t="n">
-        <v>10.80701754385964</v>
+        <v>18.0857142857143</v>
       </c>
       <c r="AI5" t="n">
-        <v>3.000000000000004</v>
+        <v>7.666666666666668</v>
       </c>
       <c r="AJ5" t="n">
-        <v>4.912499999999994</v>
+        <v>3.117647058823529</v>
       </c>
       <c r="AK5" t="n">
-        <v>6</v>
+        <v>-0.6666666666666714</v>
       </c>
       <c r="AL5" t="n">
-        <v>-7.025000000000006</v>
+        <v>0.919117647058826</v>
       </c>
       <c r="AM5" t="n">
-        <v>-12</v>
+        <v>0</v>
       </c>
       <c r="AN5" t="n">
-        <v>-96.11111111111114</v>
+        <v>15.28571428571428</v>
       </c>
       <c r="AO5" t="n">
-        <v>3.000000000000001</v>
+        <v>-1.333333333333333</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.2361111111111112</v>
-      </c>
-      <c r="AQ5" t="n">
+        <v>-0.6213235294117649</v>
+      </c>
+      <c r="AQ5" t="inlineStr"/>
+      <c r="AR5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>-1.77635683940025e-15</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>0.647058823529413</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>-21.15109364319891</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>-4.539079073050594</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>-0.02230201171377642</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>0.02130051461440481</v>
+      </c>
+      <c r="AY5" t="n">
         <v>0.3333333333333333</v>
       </c>
-      <c r="AR5" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>13</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>-89.46428571428572</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>-4.897598549872562</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>-0.009408741902962953</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>0.03421637940234924</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>0.6666666666666666</v>
-      </c>
       <c r="AZ5" t="n">
-        <v>-0.1625</v>
+        <v>-1.387778780781446e-17</v>
       </c>
       <c r="BA5" t="n">
-        <v>-2.077320226070228</v>
+        <v>-2.970238095238091</v>
       </c>
       <c r="BB5" t="n">
-        <v>-7174.325479349991</v>
+        <v>-0.125</v>
       </c>
       <c r="BC5" t="n">
-        <v>-35.38923076923078</v>
+        <v>-1.819175170068029</v>
       </c>
       <c r="BD5" t="n">
-        <v>-1.899572166667767</v>
+        <v>-3009.788359788359</v>
       </c>
       <c r="BE5" t="n">
-        <v>0.04325336700336724</v>
+        <v>0</v>
       </c>
       <c r="BF5" t="n">
-        <v>-0.5846153846153848</v>
+        <v>2.125888888888881</v>
       </c>
       <c r="BG5" t="n">
-        <v>-0.2953846153846156</v>
-      </c>
-      <c r="BH5" t="n">
-        <v>-0.1075786822110349</v>
-      </c>
+        <v>-0.1648148148148181</v>
+      </c>
+      <c r="BH5" t="inlineStr"/>
       <c r="BI5" t="n">
-        <v>-4688518.879268879</v>
+        <v>6447750</v>
       </c>
       <c r="BJ5" t="n">
-        <v>-3.506343503310418</v>
+        <v>0.5937830687830399</v>
       </c>
       <c r="BK5" t="n">
-        <v>-2.753651996151973</v>
+        <v>0.8633333333333335</v>
       </c>
       <c r="BL5" t="n">
-        <v>1.669127070505766</v>
+        <v>-4.119312169312167</v>
       </c>
       <c r="BM5" t="n">
-        <v>2.780382777625427</v>
+        <v>-1.614879180838997</v>
       </c>
       <c r="BN5" t="n">
-        <v>-3636399.219205133</v>
+        <v>11005.05050505051</v>
       </c>
       <c r="BO5" t="n">
-        <v>-13814000</v>
+        <v>0.7833333333333334</v>
       </c>
       <c r="BP5" t="n">
-        <v>-9217.794011544011</v>
+        <v>1.85422222222223</v>
       </c>
       <c r="BQ5" t="n">
-        <v>-2.812839706589727</v>
+        <v>1.764865008503392</v>
       </c>
       <c r="BR5" t="n">
-        <v>0.8230579605579571</v>
+        <v>63.10833333333335</v>
       </c>
       <c r="BS5" t="n">
-        <v>-27.27846153846156</v>
+        <v>-2527820.767195767</v>
       </c>
       <c r="BT5" t="n">
-        <v>1.26528205128205</v>
+        <v>67.03333333333333</v>
       </c>
       <c r="BU5" t="n">
-        <v>0.6411282051282399</v>
+        <v>-5.176029265873012</v>
       </c>
       <c r="BV5" t="n">
-        <v>-19238.46153846153</v>
+        <v>-13853.14803004498</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>b9aoAn8k</t>
+          <t>vuBo4Eth</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45585.41666666666</v>
+        <v>45598.70833333334</v>
       </c>
       <c r="C6" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D6" t="n">
         <v>133</v>
       </c>
       <c r="E6" t="n">
-        <v>194</v>
+        <v>528</v>
       </c>
       <c r="F6" t="n">
-        <v>39</v>
+        <v>516</v>
       </c>
       <c r="G6" t="n">
         <v>55</v>
@@ -1744,183 +1732,3061 @@
         </is>
       </c>
       <c r="L6" t="n">
+        <v>272</v>
+      </c>
+      <c r="M6" t="n">
+        <v>258</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.016666666666667</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.4980718954248367</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.105263157894737</v>
+      </c>
+      <c r="S6" t="n">
+        <v>-0.3333333333333335</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1.555555555555556</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V6" t="n">
+        <v>4.333333333333332</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0.5263157894736842</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1.421052631578947</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>22.63034188034188</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>19.40838621255288</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1041.577601301818</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>835.9396384239933</v>
+      </c>
+      <c r="AE6" t="inlineStr"/>
+      <c r="AF6" t="n">
+        <v>16.75</v>
+      </c>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>-11.5</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>2.315789473684211</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>-9.333333333333336</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>7.777777777777771</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>-208</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>69</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0.3333333333333335</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>0.4673202614379086</v>
+      </c>
+      <c r="AQ6" t="inlineStr"/>
+      <c r="AR6" t="inlineStr"/>
+      <c r="AS6" t="n">
+        <v>3.499999999999998</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>2.999999999999993</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>18.2793956043956</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>-0.1858267428468388</v>
+      </c>
+      <c r="AW6" t="inlineStr"/>
+      <c r="AX6" t="n">
+        <v>-0.001322671721763272</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>0.1578947368421053</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>2.621115567439094</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>-0.2419934640522874</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>0.7642406833147852</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>-6657.620226541796</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>-0.3051136363636364</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>-5.849999999999994</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>-4.492505941770631</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>-6914.429049856855</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>-3585800</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>-1.247556446821221</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>-0.7203951277480769</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>-2.830751701930112</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>-23340</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>-1.06</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>0.9466666666666654</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>-3.552202501481716</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>28.84</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>-2389013.851752823</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>24.12</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>-1.467742393342235</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>-1873550.104825623</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>n5Eg2hB4</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45598.625</v>
+      </c>
+      <c r="C7" t="n">
+        <v>102</v>
+      </c>
+      <c r="D7" t="n">
+        <v>133</v>
+      </c>
+      <c r="E7" t="n">
+        <v>211</v>
+      </c>
+      <c r="F7" t="n">
+        <v>370</v>
+      </c>
+      <c r="G7" t="n">
+        <v>55</v>
+      </c>
+      <c r="H7" t="n">
+        <v>551</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
         <v>9</v>
       </c>
-      <c r="M6" t="n">
-        <v>141</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>-0.4299999999999998</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0.0874166666666667</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" t="n">
+      <c r="M7" t="n">
+        <v>163</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>-0.4666666666666668</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.4602499999999999</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.1833333333333333</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2.176470588235294</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>6.214705882352941</v>
+      </c>
+      <c r="W7" t="n">
+        <v>2</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0.8833333333333334</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>1.783333333333333</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>21.48131313131313</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>18.25763663167859</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>804.5547290995599</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>856.1488261030743</v>
+      </c>
+      <c r="AE7" t="inlineStr"/>
+      <c r="AF7" t="n">
+        <v>39.38888888888889</v>
+      </c>
+      <c r="AG7" t="inlineStr"/>
+      <c r="AH7" t="n">
+        <v>27.23809523809524</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>-10.33333333333334</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>4.366666666666667</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>3.333333333333329</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>10.65294117647059</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>78.5</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>119.8650793650794</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>3</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>0.9836601307189543</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>0.1666666666666666</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>10</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>3.950000000000003</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>-29.22283966033967</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>-6.255935633683574</v>
+      </c>
+      <c r="AW7" t="inlineStr"/>
+      <c r="AX7" t="n">
+        <v>0.02435362985374841</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>0.6444444444444446</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>1.361012238790011</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>-0.2179252845919513</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>2.506918168336853</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>-12438.92072229962</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>-0.1497480739176236</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>5.038814814814856</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>-4.739188178077043</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>-15711.10843888621</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>-23887333.33333333</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>-3.729270215381291</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>-3.099492277270045</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>-2.242630656540697</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>-53042.22222222222</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>-1.582222222222222</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>2.319444444444443</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>-4.773734507706834</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>-87.00666666666667</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>-7654239.317780985</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>-95.8111111111111</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>0.9634595560149251</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>-5398260.920250453</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>rX720WuH</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45598.54166666666</v>
+      </c>
+      <c r="C8" t="n">
+        <v>103</v>
+      </c>
+      <c r="D8" t="n">
+        <v>133</v>
+      </c>
+      <c r="E8" t="n">
+        <v>206</v>
+      </c>
+      <c r="F8" t="n">
+        <v>176</v>
+      </c>
+      <c r="G8" t="n">
+        <v>55</v>
+      </c>
+      <c r="H8" t="n">
+        <v>551</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>40</v>
+      </c>
+      <c r="M8" t="n">
+        <v>83</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>2.246666666666667</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.311776315789473</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>3</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.894736842105263</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3.666666666666667</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.213815789473684</v>
+      </c>
+      <c r="U8" t="n">
+        <v>10</v>
+      </c>
+      <c r="V8" t="n">
+        <v>6.644736842105264</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.036184210526316</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1.519736842105263</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>18.08324915824916</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>18.31860651231482</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>931.5822393258702</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>848.6045219786938</v>
+      </c>
+      <c r="AE8" t="inlineStr"/>
+      <c r="AF8" t="n">
+        <v>54.5927601809955</v>
+      </c>
+      <c r="AG8" t="inlineStr"/>
+      <c r="AH8" t="n">
+        <v>34.65158371040724</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>3.666666666666664</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>9.167763157894733</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>-1.333333333333343</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>18.04605263157895</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>198.8144796380091</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>-2.666666666666667</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>-1.375</v>
+      </c>
+      <c r="AQ8" t="inlineStr"/>
+      <c r="AR8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>-3.666666666666668</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>-7.513157894736842</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>-6.828205128205127</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>-3.010274241173892</v>
+      </c>
+      <c r="AW8" t="inlineStr"/>
+      <c r="AX8" t="n">
+        <v>0.02562133061452004</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>-0.3333333333333333</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>-0.1546052631578947</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>-2.997186609686608</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>0.924074074074074</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>-3.833464744320008</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>61681.75291448316</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>0.6070646823936299</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>16.15092206643934</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>6.884009971509983</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>56423.2905982906</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>91810212.20159152</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>4.214565527065474</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>0.6445623342175066</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>4.322507122507119</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>5.758675954893064</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>166058.3554376658</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>4.640583554376658</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>-0.8056839712012085</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>9.0218298879483</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>63.50928381962868</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>42982938.03418803</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>70.63793103448273</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>5.410424224897923</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>40506685.13960454</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>bqYbtBlo</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45597.70833333334</v>
+      </c>
+      <c r="C9" t="n">
+        <v>102</v>
+      </c>
+      <c r="D9" t="n">
+        <v>133</v>
+      </c>
+      <c r="E9" t="n">
+        <v>777</v>
+      </c>
+      <c r="F9" t="n">
+        <v>39</v>
+      </c>
+      <c r="G9" t="n">
+        <v>55</v>
+      </c>
+      <c r="H9" t="n">
+        <v>551</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>67</v>
+      </c>
+      <c r="M9" t="n">
+        <v>138</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>-0.5366666666666672</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0.8171323529411763</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.040247678018576</v>
+      </c>
+      <c r="S9" t="n">
+        <v>-0.6666666666666665</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.736111111111112</v>
+      </c>
+      <c r="U9" t="n">
+        <v>3.333333333333332</v>
+      </c>
+      <c r="V9" t="n">
+        <v>6.888888888888889</v>
+      </c>
+      <c r="W9" t="n">
+        <v>-1.166666666666667</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.226006191950464</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0.1486068111455108</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>13.74509379509379</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>15.48217202346932</v>
+      </c>
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="n">
+        <v>896.1360910503383</v>
+      </c>
+      <c r="AE9" t="inlineStr"/>
+      <c r="AF9" t="n">
+        <v>35.14285714285715</v>
+      </c>
+      <c r="AG9" t="inlineStr"/>
+      <c r="AH9" t="n">
+        <v>16.80357142857143</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>-4.333333333333329</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>7.786377708978328</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>12.33333333333333</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>5.430555555555557</v>
+      </c>
+      <c r="AM9" t="inlineStr"/>
+      <c r="AN9" t="n">
+        <v>56.00980392156862</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>-0.3333333333333333</v>
+      </c>
+      <c r="AQ9" t="inlineStr"/>
+      <c r="AR9" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>4.833333333333332</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>-1.263157894736846</v>
+      </c>
+      <c r="AU9" t="inlineStr"/>
+      <c r="AV9" t="n">
+        <v>-0.5438928805307466</v>
+      </c>
+      <c r="AW9" t="inlineStr"/>
+      <c r="AX9" t="n">
+        <v>-0.008946652742442537</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>-0.3333333333333333</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>0.2012383900928792</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>-0.6309163059163048</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>-0.3563852813852815</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>-1.611253052503056</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>-21211.66666666667</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>-0.7327912365412368</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>6.794736842105266</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>2.21344696969696</v>
+      </c>
+      <c r="BH9" t="inlineStr"/>
+      <c r="BI9" t="n">
+        <v>-8491403.508771928</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>0.7450487012986855</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>-0.6666666666666667</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>1.0687049062049</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>-3.896574444074446</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>-45977.77777777778</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>-1.798245614035088</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>1.056432748538015</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>-1.084713110963122</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>-48.49473684210525</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>67198.54797980003</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>-52.75438596491229</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>1.192770146520132</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>-6833875.771219522</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>0ljCkFRb</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45597.625</v>
+      </c>
+      <c r="C10" t="n">
+        <v>102</v>
+      </c>
+      <c r="D10" t="n">
+        <v>133</v>
+      </c>
+      <c r="E10" t="n">
+        <v>47</v>
+      </c>
+      <c r="F10" t="n">
+        <v>292</v>
+      </c>
+      <c r="G10" t="n">
+        <v>55</v>
+      </c>
+      <c r="H10" t="n">
+        <v>551</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>67</v>
+      </c>
+      <c r="M10" t="n">
+        <v>32</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0.8927205882352939</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.7875000000000001</v>
+      </c>
+      <c r="S10" t="n">
+        <v>4.666666666666666</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.466911764705883</v>
+      </c>
+      <c r="U10" t="n">
+        <v>13.66666666666667</v>
+      </c>
+      <c r="V10" t="n">
+        <v>9.404411764705882</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0.7375</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1.0875</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>13.32791005291005</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>15.69023071957749</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>784.0622351799401</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>841.0297087191032</v>
+      </c>
+      <c r="AE10" t="inlineStr"/>
+      <c r="AF10" t="n">
+        <v>41.72820512820512</v>
+      </c>
+      <c r="AG10" t="inlineStr"/>
+      <c r="AH10" t="n">
+        <v>13.79487179487179</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>19</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>47.33333333333334</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>17.50735294117646</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>161</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>92.38461538461536</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>2.220446049250313e-16</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>0.3647058823529408</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>0.4666666666666667</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>-4.333333333333332</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>7.125</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>4.26209330143541</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>-3.687551366574661</v>
+      </c>
+      <c r="AW10" t="inlineStr"/>
+      <c r="AX10" t="n">
+        <v>0.002298557086179862</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>-4.012014080195897</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>0.3962962962962961</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>-3.936998051019774</v>
+      </c>
+      <c r="BD10" t="inlineStr"/>
+      <c r="BE10" t="n">
+        <v>0.1065966197545147</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>-1.800440476190488</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>8.975382614018983</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>35045.18259518259</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>64795750</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>-3.724372513008888</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>1.155</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>5.763873584328138</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>5.473109304646187</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>163160</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>2.635</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>0.7920833333333341</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>10.34809668635589</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>124.68</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>13018486.76155494</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>124.89</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>-3.008159678186047</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>8263672.957159354</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>AsQgyP6l</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45592.69791666666</v>
+      </c>
+      <c r="C11" t="n">
+        <v>102</v>
+      </c>
+      <c r="D11" t="n">
+        <v>133</v>
+      </c>
+      <c r="E11" t="n">
+        <v>448</v>
+      </c>
+      <c r="F11" t="n">
+        <v>129</v>
+      </c>
+      <c r="G11" t="n">
+        <v>55</v>
+      </c>
+      <c r="H11" t="n">
+        <v>551</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>286</v>
+      </c>
+      <c r="M11" t="n">
+        <v>258</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>-0.5233333333333334</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0.5056985294117644</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.8388157894736842</v>
+      </c>
+      <c r="S11" t="n">
+        <v>-3</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0.2697368421052637</v>
+      </c>
+      <c r="U11" t="n">
+        <v>-3.666666666666666</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.355263157894738</v>
+      </c>
+      <c r="W11" t="n">
         <v>0.3333333333333333</v>
       </c>
-      <c r="S6" t="n">
+      <c r="X11" t="n">
+        <v>-1.230263157894737</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>-1.055921052631579</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>20.9625</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>19.76698178836489</v>
+      </c>
+      <c r="AC11" t="inlineStr"/>
+      <c r="AD11" t="n">
+        <v>1087.251761429009</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>-9</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>-27.82352941176471</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>3.129411764705878</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>-15.16666666666666</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0.463815789473685</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>-6</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>-22.40131578947368</v>
+      </c>
+      <c r="AM11" t="inlineStr"/>
+      <c r="AN11" t="n">
+        <v>-295.4642857142857</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>3.833333333333333</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>-0.4375</v>
+      </c>
+      <c r="AQ11" t="inlineStr"/>
+      <c r="AR11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>6.473684210526315</v>
+      </c>
+      <c r="AU11" t="inlineStr"/>
+      <c r="AV11" t="n">
+        <v>3.53306285074029</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>-0.0459773713114643</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>0.03689127045394714</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>-0.1809210526315789</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>2.387731481481481</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>-0.8935185185185184</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>0.6932856032856058</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>-56098.50468975468</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>-0.8302397602397602</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>-6.102643678160916</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>-5.71643518518519</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>-48065.97222222223</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>-72102827.5862069</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>-2.31018518518519</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>0.6662068965517243</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>-4.030092592592595</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>-4.999770784770789</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>-138387.5862068966</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>-2.208275862068965</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>-2.068689655172413</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>-5.09639138639136</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>20.01379310344828</v>
+      </c>
+      <c r="BS11" t="n">
+        <v>-39862586.80555555</v>
+      </c>
+      <c r="BT11" t="n">
+        <v>30.42206896551727</v>
+      </c>
+      <c r="BU11" t="n">
+        <v>-1.090574980574956</v>
+      </c>
+      <c r="BV11" t="n">
+        <v>-36818643.71739371</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>h2acepbK</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45592.54166666666</v>
+      </c>
+      <c r="C12" t="n">
+        <v>101</v>
+      </c>
+      <c r="D12" t="n">
+        <v>133</v>
+      </c>
+      <c r="E12" t="n">
+        <v>736</v>
+      </c>
+      <c r="F12" t="n">
+        <v>599</v>
+      </c>
+      <c r="G12" t="n">
+        <v>55</v>
+      </c>
+      <c r="H12" t="n">
+        <v>551</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>40</v>
+      </c>
+      <c r="M12" t="n">
+        <v>163</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.8366666666666666</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0.3579779411764706</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0.8823529411764708</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.051470588235294</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.926470588235295</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0.3529411764705883</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0.5294117647058822</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>17.19810924369748</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>17.48079349674019</v>
+      </c>
+      <c r="AC12" t="inlineStr"/>
+      <c r="AD12" t="n">
+        <v>873.581322507257</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>105</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>21.49047619047619</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>11.54761904761904</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>-1.333333333333336</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>4.529411764705884</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>6.666666666666671</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>4.272058823529406</v>
+      </c>
+      <c r="AM12" t="inlineStr"/>
+      <c r="AN12" t="n">
+        <v>37.74725274725284</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>-0.6666666666666667</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>-0.6156862745098037</v>
+      </c>
+      <c r="AQ12" t="inlineStr"/>
+      <c r="AR12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>-1.666666666666664</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>-3.882352941176467</v>
+      </c>
+      <c r="AU12" t="inlineStr"/>
+      <c r="AV12" t="n">
+        <v>1.325409884342061</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>0.05250571962900731</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>0.00287292148709687</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>0.1176470588235294</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>-1.954520697167755</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>-0.1965250544662311</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>-0.5223736333111297</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>-5693.709716209716</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>0.09596375846375849</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>5.914000000000016</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>0.7790305010893235</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>-8770.098039215691</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>-6925200</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>0.6577995642701921</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>-0.07999999999999963</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>-2.434302832244001</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>0.6954261016761194</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>-17360</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>1.472666666666669</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>1.266621572871585</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>-9</v>
+      </c>
+      <c r="BS12" t="n">
+        <v>-1895626.089324619</v>
+      </c>
+      <c r="BT12" t="n">
+        <v>-6.400000000000006</v>
+      </c>
+      <c r="BU12" t="n">
+        <v>-0.08552229020980917</v>
+      </c>
+      <c r="BV12" t="n">
+        <v>-989866.5639915639</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>KdJMr7EE</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45592.54166666666</v>
+      </c>
+      <c r="C13" t="n">
+        <v>101</v>
+      </c>
+      <c r="D13" t="n">
+        <v>133</v>
+      </c>
+      <c r="E13" t="n">
+        <v>535</v>
+      </c>
+      <c r="F13" t="n">
+        <v>33</v>
+      </c>
+      <c r="G13" t="n">
+        <v>55</v>
+      </c>
+      <c r="H13" t="n">
+        <v>551</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>168</v>
+      </c>
+      <c r="M13" t="n">
+        <v>204</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.7150000000000003</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0.7690808823529414</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.125</v>
+      </c>
+      <c r="S13" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.763888888888889</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
+      </c>
+      <c r="V13" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="W13" t="n">
         <v>2</v>
       </c>
-      <c r="T6" t="n">
-        <v>0.9294117647058817</v>
-      </c>
-      <c r="U6" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="V6" t="n">
-        <v>3.003921568627451</v>
-      </c>
-      <c r="W6" t="n">
+      <c r="X13" t="n">
+        <v>0.1111111111111109</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-0.7291666666666665</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>20.98489010989011</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>18.72330400001918</v>
+      </c>
+      <c r="AC13" t="inlineStr"/>
+      <c r="AD13" t="n">
+        <v>931.8494304849846</v>
+      </c>
+      <c r="AE13" t="inlineStr"/>
+      <c r="AF13" t="n">
+        <v>2.760504201680661</v>
+      </c>
+      <c r="AG13" t="inlineStr"/>
+      <c r="AH13" t="n">
+        <v>18.45378151260504</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>6</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>8.298611111111107</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>-13</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>-3.027777777777771</v>
+      </c>
+      <c r="AM13" t="inlineStr"/>
+      <c r="AN13" t="n">
+        <v>-31.95673076923077</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>-1.216911764705883</v>
+      </c>
+      <c r="AQ13" t="inlineStr"/>
+      <c r="AR13" t="n">
+        <v>-0.3333333333333333</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>-8.5</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>-5.972222222222221</v>
+      </c>
+      <c r="AU13" t="inlineStr"/>
+      <c r="AV13" t="n">
+        <v>3.243802242821531</v>
+      </c>
+      <c r="AW13" t="inlineStr"/>
+      <c r="AX13" t="n">
+        <v>0.03704908465490844</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>0.2222222222222222</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>1.011101758323985</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>-0.001206509539842804</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>1.442806201843066</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>8855.378238639489</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>0.2052336203629224</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>-1.746476190476216</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>-0.852562663673794</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>-8895.781893004114</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>-39048000</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>5.84902731013841</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>-1.68</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>0.6248410026187656</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>1.465475104261301</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>-87840</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>-2.4</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>-0.1983333333333341</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>-2.577726697738001</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>-131.84</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>-3450137.485970819</v>
+      </c>
+      <c r="BT13" t="n">
+        <v>-142.44</v>
+      </c>
+      <c r="BU13" t="n">
+        <v>2.030217276301443</v>
+      </c>
+      <c r="BV13" t="n">
+        <v>-1287794.097429133</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>vNHAXt6D</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45592.54166666666</v>
+      </c>
+      <c r="C14" t="n">
+        <v>102</v>
+      </c>
+      <c r="D14" t="n">
+        <v>134</v>
+      </c>
+      <c r="E14" t="n">
+        <v>242</v>
+      </c>
+      <c r="F14" t="n">
+        <v>226</v>
+      </c>
+      <c r="G14" t="n">
+        <v>55</v>
+      </c>
+      <c r="H14" t="n">
+        <v>551</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>286</v>
+      </c>
+      <c r="M14" t="n">
+        <v>32</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>-1.148333333333333</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0.378555555555556</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="R14" t="n">
+        <v>-0.009803921568627416</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1.152777777777779</v>
+      </c>
+      <c r="U14" t="n">
+        <v>-1.333333333333332</v>
+      </c>
+      <c r="V14" t="n">
+        <v>2.847222222222223</v>
+      </c>
+      <c r="W14" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="X14" t="n">
+        <v>-0.8398692810457515</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-0.8431372549019607</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>17.84474275724276</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>21.17225689346916</v>
+      </c>
+      <c r="AC14" t="inlineStr"/>
+      <c r="AD14" t="n">
+        <v>879.7668607303815</v>
+      </c>
+      <c r="AE14" t="inlineStr"/>
+      <c r="AF14" t="n">
+        <v>8.803571428571431</v>
+      </c>
+      <c r="AG14" t="inlineStr"/>
+      <c r="AH14" t="n">
+        <v>16.04464285714286</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>9.166666666666671</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>5.176470588235297</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>5.333333333333329</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>1.986111111111114</v>
+      </c>
+      <c r="AM14" t="inlineStr"/>
+      <c r="AN14" t="n">
+        <v>-10.52884615384619</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>-1.111111111111111</v>
+      </c>
+      <c r="AQ14" t="inlineStr"/>
+      <c r="AR14" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>-4.333333333333336</v>
+      </c>
+      <c r="AU14" t="inlineStr"/>
+      <c r="AV14" t="n">
+        <v>2.181757328311145</v>
+      </c>
+      <c r="AW14" t="inlineStr"/>
+      <c r="AX14" t="n">
+        <v>0.04034575343889454</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>0.1176470588235294</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>3.606349206349201</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>0.3944444444444444</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>2.014719308469306</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>2967.451487906033</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>0.20987234987235</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>-2.322222222222251</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>-0.6893518518518675</v>
+      </c>
+      <c r="BH14" t="inlineStr"/>
+      <c r="BI14" t="n">
+        <v>834134.615384616</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>-5.716005291005217</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>0.8012820512820511</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>4.035978835978838</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>1.122746472277726</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>19003.49650349651</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>1.493589743589743</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>2.597649572649566</v>
+      </c>
+      <c r="BQ14" t="n">
+        <v>-0.7604441912254316</v>
+      </c>
+      <c r="BR14" t="n">
+        <v>57.29166666666666</v>
+      </c>
+      <c r="BS14" t="n">
+        <v>2958549.933862433</v>
+      </c>
+      <c r="BT14" t="n">
+        <v>55.58974358974356</v>
+      </c>
+      <c r="BU14" t="n">
+        <v>-0.7497044448607255</v>
+      </c>
+      <c r="BV14" t="n">
+        <v>261340.3909458597</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>WdE2Z2y1</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45592.45833333334</v>
+      </c>
+      <c r="C15" t="n">
+        <v>101</v>
+      </c>
+      <c r="D15" t="n">
+        <v>133</v>
+      </c>
+      <c r="E15" t="n">
+        <v>56</v>
+      </c>
+      <c r="F15" t="n">
+        <v>228</v>
+      </c>
+      <c r="G15" t="n">
+        <v>55</v>
+      </c>
+      <c r="H15" t="n">
+        <v>551</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>198</v>
+      </c>
+      <c r="M15" t="n">
+        <v>10</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0.9221666666666666</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>4</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S15" t="n">
+        <v>4.666666666666667</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0.5888888888888886</v>
+      </c>
+      <c r="U15" t="n">
+        <v>14.33333333333333</v>
+      </c>
+      <c r="V15" t="n">
+        <v>-0.2888888888888896</v>
+      </c>
+      <c r="W15" t="n">
+        <v>2.333333333333333</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0.3999999999999997</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>16.77935299994123</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>22.19319082107072</v>
+      </c>
+      <c r="AC15" t="inlineStr"/>
+      <c r="AD15" t="n">
+        <v>944.9631595713745</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>33</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>-21.02083333333334</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>47</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>4.569444444444443</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>-1.333333333333329</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>0.1500000000000021</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>11.33333333333333</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>-7.422222222222231</v>
+      </c>
+      <c r="AM15" t="inlineStr"/>
+      <c r="AN15" t="n">
+        <v>-73.45535714285717</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>-0.666666666666667</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>-0.5176470588235293</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>5.666666666666668</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>-1.399999999999995</v>
+      </c>
+      <c r="AU15" t="inlineStr"/>
+      <c r="AV15" t="n">
+        <v>2.858654364771889</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>0.02959549411162314</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>0.003005089032790918</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>-1.451857282502445</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>4.740521083854418</v>
+      </c>
+      <c r="BD15" t="inlineStr"/>
+      <c r="BE15" t="n">
+        <v>0.9983333333333335</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>-8.367653508771951</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>7.61312724014337</v>
+      </c>
+      <c r="BH15" t="inlineStr"/>
+      <c r="BI15" t="n">
+        <v>17294736.84210526</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>-0.4286412512219044</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>6.041035353535349</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>12.90907050876349</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>64777.77777777778</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>0.8815789473684212</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>0.9345394736842074</v>
+      </c>
+      <c r="BQ15" t="n">
+        <v>7.302621842906944</v>
+      </c>
+      <c r="BR15" t="n">
+        <v>-33.10526315789474</v>
+      </c>
+      <c r="BS15" t="n">
+        <v>10804150.37471489</v>
+      </c>
+      <c r="BT15" t="n">
+        <v>-44.07894736842104</v>
+      </c>
+      <c r="BU15" t="n">
+        <v>-3.422599280186972</v>
+      </c>
+      <c r="BV15" t="n">
+        <v>13476367.61833034</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>vaZNtoqR</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45591.66666666666</v>
+      </c>
+      <c r="C16" t="n">
+        <v>101</v>
+      </c>
+      <c r="D16" t="n">
+        <v>133</v>
+      </c>
+      <c r="E16" t="n">
+        <v>273</v>
+      </c>
+      <c r="F16" t="n">
+        <v>545</v>
+      </c>
+      <c r="G16" t="n">
+        <v>55</v>
+      </c>
+      <c r="H16" t="n">
+        <v>551</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="L16" t="n">
+        <v>272</v>
+      </c>
+      <c r="M16" t="n">
+        <v>204</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>-0.22</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0.6045220588235296</v>
+      </c>
+      <c r="Q16" t="n">
         <v>-1</v>
       </c>
-      <c r="X6" t="n">
-        <v>-0.5347222222222223</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>-1.729166666666667</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>14.30400432900433</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>18.69912390699542</v>
-      </c>
-      <c r="AC6" t="inlineStr"/>
-      <c r="AD6" t="n">
-        <v>986.1380862058272</v>
-      </c>
-      <c r="AE6" t="n">
+      <c r="R16" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1.833333333333333</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.541666666666667</v>
+      </c>
+      <c r="U16" t="n">
+        <v>3.166666666666668</v>
+      </c>
+      <c r="V16" t="n">
+        <v>4.027777777777779</v>
+      </c>
+      <c r="W16" t="n">
+        <v>-0.6666666666666667</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0.2083333333333334</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0.5833333333333333</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>21.36915584415584</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>19.90822250376043</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>968.5623018561785</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>993.2278683172611</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>-69</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>-3.295833333333334</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>-32</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>5.458333333333336</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>1.416666666666664</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>-12.33333333333333</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>-16.47222222222223</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>-126.5</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>-166.7436974789916</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>-2.220446049250313e-16</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>-0.06349206349206327</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>2.166666666666664</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>5.590277777777779</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>13.69398809523809</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>4.666588369374105</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>-0.05627452561414825</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>0.002448867104326222</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>0.1458333333333333</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>1.841065878565875</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>-0.2436147186147186</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>0.7011796682849329</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>-86.68256816282883</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>0.1389316823527349</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>-10.15494505494507</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>-1.113660644910638</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>3166.98717948718</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>6081282.05128205</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>-1.010540154290112</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>1.435897435897436</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>1.222213897213905</v>
+      </c>
+      <c r="BM16" t="n">
+        <v>0.06106032734321332</v>
+      </c>
+      <c r="BN16" t="n">
+        <v>42469.23076923077</v>
+      </c>
+      <c r="BO16" t="n">
+        <v>0.9743589743589742</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>1.570818070818067</v>
+      </c>
+      <c r="BQ16" t="n">
+        <v>-1.811064495932925</v>
+      </c>
+      <c r="BR16" t="n">
+        <v>105.6769230769231</v>
+      </c>
+      <c r="BS16" t="n">
+        <v>136668.9733877219</v>
+      </c>
+      <c r="BT16" t="n">
+        <v>104.8333333333333</v>
+      </c>
+      <c r="BU16" t="n">
+        <v>-0.7967608049845012</v>
+      </c>
+      <c r="BV16" t="n">
+        <v>-1170630.297455954</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>hQspntL6</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45591.58333333334</v>
+      </c>
+      <c r="C17" t="n">
+        <v>101</v>
+      </c>
+      <c r="D17" t="n">
+        <v>133</v>
+      </c>
+      <c r="E17" t="n">
+        <v>826</v>
+      </c>
+      <c r="F17" t="n">
+        <v>133</v>
+      </c>
+      <c r="G17" t="n">
+        <v>55</v>
+      </c>
+      <c r="H17" t="n">
+        <v>551</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
+        <v>128</v>
+      </c>
+      <c r="M17" t="n">
+        <v>211</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>2.495</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0.3574166666666667</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>4</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0.3529411764705883</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="n">
+        <v>13</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.856617647058824</v>
+      </c>
+      <c r="W17" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="X17" t="n">
+        <v>-0.05882352941176472</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0.1985294117647061</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>14.49107744107744</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>19.34590718073206</v>
+      </c>
+      <c r="AC17" t="inlineStr"/>
+      <c r="AD17" t="n">
+        <v>868.0773877594212</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>43</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>3.392857142857153</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>44</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>10.59821428571428</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>4.999999999999996</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>5.38602941176471</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>-13</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>-5.992647058823536</v>
+      </c>
+      <c r="AM17" t="inlineStr"/>
+      <c r="AN17" t="n">
+        <v>-13.39999999999998</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0.166666666666667</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>-0.04411764705882382</v>
+      </c>
+      <c r="AQ17" t="inlineStr"/>
+      <c r="AR17" t="n">
+        <v>-0.1428571428571429</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>1.333333333333334</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>-6.867647058823529</v>
+      </c>
+      <c r="AU17" t="inlineStr"/>
+      <c r="AV17" t="n">
+        <v>1.109530542816877</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>-0.002347620952272117</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>0.02343697858948881</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>-0.1213235294117647</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>-0.4637806637806605</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>-0.05216450216450208</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>-1.398419367747096</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>-1836.431061313417</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>-0.1620821661998135</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>-4.160148148148153</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>2.664898989898987</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>1152.660533910534</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>-720666.666666667</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>3.311724386724364</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>0.8255772005772002</v>
+      </c>
+      <c r="BM17" t="n">
+        <v>-0.739847272242244</v>
+      </c>
+      <c r="BN17" t="n">
+        <v>-7055.555555555555</v>
+      </c>
+      <c r="BO17" t="n">
+        <v>0.02222222222222237</v>
+      </c>
+      <c r="BP17" t="n">
+        <v>-5.084777777777781</v>
+      </c>
+      <c r="BQ17" t="n">
+        <v>1.340140856342543</v>
+      </c>
+      <c r="BR17" t="n">
+        <v>8.766666666666666</v>
+      </c>
+      <c r="BS17" t="n">
+        <v>2948543.47041847</v>
+      </c>
+      <c r="BT17" t="n">
+        <v>21.41111111111113</v>
+      </c>
+      <c r="BU17" t="n">
+        <v>4.259690943043893</v>
+      </c>
+      <c r="BV17" t="n">
+        <v>203668.7941843402</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>p0vxl2jf</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45591.5</v>
+      </c>
+      <c r="C18" t="n">
+        <v>102</v>
+      </c>
+      <c r="D18" t="n">
+        <v>133</v>
+      </c>
+      <c r="E18" t="n">
+        <v>431</v>
+      </c>
+      <c r="F18" t="n">
+        <v>362</v>
+      </c>
+      <c r="G18" t="n">
+        <v>55</v>
+      </c>
+      <c r="H18" t="n">
+        <v>551</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="L18" t="n">
+        <v>152</v>
+      </c>
+      <c r="M18" t="n">
+        <v>83</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1.613333333333333</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0.229607843137255</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0.3157894736842106</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.666666666666667</v>
+      </c>
+      <c r="T18" t="n">
+        <v>-1.395424836601307</v>
+      </c>
+      <c r="U18" t="n">
+        <v>8.333333333333336</v>
+      </c>
+      <c r="V18" t="n">
+        <v>-2.176470588235293</v>
+      </c>
+      <c r="W18" t="n">
+        <v>2.333333333333333</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0.4334365325077401</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>1.021671826625387</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>16.23349567099567</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>20.7141176225735</v>
+      </c>
+      <c r="AC18" t="inlineStr"/>
+      <c r="AD18" t="n">
+        <v>883.0782510807605</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>14</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>16.76666666666667</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>35</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>7.508333333333333</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>18.33333333333333</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>2.690402476780184</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>16</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>-1.189542483660119</v>
+      </c>
+      <c r="AM18" t="inlineStr"/>
+      <c r="AN18" t="n">
+        <v>-48.89047619047619</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>-3.333333333333333</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>-1.090277777777778</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>-8.000000000000002</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>-5.204334365325082</v>
+      </c>
+      <c r="AU18" t="inlineStr"/>
+      <c r="AV18" t="n">
+        <v>1.665627743712083</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>0.04286926994906622</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>0.006595534358273113</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>0.1176470588235294</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>1.491715506220853</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>-0.4465951378199833</v>
+      </c>
+      <c r="BD18" t="inlineStr"/>
+      <c r="BE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>2.92291666666668</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>-1.581351617782104</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>-1348.786819241364</v>
+      </c>
+      <c r="BI18" t="n">
+        <v>-1418750</v>
+      </c>
+      <c r="BJ18" t="n">
+        <v>1.246166432596937</v>
+      </c>
+      <c r="BK18" t="n">
+        <v>0.4249999999999998</v>
+      </c>
+      <c r="BL18" t="n">
+        <v>-1.155842291002728</v>
+      </c>
+      <c r="BM18" t="n">
+        <v>-2.927087024123125</v>
+      </c>
+      <c r="BN18" t="n">
+        <v>-16100</v>
+      </c>
+      <c r="BO18" t="n">
+        <v>0.4249999999999998</v>
+      </c>
+      <c r="BP18" t="n">
+        <v>-4.310416666666665</v>
+      </c>
+      <c r="BQ18" t="n">
+        <v>-2.060120436988129</v>
+      </c>
+      <c r="BR18" t="n">
+        <v>13.40000000000001</v>
+      </c>
+      <c r="BS18" t="n">
+        <v>-557397.7464034278</v>
+      </c>
+      <c r="BT18" t="n">
+        <v>34.15000000000001</v>
+      </c>
+      <c r="BU18" t="n">
+        <v>0.6999693611031148</v>
+      </c>
+      <c r="BV18" t="n">
+        <v>-623308.1685339094</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>lYpTkOLs</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45590.65625</v>
+      </c>
+      <c r="C19" t="n">
+        <v>101</v>
+      </c>
+      <c r="D19" t="n">
+        <v>133</v>
+      </c>
+      <c r="E19" t="n">
+        <v>573</v>
+      </c>
+      <c r="F19" t="n">
+        <v>122</v>
+      </c>
+      <c r="G19" t="n">
+        <v>55</v>
+      </c>
+      <c r="H19" t="n">
+        <v>551</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="L19" t="n">
+        <v>9</v>
+      </c>
+      <c r="M19" t="n">
+        <v>138</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>1.426666666666667</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1.359522058823529</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>3</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.895833333333333</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5.333333333333334</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3.770833333333333</v>
+      </c>
+      <c r="U19" t="n">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="V19" t="n">
+        <v>7.770833333333332</v>
+      </c>
+      <c r="W19" t="n">
+        <v>2.666666666666667</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.291666666666667</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>1.541666666666667</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>15.19888167388167</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>17.55297816242734</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>863.0573179033356</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>849.1877226677626</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>32</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>25.05357142857142</v>
+      </c>
+      <c r="AG19" t="n">
         <v>30</v>
       </c>
-      <c r="AF6" t="n">
-        <v>-7.714285714285708</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>33</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>4.589285714285715</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>2.305555555555557</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>-14</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>-14.34509803921569</v>
-      </c>
-      <c r="AM6" t="inlineStr"/>
-      <c r="AN6" t="n">
-        <v>-140.6057692307692</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>0.6095238095238094</v>
-      </c>
-      <c r="AQ6" t="inlineStr"/>
-      <c r="AR6" t="n">
-        <v>-0.75</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>-4</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>3.673611111111114</v>
-      </c>
-      <c r="AU6" t="inlineStr"/>
-      <c r="AV6" t="n">
-        <v>2.349420065520075</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>-0.01939372421721783</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>-0.003091515127249374</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>-0.4791666666666666</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>-8.106805555555553</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>-40422.8231292517</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>-19.03216374269007</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>-12.31076247165532</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>-0.75</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>-1.742690058479532</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>-0.1111111111111112</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>-0.9983333333333335</v>
-      </c>
-      <c r="BI6" t="n">
-        <v>-10700940.97222222</v>
-      </c>
-      <c r="BJ6" t="n">
-        <v>-6.675503267096332</v>
-      </c>
-      <c r="BK6" t="n">
-        <v>5.610972222222188</v>
-      </c>
-      <c r="BL6" t="n">
-        <v>3.161621762740197</v>
-      </c>
-      <c r="BM6" t="n">
-        <v>-3.574557002625617</v>
-      </c>
-      <c r="BN6" t="n">
-        <v>-13352829.06857919</v>
-      </c>
-      <c r="BO6" t="n">
-        <v>-16496125.73099415</v>
-      </c>
-      <c r="BP6" t="inlineStr"/>
-      <c r="BQ6" t="n">
-        <v>-4.982222222222219</v>
-      </c>
-      <c r="BR6" t="n">
-        <v>-1.338194444444447</v>
-      </c>
-      <c r="BS6" t="n">
-        <v>-21.11695906432749</v>
-      </c>
-      <c r="BT6" t="n">
-        <v>-0.07967836257309813</v>
-      </c>
-      <c r="BU6" t="n">
-        <v>7.788255360623793</v>
-      </c>
-      <c r="BV6" t="n">
-        <v>-58777.77777777778</v>
+      <c r="AH19" t="n">
+        <v>16.01785714285714</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>6.666666666666664</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>5.333333333333336</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>12</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>7.513888888888886</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>90</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>66.98571428571432</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>-1.333333333333333</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>-0.145833333333333</v>
+      </c>
+      <c r="AQ19" t="inlineStr"/>
+      <c r="AR19" t="n">
+        <v>-0.9333333333333333</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>-1.333333333333334</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>-1.222222222222221</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>-25.84559884559884</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>-2.672925535896542</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>-0.08260636182134844</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>-0.01594106336285508</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>0.4097222222222222</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>0.2106186868686848</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>0.4703030303030304</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>-1.924816376355604</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>17877.66439909297</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>0.2661090362070757</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>-2.083994708994709</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>7.476994949494937</v>
+      </c>
+      <c r="BH19" t="n">
+        <v>24872.94142404437</v>
+      </c>
+      <c r="BI19" t="n">
+        <v>8808531.746031746</v>
+      </c>
+      <c r="BJ19" t="n">
+        <v>-4.637184343434313</v>
+      </c>
+      <c r="BK19" t="n">
+        <v>-0.496031746031746</v>
+      </c>
+      <c r="BL19" t="n">
+        <v>8.799760101010094</v>
+      </c>
+      <c r="BM19" t="n">
+        <v>6.768493045366284</v>
+      </c>
+      <c r="BN19" t="n">
+        <v>15142.85714285714</v>
+      </c>
+      <c r="BO19" t="n">
+        <v>-0.353174603174603</v>
+      </c>
+      <c r="BP19" t="n">
+        <v>-2.611111111111111</v>
+      </c>
+      <c r="BQ19" t="n">
+        <v>7.364615726895053</v>
+      </c>
+      <c r="BR19" t="n">
+        <v>-25.52777777777777</v>
+      </c>
+      <c r="BS19" t="n">
+        <v>11441312.18434343</v>
+      </c>
+      <c r="BT19" t="n">
+        <v>-28.13888888888889</v>
+      </c>
+      <c r="BU19" t="n">
+        <v>1.135705242135828</v>
+      </c>
+      <c r="BV19" t="n">
+        <v>8557743.478787716</v>
       </c>
     </row>
   </sheetData>

--- a/data/france/p6_deployment/data_preparation/df_tagged.xlsx
+++ b/data/france/p6_deployment/data_preparation/df_tagged.xlsx
@@ -690,112 +690,112 @@
       </c>
       <c r="BA1" s="1" t="inlineStr">
         <is>
+          <t>dif_n_player_miss</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_wage_player_start</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_sub</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_age_player_start</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_value_player_sub</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_pot_player_miss</t>
+        </is>
+      </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_value_player_start</t>
+        </is>
+      </c>
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rep_player_sub</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_start</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_sub</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_wage_player_sub</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_start</t>
+        </is>
+      </c>
+      <c r="BM1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_start</t>
+        </is>
+      </c>
+      <c r="BN1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_rat_player_miss</t>
+        </is>
+      </c>
+      <c r="BO1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_value_player_miss</t>
+        </is>
+      </c>
+      <c r="BP1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_wage_player_miss</t>
+        </is>
+      </c>
+      <c r="BQ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_sub</t>
+        </is>
+      </c>
+      <c r="BR1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_miss</t>
+        </is>
+      </c>
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_rep_player_start</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_sub</t>
-        </is>
-      </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_wage_player_sub</t>
-        </is>
-      </c>
-      <c r="BE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rep_player_sub</t>
-        </is>
-      </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_hei_player_miss</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_start</t>
-        </is>
-      </c>
-      <c r="BH1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_wage_player_start</t>
-        </is>
-      </c>
-      <c r="BI1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_value_player_miss</t>
-        </is>
-      </c>
-      <c r="BJ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_start</t>
-        </is>
-      </c>
-      <c r="BK1" s="1" t="inlineStr">
-        <is>
-          <t>dif_n_player_miss</t>
-        </is>
-      </c>
-      <c r="BL1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_start</t>
-        </is>
-      </c>
-      <c r="BM1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_sub</t>
-        </is>
-      </c>
-      <c r="BN1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_wage_player_miss</t>
-        </is>
-      </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_sub</t>
+        </is>
+      </c>
+      <c r="BV1" s="1" t="inlineStr">
         <is>
           <t>dif_sum_rep_player_miss</t>
-        </is>
-      </c>
-      <c r="BP1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_miss</t>
-        </is>
-      </c>
-      <c r="BQ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_sub</t>
-        </is>
-      </c>
-      <c r="BR1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_rat_player_miss</t>
-        </is>
-      </c>
-      <c r="BS1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_value_player_start</t>
-        </is>
-      </c>
-      <c r="BT1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_pot_player_miss</t>
-        </is>
-      </c>
-      <c r="BU1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_sub</t>
-        </is>
-      </c>
-      <c r="BV1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_value_player_sub</t>
         </is>
       </c>
     </row>
@@ -957,70 +957,70 @@
         <v>-0.03947368421052633</v>
       </c>
       <c r="BA2" t="n">
-        <v>0.09467592592592666</v>
+        <v>-1.76</v>
       </c>
       <c r="BB2" t="n">
-        <v>0.2579629629629629</v>
+        <v>-15411.80555555555</v>
       </c>
       <c r="BC2" t="n">
         <v>0.81717026029526</v>
       </c>
       <c r="BD2" t="n">
+        <v>0.09467592592592666</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>-5878102.918782605</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>-137.68</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>-9301084.490740741</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>0.02785117660117664</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>0.2225925925926333</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>-4.710769716394722</v>
+      </c>
+      <c r="BK2" t="n">
         <v>-11425.89105339105</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>0.02785117660117664</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>-5.290666666666681</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>-3.683564814814829</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>-15411.80555555555</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>-23406000</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>0.2225925925926333</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>-1.76</v>
       </c>
       <c r="BL2" t="n">
         <v>-3.600092592592588</v>
       </c>
       <c r="BM2" t="n">
-        <v>-4.710769716394722</v>
+        <v>-3.683564814814829</v>
       </c>
       <c r="BN2" t="n">
+        <v>-120.84</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>-23406000</v>
+      </c>
+      <c r="BP2" t="n">
         <v>-39640</v>
-      </c>
-      <c r="BO2" t="n">
-        <v>-2.44</v>
-      </c>
-      <c r="BP2" t="n">
-        <v>0.5619999999999976</v>
       </c>
       <c r="BQ2" t="n">
         <v>-4.529477362914875</v>
       </c>
       <c r="BR2" t="n">
-        <v>-120.84</v>
+        <v>0.5619999999999976</v>
       </c>
       <c r="BS2" t="n">
-        <v>-9301084.490740741</v>
+        <v>0.2579629629629629</v>
       </c>
       <c r="BT2" t="n">
-        <v>-137.68</v>
+        <v>-5.290666666666681</v>
       </c>
       <c r="BU2" t="n">
         <v>-0.1792792970918242</v>
       </c>
       <c r="BV2" t="n">
-        <v>-5878102.918782605</v>
+        <v>-2.44</v>
       </c>
     </row>
     <row r="3">
@@ -1179,70 +1179,70 @@
         <v>-0.2941176470588235</v>
       </c>
       <c r="BA3" t="n">
-        <v>-2.724305555555556</v>
+        <v>-1.495726495726496</v>
       </c>
       <c r="BB3" t="n">
-        <v>-0.3944444444444444</v>
+        <v>-11227.23765432099</v>
       </c>
       <c r="BC3" t="n">
         <v>1.053402260333648</v>
       </c>
       <c r="BD3" t="n">
+        <v>-2.724305555555556</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>-1700310.64256076</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>-117.034188034188</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>-5175420.138888888</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>-0.20987234987235</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>6.508194444444371</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>-2.924944955837802</v>
+      </c>
+      <c r="BK3" t="n">
         <v>-6538.369855252973</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>-0.20987234987235</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>6.268518518518533</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>-3.46555555555554</v>
-      </c>
-      <c r="BH3" t="n">
-        <v>-11227.23765432099</v>
-      </c>
-      <c r="BI3" t="n">
-        <v>-6879273.504273505</v>
-      </c>
-      <c r="BJ3" t="n">
-        <v>6.508194444444371</v>
-      </c>
-      <c r="BK3" t="n">
-        <v>-1.495726495726496</v>
       </c>
       <c r="BL3" t="n">
         <v>-6.810972222222219</v>
       </c>
       <c r="BM3" t="n">
-        <v>-2.924944955837802</v>
+        <v>-3.46555555555554</v>
       </c>
       <c r="BN3" t="n">
+        <v>-109.2222222222222</v>
+      </c>
+      <c r="BO3" t="n">
+        <v>-6879273.504273505</v>
+      </c>
+      <c r="BP3" t="n">
         <v>-31730.76923076923</v>
-      </c>
-      <c r="BO3" t="n">
-        <v>-2.188034188034188</v>
-      </c>
-      <c r="BP3" t="n">
-        <v>-0.7837606837606828</v>
       </c>
       <c r="BQ3" t="n">
         <v>-4.171182587775647</v>
       </c>
       <c r="BR3" t="n">
-        <v>-109.2222222222222</v>
+        <v>-0.7837606837606828</v>
       </c>
       <c r="BS3" t="n">
-        <v>-5175420.138888888</v>
+        <v>-0.3944444444444444</v>
       </c>
       <c r="BT3" t="n">
-        <v>-117.034188034188</v>
+        <v>6.268518518518533</v>
       </c>
       <c r="BU3" t="n">
         <v>1.158863409981876</v>
       </c>
       <c r="BV3" t="n">
-        <v>-1700310.64256076</v>
+        <v>-2.188034188034188</v>
       </c>
     </row>
     <row r="4">
@@ -1401,68 +1401,68 @@
         <v>0.3441176470588235</v>
       </c>
       <c r="BA4" t="n">
-        <v>2.579433040078207</v>
+        <v>1.357142857142857</v>
       </c>
       <c r="BB4" t="n">
-        <v>-0.4703030303030304</v>
+        <v>-25562.4188128752</v>
       </c>
       <c r="BC4" t="n">
         <v>0.758852295126804</v>
       </c>
-      <c r="BD4" t="inlineStr"/>
+      <c r="BD4" t="n">
+        <v>2.579433040078207</v>
+      </c>
       <c r="BE4" t="n">
+        <v>-8681282.028538868</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>91.25</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>-11544521.5868361</v>
+      </c>
+      <c r="BH4" t="n">
         <v>-0.2661090362070757</v>
       </c>
-      <c r="BF4" t="n">
-        <v>2.663392857142867</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>-10.10789996741609</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>-25562.4188128752</v>
-      </c>
       <c r="BI4" t="n">
-        <v>-9607142.857142856</v>
+        <v>-0.5451466275659698</v>
       </c>
       <c r="BJ4" t="n">
-        <v>-0.5451466275659698</v>
-      </c>
-      <c r="BK4" t="n">
-        <v>1.357142857142857</v>
-      </c>
+        <v>-7.366801082474453</v>
+      </c>
+      <c r="BK4" t="inlineStr"/>
       <c r="BL4" t="n">
         <v>-6.73398989898989</v>
       </c>
       <c r="BM4" t="n">
-        <v>-7.366801082474453</v>
+        <v>-10.10789996741609</v>
       </c>
       <c r="BN4" t="n">
+        <v>79.75</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>-9607142.857142856</v>
+      </c>
+      <c r="BP4" t="n">
         <v>-21142.85714285714</v>
-      </c>
-      <c r="BO4" t="n">
-        <v>1.214285714285714</v>
-      </c>
-      <c r="BP4" t="n">
-        <v>1.756250000000001</v>
       </c>
       <c r="BQ4" t="n">
         <v>-7.991734302705666</v>
       </c>
       <c r="BR4" t="n">
-        <v>79.75</v>
+        <v>1.756250000000001</v>
       </c>
       <c r="BS4" t="n">
-        <v>-11544521.5868361</v>
+        <v>-0.4703030303030304</v>
       </c>
       <c r="BT4" t="n">
-        <v>91.25</v>
+        <v>2.663392857142867</v>
       </c>
       <c r="BU4" t="n">
         <v>-0.8747277246890519</v>
       </c>
       <c r="BV4" t="n">
-        <v>-8681282.028538868</v>
+        <v>1.214285714285714</v>
       </c>
     </row>
     <row r="5">
@@ -1627,68 +1627,68 @@
         <v>-1.387778780781446e-17</v>
       </c>
       <c r="BA5" t="n">
-        <v>-2.970238095238091</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>-0.125</v>
-      </c>
+        <v>0.8633333333333335</v>
+      </c>
+      <c r="BB5" t="inlineStr"/>
       <c r="BC5" t="n">
         <v>-1.819175170068029</v>
       </c>
       <c r="BD5" t="n">
+        <v>-2.970238095238091</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>-13853.14803004498</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>67.03333333333333</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>-2527820.767195767</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>0.5937830687830399</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>-1.614879180838997</v>
+      </c>
+      <c r="BK5" t="n">
         <v>-3009.788359788359</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>2.125888888888881</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>-0.1648148148148181</v>
-      </c>
-      <c r="BH5" t="inlineStr"/>
-      <c r="BI5" t="n">
-        <v>6447750</v>
-      </c>
-      <c r="BJ5" t="n">
-        <v>0.5937830687830399</v>
-      </c>
-      <c r="BK5" t="n">
-        <v>0.8633333333333335</v>
       </c>
       <c r="BL5" t="n">
         <v>-4.119312169312167</v>
       </c>
       <c r="BM5" t="n">
-        <v>-1.614879180838997</v>
+        <v>-0.1648148148148181</v>
       </c>
       <c r="BN5" t="n">
+        <v>63.10833333333335</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>6447750</v>
+      </c>
+      <c r="BP5" t="n">
         <v>11005.05050505051</v>
-      </c>
-      <c r="BO5" t="n">
-        <v>0.7833333333333334</v>
-      </c>
-      <c r="BP5" t="n">
-        <v>1.85422222222223</v>
       </c>
       <c r="BQ5" t="n">
         <v>1.764865008503392</v>
       </c>
       <c r="BR5" t="n">
-        <v>63.10833333333335</v>
+        <v>1.85422222222223</v>
       </c>
       <c r="BS5" t="n">
-        <v>-2527820.767195767</v>
+        <v>-0.125</v>
       </c>
       <c r="BT5" t="n">
-        <v>67.03333333333333</v>
+        <v>2.125888888888881</v>
       </c>
       <c r="BU5" t="n">
         <v>-5.176029265873012</v>
       </c>
       <c r="BV5" t="n">
-        <v>-13853.14803004498</v>
+        <v>0.7833333333333334</v>
       </c>
     </row>
     <row r="6">
@@ -1845,70 +1845,70 @@
         <v>0.1578947368421053</v>
       </c>
       <c r="BA6" t="n">
-        <v>2.621115567439094</v>
+        <v>0.46</v>
       </c>
       <c r="BB6" t="n">
-        <v>-0.2419934640522874</v>
+        <v>-6914.429049856855</v>
       </c>
       <c r="BC6" t="n">
         <v>0.7642406833147852</v>
       </c>
       <c r="BD6" t="n">
+        <v>2.621115567439094</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>-1873550.104825623</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>24.12</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>-2389013.851752823</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>-0.3051136363636364</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>-1.247556446821221</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>-2.830751701930112</v>
+      </c>
+      <c r="BK6" t="n">
         <v>-6657.620226541796</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>-0.3051136363636364</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>-5.849999999999994</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>-4.492505941770631</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>-6914.429049856855</v>
-      </c>
-      <c r="BI6" t="n">
-        <v>-3585800</v>
-      </c>
-      <c r="BJ6" t="n">
-        <v>-1.247556446821221</v>
-      </c>
-      <c r="BK6" t="n">
-        <v>0.46</v>
       </c>
       <c r="BL6" t="n">
         <v>-0.7203951277480769</v>
       </c>
       <c r="BM6" t="n">
-        <v>-2.830751701930112</v>
+        <v>-4.492505941770631</v>
       </c>
       <c r="BN6" t="n">
+        <v>28.84</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>-3585800</v>
+      </c>
+      <c r="BP6" t="n">
         <v>-23340</v>
-      </c>
-      <c r="BO6" t="n">
-        <v>-1.06</v>
-      </c>
-      <c r="BP6" t="n">
-        <v>0.9466666666666654</v>
       </c>
       <c r="BQ6" t="n">
         <v>-3.552202501481716</v>
       </c>
       <c r="BR6" t="n">
-        <v>28.84</v>
+        <v>0.9466666666666654</v>
       </c>
       <c r="BS6" t="n">
-        <v>-2389013.851752823</v>
+        <v>-0.2419934640522874</v>
       </c>
       <c r="BT6" t="n">
-        <v>24.12</v>
+        <v>-5.849999999999994</v>
       </c>
       <c r="BU6" t="n">
         <v>-1.467742393342235</v>
       </c>
       <c r="BV6" t="n">
-        <v>-1873550.104825623</v>
+        <v>-1.06</v>
       </c>
     </row>
     <row r="7">
@@ -2069,70 +2069,70 @@
         <v>0.6444444444444446</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.361012238790011</v>
+        <v>-1.1</v>
       </c>
       <c r="BB7" t="n">
-        <v>-0.2179252845919513</v>
+        <v>-15711.10843888621</v>
       </c>
       <c r="BC7" t="n">
         <v>2.506918168336853</v>
       </c>
       <c r="BD7" t="n">
+        <v>1.361012238790011</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>-5398260.920250453</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>-95.8111111111111</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>-7654239.317780985</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>-0.1497480739176236</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>-3.729270215381291</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>-2.242630656540697</v>
+      </c>
+      <c r="BK7" t="n">
         <v>-12438.92072229962</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>-0.1497480739176236</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>5.038814814814856</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>-4.739188178077043</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>-15711.10843888621</v>
-      </c>
-      <c r="BI7" t="n">
-        <v>-23887333.33333333</v>
-      </c>
-      <c r="BJ7" t="n">
-        <v>-3.729270215381291</v>
-      </c>
-      <c r="BK7" t="n">
-        <v>-1.1</v>
       </c>
       <c r="BL7" t="n">
         <v>-3.099492277270045</v>
       </c>
       <c r="BM7" t="n">
-        <v>-2.242630656540697</v>
+        <v>-4.739188178077043</v>
       </c>
       <c r="BN7" t="n">
+        <v>-87.00666666666667</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>-23887333.33333333</v>
+      </c>
+      <c r="BP7" t="n">
         <v>-53042.22222222222</v>
-      </c>
-      <c r="BO7" t="n">
-        <v>-1.582222222222222</v>
-      </c>
-      <c r="BP7" t="n">
-        <v>2.319444444444443</v>
       </c>
       <c r="BQ7" t="n">
         <v>-4.773734507706834</v>
       </c>
       <c r="BR7" t="n">
-        <v>-87.00666666666667</v>
+        <v>2.319444444444443</v>
       </c>
       <c r="BS7" t="n">
-        <v>-7654239.317780985</v>
+        <v>-0.2179252845919513</v>
       </c>
       <c r="BT7" t="n">
-        <v>-95.8111111111111</v>
+        <v>5.038814814814856</v>
       </c>
       <c r="BU7" t="n">
         <v>0.9634595560149251</v>
       </c>
       <c r="BV7" t="n">
-        <v>-5398260.920250453</v>
+        <v>-1.582222222222222</v>
       </c>
     </row>
     <row r="8">
@@ -2291,70 +2291,70 @@
         <v>-0.1546052631578947</v>
       </c>
       <c r="BA8" t="n">
-        <v>-2.997186609686608</v>
+        <v>0.6445623342175066</v>
       </c>
       <c r="BB8" t="n">
-        <v>0.924074074074074</v>
+        <v>56423.2905982906</v>
       </c>
       <c r="BC8" t="n">
         <v>-3.833464744320008</v>
       </c>
       <c r="BD8" t="n">
+        <v>-2.997186609686608</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>40506685.13960454</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>70.63793103448273</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>42982938.03418803</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>0.6070646823936299</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>4.214565527065474</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>5.758675954893064</v>
+      </c>
+      <c r="BK8" t="n">
         <v>61681.75291448316</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>0.6070646823936299</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>16.15092206643934</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>6.884009971509983</v>
-      </c>
-      <c r="BH8" t="n">
-        <v>56423.2905982906</v>
-      </c>
-      <c r="BI8" t="n">
-        <v>91810212.20159152</v>
-      </c>
-      <c r="BJ8" t="n">
-        <v>4.214565527065474</v>
-      </c>
-      <c r="BK8" t="n">
-        <v>0.6445623342175066</v>
       </c>
       <c r="BL8" t="n">
         <v>4.322507122507119</v>
       </c>
       <c r="BM8" t="n">
-        <v>5.758675954893064</v>
+        <v>6.884009971509983</v>
       </c>
       <c r="BN8" t="n">
+        <v>63.50928381962868</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>91810212.20159152</v>
+      </c>
+      <c r="BP8" t="n">
         <v>166058.3554376658</v>
-      </c>
-      <c r="BO8" t="n">
-        <v>4.640583554376658</v>
-      </c>
-      <c r="BP8" t="n">
-        <v>-0.8056839712012085</v>
       </c>
       <c r="BQ8" t="n">
         <v>9.0218298879483</v>
       </c>
       <c r="BR8" t="n">
-        <v>63.50928381962868</v>
+        <v>-0.8056839712012085</v>
       </c>
       <c r="BS8" t="n">
-        <v>42982938.03418803</v>
+        <v>0.924074074074074</v>
       </c>
       <c r="BT8" t="n">
-        <v>70.63793103448273</v>
+        <v>16.15092206643934</v>
       </c>
       <c r="BU8" t="n">
         <v>5.410424224897923</v>
       </c>
       <c r="BV8" t="n">
-        <v>40506685.13960454</v>
+        <v>4.640583554376658</v>
       </c>
     </row>
     <row r="9">
@@ -2507,68 +2507,68 @@
         <v>0.2012383900928792</v>
       </c>
       <c r="BA9" t="n">
-        <v>-0.6309163059163048</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>-0.3563852813852815</v>
-      </c>
+        <v>-0.6666666666666667</v>
+      </c>
+      <c r="BB9" t="inlineStr"/>
       <c r="BC9" t="n">
         <v>-1.611253052503056</v>
       </c>
       <c r="BD9" t="n">
+        <v>-0.6309163059163048</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>-6833875.771219522</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>-52.75438596491229</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>67198.54797980003</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>-0.7327912365412368</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>0.7450487012986855</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>-3.896574444074446</v>
+      </c>
+      <c r="BK9" t="n">
         <v>-21211.66666666667</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>-0.7327912365412368</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>6.794736842105266</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>2.21344696969696</v>
-      </c>
-      <c r="BH9" t="inlineStr"/>
-      <c r="BI9" t="n">
-        <v>-8491403.508771928</v>
-      </c>
-      <c r="BJ9" t="n">
-        <v>0.7450487012986855</v>
-      </c>
-      <c r="BK9" t="n">
-        <v>-0.6666666666666667</v>
       </c>
       <c r="BL9" t="n">
         <v>1.0687049062049</v>
       </c>
       <c r="BM9" t="n">
-        <v>-3.896574444074446</v>
+        <v>2.21344696969696</v>
       </c>
       <c r="BN9" t="n">
+        <v>-48.49473684210525</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>-8491403.508771928</v>
+      </c>
+      <c r="BP9" t="n">
         <v>-45977.77777777778</v>
-      </c>
-      <c r="BO9" t="n">
-        <v>-1.798245614035088</v>
-      </c>
-      <c r="BP9" t="n">
-        <v>1.056432748538015</v>
       </c>
       <c r="BQ9" t="n">
         <v>-1.084713110963122</v>
       </c>
       <c r="BR9" t="n">
-        <v>-48.49473684210525</v>
+        <v>1.056432748538015</v>
       </c>
       <c r="BS9" t="n">
-        <v>67198.54797980003</v>
+        <v>-0.3563852813852815</v>
       </c>
       <c r="BT9" t="n">
-        <v>-52.75438596491229</v>
+        <v>6.794736842105266</v>
       </c>
       <c r="BU9" t="n">
         <v>1.192770146520132</v>
       </c>
       <c r="BV9" t="n">
-        <v>-6833875.771219522</v>
+        <v>-1.798245614035088</v>
       </c>
     </row>
     <row r="10">
@@ -2729,68 +2729,68 @@
         <v>0.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>-4.012014080195897</v>
+        <v>1.155</v>
       </c>
       <c r="BB10" t="n">
-        <v>0.3962962962962961</v>
+        <v>35045.18259518259</v>
       </c>
       <c r="BC10" t="n">
         <v>-3.936998051019774</v>
       </c>
-      <c r="BD10" t="inlineStr"/>
+      <c r="BD10" t="n">
+        <v>-4.012014080195897</v>
+      </c>
       <c r="BE10" t="n">
+        <v>8263672.957159354</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>124.89</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>13018486.76155494</v>
+      </c>
+      <c r="BH10" t="n">
         <v>0.1065966197545147</v>
       </c>
-      <c r="BF10" t="n">
-        <v>-1.800440476190488</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>8.975382614018983</v>
-      </c>
-      <c r="BH10" t="n">
-        <v>35045.18259518259</v>
-      </c>
       <c r="BI10" t="n">
-        <v>64795750</v>
+        <v>-3.724372513008888</v>
       </c>
       <c r="BJ10" t="n">
-        <v>-3.724372513008888</v>
-      </c>
-      <c r="BK10" t="n">
-        <v>1.155</v>
-      </c>
+        <v>5.473109304646187</v>
+      </c>
+      <c r="BK10" t="inlineStr"/>
       <c r="BL10" t="n">
         <v>5.763873584328138</v>
       </c>
       <c r="BM10" t="n">
-        <v>5.473109304646187</v>
+        <v>8.975382614018983</v>
       </c>
       <c r="BN10" t="n">
+        <v>124.68</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>64795750</v>
+      </c>
+      <c r="BP10" t="n">
         <v>163160</v>
-      </c>
-      <c r="BO10" t="n">
-        <v>2.635</v>
-      </c>
-      <c r="BP10" t="n">
-        <v>0.7920833333333341</v>
       </c>
       <c r="BQ10" t="n">
         <v>10.34809668635589</v>
       </c>
       <c r="BR10" t="n">
-        <v>124.68</v>
+        <v>0.7920833333333341</v>
       </c>
       <c r="BS10" t="n">
-        <v>13018486.76155494</v>
+        <v>0.3962962962962961</v>
       </c>
       <c r="BT10" t="n">
-        <v>124.89</v>
+        <v>-1.800440476190488</v>
       </c>
       <c r="BU10" t="n">
         <v>-3.008159678186047</v>
       </c>
       <c r="BV10" t="n">
-        <v>8263672.957159354</v>
+        <v>2.635</v>
       </c>
     </row>
     <row r="11">
@@ -2949,70 +2949,70 @@
         <v>-0.1809210526315789</v>
       </c>
       <c r="BA11" t="n">
-        <v>2.387731481481481</v>
+        <v>0.6662068965517243</v>
       </c>
       <c r="BB11" t="n">
-        <v>-0.8935185185185184</v>
+        <v>-48065.97222222223</v>
       </c>
       <c r="BC11" t="n">
         <v>0.6932856032856058</v>
       </c>
       <c r="BD11" t="n">
+        <v>2.387731481481481</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>-36818643.71739371</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>30.42206896551727</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>-39862586.80555555</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>-0.8302397602397602</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>-2.31018518518519</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>-4.999770784770789</v>
+      </c>
+      <c r="BK11" t="n">
         <v>-56098.50468975468</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>-0.8302397602397602</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>-6.102643678160916</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>-5.71643518518519</v>
-      </c>
-      <c r="BH11" t="n">
-        <v>-48065.97222222223</v>
-      </c>
-      <c r="BI11" t="n">
-        <v>-72102827.5862069</v>
-      </c>
-      <c r="BJ11" t="n">
-        <v>-2.31018518518519</v>
-      </c>
-      <c r="BK11" t="n">
-        <v>0.6662068965517243</v>
       </c>
       <c r="BL11" t="n">
         <v>-4.030092592592595</v>
       </c>
       <c r="BM11" t="n">
-        <v>-4.999770784770789</v>
+        <v>-5.71643518518519</v>
       </c>
       <c r="BN11" t="n">
+        <v>20.01379310344828</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>-72102827.5862069</v>
+      </c>
+      <c r="BP11" t="n">
         <v>-138387.5862068966</v>
-      </c>
-      <c r="BO11" t="n">
-        <v>-2.208275862068965</v>
-      </c>
-      <c r="BP11" t="n">
-        <v>-2.068689655172413</v>
       </c>
       <c r="BQ11" t="n">
         <v>-5.09639138639136</v>
       </c>
       <c r="BR11" t="n">
-        <v>20.01379310344828</v>
+        <v>-2.068689655172413</v>
       </c>
       <c r="BS11" t="n">
-        <v>-39862586.80555555</v>
+        <v>-0.8935185185185184</v>
       </c>
       <c r="BT11" t="n">
-        <v>30.42206896551727</v>
+        <v>-6.102643678160916</v>
       </c>
       <c r="BU11" t="n">
         <v>-1.090574980574956</v>
       </c>
       <c r="BV11" t="n">
-        <v>-36818643.71739371</v>
+        <v>-2.208275862068965</v>
       </c>
     </row>
     <row r="12">
@@ -3171,70 +3171,70 @@
         <v>0.1176470588235294</v>
       </c>
       <c r="BA12" t="n">
-        <v>-1.954520697167755</v>
+        <v>-0.07999999999999963</v>
       </c>
       <c r="BB12" t="n">
-        <v>-0.1965250544662311</v>
+        <v>-8770.098039215691</v>
       </c>
       <c r="BC12" t="n">
         <v>-0.5223736333111297</v>
       </c>
       <c r="BD12" t="n">
+        <v>-1.954520697167755</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>-989866.5639915639</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>-6.400000000000006</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>-1895626.089324619</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>0.09596375846375849</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>0.6577995642701921</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>0.6954261016761194</v>
+      </c>
+      <c r="BK12" t="n">
         <v>-5693.709716209716</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>0.09596375846375849</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>5.914000000000016</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>0.7790305010893235</v>
-      </c>
-      <c r="BH12" t="n">
-        <v>-8770.098039215691</v>
-      </c>
-      <c r="BI12" t="n">
-        <v>-6925200</v>
-      </c>
-      <c r="BJ12" t="n">
-        <v>0.6577995642701921</v>
-      </c>
-      <c r="BK12" t="n">
-        <v>-0.07999999999999963</v>
       </c>
       <c r="BL12" t="n">
         <v>-2.434302832244001</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.6954261016761194</v>
+        <v>0.7790305010893235</v>
       </c>
       <c r="BN12" t="n">
+        <v>-9</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>-6925200</v>
+      </c>
+      <c r="BP12" t="n">
         <v>-17360</v>
-      </c>
-      <c r="BO12" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="BP12" t="n">
-        <v>1.472666666666669</v>
       </c>
       <c r="BQ12" t="n">
         <v>1.266621572871585</v>
       </c>
       <c r="BR12" t="n">
-        <v>-9</v>
+        <v>1.472666666666669</v>
       </c>
       <c r="BS12" t="n">
-        <v>-1895626.089324619</v>
+        <v>-0.1965250544662311</v>
       </c>
       <c r="BT12" t="n">
-        <v>-6.400000000000006</v>
+        <v>5.914000000000016</v>
       </c>
       <c r="BU12" t="n">
         <v>-0.08552229020980917</v>
       </c>
       <c r="BV12" t="n">
-        <v>-989866.5639915639</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="13">
@@ -3387,70 +3387,70 @@
         <v>0.2222222222222222</v>
       </c>
       <c r="BA13" t="n">
-        <v>1.011101758323985</v>
+        <v>-1.68</v>
       </c>
       <c r="BB13" t="n">
-        <v>-0.001206509539842804</v>
+        <v>-8895.781893004114</v>
       </c>
       <c r="BC13" t="n">
         <v>1.442806201843066</v>
       </c>
       <c r="BD13" t="n">
+        <v>1.011101758323985</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>-1287794.097429133</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>-142.44</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>-3450137.485970819</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>0.2052336203629224</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>5.84902731013841</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>1.465475104261301</v>
+      </c>
+      <c r="BK13" t="n">
         <v>8855.378238639489</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>0.2052336203629224</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>-1.746476190476216</v>
-      </c>
-      <c r="BG13" t="n">
-        <v>-0.852562663673794</v>
-      </c>
-      <c r="BH13" t="n">
-        <v>-8895.781893004114</v>
-      </c>
-      <c r="BI13" t="n">
-        <v>-39048000</v>
-      </c>
-      <c r="BJ13" t="n">
-        <v>5.84902731013841</v>
-      </c>
-      <c r="BK13" t="n">
-        <v>-1.68</v>
       </c>
       <c r="BL13" t="n">
         <v>0.6248410026187656</v>
       </c>
       <c r="BM13" t="n">
-        <v>1.465475104261301</v>
+        <v>-0.852562663673794</v>
       </c>
       <c r="BN13" t="n">
+        <v>-131.84</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>-39048000</v>
+      </c>
+      <c r="BP13" t="n">
         <v>-87840</v>
-      </c>
-      <c r="BO13" t="n">
-        <v>-2.4</v>
-      </c>
-      <c r="BP13" t="n">
-        <v>-0.1983333333333341</v>
       </c>
       <c r="BQ13" t="n">
         <v>-2.577726697738001</v>
       </c>
       <c r="BR13" t="n">
-        <v>-131.84</v>
+        <v>-0.1983333333333341</v>
       </c>
       <c r="BS13" t="n">
-        <v>-3450137.485970819</v>
+        <v>-0.001206509539842804</v>
       </c>
       <c r="BT13" t="n">
-        <v>-142.44</v>
+        <v>-1.746476190476216</v>
       </c>
       <c r="BU13" t="n">
         <v>2.030217276301443</v>
       </c>
       <c r="BV13" t="n">
-        <v>-1287794.097429133</v>
+        <v>-2.4</v>
       </c>
     </row>
     <row r="14">
@@ -3603,68 +3603,68 @@
         <v>0.1176470588235294</v>
       </c>
       <c r="BA14" t="n">
-        <v>3.606349206349201</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>0.3944444444444444</v>
-      </c>
+        <v>0.8012820512820511</v>
+      </c>
+      <c r="BB14" t="inlineStr"/>
       <c r="BC14" t="n">
         <v>2.014719308469306</v>
       </c>
       <c r="BD14" t="n">
+        <v>3.606349206349201</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>261340.3909458597</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>55.58974358974356</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>2958549.933862433</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>0.20987234987235</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>-5.716005291005217</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>1.122746472277726</v>
+      </c>
+      <c r="BK14" t="n">
         <v>2967.451487906033</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>0.20987234987235</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>-2.322222222222251</v>
-      </c>
-      <c r="BG14" t="n">
-        <v>-0.6893518518518675</v>
-      </c>
-      <c r="BH14" t="inlineStr"/>
-      <c r="BI14" t="n">
-        <v>834134.615384616</v>
-      </c>
-      <c r="BJ14" t="n">
-        <v>-5.716005291005217</v>
-      </c>
-      <c r="BK14" t="n">
-        <v>0.8012820512820511</v>
       </c>
       <c r="BL14" t="n">
         <v>4.035978835978838</v>
       </c>
       <c r="BM14" t="n">
-        <v>1.122746472277726</v>
+        <v>-0.6893518518518675</v>
       </c>
       <c r="BN14" t="n">
+        <v>57.29166666666666</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>834134.615384616</v>
+      </c>
+      <c r="BP14" t="n">
         <v>19003.49650349651</v>
-      </c>
-      <c r="BO14" t="n">
-        <v>1.493589743589743</v>
-      </c>
-      <c r="BP14" t="n">
-        <v>2.597649572649566</v>
       </c>
       <c r="BQ14" t="n">
         <v>-0.7604441912254316</v>
       </c>
       <c r="BR14" t="n">
-        <v>57.29166666666666</v>
+        <v>2.597649572649566</v>
       </c>
       <c r="BS14" t="n">
-        <v>2958549.933862433</v>
+        <v>0.3944444444444444</v>
       </c>
       <c r="BT14" t="n">
-        <v>55.58974358974356</v>
+        <v>-2.322222222222251</v>
       </c>
       <c r="BU14" t="n">
         <v>-0.7497044448607255</v>
       </c>
       <c r="BV14" t="n">
-        <v>261340.3909458597</v>
+        <v>1.493589743589743</v>
       </c>
     </row>
     <row r="15">
@@ -3825,66 +3825,66 @@
         <v>0.25</v>
       </c>
       <c r="BA15" t="n">
-        <v>-1.451857282502445</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>0.75</v>
-      </c>
+        <v>-0.75</v>
+      </c>
+      <c r="BB15" t="inlineStr"/>
       <c r="BC15" t="n">
         <v>4.740521083854418</v>
       </c>
-      <c r="BD15" t="inlineStr"/>
+      <c r="BD15" t="n">
+        <v>-1.451857282502445</v>
+      </c>
       <c r="BE15" t="n">
+        <v>13476367.61833034</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>-44.07894736842104</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>10804150.37471489</v>
+      </c>
+      <c r="BH15" t="n">
         <v>0.9983333333333335</v>
       </c>
-      <c r="BF15" t="n">
-        <v>-8.367653508771951</v>
-      </c>
-      <c r="BG15" t="n">
-        <v>7.61312724014337</v>
-      </c>
-      <c r="BH15" t="inlineStr"/>
       <c r="BI15" t="n">
-        <v>17294736.84210526</v>
+        <v>-0.4286412512219044</v>
       </c>
       <c r="BJ15" t="n">
-        <v>-0.4286412512219044</v>
-      </c>
-      <c r="BK15" t="n">
-        <v>-0.75</v>
-      </c>
+        <v>12.90907050876349</v>
+      </c>
+      <c r="BK15" t="inlineStr"/>
       <c r="BL15" t="n">
         <v>6.041035353535349</v>
       </c>
       <c r="BM15" t="n">
-        <v>12.90907050876349</v>
+        <v>7.61312724014337</v>
       </c>
       <c r="BN15" t="n">
+        <v>-33.10526315789474</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>17294736.84210526</v>
+      </c>
+      <c r="BP15" t="n">
         <v>64777.77777777778</v>
-      </c>
-      <c r="BO15" t="n">
-        <v>0.8815789473684212</v>
-      </c>
-      <c r="BP15" t="n">
-        <v>0.9345394736842074</v>
       </c>
       <c r="BQ15" t="n">
         <v>7.302621842906944</v>
       </c>
       <c r="BR15" t="n">
-        <v>-33.10526315789474</v>
+        <v>0.9345394736842074</v>
       </c>
       <c r="BS15" t="n">
-        <v>10804150.37471489</v>
+        <v>0.75</v>
       </c>
       <c r="BT15" t="n">
-        <v>-44.07894736842104</v>
+        <v>-8.367653508771951</v>
       </c>
       <c r="BU15" t="n">
         <v>-3.422599280186972</v>
       </c>
       <c r="BV15" t="n">
-        <v>13476367.61833034</v>
+        <v>0.8815789473684212</v>
       </c>
     </row>
     <row r="16">
@@ -4051,70 +4051,70 @@
         <v>0.1458333333333333</v>
       </c>
       <c r="BA16" t="n">
-        <v>1.841065878565875</v>
+        <v>1.435897435897436</v>
       </c>
       <c r="BB16" t="n">
-        <v>-0.2436147186147186</v>
+        <v>3166.98717948718</v>
       </c>
       <c r="BC16" t="n">
         <v>0.7011796682849329</v>
       </c>
       <c r="BD16" t="n">
+        <v>1.841065878565875</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>-1170630.297455954</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>104.8333333333333</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>136668.9733877219</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>0.1389316823527349</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>-1.010540154290112</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>0.06106032734321332</v>
+      </c>
+      <c r="BK16" t="n">
         <v>-86.68256816282883</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>0.1389316823527349</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>-10.15494505494507</v>
-      </c>
-      <c r="BG16" t="n">
-        <v>-1.113660644910638</v>
-      </c>
-      <c r="BH16" t="n">
-        <v>3166.98717948718</v>
-      </c>
-      <c r="BI16" t="n">
-        <v>6081282.05128205</v>
-      </c>
-      <c r="BJ16" t="n">
-        <v>-1.010540154290112</v>
-      </c>
-      <c r="BK16" t="n">
-        <v>1.435897435897436</v>
       </c>
       <c r="BL16" t="n">
         <v>1.222213897213905</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.06106032734321332</v>
+        <v>-1.113660644910638</v>
       </c>
       <c r="BN16" t="n">
+        <v>105.6769230769231</v>
+      </c>
+      <c r="BO16" t="n">
+        <v>6081282.05128205</v>
+      </c>
+      <c r="BP16" t="n">
         <v>42469.23076923077</v>
-      </c>
-      <c r="BO16" t="n">
-        <v>0.9743589743589742</v>
-      </c>
-      <c r="BP16" t="n">
-        <v>1.570818070818067</v>
       </c>
       <c r="BQ16" t="n">
         <v>-1.811064495932925</v>
       </c>
       <c r="BR16" t="n">
-        <v>105.6769230769231</v>
+        <v>1.570818070818067</v>
       </c>
       <c r="BS16" t="n">
-        <v>136668.9733877219</v>
+        <v>-0.2436147186147186</v>
       </c>
       <c r="BT16" t="n">
-        <v>104.8333333333333</v>
+        <v>-10.15494505494507</v>
       </c>
       <c r="BU16" t="n">
         <v>-0.7967608049845012</v>
       </c>
       <c r="BV16" t="n">
-        <v>-1170630.297455954</v>
+        <v>0.9743589743589742</v>
       </c>
     </row>
     <row r="17">
@@ -4273,70 +4273,70 @@
         <v>-0.1213235294117647</v>
       </c>
       <c r="BA17" t="n">
-        <v>-0.4637806637806605</v>
+        <v>0.22</v>
       </c>
       <c r="BB17" t="n">
-        <v>-0.05216450216450208</v>
+        <v>1152.660533910534</v>
       </c>
       <c r="BC17" t="n">
         <v>-1.398419367747096</v>
       </c>
       <c r="BD17" t="n">
+        <v>-0.4637806637806605</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>203668.7941843402</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>21.41111111111113</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>2948543.47041847</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>-0.1620821661998135</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>3.311724386724364</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>-0.739847272242244</v>
+      </c>
+      <c r="BK17" t="n">
         <v>-1836.431061313417</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>-0.1620821661998135</v>
-      </c>
-      <c r="BF17" t="n">
-        <v>-4.160148148148153</v>
-      </c>
-      <c r="BG17" t="n">
-        <v>2.664898989898987</v>
-      </c>
-      <c r="BH17" t="n">
-        <v>1152.660533910534</v>
-      </c>
-      <c r="BI17" t="n">
-        <v>-720666.666666667</v>
-      </c>
-      <c r="BJ17" t="n">
-        <v>3.311724386724364</v>
-      </c>
-      <c r="BK17" t="n">
-        <v>0.22</v>
       </c>
       <c r="BL17" t="n">
         <v>0.8255772005772002</v>
       </c>
       <c r="BM17" t="n">
-        <v>-0.739847272242244</v>
+        <v>2.664898989898987</v>
       </c>
       <c r="BN17" t="n">
+        <v>8.766666666666666</v>
+      </c>
+      <c r="BO17" t="n">
+        <v>-720666.666666667</v>
+      </c>
+      <c r="BP17" t="n">
         <v>-7055.555555555555</v>
-      </c>
-      <c r="BO17" t="n">
-        <v>0.02222222222222237</v>
-      </c>
-      <c r="BP17" t="n">
-        <v>-5.084777777777781</v>
       </c>
       <c r="BQ17" t="n">
         <v>1.340140856342543</v>
       </c>
       <c r="BR17" t="n">
-        <v>8.766666666666666</v>
+        <v>-5.084777777777781</v>
       </c>
       <c r="BS17" t="n">
-        <v>2948543.47041847</v>
+        <v>-0.05216450216450208</v>
       </c>
       <c r="BT17" t="n">
-        <v>21.41111111111113</v>
+        <v>-4.160148148148153</v>
       </c>
       <c r="BU17" t="n">
         <v>4.259690943043893</v>
       </c>
       <c r="BV17" t="n">
-        <v>203668.7941843402</v>
+        <v>0.02222222222222237</v>
       </c>
     </row>
     <row r="18">
@@ -4497,68 +4497,68 @@
         <v>0.1176470588235294</v>
       </c>
       <c r="BA18" t="n">
-        <v>1.491715506220853</v>
+        <v>0.4249999999999998</v>
       </c>
       <c r="BB18" t="n">
-        <v>0</v>
+        <v>-1348.786819241364</v>
       </c>
       <c r="BC18" t="n">
         <v>-0.4465951378199833</v>
       </c>
-      <c r="BD18" t="inlineStr"/>
+      <c r="BD18" t="n">
+        <v>1.491715506220853</v>
+      </c>
       <c r="BE18" t="n">
-        <v>0</v>
+        <v>-623308.1685339094</v>
       </c>
       <c r="BF18" t="n">
-        <v>2.92291666666668</v>
+        <v>34.15000000000001</v>
       </c>
       <c r="BG18" t="n">
-        <v>-1.581351617782104</v>
+        <v>-557397.7464034278</v>
       </c>
       <c r="BH18" t="n">
-        <v>-1348.786819241364</v>
+        <v>0</v>
       </c>
       <c r="BI18" t="n">
-        <v>-1418750</v>
+        <v>1.246166432596937</v>
       </c>
       <c r="BJ18" t="n">
-        <v>1.246166432596937</v>
-      </c>
-      <c r="BK18" t="n">
-        <v>0.4249999999999998</v>
-      </c>
+        <v>-2.927087024123125</v>
+      </c>
+      <c r="BK18" t="inlineStr"/>
       <c r="BL18" t="n">
         <v>-1.155842291002728</v>
       </c>
       <c r="BM18" t="n">
-        <v>-2.927087024123125</v>
+        <v>-1.581351617782104</v>
       </c>
       <c r="BN18" t="n">
+        <v>13.40000000000001</v>
+      </c>
+      <c r="BO18" t="n">
+        <v>-1418750</v>
+      </c>
+      <c r="BP18" t="n">
         <v>-16100</v>
-      </c>
-      <c r="BO18" t="n">
-        <v>0.4249999999999998</v>
-      </c>
-      <c r="BP18" t="n">
-        <v>-4.310416666666665</v>
       </c>
       <c r="BQ18" t="n">
         <v>-2.060120436988129</v>
       </c>
       <c r="BR18" t="n">
-        <v>13.40000000000001</v>
+        <v>-4.310416666666665</v>
       </c>
       <c r="BS18" t="n">
-        <v>-557397.7464034278</v>
+        <v>0</v>
       </c>
       <c r="BT18" t="n">
-        <v>34.15000000000001</v>
+        <v>2.92291666666668</v>
       </c>
       <c r="BU18" t="n">
         <v>0.6999693611031148</v>
       </c>
       <c r="BV18" t="n">
-        <v>-623308.1685339094</v>
+        <v>0.4249999999999998</v>
       </c>
     </row>
     <row r="19">
@@ -4723,70 +4723,70 @@
         <v>0.4097222222222222</v>
       </c>
       <c r="BA19" t="n">
-        <v>0.2106186868686848</v>
+        <v>-0.496031746031746</v>
       </c>
       <c r="BB19" t="n">
-        <v>0.4703030303030304</v>
+        <v>24872.94142404437</v>
       </c>
       <c r="BC19" t="n">
         <v>-1.924816376355604</v>
       </c>
       <c r="BD19" t="n">
+        <v>0.2106186868686848</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>8557743.478787716</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>-28.13888888888889</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>11441312.18434343</v>
+      </c>
+      <c r="BH19" t="n">
+        <v>0.2661090362070757</v>
+      </c>
+      <c r="BI19" t="n">
+        <v>-4.637184343434313</v>
+      </c>
+      <c r="BJ19" t="n">
+        <v>6.768493045366284</v>
+      </c>
+      <c r="BK19" t="n">
         <v>17877.66439909297</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>0.2661090362070757</v>
-      </c>
-      <c r="BF19" t="n">
-        <v>-2.083994708994709</v>
-      </c>
-      <c r="BG19" t="n">
-        <v>7.476994949494937</v>
-      </c>
-      <c r="BH19" t="n">
-        <v>24872.94142404437</v>
-      </c>
-      <c r="BI19" t="n">
-        <v>8808531.746031746</v>
-      </c>
-      <c r="BJ19" t="n">
-        <v>-4.637184343434313</v>
-      </c>
-      <c r="BK19" t="n">
-        <v>-0.496031746031746</v>
       </c>
       <c r="BL19" t="n">
         <v>8.799760101010094</v>
       </c>
       <c r="BM19" t="n">
-        <v>6.768493045366284</v>
+        <v>7.476994949494937</v>
       </c>
       <c r="BN19" t="n">
+        <v>-25.52777777777777</v>
+      </c>
+      <c r="BO19" t="n">
+        <v>8808531.746031746</v>
+      </c>
+      <c r="BP19" t="n">
         <v>15142.85714285714</v>
-      </c>
-      <c r="BO19" t="n">
-        <v>-0.353174603174603</v>
-      </c>
-      <c r="BP19" t="n">
-        <v>-2.611111111111111</v>
       </c>
       <c r="BQ19" t="n">
         <v>7.364615726895053</v>
       </c>
       <c r="BR19" t="n">
-        <v>-25.52777777777777</v>
+        <v>-2.611111111111111</v>
       </c>
       <c r="BS19" t="n">
-        <v>11441312.18434343</v>
+        <v>0.4703030303030304</v>
       </c>
       <c r="BT19" t="n">
-        <v>-28.13888888888889</v>
+        <v>-2.083994708994709</v>
       </c>
       <c r="BU19" t="n">
         <v>1.135705242135828</v>
       </c>
       <c r="BV19" t="n">
-        <v>8557743.478787716</v>
+        <v>-0.353174603174603</v>
       </c>
     </row>
   </sheetData>

--- a/data/france/p6_deployment/data_preparation/df_tagged.xlsx
+++ b/data/france/p6_deployment/data_preparation/df_tagged.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BV10"/>
+  <dimension ref="A1:BV19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -690,123 +690,123 @@
       </c>
       <c r="BA1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_rep_player_start</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_start</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_wage_player_start</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>dif_n_player_miss</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_wage_player_miss</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_sub</t>
+        </is>
+      </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_wage_player_sub</t>
+        </is>
+      </c>
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_pot_player_miss</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_start</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_miss</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_value_player_start</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_start</t>
+        </is>
+      </c>
+      <c r="BM1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_start</t>
+        </is>
+      </c>
+      <c r="BN1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_rep_player_sub</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_start</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_start</t>
-        </is>
-      </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rep_player_start</t>
-        </is>
-      </c>
-      <c r="BE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_wage_player_start</t>
-        </is>
-      </c>
-      <c r="BF1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_start</t>
-        </is>
-      </c>
-      <c r="BG1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_value_player_start</t>
-        </is>
-      </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_age_player_miss</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_sub</t>
+        </is>
+      </c>
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_value_player_sub</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_miss</t>
-        </is>
-      </c>
-      <c r="BK1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_pot_player_miss</t>
-        </is>
-      </c>
-      <c r="BL1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_sub</t>
-        </is>
-      </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>dif_sum_value_player_miss</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_wage_player_sub</t>
-        </is>
-      </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_hei_player_sub</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_start</t>
-        </is>
-      </c>
-      <c r="BQ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_n_player_miss</t>
-        </is>
-      </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_rep_player_miss</t>
+        </is>
+      </c>
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>dif_sum_rat_player_miss</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="BV1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_age_player_sub</t>
-        </is>
-      </c>
-      <c r="BT1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_sub</t>
-        </is>
-      </c>
-      <c r="BU1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_wage_player_miss</t>
-        </is>
-      </c>
-      <c r="BV1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_rep_player_miss</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>AsQgyP6l</t>
+          <t>b59ZhlYj</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45592.69791666666</v>
+        <v>45606.69791666666</v>
       </c>
       <c r="C2" t="n">
         <v>102</v>
@@ -815,10 +815,10 @@
         <v>133</v>
       </c>
       <c r="E2" t="n">
-        <v>448</v>
+        <v>56</v>
       </c>
       <c r="F2" t="n">
-        <v>129</v>
+        <v>362</v>
       </c>
       <c r="G2" t="n">
         <v>55</v>
@@ -840,195 +840,195 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>286</v>
+        <v>165</v>
       </c>
       <c r="M2" t="n">
-        <v>258</v>
+        <v>226</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.5233333333333334</v>
+        <v>3.593333333333333</v>
       </c>
       <c r="P2" t="n">
-        <v>0.5056985294117644</v>
+        <v>0.9219999999999999</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R2" t="n">
-        <v>0.8388157894736842</v>
+        <v>1.073684210526316</v>
       </c>
       <c r="S2" t="n">
-        <v>-3</v>
+        <v>6.333333333333334</v>
       </c>
       <c r="T2" t="n">
-        <v>0.2697368421052637</v>
+        <v>0.2833333333333332</v>
       </c>
       <c r="U2" t="n">
-        <v>-3.666666666666666</v>
+        <v>9.666666666666666</v>
       </c>
       <c r="V2" t="n">
-        <v>1.355263157894738</v>
+        <v>-1.683333333333334</v>
       </c>
       <c r="W2" t="n">
-        <v>0.3333333333333333</v>
+        <v>3.666666666666667</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.230263157894737</v>
+        <v>0.6131578947368423</v>
       </c>
       <c r="Y2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>1.215789473684211</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>18.54498320307144</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>23.16284513280837</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>812.060312653184</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>901.1340644267209</v>
+      </c>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="n">
+        <v>-6.305882352941168</v>
+      </c>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="n">
+        <v>-0.03921568627450966</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>2.573684210526316</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>33.33333333333333</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>-1.711111111111109</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>66</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>-46.05000000000001</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>-2.333333333333333</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>-0.9333333333333333</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR2" t="n">
         <v>0.5</v>
       </c>
-      <c r="Z2" t="n">
-        <v>-1.055921052631579</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>20.9625</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>19.76698178836489</v>
-      </c>
-      <c r="AC2" t="inlineStr"/>
-      <c r="AD2" t="n">
-        <v>1087.251761429009</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>-9</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>-27.82352941176471</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>3.129411764705878</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>-15.16666666666666</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>0.463815789473685</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>-6</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>-22.40131578947368</v>
-      </c>
-      <c r="AM2" t="inlineStr"/>
-      <c r="AN2" t="n">
-        <v>-295.4642857142857</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>3.833333333333333</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>-0.4375</v>
-      </c>
-      <c r="AQ2" t="inlineStr"/>
-      <c r="AR2" t="n">
-        <v>0</v>
-      </c>
       <c r="AS2" t="n">
-        <v>10.5</v>
+        <v>-4.66666666666667</v>
       </c>
       <c r="AT2" t="n">
-        <v>6.473684210526315</v>
-      </c>
-      <c r="AU2" t="inlineStr"/>
+        <v>-8.515789473684208</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>20.58333333333333</v>
+      </c>
       <c r="AV2" t="n">
-        <v>3.53306285074029</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>-0.0459773713114643</v>
-      </c>
+        <v>4.925892901222976</v>
+      </c>
+      <c r="AW2" t="inlineStr"/>
       <c r="AX2" t="n">
-        <v>0.03689127045394714</v>
+        <v>0.006674797625643533</v>
       </c>
       <c r="AY2" t="n">
-        <v>0.5</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="AZ2" t="n">
-        <v>-0.1809210526315789</v>
+        <v>0.2</v>
       </c>
       <c r="BA2" t="n">
-        <v>-0.8302397602397602</v>
+        <v>0.75</v>
       </c>
       <c r="BB2" t="n">
-        <v>-5.71643518518519</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>2.387731481481481</v>
-      </c>
+        <v>-1.25390625</v>
+      </c>
+      <c r="BC2" t="inlineStr"/>
       <c r="BD2" t="n">
-        <v>-0.8935185185185184</v>
+        <v>-0.8181818181818183</v>
       </c>
       <c r="BE2" t="n">
-        <v>-48065.97222222223</v>
+        <v>55732.32323232324</v>
       </c>
       <c r="BF2" t="n">
-        <v>-4.030092592592595</v>
+        <v>5.683151595063364</v>
       </c>
       <c r="BG2" t="n">
-        <v>-39862586.80555555</v>
+        <v>39495.02120428591</v>
       </c>
       <c r="BH2" t="n">
-        <v>-2.103357142857138</v>
+        <v>-41.48803827751195</v>
       </c>
       <c r="BI2" t="n">
-        <v>-36818643.71739371</v>
+        <v>5.12109375</v>
       </c>
       <c r="BJ2" t="n">
-        <v>-6.152499999999975</v>
+        <v>-1.629585326953759</v>
       </c>
       <c r="BK2" t="n">
-        <v>29.31</v>
+        <v>10247416.54829546</v>
       </c>
       <c r="BL2" t="n">
-        <v>-4.999770784770789</v>
+        <v>-1.37606534090909</v>
       </c>
       <c r="BM2" t="n">
-        <v>-72502642.85714285</v>
+        <v>4.135653409090907</v>
       </c>
       <c r="BN2" t="n">
-        <v>-56098.50468975468</v>
+        <v>0.9983333333333335</v>
       </c>
       <c r="BO2" t="n">
-        <v>-1.090574980574956</v>
+        <v>-2.866028708133975</v>
       </c>
       <c r="BP2" t="n">
-        <v>-2.31018518518519</v>
+        <v>9.865844704521166</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0.6514285714285717</v>
+        <v>13025452.27642654</v>
       </c>
       <c r="BR2" t="n">
-        <v>18.8857142857143</v>
+        <v>16447009.56937799</v>
       </c>
       <c r="BS2" t="n">
-        <v>0.6932856032856058</v>
+        <v>-3.008444944180212</v>
       </c>
       <c r="BT2" t="n">
-        <v>-5.09639138639136</v>
+        <v>0.8133971291866029</v>
       </c>
       <c r="BU2" t="n">
-        <v>-139774.2857142857</v>
+        <v>-48.01435406698565</v>
       </c>
       <c r="BV2" t="n">
-        <v>-2.26</v>
+        <v>3.10320644555939</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>h2acepbK</t>
+          <t>nRkUEVfA</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45592.54166666666</v>
+        <v>45606.54166666666</v>
       </c>
       <c r="C3" t="n">
         <v>101</v>
@@ -1037,10 +1037,10 @@
         <v>133</v>
       </c>
       <c r="E3" t="n">
-        <v>736</v>
+        <v>194</v>
       </c>
       <c r="F3" t="n">
-        <v>599</v>
+        <v>579</v>
       </c>
       <c r="G3" t="n">
         <v>55</v>
@@ -1062,204 +1062,204 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>40</v>
+        <v>249</v>
       </c>
       <c r="M3" t="n">
-        <v>163</v>
+        <v>7</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>0.8366666666666666</v>
+        <v>-2.853333333333333</v>
       </c>
       <c r="P3" t="n">
-        <v>0.3579779411764706</v>
+        <v>0.03141666666666687</v>
       </c>
       <c r="Q3" t="n">
-        <v>1</v>
+        <v>-1.25</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8823529411764708</v>
+        <v>0.1470588235294117</v>
       </c>
       <c r="S3" t="n">
-        <v>1.333333333333333</v>
+        <v>-6.5</v>
       </c>
       <c r="T3" t="n">
-        <v>1.051470588235294</v>
+        <v>0.8666666666666663</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>-11.66666666666667</v>
       </c>
       <c r="V3" t="n">
-        <v>1.926470588235295</v>
+        <v>0.6875</v>
       </c>
       <c r="W3" t="n">
-        <v>0.3333333333333333</v>
+        <v>-4.166666666666667</v>
       </c>
       <c r="X3" t="n">
-        <v>0.3529411764705883</v>
+        <v>-0.2683823529411764</v>
       </c>
       <c r="Y3" t="n">
-        <v>1</v>
+        <v>-2.75</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.5294117647058822</v>
+        <v>-0.2058823529411764</v>
       </c>
       <c r="AA3" t="n">
-        <v>17.19810924369748</v>
+        <v>25.49417989417989</v>
       </c>
       <c r="AB3" t="n">
-        <v>17.48079349674019</v>
-      </c>
-      <c r="AC3" t="inlineStr"/>
+        <v>20.97425284143889</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>1006.568069306931</v>
+      </c>
       <c r="AD3" t="n">
-        <v>873.581322507257</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>105</v>
-      </c>
+        <v>931.8853854052587</v>
+      </c>
+      <c r="AE3" t="inlineStr"/>
       <c r="AF3" t="n">
-        <v>21.49047619047619</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>14</v>
-      </c>
+        <v>-5.054945054945065</v>
+      </c>
+      <c r="AG3" t="inlineStr"/>
       <c r="AH3" t="n">
-        <v>11.54761904761904</v>
+        <v>9.054945054945058</v>
       </c>
       <c r="AI3" t="n">
-        <v>-1.333333333333336</v>
+        <v>-7.333333333333332</v>
       </c>
       <c r="AJ3" t="n">
-        <v>4.529411764705884</v>
+        <v>-0.9575163398692865</v>
       </c>
       <c r="AK3" t="n">
-        <v>6.666666666666671</v>
+        <v>-34.66666666666667</v>
       </c>
       <c r="AL3" t="n">
-        <v>4.272058823529406</v>
-      </c>
-      <c r="AM3" t="inlineStr"/>
+        <v>-9.174999999999997</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>-374.5</v>
+      </c>
       <c r="AN3" t="n">
-        <v>37.74725274725284</v>
+        <v>-121.7912087912088</v>
       </c>
       <c r="AO3" t="n">
         <v>-0.6666666666666667</v>
       </c>
       <c r="AP3" t="n">
-        <v>-0.6156862745098037</v>
+        <v>-0.09583333333333321</v>
       </c>
       <c r="AQ3" t="inlineStr"/>
       <c r="AR3" t="n">
-        <v>1.5</v>
+        <v>-2</v>
       </c>
       <c r="AS3" t="n">
-        <v>-1.666666666666664</v>
+        <v>2.083333333333334</v>
       </c>
       <c r="AT3" t="n">
-        <v>-3.882352941176467</v>
-      </c>
-      <c r="AU3" t="inlineStr"/>
+        <v>1.385620915032682</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>-2.673383942949158</v>
+      </c>
       <c r="AV3" t="n">
-        <v>1.325409884342061</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>0.05250571962900731</v>
-      </c>
+        <v>0.6348099880488967</v>
+      </c>
+      <c r="AW3" t="inlineStr"/>
       <c r="AX3" t="n">
-        <v>0.00287292148709687</v>
+        <v>-0.01185013876783483</v>
       </c>
       <c r="AY3" t="n">
-        <v>0.6666666666666666</v>
+        <v>-0.6666666666666666</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.1176470588235294</v>
+        <v>-0.2973856209150326</v>
       </c>
       <c r="BA3" t="n">
-        <v>0.08588614284266471</v>
+        <v>-0.125</v>
       </c>
       <c r="BB3" t="n">
-        <v>0.7804315476190311</v>
+        <v>1.385972222222193</v>
       </c>
       <c r="BC3" t="n">
-        <v>-1.989136904761903</v>
+        <v>-11476.85185185185</v>
       </c>
       <c r="BD3" t="n">
-        <v>-0.1997767857142858</v>
+        <v>0.1151960784313726</v>
       </c>
       <c r="BE3" t="n">
-        <v>-9276.755401234572</v>
+        <v>-1516.339869281046</v>
       </c>
       <c r="BF3" t="n">
-        <v>-2.476140873015851</v>
+        <v>-3.154558187797548</v>
       </c>
       <c r="BG3" t="n">
-        <v>-1968025.793650794</v>
+        <v>-6580.706727135299</v>
       </c>
       <c r="BH3" t="n">
-        <v>1.429861111111112</v>
+        <v>2.215686274509807</v>
       </c>
       <c r="BI3" t="n">
-        <v>-1105205.818838971</v>
+        <v>-4.319722222222225</v>
       </c>
       <c r="BJ3" t="n">
-        <v>6.160416666666691</v>
+        <v>5.918545751633985</v>
       </c>
       <c r="BK3" t="n">
-        <v>-9.833333333333343</v>
+        <v>-4744690.972222222</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.5641260591260675</v>
+        <v>-2.088194444444447</v>
       </c>
       <c r="BM3" t="n">
-        <v>-7126666.666666666</v>
+        <v>-6.894305555555547</v>
       </c>
       <c r="BN3" t="n">
-        <v>-5917.568542568542</v>
+        <v>0</v>
       </c>
       <c r="BO3" t="n">
-        <v>0.05761339706992885</v>
+        <v>3.571323529411767</v>
       </c>
       <c r="BP3" t="n">
-        <v>0.3472470238095298</v>
+        <v>-3.36043923742335</v>
       </c>
       <c r="BQ3" t="n">
-        <v>-0.125</v>
+        <v>-1439108.735518249</v>
       </c>
       <c r="BR3" t="n">
-        <v>-11.875</v>
+        <v>631372.5490196077</v>
       </c>
       <c r="BS3" t="n">
-        <v>-0.7005301944432354</v>
+        <v>-4.800637395959029</v>
       </c>
       <c r="BT3" t="n">
-        <v>1.358222546374733</v>
+        <v>0.0318627450980391</v>
       </c>
       <c r="BU3" t="n">
-        <v>-17666.66666666666</v>
+        <v>7.602941176470594</v>
       </c>
       <c r="BV3" t="n">
-        <v>0.9166666666666665</v>
+        <v>1.297049225798176</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>vNHAXt6D</t>
+          <t>WWnG5RHd</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45592.54166666666</v>
+        <v>45606.54166666666</v>
       </c>
       <c r="C4" t="n">
         <v>101</v>
       </c>
       <c r="D4" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E4" t="n">
-        <v>242</v>
+        <v>573</v>
       </c>
       <c r="F4" t="n">
         <v>226</v>
@@ -1284,199 +1284,207 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>286</v>
+        <v>249</v>
       </c>
       <c r="M4" t="n">
-        <v>32</v>
+        <v>127</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.148333333333333</v>
+        <v>0.1224999999999999</v>
       </c>
       <c r="P4" t="n">
-        <v>0.378555555555556</v>
+        <v>0.7667916666666666</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.5</v>
+        <v>-0.5</v>
       </c>
       <c r="R4" t="n">
-        <v>-0.009803921568627416</v>
+        <v>0.2205882352941175</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="T4" t="n">
-        <v>1.152777777777779</v>
+        <v>2.125</v>
       </c>
       <c r="U4" t="n">
-        <v>-1.333333333333332</v>
+        <v>4</v>
       </c>
       <c r="V4" t="n">
-        <v>2.847222222222223</v>
+        <v>5.125</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.5</v>
+        <v>0.75</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.8398692810457515</v>
+        <v>0.4558823529411766</v>
       </c>
       <c r="Y4" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="Z4" t="n">
-        <v>-0.8431372549019607</v>
+        <v>0.3970588235294119</v>
       </c>
       <c r="AA4" t="n">
-        <v>17.84474275724276</v>
+        <v>15.70002405002405</v>
       </c>
       <c r="AB4" t="n">
-        <v>21.17225689346916</v>
-      </c>
-      <c r="AC4" t="inlineStr"/>
+        <v>19.40410253016677</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>842.0533249458113</v>
+      </c>
       <c r="AD4" t="n">
-        <v>879.7668607303815</v>
+        <v>853.734544318015</v>
       </c>
       <c r="AE4" t="inlineStr"/>
       <c r="AF4" t="n">
-        <v>8.803571428571431</v>
+        <v>20.07692307692307</v>
       </c>
       <c r="AG4" t="inlineStr"/>
       <c r="AH4" t="n">
-        <v>16.04464285714286</v>
+        <v>13</v>
       </c>
       <c r="AI4" t="n">
-        <v>9.166666666666671</v>
+        <v>8.75</v>
       </c>
       <c r="AJ4" t="n">
-        <v>5.176470588235297</v>
+        <v>6.882352941176471</v>
       </c>
       <c r="AK4" t="n">
-        <v>5.333333333333329</v>
+        <v>6.333333333333329</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.986111111111114</v>
-      </c>
-      <c r="AM4" t="inlineStr"/>
+        <v>5.875</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>114.5</v>
+      </c>
       <c r="AN4" t="n">
-        <v>-10.52884615384619</v>
+        <v>65.15384615384613</v>
       </c>
       <c r="AO4" t="n">
-        <v>-0.5</v>
+        <v>-2</v>
       </c>
       <c r="AP4" t="n">
-        <v>-1.111111111111111</v>
-      </c>
-      <c r="AQ4" t="inlineStr"/>
+        <v>-0.8958333333333333</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>0</v>
+      </c>
       <c r="AR4" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AS4" t="n">
-        <v>-4.5</v>
+        <v>-4.416666666666668</v>
       </c>
       <c r="AT4" t="n">
-        <v>-4.333333333333336</v>
-      </c>
-      <c r="AU4" t="inlineStr"/>
+        <v>-7.897058823529413</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>-0.9897441911373761</v>
+      </c>
       <c r="AV4" t="n">
-        <v>2.181757328311145</v>
+        <v>-0.2057092003774734</v>
       </c>
       <c r="AW4" t="inlineStr"/>
       <c r="AX4" t="n">
-        <v>0.04034575343889454</v>
+        <v>0.003321177859312657</v>
       </c>
       <c r="AY4" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.5</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.1176470588235294</v>
+        <v>0.3713235294117647</v>
       </c>
       <c r="BA4" t="n">
-        <v>0.2044550687407831</v>
+        <v>0.469278996865204</v>
       </c>
       <c r="BB4" t="n">
-        <v>-0.7612191358024631</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>3.68518518518518</v>
-      </c>
+        <v>-3.88683820968302</v>
+      </c>
+      <c r="BC4" t="inlineStr"/>
       <c r="BD4" t="n">
-        <v>0.4012345679012346</v>
-      </c>
-      <c r="BE4" t="inlineStr"/>
+        <v>-1.172360248447205</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>2916.666666666668</v>
+      </c>
       <c r="BF4" t="n">
-        <v>4.06672839506173</v>
+        <v>2.547527652086487</v>
       </c>
       <c r="BG4" t="n">
-        <v>2944420.138888888</v>
+        <v>14048.80952380953</v>
       </c>
       <c r="BH4" t="n">
-        <v>2.447333333333333</v>
+        <v>-88.19254658385093</v>
       </c>
       <c r="BI4" t="n">
-        <v>335909.8213294647</v>
+        <v>3.244846307906641</v>
       </c>
       <c r="BJ4" t="n">
-        <v>-2.459275362318863</v>
+        <v>1.691200828157349</v>
       </c>
       <c r="BK4" t="n">
-        <v>61.16173913043477</v>
+        <v>9190759.611198187</v>
       </c>
       <c r="BL4" t="n">
-        <v>1.147207990422274</v>
+        <v>1.138714733542315</v>
       </c>
       <c r="BM4" t="n">
-        <v>1080913.043478262</v>
+        <v>6.047041100661787</v>
       </c>
       <c r="BN4" t="n">
-        <v>2967.451487906033</v>
+        <v>0.265354988149106</v>
       </c>
       <c r="BO4" t="n">
-        <v>-0.8101682048110206</v>
+        <v>-0.8440476190476183</v>
       </c>
       <c r="BP4" t="n">
-        <v>-5.886265432098753</v>
+        <v>4.965448538389722</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0.8747826086956523</v>
+        <v>7179315.95651081</v>
       </c>
       <c r="BR4" t="n">
-        <v>62.07826086956521</v>
+        <v>2884627.329192547</v>
       </c>
       <c r="BS4" t="n">
-        <v>1.998870177441606</v>
+        <v>1.452923220570284</v>
       </c>
       <c r="BT4" t="n">
-        <v>-0.68472000221999</v>
+        <v>-1.029503105590062</v>
       </c>
       <c r="BU4" t="n">
-        <v>19809.52380952381</v>
+        <v>-75.98602484472049</v>
       </c>
       <c r="BV4" t="n">
-        <v>1.514782608695652</v>
+        <v>1.117051820728289</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>KdJMr7EE</t>
+          <t>QB1LGiQc</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45592.54166666666</v>
+        <v>45606.54166666666</v>
       </c>
       <c r="C5" t="n">
         <v>101</v>
       </c>
       <c r="D5" t="n">
+        <v>134</v>
+      </c>
+      <c r="E5" t="n">
+        <v>242</v>
+      </c>
+      <c r="F5" t="n">
         <v>133</v>
-      </c>
-      <c r="E5" t="n">
-        <v>535</v>
-      </c>
-      <c r="F5" t="n">
-        <v>33</v>
       </c>
       <c r="G5" t="n">
         <v>55</v>
@@ -1498,189 +1506,195 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>168</v>
+        <v>76</v>
       </c>
       <c r="M5" t="n">
-        <v>204</v>
+        <v>7</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>0.7150000000000003</v>
+        <v>-0.0833333333333337</v>
       </c>
       <c r="P5" t="n">
-        <v>0.7690808823529414</v>
+        <v>0.3862222222222227</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.125</v>
+        <v>0.3529411764705883</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.5</v>
+        <v>-1.666666666666667</v>
       </c>
       <c r="T5" t="n">
-        <v>1.763888888888889</v>
+        <v>-0.1307189542483664</v>
       </c>
       <c r="U5" t="n">
-        <v>1</v>
+        <v>3.666666666666668</v>
       </c>
       <c r="V5" t="n">
-        <v>5.5</v>
+        <v>2.075163398692812</v>
       </c>
       <c r="W5" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="X5" t="n">
-        <v>0.1111111111111109</v>
+        <v>-1.124183006535948</v>
       </c>
       <c r="Y5" t="n">
-        <v>-1.5</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>-0.7291666666666665</v>
+        <v>-1.362745098039216</v>
       </c>
       <c r="AA5" t="n">
-        <v>20.98489010989011</v>
+        <v>18.36801716801717</v>
       </c>
       <c r="AB5" t="n">
-        <v>18.72330400001918</v>
-      </c>
-      <c r="AC5" t="inlineStr"/>
+        <v>20.40126848913614</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>839.5656575038066</v>
+      </c>
       <c r="AD5" t="n">
-        <v>931.8494304849846</v>
+        <v>895.5550622794528</v>
       </c>
       <c r="AE5" t="inlineStr"/>
       <c r="AF5" t="n">
-        <v>2.760504201680661</v>
+        <v>-9.533333333333331</v>
       </c>
       <c r="AG5" t="inlineStr"/>
       <c r="AH5" t="n">
-        <v>18.45378151260504</v>
+        <v>13.33333333333333</v>
       </c>
       <c r="AI5" t="n">
-        <v>6</v>
+        <v>18.66666666666666</v>
       </c>
       <c r="AJ5" t="n">
-        <v>8.298611111111107</v>
+        <v>9.068627450980394</v>
       </c>
       <c r="AK5" t="n">
-        <v>-13</v>
+        <v>-0.6666666666666714</v>
       </c>
       <c r="AL5" t="n">
-        <v>-3.027777777777771</v>
-      </c>
-      <c r="AM5" t="inlineStr"/>
+        <v>-5.960784313725497</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>67</v>
+      </c>
       <c r="AN5" t="n">
-        <v>-31.95673076923077</v>
+        <v>-82.5625</v>
       </c>
       <c r="AO5" t="n">
-        <v>-0.5</v>
+        <v>-0.6666666666666665</v>
       </c>
       <c r="AP5" t="n">
-        <v>-1.216911764705883</v>
+        <v>-0.7287581699346406</v>
       </c>
       <c r="AQ5" t="inlineStr"/>
       <c r="AR5" t="n">
-        <v>-0.3333333333333333</v>
+        <v>0.4</v>
       </c>
       <c r="AS5" t="n">
-        <v>-8.5</v>
+        <v>-7.666666666666668</v>
       </c>
       <c r="AT5" t="n">
-        <v>-5.972222222222221</v>
-      </c>
-      <c r="AU5" t="inlineStr"/>
+        <v>-6.290849673202615</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>0.4400632825076194</v>
+      </c>
       <c r="AV5" t="n">
-        <v>3.243802242821531</v>
+        <v>3.941938222686005</v>
       </c>
       <c r="AW5" t="inlineStr"/>
       <c r="AX5" t="n">
-        <v>0.03704908465490844</v>
+        <v>0.04461149471289846</v>
       </c>
       <c r="AY5" t="n">
-        <v>0</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.2222222222222222</v>
+        <v>-0.173202614379085</v>
       </c>
       <c r="BA5" t="n">
-        <v>0.1999037893751967</v>
+        <v>0.2327300785634117</v>
       </c>
       <c r="BB5" t="n">
-        <v>-0.8669806530917867</v>
+        <v>-2.018018144407051</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.058125567847792</v>
+        <v>1170.700390144835</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.006200897867564503</v>
+        <v>2.041666666666667</v>
       </c>
       <c r="BE5" t="n">
-        <v>-8363.079872802093</v>
+        <v>26358.58585858586</v>
       </c>
       <c r="BF5" t="n">
-        <v>0.723121425899194</v>
+        <v>2.377080696452879</v>
       </c>
       <c r="BG5" t="n">
-        <v>-3405018.438351771</v>
+        <v>-1931.834615424188</v>
       </c>
       <c r="BH5" t="n">
-        <v>-0.1857638888888893</v>
+        <v>155.9027777777778</v>
       </c>
       <c r="BI5" t="n">
-        <v>-1331663.125157184</v>
+        <v>1.751404087167955</v>
       </c>
       <c r="BJ5" t="n">
-        <v>-1.754357142857174</v>
+        <v>-4.005787037037095</v>
       </c>
       <c r="BK5" t="n">
-        <v>-146.7583333333333</v>
+        <v>3397875.309811073</v>
       </c>
       <c r="BL5" t="n">
-        <v>1.479809203398034</v>
+        <v>0.2866138234193798</v>
       </c>
       <c r="BM5" t="n">
-        <v>-39450166.66666667</v>
+        <v>0.7953797231575095</v>
       </c>
       <c r="BN5" t="n">
-        <v>9585.536968798218</v>
+        <v>0.03532115090372989</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.904294395228192</v>
+        <v>-0.7562500000000014</v>
       </c>
       <c r="BP5" t="n">
-        <v>5.845918844529933</v>
+        <v>-1.206607027336673</v>
       </c>
       <c r="BQ5" t="n">
-        <v>-1.733333333333333</v>
+        <v>553691.8360935613</v>
       </c>
       <c r="BR5" t="n">
-        <v>-135.7433333333333</v>
+        <v>7046874.999999999</v>
       </c>
       <c r="BS5" t="n">
-        <v>1.386629955366068</v>
+        <v>-1.913593482937415</v>
       </c>
       <c r="BT5" t="n">
-        <v>-2.486438973696522</v>
+        <v>2.430555555555555</v>
       </c>
       <c r="BU5" t="n">
-        <v>-89471.66666666666</v>
+        <v>139.75</v>
       </c>
       <c r="BV5" t="n">
-        <v>-2.473333333333333</v>
+        <v>-1.251739697582451</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>WdE2Z2y1</t>
+          <t>l8H0Dwy3</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45592.45833333334</v>
+        <v>45606.45833333334</v>
       </c>
       <c r="C6" t="n">
         <v>101</v>
@@ -1689,10 +1703,10 @@
         <v>133</v>
       </c>
       <c r="E6" t="n">
-        <v>56</v>
+        <v>535</v>
       </c>
       <c r="F6" t="n">
-        <v>228</v>
+        <v>545</v>
       </c>
       <c r="G6" t="n">
         <v>55</v>
@@ -1714,205 +1728,209 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="M6" t="n">
-        <v>10</v>
+        <v>204</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>2.44</v>
+        <v>0.8516666666666668</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9221666666666666</v>
+        <v>0.8468382352941179</v>
       </c>
       <c r="Q6" t="n">
-        <v>4</v>
+        <v>1.25</v>
       </c>
       <c r="R6" t="n">
-        <v>1.2</v>
+        <v>1.3125</v>
       </c>
       <c r="S6" t="n">
-        <v>4.666666666666667</v>
+        <v>2.416666666666667</v>
       </c>
       <c r="T6" t="n">
-        <v>0.5888888888888886</v>
+        <v>2.298611111111111</v>
       </c>
       <c r="U6" t="n">
-        <v>14.33333333333333</v>
+        <v>-0.08333333333333215</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.2888888888888896</v>
+        <v>2.513888888888888</v>
       </c>
       <c r="W6" t="n">
-        <v>2.333333333333333</v>
+        <v>2</v>
       </c>
       <c r="X6" t="n">
-        <v>0.3999999999999997</v>
+        <v>0.6597222222222222</v>
       </c>
       <c r="Y6" t="n">
-        <v>4</v>
+        <v>1.25</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.2</v>
+        <v>0.6041666666666667</v>
       </c>
       <c r="AA6" t="n">
-        <v>16.77935299994123</v>
+        <v>21.43512223071047</v>
       </c>
       <c r="AB6" t="n">
-        <v>22.19319082107072</v>
-      </c>
-      <c r="AC6" t="inlineStr"/>
+        <v>19.61432882338791</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>937.4240847245117</v>
+      </c>
       <c r="AD6" t="n">
-        <v>944.9631595713745</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>33</v>
-      </c>
+        <v>973.9187024677365</v>
+      </c>
+      <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="n">
-        <v>-21.02083333333334</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>47</v>
-      </c>
+        <v>-4.871794871794876</v>
+      </c>
+      <c r="AG6" t="inlineStr"/>
       <c r="AH6" t="n">
-        <v>4.569444444444443</v>
+        <v>4.625641025641023</v>
       </c>
       <c r="AI6" t="n">
-        <v>-1.333333333333329</v>
+        <v>-0.25</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.1500000000000021</v>
+        <v>1.875</v>
       </c>
       <c r="AK6" t="n">
-        <v>11.33333333333333</v>
+        <v>-26.66666666666667</v>
       </c>
       <c r="AL6" t="n">
-        <v>-7.422222222222231</v>
-      </c>
-      <c r="AM6" t="inlineStr"/>
+        <v>-14.88888888888889</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>-258</v>
+      </c>
       <c r="AN6" t="n">
-        <v>-73.45535714285717</v>
+        <v>-140.7104072398189</v>
       </c>
       <c r="AO6" t="n">
-        <v>-0.666666666666667</v>
+        <v>-2.416666666666667</v>
       </c>
       <c r="AP6" t="n">
-        <v>-0.5176470588235293</v>
+        <v>-0.4722222222222221</v>
       </c>
       <c r="AQ6" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="AR6" t="n">
-        <v>-0.8</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="AS6" t="n">
-        <v>5.666666666666668</v>
+        <v>-0.5833333333333321</v>
       </c>
       <c r="AT6" t="n">
-        <v>-1.399999999999995</v>
-      </c>
-      <c r="AU6" t="inlineStr"/>
+        <v>4.652777777777779</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>10.67658212560387</v>
+      </c>
       <c r="AV6" t="n">
-        <v>2.858654364771889</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>0.02959549411162314</v>
-      </c>
+        <v>3.291987468309244</v>
+      </c>
+      <c r="AW6" t="inlineStr"/>
       <c r="AX6" t="n">
-        <v>0.003005089032790918</v>
+        <v>-0.003490671033628913</v>
       </c>
       <c r="AY6" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333331</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0.25</v>
+        <v>0.2152777777777778</v>
       </c>
       <c r="BA6" t="n">
-        <v>0.9983333333333335</v>
+        <v>-0.0007575757575755127</v>
       </c>
       <c r="BB6" t="n">
-        <v>7.597390572390566</v>
+        <v>3.953750467639367</v>
       </c>
       <c r="BC6" t="n">
-        <v>-1.441161616161615</v>
+        <v>5228.586793864572</v>
       </c>
       <c r="BD6" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="BE6" t="inlineStr"/>
+        <v>1.266666666666667</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>49486.66666666667</v>
+      </c>
       <c r="BF6" t="n">
-        <v>6.05092592592591</v>
+        <v>1.016811912179961</v>
       </c>
       <c r="BG6" t="n">
-        <v>10801694.02356902</v>
+        <v>1983.420566681816</v>
       </c>
       <c r="BH6" t="n">
-        <v>-0.1842105263157912</v>
+        <v>102.7333333333333</v>
       </c>
       <c r="BI6" t="n">
-        <v>13485427.10130304</v>
+        <v>-0.8067340067340183</v>
       </c>
       <c r="BJ6" t="n">
-        <v>-10.06140350877195</v>
+        <v>-5.857333333333344</v>
       </c>
       <c r="BK6" t="n">
-        <v>7.421052631578959</v>
+        <v>-1407973.017209129</v>
       </c>
       <c r="BL6" t="n">
-        <v>12.94471742125879</v>
+        <v>0.4803030303030305</v>
       </c>
       <c r="BM6" t="n">
-        <v>16594736.84210526</v>
-      </c>
-      <c r="BN6" t="inlineStr"/>
+        <v>-0.02655256266369577</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>0.05851158907151333</v>
+      </c>
       <c r="BO6" t="n">
-        <v>-3.329517082750129</v>
+        <v>-2.238888888888891</v>
       </c>
       <c r="BP6" t="n">
-        <v>-0.4637626262626213</v>
+        <v>-1.886762030392092</v>
       </c>
       <c r="BQ6" t="n">
-        <v>0</v>
+        <v>537905.4802804422</v>
       </c>
       <c r="BR6" t="n">
-        <v>10.89473684210526</v>
+        <v>16367333.33333333</v>
       </c>
       <c r="BS6" t="n">
-        <v>4.741318284889715</v>
+        <v>1.333531707623393</v>
       </c>
       <c r="BT6" t="n">
-        <v>7.331533487398161</v>
+        <v>1.493333333333333</v>
       </c>
       <c r="BU6" t="n">
-        <v>64277.77777777778</v>
+        <v>94.44</v>
       </c>
       <c r="BV6" t="n">
-        <v>1.631578947368421</v>
+        <v>-4.246847356795456</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>vaZNtoqR</t>
+          <t>dYK8BH5F</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45591.66666666666</v>
+        <v>45605.70833333334</v>
       </c>
       <c r="C7" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D7" t="n">
         <v>133</v>
       </c>
       <c r="E7" t="n">
-        <v>273</v>
+        <v>431</v>
       </c>
       <c r="F7" t="n">
-        <v>545</v>
+        <v>129</v>
       </c>
       <c r="G7" t="n">
         <v>55</v>
@@ -1934,203 +1952,193 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>272</v>
+        <v>35</v>
       </c>
       <c r="M7" t="n">
-        <v>204</v>
+        <v>37</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.22</v>
+        <v>-1.573333333333334</v>
       </c>
       <c r="P7" t="n">
-        <v>0.6045220588235296</v>
+        <v>-0.5611764705882354</v>
       </c>
       <c r="Q7" t="n">
         <v>-1</v>
       </c>
       <c r="R7" t="n">
-        <v>0.75</v>
+        <v>-0.4551083591331269</v>
       </c>
       <c r="S7" t="n">
-        <v>1.833333333333333</v>
+        <v>-8</v>
       </c>
       <c r="T7" t="n">
-        <v>2.541666666666667</v>
+        <v>-3.767801857585139</v>
       </c>
       <c r="U7" t="n">
-        <v>3.166666666666668</v>
+        <v>-15.33333333333333</v>
       </c>
       <c r="V7" t="n">
-        <v>4.027777777777779</v>
+        <v>-4.659442724458206</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.6666666666666667</v>
+        <v>-1</v>
       </c>
       <c r="X7" t="n">
-        <v>0.2083333333333334</v>
+        <v>-1.987616099071208</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.5833333333333333</v>
+        <v>-1.662538699690402</v>
       </c>
       <c r="AA7" t="n">
-        <v>21.36915584415584</v>
+        <v>27.57582417582417</v>
       </c>
       <c r="AB7" t="n">
-        <v>19.90822250376043</v>
+        <v>21.63191196917977</v>
       </c>
       <c r="AC7" t="n">
-        <v>968.5623018561785</v>
+        <v>1442.054681959355</v>
       </c>
       <c r="AD7" t="n">
-        <v>993.2278683172611</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>-69</v>
-      </c>
+        <v>1124.808641832703</v>
+      </c>
+      <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="n">
-        <v>-3.295833333333334</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>-32</v>
-      </c>
+        <v>-21.52678571428572</v>
+      </c>
+      <c r="AG7" t="inlineStr"/>
       <c r="AH7" t="n">
-        <v>5.458333333333336</v>
+        <v>3.044642857142861</v>
       </c>
       <c r="AI7" t="n">
-        <v>10</v>
+        <v>-6.666666666666668</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.416666666666664</v>
+        <v>-3.009287925696595</v>
       </c>
       <c r="AK7" t="n">
-        <v>-12.33333333333333</v>
+        <v>-52.66666666666667</v>
       </c>
       <c r="AL7" t="n">
-        <v>-16.47222222222223</v>
+        <v>-32.95356037151703</v>
       </c>
       <c r="AM7" t="n">
-        <v>-126.5</v>
+        <v>-776</v>
       </c>
       <c r="AN7" t="n">
-        <v>-166.7436974789916</v>
+        <v>-369.1785714285714</v>
       </c>
       <c r="AO7" t="n">
-        <v>-2.220446049250313e-16</v>
+        <v>-2.333333333333334</v>
       </c>
       <c r="AP7" t="n">
-        <v>-0.06349206349206327</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>2</v>
-      </c>
+        <v>-1.0625</v>
+      </c>
+      <c r="AQ7" t="inlineStr"/>
       <c r="AR7" t="n">
-        <v>1.333333333333333</v>
+        <v>-0.8</v>
       </c>
       <c r="AS7" t="n">
-        <v>2.166666666666664</v>
+        <v>-7.999999999999998</v>
       </c>
       <c r="AT7" t="n">
-        <v>5.590277777777779</v>
+        <v>-0.01238390092879271</v>
       </c>
       <c r="AU7" t="n">
-        <v>13.69398809523809</v>
+        <v>62.96041666666666</v>
       </c>
       <c r="AV7" t="n">
-        <v>4.666588369374105</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>-0.05627452561414825</v>
-      </c>
+        <v>12.15054799346603</v>
+      </c>
+      <c r="AW7" t="inlineStr"/>
       <c r="AX7" t="n">
-        <v>0.002448867104326222</v>
+        <v>0.05947993307211154</v>
       </c>
       <c r="AY7" t="n">
-        <v>0</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.1458333333333333</v>
+        <v>-0.3095975232198143</v>
       </c>
       <c r="BA7" t="n">
-        <v>0.1513496402356398</v>
+        <v>-1.074074074074074</v>
       </c>
       <c r="BB7" t="n">
-        <v>-1.126245417134299</v>
+        <v>-1.495576981940587</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.826090160867935</v>
+        <v>-80511.09168609169</v>
       </c>
       <c r="BD7" t="n">
-        <v>-0.2478473625140289</v>
+        <v>0.0370370370370372</v>
       </c>
       <c r="BE7" t="n">
-        <v>3126.611111111109</v>
+        <v>-234703.7037037037</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.193087916199019</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>29353.35765057988</v>
-      </c>
+        <v>-13.95376384709822</v>
+      </c>
+      <c r="BG7" t="inlineStr"/>
       <c r="BH7" t="n">
-        <v>-1.539238095238098</v>
+        <v>-31.44444444444446</v>
       </c>
       <c r="BI7" t="n">
-        <v>-723774.2659041015</v>
+        <v>-14.69792623201715</v>
       </c>
       <c r="BJ7" t="n">
-        <v>-13.35847619047621</v>
+        <v>-8.270987654320919</v>
       </c>
       <c r="BK7" t="n">
-        <v>137.96</v>
+        <v>-54010547.13804714</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.1912996827964548</v>
+        <v>4.542921640648917</v>
       </c>
       <c r="BM7" t="n">
-        <v>13984000</v>
+        <v>-12.02681359044995</v>
       </c>
       <c r="BN7" t="n">
-        <v>350.3859836239717</v>
+        <v>-1.011538461538461</v>
       </c>
       <c r="BO7" t="n">
-        <v>-1.081336341004544</v>
+        <v>-3.243209876543208</v>
       </c>
       <c r="BP7" t="n">
-        <v>-0.9999064721286572</v>
+        <v>-14.80001865260817</v>
       </c>
       <c r="BQ7" t="n">
-        <v>1.8</v>
+        <v>-46191217.20002314</v>
       </c>
       <c r="BR7" t="n">
-        <v>133.52</v>
+        <v>-106985185.1851852</v>
       </c>
       <c r="BS7" t="n">
-        <v>0.7267449369852059</v>
+        <v>-2.166240768206876</v>
       </c>
       <c r="BT7" t="n">
-        <v>-1.755590788911988</v>
+        <v>-4</v>
       </c>
       <c r="BU7" t="n">
-        <v>60920</v>
+        <v>-45.25925925925927</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.8399999999999999</v>
+        <v>1.310001280038044</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hQspntL6</t>
+          <t>bJl87mmp</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45591.58333333334</v>
+        <v>45605.625</v>
       </c>
       <c r="C8" t="n">
         <v>101</v>
@@ -2139,10 +2147,10 @@
         <v>133</v>
       </c>
       <c r="E8" t="n">
-        <v>826</v>
+        <v>273</v>
       </c>
       <c r="F8" t="n">
-        <v>133</v>
+        <v>599</v>
       </c>
       <c r="G8" t="n">
         <v>55</v>
@@ -2164,207 +2172,207 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>128</v>
+        <v>97</v>
       </c>
       <c r="M8" t="n">
-        <v>211</v>
+        <v>141</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>2.495</v>
+        <v>0.9</v>
       </c>
       <c r="P8" t="n">
-        <v>0.3574166666666667</v>
+        <v>0.7974999999999997</v>
       </c>
       <c r="Q8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R8" t="n">
-        <v>0.3529411764705883</v>
+        <v>1.455882352941177</v>
       </c>
       <c r="S8" t="n">
-        <v>3.333333333333333</v>
+        <v>0.9999999999999996</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.125</v>
       </c>
       <c r="U8" t="n">
-        <v>13</v>
+        <v>4.333333333333332</v>
       </c>
       <c r="V8" t="n">
-        <v>1.856617647058824</v>
+        <v>6.125</v>
       </c>
       <c r="W8" t="n">
-        <v>3.5</v>
+        <v>0.6666666666666669</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.05882352941176472</v>
+        <v>0.3639705882352942</v>
       </c>
       <c r="Y8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.1985294117647061</v>
+        <v>0.375</v>
       </c>
       <c r="AA8" t="n">
-        <v>14.49107744107744</v>
+        <v>17.78020400079224</v>
       </c>
       <c r="AB8" t="n">
-        <v>19.34590718073206</v>
-      </c>
-      <c r="AC8" t="inlineStr"/>
+        <v>16.96970434595289</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>828.0477312770033</v>
+      </c>
       <c r="AD8" t="n">
-        <v>868.0773877594212</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>43</v>
-      </c>
+        <v>833.5173730538138</v>
+      </c>
+      <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="n">
-        <v>3.392857142857153</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>44</v>
-      </c>
+        <v>47.52197802197801</v>
+      </c>
+      <c r="AG8" t="inlineStr"/>
       <c r="AH8" t="n">
-        <v>10.59821428571428</v>
+        <v>29.12087912087912</v>
       </c>
       <c r="AI8" t="n">
-        <v>4.999999999999996</v>
+        <v>-4.333333333333336</v>
       </c>
       <c r="AJ8" t="n">
-        <v>5.38602941176471</v>
+        <v>12.00735294117647</v>
       </c>
       <c r="AK8" t="n">
-        <v>-13</v>
+        <v>19.33333333333333</v>
       </c>
       <c r="AL8" t="n">
-        <v>-5.992647058823536</v>
-      </c>
-      <c r="AM8" t="inlineStr"/>
+        <v>18.875</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>100</v>
+      </c>
       <c r="AN8" t="n">
-        <v>-13.39999999999998</v>
+        <v>160.7637362637362</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.166666666666667</v>
+        <v>-1.166666666666667</v>
       </c>
       <c r="AP8" t="n">
-        <v>-0.04411764705882382</v>
+        <v>-1.016666666666667</v>
       </c>
       <c r="AQ8" t="inlineStr"/>
       <c r="AR8" t="n">
-        <v>-0.1428571428571429</v>
+        <v>2.5</v>
       </c>
       <c r="AS8" t="n">
-        <v>1.333333333333334</v>
+        <v>3.333333333333329</v>
       </c>
       <c r="AT8" t="n">
-        <v>-6.867647058823529</v>
-      </c>
-      <c r="AU8" t="inlineStr"/>
+        <v>-6.518382352941178</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>-3.267153679653685</v>
+      </c>
       <c r="AV8" t="n">
-        <v>1.109530542816877</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>-0.002347620952272117</v>
-      </c>
+        <v>-1.946201504871668</v>
+      </c>
+      <c r="AW8" t="inlineStr"/>
       <c r="AX8" t="n">
-        <v>0.02343697858948881</v>
+        <v>0.03706879697187559</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.5</v>
+        <v>-5.551115123125783e-17</v>
       </c>
       <c r="AZ8" t="n">
-        <v>-0.1213235294117647</v>
+        <v>0.3051470588235294</v>
       </c>
       <c r="BA8" t="n">
-        <v>-0.1628832088390915</v>
+        <v>-0.2932698412698413</v>
       </c>
       <c r="BB8" t="n">
-        <v>2.67050130939019</v>
+        <v>-2.335912698412727</v>
       </c>
       <c r="BC8" t="n">
-        <v>-0.4599139543583988</v>
+        <v>6576.76543209876</v>
       </c>
       <c r="BD8" t="n">
-        <v>-0.05199214365881044</v>
+        <v>0.4249999999999998</v>
       </c>
       <c r="BE8" t="n">
-        <v>1163.259913954358</v>
+        <v>11545</v>
       </c>
       <c r="BF8" t="n">
-        <v>0.8398241676019467</v>
+        <v>0.6447941741706131</v>
       </c>
       <c r="BG8" t="n">
-        <v>2954255.518144407</v>
+        <v>6175.373958611945</v>
       </c>
       <c r="BH8" t="n">
-        <v>-5.081944444444446</v>
+        <v>34.87666666666667</v>
       </c>
       <c r="BI8" t="n">
-        <v>191976.6587190428</v>
+        <v>2.530174603174601</v>
       </c>
       <c r="BJ8" t="n">
-        <v>-3.924537037037055</v>
+        <v>-4.541809523809519</v>
       </c>
       <c r="BK8" t="n">
-        <v>20.27777777777777</v>
+        <v>6123503.373015874</v>
       </c>
       <c r="BL8" t="n">
-        <v>-0.7788540416166541</v>
+        <v>0.4535158730158741</v>
       </c>
       <c r="BM8" t="n">
-        <v>-908333.333333334</v>
+        <v>3.280261904761915</v>
       </c>
       <c r="BN8" t="n">
-        <v>-1889.497743541862</v>
+        <v>0.1936713172411113</v>
       </c>
       <c r="BO8" t="n">
-        <v>4.248272642390276</v>
+        <v>2.407984126984125</v>
       </c>
       <c r="BP8" t="n">
-        <v>3.338926300037372</v>
+        <v>4.013539816400225</v>
       </c>
       <c r="BQ8" t="n">
-        <v>0.2083333333333333</v>
+        <v>2172383.010915477</v>
       </c>
       <c r="BR8" t="n">
-        <v>7.916666666666671</v>
+        <v>3698583.333333334</v>
       </c>
       <c r="BS8" t="n">
-        <v>-1.41635237428304</v>
+        <v>-4.18291356812523</v>
       </c>
       <c r="BT8" t="n">
-        <v>1.339588335334142</v>
+        <v>-0.03500000000000014</v>
       </c>
       <c r="BU8" t="n">
-        <v>-7055.555555555555</v>
+        <v>35.77000000000001</v>
       </c>
       <c r="BV8" t="n">
-        <v>0.01388888888888906</v>
+        <v>2.299371585698815</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>p0vxl2jf</t>
+          <t>figxD9PM</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45591.5</v>
+        <v>45605.54166666666</v>
       </c>
       <c r="C9" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D9" t="n">
         <v>133</v>
       </c>
       <c r="E9" t="n">
-        <v>431</v>
+        <v>736</v>
       </c>
       <c r="F9" t="n">
-        <v>362</v>
+        <v>33</v>
       </c>
       <c r="G9" t="n">
         <v>55</v>
@@ -2386,195 +2394,201 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>152</v>
+        <v>312</v>
       </c>
       <c r="M9" t="n">
-        <v>83</v>
+        <v>60</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>1.613333333333333</v>
+        <v>0.5100000000000001</v>
       </c>
       <c r="P9" t="n">
-        <v>0.229607843137255</v>
+        <v>0.1464705882352939</v>
       </c>
       <c r="Q9" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="R9" t="n">
-        <v>0.3157894736842106</v>
+        <v>0.5294117647058825</v>
       </c>
       <c r="S9" t="n">
-        <v>2.666666666666667</v>
+        <v>0.916666666666667</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.395424836601307</v>
+        <v>0.9967320261437913</v>
       </c>
       <c r="U9" t="n">
-        <v>8.333333333333336</v>
+        <v>2.75</v>
       </c>
       <c r="V9" t="n">
-        <v>-2.176470588235293</v>
+        <v>3.153594771241831</v>
       </c>
       <c r="W9" t="n">
-        <v>2.333333333333333</v>
+        <v>-0.25</v>
       </c>
       <c r="X9" t="n">
-        <v>0.4334365325077401</v>
+        <v>-0.5392156862745099</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.021671826625387</v>
+        <v>-0.7941176470588236</v>
       </c>
       <c r="AA9" t="n">
-        <v>16.23349567099567</v>
+        <v>17.5893256661639</v>
       </c>
       <c r="AB9" t="n">
-        <v>20.7141176225735</v>
-      </c>
-      <c r="AC9" t="inlineStr"/>
+        <v>18.81615630556807</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>960.5680747456265</v>
+      </c>
       <c r="AD9" t="n">
-        <v>883.0782510807605</v>
+        <v>944.0294613736537</v>
       </c>
       <c r="AE9" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AF9" t="n">
-        <v>16.76666666666667</v>
+        <v>-13.91964285714286</v>
       </c>
       <c r="AG9" t="n">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="AH9" t="n">
-        <v>7.508333333333333</v>
+        <v>6.3125</v>
       </c>
       <c r="AI9" t="n">
-        <v>18.33333333333333</v>
+        <v>5.083333333333336</v>
       </c>
       <c r="AJ9" t="n">
-        <v>2.690402476780184</v>
+        <v>1.019607843137251</v>
       </c>
       <c r="AK9" t="n">
-        <v>16</v>
+        <v>-17.83333333333333</v>
       </c>
       <c r="AL9" t="n">
-        <v>-1.189542483660119</v>
-      </c>
-      <c r="AM9" t="inlineStr"/>
+        <v>-13.50326797385621</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>-151</v>
+      </c>
       <c r="AN9" t="n">
-        <v>-48.89047619047619</v>
+        <v>-119.375</v>
       </c>
       <c r="AO9" t="n">
-        <v>-3.333333333333333</v>
+        <v>-0.4166666666666665</v>
       </c>
       <c r="AP9" t="n">
-        <v>-1.090277777777778</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>0</v>
-      </c>
+        <v>-0.7058823529411766</v>
+      </c>
+      <c r="AQ9" t="inlineStr"/>
       <c r="AR9" t="n">
-        <v>-0.5</v>
+        <v>-1.333333333333333</v>
       </c>
       <c r="AS9" t="n">
-        <v>-8.000000000000002</v>
+        <v>1.083333333333332</v>
       </c>
       <c r="AT9" t="n">
-        <v>-5.204334365325082</v>
-      </c>
-      <c r="AU9" t="inlineStr"/>
+        <v>-0.1895424836601265</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>13.34281458752283</v>
+      </c>
       <c r="AV9" t="n">
-        <v>1.665627743712083</v>
+        <v>4.387524286864782</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.04286926994906622</v>
+        <v>0.04841824841824842</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.006595534358273113</v>
+        <v>0.02664562876142698</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.6666666666666666</v>
+        <v>-0.08333333333333331</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.1176470588235294</v>
+        <v>-0.2777777777777778</v>
       </c>
       <c r="BA9" t="n">
-        <v>0</v>
+        <v>-0.1473958333333334</v>
       </c>
       <c r="BB9" t="n">
-        <v>-1.605070592286509</v>
+        <v>3.575421626984166</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.473204344582182</v>
+        <v>-26318.57638888889</v>
       </c>
       <c r="BD9" t="n">
-        <v>0</v>
+        <v>-2.083333333333333</v>
       </c>
       <c r="BE9" t="n">
-        <v>-1385.342001748251</v>
+        <v>-124083.3333333333</v>
       </c>
       <c r="BF9" t="n">
-        <v>-1.199942607897157</v>
+        <v>-4.499843166701723</v>
       </c>
       <c r="BG9" t="n">
-        <v>-568637.0451675842</v>
+        <v>-4651.924001924001</v>
       </c>
       <c r="BH9" t="n">
-        <v>-4.166666666666668</v>
+        <v>-186.7083333333333</v>
       </c>
       <c r="BI9" t="n">
-        <v>-644901.5049847849</v>
+        <v>-2.936235119047637</v>
       </c>
       <c r="BJ9" t="n">
-        <v>3.25</v>
+        <v>4.813392857142844</v>
       </c>
       <c r="BK9" t="n">
-        <v>152</v>
+        <v>-10059221.23015873</v>
       </c>
       <c r="BL9" t="n">
-        <v>-3.007113506814832</v>
+        <v>-0.0387400793650805</v>
       </c>
       <c r="BM9" t="n">
-        <v>1225000</v>
-      </c>
-      <c r="BN9" t="inlineStr"/>
+        <v>-3.813640873015856</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>0.1664014713356818</v>
+      </c>
       <c r="BO9" t="n">
-        <v>0.7216312624451007</v>
+        <v>2.463541666666664</v>
       </c>
       <c r="BP9" t="n">
-        <v>1.228020976813582</v>
+        <v>0.007992091972354842</v>
       </c>
       <c r="BQ9" t="n">
-        <v>2</v>
+        <v>-5922514.068670731</v>
       </c>
       <c r="BR9" t="n">
-        <v>117</v>
+        <v>-59895416.66666667</v>
       </c>
       <c r="BS9" t="n">
-        <v>-0.4261393724629023</v>
+        <v>3.798224115066205</v>
       </c>
       <c r="BT9" t="n">
-        <v>-2.106029253690011</v>
+        <v>-2.041666666666667</v>
       </c>
       <c r="BU9" t="n">
-        <v>-21000</v>
+        <v>-169.7083333333333</v>
       </c>
       <c r="BV9" t="n">
-        <v>2</v>
+        <v>3.27031911619083</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>lYpTkOLs</t>
+          <t>Gp6AbAAT</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45590.65625</v>
+        <v>45604.69791666666</v>
       </c>
       <c r="C10" t="n">
         <v>101</v>
@@ -2583,10 +2597,10 @@
         <v>133</v>
       </c>
       <c r="E10" t="n">
-        <v>573</v>
+        <v>448</v>
       </c>
       <c r="F10" t="n">
-        <v>122</v>
+        <v>228</v>
       </c>
       <c r="G10" t="n">
         <v>55</v>
@@ -2608,191 +2622,2177 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>9</v>
+        <v>313</v>
       </c>
       <c r="M10" t="n">
-        <v>138</v>
+        <v>109</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>1.426666666666667</v>
+        <v>0.0166666666666665</v>
       </c>
       <c r="P10" t="n">
-        <v>1.359522058823529</v>
+        <v>1.118263888888889</v>
       </c>
       <c r="Q10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.895833333333333</v>
+        <v>1.575</v>
       </c>
       <c r="S10" t="n">
-        <v>5.333333333333334</v>
+        <v>4.440892098500626e-16</v>
       </c>
       <c r="T10" t="n">
-        <v>3.770833333333333</v>
+        <v>2.590277777777778</v>
       </c>
       <c r="U10" t="n">
-        <v>5.666666666666666</v>
+        <v>-3.333333333333332</v>
       </c>
       <c r="V10" t="n">
-        <v>7.770833333333332</v>
+        <v>2.166666666666666</v>
       </c>
       <c r="W10" t="n">
-        <v>2.666666666666667</v>
+        <v>0.6666666666666665</v>
       </c>
       <c r="X10" t="n">
-        <v>1.291666666666667</v>
+        <v>0.6875</v>
       </c>
       <c r="Y10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.541666666666667</v>
+        <v>1.275</v>
       </c>
       <c r="AA10" t="n">
-        <v>15.19888167388167</v>
+        <v>22.15613553113553</v>
       </c>
       <c r="AB10" t="n">
-        <v>17.55297816242734</v>
+        <v>19.87436947697364</v>
       </c>
       <c r="AC10" t="n">
-        <v>863.0573179033356</v>
+        <v>903.0457789515091</v>
       </c>
       <c r="AD10" t="n">
-        <v>849.1877226677626</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>32</v>
-      </c>
+        <v>922.9898015267552</v>
+      </c>
+      <c r="AE10" t="inlineStr"/>
       <c r="AF10" t="n">
-        <v>25.05357142857142</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>30</v>
-      </c>
+        <v>-8.85238095238094</v>
+      </c>
+      <c r="AG10" t="inlineStr"/>
       <c r="AH10" t="n">
-        <v>16.01785714285714</v>
+        <v>9.176190476190477</v>
       </c>
       <c r="AI10" t="n">
-        <v>6.666666666666664</v>
+        <v>6.333333333333336</v>
       </c>
       <c r="AJ10" t="n">
-        <v>5.333333333333336</v>
+        <v>4.700000000000001</v>
       </c>
       <c r="AK10" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AL10" t="n">
-        <v>7.513888888888886</v>
+        <v>0.05555555555555713</v>
       </c>
       <c r="AM10" t="n">
-        <v>90</v>
+        <v>-14.5</v>
       </c>
       <c r="AN10" t="n">
-        <v>66.98571428571432</v>
+        <v>-61.14285714285717</v>
       </c>
       <c r="AO10" t="n">
-        <v>-1.333333333333333</v>
+        <v>1.666666666666667</v>
       </c>
       <c r="AP10" t="n">
-        <v>-0.145833333333333</v>
+        <v>-0.8419117647058825</v>
       </c>
       <c r="AQ10" t="inlineStr"/>
       <c r="AR10" t="n">
-        <v>-0.9333333333333333</v>
+        <v>-0.875</v>
       </c>
       <c r="AS10" t="n">
-        <v>-1.333333333333334</v>
+        <v>-0.3333333333333321</v>
       </c>
       <c r="AT10" t="n">
-        <v>-1.222222222222221</v>
+        <v>3.949999999999999</v>
       </c>
       <c r="AU10" t="n">
-        <v>-25.84559884559884</v>
+        <v>-2.34494047619048</v>
       </c>
       <c r="AV10" t="n">
-        <v>-2.672925535896542</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>-0.08260636182134844</v>
-      </c>
+        <v>-0.3563265683653878</v>
+      </c>
+      <c r="AW10" t="inlineStr"/>
       <c r="AX10" t="n">
-        <v>-0.01594106336285508</v>
+        <v>-0.01620820239068646</v>
       </c>
       <c r="AY10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>0.175</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>0.1805555555555556</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>1.145731508634725</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>33086.39971139971</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>1.302222222222222</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>88440</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>8.365281902145952</v>
+      </c>
+      <c r="BG10" t="inlineStr"/>
+      <c r="BH10" t="n">
+        <v>107.3377777777778</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>9.867658439231022</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>-1.756666666666661</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>14135737.15990551</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>-0.814139377647443</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>8.695116487455181</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>0.1812987012987013</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>0.5631111111111125</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>9.813664569673335</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>9164769.304363601</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>34458666.66666666</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>1.406250116030861</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>2.462222222222223</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>105.8222222222223</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>0.6499594525033174</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>UTsToXQN</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45599.69791666666</v>
+      </c>
+      <c r="C11" t="n">
+        <v>102</v>
+      </c>
+      <c r="D11" t="n">
+        <v>133</v>
+      </c>
+      <c r="E11" t="n">
+        <v>858</v>
+      </c>
+      <c r="F11" t="n">
+        <v>303</v>
+      </c>
+      <c r="G11" t="n">
+        <v>55</v>
+      </c>
+      <c r="H11" t="n">
+        <v>551</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>312</v>
+      </c>
+      <c r="M11" t="n">
+        <v>37</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.8733333333333334</v>
+      </c>
+      <c r="P11" t="n">
+        <v>-0.1976388888888887</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.02960526315789469</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0.9583333333333339</v>
+      </c>
+      <c r="U11" t="n">
+        <v>8.333333333333332</v>
+      </c>
+      <c r="V11" t="n">
+        <v>-0.02777777777777857</v>
+      </c>
+      <c r="W11" t="n">
+        <v>-2</v>
+      </c>
+      <c r="X11" t="n">
+        <v>-1.463815789473684</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>-2</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>-1.6875</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>16.94552438302438</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>19.81343443096458</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1085.583999518684</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1002.848719162645</v>
+      </c>
+      <c r="AE11" t="inlineStr"/>
+      <c r="AF11" t="n">
+        <v>-19.65714285714286</v>
+      </c>
+      <c r="AG11" t="inlineStr"/>
+      <c r="AH11" t="n">
+        <v>-6.209523809523802</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>3.999999999999993</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>1.098684210526315</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>-8.666666666666657</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>-20.73611111111111</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>-404.5</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>-213.1047619047619</v>
+      </c>
+      <c r="AO11" t="n">
         <v>1</v>
       </c>
-      <c r="AZ10" t="n">
-        <v>0.4097222222222222</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>0.265354988149106</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>7.442762974573299</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>0.2269091779867658</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>0.469278996865204</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>24872.94142404437</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>8.808568878439559</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>11427488.77786485</v>
-      </c>
-      <c r="BH10" t="n">
-        <v>-3.6421568627451</v>
-      </c>
-      <c r="BI10" t="n">
-        <v>8583036.511756951</v>
-      </c>
-      <c r="BJ10" t="n">
-        <v>4.191176470588232</v>
-      </c>
-      <c r="BK10" t="n">
-        <v>-57.88235294117646</v>
-      </c>
-      <c r="BL10" t="n">
-        <v>6.716437662434387</v>
-      </c>
-      <c r="BM10" t="n">
-        <v>-2039705.882352941</v>
-      </c>
-      <c r="BN10" t="n">
-        <v>17619.72789115647</v>
-      </c>
-      <c r="BO10" t="n">
-        <v>1.028362203830881</v>
-      </c>
-      <c r="BP10" t="n">
-        <v>-4.613088209682985</v>
-      </c>
-      <c r="BQ10" t="n">
-        <v>-0.8235294117647058</v>
-      </c>
-      <c r="BR10" t="n">
-        <v>-51.35294117647059</v>
-      </c>
-      <c r="BS10" t="n">
-        <v>-1.997684479899821</v>
-      </c>
-      <c r="BT10" t="n">
-        <v>7.406581304736633</v>
-      </c>
-      <c r="BU10" t="n">
-        <v>294.1176470588234</v>
-      </c>
-      <c r="BV10" t="n">
-        <v>-0.8235294117647058</v>
+      <c r="AP11" t="n">
+        <v>0.5441176470588234</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>12</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>3.60526315789474</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>-2.100754411755156</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>2.606813562749183</v>
+      </c>
+      <c r="AW11" t="inlineStr"/>
+      <c r="AX11" t="n">
+        <v>0.04008347344833654</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>-0.03947368421052633</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>0.2607142857142857</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>0.385912698412767</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>-14974.45987654321</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>-1.705</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>-38065</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>-4.522005615157809</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>-11660.07215007215</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>-133.4766666666667</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>-3.705257936507934</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>-5.443333333333356</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>-9260949.900793649</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>0.1443452380952372</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>-3.582539682539689</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>0.02969827274175096</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>0.4841111111111083</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>-4.770076035076031</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>-5823011.6535035</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>-22906583.33333334</v>
+      </c>
+      <c r="BS11" t="n">
+        <v>-0.2424715019280654</v>
+      </c>
+      <c r="BT11" t="n">
+        <v>-2.365</v>
+      </c>
+      <c r="BU11" t="n">
+        <v>-116.85</v>
+      </c>
+      <c r="BV11" t="n">
+        <v>0.7924710313840713</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>Y1lKmgdB</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45599.54166666666</v>
+      </c>
+      <c r="C12" t="n">
+        <v>101</v>
+      </c>
+      <c r="D12" t="n">
+        <v>133</v>
+      </c>
+      <c r="E12" t="n">
+        <v>194</v>
+      </c>
+      <c r="F12" t="n">
+        <v>157</v>
+      </c>
+      <c r="G12" t="n">
+        <v>55</v>
+      </c>
+      <c r="H12" t="n">
+        <v>551</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>249</v>
+      </c>
+      <c r="M12" t="n">
+        <v>127</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>-1.126666666666666</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0.9549166666666671</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.411764705882353</v>
+      </c>
+      <c r="S12" t="n">
+        <v>-4.166666666666666</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U12" t="n">
+        <v>-3.666666666666666</v>
+      </c>
+      <c r="V12" t="n">
+        <v>8</v>
+      </c>
+      <c r="W12" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-0.5294117647058825</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>21.23761423761424</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>17.91499910531935</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>922.0529513128304</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>866.2312035376042</v>
+      </c>
+      <c r="AE12" t="inlineStr"/>
+      <c r="AF12" t="n">
+        <v>15.42857142857144</v>
+      </c>
+      <c r="AG12" t="inlineStr"/>
+      <c r="AH12" t="n">
+        <v>31</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>2.823529411764703</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>-14.66666666666667</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>2.625</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>-197</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>-19.76923076923077</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>-0.4375</v>
+      </c>
+      <c r="AQ12" t="inlineStr"/>
+      <c r="AR12" t="n">
+        <v>-1.666666666666667</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>4.999999999999998</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>2.823529411764699</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>-4.217684087249303</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>-0.4674721059058093</v>
+      </c>
+      <c r="AW12" t="inlineStr"/>
+      <c r="AX12" t="n">
+        <v>0.02013651507394308</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>-0.6666666666666667</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>-0.2941176470588235</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>-0.4097222222222221</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>6.742916666666616</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>-11484.29232804233</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>-1.718137254901961</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>-34930.48128342246</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>-4.192050548916285</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>-6538.369855252973</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>-133.4093137254902</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>-3.400624999999991</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>5.999795751634025</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>-5188310.763888888</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>-2.834722222222226</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>-6.84986111111111</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>-0.1982043597428214</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>-0.7543709150326769</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>-2.932686251703331</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>-1800823.912892767</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>-7323835.784313725</v>
+      </c>
+      <c r="BS12" t="n">
+        <v>1.361228729368662</v>
+      </c>
+      <c r="BT12" t="n">
+        <v>-2.384803921568627</v>
+      </c>
+      <c r="BU12" t="n">
+        <v>-124.2303921568627</v>
+      </c>
+      <c r="BV12" t="n">
+        <v>1.132436549097587</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>EuWhpKkJ</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45599.54166666666</v>
+      </c>
+      <c r="C13" t="n">
+        <v>102</v>
+      </c>
+      <c r="D13" t="n">
+        <v>133</v>
+      </c>
+      <c r="E13" t="n">
+        <v>342</v>
+      </c>
+      <c r="F13" t="n">
+        <v>399</v>
+      </c>
+      <c r="G13" t="n">
+        <v>55</v>
+      </c>
+      <c r="H13" t="n">
+        <v>551</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>165</v>
+      </c>
+      <c r="M13" t="n">
+        <v>166</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1.883333333333333</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0.9348366013071896</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.235294117647059</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.166666666666667</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.764705882352941</v>
+      </c>
+      <c r="U13" t="n">
+        <v>7.666666666666666</v>
+      </c>
+      <c r="V13" t="n">
+        <v>4.058823529411766</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.102941176470588</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>2.117647058823529</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>19.04786324786325</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>18.04814810282205</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>872.0664825060937</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>873.6203422637333</v>
+      </c>
+      <c r="AE13" t="inlineStr"/>
+      <c r="AF13" t="n">
+        <v>20.89411764705883</v>
+      </c>
+      <c r="AG13" t="inlineStr"/>
+      <c r="AH13" t="n">
+        <v>16.01568627450981</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>-7.5</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>4.494117647058827</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>-5.333333333333329</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>9.164086687306508</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>-104</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>89.375</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0.3333333333333335</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>-0.929824561403509</v>
+      </c>
+      <c r="AQ13" t="inlineStr"/>
+      <c r="AR13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>-1.166666666666668</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>-3.964705882352945</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>12.03655788655789</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>-0.01481299233423528</v>
+      </c>
+      <c r="AW13" t="inlineStr"/>
+      <c r="AX13" t="n">
+        <v>-0.02067489693449977</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>0.3441176470588235</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>-0.469278996865204</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>-0.5047266322850703</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>-25628.32261692556</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>1.384920634920635</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>-21107.14285714286</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>-8.078902627825499</v>
+      </c>
+      <c r="BG13" t="inlineStr"/>
+      <c r="BH13" t="n">
+        <v>92.93650793650794</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>-10.06083808047099</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>2.776190476190465</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>-11538066.21554814</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>2.526119088549567</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>-6.813546477005858</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>-0.265354988149106</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>1.916269841269841</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>-7.35258713403708</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>-8725156.05813271</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>-9527380.952380951</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>-0.846608401536173</v>
+      </c>
+      <c r="BT13" t="n">
+        <v>1.242063492063492</v>
+      </c>
+      <c r="BU13" t="n">
+        <v>81.24206349206348</v>
+      </c>
+      <c r="BV13" t="n">
+        <v>0.8239266777063463</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>4Md3iycn</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45599.45833333334</v>
+      </c>
+      <c r="C14" t="n">
+        <v>101</v>
+      </c>
+      <c r="D14" t="n">
+        <v>133</v>
+      </c>
+      <c r="E14" t="n">
+        <v>341</v>
+      </c>
+      <c r="F14" t="n">
+        <v>579</v>
+      </c>
+      <c r="G14" t="n">
+        <v>55</v>
+      </c>
+      <c r="H14" t="n">
+        <v>551</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>76</v>
+      </c>
+      <c r="M14" t="n">
+        <v>7</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.8166666666666665</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0.868125</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>2</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.235294117647059</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1.647058823529412</v>
+      </c>
+      <c r="U14" t="n">
+        <v>7.000000000000002</v>
+      </c>
+      <c r="V14" t="n">
+        <v>2.863970588235293</v>
+      </c>
+      <c r="W14" t="n">
+        <v>-0.3333333333333335</v>
+      </c>
+      <c r="X14" t="n">
+        <v>-0.1176470588235294</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-0.3529411764705883</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>16.68835978835979</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>18.71150218923322</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>866.0748082913971</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>867.2883567094977</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>30</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>7.24761904761904</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>8</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>18.0857142857143</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>7.666666666666668</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>3.117647058823529</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>-0.6666666666666714</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>0.919117647058826</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>15.28571428571428</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>-1.333333333333333</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>-0.6213235294117649</v>
+      </c>
+      <c r="AQ14" t="inlineStr"/>
+      <c r="AR14" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>-1.77635683940025e-15</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>0.647058823529413</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>-21.15109364319891</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>-4.539079073050594</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>-0.02230201171377642</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>0.02130051461440481</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>-1.387778780781446e-17</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>-0.125</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>0.6597222222222285</v>
+      </c>
+      <c r="BC14" t="inlineStr"/>
+      <c r="BD14" t="n">
+        <v>0.8568840579710144</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>10968.25396825397</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>1.704495464852599</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>-3009.788359788359</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>66.81159420289856</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>-0.1218055555555679</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>2.025664251207729</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>-2507961.805555555</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>-2.999999999999996</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>-4.132777777777775</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>1.862500000000001</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>-1.609450113378685</v>
+      </c>
+      <c r="BQ14" t="n">
+        <v>-35388.18027210888</v>
+      </c>
+      <c r="BR14" t="n">
+        <v>6567753.623188405</v>
+      </c>
+      <c r="BS14" t="n">
+        <v>-5.225198412698433</v>
+      </c>
+      <c r="BT14" t="n">
+        <v>0.7735507246376809</v>
+      </c>
+      <c r="BU14" t="n">
+        <v>62.77173913043478</v>
+      </c>
+      <c r="BV14" t="n">
+        <v>-1.817687074829934</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>vuBo4Eth</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45598.70833333334</v>
+      </c>
+      <c r="C15" t="n">
+        <v>102</v>
+      </c>
+      <c r="D15" t="n">
+        <v>133</v>
+      </c>
+      <c r="E15" t="n">
+        <v>528</v>
+      </c>
+      <c r="F15" t="n">
+        <v>516</v>
+      </c>
+      <c r="G15" t="n">
+        <v>55</v>
+      </c>
+      <c r="H15" t="n">
+        <v>551</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>35</v>
+      </c>
+      <c r="M15" t="n">
+        <v>141</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.016666666666667</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0.4980718954248367</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.105263157894737</v>
+      </c>
+      <c r="S15" t="n">
+        <v>-0.3333333333333335</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.555555555555556</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V15" t="n">
+        <v>4.333333333333332</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0.5263157894736842</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1.421052631578947</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>22.63034188034188</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>19.40838621255288</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1041.577601301818</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>835.9396384239933</v>
+      </c>
+      <c r="AE15" t="inlineStr"/>
+      <c r="AF15" t="n">
+        <v>16.75</v>
+      </c>
+      <c r="AG15" t="inlineStr"/>
+      <c r="AH15" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>-11.5</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>2.315789473684211</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>-9.333333333333336</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>7.777777777777771</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>-208</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>69</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0.3333333333333335</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>0.4673202614379086</v>
+      </c>
+      <c r="AQ15" t="inlineStr"/>
+      <c r="AR15" t="inlineStr"/>
+      <c r="AS15" t="n">
+        <v>3.499999999999998</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>2.999999999999993</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>18.2793956043956</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>-0.1858267428468388</v>
+      </c>
+      <c r="AW15" t="inlineStr"/>
+      <c r="AX15" t="n">
+        <v>-0.001322671721763272</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>0.1578947368421053</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>-0.2414930555555554</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>-1.118142361111154</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>-6769.648602965133</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>0.5681818181818183</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>-24162.87878787879</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>-3.594599556823809</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>-5690.795615060321</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>31.65909090909091</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>-4.463628472222211</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>-5.775568181818187</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>-2342659.603851011</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>2.620162563131313</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>-0.660306186868695</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>-0.2783279220779222</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>1.199179292929294</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>-2.482820714622179</v>
+      </c>
+      <c r="BQ15" t="n">
+        <v>-1729187.790044867</v>
+      </c>
+      <c r="BR15" t="n">
+        <v>-3711022.727272728</v>
+      </c>
+      <c r="BS15" t="n">
+        <v>-1.590826340091041</v>
+      </c>
+      <c r="BT15" t="n">
+        <v>-0.9734848484848482</v>
+      </c>
+      <c r="BU15" t="n">
+        <v>36.03409090909091</v>
+      </c>
+      <c r="BV15" t="n">
+        <v>0.9451065955661484</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>n5Eg2hB4</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45598.625</v>
+      </c>
+      <c r="C16" t="n">
+        <v>103</v>
+      </c>
+      <c r="D16" t="n">
+        <v>133</v>
+      </c>
+      <c r="E16" t="n">
+        <v>211</v>
+      </c>
+      <c r="F16" t="n">
+        <v>370</v>
+      </c>
+      <c r="G16" t="n">
+        <v>55</v>
+      </c>
+      <c r="H16" t="n">
+        <v>551</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="L16" t="n">
+        <v>12</v>
+      </c>
+      <c r="M16" t="n">
+        <v>60</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>-0.4666666666666668</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0.4602499999999999</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>-1</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0.1833333333333333</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.176470588235294</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>6.214705882352941</v>
+      </c>
+      <c r="W16" t="n">
+        <v>2</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0.8833333333333334</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1.783333333333333</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>21.48131313131313</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>18.25763663167859</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>804.5547290995599</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>856.1488261030743</v>
+      </c>
+      <c r="AE16" t="inlineStr"/>
+      <c r="AF16" t="n">
+        <v>39.38888888888889</v>
+      </c>
+      <c r="AG16" t="inlineStr"/>
+      <c r="AH16" t="n">
+        <v>27.23809523809524</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>-10.33333333333334</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>4.366666666666667</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>3.333333333333329</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>10.65294117647059</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>78.5</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>119.8650793650794</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>3</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>0.9836601307189543</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>0.1666666666666666</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>10</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>3.950000000000003</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>-29.22283966033967</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>-6.255935633683574</v>
+      </c>
+      <c r="AW16" t="inlineStr"/>
+      <c r="AX16" t="n">
+        <v>0.02435362985374841</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>0.6444444444444446</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>-0.2180976430976429</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>-3.756472128694298</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>-15721.70781893004</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>-53042.22222222222</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>-4.773181986698432</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>-12385.85404007117</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>-95.8111111111111</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>-4.744790497568246</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>5.038814814814856</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>-7659951.365506921</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>1.357145529367749</v>
+      </c>
+      <c r="BM16" t="n">
+        <v>-3.113739244294791</v>
+      </c>
+      <c r="BN16" t="n">
+        <v>-0.1489470312783456</v>
+      </c>
+      <c r="BO16" t="n">
+        <v>2.319444444444443</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>-2.203623887166287</v>
+      </c>
+      <c r="BQ16" t="n">
+        <v>-5386568.784785156</v>
+      </c>
+      <c r="BR16" t="n">
+        <v>-23887333.33333333</v>
+      </c>
+      <c r="BS16" t="n">
+        <v>0.9748778566685417</v>
+      </c>
+      <c r="BT16" t="n">
+        <v>-1.582222222222222</v>
+      </c>
+      <c r="BU16" t="n">
+        <v>-87.00666666666667</v>
+      </c>
+      <c r="BV16" t="n">
+        <v>2.524851174872797</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>rX720WuH</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45598.54166666666</v>
+      </c>
+      <c r="C17" t="n">
+        <v>102</v>
+      </c>
+      <c r="D17" t="n">
+        <v>133</v>
+      </c>
+      <c r="E17" t="n">
+        <v>206</v>
+      </c>
+      <c r="F17" t="n">
+        <v>176</v>
+      </c>
+      <c r="G17" t="n">
+        <v>55</v>
+      </c>
+      <c r="H17" t="n">
+        <v>551</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
+        <v>313</v>
+      </c>
+      <c r="M17" t="n">
+        <v>204</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>2.246666666666667</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1.311776315789473</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>3</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.894736842105263</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3.666666666666667</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.213815789473684</v>
+      </c>
+      <c r="U17" t="n">
+        <v>10</v>
+      </c>
+      <c r="V17" t="n">
+        <v>6.644736842105264</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.036184210526316</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>1.519736842105263</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>18.08324915824916</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>18.31860651231482</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>931.5822393258702</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>848.6045219786938</v>
+      </c>
+      <c r="AE17" t="inlineStr"/>
+      <c r="AF17" t="n">
+        <v>54.5927601809955</v>
+      </c>
+      <c r="AG17" t="inlineStr"/>
+      <c r="AH17" t="n">
+        <v>34.65158371040724</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>3.666666666666664</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>9.167763157894733</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>-1.333333333333343</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>18.04605263157895</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>198.8144796380091</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>-2.666666666666667</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>-1.375</v>
+      </c>
+      <c r="AQ17" t="inlineStr"/>
+      <c r="AR17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>-3.666666666666668</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>-7.513157894736842</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>-6.828205128205127</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>-3.010274241173892</v>
+      </c>
+      <c r="AW17" t="inlineStr"/>
+      <c r="AX17" t="n">
+        <v>0.02562133061452004</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>-0.3333333333333333</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>-0.1546052631578947</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>0.926074074074074</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>4.260185185185151</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>56463.66666666667</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>0.6074074074074076</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>164783.7037037037</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>8.973602827378556</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>61583.20288121488</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>67.48444444444445</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>6.891518518518524</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>16.19427865961197</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>43000033.33333333</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>-2.985592592592592</v>
+      </c>
+      <c r="BM17" t="n">
+        <v>4.33237037037037</v>
+      </c>
+      <c r="BN17" t="n">
+        <v>0.6068701702568979</v>
+      </c>
+      <c r="BO17" t="n">
+        <v>-0.8008853615520266</v>
+      </c>
+      <c r="BP17" t="n">
+        <v>5.756307003446594</v>
+      </c>
+      <c r="BQ17" t="n">
+        <v>40469272.35998174</v>
+      </c>
+      <c r="BR17" t="n">
+        <v>91362296.2962963</v>
+      </c>
+      <c r="BS17" t="n">
+        <v>5.515960050628252</v>
+      </c>
+      <c r="BT17" t="n">
+        <v>4.604444444444445</v>
+      </c>
+      <c r="BU17" t="n">
+        <v>60.40592592592591</v>
+      </c>
+      <c r="BV17" t="n">
+        <v>-3.785128220368492</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>bqYbtBlo</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45597.70833333334</v>
+      </c>
+      <c r="C18" t="n">
+        <v>101</v>
+      </c>
+      <c r="D18" t="n">
+        <v>133</v>
+      </c>
+      <c r="E18" t="n">
+        <v>777</v>
+      </c>
+      <c r="F18" t="n">
+        <v>39</v>
+      </c>
+      <c r="G18" t="n">
+        <v>55</v>
+      </c>
+      <c r="H18" t="n">
+        <v>551</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="L18" t="n">
+        <v>97</v>
+      </c>
+      <c r="M18" t="n">
+        <v>109</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>-0.5366666666666672</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0.8171323529411763</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>-1</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.040247678018576</v>
+      </c>
+      <c r="S18" t="n">
+        <v>-0.6666666666666665</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.736111111111112</v>
+      </c>
+      <c r="U18" t="n">
+        <v>3.333333333333332</v>
+      </c>
+      <c r="V18" t="n">
+        <v>6.888888888888889</v>
+      </c>
+      <c r="W18" t="n">
+        <v>-1.166666666666667</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.226006191950464</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0.1486068111455108</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>13.74509379509379</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>15.48217202346932</v>
+      </c>
+      <c r="AC18" t="inlineStr"/>
+      <c r="AD18" t="n">
+        <v>896.1360910503383</v>
+      </c>
+      <c r="AE18" t="inlineStr"/>
+      <c r="AF18" t="n">
+        <v>35.14285714285715</v>
+      </c>
+      <c r="AG18" t="inlineStr"/>
+      <c r="AH18" t="n">
+        <v>16.80357142857143</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>-4.333333333333329</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>7.786377708978328</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>12.33333333333333</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>5.430555555555557</v>
+      </c>
+      <c r="AM18" t="inlineStr"/>
+      <c r="AN18" t="n">
+        <v>56.00980392156862</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>-0.3333333333333333</v>
+      </c>
+      <c r="AQ18" t="inlineStr"/>
+      <c r="AR18" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>4.833333333333332</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>-1.263157894736846</v>
+      </c>
+      <c r="AU18" t="inlineStr"/>
+      <c r="AV18" t="n">
+        <v>-0.5438928805307466</v>
+      </c>
+      <c r="AW18" t="inlineStr"/>
+      <c r="AX18" t="n">
+        <v>-0.008946652742442537</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>-0.3333333333333333</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>0.2012383900928792</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>-0.3541526374859711</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>0.6887953610175543</v>
+      </c>
+      <c r="BC18" t="inlineStr"/>
+      <c r="BD18" t="n">
+        <v>-0.6666666666666667</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>-46444.44444444445</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>-1.091959757414315</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>-21550.18518518519</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>-52.95438596491229</v>
+      </c>
+      <c r="BI18" t="n">
+        <v>2.21852319491208</v>
+      </c>
+      <c r="BJ18" t="n">
+        <v>6.694736842105272</v>
+      </c>
+      <c r="BK18" t="n">
+        <v>157418.864571644</v>
+      </c>
+      <c r="BL18" t="n">
+        <v>-0.6275346053123805</v>
+      </c>
+      <c r="BM18" t="n">
+        <v>1.087967639356535</v>
+      </c>
+      <c r="BN18" t="n">
+        <v>-0.7450146822874097</v>
+      </c>
+      <c r="BO18" t="n">
+        <v>1.256432748538018</v>
+      </c>
+      <c r="BP18" t="n">
+        <v>-4.024444848081217</v>
+      </c>
+      <c r="BQ18" t="n">
+        <v>-7243319.023148569</v>
+      </c>
+      <c r="BR18" t="n">
+        <v>-8658070.175438596</v>
+      </c>
+      <c r="BS18" t="n">
+        <v>1.371809856809847</v>
+      </c>
+      <c r="BT18" t="n">
+        <v>-1.764912280701755</v>
+      </c>
+      <c r="BU18" t="n">
+        <v>-48.49473684210525</v>
+      </c>
+      <c r="BV18" t="n">
+        <v>-1.685154845154845</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>0ljCkFRb</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45597.625</v>
+      </c>
+      <c r="C19" t="n">
+        <v>102</v>
+      </c>
+      <c r="D19" t="n">
+        <v>133</v>
+      </c>
+      <c r="E19" t="n">
+        <v>47</v>
+      </c>
+      <c r="F19" t="n">
+        <v>292</v>
+      </c>
+      <c r="G19" t="n">
+        <v>55</v>
+      </c>
+      <c r="H19" t="n">
+        <v>551</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="L19" t="n">
+        <v>193</v>
+      </c>
+      <c r="M19" t="n">
+        <v>226</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0.8927205882352939</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>2</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0.7875000000000001</v>
+      </c>
+      <c r="S19" t="n">
+        <v>4.666666666666666</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.466911764705883</v>
+      </c>
+      <c r="U19" t="n">
+        <v>13.66666666666667</v>
+      </c>
+      <c r="V19" t="n">
+        <v>9.404411764705882</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0.7375</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>1.0875</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>13.32791005291005</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>15.69023071957749</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>784.0622351799401</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>841.0297087191032</v>
+      </c>
+      <c r="AE19" t="inlineStr"/>
+      <c r="AF19" t="n">
+        <v>41.72820512820512</v>
+      </c>
+      <c r="AG19" t="inlineStr"/>
+      <c r="AH19" t="n">
+        <v>13.79487179487179</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>19</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>47.33333333333334</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>17.50735294117646</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>161</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>92.38461538461536</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>2.220446049250313e-16</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>0.3647058823529408</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>0.4666666666666667</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>-4.333333333333332</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>7.125</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>4.26209330143541</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>-3.687551366574661</v>
+      </c>
+      <c r="AW19" t="inlineStr"/>
+      <c r="AX19" t="n">
+        <v>0.002298557086179862</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>0.3888888888888888</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>-3.656870108006473</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>34512.48057498057</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>0.8888888888888884</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>164791.6666666667</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>10.23900269450813</v>
+      </c>
+      <c r="BG19" t="inlineStr"/>
+      <c r="BH19" t="n">
+        <v>105.9583333333333</v>
+      </c>
+      <c r="BI19" t="n">
+        <v>8.992899776990697</v>
+      </c>
+      <c r="BJ19" t="n">
+        <v>-2.034457671957682</v>
+      </c>
+      <c r="BK19" t="n">
+        <v>12978205.86820587</v>
+      </c>
+      <c r="BL19" t="n">
+        <v>-3.961241746469021</v>
+      </c>
+      <c r="BM19" t="n">
+        <v>5.751681315317668</v>
+      </c>
+      <c r="BN19" t="n">
+        <v>0.1119264507422404</v>
+      </c>
+      <c r="BO19" t="n">
+        <v>0.6024305555555571</v>
+      </c>
+      <c r="BP19" t="n">
+        <v>5.485840732574999</v>
+      </c>
+      <c r="BQ19" t="n">
+        <v>8315287.711383132</v>
+      </c>
+      <c r="BR19" t="n">
+        <v>64693055.55555556</v>
+      </c>
+      <c r="BS19" t="n">
+        <v>-2.83914562902163</v>
+      </c>
+      <c r="BT19" t="n">
+        <v>2.388888888888888</v>
+      </c>
+      <c r="BU19" t="n">
+        <v>106.9166666666667</v>
+      </c>
+      <c r="BV19" t="n">
+        <v>-3.885095308816283</v>
       </c>
     </row>
   </sheetData>

--- a/data/france/p6_deployment/data_preparation/df_tagged.xlsx
+++ b/data/france/p6_deployment/data_preparation/df_tagged.xlsx
@@ -500,313 +500,313 @@
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_60_matches_expected_goals_(xg)</t>
+          <t>dif_mean_last_120_matches_expected_goals_(xg)</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_360_matches_expected_goals_(xg)</t>
+          <t>dif_mean_last_480_matches_expected_goals_(xg)</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_60_matches_expected_points</t>
+          <t>dif_mean_last_120_matches_expected_points</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_360_matches_expected_points</t>
+          <t>dif_mean_last_480_matches_expected_points</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_60_matches_shots_on_goal</t>
+          <t>dif_mean_last_120_matches_shots_on_goal</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_360_matches_shots_on_goal</t>
+          <t>dif_mean_last_480_matches_shots_on_goal</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_60_matches_goal_attempts</t>
+          <t>dif_mean_last_120_matches_goal_attempts</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_360_matches_goal_attempts</t>
+          <t>dif_mean_last_480_matches_goal_attempts</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_60_matches_goals</t>
+          <t>dif_mean_last_120_matches_goals</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_360_matches_goals</t>
+          <t>dif_mean_last_480_matches_goals</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_60_matches_points</t>
+          <t>dif_mean_last_120_matches_points</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_360_matches_points</t>
+          <t>dif_mean_last_480_matches_points</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_60_matches_goal_ratio</t>
+          <t>dif_mean_last_120_matches_goal_ratio</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_360_matches_goal_ratio</t>
+          <t>dif_mean_last_480_matches_goal_ratio</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_60_matches_PPS</t>
+          <t>dif_mean_last_120_matches_PPS</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_360_matches_PPS</t>
+          <t>dif_mean_last_480_matches_PPS</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_60_matches_attacks</t>
+          <t>dif_mean_last_120_matches_attacks</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_360_matches_attacks</t>
+          <t>dif_mean_last_480_matches_attacks</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_60_matches_dangerous_attacks</t>
+          <t>dif_mean_last_120_matches_dangerous_attacks</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_360_matches_dangerous_attacks</t>
+          <t>dif_mean_last_480_matches_dangerous_attacks</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_60_matches_dead_balls</t>
+          <t>dif_mean_last_120_matches_dead_balls</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_360_matches_dead_balls</t>
+          <t>dif_mean_last_480_matches_dead_balls</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_60_matches_ball_possession</t>
+          <t>dif_mean_last_120_matches_ball_possession</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_360_matches_ball_possession</t>
+          <t>dif_mean_last_480_matches_ball_possession</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_60_matches_total_passes</t>
+          <t>dif_mean_last_120_matches_total_passes</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_360_matches_total_passes</t>
+          <t>dif_mean_last_480_matches_total_passes</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_60_matches_yellow_cards</t>
+          <t>dif_mean_last_120_matches_yellow_cards</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_360_matches_yellow_cards</t>
+          <t>dif_mean_last_480_matches_yellow_cards</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_60_matches_red_cards</t>
+          <t>dif_mean_last_120_matches_red_cards</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_360_matches_red_cards</t>
+          <t>dif_mean_last_480_matches_red_cards</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_60_matches_defensive_actions</t>
+          <t>dif_mean_last_120_matches_defensive_actions</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_360_matches_defensive_actions</t>
+          <t>dif_mean_last_480_matches_defensive_actions</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_60_matches_PPDA</t>
+          <t>dif_mean_last_120_matches_PPDA</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_360_matches_PPDA</t>
+          <t>dif_mean_last_480_matches_PPDA</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_60_matches_KGP</t>
+          <t>dif_mean_last_120_matches_KGP</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_360_matches_KGP</t>
+          <t>dif_mean_last_480_matches_KGP</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_60_matches_clean_sheet</t>
+          <t>dif_mean_last_120_matches_clean_sheet</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_360_matches_clean_sheet</t>
+          <t>dif_mean_last_480_matches_clean_sheet</t>
         </is>
       </c>
       <c r="BA1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_age_player_miss</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rep_player_start</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_value_player_start</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_start</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_sub</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_start</t>
+        </is>
+      </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_value_player_sub</t>
+        </is>
+      </c>
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_wage_player_miss</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_sub</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
           <t>dif_sum_pot_player_miss</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rep_player_start</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_value_player_start</t>
-        </is>
-      </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_start</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>dif_n_player_miss</t>
+        </is>
+      </c>
+      <c r="BM1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_rat_player_miss</t>
+        </is>
+      </c>
+      <c r="BN1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_start</t>
+        </is>
+      </c>
+      <c r="BO1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rep_player_sub</t>
+        </is>
+      </c>
+      <c r="BP1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_rep_player_miss</t>
+        </is>
+      </c>
+      <c r="BQ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_miss</t>
+        </is>
+      </c>
+      <c r="BR1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_wage_player_start</t>
+        </is>
+      </c>
+      <c r="BS1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_sub</t>
+        </is>
+      </c>
+      <c r="BT1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_sub</t>
+        </is>
+      </c>
+      <c r="BU1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_value_player_miss</t>
+        </is>
+      </c>
+      <c r="BV1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_wage_player_sub</t>
-        </is>
-      </c>
-      <c r="BE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rep_player_sub</t>
-        </is>
-      </c>
-      <c r="BF1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_sub</t>
-        </is>
-      </c>
-      <c r="BG1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_wage_player_start</t>
-        </is>
-      </c>
-      <c r="BH1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_start</t>
-        </is>
-      </c>
-      <c r="BI1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_rat_player_miss</t>
-        </is>
-      </c>
-      <c r="BJ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_value_player_miss</t>
-        </is>
-      </c>
-      <c r="BK1" s="1" t="inlineStr">
-        <is>
-          <t>dif_n_player_miss</t>
-        </is>
-      </c>
-      <c r="BL1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_wage_player_miss</t>
-        </is>
-      </c>
-      <c r="BM1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_miss</t>
-        </is>
-      </c>
-      <c r="BN1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_sub</t>
-        </is>
-      </c>
-      <c r="BO1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_rep_player_miss</t>
-        </is>
-      </c>
-      <c r="BP1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_miss</t>
-        </is>
-      </c>
-      <c r="BQ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_sub</t>
-        </is>
-      </c>
-      <c r="BR1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_start</t>
-        </is>
-      </c>
-      <c r="BS1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_start</t>
-        </is>
-      </c>
-      <c r="BT1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_value_player_sub</t>
-        </is>
-      </c>
-      <c r="BU1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_sub</t>
-        </is>
-      </c>
-      <c r="BV1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_start</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>UTsToXQN</t>
+          <t>b59ZhlYj</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45599.69791666666</v>
+        <v>45606.69791666666</v>
       </c>
       <c r="C2" t="n">
         <v>102</v>
@@ -815,10 +815,10 @@
         <v>133</v>
       </c>
       <c r="E2" t="n">
-        <v>858</v>
+        <v>56</v>
       </c>
       <c r="F2" t="n">
-        <v>303</v>
+        <v>362</v>
       </c>
       <c r="G2" t="n">
         <v>55</v>
@@ -840,209 +840,213 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>312</v>
+        <v>243</v>
       </c>
       <c r="M2" t="n">
-        <v>37</v>
+        <v>258</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>0.8733333333333334</v>
+        <v>2.468</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.1976388888888887</v>
+        <v>0.6911538461538458</v>
       </c>
       <c r="Q2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R2" t="n">
-        <v>0.02960526315789469</v>
+        <v>0.6923076923076922</v>
       </c>
       <c r="S2" t="n">
-        <v>1.333333333333333</v>
+        <v>6.199999999999999</v>
       </c>
       <c r="T2" t="n">
-        <v>0.9583333333333339</v>
+        <v>0.2999999999999998</v>
       </c>
       <c r="U2" t="n">
-        <v>8.333333333333332</v>
+        <v>8.599999999999998</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.02777777777777857</v>
+        <v>0.7692307692307683</v>
       </c>
       <c r="W2" t="n">
-        <v>-2</v>
+        <v>3</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.463815789473684</v>
+        <v>0.1923076923076923</v>
       </c>
       <c r="Y2" t="n">
-        <v>-2</v>
+        <v>2.4</v>
       </c>
       <c r="Z2" t="n">
-        <v>-1.6875</v>
+        <v>0.346153846153846</v>
       </c>
       <c r="AA2" t="n">
-        <v>16.94552438302438</v>
+        <v>18.15321369806664</v>
       </c>
       <c r="AB2" t="n">
-        <v>19.81343443096458</v>
+        <v>21.97742432404398</v>
       </c>
       <c r="AC2" t="n">
-        <v>1085.583999518684</v>
+        <v>694.055937987128</v>
       </c>
       <c r="AD2" t="n">
-        <v>1002.848719162645</v>
-      </c>
-      <c r="AE2" t="inlineStr"/>
+        <v>907.357706627157</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>17</v>
+      </c>
       <c r="AF2" t="n">
-        <v>-19.65714285714286</v>
-      </c>
-      <c r="AG2" t="inlineStr"/>
+        <v>5.990118577075094</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>35</v>
+      </c>
       <c r="AH2" t="n">
-        <v>-6.209523809523802</v>
+        <v>12.96047430830039</v>
       </c>
       <c r="AI2" t="n">
-        <v>3.999999999999993</v>
+        <v>4.200000000000003</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.098684210526315</v>
+        <v>2.346153846153847</v>
       </c>
       <c r="AK2" t="n">
-        <v>-8.666666666666657</v>
+        <v>15.2</v>
       </c>
       <c r="AL2" t="n">
-        <v>-20.73611111111111</v>
+        <v>0.14769230769231</v>
       </c>
       <c r="AM2" t="n">
-        <v>-404.5</v>
+        <v>255.5</v>
       </c>
       <c r="AN2" t="n">
-        <v>-213.1047619047619</v>
+        <v>-24.87445887445892</v>
       </c>
       <c r="AO2" t="n">
-        <v>1</v>
+        <v>-2.399999999999999</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.5441176470588234</v>
+        <v>-0.6399999999999999</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.2</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="AS2" t="n">
-        <v>12</v>
+        <v>-8.600000000000001</v>
       </c>
       <c r="AT2" t="n">
-        <v>3.60526315789474</v>
+        <v>-2.730769230769226</v>
       </c>
       <c r="AU2" t="n">
-        <v>-2.100754411755156</v>
+        <v>11.69164351851852</v>
       </c>
       <c r="AV2" t="n">
-        <v>2.606813562749183</v>
-      </c>
-      <c r="AW2" t="inlineStr"/>
+        <v>1.3328073073568</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>0.01750592976672802</v>
+      </c>
       <c r="AX2" t="n">
-        <v>0.04008347344833654</v>
+        <v>0.02836838310231009</v>
       </c>
       <c r="AY2" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="AZ2" t="n">
-        <v>-0.03947368421052633</v>
+        <v>0.03846153846153849</v>
       </c>
       <c r="BA2" t="n">
-        <v>-135.4728260869565</v>
+        <v>-3.013888888888886</v>
       </c>
       <c r="BB2" t="n">
-        <v>0.2658119658119658</v>
+        <v>0.75</v>
       </c>
       <c r="BC2" t="n">
-        <v>-9295025.373931624</v>
+        <v>9592570.592286501</v>
       </c>
       <c r="BD2" t="n">
-        <v>-11660.07215007215</v>
+        <v>-1.565426997245179</v>
       </c>
       <c r="BE2" t="n">
-        <v>0.03279553779553779</v>
+        <v>-3.044692007052674</v>
       </c>
       <c r="BF2" t="n">
-        <v>0.8521065046065068</v>
+        <v>-0.8295454545454675</v>
       </c>
       <c r="BG2" t="n">
-        <v>-15009.02777777777</v>
+        <v>13014576.88757321</v>
       </c>
       <c r="BH2" t="n">
-        <v>-3.734134615384619</v>
+        <v>55970.58823529411</v>
       </c>
       <c r="BI2" t="n">
-        <v>-118.7880434782609</v>
+        <v>9.810888264928508</v>
       </c>
       <c r="BJ2" t="n">
-        <v>-23305072.46376812</v>
+        <v>-42.5</v>
       </c>
       <c r="BK2" t="n">
-        <v>-1.731884057971015</v>
+        <v>4.905303030303031</v>
       </c>
       <c r="BL2" t="n">
-        <v>-38829.71014492754</v>
+        <v>-0.8333333333333335</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.3340881642512059</v>
+        <v>-48.86111111111111</v>
       </c>
       <c r="BN2" t="n">
-        <v>-0.329806721056741</v>
+        <v>3.995179063360879</v>
       </c>
       <c r="BO2" t="n">
-        <v>-2.418478260869565</v>
+        <v>0.9983333333333335</v>
       </c>
       <c r="BP2" t="n">
-        <v>-5.343719806763318</v>
+        <v>0.7777777777777777</v>
       </c>
       <c r="BQ2" t="n">
-        <v>-4.713561716061704</v>
-      </c>
-      <c r="BR2" t="n">
-        <v>0.201655982905983</v>
-      </c>
+        <v>-1.668981481481467</v>
+      </c>
+      <c r="BR2" t="inlineStr"/>
       <c r="BS2" t="n">
-        <v>0.5224358974359689</v>
+        <v>3.06590715313239</v>
       </c>
       <c r="BT2" t="n">
-        <v>-5714481.355450104</v>
+        <v>5.691621289930112</v>
       </c>
       <c r="BU2" t="n">
-        <v>-4.563638167388191</v>
+        <v>16458333.33333333</v>
       </c>
       <c r="BV2" t="n">
-        <v>-3.61613247863248</v>
+        <v>39469.8352337568</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>EuWhpKkJ</t>
+          <t>nRkUEVfA</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45599.54166666666</v>
+        <v>45606.54166666666</v>
       </c>
       <c r="C3" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D3" t="n">
         <v>133</v>
       </c>
       <c r="E3" t="n">
-        <v>342</v>
+        <v>194</v>
       </c>
       <c r="F3" t="n">
-        <v>399</v>
+        <v>579</v>
       </c>
       <c r="G3" t="n">
         <v>55</v>
@@ -1064,205 +1068,213 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>165</v>
+        <v>198</v>
       </c>
       <c r="M3" t="n">
-        <v>166</v>
+        <v>10</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>1.883333333333333</v>
+        <v>-0.4200000000000002</v>
       </c>
       <c r="P3" t="n">
-        <v>0.9348366013071896</v>
+        <v>0.2163636363636361</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.5</v>
+        <v>0.5999999999999999</v>
       </c>
       <c r="R3" t="n">
-        <v>1.235294117647059</v>
+        <v>0.5054347826086957</v>
       </c>
       <c r="S3" t="n">
-        <v>0.166666666666667</v>
+        <v>-0.2000000000000011</v>
       </c>
       <c r="T3" t="n">
-        <v>1.764705882352941</v>
+        <v>0.7806324110671934</v>
       </c>
       <c r="U3" t="n">
-        <v>7.666666666666666</v>
+        <v>-3.800000000000001</v>
       </c>
       <c r="V3" t="n">
-        <v>4.058823529411766</v>
+        <v>1.594861660079051</v>
       </c>
       <c r="W3" t="n">
-        <v>1.333333333333333</v>
+        <v>-1.6</v>
       </c>
       <c r="X3" t="n">
-        <v>1.102941176470588</v>
+        <v>-0.1793478260869565</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.5</v>
+        <v>-0.6000000000000001</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.117647058823529</v>
+        <v>-0.1413043478260869</v>
       </c>
       <c r="AA3" t="n">
-        <v>19.04786324786325</v>
+        <v>22.98590270840271</v>
       </c>
       <c r="AB3" t="n">
-        <v>18.04814810282205</v>
+        <v>20.3141902780066</v>
       </c>
       <c r="AC3" t="n">
-        <v>872.0664825060937</v>
+        <v>1067.732748886656</v>
       </c>
       <c r="AD3" t="n">
-        <v>873.6203422637333</v>
-      </c>
-      <c r="AE3" t="inlineStr"/>
+        <v>934.0496687217203</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>-31.5</v>
+      </c>
       <c r="AF3" t="n">
-        <v>20.89411764705883</v>
-      </c>
-      <c r="AG3" t="inlineStr"/>
+        <v>-11.33157894736841</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>-9.5</v>
+      </c>
       <c r="AH3" t="n">
-        <v>16.01568627450981</v>
+        <v>6.671052631578945</v>
       </c>
       <c r="AI3" t="n">
-        <v>-7.5</v>
+        <v>-2.000000000000004</v>
       </c>
       <c r="AJ3" t="n">
-        <v>4.494117647058827</v>
+        <v>1.621376811594196</v>
       </c>
       <c r="AK3" t="n">
-        <v>-5.333333333333329</v>
+        <v>-20.40000000000001</v>
       </c>
       <c r="AL3" t="n">
-        <v>9.164086687306508</v>
+        <v>-11.61660079051384</v>
       </c>
       <c r="AM3" t="n">
-        <v>-104</v>
+        <v>-393</v>
       </c>
       <c r="AN3" t="n">
-        <v>89.375</v>
+        <v>-136.8523809523809</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.3333333333333335</v>
+        <v>-1</v>
       </c>
       <c r="AP3" t="n">
-        <v>-0.929824561403509</v>
+        <v>-0.6326086956521739</v>
       </c>
       <c r="AQ3" t="inlineStr"/>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AS3" t="n">
-        <v>-1.166666666666668</v>
+        <v>-0.6000000000000014</v>
       </c>
       <c r="AT3" t="n">
-        <v>-3.964705882352945</v>
+        <v>-3.172101449275367</v>
       </c>
       <c r="AU3" t="n">
-        <v>12.03655788655789</v>
+        <v>4.222235902310505</v>
       </c>
       <c r="AV3" t="n">
-        <v>-0.01481299233423528</v>
-      </c>
-      <c r="AW3" t="inlineStr"/>
+        <v>4.019923079332992</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>-0.003350309248911221</v>
+      </c>
       <c r="AX3" t="n">
-        <v>-0.02067489693449977</v>
+        <v>-0.005206338595952091</v>
       </c>
       <c r="AY3" t="n">
         <v>0</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.3441176470588235</v>
+        <v>-0.1757246376811594</v>
       </c>
       <c r="BA3" t="n">
-        <v>141</v>
+        <v>3.324715909090909</v>
       </c>
       <c r="BB3" t="n">
-        <v>-0.4646103896103899</v>
+        <v>-0.125</v>
       </c>
       <c r="BC3" t="n">
-        <v>-11417841.20971621</v>
-      </c>
-      <c r="BD3" t="inlineStr"/>
+        <v>-4638490.497076023</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>-1.985380116959064</v>
+      </c>
       <c r="BE3" t="n">
-        <v>-0.2693025210084035</v>
+        <v>-4.816397564423852</v>
       </c>
       <c r="BF3" t="n">
-        <v>0.7982385483699055</v>
+        <v>1.572953216374231</v>
       </c>
       <c r="BG3" t="n">
-        <v>-25601.4650865958</v>
+        <v>-1419514.234590597</v>
       </c>
       <c r="BH3" t="n">
-        <v>-10.06113516113516</v>
+        <v>-1034.722222222223</v>
       </c>
       <c r="BI3" t="n">
-        <v>126</v>
+        <v>-3.300817634746195</v>
       </c>
       <c r="BJ3" t="n">
-        <v>2400000</v>
+        <v>-7.988636363636374</v>
       </c>
       <c r="BK3" t="n">
-        <v>2</v>
+        <v>-4.325584795321646</v>
       </c>
       <c r="BL3" t="n">
-        <v>-5000</v>
+        <v>-0.02272727272727271</v>
       </c>
       <c r="BM3" t="n">
-        <v>4</v>
+        <v>-2.01136363636364</v>
       </c>
       <c r="BN3" t="n">
-        <v>-0.7815403718105927</v>
+        <v>-6.818567251461999</v>
       </c>
       <c r="BO3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BP3" t="n">
-        <v>-3</v>
+        <v>-0.1136363636363635</v>
       </c>
       <c r="BQ3" t="n">
-        <v>-7.353463003702288</v>
+        <v>5.308617424242414</v>
       </c>
       <c r="BR3" t="n">
-        <v>2.568813131313131</v>
+        <v>-11514.5202020202</v>
       </c>
       <c r="BS3" t="n">
-        <v>-0.5503066378066706</v>
+        <v>1.29322040219596</v>
       </c>
       <c r="BT3" t="n">
-        <v>-8837448.878434945</v>
+        <v>-3.108448834999592</v>
       </c>
       <c r="BU3" t="n">
-        <v>-8.026715581288343</v>
+        <v>326846.5909090908</v>
       </c>
       <c r="BV3" t="n">
-        <v>-6.77776575276576</v>
+        <v>-6580.706727135299</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Y1lKmgdB</t>
+          <t>QB1LGiQc</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45599.54166666666</v>
+        <v>45606.54166666666</v>
       </c>
       <c r="C4" t="n">
         <v>101</v>
       </c>
       <c r="D4" t="n">
+        <v>134</v>
+      </c>
+      <c r="E4" t="n">
+        <v>242</v>
+      </c>
+      <c r="F4" t="n">
         <v>133</v>
-      </c>
-      <c r="E4" t="n">
-        <v>194</v>
-      </c>
-      <c r="F4" t="n">
-        <v>157</v>
       </c>
       <c r="G4" t="n">
         <v>55</v>
@@ -1284,207 +1296,215 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>249</v>
+        <v>198</v>
       </c>
       <c r="M4" t="n">
-        <v>127</v>
+        <v>163</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.126666666666666</v>
+        <v>0.3290000000000001</v>
       </c>
       <c r="P4" t="n">
-        <v>0.9549166666666671</v>
+        <v>0.5506418219461697</v>
       </c>
       <c r="Q4" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.5217391304347828</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="T4" t="n">
         <v>0</v>
       </c>
-      <c r="R4" t="n">
-        <v>1.411764705882353</v>
-      </c>
-      <c r="S4" t="n">
-        <v>-4.166666666666666</v>
-      </c>
-      <c r="T4" t="n">
-        <v>1.5</v>
-      </c>
       <c r="U4" t="n">
-        <v>-3.666666666666666</v>
+        <v>5.699999999999999</v>
       </c>
       <c r="V4" t="n">
-        <v>8</v>
+        <v>1.565217391304349</v>
       </c>
       <c r="W4" t="n">
-        <v>-1.5</v>
+        <v>-0.2999999999999998</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.6956521739130435</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="Z4" t="n">
-        <v>-0.5294117647058825</v>
+        <v>-0.9130434782608696</v>
       </c>
       <c r="AA4" t="n">
-        <v>21.23761423761424</v>
+        <v>17.23355921855922</v>
       </c>
       <c r="AB4" t="n">
-        <v>17.91499910531935</v>
+        <v>21.34939913887282</v>
       </c>
       <c r="AC4" t="n">
-        <v>922.0529513128304</v>
+        <v>830.7288747699315</v>
       </c>
       <c r="AD4" t="n">
-        <v>866.2312035376042</v>
-      </c>
-      <c r="AE4" t="inlineStr"/>
+        <v>885.7396145294296</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>69</v>
+      </c>
       <c r="AF4" t="n">
-        <v>15.42857142857144</v>
-      </c>
-      <c r="AG4" t="inlineStr"/>
+        <v>-14.06190476190476</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>68</v>
+      </c>
       <c r="AH4" t="n">
-        <v>31</v>
+        <v>8.302380952380943</v>
       </c>
       <c r="AI4" t="n">
-        <v>-1.5</v>
+        <v>17.9</v>
       </c>
       <c r="AJ4" t="n">
-        <v>2.823529411764703</v>
+        <v>6.478260869565219</v>
       </c>
       <c r="AK4" t="n">
-        <v>-14.66666666666667</v>
+        <v>5.700000000000003</v>
       </c>
       <c r="AL4" t="n">
-        <v>2.625</v>
+        <v>-6.956521739130437</v>
       </c>
       <c r="AM4" t="n">
-        <v>-197</v>
+        <v>60.16666666666669</v>
       </c>
       <c r="AN4" t="n">
-        <v>-19.76923076923077</v>
+        <v>-86.95238095238091</v>
       </c>
       <c r="AO4" t="n">
-        <v>-1</v>
+        <v>-0.3499999999999996</v>
       </c>
       <c r="AP4" t="n">
-        <v>-0.4375</v>
-      </c>
-      <c r="AQ4" t="inlineStr"/>
+        <v>-1.217391304347826</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>2</v>
+      </c>
       <c r="AR4" t="n">
-        <v>-1.666666666666667</v>
+        <v>0.2571428571428571</v>
       </c>
       <c r="AS4" t="n">
-        <v>4.999999999999998</v>
+        <v>-5.550000000000001</v>
       </c>
       <c r="AT4" t="n">
-        <v>2.823529411764699</v>
+        <v>-6.347826086956523</v>
       </c>
       <c r="AU4" t="n">
-        <v>-4.217684087249303</v>
+        <v>-0.8253700912767616</v>
       </c>
       <c r="AV4" t="n">
-        <v>-0.4674721059058093</v>
-      </c>
-      <c r="AW4" t="inlineStr"/>
+        <v>4.324258497655338</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>0.0669922230538669</v>
+      </c>
       <c r="AX4" t="n">
-        <v>0.02013651507394308</v>
+        <v>0.02671768270724185</v>
       </c>
       <c r="AY4" t="n">
-        <v>-0.6666666666666667</v>
+        <v>0.09999999999999998</v>
       </c>
       <c r="AZ4" t="n">
-        <v>-0.2941176470588235</v>
+        <v>0.04347826086956524</v>
       </c>
       <c r="BA4" t="n">
-        <v>-138.9166666666667</v>
+        <v>-0.4086956521739182</v>
       </c>
       <c r="BB4" t="n">
-        <v>-0.4097222222222221</v>
+        <v>0.2378760128760129</v>
       </c>
       <c r="BC4" t="n">
-        <v>-5219610.288742689</v>
+        <v>3341954.573204573</v>
       </c>
       <c r="BD4" t="n">
-        <v>-6538.369855252973</v>
+        <v>0.4509962259962279</v>
       </c>
       <c r="BE4" t="n">
-        <v>-0.1982043597428214</v>
+        <v>-1.943603022985315</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.128607725495371</v>
+        <v>-1.971858696858675</v>
       </c>
       <c r="BG4" t="n">
-        <v>-11678.21067821068</v>
+        <v>543959.1836726898</v>
       </c>
       <c r="BH4" t="n">
-        <v>-3.389820906432746</v>
+        <v>26664.70588235294</v>
       </c>
       <c r="BI4" t="n">
-        <v>-128.9583333333333</v>
+        <v>-1.277991196946545</v>
       </c>
       <c r="BJ4" t="n">
-        <v>-7327604.166666666</v>
+        <v>155.4526854219949</v>
       </c>
       <c r="BK4" t="n">
-        <v>-1.791666666666667</v>
+        <v>1.64756632256632</v>
       </c>
       <c r="BL4" t="n">
-        <v>-34448.86363636364</v>
+        <v>2.035805626598465</v>
       </c>
       <c r="BM4" t="n">
-        <v>-0.6309027777777771</v>
+        <v>139.074168797954</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.345468560903839</v>
+        <v>0.8900876900876824</v>
       </c>
       <c r="BO4" t="n">
-        <v>-2.458333333333333</v>
+        <v>0.02823927225855205</v>
       </c>
       <c r="BP4" t="n">
-        <v>5.925347222222257</v>
+        <v>2.49616368286445</v>
       </c>
       <c r="BQ4" t="n">
-        <v>-2.873064649026176</v>
+        <v>-4.016837169650472</v>
       </c>
       <c r="BR4" t="n">
-        <v>-2.89857456140351</v>
+        <v>1532.313519813519</v>
       </c>
       <c r="BS4" t="n">
-        <v>6.788230994152002</v>
+        <v>-1.328167913796477</v>
       </c>
       <c r="BT4" t="n">
-        <v>-1781229.411965116</v>
+        <v>2.384761703638361</v>
       </c>
       <c r="BU4" t="n">
-        <v>-4.145941196118329</v>
+        <v>6999552.429667518</v>
       </c>
       <c r="BV4" t="n">
-        <v>-6.957456140350885</v>
+        <v>-2074.401920123844</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>4Md3iycn</t>
+          <t>WWnG5RHd</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45599.45833333334</v>
+        <v>45606.54166666666</v>
       </c>
       <c r="C5" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D5" t="n">
         <v>133</v>
       </c>
       <c r="E5" t="n">
-        <v>341</v>
+        <v>573</v>
       </c>
       <c r="F5" t="n">
-        <v>579</v>
+        <v>226</v>
       </c>
       <c r="G5" t="n">
         <v>55</v>
@@ -1506,211 +1526,213 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>76</v>
+        <v>128</v>
       </c>
       <c r="M5" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>0.8166666666666665</v>
+        <v>0.3025</v>
       </c>
       <c r="P5" t="n">
-        <v>0.868125</v>
+        <v>1.179209486166008</v>
       </c>
       <c r="Q5" t="n">
-        <v>2</v>
+        <v>-0.2999999999999998</v>
       </c>
       <c r="R5" t="n">
-        <v>1.235294117647059</v>
+        <v>0.9076086956521739</v>
       </c>
       <c r="S5" t="n">
-        <v>3</v>
+        <v>3.95</v>
       </c>
       <c r="T5" t="n">
-        <v>1.647058823529412</v>
+        <v>2.521739130434782</v>
       </c>
       <c r="U5" t="n">
-        <v>7.000000000000002</v>
+        <v>3.25</v>
       </c>
       <c r="V5" t="n">
-        <v>2.863970588235293</v>
+        <v>7.739130434782608</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.3333333333333335</v>
+        <v>1.2</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.1176470588235294</v>
+        <v>0.6521739130434783</v>
       </c>
       <c r="Y5" t="n">
-        <v>-1</v>
+        <v>1.95</v>
       </c>
       <c r="Z5" t="n">
-        <v>-0.3529411764705883</v>
+        <v>0.5217391304347827</v>
       </c>
       <c r="AA5" t="n">
-        <v>16.68835978835979</v>
+        <v>18.43373556998557</v>
       </c>
       <c r="AB5" t="n">
-        <v>18.71150218923322</v>
+        <v>18.26131678814803</v>
       </c>
       <c r="AC5" t="n">
-        <v>866.0748082913971</v>
+        <v>864.0591706666989</v>
       </c>
       <c r="AD5" t="n">
-        <v>867.2883567094977</v>
+        <v>862.4059338651427</v>
       </c>
       <c r="AE5" t="n">
-        <v>30</v>
+        <v>-12.5</v>
       </c>
       <c r="AF5" t="n">
-        <v>7.24761904761904</v>
+        <v>23.40000000000001</v>
       </c>
       <c r="AG5" t="n">
-        <v>8</v>
+        <v>27.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>18.0857142857143</v>
+        <v>17.75</v>
       </c>
       <c r="AI5" t="n">
-        <v>7.666666666666668</v>
+        <v>6.649999999999999</v>
       </c>
       <c r="AJ5" t="n">
-        <v>3.117647058823529</v>
+        <v>9.675724637681157</v>
       </c>
       <c r="AK5" t="n">
-        <v>-0.6666666666666714</v>
+        <v>7.200000000000003</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.919117647058826</v>
+        <v>7.478260869565219</v>
       </c>
       <c r="AM5" t="n">
+        <v>77.33333333333331</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>71.10952380952386</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>-0.9000000000000001</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>-1.195652173913043</v>
+      </c>
+      <c r="AQ5" t="n">
         <v>0</v>
       </c>
-      <c r="AN5" t="n">
-        <v>15.28571428571428</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>-1.333333333333333</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>-0.6213235294117649</v>
-      </c>
-      <c r="AQ5" t="inlineStr"/>
       <c r="AR5" t="n">
-        <v>-1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="AS5" t="n">
-        <v>-1.77635683940025e-15</v>
+        <v>-7.800000000000001</v>
       </c>
       <c r="AT5" t="n">
-        <v>0.647058823529413</v>
+        <v>-8.710144927536234</v>
       </c>
       <c r="AU5" t="n">
-        <v>-21.15109364319891</v>
+        <v>3.448555472162287</v>
       </c>
       <c r="AV5" t="n">
-        <v>-4.539079073050594</v>
+        <v>0.6403947328577217</v>
       </c>
       <c r="AW5" t="n">
-        <v>-0.02230201171377642</v>
+        <v>-0.01957237715222068</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.02130051461440481</v>
+        <v>0.001915949004117602</v>
       </c>
       <c r="AY5" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.6</v>
       </c>
       <c r="AZ5" t="n">
-        <v>-1.387778780781446e-17</v>
+        <v>0.2989130434782609</v>
       </c>
       <c r="BA5" t="n">
-        <v>63.08695652173913</v>
+        <v>-0.8918831168831183</v>
       </c>
       <c r="BB5" t="n">
-        <v>-0.125</v>
+        <v>0.4646103896103899</v>
       </c>
       <c r="BC5" t="n">
-        <v>-2483874.269005848</v>
+        <v>9091593.424850004</v>
       </c>
       <c r="BD5" t="n">
-        <v>-2724.272486772486</v>
+        <v>1.153349282296645</v>
       </c>
       <c r="BE5" t="n">
-        <v>0</v>
+        <v>1.458622348939542</v>
       </c>
       <c r="BF5" t="n">
-        <v>-1.827891156462584</v>
-      </c>
-      <c r="BG5" t="inlineStr"/>
+        <v>-3.858525100630345</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>7249853.353841536</v>
+      </c>
       <c r="BH5" t="n">
-        <v>-0.08216374269005655</v>
+        <v>3421.428571428572</v>
       </c>
       <c r="BI5" t="n">
-        <v>59.14031620553359</v>
+        <v>4.941336434573842</v>
       </c>
       <c r="BJ5" t="n">
-        <v>6350098.814229248</v>
+        <v>-86.67857142857143</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.8063241106719368</v>
+        <v>3.204241664767963</v>
       </c>
       <c r="BL5" t="n">
-        <v>10927.77777777778</v>
+        <v>-1.152597402597403</v>
       </c>
       <c r="BM5" t="n">
-        <v>1.697628458498023</v>
+        <v>-74.40584415584415</v>
       </c>
       <c r="BN5" t="n">
-        <v>-5.257582199546476</v>
+        <v>6.07155008733956</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.7193675889328064</v>
+        <v>0.2693025210084035</v>
       </c>
       <c r="BP5" t="n">
-        <v>1.917259552042168</v>
+        <v>-1.00974025974026</v>
       </c>
       <c r="BQ5" t="n">
-        <v>-1.603245464852606</v>
-      </c>
-      <c r="BR5" t="n">
-        <v>-3.001644736842103</v>
-      </c>
+        <v>1.507792207792221</v>
+      </c>
+      <c r="BR5" t="inlineStr"/>
       <c r="BS5" t="n">
-        <v>0.8474049707602376</v>
+        <v>1.132890356142454</v>
       </c>
       <c r="BT5" t="n">
-        <v>6964.640022675972</v>
+        <v>2.504547919167678</v>
       </c>
       <c r="BU5" t="n">
-        <v>1.730739795918353</v>
+        <v>3012012.987012988</v>
       </c>
       <c r="BV5" t="n">
-        <v>-4.180884502923973</v>
+        <v>13822.81746031746</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>vuBo4Eth</t>
+          <t>l8H0Dwy3</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45598.70833333334</v>
+        <v>45606.45833333334</v>
       </c>
       <c r="C6" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D6" t="n">
         <v>133</v>
       </c>
       <c r="E6" t="n">
-        <v>528</v>
+        <v>535</v>
       </c>
       <c r="F6" t="n">
-        <v>516</v>
+        <v>545</v>
       </c>
       <c r="G6" t="n">
         <v>55</v>
@@ -1732,205 +1754,215 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>35</v>
+        <v>9</v>
       </c>
       <c r="M6" t="n">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>1.016666666666667</v>
+        <v>0.3485</v>
       </c>
       <c r="P6" t="n">
-        <v>0.4980718954248367</v>
+        <v>0.7727272727272727</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.5</v>
+        <v>0.2999999999999998</v>
       </c>
       <c r="R6" t="n">
-        <v>1.105263157894737</v>
+        <v>1.090909090909091</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.3333333333333335</v>
+        <v>0.8500000000000001</v>
       </c>
       <c r="T6" t="n">
-        <v>1.555555555555556</v>
+        <v>1.65530303030303</v>
       </c>
       <c r="U6" t="n">
-        <v>1.5</v>
+        <v>-5.199999999999999</v>
       </c>
       <c r="V6" t="n">
-        <v>4.333333333333332</v>
+        <v>2.344696969696971</v>
       </c>
       <c r="W6" t="n">
-        <v>1.333333333333333</v>
+        <v>1.05</v>
       </c>
       <c r="X6" t="n">
-        <v>0.5263157894736842</v>
+        <v>0.7424242424242424</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.5</v>
+        <v>0.3</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.421052631578947</v>
+        <v>0.8409090909090908</v>
       </c>
       <c r="AA6" t="n">
-        <v>22.63034188034188</v>
+        <v>23.58265660809779</v>
       </c>
       <c r="AB6" t="n">
-        <v>19.40838621255288</v>
+        <v>19.06605241760945</v>
       </c>
       <c r="AC6" t="n">
-        <v>1041.577601301818</v>
+        <v>977.0849657927141</v>
       </c>
       <c r="AD6" t="n">
-        <v>835.9396384239933</v>
-      </c>
-      <c r="AE6" t="inlineStr"/>
+        <v>978.986566714329</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>-72</v>
+      </c>
       <c r="AF6" t="n">
-        <v>16.75</v>
-      </c>
-      <c r="AG6" t="inlineStr"/>
+        <v>-14.68170426065163</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>-44</v>
+      </c>
       <c r="AH6" t="n">
-        <v>20</v>
+        <v>0.3734335839599012</v>
       </c>
       <c r="AI6" t="n">
-        <v>-11.5</v>
+        <v>4.5</v>
       </c>
       <c r="AJ6" t="n">
-        <v>2.315789473684211</v>
+        <v>0.553030303030301</v>
       </c>
       <c r="AK6" t="n">
-        <v>-9.333333333333336</v>
+        <v>-26</v>
       </c>
       <c r="AL6" t="n">
-        <v>7.777777777777771</v>
+        <v>-14.48484848484848</v>
       </c>
       <c r="AM6" t="n">
-        <v>-208</v>
+        <v>-323.5</v>
       </c>
       <c r="AN6" t="n">
-        <v>69</v>
+        <v>-140.0366132723112</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.3333333333333335</v>
+        <v>-1.35</v>
       </c>
       <c r="AP6" t="n">
-        <v>0.4673202614379086</v>
-      </c>
-      <c r="AQ6" t="inlineStr"/>
-      <c r="AR6" t="inlineStr"/>
+        <v>-0.8142292490118577</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>0.3333333333333333</v>
+      </c>
       <c r="AS6" t="n">
-        <v>3.499999999999998</v>
+        <v>-4.800000000000001</v>
       </c>
       <c r="AT6" t="n">
-        <v>2.999999999999993</v>
+        <v>1.151515151515156</v>
       </c>
       <c r="AU6" t="n">
-        <v>18.2793956043956</v>
+        <v>11.17560581841432</v>
       </c>
       <c r="AV6" t="n">
-        <v>-0.1858267428468388</v>
-      </c>
-      <c r="AW6" t="inlineStr"/>
+        <v>4.664279349457534</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>-0.009776440490726207</v>
+      </c>
       <c r="AX6" t="n">
-        <v>-0.001322671721763272</v>
+        <v>-0.01562036321814352</v>
       </c>
       <c r="AY6" t="n">
-        <v>0</v>
+        <v>-0.15</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0.1578947368421053</v>
+        <v>0.2462121212121213</v>
       </c>
       <c r="BA6" t="n">
-        <v>110.4782608695652</v>
+        <v>-2.622222222222224</v>
       </c>
       <c r="BB6" t="n">
-        <v>-0.2427777777777778</v>
+        <v>-0.001952214452214163</v>
       </c>
       <c r="BC6" t="n">
-        <v>-2292110.992739899</v>
+        <v>-1592012.305749808</v>
       </c>
       <c r="BD6" t="n">
-        <v>-5483.231882496587</v>
+        <v>0.5062373737373775</v>
       </c>
       <c r="BE6" t="n">
-        <v>-0.2635497835497838</v>
+        <v>0.9629518194224147</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.059549687196743</v>
+        <v>3.997585081585072</v>
       </c>
       <c r="BG6" t="n">
-        <v>-6627.206473335506</v>
+        <v>777765.5768795488</v>
       </c>
       <c r="BH6" t="n">
-        <v>-4.459149305555542</v>
+        <v>51962.31884057971</v>
       </c>
       <c r="BI6" t="n">
-        <v>115.2173913043478</v>
+        <v>-1.802811796047067</v>
       </c>
       <c r="BJ6" t="n">
-        <v>-2351086.956521738</v>
+        <v>110.5869565217391</v>
       </c>
       <c r="BK6" t="n">
-        <v>1.695652173913043</v>
+        <v>-0.8564071484071434</v>
       </c>
       <c r="BL6" t="n">
-        <v>-21173.91304347826</v>
+        <v>1.352173913043478</v>
       </c>
       <c r="BM6" t="n">
-        <v>3.105072463768114</v>
+        <v>100.9695652173913</v>
       </c>
       <c r="BN6" t="n">
-        <v>-1.664777759042465</v>
+        <v>-0.07284965034965296</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.1304347826086958</v>
+        <v>0.08142375598257923</v>
       </c>
       <c r="BP6" t="n">
-        <v>-4.065217391304344</v>
+        <v>1.481159420289855</v>
       </c>
       <c r="BQ6" t="n">
-        <v>-2.452174670851136</v>
+        <v>-5.64275362318844</v>
       </c>
       <c r="BR6" t="n">
-        <v>2.632732007575758</v>
+        <v>5308.762626262625</v>
       </c>
       <c r="BS6" t="n">
-        <v>-1.006834490740772</v>
+        <v>-4.11265438809556</v>
       </c>
       <c r="BT6" t="n">
-        <v>-1750214.602063867</v>
+        <v>0.856154841890131</v>
       </c>
       <c r="BU6" t="n">
-        <v>-3.677918309830062</v>
+        <v>18508260.86956522</v>
       </c>
       <c r="BV6" t="n">
-        <v>-0.5994497053872152</v>
+        <v>2129.66676569618</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>n5Eg2hB4</t>
+          <t>dYK8BH5F</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45598.625</v>
+        <v>45605.70833333334</v>
       </c>
       <c r="C7" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D7" t="n">
         <v>133</v>
       </c>
       <c r="E7" t="n">
-        <v>211</v>
+        <v>431</v>
       </c>
       <c r="F7" t="n">
-        <v>370</v>
+        <v>129</v>
       </c>
       <c r="G7" t="n">
         <v>55</v>
@@ -1952,209 +1984,213 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>12</v>
+        <v>67</v>
       </c>
       <c r="M7" t="n">
-        <v>60</v>
+        <v>83</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.4666666666666668</v>
+        <v>-1.892</v>
       </c>
       <c r="P7" t="n">
-        <v>0.4602499999999999</v>
+        <v>-0.7069082125603869</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1</v>
+        <v>-2.4</v>
       </c>
       <c r="R7" t="n">
-        <v>0.1833333333333333</v>
+        <v>-0.7150000000000001</v>
       </c>
       <c r="S7" t="n">
-        <v>3</v>
+        <v>-7.6</v>
       </c>
       <c r="T7" t="n">
-        <v>2.176470588235294</v>
+        <v>-3.103333333333334</v>
       </c>
       <c r="U7" t="n">
+        <v>-12.8</v>
+      </c>
+      <c r="V7" t="n">
+        <v>-3.676666666666668</v>
+      </c>
+      <c r="W7" t="n">
+        <v>-2.4</v>
+      </c>
+      <c r="X7" t="n">
+        <v>-1.46</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>-3</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>-1.155</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>23.35406593406594</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>21.95796322088214</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1421.044829125362</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1106.948187644967</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>-22.5</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>-21.38095238095238</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>4.746753246753237</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>-4.800000000000001</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>-0.8716666666666679</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>-45.2</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>-30.8</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>-777</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>-342.9718614718615</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>2.220446049250313e-16</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>-0.8577075098814233</v>
+      </c>
+      <c r="AQ7" t="n">
         <v>0</v>
       </c>
-      <c r="V7" t="n">
-        <v>6.214705882352941</v>
-      </c>
-      <c r="W7" t="n">
-        <v>2</v>
-      </c>
-      <c r="X7" t="n">
-        <v>0.8833333333333334</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>1.783333333333333</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>21.48131313131313</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>18.25763663167859</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>804.5547290995599</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>856.1488261030743</v>
-      </c>
-      <c r="AE7" t="inlineStr"/>
-      <c r="AF7" t="n">
-        <v>39.38888888888889</v>
-      </c>
-      <c r="AG7" t="inlineStr"/>
-      <c r="AH7" t="n">
-        <v>27.23809523809524</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>-10.33333333333334</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>4.366666666666667</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>3.333333333333329</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>10.65294117647059</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>78.5</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>119.8650793650794</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>3</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>0.9836601307189543</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>1</v>
-      </c>
       <c r="AR7" t="n">
-        <v>0.1666666666666666</v>
+        <v>-0.8</v>
       </c>
       <c r="AS7" t="n">
-        <v>10</v>
+        <v>-3.800000000000001</v>
       </c>
       <c r="AT7" t="n">
-        <v>3.950000000000003</v>
+        <v>0.3099999999999952</v>
       </c>
       <c r="AU7" t="n">
-        <v>-29.22283966033967</v>
+        <v>42.99420164995823</v>
       </c>
       <c r="AV7" t="n">
-        <v>-6.255935633683574</v>
-      </c>
-      <c r="AW7" t="inlineStr"/>
+        <v>11.08970000702708</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>0.1198904288711784</v>
+      </c>
       <c r="AX7" t="n">
-        <v>0.02435362985374841</v>
+        <v>0.04755094145069037</v>
       </c>
       <c r="AY7" t="n">
-        <v>1</v>
+        <v>-0.4</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.6444444444444446</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="BA7" t="n">
-        <v>-95.73529411764706</v>
+        <v>-3.014871794871798</v>
       </c>
       <c r="BB7" t="n">
-        <v>-0.2180944055944056</v>
+        <v>-1.074074074074074</v>
       </c>
       <c r="BC7" t="n">
-        <v>-7582187.257187257</v>
+        <v>-54014822.44318181</v>
       </c>
       <c r="BD7" t="n">
-        <v>-12268.17644671505</v>
+        <v>4.505463489057242</v>
       </c>
       <c r="BE7" t="n">
-        <v>-0.1488545426405079</v>
+        <v>-2.242166694132834</v>
       </c>
       <c r="BF7" t="n">
-        <v>2.534633695375383</v>
+        <v>-1.490283038720492</v>
       </c>
       <c r="BG7" t="n">
-        <v>-15731.28399378399</v>
+        <v>-46198763.49631944</v>
       </c>
       <c r="BH7" t="n">
-        <v>-4.720988733488738</v>
+        <v>-229615.3846153846</v>
       </c>
       <c r="BI7" t="n">
-        <v>-86.86764705882354</v>
+        <v>-14.81761124520077</v>
       </c>
       <c r="BJ7" t="n">
-        <v>-24410784.31372549</v>
+        <v>-15.25384615384615</v>
       </c>
       <c r="BK7" t="n">
-        <v>-1.095588235294118</v>
+        <v>-14.69485216750843</v>
       </c>
       <c r="BL7" t="n">
-        <v>-53764.70588235294</v>
+        <v>0.2538461538461538</v>
       </c>
       <c r="BM7" t="n">
-        <v>1.986111111111111</v>
+        <v>-29.46923076923076</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.037261882272702</v>
+        <v>-12.06760837542087</v>
       </c>
       <c r="BO7" t="n">
-        <v>-1.610294117647059</v>
+        <v>-1.011538461538461</v>
       </c>
       <c r="BP7" t="n">
-        <v>4.895098039215696</v>
+        <v>-3.707692307692307</v>
       </c>
       <c r="BQ7" t="n">
-        <v>-2.193414287651819</v>
+        <v>-8.104230769230725</v>
       </c>
       <c r="BR7" t="n">
-        <v>1.35864413364413</v>
+        <v>-80526.01010101011</v>
       </c>
       <c r="BS7" t="n">
-        <v>-3.769133644133603</v>
+        <v>1.335927205963969</v>
       </c>
       <c r="BT7" t="n">
-        <v>-5472435.285935028</v>
+        <v>-13.96394903228341</v>
       </c>
       <c r="BU7" t="n">
-        <v>-4.763978753556771</v>
-      </c>
-      <c r="BV7" t="n">
-        <v>-3.091540404040387</v>
-      </c>
+        <v>-104358461.5384615</v>
+      </c>
+      <c r="BV7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>rX720WuH</t>
+          <t>bJl87mmp</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45598.54166666666</v>
+        <v>45605.625</v>
       </c>
       <c r="C8" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D8" t="n">
         <v>133</v>
       </c>
       <c r="E8" t="n">
-        <v>206</v>
+        <v>273</v>
       </c>
       <c r="F8" t="n">
-        <v>176</v>
+        <v>599</v>
       </c>
       <c r="G8" t="n">
         <v>55</v>
@@ -2176,207 +2212,213 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>313</v>
+        <v>40</v>
       </c>
       <c r="M8" t="n">
-        <v>204</v>
+        <v>258</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>2.246666666666667</v>
+        <v>0.8869999999999999</v>
       </c>
       <c r="P8" t="n">
-        <v>1.311776315789473</v>
+        <v>0.8586363636363631</v>
       </c>
       <c r="Q8" t="n">
-        <v>3</v>
+        <v>1.95</v>
       </c>
       <c r="R8" t="n">
-        <v>1.894736842105263</v>
+        <v>1.339920948616601</v>
       </c>
       <c r="S8" t="n">
-        <v>3.666666666666667</v>
+        <v>3.35</v>
       </c>
       <c r="T8" t="n">
-        <v>2.213815789473684</v>
+        <v>2.818181818181818</v>
       </c>
       <c r="U8" t="n">
-        <v>10</v>
+        <v>6.550000000000001</v>
       </c>
       <c r="V8" t="n">
-        <v>6.644736842105264</v>
+        <v>7.727272727272728</v>
       </c>
       <c r="W8" t="n">
-        <v>1.333333333333333</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="X8" t="n">
-        <v>1.036184210526316</v>
+        <v>0.8418972332015811</v>
       </c>
       <c r="Y8" t="n">
-        <v>2</v>
+        <v>0.6000000000000001</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.519736842105263</v>
+        <v>0.806324110671937</v>
       </c>
       <c r="AA8" t="n">
-        <v>18.08324915824916</v>
+        <v>16.48176958662253</v>
       </c>
       <c r="AB8" t="n">
-        <v>18.31860651231482</v>
+        <v>17.00419120599734</v>
       </c>
       <c r="AC8" t="n">
-        <v>931.5822393258702</v>
+        <v>815.0452012804587</v>
       </c>
       <c r="AD8" t="n">
-        <v>848.6045219786938</v>
-      </c>
-      <c r="AE8" t="inlineStr"/>
+        <v>832.2974715939531</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>64</v>
+      </c>
       <c r="AF8" t="n">
-        <v>54.5927601809955</v>
-      </c>
-      <c r="AG8" t="inlineStr"/>
+        <v>51.34999999999999</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>34.5</v>
+      </c>
       <c r="AH8" t="n">
-        <v>34.65158371040724</v>
+        <v>34.72631578947369</v>
       </c>
       <c r="AI8" t="n">
-        <v>3.666666666666664</v>
+        <v>7.699999999999996</v>
       </c>
       <c r="AJ8" t="n">
-        <v>9.167763157894733</v>
+        <v>12.01185770750988</v>
       </c>
       <c r="AK8" t="n">
-        <v>-1.333333333333343</v>
+        <v>22.59999999999999</v>
       </c>
       <c r="AL8" t="n">
-        <v>18.04605263157895</v>
+        <v>17.09090909090908</v>
       </c>
       <c r="AM8" t="n">
-        <v>-6.5</v>
+        <v>129</v>
       </c>
       <c r="AN8" t="n">
-        <v>198.8144796380091</v>
+        <v>141.0184210526315</v>
       </c>
       <c r="AO8" t="n">
-        <v>-2.666666666666667</v>
+        <v>-1.4</v>
       </c>
       <c r="AP8" t="n">
-        <v>-1.375</v>
+        <v>-1.014285714285715</v>
       </c>
       <c r="AQ8" t="inlineStr"/>
       <c r="AR8" t="n">
-        <v>0.5</v>
+        <v>1.75</v>
       </c>
       <c r="AS8" t="n">
-        <v>-3.666666666666668</v>
+        <v>5</v>
       </c>
       <c r="AT8" t="n">
-        <v>-7.513157894736842</v>
+        <v>-7.418972332015805</v>
       </c>
       <c r="AU8" t="n">
-        <v>-6.828205128205127</v>
+        <v>-11.14393398268399</v>
       </c>
       <c r="AV8" t="n">
-        <v>-3.010274241173892</v>
-      </c>
-      <c r="AW8" t="inlineStr"/>
+        <v>-0.5934227381620616</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>0.02891066469338704</v>
+      </c>
       <c r="AX8" t="n">
-        <v>0.02562133061452004</v>
+        <v>0.0232806081644242</v>
       </c>
       <c r="AY8" t="n">
-        <v>-0.3333333333333333</v>
+        <v>0.2</v>
       </c>
       <c r="AZ8" t="n">
-        <v>-0.1546052631578947</v>
+        <v>0.3122529644268776</v>
       </c>
       <c r="BA8" t="n">
-        <v>71.2777777777778</v>
+        <v>2.553511042097998</v>
       </c>
       <c r="BB8" t="n">
-        <v>0.9245370370370372</v>
+        <v>-0.2968304843304845</v>
       </c>
       <c r="BC8" t="n">
-        <v>42955590.27777778</v>
+        <v>6202021.901709399</v>
       </c>
       <c r="BD8" t="n">
-        <v>61740.84526916464</v>
+        <v>0.3604967948717963</v>
       </c>
       <c r="BE8" t="n">
-        <v>0.6112034297440996</v>
+        <v>-4.066768946762949</v>
       </c>
       <c r="BF8" t="n">
-        <v>-3.786942921512299</v>
+        <v>-2.612134971510017</v>
       </c>
       <c r="BG8" t="n">
-        <v>56387.5</v>
+        <v>1947318.169420293</v>
       </c>
       <c r="BH8" t="n">
-        <v>6.826041666666683</v>
+        <v>9038.043478260872</v>
       </c>
       <c r="BI8" t="n">
-        <v>63.88425925925927</v>
+        <v>3.892943141388116</v>
       </c>
       <c r="BJ8" t="n">
-        <v>91354629.62962963</v>
+        <v>26.51449275362319</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.6574074074074074</v>
+        <v>2.624528133903127</v>
       </c>
       <c r="BL8" t="n">
-        <v>165578.7037037037</v>
+        <v>0.3152173913043477</v>
       </c>
       <c r="BM8" t="n">
-        <v>-0.8617504409171062</v>
+        <v>27.95471014492753</v>
       </c>
       <c r="BN8" t="n">
-        <v>5.487150648394646</v>
+        <v>3.330484330484339</v>
       </c>
       <c r="BO8" t="n">
-        <v>4.652777777777779</v>
+        <v>0.1862407927001228</v>
       </c>
       <c r="BP8" t="n">
-        <v>16.07379850088182</v>
+        <v>-0.1648550724637681</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.820389359444377</v>
+        <v>-4.255387336093861</v>
       </c>
       <c r="BR8" t="n">
-        <v>-2.94988425925926</v>
+        <v>6687.499999999996</v>
       </c>
       <c r="BS8" t="n">
-        <v>4.399884259259238</v>
+        <v>2.241550813620186</v>
       </c>
       <c r="BT8" t="n">
-        <v>40585806.90342353</v>
+        <v>0.5799471561134339</v>
       </c>
       <c r="BU8" t="n">
-        <v>9.080082397666118</v>
+        <v>3163405.797101451</v>
       </c>
       <c r="BV8" t="n">
-        <v>4.315740740740736</v>
+        <v>6017.731570662192</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>bqYbtBlo</t>
+          <t>figxD9PM</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45597.70833333334</v>
+        <v>45605.54166666666</v>
       </c>
       <c r="C9" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D9" t="n">
         <v>133</v>
       </c>
       <c r="E9" t="n">
-        <v>777</v>
+        <v>736</v>
       </c>
       <c r="F9" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="G9" t="n">
         <v>55</v>
@@ -2398,187 +2440,201 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>97</v>
+        <v>272</v>
       </c>
       <c r="M9" t="n">
-        <v>109</v>
+        <v>32</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.5366666666666672</v>
+        <v>-0.2625</v>
       </c>
       <c r="P9" t="n">
-        <v>0.8171323529411763</v>
+        <v>0.002608695652173143</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1</v>
+        <v>-0.1500000000000001</v>
       </c>
       <c r="R9" t="n">
-        <v>1.040247678018576</v>
+        <v>0.3967391304347826</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.6666666666666665</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>2.736111111111112</v>
+        <v>0.1938405797101455</v>
       </c>
       <c r="U9" t="n">
-        <v>3.333333333333332</v>
+        <v>-2</v>
       </c>
       <c r="V9" t="n">
-        <v>6.888888888888889</v>
+        <v>0.304347826086957</v>
       </c>
       <c r="W9" t="n">
-        <v>-1.166666666666667</v>
+        <v>-0.25</v>
       </c>
       <c r="X9" t="n">
-        <v>1.226006191950464</v>
+        <v>-0.4474637681159421</v>
       </c>
       <c r="Y9" t="n">
-        <v>-0.5</v>
+        <v>0.3000000000000003</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.1486068111455108</v>
+        <v>-0.7282608695652173</v>
       </c>
       <c r="AA9" t="n">
-        <v>13.74509379509379</v>
+        <v>19.04541190835308</v>
       </c>
       <c r="AB9" t="n">
-        <v>15.48217202346932</v>
-      </c>
-      <c r="AC9" t="inlineStr"/>
+        <v>20.28545924190426</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>960.5680747456265</v>
+      </c>
       <c r="AD9" t="n">
-        <v>896.1360910503383</v>
-      </c>
-      <c r="AE9" t="inlineStr"/>
+        <v>972.1835593333678</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>-49.5</v>
+      </c>
       <c r="AF9" t="n">
-        <v>35.14285714285715</v>
-      </c>
-      <c r="AG9" t="inlineStr"/>
+        <v>-22.86363636363636</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>-21.5</v>
+      </c>
       <c r="AH9" t="n">
-        <v>16.80357142857143</v>
+        <v>-0.5909090909090864</v>
       </c>
       <c r="AI9" t="n">
-        <v>-4.333333333333329</v>
+        <v>1.099999999999994</v>
       </c>
       <c r="AJ9" t="n">
-        <v>7.786377708978328</v>
+        <v>-1.018115942028984</v>
       </c>
       <c r="AK9" t="n">
-        <v>12.33333333333333</v>
+        <v>-19.3</v>
       </c>
       <c r="AL9" t="n">
-        <v>5.430555555555557</v>
-      </c>
-      <c r="AM9" t="inlineStr"/>
+        <v>-17.65217391304348</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>-151</v>
+      </c>
       <c r="AN9" t="n">
-        <v>56.00980392156862</v>
+        <v>-168.6863636363636</v>
       </c>
       <c r="AO9" t="n">
-        <v>0</v>
+        <v>-0.9500000000000002</v>
       </c>
       <c r="AP9" t="n">
-        <v>-0.3333333333333333</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="AQ9" t="inlineStr"/>
       <c r="AR9" t="n">
-        <v>1.25</v>
+        <v>-1</v>
       </c>
       <c r="AS9" t="n">
-        <v>4.833333333333332</v>
+        <v>-1.4</v>
       </c>
       <c r="AT9" t="n">
-        <v>-1.263157894736846</v>
-      </c>
-      <c r="AU9" t="inlineStr"/>
+        <v>-0.911231884057969</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>13.34281458752283</v>
+      </c>
       <c r="AV9" t="n">
-        <v>-0.5438928805307466</v>
-      </c>
-      <c r="AW9" t="inlineStr"/>
+        <v>6.083197539112042</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>-0.05207654868671815</v>
+      </c>
       <c r="AX9" t="n">
-        <v>-0.008946652742442537</v>
+        <v>0.01372764796662495</v>
       </c>
       <c r="AY9" t="n">
-        <v>-0.3333333333333333</v>
+        <v>-0.3</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.2012383900928792</v>
+        <v>-0.1666666666666667</v>
       </c>
       <c r="BA9" t="n">
-        <v>-83.16666666666666</v>
+        <v>1.820652173913043</v>
       </c>
       <c r="BB9" t="n">
-        <v>-0.3533508158508161</v>
+        <v>-0.1471794871794871</v>
       </c>
       <c r="BC9" t="n">
-        <v>919963.8209013231</v>
+        <v>-10322132.47863248</v>
       </c>
       <c r="BD9" t="n">
-        <v>-21923.33333333334</v>
+        <v>-0.1124358974358977</v>
       </c>
       <c r="BE9" t="n">
-        <v>-0.7530161505161506</v>
+        <v>3.71545375318226</v>
       </c>
       <c r="BF9" t="n">
-        <v>-1.770503663003666</v>
-      </c>
-      <c r="BG9" t="inlineStr"/>
+        <v>3.710527065527089</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>-5806553.02414063</v>
+      </c>
       <c r="BH9" t="n">
-        <v>2.421639471639466</v>
+        <v>-124130.4347826087</v>
       </c>
       <c r="BI9" t="n">
-        <v>-74.05555555555554</v>
+        <v>0.05897847356295927</v>
       </c>
       <c r="BJ9" t="n">
-        <v>-15850000</v>
+        <v>-183.3913043478261</v>
       </c>
       <c r="BK9" t="n">
-        <v>-1</v>
+        <v>-2.976581196581208</v>
       </c>
       <c r="BL9" t="n">
-        <v>-63470.58823529411</v>
+        <v>-2.043478260869565</v>
       </c>
       <c r="BM9" t="n">
-        <v>4.111111111111111</v>
+        <v>-166.9565217391304</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.659990842490856</v>
+        <v>-3.953404558404543</v>
       </c>
       <c r="BO9" t="n">
-        <v>-1.611111111111111</v>
+        <v>0.1523114143474253</v>
       </c>
       <c r="BP9" t="n">
-        <v>9.870370370370381</v>
+        <v>-2</v>
       </c>
       <c r="BQ9" t="n">
-        <v>-4.151222666222679</v>
+        <v>4.761801242236004</v>
       </c>
       <c r="BR9" t="n">
-        <v>-0.3872474747474755</v>
+        <v>-26962.71604938271</v>
       </c>
       <c r="BS9" t="n">
-        <v>0.2633644133643713</v>
+        <v>3.225365436348817</v>
       </c>
       <c r="BT9" t="n">
-        <v>-7595234.258796759</v>
+        <v>-4.425276578351372</v>
       </c>
       <c r="BU9" t="n">
-        <v>-1.03398906648907</v>
+        <v>-59778260.86956522</v>
       </c>
       <c r="BV9" t="n">
-        <v>1.295677933177927</v>
+        <v>-4859.487734487735</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>0ljCkFRb</t>
+          <t>Gp6AbAAT</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45597.625</v>
+        <v>45604.69791666666</v>
       </c>
       <c r="C10" t="n">
         <v>102</v>
@@ -2587,10 +2643,10 @@
         <v>133</v>
       </c>
       <c r="E10" t="n">
-        <v>47</v>
+        <v>448</v>
       </c>
       <c r="F10" t="n">
-        <v>292</v>
+        <v>228</v>
       </c>
       <c r="G10" t="n">
         <v>55</v>
@@ -2612,186 +2668,192 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>193</v>
+        <v>168</v>
       </c>
       <c r="M10" t="n">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>2.12</v>
+        <v>0.7950000000000002</v>
       </c>
       <c r="P10" t="n">
-        <v>0.8927205882352939</v>
+        <v>1.140802005012531</v>
       </c>
       <c r="Q10" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="R10" t="n">
-        <v>0.7875000000000001</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="S10" t="n">
-        <v>4.666666666666666</v>
+        <v>3.100000000000001</v>
       </c>
       <c r="T10" t="n">
-        <v>2.466911764705883</v>
+        <v>2.049523809523809</v>
       </c>
       <c r="U10" t="n">
-        <v>13.66666666666667</v>
+        <v>0.9000000000000004</v>
       </c>
       <c r="V10" t="n">
-        <v>9.404411764705882</v>
+        <v>2.04952380952381</v>
       </c>
       <c r="W10" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0.5502645502645503</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1.063492063492063</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>20.43316995504495</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>20.32532863432863</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>903.0457789515091</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>913.5067732684679</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>-23</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>-5.84210526315789</v>
+      </c>
+      <c r="AG10" t="n">
         <v>1</v>
       </c>
-      <c r="X10" t="n">
-        <v>0.7375</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>1.0875</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>13.32791005291005</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>15.69023071957749</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>784.0622351799401</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>841.0297087191032</v>
-      </c>
-      <c r="AE10" t="inlineStr"/>
-      <c r="AF10" t="n">
-        <v>41.72820512820512</v>
-      </c>
-      <c r="AG10" t="inlineStr"/>
       <c r="AH10" t="n">
-        <v>13.79487179487179</v>
+        <v>7.511961722488039</v>
       </c>
       <c r="AI10" t="n">
-        <v>19</v>
+        <v>8.25</v>
       </c>
       <c r="AJ10" t="n">
-        <v>4.4</v>
+        <v>5.132275132275128</v>
       </c>
       <c r="AK10" t="n">
-        <v>47.33333333333334</v>
+        <v>9.5</v>
       </c>
       <c r="AL10" t="n">
-        <v>17.50735294117646</v>
+        <v>-1.154285714285706</v>
       </c>
       <c r="AM10" t="n">
-        <v>161</v>
+        <v>-14.5</v>
       </c>
       <c r="AN10" t="n">
-        <v>92.38461538461536</v>
+        <v>-51.53884711779443</v>
       </c>
       <c r="AO10" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0.8</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.3647058823529408</v>
+        <v>-0.7559523809523809</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="AR10" t="n">
-        <v>0.4666666666666667</v>
+        <v>-0.8333333333333334</v>
       </c>
       <c r="AS10" t="n">
-        <v>-4.333333333333332</v>
+        <v>-1.049999999999999</v>
       </c>
       <c r="AT10" t="n">
-        <v>7.125</v>
+        <v>1.74074074074074</v>
       </c>
       <c r="AU10" t="n">
-        <v>4.26209330143541</v>
+        <v>-2.34494047619048</v>
       </c>
       <c r="AV10" t="n">
-        <v>-3.687551366574661</v>
-      </c>
-      <c r="AW10" t="inlineStr"/>
+        <v>0.5925353699102658</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>-0.08943771594172323</v>
+      </c>
       <c r="AX10" t="n">
-        <v>0.002298557086179862</v>
+        <v>-0.01258518504703823</v>
       </c>
       <c r="AY10" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.5</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="BA10" t="n">
-        <v>-79.08695652173913</v>
+        <v>0.6540277777777774</v>
       </c>
       <c r="BB10" t="n">
-        <v>0.3899572649572649</v>
+        <v>0.1805555555555556</v>
       </c>
       <c r="BC10" t="n">
-        <v>13194843.81070319</v>
-      </c>
-      <c r="BD10" t="inlineStr"/>
+        <v>14137465.80387205</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>-0.8385732323232311</v>
+      </c>
       <c r="BE10" t="n">
-        <v>0.1112383692023584</v>
+        <v>1.387996147776875</v>
       </c>
       <c r="BF10" t="n">
-        <v>-3.961197953504861</v>
+        <v>1.169065656565635</v>
       </c>
       <c r="BG10" t="n">
-        <v>35029.09652076318</v>
+        <v>9158911.169442967</v>
       </c>
       <c r="BH10" t="n">
-        <v>9.025692623348874</v>
+        <v>90916.66666666667</v>
       </c>
       <c r="BI10" t="n">
-        <v>-65.26086956521738</v>
+        <v>9.762474093482865</v>
       </c>
       <c r="BJ10" t="n">
-        <v>60904347.82608695</v>
+        <v>105.025</v>
       </c>
       <c r="BK10" t="n">
-        <v>-1.652173913043478</v>
+        <v>9.893918350168363</v>
       </c>
       <c r="BL10" t="n">
-        <v>166304.3478260869</v>
+        <v>1.266666666666667</v>
       </c>
       <c r="BM10" t="n">
-        <v>-0.7590579710144887</v>
+        <v>104.675</v>
       </c>
       <c r="BN10" t="n">
-        <v>-2.686715070992733</v>
+        <v>8.689183501683502</v>
       </c>
       <c r="BO10" t="n">
-        <v>-0.1304347826086953</v>
+        <v>0.1812987012987013</v>
       </c>
       <c r="BP10" t="n">
-        <v>-3.94658385093166</v>
+        <v>2.475</v>
       </c>
       <c r="BQ10" t="n">
-        <v>5.41240421619753</v>
+        <v>-1.958888888888879</v>
       </c>
       <c r="BR10" t="n">
-        <v>-3.862657221250974</v>
+        <v>33059.54218106996</v>
       </c>
       <c r="BS10" t="n">
-        <v>-3.908577360139873</v>
+        <v>0.613848341392206</v>
       </c>
       <c r="BT10" t="n">
-        <v>8222087.901608052</v>
+        <v>8.357742219606251</v>
       </c>
       <c r="BU10" t="n">
-        <v>10.25697518962249</v>
-      </c>
-      <c r="BV10" t="n">
-        <v>5.871383304195803</v>
-      </c>
+        <v>35238333.33333334</v>
+      </c>
+      <c r="BV10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/france/p6_deployment/data_preparation/df_tagged.xlsx
+++ b/data/france/p6_deployment/data_preparation/df_tagged.xlsx
@@ -690,112 +690,112 @@
       </c>
       <c r="BA1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_hei_player_start</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_wage_player_sub</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_n_player_miss</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_rep_player_miss</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_sub</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rep_player_start</t>
+        </is>
+      </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_wage_player_start</t>
+        </is>
+      </c>
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_sub</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_start</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rep_player_sub</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_sub</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_start</t>
+        </is>
+      </c>
+      <c r="BM1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_age_player_miss</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rep_player_start</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_value_player_start</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_start</t>
-        </is>
-      </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_value_player_miss</t>
+        </is>
+      </c>
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_hei_player_sub</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_start</t>
-        </is>
-      </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_value_player_sub</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_pot_player_miss</t>
+        </is>
+      </c>
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>dif_sum_wage_player_miss</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_sub</t>
-        </is>
-      </c>
-      <c r="BJ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_pot_player_miss</t>
-        </is>
-      </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_pot_player_start</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
-        <is>
-          <t>dif_n_player_miss</t>
-        </is>
-      </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_miss</t>
+        </is>
+      </c>
+      <c r="BV1" s="1" t="inlineStr">
         <is>
           <t>dif_sum_rat_player_miss</t>
-        </is>
-      </c>
-      <c r="BN1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_start</t>
-        </is>
-      </c>
-      <c r="BO1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rep_player_sub</t>
-        </is>
-      </c>
-      <c r="BP1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_rep_player_miss</t>
-        </is>
-      </c>
-      <c r="BQ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_miss</t>
-        </is>
-      </c>
-      <c r="BR1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_wage_player_start</t>
-        </is>
-      </c>
-      <c r="BS1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_sub</t>
-        </is>
-      </c>
-      <c r="BT1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_sub</t>
-        </is>
-      </c>
-      <c r="BU1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_value_player_miss</t>
-        </is>
-      </c>
-      <c r="BV1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_wage_player_sub</t>
         </is>
       </c>
     </row>
@@ -963,68 +963,68 @@
         <v>0.03846153846153849</v>
       </c>
       <c r="BA2" t="n">
+        <v>-0.804332386363626</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>39433.20801747272</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>-0.8333333333333335</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>0.7777777777777777</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>5.63681954873131</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="BG2" t="inlineStr"/>
+      <c r="BH2" t="n">
+        <v>3.156536561389508</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>-1.562499999999996</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>0.9983333333333335</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>9.818788719965184</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>3.997514204545453</v>
+      </c>
+      <c r="BM2" t="n">
         <v>-3.013888888888886</v>
       </c>
-      <c r="BB2" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>9592570.592286501</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>-1.565426997245179</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>-3.044692007052674</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>-0.8295454545454675</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>13014576.88757321</v>
-      </c>
-      <c r="BH2" t="n">
+      <c r="BN2" t="n">
+        <v>9588822.798295455</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>16458333.33333333</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>-3.008203631438903</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>13001399.42893619</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>-42.5</v>
+      </c>
+      <c r="BS2" t="n">
         <v>55970.58823529411</v>
       </c>
-      <c r="BI2" t="n">
-        <v>9.810888264928508</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>-42.5</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>4.905303030303031</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>-0.8333333333333335</v>
-      </c>
-      <c r="BM2" t="n">
+      <c r="BT2" t="n">
+        <v>4.899857954545467</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>-1.668981481481467</v>
+      </c>
+      <c r="BV2" t="n">
         <v>-48.86111111111111</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>3.995179063360879</v>
-      </c>
-      <c r="BO2" t="n">
-        <v>0.9983333333333335</v>
-      </c>
-      <c r="BP2" t="n">
-        <v>0.7777777777777777</v>
-      </c>
-      <c r="BQ2" t="n">
-        <v>-1.668981481481467</v>
-      </c>
-      <c r="BR2" t="inlineStr"/>
-      <c r="BS2" t="n">
-        <v>3.06590715313239</v>
-      </c>
-      <c r="BT2" t="n">
-        <v>5.691621289930112</v>
-      </c>
-      <c r="BU2" t="n">
-        <v>16458333.33333333</v>
-      </c>
-      <c r="BV2" t="n">
-        <v>39469.8352337568</v>
       </c>
     </row>
     <row r="3">
@@ -1189,70 +1189,70 @@
         <v>-0.1757246376811594</v>
       </c>
       <c r="BA3" t="n">
-        <v>3.324715909090909</v>
+        <v>1.484413580246866</v>
       </c>
       <c r="BB3" t="n">
+        <v>-6580.820105820106</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>-0.03939393939393931</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>-0.1303030303030301</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>-3.064365019692104</v>
+      </c>
+      <c r="BF3" t="n">
         <v>-0.125</v>
       </c>
-      <c r="BC3" t="n">
-        <v>-4638490.497076023</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>-1.985380116959064</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>-4.816397564423852</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>1.572953216374231</v>
-      </c>
       <c r="BG3" t="n">
-        <v>-1419514.234590597</v>
+        <v>-11514.5202020202</v>
       </c>
       <c r="BH3" t="n">
-        <v>-1034.722222222223</v>
+        <v>1.220513844134139</v>
       </c>
       <c r="BI3" t="n">
-        <v>-3.300817634746195</v>
+        <v>-1.952160493827162</v>
       </c>
       <c r="BJ3" t="n">
-        <v>-7.988636363636374</v>
+        <v>0</v>
       </c>
       <c r="BK3" t="n">
-        <v>-4.325584795321646</v>
+        <v>-3.35642630385486</v>
       </c>
       <c r="BL3" t="n">
-        <v>-0.02272727272727271</v>
+        <v>-6.827006172839518</v>
       </c>
       <c r="BM3" t="n">
-        <v>-2.01136363636364</v>
+        <v>3.40909090909091</v>
       </c>
       <c r="BN3" t="n">
-        <v>-6.818567251461999</v>
+        <v>-4669448.302469136</v>
       </c>
       <c r="BO3" t="n">
-        <v>0</v>
+        <v>489242.4242424238</v>
       </c>
       <c r="BP3" t="n">
-        <v>-0.1136363636363635</v>
+        <v>-4.770561403508765</v>
       </c>
       <c r="BQ3" t="n">
-        <v>5.308617424242414</v>
+        <v>-1411495.030731591</v>
       </c>
       <c r="BR3" t="n">
-        <v>-11514.5202020202</v>
+        <v>-8.963636363636368</v>
       </c>
       <c r="BS3" t="n">
-        <v>1.29322040219596</v>
+        <v>-355.5555555555566</v>
       </c>
       <c r="BT3" t="n">
-        <v>-3.108448834999592</v>
+        <v>-4.376080246913588</v>
       </c>
       <c r="BU3" t="n">
-        <v>326846.5909090908</v>
+        <v>5.324242424242414</v>
       </c>
       <c r="BV3" t="n">
-        <v>-6580.706727135299</v>
+        <v>-2.836363636363643</v>
       </c>
     </row>
     <row r="4">
@@ -1419,70 +1419,70 @@
         <v>0.04347826086956524</v>
       </c>
       <c r="BA4" t="n">
+        <v>-1.971858696858675</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>-2074.401920123844</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>2.035805626598465</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>2.49616368286445</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>2.384761703638361</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>0.2378760128760129</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>1532.313519813519</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>-1.328167913796477</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>0.4509962259962279</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>0.02823927225855205</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>-1.277991196946545</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>0.8900876900876824</v>
+      </c>
+      <c r="BM4" t="n">
         <v>-0.4086956521739182</v>
       </c>
-      <c r="BB4" t="n">
-        <v>0.2378760128760129</v>
-      </c>
-      <c r="BC4" t="n">
+      <c r="BN4" t="n">
         <v>3341954.573204573</v>
       </c>
-      <c r="BD4" t="n">
-        <v>0.4509962259962279</v>
-      </c>
-      <c r="BE4" t="n">
+      <c r="BO4" t="n">
+        <v>6999552.429667518</v>
+      </c>
+      <c r="BP4" t="n">
         <v>-1.943603022985315</v>
       </c>
-      <c r="BF4" t="n">
-        <v>-1.971858696858675</v>
-      </c>
-      <c r="BG4" t="n">
+      <c r="BQ4" t="n">
         <v>543959.1836726898</v>
       </c>
-      <c r="BH4" t="n">
+      <c r="BR4" t="n">
+        <v>155.4526854219949</v>
+      </c>
+      <c r="BS4" t="n">
         <v>26664.70588235294</v>
       </c>
-      <c r="BI4" t="n">
-        <v>-1.277991196946545</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>155.4526854219949</v>
-      </c>
-      <c r="BK4" t="n">
+      <c r="BT4" t="n">
         <v>1.64756632256632</v>
       </c>
-      <c r="BL4" t="n">
-        <v>2.035805626598465</v>
-      </c>
-      <c r="BM4" t="n">
+      <c r="BU4" t="n">
+        <v>-4.016837169650472</v>
+      </c>
+      <c r="BV4" t="n">
         <v>139.074168797954</v>
-      </c>
-      <c r="BN4" t="n">
-        <v>0.8900876900876824</v>
-      </c>
-      <c r="BO4" t="n">
-        <v>0.02823927225855205</v>
-      </c>
-      <c r="BP4" t="n">
-        <v>2.49616368286445</v>
-      </c>
-      <c r="BQ4" t="n">
-        <v>-4.016837169650472</v>
-      </c>
-      <c r="BR4" t="n">
-        <v>1532.313519813519</v>
-      </c>
-      <c r="BS4" t="n">
-        <v>-1.328167913796477</v>
-      </c>
-      <c r="BT4" t="n">
-        <v>2.384761703638361</v>
-      </c>
-      <c r="BU4" t="n">
-        <v>6999552.429667518</v>
-      </c>
-      <c r="BV4" t="n">
-        <v>-2074.401920123844</v>
       </c>
     </row>
     <row r="5">
@@ -1649,68 +1649,68 @@
         <v>0.2989130434782609</v>
       </c>
       <c r="BA5" t="n">
+        <v>-3.858525100630345</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>13822.81746031746</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>-1.152597402597403</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>-1.00974025974026</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>2.504547919167678</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>0.4646103896103899</v>
+      </c>
+      <c r="BG5" t="inlineStr"/>
+      <c r="BH5" t="n">
+        <v>1.132890356142454</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>1.153349282296645</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>0.2693025210084035</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>4.941336434573842</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>6.07155008733956</v>
+      </c>
+      <c r="BM5" t="n">
         <v>-0.8918831168831183</v>
       </c>
-      <c r="BB5" t="n">
-        <v>0.4646103896103899</v>
-      </c>
-      <c r="BC5" t="n">
+      <c r="BN5" t="n">
         <v>9091593.424850004</v>
       </c>
-      <c r="BD5" t="n">
-        <v>1.153349282296645</v>
-      </c>
-      <c r="BE5" t="n">
+      <c r="BO5" t="n">
+        <v>3012012.987012988</v>
+      </c>
+      <c r="BP5" t="n">
         <v>1.458622348939542</v>
       </c>
-      <c r="BF5" t="n">
-        <v>-3.858525100630345</v>
-      </c>
-      <c r="BG5" t="n">
+      <c r="BQ5" t="n">
         <v>7249853.353841536</v>
       </c>
-      <c r="BH5" t="n">
+      <c r="BR5" t="n">
+        <v>-86.67857142857143</v>
+      </c>
+      <c r="BS5" t="n">
         <v>3421.428571428572</v>
       </c>
-      <c r="BI5" t="n">
-        <v>4.941336434573842</v>
-      </c>
-      <c r="BJ5" t="n">
-        <v>-86.67857142857143</v>
-      </c>
-      <c r="BK5" t="n">
+      <c r="BT5" t="n">
         <v>3.204241664767963</v>
       </c>
-      <c r="BL5" t="n">
-        <v>-1.152597402597403</v>
-      </c>
-      <c r="BM5" t="n">
+      <c r="BU5" t="n">
+        <v>1.507792207792221</v>
+      </c>
+      <c r="BV5" t="n">
         <v>-74.40584415584415</v>
-      </c>
-      <c r="BN5" t="n">
-        <v>6.07155008733956</v>
-      </c>
-      <c r="BO5" t="n">
-        <v>0.2693025210084035</v>
-      </c>
-      <c r="BP5" t="n">
-        <v>-1.00974025974026</v>
-      </c>
-      <c r="BQ5" t="n">
-        <v>1.507792207792221</v>
-      </c>
-      <c r="BR5" t="inlineStr"/>
-      <c r="BS5" t="n">
-        <v>1.132890356142454</v>
-      </c>
-      <c r="BT5" t="n">
-        <v>2.504547919167678</v>
-      </c>
-      <c r="BU5" t="n">
-        <v>3012012.987012988</v>
-      </c>
-      <c r="BV5" t="n">
-        <v>13822.81746031746</v>
       </c>
     </row>
     <row r="6">
@@ -1877,70 +1877,70 @@
         <v>0.2462121212121213</v>
       </c>
       <c r="BA6" t="n">
+        <v>3.997585081585072</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>2129.66676569618</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>1.352173913043478</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>1.481159420289855</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>0.856154841890131</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>-0.001952214452214163</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>5308.762626262625</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>-4.11265438809556</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>0.5062373737373775</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>0.08142375598257923</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>-1.802811796047067</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>-0.07284965034965296</v>
+      </c>
+      <c r="BM6" t="n">
         <v>-2.622222222222224</v>
       </c>
-      <c r="BB6" t="n">
-        <v>-0.001952214452214163</v>
-      </c>
-      <c r="BC6" t="n">
+      <c r="BN6" t="n">
         <v>-1592012.305749808</v>
       </c>
-      <c r="BD6" t="n">
-        <v>0.5062373737373775</v>
-      </c>
-      <c r="BE6" t="n">
+      <c r="BO6" t="n">
+        <v>18508260.86956522</v>
+      </c>
+      <c r="BP6" t="n">
         <v>0.9629518194224147</v>
       </c>
-      <c r="BF6" t="n">
-        <v>3.997585081585072</v>
-      </c>
-      <c r="BG6" t="n">
+      <c r="BQ6" t="n">
         <v>777765.5768795488</v>
       </c>
-      <c r="BH6" t="n">
+      <c r="BR6" t="n">
+        <v>110.5869565217391</v>
+      </c>
+      <c r="BS6" t="n">
         <v>51962.31884057971</v>
       </c>
-      <c r="BI6" t="n">
-        <v>-1.802811796047067</v>
-      </c>
-      <c r="BJ6" t="n">
-        <v>110.5869565217391</v>
-      </c>
-      <c r="BK6" t="n">
+      <c r="BT6" t="n">
         <v>-0.8564071484071434</v>
       </c>
-      <c r="BL6" t="n">
-        <v>1.352173913043478</v>
-      </c>
-      <c r="BM6" t="n">
+      <c r="BU6" t="n">
+        <v>-5.64275362318844</v>
+      </c>
+      <c r="BV6" t="n">
         <v>100.9695652173913</v>
-      </c>
-      <c r="BN6" t="n">
-        <v>-0.07284965034965296</v>
-      </c>
-      <c r="BO6" t="n">
-        <v>0.08142375598257923</v>
-      </c>
-      <c r="BP6" t="n">
-        <v>1.481159420289855</v>
-      </c>
-      <c r="BQ6" t="n">
-        <v>-5.64275362318844</v>
-      </c>
-      <c r="BR6" t="n">
-        <v>5308.762626262625</v>
-      </c>
-      <c r="BS6" t="n">
-        <v>-4.11265438809556</v>
-      </c>
-      <c r="BT6" t="n">
-        <v>0.856154841890131</v>
-      </c>
-      <c r="BU6" t="n">
-        <v>18508260.86956522</v>
-      </c>
-      <c r="BV6" t="n">
-        <v>2129.66676569618</v>
       </c>
     </row>
     <row r="7">
@@ -2107,69 +2107,69 @@
         <v>-0.07000000000000001</v>
       </c>
       <c r="BA7" t="n">
+        <v>-1.484647550776572</v>
+      </c>
+      <c r="BB7" t="inlineStr"/>
+      <c r="BC7" t="n">
+        <v>0.2538461538461538</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>-3.707692307692307</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>-13.97346036803287</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>-1.074074074074074</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>-80543.64095500459</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>1.343281179604713</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>4.465588682524167</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>-1.011538461538461</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>-14.82630979968759</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>-12.11103508200283</v>
+      </c>
+      <c r="BM7" t="n">
         <v>-3.014871794871798</v>
       </c>
-      <c r="BB7" t="n">
-        <v>-1.074074074074074</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>-54014822.44318181</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>4.505463489057242</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>-2.242166694132834</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>-1.490283038720492</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>-46198763.49631944</v>
-      </c>
-      <c r="BH7" t="n">
+      <c r="BN7" t="n">
+        <v>-54019373.57445422</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>-104358461.5384615</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>-2.240044783495648</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>-46200713.52752107</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>-15.25384615384615</v>
+      </c>
+      <c r="BS7" t="n">
         <v>-229615.3846153846</v>
       </c>
-      <c r="BI7" t="n">
-        <v>-14.81761124520077</v>
-      </c>
-      <c r="BJ7" t="n">
-        <v>-15.25384615384615</v>
-      </c>
-      <c r="BK7" t="n">
-        <v>-14.69485216750843</v>
-      </c>
-      <c r="BL7" t="n">
-        <v>0.2538461538461538</v>
-      </c>
-      <c r="BM7" t="n">
+      <c r="BT7" t="n">
+        <v>-14.69157977625721</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>-8.104230769230725</v>
+      </c>
+      <c r="BV7" t="n">
         <v>-29.46923076923076</v>
       </c>
-      <c r="BN7" t="n">
-        <v>-12.06760837542087</v>
-      </c>
-      <c r="BO7" t="n">
-        <v>-1.011538461538461</v>
-      </c>
-      <c r="BP7" t="n">
-        <v>-3.707692307692307</v>
-      </c>
-      <c r="BQ7" t="n">
-        <v>-8.104230769230725</v>
-      </c>
-      <c r="BR7" t="n">
-        <v>-80526.01010101011</v>
-      </c>
-      <c r="BS7" t="n">
-        <v>1.335927205963969</v>
-      </c>
-      <c r="BT7" t="n">
-        <v>-13.96394903228341</v>
-      </c>
-      <c r="BU7" t="n">
-        <v>-104358461.5384615</v>
-      </c>
-      <c r="BV7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -2333,70 +2333,70 @@
         <v>0.3122529644268776</v>
       </c>
       <c r="BA8" t="n">
+        <v>-2.612134971510017</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>6017.731570662192</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>0.3152173913043477</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>-0.1648550724637681</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>0.5799471561134339</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>-0.2968304843304845</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>6687.499999999996</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>2.241550813620186</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>0.3604967948717963</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>0.1862407927001228</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>3.892943141388116</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>3.330484330484339</v>
+      </c>
+      <c r="BM8" t="n">
         <v>2.553511042097998</v>
       </c>
-      <c r="BB8" t="n">
-        <v>-0.2968304843304845</v>
-      </c>
-      <c r="BC8" t="n">
+      <c r="BN8" t="n">
         <v>6202021.901709399</v>
       </c>
-      <c r="BD8" t="n">
-        <v>0.3604967948717963</v>
-      </c>
-      <c r="BE8" t="n">
+      <c r="BO8" t="n">
+        <v>3163405.797101451</v>
+      </c>
+      <c r="BP8" t="n">
         <v>-4.066768946762949</v>
       </c>
-      <c r="BF8" t="n">
-        <v>-2.612134971510017</v>
-      </c>
-      <c r="BG8" t="n">
+      <c r="BQ8" t="n">
         <v>1947318.169420293</v>
       </c>
-      <c r="BH8" t="n">
+      <c r="BR8" t="n">
+        <v>26.51449275362319</v>
+      </c>
+      <c r="BS8" t="n">
         <v>9038.043478260872</v>
       </c>
-      <c r="BI8" t="n">
-        <v>3.892943141388116</v>
-      </c>
-      <c r="BJ8" t="n">
-        <v>26.51449275362319</v>
-      </c>
-      <c r="BK8" t="n">
+      <c r="BT8" t="n">
         <v>2.624528133903127</v>
       </c>
-      <c r="BL8" t="n">
-        <v>0.3152173913043477</v>
-      </c>
-      <c r="BM8" t="n">
+      <c r="BU8" t="n">
+        <v>-4.255387336093861</v>
+      </c>
+      <c r="BV8" t="n">
         <v>27.95471014492753</v>
-      </c>
-      <c r="BN8" t="n">
-        <v>3.330484330484339</v>
-      </c>
-      <c r="BO8" t="n">
-        <v>0.1862407927001228</v>
-      </c>
-      <c r="BP8" t="n">
-        <v>-0.1648550724637681</v>
-      </c>
-      <c r="BQ8" t="n">
-        <v>-4.255387336093861</v>
-      </c>
-      <c r="BR8" t="n">
-        <v>6687.499999999996</v>
-      </c>
-      <c r="BS8" t="n">
-        <v>2.241550813620186</v>
-      </c>
-      <c r="BT8" t="n">
-        <v>0.5799471561134339</v>
-      </c>
-      <c r="BU8" t="n">
-        <v>3163405.797101451</v>
-      </c>
-      <c r="BV8" t="n">
-        <v>6017.731570662192</v>
       </c>
     </row>
     <row r="9">
@@ -2561,70 +2561,70 @@
         <v>-0.1666666666666667</v>
       </c>
       <c r="BA9" t="n">
-        <v>1.820652173913043</v>
+        <v>3.914675925925962</v>
       </c>
       <c r="BB9" t="n">
-        <v>-0.1471794871794871</v>
+        <v>-4859.487734487735</v>
       </c>
       <c r="BC9" t="n">
-        <v>-10322132.47863248</v>
+        <v>-2.059288537549407</v>
       </c>
       <c r="BD9" t="n">
-        <v>-0.1124358974358977</v>
+        <v>-2.039525691699605</v>
       </c>
       <c r="BE9" t="n">
-        <v>3.71545375318226</v>
+        <v>-4.421112316857929</v>
       </c>
       <c r="BF9" t="n">
-        <v>3.710527065527089</v>
+        <v>-0.1380092592592592</v>
       </c>
       <c r="BG9" t="n">
-        <v>-5806553.02414063</v>
+        <v>-27074.21296296296</v>
       </c>
       <c r="BH9" t="n">
-        <v>-124130.4347826087</v>
+        <v>3.226187005002796</v>
       </c>
       <c r="BI9" t="n">
-        <v>0.05897847356295927</v>
+        <v>-0.06916666666666771</v>
       </c>
       <c r="BJ9" t="n">
-        <v>-183.3913043478261</v>
+        <v>0.1461315049472944</v>
       </c>
       <c r="BK9" t="n">
-        <v>-2.976581196581208</v>
+        <v>0.1080145017425735</v>
       </c>
       <c r="BL9" t="n">
-        <v>-2.043478260869565</v>
+        <v>-3.962129629629615</v>
       </c>
       <c r="BM9" t="n">
-        <v>-166.9565217391304</v>
+        <v>1.760457839262187</v>
       </c>
       <c r="BN9" t="n">
-        <v>-3.953404558404543</v>
+        <v>-10371972.22222222</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.1523114143474253</v>
+        <v>-60346640.31620553</v>
       </c>
       <c r="BP9" t="n">
-        <v>-2</v>
+        <v>3.541318441142977</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.761801242236004</v>
+        <v>-5787876.099128295</v>
       </c>
       <c r="BR9" t="n">
-        <v>-26962.71604938271</v>
+        <v>-184.5237154150198</v>
       </c>
       <c r="BS9" t="n">
-        <v>3.225365436348817</v>
+        <v>-125644.2687747036</v>
       </c>
       <c r="BT9" t="n">
-        <v>-4.425276578351372</v>
+        <v>-3.018425925925939</v>
       </c>
       <c r="BU9" t="n">
-        <v>-59778260.86956522</v>
+        <v>4.827555053642016</v>
       </c>
       <c r="BV9" t="n">
-        <v>-4859.487734487735</v>
+        <v>-168.3083003952569</v>
       </c>
     </row>
     <row r="10">
@@ -2791,69 +2791,69 @@
         <v>0.1904761904761905</v>
       </c>
       <c r="BA10" t="n">
+        <v>1.128178335074864</v>
+      </c>
+      <c r="BB10" t="inlineStr"/>
+      <c r="BC10" t="n">
+        <v>1.266666666666667</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>2.475</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>8.342483318686334</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>0.1805555555555556</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>33062.08721833721</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>0.5634825158133445</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>-0.8208050330895134</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>0.1812987012987013</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>9.706325445648744</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>8.707919714385227</v>
+      </c>
+      <c r="BM10" t="n">
         <v>0.6540277777777774</v>
       </c>
-      <c r="BB10" t="n">
-        <v>0.1805555555555556</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>14137465.80387205</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>-0.8385732323232311</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>1.387996147776875</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>1.169065656565635</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>9158911.169442967</v>
-      </c>
-      <c r="BH10" t="n">
+      <c r="BN10" t="n">
+        <v>14139000.18504006</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>35238333.33333334</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>1.406234091722837</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>9153044.356019918</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>105.025</v>
+      </c>
+      <c r="BS10" t="n">
         <v>90916.66666666667</v>
       </c>
-      <c r="BI10" t="n">
-        <v>9.762474093482865</v>
-      </c>
-      <c r="BJ10" t="n">
-        <v>105.025</v>
-      </c>
-      <c r="BK10" t="n">
-        <v>9.893918350168363</v>
-      </c>
-      <c r="BL10" t="n">
-        <v>1.266666666666667</v>
-      </c>
-      <c r="BM10" t="n">
+      <c r="BT10" t="n">
+        <v>9.884371734587262</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>-1.958888888888879</v>
+      </c>
+      <c r="BV10" t="n">
         <v>104.675</v>
       </c>
-      <c r="BN10" t="n">
-        <v>8.689183501683502</v>
-      </c>
-      <c r="BO10" t="n">
-        <v>0.1812987012987013</v>
-      </c>
-      <c r="BP10" t="n">
-        <v>2.475</v>
-      </c>
-      <c r="BQ10" t="n">
-        <v>-1.958888888888879</v>
-      </c>
-      <c r="BR10" t="n">
-        <v>33059.54218106996</v>
-      </c>
-      <c r="BS10" t="n">
-        <v>0.613848341392206</v>
-      </c>
-      <c r="BT10" t="n">
-        <v>8.357742219606251</v>
-      </c>
-      <c r="BU10" t="n">
-        <v>35238333.33333334</v>
-      </c>
-      <c r="BV10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/france/p6_deployment/data_preparation/df_tagged.xlsx
+++ b/data/france/p6_deployment/data_preparation/df_tagged.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BV10"/>
+  <dimension ref="A1:BV14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,325 +500,325 @@
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_120_matches_expected_goals_(xg)</t>
+          <t>dif_mean_last_60_matches_expected_goals_(xg)</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_480_matches_expected_goals_(xg)</t>
+          <t>dif_mean_last_360_matches_expected_goals_(xg)</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_120_matches_expected_points</t>
+          <t>dif_mean_last_60_matches_expected_points</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_480_matches_expected_points</t>
+          <t>dif_mean_last_360_matches_expected_points</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_120_matches_shots_on_goal</t>
+          <t>dif_mean_last_60_matches_shots_on_goal</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_480_matches_shots_on_goal</t>
+          <t>dif_mean_last_360_matches_shots_on_goal</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_120_matches_goal_attempts</t>
+          <t>dif_mean_last_60_matches_goal_attempts</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_480_matches_goal_attempts</t>
+          <t>dif_mean_last_360_matches_goal_attempts</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_120_matches_goals</t>
+          <t>dif_mean_last_60_matches_goals</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_480_matches_goals</t>
+          <t>dif_mean_last_360_matches_goals</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_120_matches_points</t>
+          <t>dif_mean_last_60_matches_points</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_480_matches_points</t>
+          <t>dif_mean_last_360_matches_points</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_120_matches_goal_ratio</t>
+          <t>dif_mean_last_60_matches_goal_ratio</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_480_matches_goal_ratio</t>
+          <t>dif_mean_last_360_matches_goal_ratio</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_120_matches_PPS</t>
+          <t>dif_mean_last_60_matches_PPS</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_480_matches_PPS</t>
+          <t>dif_mean_last_360_matches_PPS</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_120_matches_attacks</t>
+          <t>dif_mean_last_60_matches_attacks</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_480_matches_attacks</t>
+          <t>dif_mean_last_360_matches_attacks</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_120_matches_dangerous_attacks</t>
+          <t>dif_mean_last_60_matches_dangerous_attacks</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_480_matches_dangerous_attacks</t>
+          <t>dif_mean_last_360_matches_dangerous_attacks</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_120_matches_dead_balls</t>
+          <t>dif_mean_last_60_matches_dead_balls</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_480_matches_dead_balls</t>
+          <t>dif_mean_last_360_matches_dead_balls</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_120_matches_ball_possession</t>
+          <t>dif_mean_last_60_matches_ball_possession</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_480_matches_ball_possession</t>
+          <t>dif_mean_last_360_matches_ball_possession</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_120_matches_total_passes</t>
+          <t>dif_mean_last_60_matches_total_passes</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_480_matches_total_passes</t>
+          <t>dif_mean_last_360_matches_total_passes</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_120_matches_yellow_cards</t>
+          <t>dif_mean_last_60_matches_yellow_cards</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_480_matches_yellow_cards</t>
+          <t>dif_mean_last_360_matches_yellow_cards</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_120_matches_red_cards</t>
+          <t>dif_mean_last_60_matches_red_cards</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_480_matches_red_cards</t>
+          <t>dif_mean_last_360_matches_red_cards</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_120_matches_defensive_actions</t>
+          <t>dif_mean_last_60_matches_defensive_actions</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_480_matches_defensive_actions</t>
+          <t>dif_mean_last_360_matches_defensive_actions</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_120_matches_PPDA</t>
+          <t>dif_mean_last_60_matches_PPDA</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_480_matches_PPDA</t>
+          <t>dif_mean_last_360_matches_PPDA</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_120_matches_KGP</t>
+          <t>dif_mean_last_60_matches_KGP</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_480_matches_KGP</t>
+          <t>dif_mean_last_360_matches_KGP</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_120_matches_clean_sheet</t>
+          <t>dif_mean_last_60_matches_clean_sheet</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_480_matches_clean_sheet</t>
+          <t>dif_mean_last_360_matches_clean_sheet</t>
         </is>
       </c>
       <c r="BA1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_age_player_sub</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_sub</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_start</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_start</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_value_player_sub</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_sub</t>
+        </is>
+      </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
+          <t>dif_n_player_miss</t>
+        </is>
+      </c>
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_rep_player_miss</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_wage_player_miss</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rep_player_start</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_start</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rep_player_sub</t>
+        </is>
+      </c>
+      <c r="BM1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_pot_player_miss</t>
+        </is>
+      </c>
+      <c r="BN1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_wage_player_start</t>
+        </is>
+      </c>
+      <c r="BO1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_miss</t>
+        </is>
+      </c>
+      <c r="BP1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_wage_player_sub</t>
+        </is>
+      </c>
+      <c r="BQ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_value_player_miss</t>
+        </is>
+      </c>
+      <c r="BR1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_value_player_start</t>
+        </is>
+      </c>
+      <c r="BS1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_hei_player_start</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_wage_player_sub</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_n_player_miss</t>
-        </is>
-      </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_rep_player_miss</t>
-        </is>
-      </c>
-      <c r="BE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_sub</t>
-        </is>
-      </c>
-      <c r="BF1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rep_player_start</t>
-        </is>
-      </c>
-      <c r="BG1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_wage_player_start</t>
-        </is>
-      </c>
-      <c r="BH1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_sub</t>
-        </is>
-      </c>
-      <c r="BI1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_start</t>
-        </is>
-      </c>
-      <c r="BJ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rep_player_sub</t>
-        </is>
-      </c>
-      <c r="BK1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_sub</t>
-        </is>
-      </c>
-      <c r="BL1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_start</t>
-        </is>
-      </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_rat_player_miss</t>
+        </is>
+      </c>
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_age_player_miss</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_value_player_start</t>
-        </is>
-      </c>
-      <c r="BO1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_value_player_miss</t>
-        </is>
-      </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BV1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_hei_player_sub</t>
-        </is>
-      </c>
-      <c r="BQ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_value_player_sub</t>
-        </is>
-      </c>
-      <c r="BR1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_pot_player_miss</t>
-        </is>
-      </c>
-      <c r="BS1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_wage_player_miss</t>
-        </is>
-      </c>
-      <c r="BT1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_start</t>
-        </is>
-      </c>
-      <c r="BU1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_miss</t>
-        </is>
-      </c>
-      <c r="BV1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_rat_player_miss</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>b59ZhlYj</t>
+          <t>GryrQGK8</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45606.69791666666</v>
+        <v>45619.625</v>
       </c>
       <c r="C2" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D2" t="n">
         <v>133</v>
       </c>
       <c r="E2" t="n">
-        <v>56</v>
+        <v>528</v>
       </c>
       <c r="F2" t="n">
-        <v>362</v>
+        <v>157</v>
       </c>
       <c r="G2" t="n">
         <v>55</v>
@@ -840,213 +840,207 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>243</v>
+        <v>272</v>
       </c>
       <c r="M2" t="n">
-        <v>258</v>
+        <v>67</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>2.468</v>
+        <v>2.813333333333333</v>
       </c>
       <c r="P2" t="n">
-        <v>0.6911538461538458</v>
+        <v>1.681041666666667</v>
       </c>
       <c r="Q2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R2" t="n">
-        <v>0.6923076923076922</v>
+        <v>2.614035087719298</v>
       </c>
       <c r="S2" t="n">
-        <v>6.199999999999999</v>
+        <v>2</v>
       </c>
       <c r="T2" t="n">
-        <v>0.2999999999999998</v>
+        <v>3.091503267973856</v>
       </c>
       <c r="U2" t="n">
-        <v>8.599999999999998</v>
+        <v>8.333333333333332</v>
       </c>
       <c r="V2" t="n">
-        <v>0.7692307692307683</v>
+        <v>9.52941176470588</v>
       </c>
       <c r="W2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="X2" t="n">
-        <v>0.1923076923076923</v>
+        <v>1.134502923976608</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.4</v>
+        <v>4</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.346153846153846</v>
+        <v>1.43859649122807</v>
       </c>
       <c r="AA2" t="n">
-        <v>18.15321369806664</v>
+        <v>18.73080993080993</v>
       </c>
       <c r="AB2" t="n">
-        <v>21.97742432404398</v>
+        <v>18.62351910120228</v>
       </c>
       <c r="AC2" t="n">
-        <v>694.055937987128</v>
+        <v>1082.572233516092</v>
       </c>
       <c r="AD2" t="n">
-        <v>907.357706627157</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>17</v>
-      </c>
+        <v>808.6021141197862</v>
+      </c>
+      <c r="AE2" t="inlineStr"/>
       <c r="AF2" t="n">
-        <v>5.990118577075094</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>35</v>
-      </c>
+        <v>26.00952380952383</v>
+      </c>
+      <c r="AG2" t="inlineStr"/>
       <c r="AH2" t="n">
-        <v>12.96047430830039</v>
+        <v>27.65238095238095</v>
       </c>
       <c r="AI2" t="n">
-        <v>4.200000000000003</v>
+        <v>-3</v>
       </c>
       <c r="AJ2" t="n">
-        <v>2.346153846153847</v>
+        <v>1.795321637426898</v>
       </c>
       <c r="AK2" t="n">
-        <v>15.2</v>
+        <v>-18</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.14769230769231</v>
+        <v>9.973856209150327</v>
       </c>
       <c r="AM2" t="n">
-        <v>255.5</v>
+        <v>-318</v>
       </c>
       <c r="AN2" t="n">
-        <v>-24.87445887445892</v>
+        <v>62.70535714285717</v>
       </c>
       <c r="AO2" t="n">
-        <v>-2.399999999999999</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="AP2" t="n">
-        <v>-0.6399999999999999</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>0</v>
-      </c>
+        <v>-0.2352941176470591</v>
+      </c>
+      <c r="AQ2" t="inlineStr"/>
       <c r="AR2" t="n">
-        <v>0.6666666666666666</v>
+        <v>-0.6666666666666667</v>
       </c>
       <c r="AS2" t="n">
-        <v>-8.600000000000001</v>
+        <v>8.666666666666664</v>
       </c>
       <c r="AT2" t="n">
-        <v>-2.730769230769226</v>
+        <v>5.918128654970758</v>
       </c>
       <c r="AU2" t="n">
-        <v>11.69164351851852</v>
+        <v>6.318141341417205</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.3328073073568</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>0.01750592976672802</v>
-      </c>
+        <v>-1.679622086236375</v>
+      </c>
+      <c r="AW2" t="inlineStr"/>
       <c r="AX2" t="n">
-        <v>0.02836838310231009</v>
+        <v>0.002038076485852941</v>
       </c>
       <c r="AY2" t="n">
-        <v>0.6</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.03846153846153849</v>
+        <v>0.2690058479532164</v>
       </c>
       <c r="BA2" t="n">
-        <v>-0.804332386363626</v>
+        <v>1.502354163270446</v>
       </c>
       <c r="BB2" t="n">
-        <v>39433.20801747272</v>
+        <v>-0.4973509269889149</v>
       </c>
       <c r="BC2" t="n">
-        <v>-0.8333333333333335</v>
+        <v>-0.3442460317460352</v>
       </c>
       <c r="BD2" t="n">
-        <v>0.7777777777777777</v>
+        <v>-3.3958897005772</v>
       </c>
       <c r="BE2" t="n">
-        <v>5.63681954873131</v>
+        <v>-1463108.937376471</v>
       </c>
       <c r="BF2" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="BG2" t="inlineStr"/>
+        <v>-3.165570413251402</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>-0.7318840579710142</v>
+      </c>
       <c r="BH2" t="n">
-        <v>3.156536561389508</v>
+        <v>-1.427536231884058</v>
       </c>
       <c r="BI2" t="n">
-        <v>-1.562499999999996</v>
+        <v>-32400</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.9983333333333335</v>
+        <v>-0.4146825396825395</v>
       </c>
       <c r="BK2" t="n">
-        <v>9.818788719965184</v>
+        <v>-3.007434839466086</v>
       </c>
       <c r="BL2" t="n">
-        <v>3.997514204545453</v>
+        <v>-0.1982043597428214</v>
       </c>
       <c r="BM2" t="n">
-        <v>-3.013888888888886</v>
+        <v>-69.55072463768116</v>
       </c>
       <c r="BN2" t="n">
-        <v>9588822.798295455</v>
+        <v>-10586.65281850765</v>
       </c>
       <c r="BO2" t="n">
-        <v>16458333.33333333</v>
+        <v>0.07035024154586722</v>
       </c>
       <c r="BP2" t="n">
-        <v>-3.008203631438903</v>
+        <v>-5548.754743473996</v>
       </c>
       <c r="BQ2" t="n">
-        <v>13001399.42893619</v>
+        <v>-7513768.115942028</v>
       </c>
       <c r="BR2" t="n">
-        <v>-42.5</v>
+        <v>-4670370.417343073</v>
       </c>
       <c r="BS2" t="n">
-        <v>55970.58823529411</v>
+        <v>2.294411751442965</v>
       </c>
       <c r="BT2" t="n">
-        <v>4.899857954545467</v>
+        <v>-51.03985507246378</v>
       </c>
       <c r="BU2" t="n">
-        <v>-1.668981481481467</v>
+        <v>2.561473429951693</v>
       </c>
       <c r="BV2" t="n">
-        <v>-48.86111111111111</v>
+        <v>1.241577693274536</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>nRkUEVfA</t>
+          <t>SMfm4Zck</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45606.54166666666</v>
+        <v>45619.54166666666</v>
       </c>
       <c r="C3" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D3" t="n">
         <v>133</v>
       </c>
       <c r="E3" t="n">
-        <v>194</v>
+        <v>273</v>
       </c>
       <c r="F3" t="n">
-        <v>579</v>
+        <v>303</v>
       </c>
       <c r="G3" t="n">
         <v>55</v>
@@ -1068,213 +1062,209 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>198</v>
+        <v>40</v>
       </c>
       <c r="M3" t="n">
-        <v>10</v>
+        <v>258</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.4200000000000002</v>
+        <v>-0.438333333333333</v>
       </c>
       <c r="P3" t="n">
-        <v>0.2163636363636361</v>
+        <v>0.4228676470588231</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.5999999999999999</v>
+        <v>-1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.5054347826086957</v>
+        <v>0.5392156862745097</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.2000000000000011</v>
+        <v>1</v>
       </c>
       <c r="T3" t="n">
-        <v>0.7806324110671934</v>
+        <v>2.904411764705882</v>
       </c>
       <c r="U3" t="n">
-        <v>-3.800000000000001</v>
+        <v>1.5</v>
       </c>
       <c r="V3" t="n">
-        <v>1.594861660079051</v>
+        <v>3.11029411764706</v>
       </c>
       <c r="W3" t="n">
-        <v>-1.6</v>
+        <v>-2.666666666666667</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.1793478260869565</v>
+        <v>-0.4791666666666667</v>
       </c>
       <c r="Y3" t="n">
-        <v>-0.6000000000000001</v>
+        <v>-2</v>
       </c>
       <c r="Z3" t="n">
-        <v>-0.1413043478260869</v>
+        <v>0.01960784313725461</v>
       </c>
       <c r="AA3" t="n">
-        <v>22.98590270840271</v>
+        <v>21.23667998667999</v>
       </c>
       <c r="AB3" t="n">
-        <v>20.3141902780066</v>
+        <v>20.03143009467313</v>
       </c>
       <c r="AC3" t="n">
-        <v>1067.732748886656</v>
+        <v>957.5667327014309</v>
       </c>
       <c r="AD3" t="n">
-        <v>934.0496687217203</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>-31.5</v>
-      </c>
+        <v>972.6379834555144</v>
+      </c>
+      <c r="AE3" t="inlineStr"/>
       <c r="AF3" t="n">
-        <v>-11.33157894736841</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>-9.5</v>
-      </c>
+        <v>-0.401098901098905</v>
+      </c>
+      <c r="AG3" t="inlineStr"/>
       <c r="AH3" t="n">
-        <v>6.671052631578945</v>
+        <v>2.736263736263737</v>
       </c>
       <c r="AI3" t="n">
-        <v>-2.000000000000004</v>
+        <v>0.3333333333333357</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.621376811594196</v>
+        <v>3.323529411764707</v>
       </c>
       <c r="AK3" t="n">
-        <v>-20.40000000000001</v>
+        <v>-19</v>
       </c>
       <c r="AL3" t="n">
-        <v>-11.61660079051384</v>
+        <v>-12.11029411764706</v>
       </c>
       <c r="AM3" t="n">
-        <v>-393</v>
+        <v>-275.5</v>
       </c>
       <c r="AN3" t="n">
-        <v>-136.8523809523809</v>
+        <v>-129.7857142857143</v>
       </c>
       <c r="AO3" t="n">
-        <v>-1</v>
+        <v>-0.1666666666666667</v>
       </c>
       <c r="AP3" t="n">
-        <v>-0.6326086956521739</v>
-      </c>
-      <c r="AQ3" t="inlineStr"/>
+        <v>0.02745098039215699</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>2</v>
+      </c>
       <c r="AR3" t="n">
-        <v>-2</v>
+        <v>1.2</v>
       </c>
       <c r="AS3" t="n">
-        <v>-0.6000000000000014</v>
+        <v>8.666666666666668</v>
       </c>
       <c r="AT3" t="n">
-        <v>-3.172101449275367</v>
+        <v>-1.267973856209146</v>
       </c>
       <c r="AU3" t="n">
-        <v>4.222235902310505</v>
+        <v>9.321024309273934</v>
       </c>
       <c r="AV3" t="n">
-        <v>4.019923079332992</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>-0.003350309248911221</v>
-      </c>
+        <v>5.074997718499862</v>
+      </c>
+      <c r="AW3" t="inlineStr"/>
       <c r="AX3" t="n">
-        <v>-0.005206338595952091</v>
+        <v>0.03106097615582111</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="AZ3" t="n">
-        <v>-0.1757246376811594</v>
+        <v>0.3431372549019608</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.484413580246866</v>
+        <v>3.102447569139294</v>
       </c>
       <c r="BB3" t="n">
-        <v>-6580.820105820106</v>
+        <v>-0.8182416539183492</v>
       </c>
       <c r="BC3" t="n">
-        <v>-0.03939393939393931</v>
+        <v>0.543146135265701</v>
       </c>
       <c r="BD3" t="n">
-        <v>-0.1303030303030301</v>
+        <v>-1.11089975845411</v>
       </c>
       <c r="BE3" t="n">
-        <v>-3.064365019692104</v>
+        <v>-3750635.259686011</v>
       </c>
       <c r="BF3" t="n">
-        <v>-0.125</v>
+        <v>-3.974461152882213</v>
       </c>
       <c r="BG3" t="n">
-        <v>-11514.5202020202</v>
+        <v>-1.434782608695652</v>
       </c>
       <c r="BH3" t="n">
-        <v>1.220513844134139</v>
+        <v>-2.608695652173913</v>
       </c>
       <c r="BI3" t="n">
-        <v>-1.952160493827162</v>
+        <v>-29304.34782608696</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0</v>
+        <v>-0.03321256038647369</v>
       </c>
       <c r="BK3" t="n">
-        <v>-3.35642630385486</v>
+        <v>-0.2917270531400931</v>
       </c>
       <c r="BL3" t="n">
-        <v>-6.827006172839518</v>
+        <v>0.2244944612613784</v>
       </c>
       <c r="BM3" t="n">
-        <v>3.40909090909091</v>
+        <v>-110.0434782608696</v>
       </c>
       <c r="BN3" t="n">
-        <v>-4669448.302469136</v>
+        <v>-8359.51086956522</v>
       </c>
       <c r="BO3" t="n">
-        <v>489242.4242424238</v>
+        <v>-9.494720496894416</v>
       </c>
       <c r="BP3" t="n">
-        <v>-4.770561403508765</v>
+        <v>-5591.640519046534</v>
       </c>
       <c r="BQ3" t="n">
-        <v>-1411495.030731591</v>
+        <v>-19795652.17391304</v>
       </c>
       <c r="BR3" t="n">
-        <v>-8.963636363636368</v>
+        <v>-3101265.851449277</v>
       </c>
       <c r="BS3" t="n">
-        <v>-355.5555555555566</v>
+        <v>-2.14299516908207</v>
       </c>
       <c r="BT3" t="n">
-        <v>-4.376080246913588</v>
+        <v>-91.60869565217391</v>
       </c>
       <c r="BU3" t="n">
-        <v>5.324242424242414</v>
+        <v>2.911697722567286</v>
       </c>
       <c r="BV3" t="n">
-        <v>-2.836363636363643</v>
+        <v>-4.366156299840526</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>QB1LGiQc</t>
+          <t>Im9H9ezS</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45606.54166666666</v>
+        <v>45618.70833333334</v>
       </c>
       <c r="C4" t="n">
         <v>101</v>
       </c>
       <c r="D4" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E4" t="n">
-        <v>242</v>
+        <v>206</v>
       </c>
       <c r="F4" t="n">
-        <v>133</v>
+        <v>226</v>
       </c>
       <c r="G4" t="n">
         <v>55</v>
@@ -1296,203 +1286,195 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>198</v>
+        <v>40</v>
       </c>
       <c r="M4" t="n">
-        <v>163</v>
+        <v>10</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>0.3290000000000001</v>
+        <v>1.693333333333333</v>
       </c>
       <c r="P4" t="n">
-        <v>0.5506418219461697</v>
+        <v>1.283533834586466</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.05</v>
+        <v>2</v>
       </c>
       <c r="R4" t="n">
-        <v>0.5217391304347828</v>
+        <v>1.365325077399381</v>
       </c>
       <c r="S4" t="n">
-        <v>1.7</v>
+        <v>2.666666666666666</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.964912280701755</v>
       </c>
       <c r="U4" t="n">
-        <v>5.699999999999999</v>
+        <v>4.833333333333334</v>
       </c>
       <c r="V4" t="n">
-        <v>1.565217391304349</v>
+        <v>8.852631578947369</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.2999999999999998</v>
+        <v>0.6666666666666665</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.6956521739130435</v>
+        <v>0.9934210526315788</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.3</v>
+        <v>3</v>
       </c>
       <c r="Z4" t="n">
-        <v>-0.9130434782608696</v>
+        <v>1.365325077399381</v>
       </c>
       <c r="AA4" t="n">
-        <v>17.23355921855922</v>
+        <v>20.54377104377105</v>
       </c>
       <c r="AB4" t="n">
-        <v>21.34939913887282</v>
+        <v>17.78570010105896</v>
       </c>
       <c r="AC4" t="n">
-        <v>830.7288747699315</v>
+        <v>816.5509352246092</v>
       </c>
       <c r="AD4" t="n">
-        <v>885.7396145294296</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>69</v>
-      </c>
+        <v>763.2458916610069</v>
+      </c>
+      <c r="AE4" t="inlineStr"/>
       <c r="AF4" t="n">
-        <v>-14.06190476190476</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>68</v>
-      </c>
+        <v>79.875</v>
+      </c>
+      <c r="AG4" t="inlineStr"/>
       <c r="AH4" t="n">
-        <v>8.302380952380943</v>
+        <v>45.64583333333334</v>
       </c>
       <c r="AI4" t="n">
-        <v>17.9</v>
+        <v>6.333333333333336</v>
       </c>
       <c r="AJ4" t="n">
-        <v>6.478260869565219</v>
+        <v>8.783281733746133</v>
       </c>
       <c r="AK4" t="n">
-        <v>5.700000000000003</v>
+        <v>33</v>
       </c>
       <c r="AL4" t="n">
-        <v>-6.956521739130437</v>
+        <v>36.8280701754386</v>
       </c>
       <c r="AM4" t="n">
-        <v>60.16666666666669</v>
+        <v>272.5</v>
       </c>
       <c r="AN4" t="n">
-        <v>-86.95238095238091</v>
+        <v>390.8970588235293</v>
       </c>
       <c r="AO4" t="n">
-        <v>-0.3499999999999996</v>
+        <v>-2</v>
       </c>
       <c r="AP4" t="n">
-        <v>-1.217391304347826</v>
+        <v>-0.6964285714285712</v>
       </c>
       <c r="AQ4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.2571428571428571</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="AS4" t="n">
-        <v>-5.550000000000001</v>
+        <v>-9.999999999999998</v>
       </c>
       <c r="AT4" t="n">
-        <v>-6.347826086956523</v>
+        <v>-8.588235294117645</v>
       </c>
       <c r="AU4" t="n">
-        <v>-0.8253700912767616</v>
+        <v>8.705217383235954</v>
       </c>
       <c r="AV4" t="n">
-        <v>4.324258497655338</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>0.0669922230538669</v>
-      </c>
+        <v>-7.197875069560236</v>
+      </c>
+      <c r="AW4" t="inlineStr"/>
       <c r="AX4" t="n">
-        <v>0.02671768270724185</v>
+        <v>0.04341819058242329</v>
       </c>
       <c r="AY4" t="n">
-        <v>0.09999999999999998</v>
+        <v>0</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.04347826086956524</v>
+        <v>0.2105263157894737</v>
       </c>
       <c r="BA4" t="n">
-        <v>-1.971858696858675</v>
+        <v>1.788861138861137</v>
       </c>
       <c r="BB4" t="n">
-        <v>-2074.401920123844</v>
+        <v>12.23600982350982</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.035805626598465</v>
+        <v>0.5393518518518476</v>
       </c>
       <c r="BD4" t="n">
-        <v>2.49616368286445</v>
+        <v>8.764969135802474</v>
       </c>
       <c r="BE4" t="n">
-        <v>2.384761703638361</v>
+        <v>44315454.02514152</v>
       </c>
       <c r="BF4" t="n">
-        <v>0.2378760128760129</v>
+        <v>7.994284881784864</v>
       </c>
       <c r="BG4" t="n">
-        <v>1532.313519813519</v>
+        <v>0.8223443223443225</v>
       </c>
       <c r="BH4" t="n">
-        <v>-1.328167913796477</v>
+        <v>4.783882783882784</v>
       </c>
       <c r="BI4" t="n">
-        <v>0.4509962259962279</v>
+        <v>203510.1214574899</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.02823927225855205</v>
+        <v>1.074074074074074</v>
       </c>
       <c r="BK4" t="n">
-        <v>-1.277991196946545</v>
+        <v>12.0804012345679</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.8900876900876824</v>
+        <v>1.011538461538461</v>
       </c>
       <c r="BM4" t="n">
-        <v>-0.4086956521739182</v>
-      </c>
-      <c r="BN4" t="n">
-        <v>3341954.573204573</v>
-      </c>
+        <v>78.77289377289375</v>
+      </c>
+      <c r="BN4" t="inlineStr"/>
       <c r="BO4" t="n">
-        <v>6999552.429667518</v>
+        <v>8.72716727716724</v>
       </c>
       <c r="BP4" t="n">
-        <v>-1.943603022985315</v>
+        <v>76949.79256854256</v>
       </c>
       <c r="BQ4" t="n">
-        <v>543959.1836726898</v>
+        <v>97692032.96703297</v>
       </c>
       <c r="BR4" t="n">
-        <v>155.4526854219949</v>
+        <v>51703290.89506172</v>
       </c>
       <c r="BS4" t="n">
-        <v>26664.70588235294</v>
+        <v>-0.8117283950617491</v>
       </c>
       <c r="BT4" t="n">
-        <v>1.64756632256632</v>
+        <v>87.95970695970698</v>
       </c>
       <c r="BU4" t="n">
-        <v>-4.016837169650472</v>
+        <v>3.71114163614164</v>
       </c>
       <c r="BV4" t="n">
-        <v>139.074168797954</v>
+        <v>3.008787046287068</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>WWnG5RHd</t>
+          <t>xdpX3Q36</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45606.54166666666</v>
+        <v>45618.625</v>
       </c>
       <c r="C5" t="n">
         <v>103</v>
@@ -1501,10 +1483,10 @@
         <v>133</v>
       </c>
       <c r="E5" t="n">
-        <v>573</v>
+        <v>47</v>
       </c>
       <c r="F5" t="n">
-        <v>226</v>
+        <v>133</v>
       </c>
       <c r="G5" t="n">
         <v>55</v>
@@ -1526,213 +1508,207 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>128</v>
+        <v>67</v>
       </c>
       <c r="M5" t="n">
-        <v>10</v>
+        <v>163</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>0.3025</v>
+        <v>1.623333333333333</v>
       </c>
       <c r="P5" t="n">
-        <v>1.179209486166008</v>
+        <v>1.107142857142857</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.2999999999999998</v>
+        <v>2</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9076086956521739</v>
+        <v>1.235294117647059</v>
       </c>
       <c r="S5" t="n">
-        <v>3.95</v>
+        <v>1.5</v>
       </c>
       <c r="T5" t="n">
-        <v>2.521739130434782</v>
+        <v>1.448529411764706</v>
       </c>
       <c r="U5" t="n">
-        <v>3.25</v>
+        <v>10.5</v>
       </c>
       <c r="V5" t="n">
-        <v>7.739130434782608</v>
+        <v>8.97058823529412</v>
       </c>
       <c r="W5" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="X5" t="n">
-        <v>0.6521739130434783</v>
+        <v>0.4632352941176472</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.5217391304347827</v>
+        <v>0.3529411764705883</v>
       </c>
       <c r="AA5" t="n">
-        <v>18.43373556998557</v>
+        <v>14.49264069264069</v>
       </c>
       <c r="AB5" t="n">
-        <v>18.26131678814803</v>
+        <v>16.33503780842225</v>
       </c>
       <c r="AC5" t="n">
-        <v>864.0591706666989</v>
+        <v>732.0561589530495</v>
       </c>
       <c r="AD5" t="n">
-        <v>862.4059338651427</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>-12.5</v>
-      </c>
+        <v>822.5657258801275</v>
+      </c>
+      <c r="AE5" t="inlineStr"/>
       <c r="AF5" t="n">
-        <v>23.40000000000001</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>27.5</v>
-      </c>
+        <v>36.17582417582416</v>
+      </c>
+      <c r="AG5" t="inlineStr"/>
       <c r="AH5" t="n">
-        <v>17.75</v>
+        <v>20.74725274725274</v>
       </c>
       <c r="AI5" t="n">
-        <v>6.649999999999999</v>
+        <v>6.666666666666664</v>
       </c>
       <c r="AJ5" t="n">
-        <v>9.675724637681157</v>
+        <v>6.058823529411775</v>
       </c>
       <c r="AK5" t="n">
-        <v>7.200000000000003</v>
+        <v>11</v>
       </c>
       <c r="AL5" t="n">
-        <v>7.478260869565219</v>
+        <v>12.72058823529412</v>
       </c>
       <c r="AM5" t="n">
-        <v>77.33333333333331</v>
+        <v>169</v>
       </c>
       <c r="AN5" t="n">
-        <v>71.10952380952386</v>
+        <v>114.7142857142858</v>
       </c>
       <c r="AO5" t="n">
-        <v>-0.9000000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AP5" t="n">
-        <v>-1.195652173913043</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>0</v>
-      </c>
+        <v>-0.5</v>
+      </c>
+      <c r="AQ5" t="inlineStr"/>
       <c r="AR5" t="n">
-        <v>0.3333333333333333</v>
+        <v>-0.2000000000000001</v>
       </c>
       <c r="AS5" t="n">
-        <v>-7.800000000000001</v>
+        <v>-0.6666666666666679</v>
       </c>
       <c r="AT5" t="n">
-        <v>-8.710144927536234</v>
+        <v>0.823529411764703</v>
       </c>
       <c r="AU5" t="n">
-        <v>3.448555472162287</v>
+        <v>-5.606633545600937</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.6403947328577217</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>-0.01957237715222068</v>
-      </c>
+        <v>-3.504032569141964</v>
+      </c>
+      <c r="AW5" t="inlineStr"/>
       <c r="AX5" t="n">
-        <v>0.001915949004117602</v>
+        <v>0.01959409448773485</v>
       </c>
       <c r="AY5" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.2989130434782609</v>
+        <v>0.05882352941176469</v>
       </c>
       <c r="BA5" t="n">
-        <v>-3.858525100630345</v>
+        <v>-4.058220326895452</v>
       </c>
       <c r="BB5" t="n">
-        <v>13822.81746031746</v>
+        <v>0.5217620606171209</v>
       </c>
       <c r="BC5" t="n">
-        <v>-1.152597402597403</v>
+        <v>-2.393249805749804</v>
       </c>
       <c r="BD5" t="n">
-        <v>-1.00974025974026</v>
+        <v>5.695516058016068</v>
       </c>
       <c r="BE5" t="n">
-        <v>2.504547919167678</v>
+        <v>6594888.099998033</v>
       </c>
       <c r="BF5" t="n">
-        <v>0.4646103896103899</v>
-      </c>
-      <c r="BG5" t="inlineStr"/>
+        <v>7.271889870742896</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>2.834224598930481</v>
+      </c>
       <c r="BH5" t="n">
-        <v>1.132890356142454</v>
+        <v>4.144385026737968</v>
       </c>
       <c r="BI5" t="n">
-        <v>1.153349282296645</v>
+        <v>145582.8877005348</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.2693025210084035</v>
+        <v>0.2039805102305103</v>
       </c>
       <c r="BK5" t="n">
-        <v>4.941336434573842</v>
+        <v>2.493592981092974</v>
       </c>
       <c r="BL5" t="n">
-        <v>6.07155008733956</v>
+        <v>-0.05254680888177998</v>
       </c>
       <c r="BM5" t="n">
-        <v>-0.8918831168831183</v>
+        <v>242.2807486631016</v>
       </c>
       <c r="BN5" t="n">
-        <v>9091593.424850004</v>
+        <v>24709.39685314685</v>
       </c>
       <c r="BO5" t="n">
-        <v>3012012.987012988</v>
+        <v>-3.257435701553362</v>
       </c>
       <c r="BP5" t="n">
-        <v>1.458622348939542</v>
+        <v>2657.749766573295</v>
       </c>
       <c r="BQ5" t="n">
-        <v>7249853.353841536</v>
+        <v>63966844.91978609</v>
       </c>
       <c r="BR5" t="n">
-        <v>-86.67857142857143</v>
+        <v>11333323.62082362</v>
       </c>
       <c r="BS5" t="n">
-        <v>3421.428571428572</v>
+        <v>-2.510714516964526</v>
       </c>
       <c r="BT5" t="n">
-        <v>3.204241664767963</v>
+        <v>223.2085561497326</v>
       </c>
       <c r="BU5" t="n">
-        <v>1.507792207792221</v>
+        <v>-1.615530303030301</v>
       </c>
       <c r="BV5" t="n">
-        <v>-74.40584415584415</v>
+        <v>-2.578324699069981</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>l8H0Dwy3</t>
+          <t>b59ZhlYj</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45606.45833333334</v>
+        <v>45606.69791666666</v>
       </c>
       <c r="C6" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D6" t="n">
         <v>133</v>
       </c>
       <c r="E6" t="n">
-        <v>535</v>
+        <v>56</v>
       </c>
       <c r="F6" t="n">
-        <v>545</v>
+        <v>362</v>
       </c>
       <c r="G6" t="n">
         <v>55</v>
@@ -1754,215 +1730,195 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>9</v>
+        <v>243</v>
       </c>
       <c r="M6" t="n">
-        <v>138</v>
+        <v>258</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>0.3485</v>
+        <v>3.593333333333333</v>
       </c>
       <c r="P6" t="n">
-        <v>0.7727272727272727</v>
+        <v>0.9219999999999999</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.2999999999999998</v>
+        <v>5</v>
       </c>
       <c r="R6" t="n">
-        <v>1.090909090909091</v>
+        <v>1.073684210526316</v>
       </c>
       <c r="S6" t="n">
-        <v>0.8500000000000001</v>
+        <v>6.333333333333334</v>
       </c>
       <c r="T6" t="n">
-        <v>1.65530303030303</v>
+        <v>0.2833333333333332</v>
       </c>
       <c r="U6" t="n">
-        <v>-5.199999999999999</v>
+        <v>9.666666666666666</v>
       </c>
       <c r="V6" t="n">
-        <v>2.344696969696971</v>
+        <v>-1.683333333333334</v>
       </c>
       <c r="W6" t="n">
-        <v>1.05</v>
+        <v>3.666666666666667</v>
       </c>
       <c r="X6" t="n">
-        <v>0.7424242424242424</v>
+        <v>0.6131578947368423</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.3</v>
+        <v>2</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.8409090909090908</v>
+        <v>1.215789473684211</v>
       </c>
       <c r="AA6" t="n">
-        <v>23.58265660809779</v>
+        <v>18.54498320307144</v>
       </c>
       <c r="AB6" t="n">
-        <v>19.06605241760945</v>
+        <v>23.16284513280837</v>
       </c>
       <c r="AC6" t="n">
-        <v>977.0849657927141</v>
+        <v>812.060312653184</v>
       </c>
       <c r="AD6" t="n">
-        <v>978.986566714329</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>-72</v>
-      </c>
+        <v>901.1340644267209</v>
+      </c>
+      <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="n">
-        <v>-14.68170426065163</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>-44</v>
-      </c>
+        <v>-6.305882352941168</v>
+      </c>
+      <c r="AG6" t="inlineStr"/>
       <c r="AH6" t="n">
-        <v>0.3734335839599012</v>
+        <v>-0.03921568627450966</v>
       </c>
       <c r="AI6" t="n">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.553030303030301</v>
+        <v>2.573684210526316</v>
       </c>
       <c r="AK6" t="n">
-        <v>-26</v>
+        <v>33.33333333333333</v>
       </c>
       <c r="AL6" t="n">
-        <v>-14.48484848484848</v>
+        <v>-1.711111111111109</v>
       </c>
       <c r="AM6" t="n">
-        <v>-323.5</v>
+        <v>66</v>
       </c>
       <c r="AN6" t="n">
-        <v>-140.0366132723112</v>
+        <v>-46.05000000000001</v>
       </c>
       <c r="AO6" t="n">
-        <v>-1.35</v>
+        <v>-2.333333333333333</v>
       </c>
       <c r="AP6" t="n">
-        <v>-0.8142292490118577</v>
+        <v>-0.9333333333333333</v>
       </c>
       <c r="AQ6" t="n">
         <v>0</v>
       </c>
       <c r="AR6" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="AS6" t="n">
-        <v>-4.800000000000001</v>
+        <v>-4.66666666666667</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.151515151515156</v>
+        <v>-8.515789473684208</v>
       </c>
       <c r="AU6" t="n">
-        <v>11.17560581841432</v>
+        <v>20.58333333333333</v>
       </c>
       <c r="AV6" t="n">
-        <v>4.664279349457534</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>-0.009776440490726207</v>
-      </c>
+        <v>4.925892901222976</v>
+      </c>
+      <c r="AW6" t="inlineStr"/>
       <c r="AX6" t="n">
-        <v>-0.01562036321814352</v>
+        <v>0.006674797625643533</v>
       </c>
       <c r="AY6" t="n">
-        <v>-0.15</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0.2462121212121213</v>
+        <v>0.2</v>
       </c>
       <c r="BA6" t="n">
-        <v>3.997585081585072</v>
+        <v>3.156536561389508</v>
       </c>
       <c r="BB6" t="n">
-        <v>2129.66676569618</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>1.352173913043478</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>1.481159420289855</v>
-      </c>
+        <v>9.818788719965184</v>
+      </c>
+      <c r="BC6" t="inlineStr"/>
+      <c r="BD6" t="inlineStr"/>
       <c r="BE6" t="n">
-        <v>0.856154841890131</v>
+        <v>13001399.42893619</v>
       </c>
       <c r="BF6" t="n">
-        <v>-0.001952214452214163</v>
+        <v>5.63681954873131</v>
       </c>
       <c r="BG6" t="n">
-        <v>5308.762626262625</v>
+        <v>-3</v>
       </c>
       <c r="BH6" t="n">
-        <v>-4.11265438809556</v>
+        <v>-1</v>
       </c>
       <c r="BI6" t="n">
-        <v>0.5062373737373775</v>
-      </c>
-      <c r="BJ6" t="n">
-        <v>0.08142375598257923</v>
-      </c>
-      <c r="BK6" t="n">
-        <v>-1.802811796047067</v>
-      </c>
+        <v>44000</v>
+      </c>
+      <c r="BJ6" t="inlineStr"/>
+      <c r="BK6" t="inlineStr"/>
       <c r="BL6" t="n">
-        <v>-0.07284965034965296</v>
+        <v>0.9983333333333335</v>
       </c>
       <c r="BM6" t="n">
-        <v>-2.622222222222224</v>
-      </c>
-      <c r="BN6" t="n">
-        <v>-1592012.305749808</v>
-      </c>
+        <v>-202</v>
+      </c>
+      <c r="BN6" t="inlineStr"/>
       <c r="BO6" t="n">
-        <v>18508260.86956522</v>
+        <v>13.5</v>
       </c>
       <c r="BP6" t="n">
-        <v>0.9629518194224147</v>
+        <v>39433.20801747272</v>
       </c>
       <c r="BQ6" t="n">
-        <v>777765.5768795488</v>
-      </c>
-      <c r="BR6" t="n">
-        <v>110.5869565217391</v>
-      </c>
-      <c r="BS6" t="n">
-        <v>51962.31884057971</v>
-      </c>
+        <v>1425000</v>
+      </c>
+      <c r="BR6" t="inlineStr"/>
+      <c r="BS6" t="inlineStr"/>
       <c r="BT6" t="n">
-        <v>-0.8564071484071434</v>
+        <v>-201</v>
       </c>
       <c r="BU6" t="n">
-        <v>-5.64275362318844</v>
+        <v>5.5</v>
       </c>
       <c r="BV6" t="n">
-        <v>100.9695652173913</v>
+        <v>-3.008203631438903</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>dYK8BH5F</t>
+          <t>nRkUEVfA</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45605.70833333334</v>
+        <v>45606.54166666666</v>
       </c>
       <c r="C7" t="n">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="D7" t="n">
         <v>133</v>
       </c>
       <c r="E7" t="n">
-        <v>431</v>
+        <v>194</v>
       </c>
       <c r="F7" t="n">
-        <v>129</v>
+        <v>579</v>
       </c>
       <c r="G7" t="n">
         <v>55</v>
@@ -1984,213 +1940,207 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>67</v>
+        <v>198</v>
       </c>
       <c r="M7" t="n">
-        <v>83</v>
+        <v>10</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.892</v>
+        <v>-1.455833333333334</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.7069082125603869</v>
+        <v>0.1158088235294119</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.4</v>
+        <v>-0.25</v>
       </c>
       <c r="R7" t="n">
-        <v>-0.7150000000000001</v>
+        <v>0.3235294117647058</v>
       </c>
       <c r="S7" t="n">
-        <v>-7.6</v>
+        <v>-2.333333333333333</v>
       </c>
       <c r="T7" t="n">
-        <v>-3.103333333333334</v>
+        <v>1.238970588235294</v>
       </c>
       <c r="U7" t="n">
-        <v>-12.8</v>
+        <v>-8.916666666666666</v>
       </c>
       <c r="V7" t="n">
-        <v>-3.676666666666668</v>
+        <v>0.4558823529411775</v>
       </c>
       <c r="W7" t="n">
-        <v>-2.4</v>
+        <v>-2.25</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.46</v>
+        <v>-0.1372549019607843</v>
       </c>
       <c r="Y7" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="Z7" t="n">
-        <v>-1.155</v>
+        <v>0.1372549019607845</v>
       </c>
       <c r="AA7" t="n">
-        <v>23.35406593406594</v>
+        <v>25.82774725274725</v>
       </c>
       <c r="AB7" t="n">
-        <v>21.95796322088214</v>
+        <v>21.30585665787032</v>
       </c>
       <c r="AC7" t="n">
-        <v>1421.044829125362</v>
+        <v>933.2350357380922</v>
       </c>
       <c r="AD7" t="n">
-        <v>1106.948187644967</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>-22.5</v>
-      </c>
+        <v>923.4714813019541</v>
+      </c>
+      <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="n">
-        <v>-21.38095238095238</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>23.5</v>
-      </c>
+        <v>-5.054945054945065</v>
+      </c>
+      <c r="AG7" t="inlineStr"/>
       <c r="AH7" t="n">
-        <v>4.746753246753237</v>
+        <v>9.054945054945058</v>
       </c>
       <c r="AI7" t="n">
-        <v>-4.800000000000001</v>
+        <v>-6.083333333333332</v>
       </c>
       <c r="AJ7" t="n">
-        <v>-0.8716666666666679</v>
+        <v>-0.6797385620915009</v>
       </c>
       <c r="AK7" t="n">
-        <v>-45.2</v>
+        <v>-25.33333333333333</v>
       </c>
       <c r="AL7" t="n">
-        <v>-30.8</v>
+        <v>-8.852941176470594</v>
       </c>
       <c r="AM7" t="n">
-        <v>-777</v>
+        <v>-230</v>
       </c>
       <c r="AN7" t="n">
-        <v>-342.9718614718615</v>
+        <v>-115.2952380952381</v>
       </c>
       <c r="AO7" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>-0.9166666666666665</v>
       </c>
       <c r="AP7" t="n">
-        <v>-0.8577075098814233</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>0</v>
-      </c>
+        <v>-0.2058823529411766</v>
+      </c>
+      <c r="AQ7" t="inlineStr"/>
       <c r="AR7" t="n">
-        <v>-0.8</v>
+        <v>-2</v>
       </c>
       <c r="AS7" t="n">
-        <v>-3.800000000000001</v>
+        <v>-0.9166666666666643</v>
       </c>
       <c r="AT7" t="n">
-        <v>0.3099999999999952</v>
+        <v>0.764705882352942</v>
       </c>
       <c r="AU7" t="n">
-        <v>42.99420164995823</v>
+        <v>0.005719663824987009</v>
       </c>
       <c r="AV7" t="n">
-        <v>11.08970000702708</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>0.1198904288711784</v>
-      </c>
+        <v>1.05064835128484</v>
+      </c>
+      <c r="AW7" t="inlineStr"/>
       <c r="AX7" t="n">
-        <v>0.04755094145069037</v>
+        <v>-0.01185013876783483</v>
       </c>
       <c r="AY7" t="n">
-        <v>-0.4</v>
+        <v>-0.08333333333333331</v>
       </c>
       <c r="AZ7" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.1830065359477124</v>
       </c>
       <c r="BA7" t="n">
-        <v>-1.484647550776572</v>
-      </c>
-      <c r="BB7" t="inlineStr"/>
+        <v>1.220513844134139</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>-3.35642630385486</v>
+      </c>
       <c r="BC7" t="n">
-        <v>0.2538461538461538</v>
+        <v>-1.952160493827162</v>
       </c>
       <c r="BD7" t="n">
-        <v>-3.707692307692307</v>
+        <v>-4.376080246913588</v>
       </c>
       <c r="BE7" t="n">
-        <v>-13.97346036803287</v>
+        <v>-1411495.030731591</v>
       </c>
       <c r="BF7" t="n">
-        <v>-1.074074074074074</v>
+        <v>-3.064365019692104</v>
       </c>
       <c r="BG7" t="n">
-        <v>-80543.64095500459</v>
+        <v>-0.03939393939393931</v>
       </c>
       <c r="BH7" t="n">
-        <v>1.343281179604713</v>
+        <v>-0.1303030303030301</v>
       </c>
       <c r="BI7" t="n">
-        <v>4.465588682524167</v>
+        <v>-355.5555555555566</v>
       </c>
       <c r="BJ7" t="n">
-        <v>-1.011538461538461</v>
+        <v>-0.125</v>
       </c>
       <c r="BK7" t="n">
-        <v>-14.82630979968759</v>
+        <v>-6.827006172839518</v>
       </c>
       <c r="BL7" t="n">
-        <v>-12.11103508200283</v>
+        <v>0</v>
       </c>
       <c r="BM7" t="n">
-        <v>-3.014871794871798</v>
+        <v>-8.963636363636368</v>
       </c>
       <c r="BN7" t="n">
-        <v>-54019373.57445422</v>
+        <v>-11514.5202020202</v>
       </c>
       <c r="BO7" t="n">
-        <v>-104358461.5384615</v>
+        <v>5.324242424242414</v>
       </c>
       <c r="BP7" t="n">
-        <v>-2.240044783495648</v>
+        <v>-6580.820105820106</v>
       </c>
       <c r="BQ7" t="n">
-        <v>-46200713.52752107</v>
+        <v>489242.4242424238</v>
       </c>
       <c r="BR7" t="n">
-        <v>-15.25384615384615</v>
+        <v>-4669448.302469136</v>
       </c>
       <c r="BS7" t="n">
-        <v>-229615.3846153846</v>
+        <v>1.484413580246866</v>
       </c>
       <c r="BT7" t="n">
-        <v>-14.69157977625721</v>
+        <v>-2.836363636363643</v>
       </c>
       <c r="BU7" t="n">
-        <v>-8.104230769230725</v>
+        <v>3.40909090909091</v>
       </c>
       <c r="BV7" t="n">
-        <v>-29.46923076923076</v>
+        <v>-4.770561403508765</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>bJl87mmp</t>
+          <t>QB1LGiQc</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45605.625</v>
+        <v>45606.54166666666</v>
       </c>
       <c r="C8" t="n">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D8" t="n">
+        <v>134</v>
+      </c>
+      <c r="E8" t="n">
+        <v>242</v>
+      </c>
+      <c r="F8" t="n">
         <v>133</v>
-      </c>
-      <c r="E8" t="n">
-        <v>273</v>
-      </c>
-      <c r="F8" t="n">
-        <v>599</v>
       </c>
       <c r="G8" t="n">
         <v>55</v>
@@ -2212,213 +2162,207 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>40</v>
+        <v>198</v>
       </c>
       <c r="M8" t="n">
-        <v>258</v>
+        <v>163</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>0.8869999999999999</v>
+        <v>-0.0833333333333337</v>
       </c>
       <c r="P8" t="n">
-        <v>0.8586363636363631</v>
+        <v>0.3862222222222227</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.339920948616601</v>
+        <v>0.3529411764705883</v>
       </c>
       <c r="S8" t="n">
-        <v>3.35</v>
+        <v>-1.666666666666667</v>
       </c>
       <c r="T8" t="n">
-        <v>2.818181818181818</v>
+        <v>-0.1307189542483664</v>
       </c>
       <c r="U8" t="n">
-        <v>6.550000000000001</v>
+        <v>3.666666666666668</v>
       </c>
       <c r="V8" t="n">
-        <v>7.727272727272728</v>
+        <v>2.075163398692812</v>
       </c>
       <c r="W8" t="n">
-        <v>0.3999999999999999</v>
+        <v>-1</v>
       </c>
       <c r="X8" t="n">
-        <v>0.8418972332015811</v>
+        <v>-1.124183006535948</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.6000000000000001</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.806324110671937</v>
+        <v>-1.362745098039216</v>
       </c>
       <c r="AA8" t="n">
-        <v>16.48176958662253</v>
+        <v>18.36801716801717</v>
       </c>
       <c r="AB8" t="n">
-        <v>17.00419120599734</v>
+        <v>20.40126848913614</v>
       </c>
       <c r="AC8" t="n">
-        <v>815.0452012804587</v>
+        <v>839.5656575038066</v>
       </c>
       <c r="AD8" t="n">
-        <v>832.2974715939531</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>64</v>
-      </c>
+        <v>895.5550622794528</v>
+      </c>
+      <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="n">
-        <v>51.34999999999999</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>34.5</v>
-      </c>
+        <v>-9.533333333333331</v>
+      </c>
+      <c r="AG8" t="inlineStr"/>
       <c r="AH8" t="n">
-        <v>34.72631578947369</v>
+        <v>13.33333333333333</v>
       </c>
       <c r="AI8" t="n">
-        <v>7.699999999999996</v>
+        <v>18.66666666666666</v>
       </c>
       <c r="AJ8" t="n">
-        <v>12.01185770750988</v>
+        <v>9.068627450980394</v>
       </c>
       <c r="AK8" t="n">
-        <v>22.59999999999999</v>
+        <v>-0.6666666666666714</v>
       </c>
       <c r="AL8" t="n">
-        <v>17.09090909090908</v>
+        <v>-5.960784313725497</v>
       </c>
       <c r="AM8" t="n">
-        <v>129</v>
+        <v>67</v>
       </c>
       <c r="AN8" t="n">
-        <v>141.0184210526315</v>
+        <v>-82.5625</v>
       </c>
       <c r="AO8" t="n">
-        <v>-1.4</v>
+        <v>-0.6666666666666665</v>
       </c>
       <c r="AP8" t="n">
-        <v>-1.014285714285715</v>
+        <v>-0.7287581699346406</v>
       </c>
       <c r="AQ8" t="inlineStr"/>
       <c r="AR8" t="n">
-        <v>1.75</v>
+        <v>0.4</v>
       </c>
       <c r="AS8" t="n">
-        <v>5</v>
+        <v>-7.666666666666668</v>
       </c>
       <c r="AT8" t="n">
-        <v>-7.418972332015805</v>
+        <v>-6.290849673202615</v>
       </c>
       <c r="AU8" t="n">
-        <v>-11.14393398268399</v>
+        <v>0.4400632825076194</v>
       </c>
       <c r="AV8" t="n">
-        <v>-0.5934227381620616</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>0.02891066469338704</v>
-      </c>
+        <v>3.941938222686005</v>
+      </c>
+      <c r="AW8" t="inlineStr"/>
       <c r="AX8" t="n">
-        <v>0.0232806081644242</v>
+        <v>0.04461149471289846</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.2</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.3122529644268776</v>
+        <v>-0.173202614379085</v>
       </c>
       <c r="BA8" t="n">
-        <v>-2.612134971510017</v>
+        <v>-1.328167913796477</v>
       </c>
       <c r="BB8" t="n">
-        <v>6017.731570662192</v>
+        <v>-1.277991196946545</v>
       </c>
       <c r="BC8" t="n">
-        <v>0.3152173913043477</v>
+        <v>0.4509962259962279</v>
       </c>
       <c r="BD8" t="n">
-        <v>-0.1648550724637681</v>
+        <v>1.64756632256632</v>
       </c>
       <c r="BE8" t="n">
-        <v>0.5799471561134339</v>
+        <v>543959.1836726898</v>
       </c>
       <c r="BF8" t="n">
-        <v>-0.2968304843304845</v>
+        <v>2.384761703638361</v>
       </c>
       <c r="BG8" t="n">
-        <v>6687.499999999996</v>
+        <v>2.035805626598465</v>
       </c>
       <c r="BH8" t="n">
-        <v>2.241550813620186</v>
+        <v>2.49616368286445</v>
       </c>
       <c r="BI8" t="n">
-        <v>0.3604967948717963</v>
+        <v>26664.70588235294</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.1862407927001228</v>
+        <v>0.2378760128760129</v>
       </c>
       <c r="BK8" t="n">
-        <v>3.892943141388116</v>
+        <v>0.8900876900876824</v>
       </c>
       <c r="BL8" t="n">
-        <v>3.330484330484339</v>
+        <v>0.02823927225855205</v>
       </c>
       <c r="BM8" t="n">
-        <v>2.553511042097998</v>
+        <v>155.4526854219949</v>
       </c>
       <c r="BN8" t="n">
-        <v>6202021.901709399</v>
+        <v>1532.313519813519</v>
       </c>
       <c r="BO8" t="n">
-        <v>3163405.797101451</v>
+        <v>-4.016837169650472</v>
       </c>
       <c r="BP8" t="n">
-        <v>-4.066768946762949</v>
+        <v>-2074.401920123844</v>
       </c>
       <c r="BQ8" t="n">
-        <v>1947318.169420293</v>
+        <v>6999552.429667518</v>
       </c>
       <c r="BR8" t="n">
-        <v>26.51449275362319</v>
+        <v>3341954.573204573</v>
       </c>
       <c r="BS8" t="n">
-        <v>9038.043478260872</v>
+        <v>-1.971858696858675</v>
       </c>
       <c r="BT8" t="n">
-        <v>2.624528133903127</v>
+        <v>139.074168797954</v>
       </c>
       <c r="BU8" t="n">
-        <v>-4.255387336093861</v>
+        <v>-0.4086956521739182</v>
       </c>
       <c r="BV8" t="n">
-        <v>27.95471014492753</v>
+        <v>-1.943603022985315</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>figxD9PM</t>
+          <t>WWnG5RHd</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45605.54166666666</v>
+        <v>45606.54166666666</v>
       </c>
       <c r="C9" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D9" t="n">
         <v>133</v>
       </c>
       <c r="E9" t="n">
-        <v>736</v>
+        <v>573</v>
       </c>
       <c r="F9" t="n">
-        <v>33</v>
+        <v>226</v>
       </c>
       <c r="G9" t="n">
         <v>55</v>
@@ -2440,213 +2384,207 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>272</v>
+        <v>128</v>
       </c>
       <c r="M9" t="n">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.2625</v>
+        <v>0.1224999999999999</v>
       </c>
       <c r="P9" t="n">
-        <v>0.002608695652173143</v>
+        <v>0.7667916666666666</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.1500000000000001</v>
+        <v>-0.5</v>
       </c>
       <c r="R9" t="n">
-        <v>0.3967391304347826</v>
+        <v>0.2205882352941175</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1938405797101455</v>
+        <v>2.125</v>
       </c>
       <c r="U9" t="n">
+        <v>4</v>
+      </c>
+      <c r="V9" t="n">
+        <v>5.125</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0.4558823529411766</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0.3970588235294119</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>15.70002405002405</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>19.40410253016677</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>842.0533249458113</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>853.734544318015</v>
+      </c>
+      <c r="AE9" t="inlineStr"/>
+      <c r="AF9" t="n">
+        <v>20.07692307692307</v>
+      </c>
+      <c r="AG9" t="inlineStr"/>
+      <c r="AH9" t="n">
+        <v>13</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>6.882352941176471</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>6.333333333333329</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>5.875</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>114.5</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>65.15384615384613</v>
+      </c>
+      <c r="AO9" t="n">
         <v>-2</v>
       </c>
-      <c r="V9" t="n">
-        <v>0.304347826086957</v>
-      </c>
-      <c r="W9" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="X9" t="n">
-        <v>-0.4474637681159421</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>0.3000000000000003</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>-0.7282608695652173</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>19.04541190835308</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>20.28545924190426</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>960.5680747456265</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>972.1835593333678</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>-49.5</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>-22.86363636363636</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>-21.5</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>-0.5909090909090864</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>1.099999999999994</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>-1.018115942028984</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>-19.3</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>-17.65217391304348</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>-151</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>-168.6863636363636</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>-0.9500000000000002</v>
-      </c>
       <c r="AP9" t="n">
-        <v>-0.9999999999999998</v>
-      </c>
-      <c r="AQ9" t="inlineStr"/>
+        <v>-0.8958333333333333</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>0</v>
+      </c>
       <c r="AR9" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AS9" t="n">
-        <v>-1.4</v>
+        <v>-4.416666666666668</v>
       </c>
       <c r="AT9" t="n">
-        <v>-0.911231884057969</v>
+        <v>-7.897058823529413</v>
       </c>
       <c r="AU9" t="n">
-        <v>13.34281458752283</v>
+        <v>-0.9897441911373761</v>
       </c>
       <c r="AV9" t="n">
-        <v>6.083197539112042</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>-0.05207654868671815</v>
-      </c>
+        <v>-0.2057092003774734</v>
+      </c>
+      <c r="AW9" t="inlineStr"/>
       <c r="AX9" t="n">
-        <v>0.01372764796662495</v>
+        <v>0.003321177859312657</v>
       </c>
       <c r="AY9" t="n">
-        <v>-0.3</v>
+        <v>0.5</v>
       </c>
       <c r="AZ9" t="n">
-        <v>-0.1666666666666667</v>
+        <v>0.3713235294117647</v>
       </c>
       <c r="BA9" t="n">
-        <v>3.914675925925962</v>
+        <v>1.039840327156497</v>
       </c>
       <c r="BB9" t="n">
-        <v>-4859.487734487735</v>
+        <v>4.779521071249007</v>
       </c>
       <c r="BC9" t="n">
-        <v>-2.059288537549407</v>
+        <v>1.184638047138041</v>
       </c>
       <c r="BD9" t="n">
-        <v>-2.039525691699605</v>
+        <v>3.236012906846227</v>
       </c>
       <c r="BE9" t="n">
-        <v>-4.421112316857929</v>
+        <v>7204388.983157365</v>
       </c>
       <c r="BF9" t="n">
-        <v>-0.1380092592592592</v>
+        <v>2.565736102133158</v>
       </c>
       <c r="BG9" t="n">
-        <v>-27074.21296296296</v>
+        <v>-1.523809523809524</v>
       </c>
       <c r="BH9" t="n">
-        <v>3.226187005002796</v>
+        <v>-1.523809523809524</v>
       </c>
       <c r="BI9" t="n">
-        <v>-0.06916666666666771</v>
+        <v>-12105.26315789474</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.1461315049472944</v>
+        <v>0.4632996632996635</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.1080145017425735</v>
+        <v>6.154980359147032</v>
       </c>
       <c r="BL9" t="n">
-        <v>-3.962129629629615</v>
+        <v>0.2686186974789917</v>
       </c>
       <c r="BM9" t="n">
-        <v>1.760457839262187</v>
-      </c>
-      <c r="BN9" t="n">
-        <v>-10371972.22222222</v>
-      </c>
+        <v>-119.3809523809524</v>
+      </c>
+      <c r="BN9" t="inlineStr"/>
       <c r="BO9" t="n">
-        <v>-60346640.31620553</v>
+        <v>7.774603174603158</v>
       </c>
       <c r="BP9" t="n">
-        <v>3.541318441142977</v>
+        <v>13822.81746031746</v>
       </c>
       <c r="BQ9" t="n">
-        <v>-5787876.099128295</v>
+        <v>-7821428.571428571</v>
       </c>
       <c r="BR9" t="n">
-        <v>-184.5237154150198</v>
+        <v>9101203.352974188</v>
       </c>
       <c r="BS9" t="n">
-        <v>-125644.2687747036</v>
+        <v>-3.779741863075202</v>
       </c>
       <c r="BT9" t="n">
-        <v>-3.018425925925939</v>
+        <v>-103.8095238095238</v>
       </c>
       <c r="BU9" t="n">
-        <v>4.827555053642016</v>
+        <v>-1.958730158730159</v>
       </c>
       <c r="BV9" t="n">
-        <v>-168.3083003952569</v>
+        <v>1.314882074624762</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Gp6AbAAT</t>
+          <t>l8H0Dwy3</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45604.69791666666</v>
+        <v>45606.45833333334</v>
       </c>
       <c r="C10" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D10" t="n">
         <v>133</v>
       </c>
       <c r="E10" t="n">
-        <v>448</v>
+        <v>535</v>
       </c>
       <c r="F10" t="n">
-        <v>228</v>
+        <v>545</v>
       </c>
       <c r="G10" t="n">
         <v>55</v>
@@ -2668,191 +2606,1077 @@
         </is>
       </c>
       <c r="L10" t="n">
+        <v>9</v>
+      </c>
+      <c r="M10" t="n">
+        <v>138</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.8516666666666668</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0.8468382352941179</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.3125</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.416666666666667</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.298611111111111</v>
+      </c>
+      <c r="U10" t="n">
+        <v>-0.08333333333333215</v>
+      </c>
+      <c r="V10" t="n">
+        <v>2.513888888888888</v>
+      </c>
+      <c r="W10" t="n">
+        <v>2</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0.6597222222222222</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0.6041666666666667</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>21.43512223071047</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>19.61432882338791</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>937.4240847245117</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>973.9187024677365</v>
+      </c>
+      <c r="AE10" t="inlineStr"/>
+      <c r="AF10" t="n">
+        <v>-4.871794871794876</v>
+      </c>
+      <c r="AG10" t="inlineStr"/>
+      <c r="AH10" t="n">
+        <v>4.625641025641023</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>1.875</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>-26.66666666666667</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>-14.88888888888889</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>-258</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>-140.7104072398189</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>-2.416666666666667</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>-0.4722222222222221</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>-0.5833333333333321</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>4.652777777777779</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>10.67658212560387</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>3.291987468309244</v>
+      </c>
+      <c r="AW10" t="inlineStr"/>
+      <c r="AX10" t="n">
+        <v>-0.003490671033628913</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>0.08333333333333331</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>0.2152777777777778</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>-3.893524351465526</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>-1.773787055355669</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>0.5072828282828326</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>-0.8538282828282746</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>609458.2723014113</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>0.6149314048333565</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>1.652173913043478</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>0.347826086956522</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>40695.65217391304</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>-4.040404040384082e-05</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>-0.06856565656566715</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>0.07638851344733655</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>138.0869565217391</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>5308.762626262625</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>-13.02608695652177</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>2180.857241886657</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>25178260.86956522</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>-1581755.303030305</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>4.018161616161592</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>122.8695652173913</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>-8.333333333333332</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>0.6477676517382633</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>dYK8BH5F</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45605.70833333334</v>
+      </c>
+      <c r="C11" t="n">
+        <v>104</v>
+      </c>
+      <c r="D11" t="n">
+        <v>133</v>
+      </c>
+      <c r="E11" t="n">
+        <v>431</v>
+      </c>
+      <c r="F11" t="n">
+        <v>129</v>
+      </c>
+      <c r="G11" t="n">
+        <v>55</v>
+      </c>
+      <c r="H11" t="n">
+        <v>551</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>67</v>
+      </c>
+      <c r="M11" t="n">
+        <v>83</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>-1.573333333333334</v>
+      </c>
+      <c r="P11" t="n">
+        <v>-0.5611764705882354</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="R11" t="n">
+        <v>-0.4551083591331269</v>
+      </c>
+      <c r="S11" t="n">
+        <v>-8</v>
+      </c>
+      <c r="T11" t="n">
+        <v>-3.767801857585139</v>
+      </c>
+      <c r="U11" t="n">
+        <v>-15.33333333333333</v>
+      </c>
+      <c r="V11" t="n">
+        <v>-4.659442724458206</v>
+      </c>
+      <c r="W11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X11" t="n">
+        <v>-1.987616099071208</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>-1.662538699690402</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>27.57582417582417</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>21.63191196917977</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1442.054681959355</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1124.808641832703</v>
+      </c>
+      <c r="AE11" t="inlineStr"/>
+      <c r="AF11" t="n">
+        <v>-21.52678571428572</v>
+      </c>
+      <c r="AG11" t="inlineStr"/>
+      <c r="AH11" t="n">
+        <v>3.044642857142861</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>-6.666666666666668</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>-3.009287925696595</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>-52.66666666666667</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>-32.95356037151703</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>-776</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>-369.1785714285714</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>-2.333333333333334</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>-1.0625</v>
+      </c>
+      <c r="AQ11" t="inlineStr"/>
+      <c r="AR11" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>-7.999999999999998</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>-0.01238390092879271</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>62.96041666666666</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>12.15054799346603</v>
+      </c>
+      <c r="AW11" t="inlineStr"/>
+      <c r="AX11" t="n">
+        <v>0.05947993307211154</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>-0.3333333333333333</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>-0.3095975232198143</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>1.343281179604713</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>-14.82630979968759</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>4.465588682524167</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>-14.69157977625721</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>-46200713.52752107</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>-13.97346036803287</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>1.653846153846154</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>-2.307692307692307</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>-229615.3846153846</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>-1.074074074074074</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>-12.11103508200283</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>-1.011538461538461</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>82.84615384615387</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>-80543.64095500459</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>-5.552564102564077</v>
+      </c>
+      <c r="BP11" t="inlineStr"/>
+      <c r="BQ11" t="n">
+        <v>-102613461.5384615</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>-54019373.57445422</v>
+      </c>
+      <c r="BS11" t="n">
+        <v>-1.484647550776572</v>
+      </c>
+      <c r="BT11" t="n">
+        <v>66.23076923076923</v>
+      </c>
+      <c r="BU11" t="n">
+        <v>-0.8698717948717984</v>
+      </c>
+      <c r="BV11" t="n">
+        <v>-2.240044783495648</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>bJl87mmp</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45605.625</v>
+      </c>
+      <c r="C12" t="n">
+        <v>103</v>
+      </c>
+      <c r="D12" t="n">
+        <v>133</v>
+      </c>
+      <c r="E12" t="n">
+        <v>273</v>
+      </c>
+      <c r="F12" t="n">
+        <v>599</v>
+      </c>
+      <c r="G12" t="n">
+        <v>55</v>
+      </c>
+      <c r="H12" t="n">
+        <v>551</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>40</v>
+      </c>
+      <c r="M12" t="n">
+        <v>258</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0.7974999999999997</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.455882352941177</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0.9999999999999996</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.125</v>
+      </c>
+      <c r="U12" t="n">
+        <v>4.333333333333332</v>
+      </c>
+      <c r="V12" t="n">
+        <v>6.125</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0.6666666666666669</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0.3639705882352942</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>17.78020400079224</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>16.96970434595289</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>828.0477312770033</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>833.5173730538138</v>
+      </c>
+      <c r="AE12" t="inlineStr"/>
+      <c r="AF12" t="n">
+        <v>47.52197802197801</v>
+      </c>
+      <c r="AG12" t="inlineStr"/>
+      <c r="AH12" t="n">
+        <v>29.12087912087912</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>-4.333333333333336</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>12.00735294117647</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>19.33333333333333</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>18.875</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>100</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>160.7637362637362</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>-1.166666666666667</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>-1.016666666666667</v>
+      </c>
+      <c r="AQ12" t="inlineStr"/>
+      <c r="AR12" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>3.333333333333329</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>-6.518382352941178</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>-3.267153679653685</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>-1.946201504871668</v>
+      </c>
+      <c r="AW12" t="inlineStr"/>
+      <c r="AX12" t="n">
+        <v>0.03706879697187559</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>-5.551115123125783e-17</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>0.3051470588235294</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>2.236046430595298</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>3.912788506397519</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>0.3162942834138498</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>2.619424315619966</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>1858414.952998129</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>0.6143664084453633</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>43000</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>-0.3028884863123997</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>3.35526368760064</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>0.1894404676359562</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>8</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>6572.532781228427</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>3</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>5716.115613709597</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>15200000</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>6185597.574476648</v>
+      </c>
+      <c r="BS12" t="n">
+        <v>-2.855958132045089</v>
+      </c>
+      <c r="BT12" t="n">
+        <v>7</v>
+      </c>
+      <c r="BU12" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BV12" t="n">
+        <v>-3.983780619964818</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>figxD9PM</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45605.54166666666</v>
+      </c>
+      <c r="C13" t="n">
+        <v>102</v>
+      </c>
+      <c r="D13" t="n">
+        <v>133</v>
+      </c>
+      <c r="E13" t="n">
+        <v>736</v>
+      </c>
+      <c r="F13" t="n">
+        <v>33</v>
+      </c>
+      <c r="G13" t="n">
+        <v>55</v>
+      </c>
+      <c r="H13" t="n">
+        <v>551</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>272</v>
+      </c>
+      <c r="M13" t="n">
+        <v>32</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.5100000000000001</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0.1464705882352939</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0.5294117647058825</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.916666666666667</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0.9967320261437913</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="V13" t="n">
+        <v>3.153594771241831</v>
+      </c>
+      <c r="W13" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="X13" t="n">
+        <v>-0.5392156862745099</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-0.7941176470588236</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>17.5893256661639</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>18.81615630556807</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>960.5680747456265</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>944.0294613736537</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>10</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>-13.91964285714286</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>6.3125</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>5.083333333333336</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1.019607843137251</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>-17.83333333333333</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>-13.50326797385621</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>-151</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>-119.375</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>-0.4166666666666665</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>-0.7058823529411766</v>
+      </c>
+      <c r="AQ13" t="inlineStr"/>
+      <c r="AR13" t="n">
+        <v>-1.333333333333333</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>1.083333333333332</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>-0.1895424836601265</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>13.34281458752283</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>4.387524286864782</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>0.04841824841824842</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>0.02664562876142698</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>-0.08333333333333331</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>-0.2777777777777778</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>3.226187005002796</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>0.1080145017425735</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>-0.06916666666666771</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>-3.018425925925939</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>-5787876.099128295</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>-4.421112316857929</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>0.3043478260869565</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>0.8695652173913042</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>-132826.0869565217</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>-0.1380092592592592</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>-3.962129629629615</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>0.1461315049472944</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>5.521739130434781</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>-27074.21296296296</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>-0.1847826086956559</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>-4859.487734487735</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>-47473913.04347827</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>-10371972.22222222</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>3.914675925925962</v>
+      </c>
+      <c r="BT13" t="n">
+        <v>6.782608695652186</v>
+      </c>
+      <c r="BU13" t="n">
+        <v>1.394927536231886</v>
+      </c>
+      <c r="BV13" t="n">
+        <v>3.541318441142977</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>Gp6AbAAT</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45604.69791666666</v>
+      </c>
+      <c r="C14" t="n">
+        <v>102</v>
+      </c>
+      <c r="D14" t="n">
+        <v>133</v>
+      </c>
+      <c r="E14" t="n">
+        <v>448</v>
+      </c>
+      <c r="F14" t="n">
+        <v>228</v>
+      </c>
+      <c r="G14" t="n">
+        <v>55</v>
+      </c>
+      <c r="H14" t="n">
+        <v>551</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
         <v>168</v>
       </c>
-      <c r="M10" t="n">
+      <c r="M14" t="n">
         <v>211</v>
       </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0.7950000000000002</v>
-      </c>
-      <c r="P10" t="n">
-        <v>1.140802005012531</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.333333333333333</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3.100000000000001</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.049523809523809</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0.9000000000000004</v>
-      </c>
-      <c r="V10" t="n">
-        <v>2.04952380952381</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X10" t="n">
-        <v>0.5502645502645503</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>1.063492063492063</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>20.43316995504495</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>20.32532863432863</v>
-      </c>
-      <c r="AC10" t="n">
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.0166666666666665</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.118263888888889</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.575</v>
+      </c>
+      <c r="S14" t="n">
+        <v>4.440892098500626e-16</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.590277777777778</v>
+      </c>
+      <c r="U14" t="n">
+        <v>-3.333333333333332</v>
+      </c>
+      <c r="V14" t="n">
+        <v>2.166666666666666</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0.6666666666666665</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0.6875</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>1.275</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>22.15613553113553</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>19.87436947697364</v>
+      </c>
+      <c r="AC14" t="n">
         <v>903.0457789515091</v>
       </c>
-      <c r="AD10" t="n">
-        <v>913.5067732684679</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>-23</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>-5.84210526315789</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>7.511961722488039</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>8.25</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>5.132275132275128</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>-1.154285714285706</v>
-      </c>
-      <c r="AM10" t="n">
+      <c r="AD14" t="n">
+        <v>922.9898015267552</v>
+      </c>
+      <c r="AE14" t="inlineStr"/>
+      <c r="AF14" t="n">
+        <v>-8.85238095238094</v>
+      </c>
+      <c r="AG14" t="inlineStr"/>
+      <c r="AH14" t="n">
+        <v>9.176190476190477</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>6.333333333333336</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>4.700000000000001</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>10</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>0.05555555555555713</v>
+      </c>
+      <c r="AM14" t="n">
         <v>-14.5</v>
       </c>
-      <c r="AN10" t="n">
-        <v>-51.53884711779443</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>-0.7559523809523809</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>-0.3333333333333333</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>-0.8333333333333334</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>-1.049999999999999</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>1.74074074074074</v>
-      </c>
-      <c r="AU10" t="n">
+      <c r="AN14" t="n">
+        <v>-61.14285714285717</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>-0.8419117647058825</v>
+      </c>
+      <c r="AQ14" t="inlineStr"/>
+      <c r="AR14" t="n">
+        <v>-0.875</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>-0.3333333333333321</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>3.949999999999999</v>
+      </c>
+      <c r="AU14" t="n">
         <v>-2.34494047619048</v>
       </c>
-      <c r="AV10" t="n">
-        <v>0.5925353699102658</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>-0.08943771594172323</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>-0.01258518504703823</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>0.1904761904761905</v>
-      </c>
-      <c r="BA10" t="n">
+      <c r="AV14" t="n">
+        <v>-0.3563265683653878</v>
+      </c>
+      <c r="AW14" t="inlineStr"/>
+      <c r="AX14" t="n">
+        <v>-0.01620820239068646</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>0.175</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>0.5634825158133445</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>9.706325445648744</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>-0.8208050330895134</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>9.884371734587262</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>9153044.356019918</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>8.342483318686334</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>-4</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>-4</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>-3000</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>0.1805555555555556</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>8.707919714385227</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>0.1812987012987013</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>-282</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>33062.08721833721</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>-0.8000000000000114</v>
+      </c>
+      <c r="BP14" t="inlineStr"/>
+      <c r="BQ14" t="n">
+        <v>-6250000</v>
+      </c>
+      <c r="BR14" t="n">
+        <v>14139000.18504006</v>
+      </c>
+      <c r="BS14" t="n">
         <v>1.128178335074864</v>
       </c>
-      <c r="BB10" t="inlineStr"/>
-      <c r="BC10" t="n">
-        <v>1.266666666666667</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>2.475</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>8.342483318686334</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>0.1805555555555556</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>33062.08721833721</v>
-      </c>
-      <c r="BH10" t="n">
-        <v>0.5634825158133445</v>
-      </c>
-      <c r="BI10" t="n">
-        <v>-0.8208050330895134</v>
-      </c>
-      <c r="BJ10" t="n">
-        <v>0.1812987012987013</v>
-      </c>
-      <c r="BK10" t="n">
-        <v>9.706325445648744</v>
-      </c>
-      <c r="BL10" t="n">
-        <v>8.707919714385227</v>
-      </c>
-      <c r="BM10" t="n">
-        <v>0.6540277777777774</v>
-      </c>
-      <c r="BN10" t="n">
-        <v>14139000.18504006</v>
-      </c>
-      <c r="BO10" t="n">
-        <v>35238333.33333334</v>
-      </c>
-      <c r="BP10" t="n">
+      <c r="BT14" t="n">
+        <v>-266</v>
+      </c>
+      <c r="BU14" t="n">
+        <v>-6</v>
+      </c>
+      <c r="BV14" t="n">
         <v>1.406234091722837</v>
-      </c>
-      <c r="BQ10" t="n">
-        <v>9153044.356019918</v>
-      </c>
-      <c r="BR10" t="n">
-        <v>105.025</v>
-      </c>
-      <c r="BS10" t="n">
-        <v>90916.66666666667</v>
-      </c>
-      <c r="BT10" t="n">
-        <v>9.884371734587262</v>
-      </c>
-      <c r="BU10" t="n">
-        <v>-1.958888888888879</v>
-      </c>
-      <c r="BV10" t="n">
-        <v>104.675</v>
       </c>
     </row>
   </sheetData>
